--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -575,16 +575,17 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B3" s="13" t="d">
-        <v>2026-10-31T00:00:00.000Z</v>
+        <v>2026-10-15T00:00:00.000Z</v>
       </c>
       <c r="C3" s="14" t="str">
-        <v>苏州工学院·江苏省具身智能工业机器人及其人机协作高校重点实验室</v>
+        <v>山东科技大学·山东省智能感知与自主控制重点实验室</v>
       </c>
       <c r="D3" s="15" t="str">
-        <v>具身智能导航与灵巧操作；医疗机器人力触觉反馈与人机协同；特种机器人</v>
+        <v>多模态视觉感知与信息融合；混杂系统建模与反馈镇定；自主决策、协同控制及感知—决策—控制一体化（公告未限定应用于机器人）</v>
       </c>
       <c r="E3" s="15" t="str">
-        <v>1—3万元/项。</v>
+        <v>一般2万元/项（1—2项）；
+重点5万元/项（2—3项）</v>
       </c>
       <c r="F3" s="16" t="str">
         <v>公告</v>
@@ -595,39 +596,39 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B4" s="13" t="d">
-        <v>2026-11-10T00:00:00.000Z</v>
+        <v>2026-10-15T00:00:00.000Z</v>
       </c>
       <c r="C4" s="14" t="str">
-        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
+        <v>浙江理工大学·教育部绿色纺织国际合作联合实验室（2027年度）</v>
       </c>
       <c r="D4" s="15" t="str">
-        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
+        <v>柔性电子与纺织具身智能；机器视觉与纺织AI智能检测（须服务纺织研究）</v>
       </c>
       <c r="E4" s="15" t="str">
-        <v>0.5万元/项</v>
+        <v>一般1—2万元/项，特别突出的项目可增加。</v>
       </c>
       <c r="F4" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="12" t="str">
+      <c r="A5" t="str" s="12">
         <v>受理中·条件待核</v>
       </c>
-      <c r="B5" s="13" t="d">
-        <v>2026-10-20T00:00:00.000Z</v>
-      </c>
-      <c r="C5" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
-      </c>
-      <c r="D5" s="15" t="str">
-        <v>具身智能在自主系统中的应用；运载工具协同控制；多模态运行环境感知及跨场景泛化</v>
-      </c>
-      <c r="E5" s="15" t="str">
-        <v>4—10万元；约10项</v>
-      </c>
-      <c r="F5" s="16" t="str">
-        <v>公告</v>
+      <c r="B5" t="n" s="13">
+        <v>46310</v>
+      </c>
+      <c r="C5" t="str" s="14">
+        <v>太原理工大学／山西虹安科技股份有限公司·受限空间应急救援生命通道构建技术与装备山西省重点实验室</v>
+      </c>
+      <c r="D5" t="str" s="15">
+        <v>方向1受限环境感知/探测；方向2多源融合与救援路径规划；方向3生命通道构建装备与控制；具体应用为矿山/隧道救援，不虚构医疗机器人任务。</v>
+      </c>
+      <c r="E5" t="str" s="15">
+        <v>一般2万元/项（4项）；重点3万元/项（2项）。</v>
+      </c>
+      <c r="F5" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
@@ -635,16 +636,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B6" s="13" t="d">
-        <v>2026-10-20T00:00:00.000Z</v>
+        <v>2026-10-18T00:00:00.000Z</v>
       </c>
       <c r="C6" s="14" t="str">
-        <v>北京航空航天大学·空地一体新航行系统技术全国重点实验室</v>
+        <v>天津大学·精密测试技术及仪器全国重点实验室</v>
       </c>
       <c r="D6" s="15" t="str">
-        <v>基于通信质量感知的低空三维航路规划；安全约束下航路规划与原理验证</v>
+        <v>水下无人平台协同的稳健水声通信；数控机床六自由度误差在线测量与补偿</v>
       </c>
       <c r="E6" s="15" t="str">
-        <v>需求牵引不超过25万元，前沿探索不超过15万元</v>
+        <v>普通4—8万元</v>
       </c>
       <c r="F6" s="16" t="str">
         <v>公告</v>
@@ -655,16 +656,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B7" s="13" t="d">
-        <v>2026-10-30T00:00:00.000Z</v>
+        <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C7" s="14" t="str">
-        <v>重庆交通大学·交通工程应用机器人重庆市工程实验室</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D7" s="15" t="str">
-        <v>交通基础设施建设、管理与养护机器人；交通装备运行维护机器人关键技术与整机集成</v>
+        <v>具身智能在自主系统中的应用；运载工具协同控制；多模态运行环境感知及跨场景泛化</v>
       </c>
       <c r="E7" s="15" t="str">
-        <v>0.5—2万元/项；方向1—3各1—3项；调研方向另列。</v>
+        <v>4—10万元；约10项</v>
       </c>
       <c r="F7" s="16" t="str">
         <v>公告</v>
@@ -675,17 +676,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B8" s="13" t="d">
-        <v>2026-10-15T00:00:00.000Z</v>
+        <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C8" s="14" t="str">
-        <v>山东科技大学·山东省智能感知与自主控制重点实验室</v>
+        <v>北京航空航天大学·空地一体新航行系统技术全国重点实验室</v>
       </c>
       <c r="D8" s="15" t="str">
-        <v>多模态视觉感知与信息融合；混杂系统建模与反馈镇定；自主决策、协同控制及感知—决策—控制一体化（公告未限定应用于机器人）</v>
+        <v>基于通信质量感知的低空三维航路规划；安全约束下航路规划与原理验证</v>
       </c>
       <c r="E8" s="15" t="str">
-        <v>一般2万元/项（1—2项）；
-重点5万元/项（2—3项）</v>
+        <v>需求牵引不超过25万元，前沿探索不超过15万元</v>
       </c>
       <c r="F8" s="16" t="str">
         <v>公告</v>
@@ -696,16 +696,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B9" s="13" t="d">
-        <v>2026-10-15T00:00:00.000Z</v>
+        <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C9" s="14" t="str">
-        <v>浙江理工大学·教育部绿色纺织国际合作联合实验室（2027年度）</v>
+        <v>南昌航空大学·江西省机载系统智能检测技术产业技术工程化中心（同公告联署：南昌市航空软件共性技术研发重点实验室）</v>
       </c>
       <c r="D9" s="15" t="str">
-        <v>柔性电子与纺织具身智能；机器视觉与纺织AI智能检测（须服务纺织研究）</v>
+        <v>机载智能导航与人类导航信息统一；拓扑与几何规划耦合；机载巡检目标识别；智能对抗与系统测试（保留公告1—5方向）</v>
       </c>
       <c r="E9" s="15" t="str">
-        <v>一般1—2万元/项，特别突出的项目可增加。</v>
+        <v>0.5—1万元/项（4—5项）</v>
       </c>
       <c r="F9" s="16" t="str">
         <v>公告</v>
@@ -716,16 +716,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B10" s="13" t="d">
-        <v>2026-10-18T00:00:00.000Z</v>
+        <v>2026-10-26T00:00:00.000Z</v>
       </c>
       <c r="C10" s="14" t="str">
-        <v>天津大学·精密测试技术及仪器全国重点实验室</v>
+        <v>西南交通大学·轨道交通运载系统全国重点实验室</v>
       </c>
       <c r="D10" s="15" t="str">
-        <v>水下无人平台协同的稳健水声通信；数控机床六自由度误差在线测量与补偿</v>
+        <v>面向检修作业的具身智能与人机协同</v>
       </c>
       <c r="E10" s="15" t="str">
-        <v>普通4—8万元</v>
+        <v>8—10万元</v>
       </c>
       <c r="F10" s="16" t="str">
         <v>公告</v>
@@ -736,16 +736,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B11" s="13" t="d">
-        <v>2026-10-20T00:00:00.000Z</v>
+        <v>2026-10-27T00:00:00.000Z</v>
       </c>
       <c r="C11" s="14" t="str">
-        <v>南昌航空大学·江西省机载系统智能检测技术产业技术工程化中心（同公告联署：南昌市航空软件共性技术研发重点实验室）</v>
+        <v>大连理工大学·工业装备智能控制与优化教育部重点实验室</v>
       </c>
       <c r="D11" s="15" t="str">
-        <v>机载智能导航与人类导航信息统一；拓扑与几何规划耦合；机载巡检目标识别；智能对抗与系统测试（保留公告1—5方向）</v>
+        <v>工业装备的智能检测与控制技术；工业控制嵌入式软件及系统</v>
       </c>
       <c r="E11" s="15" t="str">
-        <v>0.5—1万元/项（4—5项）</v>
+        <v>3万元</v>
       </c>
       <c r="F11" s="16" t="str">
         <v>公告</v>
@@ -756,16 +756,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B12" s="13" t="d">
-        <v>2026-10-26T00:00:00.000Z</v>
+        <v>2026-10-30T00:00:00.000Z</v>
       </c>
       <c r="C12" s="14" t="str">
-        <v>西南交通大学·轨道交通运载系统全国重点实验室</v>
+        <v>重庆交通大学·交通工程应用机器人重庆市工程实验室</v>
       </c>
       <c r="D12" s="15" t="str">
-        <v>面向检修作业的具身智能与人机协同</v>
+        <v>交通基础设施建设、管理与养护机器人；交通装备运行维护机器人关键技术与整机集成</v>
       </c>
       <c r="E12" s="15" t="str">
-        <v>8—10万元</v>
+        <v>0.5—2万元/项；方向1—3各1—3项；调研方向另列。</v>
       </c>
       <c r="F12" s="16" t="str">
         <v>公告</v>
@@ -776,16 +776,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B13" s="13" t="d">
-        <v>2026-10-27T00:00:00.000Z</v>
+        <v>2026-10-31T00:00:00.000Z</v>
       </c>
       <c r="C13" s="14" t="str">
-        <v>大连理工大学·工业装备智能控制与优化教育部重点实验室</v>
+        <v>苏州工学院·江苏省具身智能工业机器人及其人机协作高校重点实验室</v>
       </c>
       <c r="D13" s="15" t="str">
-        <v>工业装备的智能检测与控制技术；工业控制嵌入式软件及系统</v>
+        <v>具身智能导航与灵巧操作；医疗机器人力触觉反馈与人机协同；特种机器人</v>
       </c>
       <c r="E13" s="15" t="str">
-        <v>3万元</v>
+        <v>1—3万元/项。</v>
       </c>
       <c r="F13" s="16" t="str">
         <v>公告</v>
@@ -816,16 +816,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B15" s="13" t="d">
-        <v>2026-11-15T00:00:00.000Z</v>
+        <v>2026-11-10T00:00:00.000Z</v>
       </c>
       <c r="C15" s="14" t="str">
-        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
       </c>
       <c r="D15" s="15" t="str">
-        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
       </c>
       <c r="E15" s="15" t="str">
-        <v>重点3万元、一般2万元</v>
+        <v>0.5万元/项</v>
       </c>
       <c r="F15" s="16" t="str">
         <v>公告</v>
@@ -836,18 +836,38 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B16" s="13" t="d">
+        <v>2026-11-15T00:00:00.000Z</v>
+      </c>
+      <c r="C16" s="14" t="str">
+        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+      </c>
+      <c r="D16" s="15" t="str">
+        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+      </c>
+      <c r="E16" s="15" t="str">
+        <v>重点3万元、一般2万元</v>
+      </c>
+      <c r="F16" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="12" t="str">
+        <v>受理中·条件待核</v>
+      </c>
+      <c r="B17" s="13" t="d">
         <v>2026-11-30T00:00:00.000Z</v>
       </c>
-      <c r="C16" s="14" t="str">
+      <c r="C17" s="14" t="str">
         <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
-      <c r="D16" s="15" t="str">
+      <c r="D17" s="15" t="str">
         <v>机器人加工技能学习与自主控制；多机器人协同；人形机器人感知、灵巧操作与全身控制</v>
       </c>
-      <c r="E16" s="15" t="str">
+      <c r="E17" s="15" t="str">
         <v>公告未公布资助强度，需咨询</v>
       </c>
-      <c r="F16" s="16" t="str">
+      <c r="F17" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
@@ -855,34 +875,36 @@
   <hyperlinks>
     <hyperlink ref="C2" location="'02项目完整详情'!A2"/>
     <hyperlink ref="F2" ns1:id="R0703188348514edb"/>
-    <hyperlink ref="C3" location="'02项目完整详情'!A10"/>
-    <hyperlink ref="F3" ns1:id="R02deb72e2d4c4fc2"/>
-    <hyperlink ref="C4" location="'02项目完整详情'!A11"/>
-    <hyperlink ref="F4" ns1:id="Rb0dfb47d911a4186"/>
-    <hyperlink ref="C5" location="'02项目完整详情'!A138"/>
-    <hyperlink ref="F5" ns1:id="R03ccbeb508f24d98"/>
-    <hyperlink ref="C6" location="'02项目完整详情'!A3"/>
-    <hyperlink ref="F6" ns1:id="Rf39712aab58b4977"/>
-    <hyperlink ref="C7" location="'02项目完整详情'!A4"/>
-    <hyperlink ref="F7" ns1:id="R29f5a7d822fa4ff0"/>
-    <hyperlink ref="C8" location="'02项目完整详情'!A47"/>
-    <hyperlink ref="F8" ns1:id="Rfa73da6bd12f484e"/>
-    <hyperlink ref="C9" location="'02项目完整详情'!A5"/>
-    <hyperlink ref="F9" ns1:id="Rcec38ef0c81f4e03"/>
-    <hyperlink ref="C10" location="'02项目完整详情'!A6"/>
-    <hyperlink ref="F10" ns1:id="Rcc6b937cc2db4463"/>
-    <hyperlink ref="C11" location="'02项目完整详情'!A149"/>
-    <hyperlink ref="F11" ns1:id="R7683ff081f9341d2"/>
-    <hyperlink ref="C12" location="'02项目完整详情'!A7"/>
-    <hyperlink ref="F12" ns1:id="R5649c5cdeb214215"/>
-    <hyperlink ref="C13" location="'02项目完整详情'!A8"/>
-    <hyperlink ref="F13" ns1:id="R1fb1d42b338a46e2"/>
+    <hyperlink ref="C13" location="'02项目完整详情'!A10"/>
+    <hyperlink ref="F13" ns1:id="R02deb72e2d4c4fc2"/>
+    <hyperlink ref="C15" location="'02项目完整详情'!A11"/>
+    <hyperlink ref="F15" ns1:id="Rb0dfb47d911a4186"/>
+    <hyperlink ref="C7" location="'02项目完整详情'!A138"/>
+    <hyperlink ref="F7" ns1:id="R03ccbeb508f24d98"/>
+    <hyperlink ref="C8" location="'02项目完整详情'!A3"/>
+    <hyperlink ref="F8" ns1:id="Rf39712aab58b4977"/>
+    <hyperlink ref="C12" location="'02项目完整详情'!A4"/>
+    <hyperlink ref="F12" ns1:id="R29f5a7d822fa4ff0"/>
+    <hyperlink ref="C3" location="'02项目完整详情'!A47"/>
+    <hyperlink ref="F3" ns1:id="Rfa73da6bd12f484e"/>
+    <hyperlink ref="C4" location="'02项目完整详情'!A5"/>
+    <hyperlink ref="F4" ns1:id="Rcec38ef0c81f4e03"/>
+    <hyperlink ref="C6" location="'02项目完整详情'!A6"/>
+    <hyperlink ref="F6" ns1:id="Rcc6b937cc2db4463"/>
+    <hyperlink ref="C9" location="'02项目完整详情'!A149"/>
+    <hyperlink ref="F9" ns1:id="R7683ff081f9341d2"/>
+    <hyperlink ref="C10" location="'02项目完整详情'!A7"/>
+    <hyperlink ref="F10" ns1:id="R5649c5cdeb214215"/>
+    <hyperlink ref="C11" location="'02项目完整详情'!A8"/>
+    <hyperlink ref="F11" ns1:id="R1fb1d42b338a46e2"/>
     <hyperlink ref="C14" location="'02项目完整详情'!A9"/>
     <hyperlink ref="F14" ns1:id="Rc8744d7119ac4fd0"/>
-    <hyperlink ref="C15" location="'02项目完整详情'!A12"/>
-    <hyperlink ref="F15" ns1:id="R59533ec0b37d42df"/>
-    <hyperlink ref="C16" location="'02项目完整详情'!A13"/>
-    <hyperlink ref="F16" ns1:id="Rc2d55cd36ec74ace"/>
+    <hyperlink ref="C16" location="'02项目完整详情'!A12"/>
+    <hyperlink ref="F16" ns1:id="R59533ec0b37d42df"/>
+    <hyperlink ref="C17" location="'02项目完整详情'!A13"/>
+    <hyperlink ref="F17" ns1:id="Rc2d55cd36ec74ace"/>
+    <hyperlink ref="C5" location="'02项目完整详情'!A183" display="项目完整详情"/>
+    <hyperlink ref="F5" ns1:id="rIdResume17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5226,7 +5248,7 @@
         <v>M085</v>
       </c>
       <c r="B49" s="3" t="str">
-        <v>正式开放课题公告</v>
+        <v>正式2026公告；机器人具体任务边界待核</v>
       </c>
       <c r="C49" s="3" t="str">
         <v>武汉理工大学</v>
@@ -5240,55 +5262,50 @@
       <c r="F49" s="3" t="str">
         <v>2026</v>
       </c>
-      <c r="G49" s="6" t="d">
-        <v>2026-10-31T00:00:00.000Z</v>
-      </c>
-      <c r="H49" s="3" t="str"/>
+      <c r="G49" s="6" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H49" s="3" t="str">
+        <v>时点未载（北京时间）</v>
+      </c>
       <c r="I49" s="3" t="str">
-        <v>方向待核：交通物联网公告中未找到机器人或自主运行装备的明确任务；交通信息与多模态感知不能单独作为保留理由。</v>
+        <v>公告列交通信息多模态感知等4方向，未写明机器人/无人交通的具体任务；不仅凭物联网/感知名称判相关。</v>
       </c>
       <c r="J49" s="3" t="str">
-        <v>1—3万元</v>
+        <v>拟5—8项；平均1—3万元/项（原文口径，非统一定额）。</v>
       </c>
       <c r="K49" s="3" t="str">
-        <v>官方明确｜凡研究方向符合开放课题指南的研究人员（高级职称或博士学位获得者），均可根据课题指南提出申请，经本实验室学术委员会择优批准，获得课题基金资助。</v>
+        <v>高级职称或博士；研究方向符合指南。</v>
       </c>
       <c r="L49" s="3" t="str">
-        <v>官方明确｜合作要求：‌申请人需与实验室至少1名固定研究人员联合申报；</v>
+        <v>至少1名实验室固定人员联合；鼓励跨单位及国际团队。</v>
       </c>
       <c r="M49" s="3" t="str">
-        <v>官方明确｜经费在武汉理工大学账上，获批后一次性划拨至该校账上；获批者可来校报账或由实验室秘书协助。不能写成外拨至申请人单位。</v>
+        <v>经费在武汉理工大学账上，自行或秘书协助报账；获批一次性划入校内账户。允许科目未载；不能当作外拨至本人单位。</v>
       </c>
       <c r="N49" s="3" t="str">
-        <v>官方明确｜基金课题执行期一般为两年，本次研究工作的起始时间为2027.1.1~2028.12.31。</v>
+        <v>2027-01-01—2028-12-31，2年。</v>
       </c>
       <c r="O49" s="3" t="str">
-        <v>官方明确｜5、 年度报告和结题要求 每年应在12月31日前将年度报告寄到实验室，申报课题必须按照申请内容及“年度进度报告”进度完成，对于基金使用不合理或者没有足够理由未能按进度完成计划的课题，实验室主任有权暂时中止或取消资助资金。
-鼓励研究人员多投高水平国际期刊、中文期刊或国际学术会议论文，结题要求应符合以下论文发表指标的基本要求之一：
-（1）中科院一区或CCF推荐A类国际国内期刊论文、CCF推荐A类国际学术会议论文1篇（会议论文指“Full paper”或“Regular paper”）；
-（2）SCI检索期刊或CCF推荐国际国内期刊或国际学术会议论文2篇。
-获本实验室资助课题所取得的研究成果归本实验室与课题承担人所在单位共同拥有。
-（1）论文：应属“交通物联网技术湖北省重点实验室（武汉理工大学）”或Hubei Key Laboratory of Transportation Internet of Things(Wuhan University of Technology)为作者单位之一；
-（3）鉴定成果：应明确标署“交通物联网技术湖北省重点实验室（武汉理工大学）”为该项目成果的主要完成单位之一；
-（4）专利：申请单位应为武汉理工大学。</v>
+        <v>年度12月31日前报告；结题为中科院一区/CCF A期刊或A会议Full/Regular 1篇，或SCI/CCF期刊或会议2篇；报告及成果复印件；实验室作者单位之一，专著/鉴定需标注。</v>
       </c>
       <c r="P49" s="3" t="str">
-        <v>官方明确｜获本实验室资助课题所取得的研究成果归本实验室与课题承担人所在单位共同拥有。</v>
+        <v>实验室与承担人单位共有；专利申请单位须武汉理工大学。</v>
       </c>
       <c r="Q49" s="3" t="str">
-        <v>官方明确｜申请人从网址（https://ai.whut.edu.cn/）上下载并填写开放课题研究基金申请书，由所在单位同意、签署意见并加盖公章后，将申请表寄回交通物联网湖北省重点实验室（需提交一份电子版，二份纸质版本），电子版发送至：iot@whut.edu.cn，纸质版邮寄至：湖北省武汉市洪山区工大路学海楼524办公室郭老师收。</v>
+        <v>单位意见盖章；电子1份iot@whut.edu.cn，纸质2份寄洪山区工大路学海楼524郭老师；12月底通知并签合同。</v>
       </c>
       <c r="R49" s="3" t="str">
         <v>已知背景：南京信息工程大学现职、博士。个人条件、在研限项及实际合作人尚未逐项确认；须按公告条款核对，受理窗口状态不代表可申请。</v>
       </c>
       <c r="S49" s="3" t="str">
-        <v>筛选/证据缺口：交通物联网公告中未找到机器人或自主运行装备的明确任务；交通信息与多模态感知不能单独作为保留理由。</v>
+        <v>申请书DOC工具不支持，需用户下载；需确认所申报机器人感知/自主交通具体任务是否属于年度范围，及允许报销科目和合同条款。</v>
       </c>
       <c r="T49" s="3" t="str">
         <v>https://ai.whut.edu.cn/kxyj/kyzx/202608/t20260831_1414539.shtml</v>
       </c>
       <c r="U49" s="3" t="str">
-        <v>https://ai.whut.edu.cn/kxyj/kyzx/202608/t20260831_1414539.shtml</v>
+        <v>https://ai.whut.edu.cn/kxyj/kyzx/202608/P020260831508416009465.doc</v>
       </c>
       <c r="V49" s="3" t="str">
         <v>2026-10-08（北京时间；截止日当天时点未明示的转待核）</v>
@@ -5302,7 +5319,7 @@
         <v>P2 湖北·武汉</v>
       </c>
       <c r="Z49" s="3" t="str">
-        <v>iot@whut.edu.cn</v>
+        <v>郭老师；iot@whut.edu.cn</v>
       </c>
       <c r="AA49" s="3" t="str"/>
     </row>
@@ -10318,7 +10335,9 @@
       <c r="G107" s="6" t="d">
         <v>2026-04-22T00:00:00.000Z</v>
       </c>
-      <c r="H107" s="3" t="str"/>
+      <c r="H107" s="3" t="str">
+        <v>18:00（北京时间）</v>
+      </c>
       <c r="I107" s="3" t="str">
         <v>无人系统多源感知、导航与控制</v>
       </c>
@@ -16172,8 +16191,8 @@
       <c r="AA176" t="str" s="3"/>
     </row>
     <row r="177" ht="79.5" customHeight="1">
-      <c r="A177" t="str" s="3">
-        <v>N027</v>
+      <c r="A177" s="3" t="str">
+        <v>M169</v>
       </c>
       <c r="B177" t="str" s="3">
         <v>官方正式年度指南已读取</v>
@@ -16250,7 +16269,576 @@
       <c r="Z177" t="str" s="3">
         <v>王博15380759943；江雨韩18696143266；葛立波15850524302；wangbo_nuaa@nuaa.edu.cn</v>
       </c>
-      <c r="AA177" t="str" s="3"/>
+      <c r="AA177" s="3" t="str">
+        <v>原编号M169；N027为本次误设别名，停用；复核恢复，非新增。</v>
+      </c>
+    </row>
+    <row r="178" ht="79.5" customHeight="1">
+      <c r="A178" t="str" s="3">
+        <v>N029</v>
+      </c>
+      <c r="B178" t="str" s="3">
+        <v>正式年度通知已读；具体指南验证码阻塞</v>
+      </c>
+      <c r="C178" t="str" s="3">
+        <v>成都大学</v>
+      </c>
+      <c r="D178" t="str" s="3">
+        <v>模式识别与智能信息处理四川省教育厅高校重点实验室</v>
+      </c>
+      <c r="E178" t="str" s="3">
+        <v>已截止·任务待核</v>
+      </c>
+      <c r="F178" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G178" t="n" s="6">
+        <v>46265</v>
+      </c>
+      <c r="H178" t="str" s="3">
+        <v>17:00（北京时间）</v>
+      </c>
+      <c r="I178" t="str" s="3">
+        <v>年度具体任务在申报指南，尚未取得；不凭模式识别平台名确定机器人相关性。</v>
+      </c>
+      <c r="J178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="K178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="L178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="M178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="N178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="O178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="P178" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="Q178" t="str" s="3">
+        <v>先电子申请ligen@cdu.edu.cn审核，通过后纸质3份送第十教学楼10107；截止前送达。</v>
+      </c>
+      <c r="R178" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S178" t="str" s="3">
+        <v>需下载2026修订版指南，核实际任务、校外资格、金额、合作、周期、经费及外拨、成果和IP。正文截止已过，不列首页。</v>
+      </c>
+      <c r="T178" t="str" s="3">
+        <v>https://computer.cdu.edu.cn/info/1023/12282.htm</v>
+      </c>
+      <c r="U178" t="str" s="3">
+        <v>https://computer.cdu.edu.cn/system/_content/download.jsp?owner=1663618310&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=18211634</v>
+      </c>
+      <c r="V178" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W178" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X178" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y178" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="Z178" t="str" s="3">
+        <v>李老师；18853318883；ligen@cdu.edu.cn</v>
+      </c>
+      <c r="AA178" t="str" s="3"/>
+    </row>
+    <row r="179" ht="79.5" customHeight="1">
+      <c r="A179" t="str" s="3">
+        <v>N030</v>
+      </c>
+      <c r="B179" t="str" s="3">
+        <v>官方2025通知搜索定位；首次打开超时</v>
+      </c>
+      <c r="C179" t="str" s="3">
+        <v>成都大学</v>
+      </c>
+      <c r="D179" t="str" s="3">
+        <v>四川省智能康复系统感知与控制国际联合研究中心</v>
+      </c>
+      <c r="E179" t="str" s="3">
+        <v>线索待核</v>
+      </c>
+      <c r="F179" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G179" t="str" s="6">
+        <v>未确认</v>
+      </c>
+      <c r="H179" t="str" s="3">
+        <v>时点未取得</v>
+      </c>
+      <c r="I179" t="str" s="3">
+        <v>年度具体任务尚未取得；智能康复平台仅作相关候选。</v>
+      </c>
+      <c r="J179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="K179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="L179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="M179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="N179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="O179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="P179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="Q179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="R179" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S179" t="str" s="3">
+        <v>需完整2025正文及附件；2026/2027新指南未取得。逐项核任务、校外资格、金额、截止、合作及经费、周期、成果、IP、提交。</v>
+      </c>
+      <c r="T179" t="str" s="3">
+        <v>https://ele.cdu.edu.cn/info/1061/10210.htm</v>
+      </c>
+      <c r="U179" t="str" s="3">
+        <v>见公告附件，尚未取得</v>
+      </c>
+      <c r="V179" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W179" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X179" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y179" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="Z179" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="AA179" t="str" s="3"/>
+    </row>
+    <row r="180" ht="79.5" customHeight="1">
+      <c r="A180" t="str" s="3">
+        <v>N031</v>
+      </c>
+      <c r="B180" t="str" s="3">
+        <v>官方2026通知搜索定位；首次打开412</v>
+      </c>
+      <c r="C180" t="str" s="3">
+        <v>西华大学</v>
+      </c>
+      <c r="D180" t="str" s="3">
+        <v>智能空地融合载具及管控教育部工程研究中心</v>
+      </c>
+      <c r="E180" t="str" s="3">
+        <v>线索待核</v>
+      </c>
+      <c r="F180" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G180" t="str" s="6">
+        <v>未确认</v>
+      </c>
+      <c r="H180" t="str" s="3">
+        <v>时点未取得</v>
+      </c>
+      <c r="I180" t="str" s="3">
+        <v>年度具体无人/空地载具任务待取得；不把平台名当年度任务。</v>
+      </c>
+      <c r="J180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="K180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="L180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="M180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="N180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="O180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="P180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="Q180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="R180" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S180" t="str" s="3">
+        <v>需完整2026正文及指南/管理/申请附件，确认机器人自主系统任务与全部申报经费条款；2027未取得。</v>
+      </c>
+      <c r="T180" t="str" s="3">
+        <v>https://jybgczx.xhu.edu.cn/aa/a4/c11041a240292/page.htm</v>
+      </c>
+      <c r="U180" t="str" s="3">
+        <v>见公告附件，尚未取得</v>
+      </c>
+      <c r="V180" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W180" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X180" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y180" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="Z180" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="AA180" t="str" s="3"/>
+    </row>
+    <row r="181" ht="79.5" customHeight="1">
+      <c r="A181" t="str" s="3">
+        <v>N032</v>
+      </c>
+      <c r="B181" t="str" s="3">
+        <v>官方2026通知搜索定位；首次打开412</v>
+      </c>
+      <c r="C181" t="str" s="3">
+        <v>云南农业大学</v>
+      </c>
+      <c r="D181" t="str" s="3">
+        <v>云南省作物生产与智慧农业重点实验室</v>
+      </c>
+      <c r="E181" t="str" s="3">
+        <v>线索待核</v>
+      </c>
+      <c r="F181" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G181" t="str" s="6">
+        <v>未确认</v>
+      </c>
+      <c r="H181" t="str" s="3">
+        <v>时点未取得</v>
+      </c>
+      <c r="I181" t="str" s="3">
+        <v>具体任务未取得；须确认是否包含农机机器人/感知控制，不能因智慧农业名称保留为相关项目。</v>
+      </c>
+      <c r="J181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="K181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="L181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="M181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="N181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="O181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="P181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="Q181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="R181" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S181" t="str" s="3">
+        <v>需完整2026正文及附件，先核任务；无农机机器人及相关感知控制任务则剔除。其余资格、金额、截止、合作、经费、成果、IP待核。</v>
+      </c>
+      <c r="T181" t="str" s="3">
+        <v>https://www.ynau.edu.cn/info/1060/87504.htm</v>
+      </c>
+      <c r="U181" t="str" s="3">
+        <v>见公告附件，尚未取得</v>
+      </c>
+      <c r="V181" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W181" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X181" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y181" t="str" s="3">
+        <v>云南·昆明</v>
+      </c>
+      <c r="Z181" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="AA181" t="str" s="3"/>
+    </row>
+    <row r="182" ht="79.5" customHeight="1">
+      <c r="A182" t="str" s="3">
+        <v>N033</v>
+      </c>
+      <c r="B182" t="str" s="3">
+        <v>正式历史指南已读；2026/2027未取得</v>
+      </c>
+      <c r="C182" t="str" s="3">
+        <v>天津工业大学</v>
+      </c>
+      <c r="D182" t="str" s="3">
+        <v>天津市电气装备智能控制重点实验室</v>
+      </c>
+      <c r="E182" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F182" t="str" s="3">
+        <v>2021</v>
+      </c>
+      <c r="G182" t="n" s="6">
+        <v>44434</v>
+      </c>
+      <c r="H182" t="str" s="3">
+        <v>时点未载，以收到邮件为准</v>
+      </c>
+      <c r="I182" t="str" s="3">
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+      </c>
+      <c r="J182" t="str" s="3">
+        <v>重点2万元/项；一般1万元/项。</v>
+      </c>
+      <c r="K182" t="str" s="3">
+        <v>非天津工业大学在编，相关科研基础；本室未结题项目须结题后再申报；学历职称年龄门槛未载。</v>
+      </c>
+      <c r="L182" t="str" s="3">
+        <v>必须与实验室合作，选择固定人员共同研究；访问天数未载。</v>
+      </c>
+      <c r="M182" t="str" s="3">
+        <v>实验室合作者负责报销及流程；允许科目及外拨未载。</v>
+      </c>
+      <c r="N182" t="str" s="3">
+        <v>1年。</v>
+      </c>
+      <c r="O182" t="str" s="3">
+        <v>论文、专利、奖项须实验室署名；数量和等级未载，任务书待核。</v>
+      </c>
+      <c r="P182" t="str" s="3">
+        <v>实验室与研究者所在单位共同所有。</v>
+      </c>
+      <c r="Q182" t="str" s="3">
+        <v>纸质1份A4双面左装订，单位签章邮寄西青区宾水西道399号300387；电子同时发送chengyi@tiangong.edu.cn，内容一致。</v>
+      </c>
+      <c r="R182" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S182" t="str" s="3">
+        <v>2026/2027新年度指南未取得；历史申请模板及任务书的具体结题数量、科目和外拨待取得。</v>
+      </c>
+      <c r="T182" t="str" s="3">
+        <v>https://aeeet.tiangong.edu.cn/2021/0816/c6096a69693/page.psp</v>
+      </c>
+      <c r="U182" t="str" s="3">
+        <v>见公告附件，尚未取得</v>
+      </c>
+      <c r="V182" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W182" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X182" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y182" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="Z182" t="str" s="3">
+        <v>成怡13920345202；chengyi@tiangong.edu.cn</v>
+      </c>
+      <c r="AA182" t="str" s="3"/>
+    </row>
+    <row r="183" ht="79.5" customHeight="1">
+      <c r="A183" t="str" s="3">
+        <v>N034</v>
+      </c>
+      <c r="B183" t="str" s="3">
+        <v>官方正式指南已核，当前申报窗口内</v>
+      </c>
+      <c r="C183" t="str" s="3">
+        <v>太原理工大学／山西虹安科技股份有限公司</v>
+      </c>
+      <c r="D183" t="str" s="3">
+        <v>受限空间应急救援生命通道构建技术与装备山西省重点实验室</v>
+      </c>
+      <c r="E183" t="str" s="3">
+        <v>受理中·条件待核</v>
+      </c>
+      <c r="F183" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G183" t="n" s="6">
+        <v>46310</v>
+      </c>
+      <c r="H183" t="str" s="3">
+        <v>具体时点未载（北京时间）</v>
+      </c>
+      <c r="I183" t="str" s="3">
+        <v>方向1受限环境感知/探测；方向2多源融合与救援路径规划；方向3生命通道构建装备与控制；具体应用为矿山/隧道救援，不虚构医疗机器人任务。</v>
+      </c>
+      <c r="J183" t="str" s="3">
+        <v>一般2万元/项（4项）；重点3万元/项（2项）。</v>
+      </c>
+      <c r="K183" t="str" s="3">
+        <v>依托单位之外国内高校、科研院所、企业及科研机构人员；学历、职称、年龄、限项正文未载，申请表/任务书待核。</v>
+      </c>
+      <c r="L183" t="str" s="3">
+        <v>鼓励科研合作；部分成果署名路径须实验室人员通讯；未明示申请时强制固定合作及访问天数。</v>
+      </c>
+      <c r="M183" t="str" s="3">
+        <v>允许科目、报销地点、外拨及拨款节点正文未载，需任务书/办法确认。</v>
+      </c>
+      <c r="N183" t="str" s="3">
+        <v>原则1年；所有项目2027年10月前完成验收。</v>
+      </c>
+      <c r="O183" t="str" s="3">
+        <v>一般相关论文≥2篇；重点≥3篇且SCI≥1篇；申请人第一作者+实验室第一单位，或申请人第一作者+实验室人员通讯+实验室第二单位；基金号；标注其他实验室/平台者不计考核；结题报告。</v>
+      </c>
+      <c r="P183" t="str" s="3">
+        <v>正文未载；不能把署名规则当成果权属。</v>
+      </c>
+      <c r="Q183" t="str" s="3">
+        <v>截止前电子申请书及签章PDF发wtao8909@126.com，按范围自拟题，评审后按任务书实施。</v>
+      </c>
+      <c r="R183" t="str" s="3">
+        <v>本人博士且在国内高校任职；额外资格限项未取得、实际合作/成果署名安排待确认；不认定已满足全部条件。</v>
+      </c>
+      <c r="S183" t="str" s="3">
+        <v>申请书下载有验证码；需原表以核额外资格/限项与条款；经费科目/报销/外拨/拨付和成果IP未载，需正式办法或主办方书面答复。</v>
+      </c>
+      <c r="T183" t="str" s="3">
+        <v>https://aqyj.tyut.edu.cn/info/1085/12050.htm</v>
+      </c>
+      <c r="U183" t="str" s="3">
+        <v>https://aqyj.tyut.edu.cn/system/_content/download.jsp?owner=1496470707&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=2C927014D5412DE1400181B1F79077C8</v>
+      </c>
+      <c r="V183" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W183" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X183" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y183" t="str" s="3">
+        <v>山西·晋中</v>
+      </c>
+      <c r="Z183" t="str" s="3">
+        <v>王涛18811778870、杨雪林13008316833；wtao8909@126.com</v>
+      </c>
+      <c r="AA183" t="str" s="3"/>
+    </row>
+    <row r="184" ht="79.5" customHeight="1">
+      <c r="A184" t="str" s="3">
+        <v>N035</v>
+      </c>
+      <c r="B184" t="str" s="3">
+        <v>正式历史指南已读；实施方案PDF超时</v>
+      </c>
+      <c r="C184" t="str" s="3">
+        <v>辽宁工程技术大学</v>
+      </c>
+      <c r="D184" t="str" s="3">
+        <v>矿山液压技术与装备国家地方联合工程研究中心</v>
+      </c>
+      <c r="E184" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F184" t="str" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G184" t="n" s="6">
+        <v>45163</v>
+      </c>
+      <c r="H184" t="str" s="3">
+        <v>时点未载（北京时间）</v>
+      </c>
+      <c r="I184" t="str" s="3">
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+      </c>
+      <c r="J184" t="str" s="3">
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+      </c>
+      <c r="K184" t="str" s="3">
+        <v>在职在岗高校/科研院所/企事业相关人员；一般副高以上或博士；≤45周岁（1978-08-25后出生，按原文不改）；本室在研者不得申请。</v>
+      </c>
+      <c r="L184" t="str" s="3">
+        <v>鼓励实验室人员联合申请；成果须与固定人员合作发表；访问天数未载。</v>
+      </c>
+      <c r="M184" t="str" s="3">
+        <v>具体经费及外拨须实施方案，附件首次超时未取得。</v>
+      </c>
+      <c r="N184" t="str" s="3">
+        <v>一般2年；中期进展报告。</v>
+      </c>
+      <c r="O184" t="str" s="3">
+        <v>一般成果须中心第一或通讯单位；重点至少1项中心第一单位成果；所有成果合作发表并基金号；具体数量等级须实施方案。</v>
+      </c>
+      <c r="P184" t="str" s="3">
+        <v>辽宁工程技术大学与研究者所在单位共享。</v>
+      </c>
+      <c r="Q184" t="str" s="3">
+        <v>单位审查推荐盖章，纸质3份及电子递交；阜新玉龙路88号清雅楼305；邮箱zhaoguochao@lntu.edu.cn。</v>
+      </c>
+      <c r="R184" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；实际限项和强制合作尚未确认。</v>
+      </c>
+      <c r="S184" t="str" s="3">
+        <v>需2023实施方案PDF及申请附件以补全经费、结题指标；2026/2027指南未取得，不能套用历史年龄及条款。</v>
+      </c>
+      <c r="T184" t="str" s="3">
+        <v>https://jxgcxy.lntu.edu.cn/info/1056/4059.htm</v>
+      </c>
+      <c r="U184" t="str" s="3">
+        <v>https://jxgcxy.lntu.edu.cn/system/_content/download.jsp?owner=1500399521&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=F0601718C8256005472EC002F85F739B</v>
+      </c>
+      <c r="V184" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W184" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X184" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y184" t="str" s="3">
+        <v>辽宁·阜新</v>
+      </c>
+      <c r="Z184" t="str" s="3">
+        <v>郭/赵；18600443690、18241892970、0418-5110071；zhaoguochao@lntu.edu.cn</v>
+      </c>
+      <c r="AA184" t="str" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16649,6 +17237,13 @@
     <hyperlink ref="T175" ns1:id="rIdSystematic397"/>
     <hyperlink ref="T176" ns1:id="rIdSystematic398"/>
     <hyperlink ref="T177" ns1:id="rIdSystematic399"/>
+    <hyperlink ref="T178" ns1:id="rIdResume400"/>
+    <hyperlink ref="T179" ns1:id="rIdResume401"/>
+    <hyperlink ref="T180" ns1:id="rIdResume402"/>
+    <hyperlink ref="T181" ns1:id="rIdResume403"/>
+    <hyperlink ref="T182" ns1:id="rIdResume404"/>
+    <hyperlink ref="T183" ns1:id="rIdResume405"/>
+    <hyperlink ref="T184" ns1:id="rIdResume406"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -28189,8 +28784,8 @@
       <c r="D363" t="str" s="3">
         <v>2026-10-09</v>
       </c>
-      <c r="E363" t="str" s="3">
-        <v>空间智能感知与大模型应用联合实验室；年度2026；编号N027；官方正式年度指南已读取</v>
+      <c r="E363" s="3" t="str">
+        <v>空间智能感知与大模型应用联合实验室；年度2026；编号M169（复核恢复，非新增）；官方正式年度指南已读取</v>
       </c>
       <c r="F363" t="str" s="3">
         <v>年度已截止；申报模板未取得，合同细化验收/拨款和允许科目待核。SCI‘二区’及核心期刊口径正文未定义，不自行指定分区体系。</v>
@@ -28812,6 +29407,2748 @@
       </c>
       <c r="I384" t="str" s="3">
         <v>systematic_search_20261009.json 第94批</v>
+      </c>
+    </row>
+    <row r="385" ht="52.5" customHeight="1">
+      <c r="A385" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B385" t="str" s="3">
+        <v>天津理工大学</v>
+      </c>
+      <c r="C385" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D385" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E385" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F385" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G385" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H385" t="str" s="3"/>
+      <c r="I385" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第19项；site:tjut.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="386" ht="52.5" customHeight="1">
+      <c r="A386" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B386" t="str" s="3">
+        <v>天津工业大学</v>
+      </c>
+      <c r="C386" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D386" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E386" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：天津市电气装备智能控制重点实验室开放基金申请指南；2024年重点实验室开放课题立项公示</v>
+      </c>
+      <c r="F386" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G386" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H386" t="str" s="3">
+        <v>https://aeeet.tiangong.edu.cn/2021/0816/c6096a69693/page.psp
+https://laits.tiangong.edu.cn/2024/0321/c6073a92687/page.htm</v>
+      </c>
+      <c r="I386" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第20项；site:tiangong.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="387" ht="52.5" customHeight="1">
+      <c r="A387" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B387" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C387" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D387" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E387" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F387" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G387" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H387" t="str" s="3"/>
+      <c r="I387" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第21项；site:hebut.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="388" ht="52.5" customHeight="1">
+      <c r="A388" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B388" t="str" s="3">
+        <v>河北大学</v>
+      </c>
+      <c r="C388" t="str" s="3">
+        <v>河北</v>
+      </c>
+      <c r="D388" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E388" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F388" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G388" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H388" t="str" s="3"/>
+      <c r="I388" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第22项；site:hbu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="389" ht="52.5" customHeight="1">
+      <c r="A389" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B389" t="str" s="3">
+        <v>石家庄铁道大学</v>
+      </c>
+      <c r="C389" t="str" s="3">
+        <v>河北</v>
+      </c>
+      <c r="D389" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E389" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F389" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G389" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H389" t="str" s="3"/>
+      <c r="I389" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第23项；site:stdu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="390" ht="52.5" customHeight="1">
+      <c r="A390" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B390" t="str" s="3">
+        <v>河北工程大学</v>
+      </c>
+      <c r="C390" t="str" s="3">
+        <v>河北</v>
+      </c>
+      <c r="D390" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E390" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F390" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G390" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H390" t="str" s="3"/>
+      <c r="I390" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第24项；site:hebeu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="391" ht="52.5" customHeight="1">
+      <c r="A391" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B391" t="str" s="3">
+        <v>太原科技大学</v>
+      </c>
+      <c r="C391" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D391" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E391" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F391" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G391" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H391" t="str" s="3"/>
+      <c r="I391" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第25项；site:tyust.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="392" ht="52.5" customHeight="1">
+      <c r="A392" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B392" t="str" s="3">
+        <v>太原理工大学</v>
+      </c>
+      <c r="C392" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D392" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E392" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：关于组织申报2026年度山西省重点实验室的通知 截止日期8月28日18时-太原理工大学科学技术研究院网站；2026年优秀青年博士招聘公告-山西省煤矿智能装备工程研究中心；受限空间应急救援生命通道构建技术与装备山西省重点实验室 开放课题申报指南-安全与应急管理工程学院；山西省煤矿智能装备工程研究中心；太原理工大学煤电清洁智能控制教育部重点实验室</v>
+      </c>
+      <c r="F392" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G392" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H392" t="str" s="3">
+        <v>https://kj.tyut.edu.cn/info/1093/23100.htm
+https://mkzn.tyut.edu.cn/info/1021/1662.htm
+https://aqyj.tyut.edu.cn/info/1085/12050.htm
+https://mkzn.tyut.edu.cn/index.htm
+https://cicce.tyut.edu.cn/homepage/sysweb/docs/2025/10/31/f4ffbfe271bc4735b51223e662850112.pdf</v>
+      </c>
+      <c r="I392" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第26项；site:tyut.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="393" ht="52.5" customHeight="1">
+      <c r="A393" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B393" t="str" s="3">
+        <v>山西大学</v>
+      </c>
+      <c r="C393" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D393" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E393" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：运行管理 - 生物医药与健康山西省实验室</v>
+      </c>
+      <c r="F393" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G393" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H393" t="str" s="3">
+        <v>https://bmhlsp.sxu.edu.cn/yxgl/kfkt/26b96da9ed1643daadc175b19adfbdf4.htm</v>
+      </c>
+      <c r="I393" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第27项；site:sxu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="394" ht="52.5" customHeight="1">
+      <c r="A394" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B394" t="str" s="3">
+        <v>内蒙古大学</v>
+      </c>
+      <c r="C394" t="str" s="3">
+        <v>内蒙古</v>
+      </c>
+      <c r="D394" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E394" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：内蒙古自治区草地生态学重点实验室 2026年度开放课题申报指南-内蒙古草地生态学重点实验室；牧草与特色作物生物学教育部重点实验室</v>
+      </c>
+      <c r="F394" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G394" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H394" t="str" s="3">
+        <v>https://ecology.imu.edu.cn/info/1016/1403.htm
+https://hec.imu.edu.cn/__local/0/2B/C7/90F1D818A286F97837DB3317EF6_9DA9183C_26282.pdf</v>
+      </c>
+      <c r="I394" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第28项；site:imu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="395" ht="52.5" customHeight="1">
+      <c r="A395" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B395" t="str" s="3">
+        <v>沈阳工业大学</v>
+      </c>
+      <c r="C395" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D395" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E395" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F395" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G395" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H395" t="str" s="3"/>
+      <c r="I395" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第29项；site:sut.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="396" ht="52.5" customHeight="1">
+      <c r="A396" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B396" t="str" s="3">
+        <v>沈阳理工大学</v>
+      </c>
+      <c r="C396" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D396" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E396" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F396" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G396" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H396" t="str" s="3"/>
+      <c r="I396" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第30项；site:sylu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="397" ht="52.5" customHeight="1">
+      <c r="A397" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B397" t="str" s="3">
+        <v>辽宁工程技术大学</v>
+      </c>
+      <c r="C397" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D397" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E397" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：矿山液压技术与装备国家地方联合工程研究中心2023年度开放研究基金申请指南-辽宁工程技术大学机械工程学院</v>
+      </c>
+      <c r="F397" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G397" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H397" t="str" s="3">
+        <v>https://jxgcxy.lntu.edu.cn/info/1056/4059.htm</v>
+      </c>
+      <c r="I397" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第31项；site:lntu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="398" ht="52.5" customHeight="1">
+      <c r="A398" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B398" t="str" s="3">
+        <v>大连海事大学</v>
+      </c>
+      <c r="C398" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D398" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E398" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：船舶混合动力推进与控制重点实验室-大连海事大学；大连市水下机器人工程研究中心-大连海事大学</v>
+      </c>
+      <c r="F398" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G398" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H398" t="str" s="3">
+        <v>https://www.dlmu.edu.cn/info/1465/127618.htm
+https://www.dlmu.edu.cn/info/1465/123148.htm</v>
+      </c>
+      <c r="I398" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第32项；site:dlmu.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="399" ht="52.5" customHeight="1">
+      <c r="A399" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B399" t="str" s="3">
+        <v>辽宁科技大学</v>
+      </c>
+      <c r="C399" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D399" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E399" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：辽科大机械学院举办2026年辽宁省重点实验室学术报告会共促学科交叉新突破-辽宁科技大学—新闻网</v>
+      </c>
+      <c r="F399" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G399" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H399" t="str" s="3">
+        <v>https://www.ustl.edu.cn/news/info/1005/13502.htm</v>
+      </c>
+      <c r="I399" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第33项；site:ustl.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="400" ht="52.5" customHeight="1">
+      <c r="A400" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B400" t="str" s="3">
+        <v>长春工业大学</v>
+      </c>
+      <c r="C400" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D400" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E400" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F400" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G400" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H400" t="str" s="3"/>
+      <c r="I400" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第34项；site:ccut.edu.cn (开放课题 OR 开放基金) (机器人 OR 智能装备 OR 感知 OR 自主 OR 控制) (2026 OR 2027)</v>
+      </c>
+    </row>
+    <row r="401" ht="52.5" customHeight="1">
+      <c r="A401" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B401" t="str" s="3">
+        <v>东北电力大学</v>
+      </c>
+      <c r="C401" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D401" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E401" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：先进机器人机构与传感实验室-东北电力大学机械工程学院</v>
+      </c>
+      <c r="F401" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G401" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H401" t="str" s="3">
+        <v>https://mach.neepu.edu.cn/info/1232/3478.htm</v>
+      </c>
+      <c r="I401" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第35项；site:neepu.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="402" ht="52.5" customHeight="1">
+      <c r="A402" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B402" t="str" s="3">
+        <v>吉林农业大学</v>
+      </c>
+      <c r="C402" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D402" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E402" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：吉林省家政服务业研究中心2023年度开放课题申报指南-人文学院(家政学院）；吉林省家政服务业研究中心2022年度开放课题申报指南-人文学院(家政学院）</v>
+      </c>
+      <c r="F402" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G402" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H402" t="str" s="3">
+        <v>https://renwen.jlau.edu.cn/info/1041/2030.htm
+https://renwen.jlau.edu.cn/info/1041/1941.htm</v>
+      </c>
+      <c r="I402" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第36项；site:jlau.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="403" ht="52.5" customHeight="1">
+      <c r="A403" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B403" t="str" s="3">
+        <v>东北林业大学</v>
+      </c>
+      <c r="C403" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D403" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E403" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：关于申报森林生态系统可持续经营教育部重点实验室(东北林业大学)2026-2027年度开放基金的通知-东北林业大学森林生态系统可持续经营教育部重点实验室；东北林业大学木质新型材料教育部工程研究中心；森林植物生态学教育部重点实验室；开放基金管理办法-森林植物生态学教育部重点实验室；重点实验室开放基金管理办法（试行）-东北林业大学森林生态系统可持续经营教育部重点实验室；东北盐碱植被恢复与重建教育部重点实验室（东北林业大学）开放基金管理办法 （2021年修订）-东北盐碱植被恢复与重建教育部重点实验室（东北林业大学）；开放基金管理办法-林木遗传育种全国重点实验室(东北林业大学)</v>
+      </c>
+      <c r="F403" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G403" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H403" t="str" s="3">
+        <v>https://sfem.nefu.edu.cn/info/1151/1707.htm
+https://wnm.nefu.edu.cn/
+https://klp.nefu.edu.cn/
+https://klp.nefu.edu.cn/info/1044/1090.htm
+https://sfem.nefu.edu.cn/info/1185/1406.htm
+https://yjd.nefu.edu.cn/info/1217/1353.htm
+https://tblab.nefu.edu.cn/info/1079/1931.htm</v>
+      </c>
+      <c r="I403" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第37项；site:nefu.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="404" ht="52.5" customHeight="1">
+      <c r="A404" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B404" t="str" s="3">
+        <v>黑龙江大学</v>
+      </c>
+      <c r="C404" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D404" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E404" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：黑龙江省重点实验室建设管理暂行办法-黑龙江大学科学技术处；关于功能无机材料化学教育部重点实验室2025年度开放课题申请通知-功能无机材料化学教育部重点实验室；2013年开放课题基金-功能无机材料化学教育部重点实验室</v>
+      </c>
+      <c r="F404" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G404" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H404" t="str" s="3">
+        <v>https://kxjs.hlju.edu.cn/info/1158/1366.htm
+https://klfimc.hlju.edu.cn/info/1037/1608.htm
+https://klfimc.hlju.edu.cn/info/1027/1108.htm</v>
+      </c>
+      <c r="I404" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第38项；site:hlju.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="405" ht="52.5" customHeight="1">
+      <c r="A405" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B405" t="str" s="3">
+        <v>武汉理工大学</v>
+      </c>
+      <c r="C405" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D405" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E405" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：材料复合新技术全国重点实验室第八届学术委员会第二次会议在汉召开-武汉理工大学新闻经纬</v>
+      </c>
+      <c r="F405" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G405" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H405" t="str" s="3">
+        <v>https://news.whut.edu.cn/lgzx/202607/t20260703_1405418.shtml</v>
+      </c>
+      <c r="I405" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第39项；site:whut.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="406" ht="52.5" customHeight="1">
+      <c r="A406" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B406" t="str" s="3">
+        <v>湖北工业大学</v>
+      </c>
+      <c r="C406" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D406" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E406" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：开放课题指南-河湖健康智慧感知与生态修复教育部重点实验室；太阳能高效利用及储能运行控制湖北省重点实验室；发酵工程教育部重点实验室；2026年度开放基金申请指南-现代制造质量工程湖北省重点实验室；关于组织申报2026年度湖北工业大学省新型智库（培育）建设专项课题暨湖北工业研究院开放基金项目的通知-湖北工业大学科学技术发展研究院；2026年度开放研究基金项目支持指南公示-太阳能高效利用及储能运行控制湖北省重点实验室；2026年开放基金（基础研究类）申报指南征集通知-太阳能高效利用及储能运行控制湖北省重点实验室；发酵工程教育部重点实验室</v>
+      </c>
+      <c r="F406" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G406" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H406" t="str" s="3">
+        <v>https://ihperrl.hbut.edu.cn/kfjj/kfktzn.htm
+https://sees.hbut.edu.cn/
+https://klfe.hbut.edu.cn/
+https://mmqe.hbut.edu.cn/info/1047/2232.htm
+https://kjcy.hbut.edu.cn/info/1053/10485.htm
+https://sees.hbut.edu.cn/info/1021/2212.htm
+https://sees.hbut.edu.cn/info/1021/2192.htm
+https://klfe.hbut.edu.cn/__local/5/C4/39/43079976B693733A761A838CE2B_D2D65A07_303AB.pdf?e=.pdf</v>
+      </c>
+      <c r="I406" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第40项；site:hbut.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="407" ht="52.5" customHeight="1">
+      <c r="A407" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B407" t="str" s="3">
+        <v>河南科技大学</v>
+      </c>
+      <c r="C407" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D407" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E407" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：关于2025年开放基金资助名单的通告-高端轴承摩擦学技术与应用国家地方联合工程实验室；河南科技大学农学院实验室简介-河南科技大学农学院；高端轴承摩擦学技术与应用国家地方联合工程实验室；金属材料磨损控制与成型技术国家地方联合工程研究中心；高端轴承摩擦学技术与应用国家地方联合工程实验室张永振课题组：PTFE自润滑涂层界面改性研究取得进展-高端轴承摩擦学技术与应用国家地方联合工程实验室；傅丽华-高端轴承摩擦学技术与应用国家地方联合工程实验室；我校高端轴承摩擦学技术与应用国家地方联合工程实验室召开学术委员会暨专家咨询委员会工作会议-河南科技大学；高端轴承摩擦学技术与应用国家地方联合工程实验室/河南省材料摩擦学重点实验室召开第一届学术委员会暨专家咨询委员会-高端轴承摩擦学技术与应用国家地方联合工程实验室</v>
+      </c>
+      <c r="F407" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G407" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H407" t="str" s="3">
+        <v>https://tribo.haust.edu.cn/info/1112/1355.htm
+https://nx.haust.edu.cn/info/1058/1028.htm
+https://tribo.haust.edu.cn/
+https://nmcl.haust.edu.cn/
+https://tribo.haust.edu.cn/info/1123/1395.htm
+https://tribo.haust.edu.cn/info/1133/1435.htm
+https://www.haust.edu.cn/dyfxgndetail.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=76869&amp;wbtreeid=1063
+https://tribo.haust.edu.cn/info/1042/1264.htm</v>
+      </c>
+      <c r="I407" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第41项；site:haust.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="408" ht="52.5" customHeight="1">
+      <c r="A408" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B408" t="str" s="3">
+        <v>河南理工大学</v>
+      </c>
+      <c r="C408" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D408" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E408" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：《河南省空间大数据获取装备研制与应用工程技术研究中心2026年度开放基金资助课题》申请指南-河南理工大学测绘与空天信息学院；《中部粮食主产区国土生态与土地利用野外科学观测研究站2026年度开放基金资助课题》申请指南-河南理工大学测绘与国土信息工程学院；《自然资源部矿山时空信息与生态修复重点实验室2026年度开放基金资助课题》申请指南-河南理工大学测绘与空天信息学院；智能装备直驱技术与控制国际联合实验室管理办法（试行）....................；深井瓦斯抽采与围岩控制技术国家地方联合工程实验室开放基金申请指南（2025年度）-河南理工大学能源科学与工程学院</v>
+      </c>
+      <c r="F408" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G408" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H408" t="str" s="3">
+        <v>https://chxy.hpu.edu.cn/info/1056/7459.htm
+https://chxy.hpu.edu.cn/info/1056/7458.htm
+https://chxy.hpu.edu.cn/info/1056/7387.htm
+https://seea.hpu.edu.cn/virtual_attach_file.vsb?afc=4M7U8bMRTkMN7YnimG8nNQ2Um6fMR9DsoR7ZMlWkU8VVU490gihFp2hmCIa0LSyPUSy4UYyiLzCPLRAVMNl8nRVVozfVoRLioRTkM4n7M7VFnmv4U4AVnRVFMzGbnRGJv2nto4OeosMTQI70qIbtpYyPLm7Yg4UPozUJqdsnx&amp;e=.pdf&amp;nid=4194&amp;oid=1941714436&amp;tid=1212
+https://sese.hpu.edu.cn/info/1112/6547.htm</v>
+      </c>
+      <c r="I408" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第42项；site:hpu.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="409" ht="52.5" customHeight="1">
+      <c r="A409" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B409" t="str" s="3">
+        <v>河南大学</v>
+      </c>
+      <c r="C409" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D409" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E409" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：被诸多媒体报道。担任 Adv. Mater.，Adv. Energy Mater 等 10 余本知名期刊的独立审稿人。先后主持国家自然科学基金优秀青年项目、面上/青年项目、省市级自然科学基金项目、国家及地方重点实验室开放基金共 10 项。担任国自然、省、市级自然基金项目的评审专家。先后入选 Aggregate、Chin. J. Chem. 和 JMCA 杂志新锐科学家，荣获 Aggregate 优秀编委，多次入选全球前 2% 顶尖科学家榜单。</v>
+      </c>
+      <c r="F409" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G409" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H409" t="str" s="3">
+        <v>https://kyc.henu.edu.cn/__local/5/3B/29/A4FA17D21BF92996508D2E47656_80207749_2E123A.pdf</v>
+      </c>
+      <c r="I409" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第43项；site:henu.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="410" ht="52.5" customHeight="1">
+      <c r="A410" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B410" t="str" s="3">
+        <v>郑州轻工业大学</v>
+      </c>
+      <c r="C410" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D410" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E410" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F410" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G410" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H410" t="str" s="3"/>
+      <c r="I410" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第44项；site:zzuli.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="411" ht="52.5" customHeight="1">
+      <c r="A411" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B411" t="str" s="3">
+        <v>长沙理工大学</v>
+      </c>
+      <c r="C411" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D411" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E411" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：关于组织新进博士申报2026年上半年科研平台自由探索类开放基金项目的通知-长沙理工大学-科学技术处；关于下达长沙理工大学2026年上半年科研平台自由探索类开放基金项目立项的通知-人文与社会科学研究处；关于下达长沙理工大学2026年上半年科研平台自由探索类开放基金项目立项的通知-长沙理工大学-科学技术处</v>
+      </c>
+      <c r="F411" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G411" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H411" t="str" s="3">
+        <v>https://www.csust.edu.cn/kxyjb/info/1031/8608.htm
+https://www.csust.edu.cn/rwshkx/info/1179/11301.htm
+https://www.csust.edu.cn/kxyjb/info/1031/8622.htm</v>
+      </c>
+      <c r="I411" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第45项；site:csust.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="412" ht="52.5" customHeight="1">
+      <c r="A412" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B412" t="str" s="3">
+        <v>湖南科技大学</v>
+      </c>
+      <c r="C412" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D412" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E412" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：吕黎曙_湖南科技大学海洋实验室；测绘遥感信息工程湖南省重点实验室开放基金管理办法；地理空间信息技术国家地方联合工程实验室；测绘遥感信息工程湖南省重点实验室开放基金管理办法</v>
+      </c>
+      <c r="F412" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G412" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H412" t="str" s="3">
+        <v>https://marinelab.hnust.edu.cn/yjdw/hdzybzzbyaqjsyjry/069f2044792b4e58b059b68301d6a333.htm
+https://3s.hnust.edu.cn/docs//2021-03/492b541cbe0641fd8ff3063b75f9454a.pdf
+https://3s.hnust.edu.cn/yjdw/yjjgry/qtkyry/86074afe2f184e1c85e060a93861bae6.htm
+https://3s.hnust.edu.cn/docs/2025-09/5300c706a64e42289e973a6122594f31.pdf</v>
+      </c>
+      <c r="I412" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第46项；site:hnust.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="413" ht="52.5" customHeight="1">
+      <c r="A413" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B413" t="str" s="3">
+        <v>湘潭大学</v>
+      </c>
+      <c r="C413" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D413" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E413" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：湖南省普通高等学校重点实验室建设与管理暂行办法-湘潭大学科技处；转发湖南省科学技术厅关于印发《湖南省重点实验室建设与运行管理办法》的通知-湘潭大学科技处</v>
+      </c>
+      <c r="F413" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G413" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H413" t="str" s="3">
+        <v>https://kjc.xtu.edu.cn/info/1071/3880.htm
+https://kjc.xtu.edu.cn/info/1005/4326.htm</v>
+      </c>
+      <c r="I413" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第47项；site:xtu.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="414" ht="52.5" customHeight="1">
+      <c r="A414" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B414" t="str" s="3">
+        <v>湖南工业大学</v>
+      </c>
+      <c r="C414" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D414" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E414" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F414" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G414" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H414" t="str" s="3"/>
+      <c r="I414" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第48项；site:hut.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="415" ht="52.5" customHeight="1">
+      <c r="A415" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B415" t="str" s="3">
+        <v>山东理工大学</v>
+      </c>
+      <c r="C415" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D415" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E415" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F415" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G415" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H415" t="str" s="3"/>
+      <c r="I415" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第49项；site:sdut.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="416" ht="52.5" customHeight="1">
+      <c r="A416" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B416" t="str" s="3">
+        <v>青岛理工大学</v>
+      </c>
+      <c r="C416" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D416" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E416" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F416" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G416" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H416" t="str" s="3"/>
+      <c r="I416" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第50项；site:qut.edu.cn "开放基金" 2026 2027</v>
+      </c>
+    </row>
+    <row r="417" ht="52.5" customHeight="1">
+      <c r="A417" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B417" t="str" s="3">
+        <v>济南大学</v>
+      </c>
+      <c r="C417" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D417" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E417" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：山东省黄河三角洲生态环境重点实验室（筹）召开建设工作推进会-济南大学；济南大学省部级重点实验室开放基金管理办法（试行）-济南大学党委办公室 校长办公室</v>
+      </c>
+      <c r="F417" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G417" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H417" t="str" s="3">
+        <v>https://www.ujn.edu.cn/info/1047/337943.htm
+https://xiaoban.ujn.edu.cn/info/1157/2582.htm</v>
+      </c>
+      <c r="I417" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第51项；site:ujn.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="418" ht="52.5" customHeight="1">
+      <c r="A418" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B418" t="str" s="3">
+        <v>齐鲁工业大学（山东省科学院）</v>
+      </c>
+      <c r="C418" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D418" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E418" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：山东省数控机床功能部件关键技术重点实验室2026年度开放课题申请指南；山东省无人系统智能技术与装备重点实验室2026年度开放课题申请指南</v>
+      </c>
+      <c r="F418" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G418" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H418" t="str" s="3">
+        <v>https://sdjxy.qlu.edu.cn/2026/0721/c10761a281476/page.htm
+https://slx.qlu.edu.cn/_t1249/2026/0409/c3946a275414/page.htm</v>
+      </c>
+      <c r="I418" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第52项；site:qlu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="419" ht="52.5" customHeight="1">
+      <c r="A419" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B419" t="str" s="3">
+        <v>山东农业大学</v>
+      </c>
+      <c r="C419" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D419" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E419" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F419" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G419" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H419" t="str" s="3"/>
+      <c r="I419" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第53项；site:sdau.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="420" ht="52.5" customHeight="1">
+      <c r="A420" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B420" t="str" s="3">
+        <v>上海电机学院</v>
+      </c>
+      <c r="C420" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D420" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E420" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：无人机综合测试实验室</v>
+      </c>
+      <c r="F420" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G420" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H420" t="str" s="3">
+        <v>https://aist.sdju.edu.cn/2026/0622/c9436a152384/page.htm</v>
+      </c>
+      <c r="I420" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第54项；site:sdju.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="421" ht="52.5" customHeight="1">
+      <c r="A421" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B421" t="str" s="3">
+        <v>上海应用技术大学</v>
+      </c>
+      <c r="C421" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D421" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E421" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：上海市重点实验室建设与运行管理办法-信息公开网</v>
+      </c>
+      <c r="F421" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G421" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H421" t="str" s="3">
+        <v>https://info.sit.edu.cn/info/1961/29311.htm</v>
+      </c>
+      <c r="I421" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第55项；site:sit.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="422" ht="52.5" customHeight="1">
+      <c r="A422" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B422" t="str" s="3">
+        <v>南通大学</v>
+      </c>
+      <c r="C422" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D422" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E422" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：重点实验室名称：江苏省神经</v>
+      </c>
+      <c r="F422" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G422" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H422" t="str" s="3">
+        <v>https://kjc.ntu.edu.cn/_upload/article/files/62/24/047eb975429085c73d4013d974f1/104e1485-4869-472b-b0b9-f2ad2544a8a5.pdf</v>
+      </c>
+      <c r="I422" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第56项；site:ntu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="423" ht="52.5" customHeight="1">
+      <c r="A423" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B423" t="str" s="3">
+        <v>徐州工程学院</v>
+      </c>
+      <c r="C423" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D423" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E423" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F423" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G423" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H423" t="str" s="3"/>
+      <c r="I423" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第57项；site:xzit.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="424" ht="52.5" customHeight="1">
+      <c r="A424" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B424" t="str" s="3">
+        <v>淮阴工学院</v>
+      </c>
+      <c r="C424" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D424" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E424" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F424" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G424" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H424" t="str" s="3"/>
+      <c r="I424" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第58项；site:hyit.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="425" ht="52.5" customHeight="1">
+      <c r="A425" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B425" t="str" s="3">
+        <v>浙江科技大学</v>
+      </c>
+      <c r="C425" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D425" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E425" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F425" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G425" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H425" t="str" s="3"/>
+      <c r="I425" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第59项；site:zust.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="426" ht="52.5" customHeight="1">
+      <c r="A426" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B426" t="str" s="3">
+        <v>宁波大学</v>
+      </c>
+      <c r="C426" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D426" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E426" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F426" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G426" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H426" t="str" s="3"/>
+      <c r="I426" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第60项；site:nbu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="427" ht="52.5" customHeight="1">
+      <c r="A427" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B427" t="str" s="3">
+        <v>温州大学</v>
+      </c>
+      <c r="C427" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D427" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E427" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：全省滩涂整治工程技术与全寿命智能监测重点实验室2026年度开放项目申报通知-温州大学建筑工程学院；科研平台-温州大学建筑工程学院</v>
+      </c>
+      <c r="F427" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G427" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H427" t="str" s="3">
+        <v>https://cace.wzu.edu.cn/info/1702/157895.htm
+https://cace.wzu.edu.cn/xkky/kypt.htm</v>
+      </c>
+      <c r="I427" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第61项；site:wzu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="428" ht="52.5" customHeight="1">
+      <c r="A428" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B428" t="str" s="3">
+        <v>福州大学</v>
+      </c>
+      <c r="C428" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D428" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E428" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：数字能源福建省高校重点实验室开放课题指南-福州大学电气工程与自动化学院；数字能源福建省高校重点实验室2026年度开放课题评审结果公示-福州大学电气工程与自动化学院；福建省太赫兹功能器件与智能传感重点实验室；能源与环境光催化国家重点实验室；能源与环境光催化国家重点实验室；省部共建能源与环境光催化国家重点实验室</v>
+      </c>
+      <c r="F428" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G428" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H428" t="str" s="3">
+        <v>https://dqxy.fzu.edu.cn/info/1034/8270.htm
+https://dqxy.fzu.edu.cn/info/1034/8195.htm
+https://thz.fzu.edu.cn/
+https://kjc.fzu.edu.cn/__local/F/CF/10/67DDF34CC56CC0B560D75BD9778_B0F7475F_257A1.pdf?e=.pdf
+https://sklpee.fzu.edu.cn/__local/D/0A/43/44C0B3E68978756ADE4B46C2B33_4E0A31F0_2583B.pdf?e=.pdf
+https://kjc.fzu.edu.cn/__local/3/73/8F/F6FFBF2882A214DEB0C9BD6245E_92A84832_2E005.pdf?e=.pdf</v>
+      </c>
+      <c r="I428" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第62项；site:fzu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="429" ht="52.5" customHeight="1">
+      <c r="A429" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B429" t="str" s="3">
+        <v>华侨大学</v>
+      </c>
+      <c r="C429" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D429" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E429" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：华侨大学 XJZ--Home-- 机械系统与振动全国重点实验室开放课题，2026.01-2027.12，项目负责人</v>
+      </c>
+      <c r="F429" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G429" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H429" t="str" s="3">
+        <v>https://faculty.hqu.edu.cn/xujiangzhang/en/kyxm/243565/content/17268.htm</v>
+      </c>
+      <c r="I429" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第63项；site:hqu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="430" ht="52.5" customHeight="1">
+      <c r="A430" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B430" t="str" s="3">
+        <v>集美大学</v>
+      </c>
+      <c r="C430" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D430" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E430" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F430" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G430" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H430" t="str" s="3"/>
+      <c r="I430" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第64项；site:jmu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="431" ht="52.5" customHeight="1">
+      <c r="A431" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B431" t="str" s="3">
+        <v>江西理工大学</v>
+      </c>
+      <c r="C431" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D431" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E431" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：国家市场监督管理总局重点实验室（稀土产品检测与溯源）2026年度开放研究基金申请指南-江西理工大学科学技术处；战略有色金属绿色低碳冶金江西省重点实验室2025年度自由探索青年项目申请指南-江西理工大学科学技术处；多维智能感知与控制江西省重点实验室-江西理工大学信息工程学院；开放课题-江西理工大学分析测试中心；国家市场监督管理总局重点实验室（稀土产品检测与溯源）2025年度开放研究基金申请指南-江西理工大学科学技术处</v>
+      </c>
+      <c r="F431" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G431" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H431" t="str" s="3">
+        <v>https://kjc.jxust.edu.cn/info/1018/4591.htm
+https://kjc.jxust.edu.cn/info/1018/4502.htm
+https://ie.jxust.edu.cn/info/1050/2028.htm
+https://nfxcs.jxust.edu.cn/kfkt.htm
+https://kjc.jxust.edu.cn/info/1018/4146.htm</v>
+      </c>
+      <c r="I431" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第65项；site:jxust.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="432" ht="52.5" customHeight="1">
+      <c r="A432" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B432" t="str" s="3">
+        <v>华东交通大学</v>
+      </c>
+      <c r="C432" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D432" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E432" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：交通智能运维技术与装备教育部重点实验室2026年度开放课题申请指南-华东交通大学机电与车辆工程学院网站；山区土木工程安全与韧性全国重点实验室开放课题管理办法-山区土木工程安全与韧性全国重点实验室；关于公布交通智能运维技术与装备教育部重点实验室2025年度开放课题评审结果的通知-交通智能运维技术与装备教育部重点实验室；学术交流-山区土木工程安全与韧性全国重点实验室；交通智能运维技术与装备教育部重点实验室 2026 年度学术委员会会议顺利召开-交通智能运维技术与装备教育部重点实验室；全国重点实验室学术报告-山区土木工程安全与韧性全国重点实验室；规章制度-山区土木工程安全与韧性全国重点实验室；山区土木工程安全与韧性全国重点实验室 2026年度开放基金申请指南-山区土木工程安全与韧性全国重点实验室</v>
+      </c>
+      <c r="F432" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G432" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H432" t="str" s="3">
+        <v>https://me.ecjtu.edu.cn/info/1156/5774.htm
+https://sqtmqz.ecjtu.edu.cn/info/1030/3801.htm
+https://tiom.ecjtu.edu.cn/info/1047/3632.htm
+https://sqtmqz.ecjtu.edu.cn/kfjl/xsjl.htm
+https://tiom.ecjtu.edu.cn/info/1047/3662.htm
+https://sqtmqz.ecjtu.edu.cn/info/1034/3141.htm
+https://sqtmqz.ecjtu.edu.cn/kfjl/kfkt/gzzd.htm
+https://sqtmqz.ecjtu.edu.cn/info/1031/3831.htm</v>
+      </c>
+      <c r="I432" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第66项；site:ecjtu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="433" ht="52.5" customHeight="1">
+      <c r="A433" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B433" t="str" s="3">
+        <v>安徽理工大学</v>
+      </c>
+      <c r="C433" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D433" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E433" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：工业粉尘防控与职业安全健康教育部重点实验室2025、2026年度开放课题申请指南-工业粉尘防控与职业健康；煤炭无人化开采数智技术全国重点实验室；信息公告-煤炭无人化开采数智技术全国重点实验室；煤炭无人化开采数智技术全国重点实验室2026年度开放基金课题（第一批）申请指南-煤炭无人化开采数智技术全国重点实验室；2026年度工业粉尘深度净化与职业健康安全安徽省高校重点实验室开放基金课题申请指南-医学院；2026年度特种聚合物安徽省重点实验室开放基金申请指南-安徽理工大学化工与爆破学院欢迎您！</v>
+      </c>
+      <c r="F433" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G433" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H433" t="str" s="3">
+        <v>https://eklab.aust.edu.cn/info/1004/1214.htm
+https://cdsys.aust.edu.cn/
+https://cdsys.aust.edu.cn/index/xxgs.htm
+https://cdsys.aust.edu.cn/info/1021/2502.htm
+https://yxy.aust.edu.cn/info/1013/8872.htm
+https://scbe.aust.edu.cn/info/1055/8114.htm</v>
+      </c>
+      <c r="I433" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第67项；site:aust.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="434" ht="52.5" customHeight="1">
+      <c r="A434" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B434" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="C434" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D434" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E434" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：安徽省环境污染控制与资源化重点实验室 2025年度开放课题申报指南；开放课题申报指南（2025第二批）；开放课题申报指南（2025）；安徽建筑大学安徽省智能建筑与建筑节能重点实验室2025年开放课题评审结果公告；关于安徽省建筑经济与房地产管理研究中心、安徽省房地产与住房公积金研究院2022-2023年度开放课题（主任基金）结题评审结果的通知；关于开展2026年度安徽省智能建筑与建筑节能重点实验室开放课题（主任基金）项目结题评审工作的通知；安徽省地域环境健康与空间智慧感知工程研究中心 2025 年度开放课题（校外）申报通知；特种电线电缆国家地方联合工程研究中心2025年开放课题资助项目评审结果公告</v>
+      </c>
+      <c r="F434" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G434" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H434" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/resource/2025/1104/c9947a258976/page.htm
+https://www.ahjzu.edu.cn/gjgcsys/2025/1113/c9701a259373/page.htm
+https://www.ahjzu.edu.cn/gjgcsys/2025/1113/c9701a262080/page.htm
+https://www.ahjzu.edu.cn/Intelligent/2025/1224/c9785a261870/page.htm
+https://www.ahjzu.edu.cn/glxy/2026/0223/c6293a263902/page.htm
+https://www.ahjzu.edu.cn/Intelligent/2026/0414/c9785a268612/page.htm
+https://www.ahjzu.edu.cn/jzygh/2025/1103/c5892a258871/page.htm
+https://www.ahjzu.edu.cn/2026/0123/c845a263350/page.htm</v>
+      </c>
+      <c r="I434" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第68项；site:ahjzu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="435" ht="52.5" customHeight="1">
+      <c r="A435" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B435" t="str" s="3">
+        <v>广西师范大学</v>
+      </c>
+      <c r="C435" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D435" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E435" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：广西核物理与核技术重点实验室；4. 国际合作开放课题（拟资助 1~2 项，资助经费 8~10 万）；2025年广西多源信息挖掘与安全重点验室开放课题基金（自筹经费）申请指南；广西高校认知神经科学与应用心理重点实验室；2025年度广西高校认知神经科学与应用心理重点实验室自主课题和开放课题立项通知；开放课题；开放课题；实验室概况</v>
+      </c>
+      <c r="F435" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G435" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H435" t="str" s="3">
+        <v>https://np.gxnu.edu.cn/main.htm
+https://www.gxnu.edu.cn/_upload/article/files/a1/28/9c6a4aae485dba26d5f3db402900/32dbd39b-7479-4abe-a4cf-f5c99840786e.pdf
+https://mims.gxnu.edu.cn/2025/1011/c6728a327370/page.htm
+https://jyxb.gxnu.edu.cn/_upload/article/files/59/36/24143df940ebaabe6e2c9cfec0c4/14bf4e8a-5747-486d-991e-e16c71e30ad4.pdf
+https://jyxb.gxnu.edu.cn/2025/0430/c10387a314428/pagem.htm
+https://reae.gxnu.edu.cn/kfkt/list.htm
+https://reae.gxnu.edu.cn/kfjl/list.htm
+https://jyxb.gxnu.edu.cn/10384/listm.htm</v>
+      </c>
+      <c r="I435" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第69项；site:gxnu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="436" ht="52.5" customHeight="1">
+      <c r="A436" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B436" t="str" s="3">
+        <v>海南大学</v>
+      </c>
+      <c r="C436" t="str" s="3">
+        <v>海南</v>
+      </c>
+      <c r="D436" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E436" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：数字医学工程全国重点实验室（海南大学）2026年度开放课题申报指南-海南大学生物医学工程学院；热带海洋工程材料及评价全国重点实验室2026年开放研究课题申报指南-热带海洋工程材料及评价全国重点实验室；宋凤阁-南海海洋资源利用国家重点实验室；海南省食品营养与功能食品重点实验室开放课题申请指南（2026年）-食品科学与工程学院；开放课题-热带海洋工程材料及评价全国重点实验室</v>
+      </c>
+      <c r="F436" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G436" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H436" t="str" s="3">
+        <v>https://bme.hainanu.edu.cn/info/1051/11911.htm
+https://skltm.hainanu.edu.cn/info/1091/6891.htm
+https://hb.hainanu.edu.cn/nanhaihaiyang/info/1051/6722_1.htm
+https://foodsci.hainanu.edu.cn/info/1051/13784.htm
+https://skltm.hainanu.edu.cn/kxyj/kfkt.htm</v>
+      </c>
+      <c r="I436" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第70项；site:hainanu.edu.cn "开放课题" 2026 2027</v>
+      </c>
+    </row>
+    <row r="437" ht="52.5" customHeight="1">
+      <c r="A437" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B437" t="str" s="3">
+        <v>海南师范大学</v>
+      </c>
+      <c r="C437" t="str" s="3">
+        <v>海南</v>
+      </c>
+      <c r="D437" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E437" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：热带药用资源化学教育部重点实验室 2026开放课题申报通知 - 最新动态 - 教育部重点实验室；2026年度海南省激光技术与光电功能材料重点实验室 开放基金拟资助项目公示；海南省水环境污染治理与资源化重点实验室2026年度开放基金立项公告；关于海南师范大学 2026 年大学生创新创业开放基金（榕树基金）第二批项目申报暨首届 “创梦杯”OPC 创新创业大赛的补充通知 - 海南师范大学大学生就业网；海南省热带药用植物化学重点实验室 2026年度开放基金立项公告；海南省水环境污染治理与资源化重点实验室2026年度开放基金评审结果公示</v>
+      </c>
+      <c r="F437" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G437" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H437" t="str" s="3">
+        <v>https://sbgjsys.hainnu.edu.cn/html/2026/tzgg_new_0602/579.html
+https://wdxy.hainnu.edu.cn/2026/0609/c3498a165977/page.htm
+https://hgxy.hainnu.edu.cn/2026/0714/c3260a167152/page.htm
+https://jy.hainnu.edu.cn/index.php/web/Index/notice-detail?id=96
+https://hgxy.hainnu.edu.cn/2026/0720/c3260a167354/page.htm
+https://webplus.hainnu.edu.cn/_s68/2026/0630/c3260a166656/page.psp</v>
+      </c>
+      <c r="I437" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第71项；site:hainnu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="438" ht="52.5" customHeight="1">
+      <c r="A438" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B438" t="str" s="3">
+        <v>桂林理工大学</v>
+      </c>
+      <c r="C438" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D438" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E438" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：关于申请2026年度有色金属及材料加工新技术教育部重点实验室、广西光电材料与器件重点实验室开放基金的通知-广西光电材料与器件重点实验室；西安交通大学丁向东教授应邀为重点实验室做学术报告-广西光电材料与器件重点实验室</v>
+      </c>
+      <c r="F438" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G438" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H438" t="str" s="3">
+        <v>https://oem.glut.edu.cn/info/1045/1789.htm
+https://oem.glut.edu.cn/info/1039/1809.htm</v>
+      </c>
+      <c r="I438" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第72项；site:glut.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="439" ht="52.5" customHeight="1">
+      <c r="A439" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B439" t="str" s="3">
+        <v>西南科技大学</v>
+      </c>
+      <c r="C439" t="str" s="3">
+        <v>四川</v>
+      </c>
+      <c r="D439" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E439" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F439" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G439" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H439" t="str" s="3"/>
+      <c r="I439" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第73项；site:swust.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="440" ht="52.5" customHeight="1">
+      <c r="A440" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B440" t="str" s="3">
+        <v>西南大学</v>
+      </c>
+      <c r="C440" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D440" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E440" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：中心动态：西南大学李月臣教授团队在再生稻气候风险评估方向取得新进展-遥感大数据应用重庆市工程研究中心；岩溶环境重庆市重点实验室（西南大学）；实验室开放基金指南-发光分析与分子传感教育部重点实验室；岩溶环境重庆市重点实验室（西南大学）</v>
+      </c>
+      <c r="F440" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G440" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H440" t="str" s="3">
+        <v>https://rsdata.swu.edu.cn/info/1016/1353.htm
+https://karst.swu.edu.cn/__local/3/E8/0C/300F8CAD4E18090BD6389F6F9C9_A459B977_274E6.pdf?e=.pdf
+https://lams.swu.edu.cn/info/1016/1085.htm
+https://karst.swu.edu.cn/__local/0/63/36/85402D33401883D5E5E3D9B470A_A138647B_2A023.pdf?e=.pdf</v>
+      </c>
+      <c r="I440" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第74项；site:swu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="441" ht="52.5" customHeight="1">
+      <c r="A441" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B441" t="str" s="3">
+        <v>成都大学</v>
+      </c>
+      <c r="C441" t="str" s="3">
+        <v>四川</v>
+      </c>
+      <c r="D441" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E441" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：科研平台-计算机学院；关于申报2026年模式识别与智能信息处理四川省教育厅高校重点实验室开放基金项目的通知-计算机学院；2024年模式识别与智能信息处理高校重点实验室开放基金项目立项公告-模式识别与智能信息处理；肉类加工四川省重点实验室；2026年度开放基金项目申报公告-肉类加工四川省重点实验室；〖开放基金〗2026年度药食同源植物资源开发四川省教育厅高校重点实验室开放基金申报通知-药食同源植物资源开发四川省教育厅高校重点实验室；四川省智能康复系统感知与控制国际联合研究中心2025年度开放基金课题申报通知-电子信息与电气工程学院</v>
+      </c>
+      <c r="F441" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G441" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H441" t="str" s="3">
+        <v>https://computer.cdu.edu.cn/kxyj/kypt.htm
+https://computer.cdu.edu.cn/info/1023/12282.htm
+https://computer.cdu.edu.cn/zdsys/info/1012/1114.htm
+https://scmplab.cdu.edu.cn/
+https://scmplab.cdu.edu.cn/info/1027/2111.htm
+https://meprdlab.cdu.edu.cn/info/1006/1595.htm
+https://ele.cdu.edu.cn/info/1061/10210.htm</v>
+      </c>
+      <c r="I441" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第75项；site:cdu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="442" ht="52.5" customHeight="1">
+      <c r="A442" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B442" t="str" s="3">
+        <v>西华大学</v>
+      </c>
+      <c r="C442" t="str" s="3">
+        <v>四川</v>
+      </c>
+      <c r="D442" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E442" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：智能空地融合载具及管控教育部工程研究中心2026年度开放基金项目申报通知；汽车测控与安全四川省重点实验室、新能源汽车智能控制与仿真测试技术四川省工程研究中心 2026年度开放基金项目申报通知；智能空地融合载具及管控教育部工程研究中心；材料与表面技术教育部重点实验室2026年开放基金项目申报通知；汽车测控与安全四川省重点实验室、新能源汽车智能控制与仿真测试技术四川省工程研究中心2026年度开放基金项目结题 验收通知；四川省智能微电网群运行控制工程技术研究中心2026年度开放课题申请通知；智能空地融合载具及管控教育部工程研究中心</v>
+      </c>
+      <c r="F442" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G442" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H442" t="str" s="3">
+        <v>https://jybgczx.xhu.edu.cn/aa/a4/c11041a240292/page.htm
+https://qc.xhu.edu.cn/a7/f0/c692a239600/page.htm
+https://jybgczx.xhu.edu.cn/
+https://mse.xhu.edu.cn/_t316/b6/b3/c810a243379/page.htm
+https://qc.xhu.edu.cn/ab/fd/c692a240637/page.htm
+https://seie.xhu.edu.cn/c0/98/c1927a245912/page.htm
+https://hkht.xhu.edu.cn/_upload/article/files/41/df/ff9b2e4f4b8992d4a5ee72e24dce/b68d94d1-85b4-455e-8324-7a47dfa74024.pdf</v>
+      </c>
+      <c r="I442" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第76项；site:xhu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="443" ht="52.5" customHeight="1">
+      <c r="A443" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B443" t="str" s="3">
+        <v>贵州师范大学</v>
+      </c>
+      <c r="C443" t="str" s="3">
+        <v>贵州</v>
+      </c>
+      <c r="D443" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E443" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：“贵州省射电天文数据处理重点实验室首届学术委员会”和“基于FAST漂移扫描巡天的脉冲星统计观测和理论研究联合重点项目启动会”在贵州师范大学顺利召开-贵州师范大学物理与电子科学学院</v>
+      </c>
+      <c r="F443" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G443" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H443" t="str" s="3">
+        <v>https://phy.gznu.edu.cn/info/1081/93675.htm</v>
+      </c>
+      <c r="I443" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第77项；site:gznu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="444" ht="52.5" customHeight="1">
+      <c r="A444" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B444" t="str" s="3">
+        <v>云南大学</v>
+      </c>
+      <c r="C444" t="str" s="3">
+        <v>云南</v>
+      </c>
+      <c r="D444" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E444" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：云南省软件工程重点实验室文件</v>
+      </c>
+      <c r="F444" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G444" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H444" t="str" s="3">
+        <v>https://www.sei.ynu.edu.cn/__local/B/2E/3A/C75AF1DA5279CFD48D4DBFE7737_F10A5B61_59511.pdf</v>
+      </c>
+      <c r="I444" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第78项；site:ynu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="445" ht="52.5" customHeight="1">
+      <c r="A445" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B445" t="str" s="3">
+        <v>云南农业大学</v>
+      </c>
+      <c r="C445" t="str" s="3">
+        <v>云南</v>
+      </c>
+      <c r="D445" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E445" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：云南省作物生产与智慧农业重点实验室2026年度开放基金课题申请指南-云南农业大学；云南省农业微生物组重点实验室（筹）2026年度开放课题申请指南-云南农业大学</v>
+      </c>
+      <c r="F445" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G445" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H445" t="str" s="3">
+        <v>https://www.ynau.edu.cn/info/1060/87504.htm
+https://www.ynau.edu.cn/info/1060/79544.htm</v>
+      </c>
+      <c r="I445" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第79项；site:ynau.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="446" ht="52.5" customHeight="1">
+      <c r="A446" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B446" t="str" s="3">
+        <v>西藏农牧学院</v>
+      </c>
+      <c r="C446" t="str" s="3">
+        <v>西藏</v>
+      </c>
+      <c r="D446" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E446" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：清华大学水圈全国重点实验室与西藏农牧大学合作交流会-西藏农牧大学-科研处；我校教师张存副教授获教育部重点实验室开放基金资助-西藏农牧大学 水利土木工程学院</v>
+      </c>
+      <c r="F446" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G446" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H446" t="str" s="3">
+        <v>https://www.xza.edu.cn/keyanchu/info/1032/11192.htm
+https://www.xza.edu.cn/sltmgcxy/info/1701/12481.htm</v>
+      </c>
+      <c r="I446" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第80项；site:xza.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="447" ht="52.5" customHeight="1">
+      <c r="A447" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B447" t="str" s="3">
+        <v>西安邮电大学</v>
+      </c>
+      <c r="C447" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D447" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E447" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F447" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G447" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H447" t="str" s="3"/>
+      <c r="I447" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第81项；site:xupt.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="448" ht="52.5" customHeight="1">
+      <c r="A448" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B448" t="str" s="3">
+        <v>陕西科技大学</v>
+      </c>
+      <c r="C448" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D448" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E448" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F448" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G448" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H448" t="str" s="3"/>
+      <c r="I448" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第82项；site:sust.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="449" ht="52.5" customHeight="1">
+      <c r="A449" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B449" t="str" s="3">
+        <v>陕西理工大学</v>
+      </c>
+      <c r="C449" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D449" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E449" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F449" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G449" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H449" t="str" s="3"/>
+      <c r="I449" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第83项；site:snut.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="450" ht="52.5" customHeight="1">
+      <c r="A450" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B450" t="str" s="3">
+        <v>西北师范大学</v>
+      </c>
+      <c r="C450" t="str" s="3">
+        <v>甘肃</v>
+      </c>
+      <c r="D450" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E450" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：甘肃省绿洲资源环境与可持续发展重点实验室2025年学术委员会会议在西北师大举行；2025年生态功能高分子材料教育部重点实验室学术委员会会议在西北师大召开</v>
+      </c>
+      <c r="F450" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G450" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H450" t="str" s="3">
+        <v>https://www.nwnu.edu.cn/2025/1210/c8722a266792/page.htm
+https://www.nwnu.edu.cn/2025/1028/c7022a262751/page.htm</v>
+      </c>
+      <c r="I450" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第84项；site:nwnu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="451" ht="52.5" customHeight="1">
+      <c r="A451" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B451" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C451" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D451" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E451" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：科研平台-西北土地退化与生态恢复国家重点实验室培育基地；宁夏科学工程计算与数据分析重点实验室-宁夏大学；省部共建煤炭高效利用与绿色化工国家重点实验室开放课题管理办法-省部共建国家重点实验室；实验室简介-宁夏科学工程计算与数据分析重点实验室</v>
+      </c>
+      <c r="F451" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G451" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H451" t="str" s="3">
+        <v>https://eco.nxu.edu.cn/hzjl/gjhz/kypt.htm
+https://www.nxu.edu.cn/info/1443/11405.htm
+https://nengyuan.nxu.edu.cn/info/1033/1371.htm
+https://jssjfx.nxu.edu.cn/sysjj.htm</v>
+      </c>
+      <c r="I451" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第85项；site:nxu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="452" ht="52.5" customHeight="1">
+      <c r="A452" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B452" t="str" s="3">
+        <v>宁夏理工学院</v>
+      </c>
+      <c r="C452" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D452" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E452" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F452" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G452" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H452" t="str" s="3"/>
+      <c r="I452" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第86项；site:nxist.com "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="453" ht="52.5" customHeight="1">
+      <c r="A453" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B453" t="str" s="3">
+        <v>青海民族大学</v>
+      </c>
+      <c r="C453" t="str" s="3">
+        <v>青海</v>
+      </c>
+      <c r="D453" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E453" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F453" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G453" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H453" t="str" s="3"/>
+      <c r="I453" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第87项；site:qhmu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="454" ht="52.5" customHeight="1">
+      <c r="A454" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B454" t="str" s="3">
+        <v>新疆农业大学</v>
+      </c>
+      <c r="C454" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D454" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E454" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：农业农村部西北绿洲农业环境重点实验室2026年度开放基金项目申请指南</v>
+      </c>
+      <c r="F454" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G454" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H454" t="str" s="3">
+        <v>https://kyc.xjau.edu.cn/2026/0403/c2905a114499/page.psp</v>
+      </c>
+      <c r="I454" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第88项；site:xjau.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="455" ht="52.5" customHeight="1">
+      <c r="A455" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B455" t="str" s="3">
+        <v>石河子大学</v>
+      </c>
+      <c r="C455" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D455" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E455" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：计算智能与网络信息安全兵团重点实验室2024年度开放课题基金申请指南</v>
+      </c>
+      <c r="F455" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G455" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H455" t="str" s="3">
+        <v>https://cs.shzu.edu.cn/_t513/2024/0921/c12051a209837/page.htm</v>
+      </c>
+      <c r="I455" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第89项；site:shzu.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="456" ht="52.5" customHeight="1">
+      <c r="A456" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B456" t="str" s="3">
+        <v>塔里木大学</v>
+      </c>
+      <c r="C456" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D456" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E456" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：李树伟教授团队揭示生物活性小分子紫草素促进小鼠皮肤烧烫伤创伤愈合机制-兵团塔里木盆地生物资源保护利用重点实验室</v>
+      </c>
+      <c r="F456" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G456" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H456" t="str" s="3">
+        <v>https://lab.taru.edu.cn/info/14074/255568.htm</v>
+      </c>
+      <c r="I456" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第90项；site:taru.edu.cn "开放基金" 机器人 感知 2026 2027</v>
+      </c>
+    </row>
+    <row r="457" ht="52.5" customHeight="1">
+      <c r="A457" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B457" t="str" s="3">
+        <v>港理工/无人自主系统研究中心</v>
+      </c>
+      <c r="C457" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D457" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E457" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F457" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G457" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H457" t="str" s="3"/>
+      <c r="I457" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第91项；site:polyu.edu.hk/rcuas "funding" "application"</v>
+      </c>
+    </row>
+    <row r="458" ht="52.5" customHeight="1">
+      <c r="A458" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B458" t="str" s="3">
+        <v>港理工/智能可穿戴研究院</v>
+      </c>
+      <c r="C458" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D458" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E458" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F458" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G458" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H458" t="str" s="3"/>
+      <c r="I458" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第92项；site:polyu.edu.hk/riiwear "funding" "eligible"</v>
+      </c>
+    </row>
+    <row r="459" ht="52.5" customHeight="1">
+      <c r="A459" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B459" t="str" s="3">
+        <v>港理工/辅助科技研究中心</v>
+      </c>
+      <c r="C459" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D459" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E459" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F459" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G459" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H459" t="str" s="3"/>
+      <c r="I459" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第93项；site:polyu.edu.hk "Assistive Technology" "funding" "application"</v>
+      </c>
+    </row>
+    <row r="460" ht="52.5" customHeight="1">
+      <c r="A460" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B460" t="str" s="3">
+        <v>港理工/深圳研究院</v>
+      </c>
+      <c r="C460" t="str" s="3">
+        <v>广东深圳</v>
+      </c>
+      <c r="D460" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E460" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F460" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G460" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H460" t="str" s="3"/>
+      <c r="I460" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第94项；site:polyu-szbase.com 开放 基金 2026</v>
+      </c>
+    </row>
+    <row r="461" ht="52.5" customHeight="1">
+      <c r="A461" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B461" t="str" s="3">
+        <v>澳门大学/协作机器人与软体机器人实验室</v>
+      </c>
+      <c r="C461" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D461" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E461" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F461" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G461" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H461" t="str" s="3"/>
+      <c r="I461" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第95项；site:um.edu.mo "开放" "机器人" "基金"</v>
+      </c>
+    </row>
+    <row r="462" ht="52.5" customHeight="1">
+      <c r="A462" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B462" t="str" s="3">
+        <v>澳门大学/无人系统与控制实验室</v>
+      </c>
+      <c r="C462" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D462" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E462" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F462" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G462" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H462" t="str" s="3"/>
+      <c r="I462" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第96项；site:um.edu.mo "open research" "control" "2026"</v>
+      </c>
+    </row>
+    <row r="463" ht="52.5" customHeight="1">
+      <c r="A463" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B463" t="str" s="3">
+        <v>华南理工/机器人系统集成与无人船平台</v>
+      </c>
+      <c r="C463" t="str" s="3">
+        <v>广东广州</v>
+      </c>
+      <c r="D463" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E463" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F463" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G463" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H463" t="str" s="3"/>
+      <c r="I463" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第97项；site:scut.edu.cn "开放基金" "机器人" "无人船"</v>
+      </c>
+    </row>
+    <row r="464" ht="52.5" customHeight="1">
+      <c r="A464" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B464" t="str" s="3">
+        <v>中科院自动化所/科研平台目录</v>
+      </c>
+      <c r="C464" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D464" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E464" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所；多模态人工智能系统全国重点实验室副主任招聘启事----中国科学院自动化研究所</v>
+      </c>
+      <c r="F464" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G464" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H464" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html
+https://www.ia.cas.cn/qtgn/tzgg/202510/t20251030_7999657.html</v>
+      </c>
+      <c r="I464" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第98项；site:ia.cas.cn "科研平台" "重点实验室"</v>
+      </c>
+    </row>
+    <row r="465" ht="52.5" customHeight="1">
+      <c r="A465" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B465" t="str" s="3">
+        <v>西北工业大学/机器人及无人系统平台</v>
+      </c>
+      <c r="C465" t="str" s="3">
+        <v>陕西西安</v>
+      </c>
+      <c r="D465" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E465" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：本次定向查询未定位具体开放公告/平台目录</v>
+      </c>
+      <c r="F465" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G465" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H465" t="str" s="3"/>
+      <c r="I465" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第99项；site:nwpu.edu.cn "开放基金" "机器人" "2027"</v>
+      </c>
+    </row>
+    <row r="466" ht="52.5" customHeight="1">
+      <c r="A466" t="str" s="3">
+        <v>2026-10-09接续机构发现</v>
+      </c>
+      <c r="B466" t="str" s="3">
+        <v>重庆大学/省部级相关平台</v>
+      </c>
+      <c r="C466" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D466" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E466" t="str" s="3">
+        <v>检索2026/2027及历史机制；定位入口：山区土木工程安全与韧性全国重点实验室 2025年度开放基金申请指南-重庆大学土木工程学院</v>
+      </c>
+      <c r="F466" t="str" s="3">
+        <v>机构完整目录尚未取得；本行只记录发现阶段，待逐平台补查；不得解释为无开放基金。</v>
+      </c>
+      <c r="G466" t="str" s="3">
+        <v>发现检索已执行；逐室核验见其他记录。</v>
+      </c>
+      <c r="H466" t="str" s="3">
+        <v>https://civil.cqu.edu.cn/info/1327/17713.htm</v>
+      </c>
+      <c r="I466" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第100项；site:cqu.edu.cn "开放课题" "机器人" "2027"</v>
+      </c>
+    </row>
+    <row r="467" ht="52.5" customHeight="1">
+      <c r="A467" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B467" t="str" s="3">
+        <v>成都大学</v>
+      </c>
+      <c r="C467" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="D467" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E467" t="str" s="3">
+        <v>模式识别与智能信息处理四川省教育厅高校重点实验室；2026；N029；正式年度通知已读；具体指南验证码阻塞</v>
+      </c>
+      <c r="F467" t="str" s="3">
+        <v>需下载2026修订版指南，核实际任务、校外资格、金额、合作、周期、经费及外拨、成果和IP。正文截止已过，不列首页。</v>
+      </c>
+      <c r="G467" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H467" t="str" s="3">
+        <v>https://computer.cdu.edu.cn/info/1023/12282.htm</v>
+      </c>
+      <c r="I467" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="468" ht="52.5" customHeight="1">
+      <c r="A468" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B468" t="str" s="3">
+        <v>成都大学</v>
+      </c>
+      <c r="C468" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="D468" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E468" t="str" s="3">
+        <v>四川省智能康复系统感知与控制国际联合研究中心；2025；N030；官方2025通知搜索定位；首次打开超时</v>
+      </c>
+      <c r="F468" t="str" s="3">
+        <v>需完整2025正文及附件；2026/2027新指南未取得。逐项核任务、校外资格、金额、截止、合作及经费、周期、成果、IP、提交。</v>
+      </c>
+      <c r="G468" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H468" t="str" s="3">
+        <v>https://ele.cdu.edu.cn/info/1061/10210.htm</v>
+      </c>
+      <c r="I468" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="469" ht="52.5" customHeight="1">
+      <c r="A469" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B469" t="str" s="3">
+        <v>西华大学</v>
+      </c>
+      <c r="C469" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="D469" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E469" t="str" s="3">
+        <v>智能空地融合载具及管控教育部工程研究中心；2026；N031；官方2026通知搜索定位；首次打开412</v>
+      </c>
+      <c r="F469" t="str" s="3">
+        <v>需完整2026正文及指南/管理/申请附件，确认机器人自主系统任务与全部申报经费条款；2027未取得。</v>
+      </c>
+      <c r="G469" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H469" t="str" s="3">
+        <v>https://jybgczx.xhu.edu.cn/aa/a4/c11041a240292/page.htm</v>
+      </c>
+      <c r="I469" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="470" ht="52.5" customHeight="1">
+      <c r="A470" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B470" t="str" s="3">
+        <v>云南农业大学</v>
+      </c>
+      <c r="C470" t="str" s="3">
+        <v>云南·昆明</v>
+      </c>
+      <c r="D470" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E470" t="str" s="3">
+        <v>云南省作物生产与智慧农业重点实验室；2026；N032；官方2026通知搜索定位；首次打开412</v>
+      </c>
+      <c r="F470" t="str" s="3">
+        <v>需完整2026正文及附件，先核任务；无农机机器人及相关感知控制任务则剔除。其余资格、金额、截止、合作、经费、成果、IP待核。</v>
+      </c>
+      <c r="G470" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H470" t="str" s="3">
+        <v>https://www.ynau.edu.cn/info/1060/87504.htm</v>
+      </c>
+      <c r="I470" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="471" ht="52.5" customHeight="1">
+      <c r="A471" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B471" t="str" s="3">
+        <v>天津工业大学</v>
+      </c>
+      <c r="C471" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D471" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E471" t="str" s="3">
+        <v>天津市电气装备智能控制重点实验室；2021；N033；正式历史指南已读；2026/2027未取得</v>
+      </c>
+      <c r="F471" t="str" s="3">
+        <v>2026/2027新年度指南未取得；历史申请模板及任务书的具体结题数量、科目和外拨待取得。</v>
+      </c>
+      <c r="G471" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H471" t="str" s="3">
+        <v>https://aeeet.tiangong.edu.cn/2021/0816/c6096a69693/page.psp</v>
+      </c>
+      <c r="I471" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="472" ht="52.5" customHeight="1">
+      <c r="A472" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B472" t="str" s="3">
+        <v>太原理工大学／山西虹安科技股份有限公司</v>
+      </c>
+      <c r="C472" t="str" s="3">
+        <v>山西·晋中</v>
+      </c>
+      <c r="D472" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E472" t="str" s="3">
+        <v>受限空间应急救援生命通道构建技术与装备山西省重点实验室；2026；N034；官方正式指南已核，当前申报窗口内</v>
+      </c>
+      <c r="F472" t="str" s="3">
+        <v>申请书下载有验证码；需原表以核额外资格/限项与条款；经费科目/报销/外拨/拨付和成果IP未载，需正式办法或主办方书面答复。</v>
+      </c>
+      <c r="G472" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H472" t="str" s="3">
+        <v>https://aqyj.tyut.edu.cn/info/1085/12050.htm</v>
+      </c>
+      <c r="I472" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="473" ht="52.5" customHeight="1">
+      <c r="A473" t="str" s="3">
+        <v>2026-10-09接续项目核验</v>
+      </c>
+      <c r="B473" t="str" s="3">
+        <v>辽宁工程技术大学</v>
+      </c>
+      <c r="C473" t="str" s="3">
+        <v>辽宁·阜新</v>
+      </c>
+      <c r="D473" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E473" t="str" s="3">
+        <v>矿山液压技术与装备国家地方联合工程研究中心；2023；N035；正式历史指南已读；实施方案PDF超时</v>
+      </c>
+      <c r="F473" t="str" s="3">
+        <v>需2023实施方案PDF及申请附件以补全经费、结题指标；2026/2027指南未取得，不能套用历史年龄及条款。</v>
+      </c>
+      <c r="G473" t="str" s="3">
+        <v>仅完成所列年度已取得资料；其他平台年度继续补查。</v>
+      </c>
+      <c r="H473" t="str" s="3">
+        <v>https://jxgcxy.lntu.edu.cn/info/1056/4059.htm</v>
+      </c>
+      <c r="I473" t="str" s="3">
+        <v>resume_sources_20261009.json；字段来源为对应官方通知/首次附件返回</v>
+      </c>
+    </row>
+    <row r="474" ht="52.5" customHeight="1">
+      <c r="A474" t="str" s="3">
+        <v>2026-10-09目录/资格核验</v>
+      </c>
+      <c r="B474" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C474" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D474" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E474" t="str" s="3">
+        <v>取得校历4页实验室总目录；定位机器人、协作机器人、软传感执行器机器人、无人系统、控制、自动化、沉浸交互、图像处理、视像处理及医工等平台。</v>
+      </c>
+      <c r="F474" t="str" s="3">
+        <v>各室对外开放机制需逐项查；教学实验室不等同设开放基金。</v>
+      </c>
+      <c r="G474" t="str" s="3">
+        <v>部分目录/资格已核；相关平台机制待逐项完成。</v>
+      </c>
+      <c r="H474" t="str" s="3">
+        <v>https://reg.um.edu.mo/download/um-academic-calendar/11labs.pdf</v>
+      </c>
+      <c r="I474" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="475" ht="52.5" customHeight="1">
+      <c r="A475" t="str" s="3">
+        <v>2026-10-09目录/资格核验</v>
+      </c>
+      <c r="B475" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C475" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D475" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E475" t="str" s="3">
+        <v>取得官方实验室/研究院/中心总目录及12个相关中心入口；覆盖先进制造、可穿戴、智慧老龄、辅助科技、电动车、未来交通、无人系统、低空经济、轨道交通等。</v>
+      </c>
+      <c r="F475" t="str" s="3">
+        <v>两中心页面首次失败；各中心外部负责人机制与年度窗口继续查，不能把已获资助列表当受理公告。</v>
+      </c>
+      <c r="G475" t="str" s="3">
+        <v>部分目录/资格已核；相关平台机制待逐项完成。</v>
+      </c>
+      <c r="H475" t="str" s="3">
+        <v>https://www.polyu.edu.hk/research/labs-institutes-centres/</v>
+      </c>
+      <c r="I475" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="476" ht="52.5" customHeight="1">
+      <c r="A476" t="str" s="3">
+        <v>2026-10-09目录/资格核验</v>
+      </c>
+      <c r="B476" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C476" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D476" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E476" t="str" s="3">
+        <v>校级科研平台目录已读，列气候前沿、人才大数据、智慧医疗3项；智慧医疗相关基金定向查，未取得正式开放指南。</v>
+      </c>
+      <c r="F476" t="str" s="3">
+        <v>校级页面非所有学院实验室目录；省部级旧目录复用，学院层级仍需核。</v>
+      </c>
+      <c r="G476" t="str" s="3">
+        <v>部分目录/资格已核；相关平台机制待逐项完成。</v>
+      </c>
+      <c r="H476" t="str" s="3">
+        <v>https://www.nuist.edu.cn/kxyj/xjkypt.htm</v>
+      </c>
+      <c r="I476" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="477" ht="52.5" customHeight="1">
+      <c r="A477" t="str" s="3">
+        <v>2026-10-09目录/资格核验</v>
+      </c>
+      <c r="B477" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C477" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D477" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E477" t="str" s="3">
+        <v>RIAM第五轮2025指南：申请人限PolyU全职学术人员且RIAM成员/RAP及以上；排除作为校外负责人开放基金。PAIR联合高校种子基金指南须教职工SSO登录。</v>
+      </c>
+      <c r="F477" t="str" s="3">
+        <v>PAIR合作方资格、外部经费、任务范围与受理窗口未取得；不以HK100万上限认定可申请。</v>
+      </c>
+      <c r="G477" t="str" s="3">
+        <v>部分目录/资格已核；相关平台机制待逐项完成。</v>
+      </c>
+      <c r="H477" t="str" s="3">
+        <v>https://www.polyu.edu.hk/riam/research/funding-opportunities/
+https://www.polyu.edu.hk/pair/intranet/guidelines-and-procedures/?sc_lang=en</v>
+      </c>
+      <c r="I477" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
       </c>
     </row>
   </sheetData>
@@ -30875,21 +34212,61 @@
     </row>
     <row r="102" ht="96" customHeight="1">
       <c r="A102" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B102" t="n" s="13">
+        <v>44434</v>
+      </c>
+      <c r="C102" t="str" s="14">
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+      </c>
+      <c r="D102" t="str" s="15">
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+      </c>
+      <c r="E102" t="str" s="15">
+        <v>重点2万元/项；一般1万元/项。</v>
+      </c>
+      <c r="F102" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="103" ht="96" customHeight="1">
+      <c r="A103" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B103" t="n" s="13">
+        <v>45163</v>
+      </c>
+      <c r="C103" t="str" s="14">
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+      </c>
+      <c r="D103" t="str" s="15">
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+      </c>
+      <c r="E103" t="str" s="15">
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+      </c>
+      <c r="F103" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="104" ht="96" customHeight="1">
+      <c r="A104" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B102" t="n" s="13">
+      <c r="B104" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C102" t="str" s="14">
+      <c r="C104" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D102" t="str" s="15">
+      <c r="D104" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E102" t="str" s="15">
+      <c r="E104" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F102" t="str" s="16">
+      <c r="F104" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -31085,8 +34462,8 @@
     <hyperlink ref="F96" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C97" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F97" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F102" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F104" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C98" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F98" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C99" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -31097,6 +34474,10 @@
     <hyperlink ref="F101" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F102" ns1:id="rIdResume103"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdResume104"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -32667,136 +36048,240 @@
       </c>
     </row>
     <row r="53" ht="66" customHeight="1">
-      <c r="A53" s="20" t="str">
+      <c r="A53" t="str" s="20">
+        <v>线索待核</v>
+      </c>
+      <c r="B53" t="str" s="13">
+        <v>未确认</v>
+      </c>
+      <c r="C53" t="str" s="14">
+        <v>成都大学·四川省智能康复系统感知与控制国际联合研究中心</v>
+      </c>
+      <c r="D53" t="str" s="15">
+        <v>年度具体任务尚未取得；智能康复平台仅作相关候选。</v>
+      </c>
+      <c r="E53" t="str" s="15">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="F53" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G53" t="str" s="3">
+        <v>需完整2025正文及附件；2026/2027新指南未取得。逐项核任务、校外资格、金额、截止、合作及经费、周期、成果、IP、提交。</v>
+      </c>
+      <c r="H53" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+    </row>
+    <row r="54" ht="66" customHeight="1">
+      <c r="A54" t="str" s="20">
+        <v>线索待核</v>
+      </c>
+      <c r="B54" t="str" s="13">
+        <v>未确认</v>
+      </c>
+      <c r="C54" t="str" s="14">
+        <v>西华大学·智能空地融合载具及管控教育部工程研究中心</v>
+      </c>
+      <c r="D54" t="str" s="15">
+        <v>年度具体无人/空地载具任务待取得；不把平台名当年度任务。</v>
+      </c>
+      <c r="E54" t="str" s="15">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="F54" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G54" t="str" s="3">
+        <v>需完整2026正文及指南/管理/申请附件，确认机器人自主系统任务与全部申报经费条款；2027未取得。</v>
+      </c>
+      <c r="H54" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+    </row>
+    <row r="55" ht="66" customHeight="1">
+      <c r="A55" t="str" s="20">
+        <v>线索待核</v>
+      </c>
+      <c r="B55" t="str" s="13">
+        <v>未确认</v>
+      </c>
+      <c r="C55" t="str" s="14">
+        <v>云南农业大学·云南省作物生产与智慧农业重点实验室</v>
+      </c>
+      <c r="D55" t="str" s="15">
+        <v>具体任务未取得；须确认是否包含农机机器人/感知控制，不能因智慧农业名称保留为相关项目。</v>
+      </c>
+      <c r="E55" t="str" s="15">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="F55" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G55" t="str" s="3">
+        <v>需完整2026正文及附件，先核任务；无农机机器人及相关感知控制任务则剔除。其余资格、金额、截止、合作、经费、成果、IP待核。</v>
+      </c>
+      <c r="H55" t="str" s="3">
+        <v>未取得/公开正文未载</v>
+      </c>
+    </row>
+    <row r="56" ht="66" customHeight="1">
+      <c r="A56" s="20" t="str">
         <v>方向待核·公告已发布</v>
       </c>
-      <c r="B53" s="13" t="d">
+      <c r="B56" s="13" t="d">
         <v>2026-10-10T00:00:00.000Z</v>
       </c>
-      <c r="C53" s="14" t="str">
+      <c r="C56" s="14" t="str">
         <v>新疆工程学院·新疆煤炭资源绿色开采教育部重点实验室</v>
       </c>
-      <c r="D53" s="15" t="str">
+      <c r="D56" s="15" t="str">
         <v>方向待核：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。</v>
       </c>
-      <c r="E53" s="15" t="str">
+      <c r="E56" s="15" t="str">
         <v>5—10万元</v>
       </c>
-      <c r="F53" s="16" t="str">
+      <c r="F56" s="16" t="str">
         <v>公告</v>
       </c>
-      <c r="G53" s="3" t="str">
+      <c r="G56" s="3" t="str">
         <v>筛选/证据缺口：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。
 知识产权：已取得公开资料未载明知识产权的完整条款。</v>
       </c>
-      <c r="H53" s="3" t="str">
+      <c r="H56" s="3" t="str">
         <v>gcxykfkt2026@163.com</v>
       </c>
     </row>
-    <row r="54" ht="66" customHeight="1">
-      <c r="A54" s="20" t="str">
+    <row r="57" ht="66" customHeight="1">
+      <c r="A57" s="20" t="str">
         <v>方向待核·公告已发布</v>
       </c>
-      <c r="B54" s="13" t="d">
+      <c r="B57" s="13" t="d">
         <v>2026-10-12T00:00:00.000Z</v>
       </c>
-      <c r="C54" s="14" t="str">
+      <c r="C57" s="14" t="str">
         <v>中北大学·电子测试技术全国重点实验室</v>
       </c>
-      <c r="D54" s="15" t="str">
+      <c r="D57" s="15" t="str">
         <v>方向待核：本期方向为电子测试与仪器，正文未取得明确机器人任务证据；机器人文字出现在相邻文章，不能据此保留。</v>
       </c>
-      <c r="E54" s="15" t="str">
+      <c r="E57" s="15" t="str">
         <v>每项不超过10万元。</v>
       </c>
-      <c r="F54" s="16" t="str">
+      <c r="F57" s="16" t="str">
         <v>公告</v>
       </c>
-      <c r="G54" s="3" t="str">
+      <c r="G57" s="3" t="str">
         <v>筛选/证据缺口：本期方向为电子测试与仪器，正文未取得明确机器人任务证据；机器人文字出现在相邻文章，不能据此保留。
 经费使用及外拨：公告仅说明基金由实验室管理，未明确外拨和开支细则，须查管理办法或合同。
 知识产权：已取得公开资料未载明知识产权的完整条款。</v>
       </c>
-      <c r="H54" s="3" t="str">
+      <c r="H57" s="3" t="str">
         <v>zhangle@nuc.edu.cn</v>
       </c>
     </row>
-    <row r="55" ht="66" customHeight="1">
-      <c r="A55" s="20" t="str">
+    <row r="58" ht="66" customHeight="1">
+      <c r="A58" s="20" t="str">
         <v>方向待核·公告已发布</v>
       </c>
-      <c r="B55" s="13" t="d">
+      <c r="B58" s="13" t="d">
         <v>2026-10-31T00:00:00.000Z</v>
       </c>
-      <c r="C55" s="14" t="str">
+      <c r="C58" s="14" t="str">
         <v>中国科学技术大学·脑启发智能感知与认知教育部重点实验室</v>
       </c>
-      <c r="D55" s="15" t="str">
+      <c r="D58" s="15" t="str">
         <v>方向待核：公告资助脑启发感知、认知、芯片及示范系统，但未明确机器人验证对象；需确认机器人感知或具身任务是否属于本期范围。</v>
       </c>
-      <c r="E55" s="15" t="str">
+      <c r="E58" s="15" t="str">
         <v>5万元/项</v>
       </c>
-      <c r="F55" s="16" t="str">
+      <c r="F58" s="16" t="str">
         <v>公告</v>
       </c>
-      <c r="G55" s="3" t="str">
+      <c r="G58" s="3" t="str">
         <v>正文已取得完整资格/外拨/权属，不能重复列为未知；年度任务为脑成像、脑启发视觉听觉嗅觉、知识图谱推理决策、芯片系统。机器人相关具体任务适用范围仍待核；申请/任务书等附件未取得。</v>
       </c>
-      <c r="H55" s="3" t="str">
+      <c r="H58" s="3" t="str">
         <v>童老师0551-63607515；niant209@ustc.edu.cn</v>
       </c>
     </row>
-    <row r="56" ht="66" customHeight="1">
-      <c r="A56" s="20" t="str">
+    <row r="59" ht="66" customHeight="1">
+      <c r="A59" s="20" t="str">
         <v>方向待核·公告已发布</v>
       </c>
-      <c r="B56" s="13" t="d">
+      <c r="B59" s="13" t="d">
         <v>2026-10-31T00:00:00.000Z</v>
       </c>
-      <c r="C56" s="14" t="str">
+      <c r="C59" s="14" t="str">
         <v>武汉理工大学·交通物联网技术湖北省重点实验室</v>
       </c>
-      <c r="D56" s="15" t="str">
-        <v>方向待核：交通物联网公告中未找到机器人或自主运行装备的明确任务；交通信息与多模态感知不能单独作为保留理由。</v>
-      </c>
-      <c r="E56" s="15" t="str">
-        <v>1—3万元</v>
-      </c>
-      <c r="F56" s="16" t="str">
+      <c r="D59" s="15" t="str">
+        <v>公告列交通信息多模态感知等4方向，未写明机器人/无人交通的具体任务；不仅凭物联网/感知名称判相关。</v>
+      </c>
+      <c r="E59" s="15" t="str">
+        <v>拟5—8项；平均1—3万元/项（原文口径，非统一定额）。</v>
+      </c>
+      <c r="F59" s="16" t="str">
         <v>公告</v>
       </c>
-      <c r="G56" s="3" t="str">
-        <v>筛选/证据缺口：交通物联网公告中未找到机器人或自主运行装备的明确任务；交通信息与多模态感知不能单独作为保留理由。</v>
-      </c>
-      <c r="H56" s="3" t="str">
-        <v>iot@whut.edu.cn</v>
-      </c>
-    </row>
-    <row r="57" ht="66" customHeight="1">
-      <c r="A57" s="20" t="str">
+      <c r="G59" s="3" t="str">
+        <v>申请书DOC工具不支持，需用户下载；需确认所申报机器人感知/自主交通具体任务是否属于年度范围，及允许报销科目和合同条款。</v>
+      </c>
+      <c r="H59" s="3" t="str">
+        <v>郭老师；iot@whut.edu.cn</v>
+      </c>
+    </row>
+    <row r="60" ht="66" customHeight="1">
+      <c r="A60" s="20" t="str">
         <v>2026年度受理窗口待核</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <v>未取得</v>
       </c>
-      <c r="C57" s="14" t="str">
+      <c r="C60" s="14" t="str">
         <v>青岛大学／青岛大学附属医院·山东省数字医学与计算机辅助手术重点实验室</v>
       </c>
-      <c r="D57" s="15" t="str">
+      <c r="D60" s="15" t="str">
         <v>虚拟手术机器人关键技术研发；计算机辅助手术设备、医学影像处理与医学数据分析、临床三维重建（官方年度指南明确列示）</v>
       </c>
-      <c r="E57" s="15" t="str">
+      <c r="E60" s="15" t="str">
         <v>1—3万元/项；公告提及2025及2026每年度各2项</v>
       </c>
-      <c r="F57" s="16" t="str">
+      <c r="F60" s="16" t="str">
         <v>公告</v>
       </c>
-      <c r="G57" s="3" t="str">
+      <c r="G60" s="3" t="str">
         <v>取得2025-10-10跨年度公开指南，但未核实2026批次当期受理。需确认2026实际受理窗口与截止时间、项目合同、经费外拨及临床数据/固定合作要求。</v>
       </c>
-      <c r="H57" s="3" t="str">
+      <c r="H60" s="3" t="str">
         <v>loojourney@163.com</v>
+      </c>
+    </row>
+    <row r="61" ht="66" customHeight="1">
+      <c r="A61" t="str" s="20">
+        <v>已截止·任务待核</v>
+      </c>
+      <c r="B61" t="n" s="13">
+        <v>46265</v>
+      </c>
+      <c r="C61" t="str" s="14">
+        <v>成都大学·模式识别与智能信息处理四川省教育厅高校重点实验室</v>
+      </c>
+      <c r="D61" t="str" s="15">
+        <v>年度具体任务在申报指南，尚未取得；不凭模式识别平台名确定机器人相关性。</v>
+      </c>
+      <c r="E61" t="str" s="15">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="F61" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G61" t="str" s="3">
+        <v>需下载2026修订版指南，核实际任务、校外资格、金额、合作、周期、经费及外拨、成果和IP。正文截止已过，不列首页。</v>
+      </c>
+      <c r="H61" t="str" s="3">
+        <v>李老师；18853318883；ligen@cdu.edu.cn</v>
       </c>
     </row>
   </sheetData>
@@ -32869,14 +36354,14 @@
     <hyperlink ref="F22" ns1:id="R23174a5763434750"/>
     <hyperlink ref="C23" location="'02项目完整详情'!A39"/>
     <hyperlink ref="F23" ns1:id="R8ec89a5433eb4d09"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A45"/>
-    <hyperlink ref="F53" ns1:id="Rba0663bbe3774f6b"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A46"/>
-    <hyperlink ref="F54" ns1:id="Rcf6a5473b1eb4a54"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A48"/>
-    <hyperlink ref="F55" ns1:id="R21f68751bbc1488c"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A49"/>
-    <hyperlink ref="F56" ns1:id="R007532abefe345a9"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A45"/>
+    <hyperlink ref="F56" ns1:id="Rba0663bbe3774f6b"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A46"/>
+    <hyperlink ref="F57" ns1:id="Rcf6a5473b1eb4a54"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A48"/>
+    <hyperlink ref="F58" ns1:id="R21f68751bbc1488c"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A49"/>
+    <hyperlink ref="F59" ns1:id="R007532abefe345a9"/>
     <hyperlink ref="C32" location="'02项目完整详情'!A50"/>
     <hyperlink ref="F32" ns1:id="R3e5ed88181034131"/>
     <hyperlink ref="C47" location="'02项目完整详情'!A159"/>
@@ -32897,8 +36382,8 @@
     <hyperlink ref="F24" ns1:id="R3b497cd64a5c4936"/>
     <hyperlink ref="C37" location="'02项目完整详情'!A57"/>
     <hyperlink ref="F37" ns1:id="Rc95eacc5d5994507"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A150"/>
-    <hyperlink ref="F57" ns1:id="Rca33aafc73934cba"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A150"/>
+    <hyperlink ref="F60" ns1:id="Rca33aafc73934cba"/>
     <hyperlink ref="C38" location="'02项目完整详情'!A58"/>
     <hyperlink ref="F38" ns1:id="Rc2e98f3f226b4076"/>
     <hyperlink ref="C41" location="'02项目完整详情'!A169" display="项目完整详情"/>
@@ -32913,6 +36398,14 @@
     <hyperlink ref="F52" ns1:id="rIdSystematic58"/>
     <hyperlink ref="C43" location="'02项目完整详情'!A174" display="项目完整详情"/>
     <hyperlink ref="F43" ns1:id="rIdSystematic59"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A178" display="项目完整详情"/>
+    <hyperlink ref="F61" ns1:id="rIdResume60"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A179" display="项目完整详情"/>
+    <hyperlink ref="F53" ns1:id="rIdResume61"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A180" display="项目完整详情"/>
+    <hyperlink ref="F54" ns1:id="rIdResume62"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A181" display="项目完整详情"/>
+    <hyperlink ref="F55" ns1:id="rIdResume63"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -16840,6 +16840,87 @@
       </c>
       <c r="AA184" t="str" s="3"/>
     </row>
+    <row r="185" ht="79.5" customHeight="1">
+      <c r="A185" t="str" s="3">
+        <v>N036</v>
+      </c>
+      <c r="B185" t="str" s="3">
+        <v>正式2025研究项目种子基金指南PDF已核；2026/2027未取得</v>
+      </c>
+      <c r="C185" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="D185" t="str" s="3">
+        <v>Research Centre for Low Altitude Economy（低空经济研究中心）</v>
+      </c>
+      <c r="E185" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F185" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G185" t="n" s="6">
+        <v>45775</v>
+      </c>
+      <c r="H185" t="str" s="3">
+        <v>时点及采用时区未载</v>
+      </c>
+      <c r="I185" t="str" s="3">
+        <v>明确可靠感知、鲁棒控制、应急安全飞行及无人机应用；须关联低空经济。</v>
+      </c>
+      <c r="J185" t="str" s="3">
+        <v>应用/平台≤50万港币；基础≤30万港币；探索初始15万港币；卓越奖励为已获外部经费的10%、≤30万港币（奖励非独立新研究项目资助）。</v>
+      </c>
+      <c r="K185" t="str" s="3">
+        <v>鼓励中心成员与本地/海外大学研究人员合作；未明确海外人员可独立担任负责人，学历职称年龄限项未载。</v>
+      </c>
+      <c r="L185" t="str" s="3">
+        <v>强烈鼓励跨部门/跨学科合作；须参加中心展示成果活动；访问天数未载。</v>
+      </c>
+      <c r="M185" t="str" s="3">
+        <v>应用/基础项目分两次拨付，第二次视进展；比例未载。允许支出、跨境/外拨及校外承担单位经费份额未载。</v>
+      </c>
+      <c r="N185" t="str" s="3">
+        <v>应用/基础最长2年；探索6—12个月，评估后可能延长。</v>
+      </c>
+      <c r="O185" t="str" s="3">
+        <v>按目标、成果影响及合作等验收；应用类演示/原型系统，基础类高质量论文及争取外部基金；年度与结题报告；成果署中心单位及基金号；论文数量/分区门槛未载。</v>
+      </c>
+      <c r="P185" t="str" s="3">
+        <v>指南未载；单位署名不作为成果权属。</v>
+      </c>
+      <c r="Q185" t="str" s="3">
+        <v>按指定申请表，2025-04-28前直接交info.rclae@polyu.edu.hk；须说明研究时序及后续外部基金申请计划。获外部资助负责人须在PGMS归属中心。</v>
+      </c>
+      <c r="R185" t="str" s="3">
+        <v>本人现职南京信息工程大学；校外负责人资格待官方确认。</v>
+      </c>
+      <c r="S185" t="str" s="3">
+        <v>2025截止已过；需确认是否有2026/2027轮次、校外/大陆人员能否负责人、校内固定合作及配套出资、经费可外拨/使用和成果权属。资格不因鼓励海外合作推定已符合。</v>
+      </c>
+      <c r="T185" t="str" s="3">
+        <v>https://www.polyu.edu.hk/rclae/-/media/department/rclae/research/rclae-seed-fund/guideline-of-project-application-rclae.pdf?hash=819336D280E1BF493E450BE2101E582E&amp;rev=0ca29d677b05438daae12be0cee8fccb</v>
+      </c>
+      <c r="U185" t="str" s="3">
+        <v>申请表入口未取得，指南PDF已核。</v>
+      </c>
+      <c r="V185" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W185" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X185" t="str" s="3">
+        <v>2025指南已核；校外可合作不等同校外可独立申报。</v>
+      </c>
+      <c r="Y185" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="Z185" t="str" s="3">
+        <v>info.rclae@polyu.edu.hk</v>
+      </c>
+      <c r="AA185" t="str" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -17244,6 +17325,7 @@
     <hyperlink ref="T182" ns1:id="rIdResume404"/>
     <hyperlink ref="T183" ns1:id="rIdResume405"/>
     <hyperlink ref="T184" ns1:id="rIdResume406"/>
+    <hyperlink ref="T185" ns1:id="rIdResume407"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -32149,6 +32231,2350 @@
       </c>
       <c r="I477" t="str" s="3">
         <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="478" ht="52.5" customHeight="1">
+      <c r="A478" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B478" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C478" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D478" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E478" t="str" s="3">
+        <v>查询：site:scut.edu.cn "国家级科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F478" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G478" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H478" t="str" s="3"/>
+      <c r="I478" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第101项</v>
+      </c>
+    </row>
+    <row r="479" ht="52.5" customHeight="1">
+      <c r="A479" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B479" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C479" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D479" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E479" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "科研平台" "重点实验室"；定位：超高温结构复合材料重点实验室；西安市特种医学与健康工程重点实验室-西北工业大学生命科学与技术学院；智能博弈与信息处理陕西省高等学校重点实验室-数学与统计学院</v>
+      </c>
+      <c r="F479" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G479" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H479" t="str" s="3">
+        <v>https://cailiao.nwpu.edu.cn/__local/B/E9/29/EB064D2048C82C9CF6FCE9EF21F_0EC285D9_C82BDE.pdf
+https://life.nwpu.edu.cn/info/1101/17281.htm
+https://math.nwpu.edu.cn/info/1482/23417.htm</v>
+      </c>
+      <c r="I479" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第102项</v>
+      </c>
+    </row>
+    <row r="480" ht="52.5" customHeight="1">
+      <c r="A480" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B480" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C480" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D480" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E480" t="str" s="3">
+        <v>查询：site:cqu.edu.cn "省部级" "科研平台" "目录"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F480" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G480" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H480" t="str" s="3"/>
+      <c r="I480" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第103项</v>
+      </c>
+    </row>
+    <row r="481" ht="52.5" customHeight="1">
+      <c r="A481" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B481" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C481" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D481" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E481" t="str" s="3">
+        <v>查询：site:nuist.edu.cn "机器人" "重点实验室" "开放"；定位：自动化学院举办科研实验室开放日活动</v>
+      </c>
+      <c r="F481" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G481" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H481" t="str" s="3">
+        <v>https://auto.nuist.edu.cn/2020/0628/c313a160147/pagem.psp</v>
+      </c>
+      <c r="I481" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第104项</v>
+      </c>
+    </row>
+    <row r="482" ht="52.5" customHeight="1">
+      <c r="A482" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B482" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C482" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D482" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E482" t="str" s="3">
+        <v>查询：site:ia.cas.cn "实验室" "开放课题" "2026"；定位：多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所；中国科学院自动化研究所复杂系统认知与决策国家级重点实验室招聘启事----中国科学院自动化研究所</v>
+      </c>
+      <c r="F482" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G482" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H482" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://www.ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html
+https://ia.cas.cn/qtgn/tzgg/202604/t20260408_8182639.html</v>
+      </c>
+      <c r="I482" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第105项</v>
+      </c>
+    </row>
+    <row r="483" ht="52.5" customHeight="1">
+      <c r="A483" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B483" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C483" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D483" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E483" t="str" s="3">
+        <v>查询：site:scut.edu.cn "省部级科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F483" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G483" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H483" t="str" s="3"/>
+      <c r="I483" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第106项</v>
+      </c>
+    </row>
+    <row r="484" ht="52.5" customHeight="1">
+      <c r="A484" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B484" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C484" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D484" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E484" t="str" s="3">
+        <v>查询：site:um.edu.mo "Robotics Laboratory" "funding"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F484" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G484" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H484" t="str" s="3"/>
+      <c r="I484" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第107项</v>
+      </c>
+    </row>
+    <row r="485" ht="52.5" customHeight="1">
+      <c r="A485" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B485" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C485" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D485" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E485" t="str" s="3">
+        <v>查询：site:um.edu.mo "Sensor-based Cooperative Robotics" "fund"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F485" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G485" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H485" t="str" s="3"/>
+      <c r="I485" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第108项</v>
+      </c>
+    </row>
+    <row r="486" ht="52.5" customHeight="1">
+      <c r="A486" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B486" t="str" s="3">
+        <v>华南理工/自动化学院</v>
+      </c>
+      <c r="C486" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D486" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E486" t="str" s="3">
+        <v>查询：site:scut.edu.cn/automation "科研平台"；定位：持续推进食品工程技术创新与转化　淀粉与植物蛋白深加工教育部工程研究中心召开学术会议；矢志创新发展 建设科技强国 我室开展公众开放日科普活动</v>
+      </c>
+      <c r="F486" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G486" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H486" t="str" s="3">
+        <v>https://news.scut.edu.cn/2026/0121/c160a59353/page.htm
+https://www2.scut.edu.cn/sklppe/2025/0616/c13921a594198/page.htm</v>
+      </c>
+      <c r="I486" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第109项</v>
+      </c>
+    </row>
+    <row r="487" ht="52.5" customHeight="1">
+      <c r="A487" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B487" t="str" s="3">
+        <v>华南理工/计算机学院</v>
+      </c>
+      <c r="C487" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D487" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E487" t="str" s="3">
+        <v>查询：site:scut.edu.cn "科研平台" "人机"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F487" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G487" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H487" t="str" s="3"/>
+      <c r="I487" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第110项</v>
+      </c>
+    </row>
+    <row r="488" ht="52.5" customHeight="1">
+      <c r="A488" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B488" t="str" s="3">
+        <v>重庆大学/自动化学院</v>
+      </c>
+      <c r="C488" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D488" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E488" t="str" s="3">
+        <v>查询：site:aut.cqu.edu.cn "科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F488" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G488" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H488" t="str" s="3"/>
+      <c r="I488" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第111项</v>
+      </c>
+    </row>
+    <row r="489" ht="52.5" customHeight="1">
+      <c r="A489" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B489" t="str" s="3">
+        <v>重庆大学/机械学院</v>
+      </c>
+      <c r="C489" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D489" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E489" t="str" s="3">
+        <v>查询：site:me.cqu.edu.cn "科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F489" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G489" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H489" t="str" s="3"/>
+      <c r="I489" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第112项</v>
+      </c>
+    </row>
+    <row r="490" ht="52.5" customHeight="1">
+      <c r="A490" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B490" t="str" s="3">
+        <v>西北工业/自动化学院</v>
+      </c>
+      <c r="C490" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D490" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E490" t="str" s="3">
+        <v>查询：site:au.nwpu.edu.cn "科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F490" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G490" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H490" t="str" s="3"/>
+      <c r="I490" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第113项</v>
+      </c>
+    </row>
+    <row r="491" ht="52.5" customHeight="1">
+      <c r="A491" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B491" t="str" s="3">
+        <v>西北工业/航海学院</v>
+      </c>
+      <c r="C491" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D491" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E491" t="str" s="3">
+        <v>查询：site:hanghai.nwpu.edu.cn "科研平台"；定位：清华大学社会科学学院研究中心来航海学院调研-航海学院</v>
+      </c>
+      <c r="F491" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G491" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H491" t="str" s="3">
+        <v>https://hanghai.nwpu.edu.cn/info/1598/9624.htm</v>
+      </c>
+      <c r="I491" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第114项</v>
+      </c>
+    </row>
+    <row r="492" ht="52.5" customHeight="1">
+      <c r="A492" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B492" t="str" s="3">
+        <v>西北工业/计算机学院</v>
+      </c>
+      <c r="C492" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D492" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E492" t="str" s="3">
+        <v>查询：site:jsj.nwpu.edu.cn "科研平台"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F492" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G492" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H492" t="str" s="3"/>
+      <c r="I492" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第115项</v>
+      </c>
+    </row>
+    <row r="493" ht="52.5" customHeight="1">
+      <c r="A493" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B493" t="str" s="3">
+        <v>华南理工/机械学院</v>
+      </c>
+      <c r="C493" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D493" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E493" t="str" s="3">
+        <v>查询：site:scut.edu.cn "科研平台" "机器人及系统集成"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F493" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G493" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H493" t="str" s="3"/>
+      <c r="I493" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第116项</v>
+      </c>
+    </row>
+    <row r="494" ht="52.5" customHeight="1">
+      <c r="A494" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B494" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C494" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D494" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E494" t="str" s="3">
+        <v>查询：site:scut.edu.cn "广东省机器人及系统集成工程技术研究中心" 开放 基金 2026 2027；定位：2016年度广东省工程技术研究中心认定名单</v>
+      </c>
+      <c r="F494" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G494" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H494" t="str" s="3">
+        <v>https://www2.scut.edu.cn/_upload/article/files/8b/d6/0cb811684fb3a127b5c74d670dd2/9d2efd16-1d6d-48b3-8d8c-1cd69ed1c98c.pdf</v>
+      </c>
+      <c r="I494" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第117项</v>
+      </c>
+    </row>
+    <row r="495" ht="52.5" customHeight="1">
+      <c r="A495" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B495" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C495" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D495" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E495" t="str" s="3">
+        <v>查询：site:scut.edu.cn "广东省智能无人船与系统技术工程研究中心" 开放 基金 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F495" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G495" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H495" t="str" s="3"/>
+      <c r="I495" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第118项</v>
+      </c>
+    </row>
+    <row r="496" ht="52.5" customHeight="1">
+      <c r="A496" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B496" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C496" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D496" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E496" t="str" s="3">
+        <v>查询：site:scut.edu.cn "广东省智能焊接制造装备及机器人工程技术研究中心" 开放 基金 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F496" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G496" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H496" t="str" s="3"/>
+      <c r="I496" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第119项</v>
+      </c>
+    </row>
+    <row r="497" ht="52.5" customHeight="1">
+      <c r="A497" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B497" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C497" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D497" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E497" t="str" s="3">
+        <v>查询：site:scut.edu.cn "广东省人机共生智能研究中心" 开放 基金 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F497" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G497" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H497" t="str" s="3"/>
+      <c r="I497" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第120项</v>
+      </c>
+    </row>
+    <row r="498" ht="52.5" customHeight="1">
+      <c r="A498" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B498" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C498" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D498" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E498" t="str" s="3">
+        <v>查询：site:scut.edu.cn "手术机器人联合实验室" 开放 基金 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F498" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G498" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H498" t="str" s="3"/>
+      <c r="I498" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第121项</v>
+      </c>
+    </row>
+    <row r="499" ht="52.5" customHeight="1">
+      <c r="A499" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B499" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C499" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D499" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E499" t="str" s="3">
+        <v>查询：site:scut.edu.cn "超级机器人研究院" funding call 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F499" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G499" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H499" t="str" s="3"/>
+      <c r="I499" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第122项</v>
+      </c>
+    </row>
+    <row r="500" ht="52.5" customHeight="1">
+      <c r="A500" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B500" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C500" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D500" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E500" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "陕西省语音与图像信息处理重点实验室" 开放 基金 2026 2027；定位：陕西省语音与图像信息处理重点实验室第六届学术委员会第二次会议成功举办-计算机学院</v>
+      </c>
+      <c r="F500" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G500" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H500" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1598/14525.htm</v>
+      </c>
+      <c r="I500" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第123项</v>
+      </c>
+    </row>
+    <row r="501" ht="52.5" customHeight="1">
+      <c r="A501" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B501" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C501" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D501" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E501" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "移动平台环境感知及空天应用国家级国际联合研究中心" 开放 基金 2026 2027；定位：西北工业大学计算机学院2026年暑期校园开放日活动方案-计算机学院；2025年西北工业大学计算机学院暑期校园开放日暨研究生招生宣传日活动方案-计算机学院</v>
+      </c>
+      <c r="F501" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G501" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H501" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1599/29795.htm
+https://jsj.nwpu.edu.cn/info/1599/26125.htm</v>
+      </c>
+      <c r="I501" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第124项</v>
+      </c>
+    </row>
+    <row r="502" ht="52.5" customHeight="1">
+      <c r="A502" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B502" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C502" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D502" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E502" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "无人航行实时智能感知与计算技术创新引智基地" funding call 2026 2027；定位：西北工业大学计算机学院2026年暑期校园开放日活动方案-计算机学院；2025年西北工业大学计算机学院暑期校园开放日暨研究生招生宣传日活动方案-计算机学院</v>
+      </c>
+      <c r="F502" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G502" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H502" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1599/29795.htm
+https://jsj.nwpu.edu.cn/info/1599/26125.htm</v>
+      </c>
+      <c r="I502" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第125项</v>
+      </c>
+    </row>
+    <row r="503" ht="52.5" customHeight="1">
+      <c r="A503" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B503" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C503" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D503" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E503" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "智能感知与计算工信部重点实验室" 开放 基金 2026 2027；定位：西北工业大学-龙湖联合实验室揭牌并举行第一次技术研讨会议-计算机学院</v>
+      </c>
+      <c r="F503" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G503" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H503" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1598/8889.htm</v>
+      </c>
+      <c r="I503" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第126项</v>
+      </c>
+    </row>
+    <row r="504" ht="52.5" customHeight="1">
+      <c r="A504" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B504" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C504" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D504" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E504" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "陕西省嵌入式系统技术重点实验室" 开放 基金 2026 2027；定位：陕西省嵌入式系统技术重点实验室-计算机学院；西北工业大学计算机学院陕西省嵌入式系统技术重点实验室非事业编制人员招聘启事-人力资源部；西北工业大学计算机学院陕西省嵌入式系统技术重点实验室非事业编制人员招聘启事-人力资源部</v>
+      </c>
+      <c r="F504" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G504" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H504" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1658/7527.htm
+https://renshi.nwpu.edu.cn/info/1326/31135.htm
+https://renshi.nwpu.edu.cn/info/1264/30575.htm</v>
+      </c>
+      <c r="I504" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第127项</v>
+      </c>
+    </row>
+    <row r="505" ht="52.5" customHeight="1">
+      <c r="A505" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B505" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C505" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D505" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E505" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "机器人仿真技术实验室" 开放 基金 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F505" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G505" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H505" t="str" s="3"/>
+      <c r="I505" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第128项</v>
+      </c>
+    </row>
+    <row r="506" ht="52.5" customHeight="1">
+      <c r="A506" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B506" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C506" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D506" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E506" t="str" s="3">
+        <v>查询：site:ia.cas.cn "脑认知功能图谱与类脑智能交叉研究平台" funding call 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F506" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G506" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H506" t="str" s="3"/>
+      <c r="I506" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第129项</v>
+      </c>
+    </row>
+    <row r="507" ht="52.5" customHeight="1">
+      <c r="A507" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B507" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C507" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D507" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E507" t="str" s="3">
+        <v>查询：site:ia.cas.cn "国家专用集成电路设计工程技术研究中心" 开放 基金 2026 2027；定位：国家专用集成电路设计工程技术研究中心----中国科学院自动化研究所；国家专用集成电路设计工程技术研究中心----中国科学院自动化研究所；紫东太初大模型研究中心----中国科学院自动化研究所；为所长助理；徐波、卢汉清为模式识别国家重点实验室副主任，易建强为复杂系统与智能科学开放实验室副主任，彭思龙为国家专用集成电路设计工程技术研究中心副主任，刘迎建为文字识别工程中心主任，张立清为文字识别工程中心副主任，孙敦圣为综合自动化技术工程中心主任，邹益仁、林红权为综合自动化技术工程中心副主任，王飞跃为智能控制与系统工程中心主任，杨一平为互联网研究发展中心主任，王晓功为互联网研究发展中心副主任，房自正为所综合办公室副主任。任期自 2002 年 2 月 27 日起至研究所本届领导班子届满。</v>
+      </c>
+      <c r="F507" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G507" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H507" t="str" s="3">
+        <v>https://www.ia.cas.cn/jgsz/kyxt/bm4/
+https://ia.cas.cn/jgsz/kyxt/bm4/
+https://ia.cas.cn/jgsz/kyxt/zztc/
+https://www.ia.cas.cn/60zhsq/sqlsyg/202005/W020200518639608854729.pdf</v>
+      </c>
+      <c r="I507" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第130项</v>
+      </c>
+    </row>
+    <row r="508" ht="52.5" customHeight="1">
+      <c r="A508" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B508" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C508" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D508" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E508" t="str" s="3">
+        <v>查询：site:ia.cas.cn "精密感知与控制研究中心" 开放 基金 2026 2027；定位：精密感知与控制研究中心党支部召开全体党员大会----中国科学院自动化研究所；精密感知与控制研究中心党支部召开支部党员大会----中国科学院自动化研究所</v>
+      </c>
+      <c r="F508" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G508" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H508" t="str" s="3">
+        <v>https://ia.cas.cn/dqyd/zbgz/202208/t20220824_6503572.html
+https://ia.cas.cn/dqyd/zbgz/202012/t20201222_5834220.html</v>
+      </c>
+      <c r="I508" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第131项</v>
+      </c>
+    </row>
+    <row r="509" ht="52.5" customHeight="1">
+      <c r="A509" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B509" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C509" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D509" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E509" t="str" s="3">
+        <v>查询：site:um.edu.mo "Soft Sensors-Actuators-Robots Laboratory" funding call 2026 2027；定位：Soft Sensors-Actuators-Robots Laboratory柔性傳感器、執行器、機械人實驗室 – Faculty of Science and Technology | University of Macau；Laboratories – Faculty of Science and Technology | University of Macau；Laboratories – Faculty of Science and Technology | University of Macau</v>
+      </c>
+      <c r="F509" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G509" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H509" t="str" s="3">
+        <v>https://www.fst.um.edu.mo/research/laboratories/soft-sensors-actuators-robots-laboratory/
+https://www.fst.um.edu.mo/eme/laboratories/
+https://www.fst.um.edu.mo/research/laboratories/</v>
+      </c>
+      <c r="I509" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第132项</v>
+      </c>
+    </row>
+    <row r="510" ht="52.5" customHeight="1">
+      <c r="A510" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B510" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C510" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D510" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E510" t="str" s="3">
+        <v>查询：site:um.edu.mo "Intelligent Unmanned Systems Laboratory" funding call 2026 2027；定位：Intelligent Unmanned Systems Laboratory智能無人系統實驗室 – Faculty of Science and Technology | University of Macau；Laboratories – Faculty of Science and Technology | University of Macau；Laboratories – Faculty of Science and Technology | University of Macau；RESEARCH CENTRES AND LABORATORIES</v>
+      </c>
+      <c r="F510" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G510" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H510" t="str" s="3">
+        <v>https://www.fst.um.edu.mo/research/laboratories/intelligent-unmanned-systems-laboratory/
+https://www.fst.um.edu.mo/eme/laboratories/
+https://www.fst.um.edu.mo/research/laboratories/
+https://reg.um.edu.mo/download/um-academic-calendar/11labs.pdf</v>
+      </c>
+      <c r="I510" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第133项</v>
+      </c>
+    </row>
+    <row r="511" ht="52.5" customHeight="1">
+      <c r="A511" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B511" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C511" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D511" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E511" t="str" s="3">
+        <v>查询：site:um.edu.mo "Immersive Interactive Technology Laboratory" funding call 2026 2027；定位：Immersive Interactive Technology Laboratory沉浸式交互技術實驗室 – Faculty of Science and Technology | University of Macau；Laboratories – Faculty of Science and Technology | University of Macau；RESEARCH CENTRES AND LABORATORIES</v>
+      </c>
+      <c r="F511" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G511" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H511" t="str" s="3">
+        <v>https://www.fst.um.edu.mo/research/laboratories/immersive-interactive-technology-laboratory/
+https://www.fst.um.edu.mo/research/laboratories/
+https://reg.um.edu.mo/download/um-academic-calendar/11labs.pdf</v>
+      </c>
+      <c r="I511" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第134项</v>
+      </c>
+    </row>
+    <row r="512" ht="52.5" customHeight="1">
+      <c r="A512" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B512" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C512" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D512" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E512" t="str" s="3">
+        <v>查询：site:um.edu.mo "Data-Driven Intelligent Systems Laboratory" funding call 2026 2027；定位：Laboratories – Faculty of Science and Technology | University of Macau；RESEARCH CENTRES AND LABORATORIES</v>
+      </c>
+      <c r="F512" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G512" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H512" t="str" s="3">
+        <v>https://www.fst.um.edu.mo/research/laboratories/
+https://reg.um.edu.mo/download/um-academic-calendar/11labs.pdf</v>
+      </c>
+      <c r="I512" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第135项</v>
+      </c>
+    </row>
+    <row r="513" ht="52.5" customHeight="1">
+      <c r="A513" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B513" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C513" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D513" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E513" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "Research Institute for Artificial Intelligence of Things" funding call 2026 2027；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F513" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G513" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H513" t="str" s="3"/>
+      <c r="I513" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第136项</v>
+      </c>
+    </row>
+    <row r="514" ht="52.5" customHeight="1">
+      <c r="A514" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B514" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C514" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D514" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E514" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "Research Institute for Smart Ageing" funding call 2026 2027；定位：PolyU collaborates with University of Toronto to explore establishment of joint research centre, driving gerontechnology innovation in response to ageing population | Research Institute for Smart Ageing；Projects Funded by RISA | Research Institute for Smart Ageing；PolyU ranks among leading universities in multiple RGC funding schemes, underscoring distinctive research leadership | RCESGA</v>
+      </c>
+      <c r="F514" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G514" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H514" t="str" s="3">
+        <v>https://www.polyu.edu.hk/risa/news-and-events/news/2026/polyu-collaborates-with-university-of-toronto-to-explore-establishment-of-joint-research-centre/
+https://www.polyu.edu.hk/risa/Research/Projects-Funded-by-RISA
+https://www.polyu.edu.hk/rcesga/news-n-events/news/2026/20260820-polyu-ranks-among-leading-universities/</v>
+      </c>
+      <c r="I514" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第137项</v>
+      </c>
+    </row>
+    <row r="515" ht="52.5" customHeight="1">
+      <c r="A515" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B515" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C515" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D515" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E515" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "Research Centre for Low Altitude Economy" funding call 2026 2027；定位：Research Centre for Low Altitude Economy | RCLAE；PolyU and Tianlu Flying-auto (Hong Kong) Ltd. Launch Joint Laboratory to Drive Research Impact and Industrial Innovation in Low-Altitude Economy | RCLAE</v>
+      </c>
+      <c r="F515" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G515" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H515" t="str" s="3">
+        <v>https://www.polyu.edu.hk/en/rclae/sitecore/content/aae/research/research-centres-and-groups/archieved_research-centre-for-low-altitude-economy/
+https://www.polyu.edu.hk/rclae/news-and-events/news/2026/20260308---signing-n-unveiling-ceremony/</v>
+      </c>
+      <c r="I515" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第138项</v>
+      </c>
+    </row>
+    <row r="516" ht="52.5" customHeight="1">
+      <c r="A516" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B516" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C516" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D516" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E516" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "Research Centre for Future Caring Mobility" funding call 2026 2027；定位：Vision and Mission | Research Centre for Future (Caring) Mobility；Research | Research Centre for Future (Caring) Mobility；Home | Research Centre for Future (Caring) Mobility；Lifelong Care in Mobility | Research Centre for Future (Caring) Mobility；Urbanization of Caring Mobility | Research Centre for Future (Caring) Mobility；Experience &amp; Security in Caring Mobility | Research Centre for Future (Caring) Mobility；Hybrid Care in Mobility | Research Centre for Future (Caring) Mobility</v>
+      </c>
+      <c r="F516" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G516" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H516" t="str" s="3">
+        <v>https://www.polyu.edu.hk/sdrcfcm/About-RcFCM/View-and-Mission?sc_lang=en
+https://www.polyu.edu.hk/sdrcfcm/research/?sc_lang=en
+https://www.polyu.edu.hk/sdrcfcm
+https://www.polyu.edu.hk/sdrcfcm/research/program-3?sc_lang=en
+https://www.polyu.edu.hk/sdrcfcm/research/program-5/
+https://www.polyu.edu.hk/sdrcfcm/research/program-1/
+https://www.polyu.edu.hk/sdrcfcm/research/program-2/</v>
+      </c>
+      <c r="I516" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第139项</v>
+      </c>
+    </row>
+    <row r="517" ht="52.5" customHeight="1">
+      <c r="A517" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B517" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C517" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D517" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E517" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "Research Centre for Electric Vehicles" funding call 2026 2027；定位：Position Openings | Research Centre for Electric Vehicles；Vision and Mission | Research Centre for Electric Vehicles；RCEV Shines at the 51st International Exhibition of Inventions Geneva, Winning a Gold Medal and a Silver Medal | Research Centre for Electric Vehicles；Research Themes | Research Centre for Electric Vehicles；Home | Research Centre for Electric Vehicles；Research Centres and Labs | Department of Electrical and Electronic Engineering；Contact Us | Research Centre for Electric Vehicles</v>
+      </c>
+      <c r="F517" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G517" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H517" t="str" s="3">
+        <v>https://www.polyu.edu.hk/rcev/home/position-openings/
+https://www.polyu.edu.hk/rcev/about-rcev/vision-and-mission
+https://www.polyu.edu.hk/rcev/research/rewards/2026/ieig51st/
+https://www.polyu.edu.hk/rcev/Research/Research-Themes
+https://www.polyu.edu.hk/rcev?sc_lang=en
+https://www.polyu.edu.hk/eee/research/research-centres-and-labs/?sc_lang=en
+https://www.polyu.edu.hk/rcev/About-RCEV/Contact-Us</v>
+      </c>
+      <c r="I517" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第140项</v>
+      </c>
+    </row>
+    <row r="518" ht="52.5" customHeight="1">
+      <c r="A518" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B518" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C518" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D518" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E518" t="str" s="3">
+        <v>查询：site:polyu.edu.hk/rclae "seed fund" "2026"；定位：CEE Members Secure Youth Seed Fund | Department of Civil and Environmental Engineering；Projects – Laboratory of Radio Frequency Microelectronic Circuits (RFMC)；RCRE Seed Fund Projects；Flipped Learning Signature Showcases: Successes, Insights and Challenges – Presentations and Posters | Educational Development Centre；Micro Fund 2025/26 Cohort 2 Online Briefing Session | Knowledge Transfer and Entrepreneurship Office；Prof. Cheng Song Secures Highly Competitive ITF Fund for "Drop-in" Sustainable Aviation Fuel Technology | Department of Mechanical Engineering</v>
+      </c>
+      <c r="F518" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G518" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H518" t="str" s="3">
+        <v>https://www.polyu.edu.hk/cee/news-and-events/newsletter/2026aprspring/achievements/cee-members-secure-youth-seed-fund/
+https://staff.eie.polyu.edu.hk/xinyuzhou/projects/
+https://www.polyu.edu.hk/rcre/Research/RCRE-Seed-Fund-Projects?sc_lang=sc
+https://www.polyu.edu.hk/edc/engage-in-cpd-activities/workshops-seminars/workshop-20260624a/
+https://www.polyu.edu.hk/kteo/about-kteo/news-and-events/events/2026/03/mf2026-cohort-2_briefing-session/?sc_lang=en
+https://www.polyu.edu.hk/me/news-and-events/news/2026/03-06-prof-cheng-song-secures-highly-competitive-itf-fund/</v>
+      </c>
+      <c r="I518" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第141项</v>
+      </c>
+    </row>
+    <row r="519" ht="52.5" customHeight="1">
+      <c r="A519" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B519" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C519" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D519" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E519" t="str" s="3">
+        <v>查询：site:polyu.edu.hk/rclae "funding" "2027"；定位：Belt and Road Funding Schemes | Global Engagement Office；Micro Fund Scheme | Knowledge Transfer and Entrepreneurship Office；Funding Opportunities | Student Affairs Office；Funding Opportunities | Student Affairs Office；Non-local Study Fund | Office of Undergraduate Studies；PolyU Angel Fund 2027-28 (TSSSU+)；Angel Fund Scheme (TSSSU+) | Knowledge Transfer and Entrepreneurship Office</v>
+      </c>
+      <c r="F519" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G519" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H519" t="str" s="3">
+        <v>https://www.polyu.edu.hk/geo/partnerships/belt-and-road-initiatives/belt-and-road-funding-schemes/?sc_lang=en
+https://www.polyu.edu.hk/en/kteo/entrepreneurship/funding_investment/polyu-micro-fund-scheme/
+https://www.polyu.edu.hk/sao/student-development-section/polyu-student-organisations/2one-stop-guide/interest-club/funding-opportunities-soc/?sc_lang=en
+https://www.polyu.edu.hk/sao/student-development-section/polyu-student-organisations/2one-stop-guide/faculty-school-departmental-association/funding-opportunities-fac/?sc_lang=en
+https://www.polyu.edu.hk/ous/non-local-gur-study/non-local-study-fund/non-local-study-fund/
+https://www.polyu.edu.hk/pfs2/index.php/349242?lang=en
+https://www.polyu.edu.hk/kteo/entrepreneurship/funding_investment/polyventures-angel-fund-scheme/tsssu-plus/</v>
+      </c>
+      <c r="I519" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第142项</v>
+      </c>
+    </row>
+    <row r="520" ht="52.5" customHeight="1">
+      <c r="A520" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B520" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C520" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D520" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E520" t="str" s="3">
+        <v>查询：site:polyu.edu.hk/rclae "project application" "eligible"；定位：State Key Laboratory of Ultra-precision Machining Technology (SKL-UPMT)；Call for Application | State Key Laboratory of Ultra-precision Machining Technology</v>
+      </c>
+      <c r="F520" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G520" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H520" t="str" s="3">
+        <v>https://www.polyu.edu.hk/sklumt/-/media/department/sklumt/content/open-project/sklupmt-open-project-2026---appn-guidelines_en-%28202512%29.pdf?hash=1AA8B10CBF8EDCF596A255DF621A0409&amp;rev=ff83769253864193ab680ce669f0733b
+https://www.polyu.edu.hk/sklumt/open-research-project/call-for-application/</v>
+      </c>
+      <c r="I520" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第143项</v>
+      </c>
+    </row>
+    <row r="521" ht="52.5" customHeight="1">
+      <c r="A521" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B521" t="str" s="3">
+        <v>石河子大学</v>
+      </c>
+      <c r="C521" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D521" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E521" t="str" s="3">
+        <v>查询：site:cs.shzu.edu.cn/_t513/2024/0921/c12051a209837/page.htm；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F521" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G521" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H521" t="str" s="3"/>
+      <c r="I521" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第144项</v>
+      </c>
+    </row>
+    <row r="522" ht="52.5" customHeight="1">
+      <c r="A522" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B522" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C522" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D522" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E522" t="str" s="3">
+        <v>查询：site:jsj.nwpu.edu.cn ("研究机构" OR "网络与机器人系统")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F522" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G522" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H522" t="str" s="3"/>
+      <c r="I522" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第145项</v>
+      </c>
+    </row>
+    <row r="523" ht="52.5" customHeight="1">
+      <c r="A523" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B523" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C523" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D523" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E523" t="str" s="3">
+        <v>查询：site:civil.cqu.edu.cn/info/1327/17713.htm；定位：建筑CAI实验室-重庆大学土木工程学院</v>
+      </c>
+      <c r="F523" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G523" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H523" t="str" s="3">
+        <v>https://civil.cqu.edu.cn/chssjgy.jsp?a1003978c=10&amp;a1003978p=5&amp;a1003978t=607&amp;urltype=tree.TreeTempUrl&amp;wbtreeid=1112</v>
+      </c>
+      <c r="I523" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第146项</v>
+      </c>
+    </row>
+    <row r="524" ht="52.5" customHeight="1">
+      <c r="A524" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B524" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C524" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D524" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E524" t="str" s="3">
+        <v>查询：site:ia.cas.cn ("工业视觉智能装备" OR "脑图谱与类脑智能" OR "模式识别实验室") ("开放基金" OR "开放课题")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F524" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G524" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H524" t="str" s="3"/>
+      <c r="I524" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第147项</v>
+      </c>
+    </row>
+    <row r="525" ht="52.5" customHeight="1">
+      <c r="A525" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B525" t="str" s="3">
+        <v>福建理工大学</v>
+      </c>
+      <c r="C525" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D525" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E525" t="str" s="3">
+        <v>查询：site:fjut.edu.cn ("无人驾驶" OR "工业控制" OR "海洋装备" OR "机器人") ("开放基金" OR "开放课题")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F525" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G525" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H525" t="str" s="3"/>
+      <c r="I525" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第148项</v>
+      </c>
+    </row>
+    <row r="526" ht="52.5" customHeight="1">
+      <c r="A526" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B526" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C526" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D526" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E526" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn ("智能决策与智能机器人系统实验室" OR "工业互联网技术及应用工程研究中心") ("开放基金" OR "开放课题" OR "2026" OR "2027")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F526" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G526" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H526" t="str" s="3"/>
+      <c r="I526" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第149项</v>
+      </c>
+    </row>
+    <row r="527" ht="52.5" customHeight="1">
+      <c r="A527" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B527" t="str" s="3">
+        <v>广西多源信息</v>
+      </c>
+      <c r="C527" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D527" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E527" t="str" s="3">
+        <v>查询：("广西多源信息" OR "广西多源") ("开放基金" OR "开放课题") ("2026" OR "2027" OR "2025")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F527" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G527" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H527" t="str" s="3"/>
+      <c r="I527" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第150项</v>
+      </c>
+    </row>
+    <row r="528" ht="52.5" customHeight="1">
+      <c r="A528" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B528" t="str" s="3">
+        <v>安徽理工大学</v>
+      </c>
+      <c r="C528" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D528" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E528" t="str" s="3">
+        <v>查询：site:aust.edu.cn ("煤炭无人化开采数智技术" OR "工业粉尘防控") ("开放基金" OR "开放课题")；定位：煤炭无人化开采数智技术全国重点实验室；工业粉尘防控与职业安全健康教育部重点实验室2025、2026年度开放课题申请指南-工业粉尘防控与职业健康；2021年工业粉尘防控与职业安全健康教育部重点实验室开放基金申请指南-工业粉尘防控与职业健康</v>
+      </c>
+      <c r="F528" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G528" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H528" t="str" s="3">
+        <v>https://cdsys.aust.edu.cn/
+https://eklab.aust.edu.cn/info/1004/1214.htm
+https://eklab.aust.edu.cn/info/1009/1039.htm</v>
+      </c>
+      <c r="I528" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第151项</v>
+      </c>
+    </row>
+    <row r="529" ht="52.5" customHeight="1">
+      <c r="A529" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B529" t="str" s="3">
+        <v>香港理工大学内地研究院</v>
+      </c>
+      <c r="C529" t="str" s="3">
+        <v>广东/江苏等</v>
+      </c>
+      <c r="D529" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E529" t="str" s="3">
+        <v>查询：site:polyu.edu.hk ("研究院" OR "Research Institute") ("开放基金" OR "开放课题" OR "open fund") ("Shenzhen" OR "深圳" OR "南京" OR "无锡")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F529" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G529" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H529" t="str" s="3"/>
+      <c r="I529" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第152项</v>
+      </c>
+    </row>
+    <row r="530" ht="52.5" customHeight="1">
+      <c r="A530" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B530" t="str" s="3">
+        <v>机器人院所补漏</v>
+      </c>
+      <c r="C530" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D530" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E530" t="str" s="3">
+        <v>查询：("开放基金" OR "开放课题") ("2026" OR "2027") ("机器人" OR "具身智能") ("研究院" OR "研究所")；定位：fund-deadlines - 基金申请截止时间</v>
+      </c>
+      <c r="F530" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G530" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H530" t="str" s="3">
+        <v>https://fund-ddl.com/</v>
+      </c>
+      <c r="I530" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第153项</v>
+      </c>
+    </row>
+    <row r="531" ht="52.5" customHeight="1">
+      <c r="A531" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B531" t="str" s="3">
+        <v>江苏省属智能装备平台</v>
+      </c>
+      <c r="C531" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D531" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E531" t="str" s="3">
+        <v>查询：("常州大学" OR "江苏理工学院" OR "扬州大学" OR "苏州科技大学") ("开放基金" OR "开放课题") ("2026" OR "2027") ("机器人" OR "智能装备" OR "感知")；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F531" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G531" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H531" t="str" s="3"/>
+      <c r="I531" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第154项</v>
+      </c>
+    </row>
+    <row r="532" ht="52.5" customHeight="1">
+      <c r="A532" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B532" t="str" s="3">
+        <v>省高校机器人平台补漏</v>
+      </c>
+      <c r="C532" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D532" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E532" t="str" s="3">
+        <v>查询：("省高校重点实验室" OR "省教育厅重点实验室") ("机器人" OR "具身" OR "智能感知") ("开放基金" OR "开放课题") ("2026" OR "2027")；定位：10项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F532" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G532" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H532" t="str" s="3">
+        <v>https://www.letpub.com.cn/index.php?article_id=1576&amp;page=grant_article_details</v>
+      </c>
+      <c r="I532" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第155项</v>
+      </c>
+    </row>
+    <row r="533" ht="52.5" customHeight="1">
+      <c r="A533" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B533" t="str" s="3">
+        <v>扬州大学</v>
+      </c>
+      <c r="C533" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D533" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E533" t="str" s="3">
+        <v>查询：site:yzu.edu.cn 开放课题 机器人；定位：扬州大学江苏省重点实验室；公开 – 转座子实验室</v>
+      </c>
+      <c r="F533" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G533" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H533" t="str" s="3">
+        <v>https://sjxy.yzu.edu.cn/__local/E/BB/8C/8CDF21785A7954A24B8CC2A0313_7EEBF50C_3292A.pdf?e=.pdf
+https://tnlab.yzu.edu.cn/category/uncategorized</v>
+      </c>
+      <c r="I533" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第156项</v>
+      </c>
+    </row>
+    <row r="534" ht="52.5" customHeight="1">
+      <c r="A534" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B534" t="str" s="3">
+        <v>江苏理工学院</v>
+      </c>
+      <c r="C534" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D534" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E534" t="str" s="3">
+        <v>查询：site:jsut.edu.cn 开放基金 智能；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F534" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G534" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H534" t="str" s="3"/>
+      <c r="I534" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第157项</v>
+      </c>
+    </row>
+    <row r="535" ht="52.5" customHeight="1">
+      <c r="A535" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B535" t="str" s="3">
+        <v>常州大学</v>
+      </c>
+      <c r="C535" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D535" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E535" t="str" s="3">
+        <v>查询：site:cczu.edu.cn 开放课题 机器人；定位：关于组织申报2026年常州市科技项目-智能制造龙城实验室开放课题的通知；关于组织申报2025年常州市科技计划（应用基础研究专项-智能制造龙城实验室定向开放课题）项目的通知；石油和化工行业动力电池安全与事故防控技术工程实验室2025年度开放课题指南</v>
+      </c>
+      <c r="F535" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G535" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H535" t="str" s="3">
+        <v>https://iimt.cczu.edu.cn/2026/0519/c22023a415871/page.htm
+https://iimt.cczu.edu.cn/2025/0521/c22023a391481/page.htm
+https://ipsem.cczu.edu.cn/2025/1027/c15269a402781/page.htm</v>
+      </c>
+      <c r="I535" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第158项</v>
+      </c>
+    </row>
+    <row r="536" ht="52.5" customHeight="1">
+      <c r="A536" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B536" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="C536" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D536" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E536" t="str" s="3">
+        <v>查询："人机共融系统与智能装备" "开放"；定位：2025年度国家省部级重点实验室开放课题</v>
+      </c>
+      <c r="F536" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G536" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H536" t="str" s="3">
+        <v>https://www.hfuu.edu.cn/kjc/74/ff/c11997a161023/page.htm</v>
+      </c>
+      <c r="I536" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第159项</v>
+      </c>
+    </row>
+    <row r="537" ht="52.5" customHeight="1">
+      <c r="A537" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B537" t="str" s="3">
+        <v>安徽大学</v>
+      </c>
+      <c r="C537" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D537" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E537" t="str" s="3">
+        <v>查询：site:ahu.edu.cn "人机共融系统与智能装备" "开放课题"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F537" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G537" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H537" t="str" s="3"/>
+      <c r="I537" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第160项</v>
+      </c>
+    </row>
+    <row r="538" ht="52.5" customHeight="1">
+      <c r="A538" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B538" t="str" s="3">
+        <v>西南科技大学</v>
+      </c>
+      <c r="C538" t="str" s="3">
+        <v>四川</v>
+      </c>
+      <c r="D538" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E538" t="str" s="3">
+        <v>查询：site:swust.edu.cn "开放基金" "机器人"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F538" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G538" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H538" t="str" s="3"/>
+      <c r="I538" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第161项</v>
+      </c>
+    </row>
+    <row r="539" ht="52.5" customHeight="1">
+      <c r="A539" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B539" t="str" s="3">
+        <v>天津理工大学</v>
+      </c>
+      <c r="C539" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D539" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E539" t="str" s="3">
+        <v>查询：site:tjut.edu.cn "机器人" "开放课题"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F539" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G539" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H539" t="str" s="3"/>
+      <c r="I539" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第162项</v>
+      </c>
+    </row>
+    <row r="540" ht="52.5" customHeight="1">
+      <c r="A540" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B540" t="str" s="3">
+        <v>青岛理工大学</v>
+      </c>
+      <c r="C540" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D540" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E540" t="str" s="3">
+        <v>查询：site:qut.edu.cn "开放基金" "机器人"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F540" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G540" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H540" t="str" s="3"/>
+      <c r="I540" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第163项</v>
+      </c>
+    </row>
+    <row r="541" ht="52.5" customHeight="1">
+      <c r="A541" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B541" t="str" s="3">
+        <v>江苏省能源动力高端装备</v>
+      </c>
+      <c r="C541" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D541" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E541" t="str" s="3">
+        <v>查询：江苏省能源动力高端装备工程研究中心 开放课题 2025；定位：“江苏省能源动力高端装备工程研究中心”开放课题申报通知；江苏省能源动力高端装备工程研究中心学术委员会会议顺利召开；关于申请2025年度航空飞行器热管理与能量利用重点实验室开放课题的通知；关于发布江苏省多能融合与灵活性发电技术重点实验室2025年度开放基金项目指南的通知-能源与动力工程学院；关于公布江苏省智能制造装备关键技术工程研究中心2025年度开放基金申请的通知-科技处；教育部新能源系统高端装备和智慧运行工程研究中心；江苏省发展和改革委员会 通知公告 关于组织开展2025年江苏省工程研究中心申报工作的通知</v>
+      </c>
+      <c r="F541" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G541" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H541" t="str" s="3">
+        <v>https://cmee.cczu.edu.cn/2025/0620/c22043a395328/page.htm
+https://cmee.cczu.edu.cn/_t1046/2024/0527/c3305a363528/page.psp
+https://cepe.nuaa.edu.cn/2025/1201/c15758a388849/page.htm
+https://nd.njit.edu.cn/info/1194/6470.htm
+https://kjc.squ.edu.cn/info/1008/2302.htm
+https://seee.qhu.edu.cn/docs/2024-11/1e5dc53ded204253ac27ede7c3c72671.pdf
+https://fzggw.jiangsu.gov.cn/art/2025/4/24/art_284_11554685.html</v>
+      </c>
+      <c r="I541" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第164项</v>
+      </c>
+    </row>
+    <row r="542" ht="52.5" customHeight="1">
+      <c r="A542" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B542" t="str" s="3">
+        <v>青岛理工大学</v>
+      </c>
+      <c r="C542" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D542" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E542" t="str" s="3">
+        <v>查询：滨海人居环境学术创新中心 开放基金 2026；定位：关于生态环境部湖泊污染控制重点实验室2026年度开放基金申请的通知_中国环境科学研究院；自然资源部海上丝路海洋资源环境组网观测技术创新中心开放基金课题(第三批)申请指南；青岛市现代分析与近海生态环境安全保障重点实验室2026年度开放基金申请指南_通知公告_门户网站；特种环境复合材料技术国家级重点实验室开放基金指南（2026年度）；青岛理工大学滨海人居环境学术创新中心开放课题2021年度申报指南-青岛理工大学科技处；全省极端环境材料表面与界面重点实验室开放基金项目申请指南 - 海洋关键材料全国重点实验室；海洋关键材料全国重点实验室2026年度开放基金项目申请指南 - 海洋关键材料全国重点实验室</v>
+      </c>
+      <c r="F542" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G542" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H542" t="str" s="3">
+        <v>https://www.craes.cn/tzgg/tz/xxgk/202609/t20260929_1175497.shtml
+https://ocean.upc.edu.cn/2026/0424/c15098a488720/page.htm
+https://www.fio.org.cn/news/tzgg-detail-14972.htm
+https://ccms.hit.edu.cn/2026/0918/c13809a401763/page.htm
+https://kjch.qut.edu.cn/info/1035/2935.htm
+https://marinelab.nimte.cas.cn/news/notice/202606/t20260602_840372.html
+https://marinelab.nimte.cas.cn/news/notice/202603/t20260325_827993.html</v>
+      </c>
+      <c r="I542" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第165项</v>
+      </c>
+    </row>
+    <row r="543" ht="52.5" customHeight="1">
+      <c r="A543" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B543" t="str" s="3">
+        <v>安徽大学</v>
+      </c>
+      <c r="C543" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D543" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E543" t="str" s="3">
+        <v>查询：安徽大学 人机共融 开放课题 申请；定位：2025年度国家省部级重点实验室开放课题；开放交流；关于高节能电机及控制技术国家地方联合工程实验室关于接受2022年第一批开放课题申请的通知；开放课题；2026年度开放课题申请公告；关于杂化材料结构与功能调控教育部重点实验室2022年开放课题申报指南；2025年度安徽省智能计算及应用重点实验室开放课题申请与中期检查等有关事项的通知_通知公告_安徽省智能计算及应用重点实验室</v>
+      </c>
+      <c r="F543" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G543" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H543" t="str" s="3">
+        <v>https://www.hfuu.edu.cn/kjc/74/ff/c11997a161023/page.htm
+https://sai.ahu.edu.cn/kfjl/list.htm
+https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm
+https://sai.ahu.edu.cn/kfkt/list.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://www.chzu.edu.cn/2022/0418/c18154a253752/page.htm
+https://znjs.chnu.edu.cn/tzgg/content_134807</v>
+      </c>
+      <c r="I543" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第166项</v>
+      </c>
+    </row>
+    <row r="544" ht="52.5" customHeight="1">
+      <c r="A544" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B544" t="str" s="3">
+        <v>广西多源信息</v>
+      </c>
+      <c r="C544" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D544" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E544" t="str" s="3">
+        <v>查询：多源信息挖掘 安全 开放基金 2025；定位：2025年广西多源信息挖掘与安全重点验室开放课题基金（自筹经费）申请指南；智能算法安全全国重点实验室2025年度开放课题申请指南--智能算法安全全国重点实验室；关于申报2024年广西多源信息挖掘与安全重点实验室开放基金项目的通知；大数据智能分析与行业应用湖北省重点实验室关于下达2025年度开放基金的通知-湖北大学计算机学院；中国科学院文献情报中心智能情报支撑战略决策重点实验室2025年度开放基金申报指南--中国科学院文献情报中心；申请指南--岩土力学与工程安全全国重点实验室；露天煤矿灾害防治与生态保护全国重点实验室2025年度开放基金申请指南-矿山灾害预防控制实验室</v>
+      </c>
+      <c r="F544" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G544" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H544" t="str" s="3">
+        <v>https://mims.gxnu.edu.cn/2025/1011/c6728a327370/page.htm
+https://klais.ict.ac.cn/tzgg/xmzj/202506/t20250625_588836.html
+https://mims.gxnu.edu.cn/2024/0411/c6728a286224/page.htm
+https://cs.hubu.edu.cn/zinfogh.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=9455&amp;wbtreeid=1166
+https://las.cas.cn/news/tzgg/202506/t20250623_7873422.html
+https://www.sklgme.org/kfjl/kfjj/sqzn/
+https://mdpc.sdust.edu.cn/info/1026/2519.htm</v>
+      </c>
+      <c r="I544" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第167项</v>
+      </c>
+    </row>
+    <row r="545" ht="52.5" customHeight="1">
+      <c r="A545" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B545" t="str" s="3">
+        <v>中国科学院自动化所</v>
+      </c>
+      <c r="C545" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D545" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E545" t="str" s="3">
+        <v>查询：site:ivi.ia.ac.cn 开放课题；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F545" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G545" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H545" t="str" s="3"/>
+      <c r="I545" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第168项</v>
+      </c>
+    </row>
+    <row r="546" ht="52.5" customHeight="1">
+      <c r="A546" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B546" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C546" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D546" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E546" t="str" s="3">
+        <v>查询：site:nuist.edu.cn "机器人" "开放基金" "2026"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F546" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G546" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H546" t="str" s="3"/>
+      <c r="I546" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第169项</v>
+      </c>
+    </row>
+    <row r="547" ht="52.5" customHeight="1">
+      <c r="A547" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B547" t="str" s="3">
+        <v>中国科学院自动化所</v>
+      </c>
+      <c r="C547" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D547" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E547" t="str" s="3">
+        <v>查询：site:brain-ai.ia.ac.cn 开放基金；定位：脑网络组研究中心揭示颅内电刺激改善个体情绪状态的新机制----脑图谱与类脑智能实验室；自动化所举办第二十届“自动化之光”公众科学日活动----脑图谱与类脑智能实验室；脑图谱与类脑智能实验室研发可穿戴经颅磁刺激设备----脑图谱与类脑智能实验室；类脑认知智能团队打造全脉冲神经网络的类脑认知智能引擎----脑图谱与类脑智能实验室；脑图谱与类脑智能实验室生命科学智能与系统团队存算一体化高级工程师招聘启事----脑图谱与类脑智能实验室；脑启发神经环路演化赋能脉冲神经网络创新----脑图谱与类脑智能实验室；脑图谱与类脑智能实验室余山研究员作“当AI遇见脑科学”科普报告----脑图谱与类脑智能实验室</v>
+      </c>
+      <c r="F547" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G547" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H547" t="str" s="3">
+        <v>https://brain-ai.ia.ac.cn/xsyl/kydt/202411/t20241125_251089.html
+https://brain-ai.ia.ac.cn/kxcb/kpdt/202411/t20241125_251226.html
+https://brain-ai.ia.ac.cn/sylb/202503/t20250327_509060.html
+https://brain-ai.ia.ac.cn/xsyl/kydt/202411/t20241125_251084.html
+https://brain-ai.ia.ac.cn/rcpy/rcxq/202411/t20241125_251220.html
+https://brain-ai.ia.ac.cn/xsyl/kydt/202411/t20241125_251082.html
+https://brain-ai.ia.ac.cn/kxcb/kpdt/202411/t20241125_251223.html</v>
+      </c>
+      <c r="I547" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第170项</v>
+      </c>
+    </row>
+    <row r="548" ht="52.5" customHeight="1">
+      <c r="A548" t="str" s="3">
+        <v>2026-10-09逐平台机制/补漏</v>
+      </c>
+      <c r="B548" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C548" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D548" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E548" t="str" s="3">
+        <v>查询：site:nuist.edu.cn "智慧医疗" "开放课题"；定位：本次未定位正式项目公告</v>
+      </c>
+      <c r="F548" t="str" s="3">
+        <v>未定位公告不等同确认没有基金；机构未查完整目录及逐室年份见相邻目录行。</v>
+      </c>
+      <c r="G548" t="str" s="3">
+        <v>仅完成本行具体查询；正式项目、剔除与首次访问障碍另列。</v>
+      </c>
+      <c r="H548" t="str" s="3"/>
+      <c r="I548" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第171项</v>
+      </c>
+    </row>
+    <row r="549" ht="52.5" customHeight="1">
+      <c r="A549" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B549" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C549" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D549" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E549" t="str" s="3">
+        <v>官方科研部门9个实体：多模态AI、复杂系统认知决策、专用集成电路工程中心、分子影像、工业视觉智能装备、模式识别、脑图谱类脑、紫东太初、伦理治理；工业视觉6研究部及脑机机器人任务已读；2项2026基金复用原记录。</v>
+      </c>
+      <c r="F549" t="str" s="3">
+        <v>工业视觉/脑图谱定向未定位新增正式开放公告；其他非已有平台逐室机制仍需核，不认定9个全部完成。</v>
+      </c>
+      <c r="G549" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H549" t="str" s="3">
+        <v>https://ia.cas.cn/jgsz/kyxt/
+https://ia.cas.cn/jgsz/kyxt/gysj/
+https://ia.cas.cn/jgsz/kyxt/brain/</v>
+      </c>
+      <c r="I549" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="550" ht="52.5" customHeight="1">
+      <c r="A550" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B550" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C550" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D550" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E550" t="str" s="3">
+        <v>计算机信息工程/智能计算/网络机器人系资料及研究机构目录已读；明确智能决策机器人系统、工业互联网省工程中心、移动平台感知国际中心、无人航行实时感知基地、嵌入式省重点实验室、语音图像省重点实验室、机器人仿真、工信部智能感知计算等。</v>
+      </c>
+      <c r="F550" t="str" s="3">
+        <v>2026/2027和历史开放机制定向查询未定位额外正式公告；机电目录首次超时，电子目录后段未取得；全校其他学院目录仍未齐。</v>
+      </c>
+      <c r="G550" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H550" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1657/7520.htm
+https://jsj.nwpu.edu.cn/info/1657/7521.htm
+https://jsj.nwpu.edu.cn/info/1657/10601.htm
+https://jsj.nwpu.edu.cn/snew/list.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1556</v>
+      </c>
+      <c r="I550" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="551" ht="52.5" customHeight="1">
+      <c r="A551" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B551" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C551" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D551" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E551" t="str" s="3">
+        <v>逐名查询机器人系统集成、智能无人船、智能焊接机器人、人机共生智能、手术机器人联合实验室、超级机器人研究院6平台；年度2026/2027及历史机制查询留源。</v>
+      </c>
+      <c r="F551" t="str" s="3">
+        <v>中央现行平台总目录未取得；主页首次超时；旧6项目录不足以代表全校，各平台正式外部基金未确认。</v>
+      </c>
+      <c r="G551" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H551" t="str" s="3">
+        <v>https://www.scut.edu.cn/new/
+https://www.scut.edu.cn/faculty/lab.htm</v>
+      </c>
+      <c r="I551" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="552" ht="52.5" customHeight="1">
+      <c r="A552" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B552" t="str" s="3">
+        <v>香港理工大学</v>
+      </c>
+      <c r="C552" t="str" s="3">
+        <v>香港/内地研究院</v>
+      </c>
+      <c r="D552" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E552" t="str" s="3">
+        <v>主目录12相关中心入口及跨校机制定向核；RCLAE2025指南3页全文已核，N036历史新增；RIAM校内限制已剔除；PAIR合作指南SSO受阻。</v>
+      </c>
+      <c r="F552" t="str" s="3">
+        <v>PAIR外部资格与配套经费未核；内地研究院逐院年度机制尚未查齐；RCLAE2026/2027正式轮次未取得。</v>
+      </c>
+      <c r="G552" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H552" t="str" s="3">
+        <v>https://www.polyu.edu.hk/research/labs-institutes-centres/
+https://www.polyu.edu.hk/rclae/-/media/department/rclae/research/rclae-seed-fund/guideline-of-project-application-rclae.pdf?hash=819336D280E1BF493E450BE2101E582E&amp;rev=0ca29d677b05438daae12be0cee8fccb</v>
+      </c>
+      <c r="I552" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="553" ht="52.5" customHeight="1">
+      <c r="A553" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B553" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C553" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D553" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E553" t="str" s="3">
+        <v>4页实验室目录复用；软传感执行器机器人、无人系统2页首次失败；机械/计算机实验室目录首次404或重定向受阻。</v>
+      </c>
+      <c r="F553" t="str" s="3">
+        <v>机器人等相关实验室尚未查齐外部基金机制；学院改版目录需人工原件；已有IoT线索不代表全校完成。</v>
+      </c>
+      <c r="G553" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H553" t="str" s="3">
+        <v>https://reg.um.edu.mo/download/um-academic-calendar/11labs.pdf
+https://www.fst.um.edu.mo/eme/laboratories/
+https://www.cis.um.edu.mo/labs.html</v>
+      </c>
+      <c r="I553" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="554" ht="52.5" customHeight="1">
+      <c r="A554" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B554" t="str" s="3">
+        <v>安徽理工大学</v>
+      </c>
+      <c r="C554" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D554" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E554" t="str" s="3">
+        <v>煤炭无人化全国重点实验室首页确认2026第一批为已有M018，未重复；粉尘防控2025/2026共享批次全文已读，任务为粉尘机理、防控、职业危害，剔除E075。</v>
+      </c>
+      <c r="F554" t="str" s="3">
+        <v>不由实验室宣传的机器人研究反推所有开放任务相关；其他平台及2027公告继续补查。</v>
+      </c>
+      <c r="G554" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H554" t="str" s="3">
+        <v>https://cdsys.aust.edu.cn/
+https://eklab.aust.edu.cn/info/1004/1214.htm</v>
+      </c>
+      <c r="I554" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="555" ht="52.5" customHeight="1">
+      <c r="A555" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B555" t="str" s="3">
+        <v>石河子大学</v>
+      </c>
+      <c r="C555" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D555" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E555" t="str" s="3">
+        <v>计算智能与网络信息安全兵团重点实验室2024公告全文已核，任务为安全可信、密码、隐私与工控安全，E074剔除；目录另列室内外一体定位平台。</v>
+      </c>
+      <c r="F555" t="str" s="3">
+        <v>定位平台及其他工学院逐室2026/2027尚未查齐。</v>
+      </c>
+      <c r="G555" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H555" t="str" s="3">
+        <v>https://cs.shzu.edu.cn/_t513/2024/0921/c12051a209837/page.htm</v>
+      </c>
+      <c r="I555" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="556" ht="52.5" customHeight="1">
+      <c r="A556" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B556" t="str" s="3">
+        <v>广西师范大学</v>
+      </c>
+      <c r="C556" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D556" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E556" t="str" s="3">
+        <v>多源信息挖掘与安全重点实验室2025全文明确经费自筹，E076剔除，不纳入有资助项目台账。</v>
+      </c>
+      <c r="F556" t="str" s="3">
+        <v>本结论仅2025轮次；2024及2026/2027不套用同一资助结论。</v>
+      </c>
+      <c r="G556" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H556" t="str" s="3">
+        <v>https://mims.gxnu.edu.cn/2025/1011/c6728a327370/page.htm</v>
+      </c>
+      <c r="I556" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="557" ht="52.5" customHeight="1">
+      <c r="A557" t="str" s="3">
+        <v>2026-10-09具体平台目录/年度核验</v>
+      </c>
+      <c r="B557" t="str" s="3">
+        <v>常州大学</v>
+      </c>
+      <c r="C557" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D557" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E557" t="str" s="3">
+        <v>2026龙城已剔除M175复用：该批面向机械及大数据学院内部遴选；2025历史正文明确常州大学第一承担单位、固定合作、每年会议、≤10万及至少2论文；不据此覆盖2026校内限制。</v>
+      </c>
+      <c r="F557" t="str" s="3">
+        <v>2025是否允许校外负责人未明，未擅自新增个人项目；能源动力工程中心2025方向为图片/附件，尚待查。</v>
+      </c>
+      <c r="G557" t="str" s="3">
+        <v>已查范围仅限本行明确平台与年度，剩余缺口继续执行。</v>
+      </c>
+      <c r="H557" t="str" s="3">
+        <v>https://iimt.cczu.edu.cn/2025/0521/c22023a391481/page.htm
+https://cmee.cczu.edu.cn/2025/0620/c22043a395328/page.htm</v>
+      </c>
+      <c r="I557" t="str" s="3">
+        <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
       </c>
     </row>
   </sheetData>
@@ -32417,24 +34843,24 @@
         <v>公告</v>
       </c>
     </row>
-    <row r="13" ht="66" customHeight="1">
-      <c r="A13" s="18" t="str">
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B13" s="13" t="d">
-        <v>2018-06-30T00:00:00.000Z</v>
-      </c>
-      <c r="C13" s="14" t="str">
-        <v>广东工业大学·微电子精密制造技术与装备教育部重点实验室（现网站名：电子精密制造装备及技术）</v>
-      </c>
-      <c r="D13" s="15" t="str">
-        <v>精密操作机器人机构优化、复杂机电系统精密运动控制、视觉定位、少自由度精密操作机器人</v>
-      </c>
-      <c r="E13" s="15" t="str">
-        <v>平均2—3万元</v>
-      </c>
-      <c r="F13" s="16" t="str">
-        <v>公告</v>
+      <c r="B13" t="n" s="13">
+        <v>45775</v>
+      </c>
+      <c r="C13" t="str" s="14">
+        <v>香港理工大学·Research Centre for Low Altitude Economy（低空经济研究中心）</v>
+      </c>
+      <c r="D13" t="str" s="15">
+        <v>明确可靠感知、鲁棒控制、应急安全飞行及无人机应用；须关联低空经济。</v>
+      </c>
+      <c r="E13" t="str" s="15">
+        <v>平台/应用≤50万港币；基础≤30万港币；探索15万港币</v>
+      </c>
+      <c r="F13" t="str" s="16">
+        <v>正式指南</v>
       </c>
     </row>
     <row r="14" ht="66" customHeight="1">
@@ -32442,16 +34868,16 @@
         <v>已截止</v>
       </c>
       <c r="B14" s="13" t="d">
-        <v>2023-10-15T00:00:00.000Z</v>
+        <v>2018-06-30T00:00:00.000Z</v>
       </c>
       <c r="C14" s="14" t="str">
-        <v>中国科学院深圳先进技术研究院·广东省机器人与智能系统重点实验室（智能仿生研究中心）</v>
+        <v>广东工业大学·微电子精密制造技术与装备教育部重点实验室（现网站名：电子精密制造装备及技术）</v>
       </c>
       <c r="D14" s="15" t="str">
-        <v>穿戴、工业、软体及康复机器人</v>
+        <v>精密操作机器人机构优化、复杂机电系统精密运动控制、视觉定位、少自由度精密操作机器人</v>
       </c>
       <c r="E14" s="15" t="str">
-        <v>5—10万元（2023年度）</v>
+        <v>平均2—3万元</v>
       </c>
       <c r="F14" s="16" t="str">
         <v>公告</v>
@@ -32462,16 +34888,16 @@
         <v>已截止</v>
       </c>
       <c r="B15" s="13" t="d">
-        <v>2024-11-29T00:00:00.000Z</v>
+        <v>2023-10-15T00:00:00.000Z</v>
       </c>
       <c r="C15" s="14" t="str">
-        <v>广东工业大学·广东省智能决策与协同控制重点实验室</v>
+        <v>中国科学院深圳先进技术研究院·广东省机器人与智能系统重点实验室（智能仿生研究中心）</v>
       </c>
       <c r="D15" s="15" t="str">
-        <v>无人自主系统的深度/强化学习优化决策、状态估计与协同控制</v>
+        <v>穿戴、工业、软体及康复机器人</v>
       </c>
       <c r="E15" s="15" t="str">
-        <v>5—10万元</v>
+        <v>5—10万元（2023年度）</v>
       </c>
       <c r="F15" s="16" t="str">
         <v>公告</v>
@@ -32482,13 +34908,13 @@
         <v>已截止</v>
       </c>
       <c r="B16" s="13" t="d">
-        <v>2026-01-05T00:00:00.000Z</v>
+        <v>2024-11-29T00:00:00.000Z</v>
       </c>
       <c r="C16" s="14" t="str">
-        <v>哈尔滨工业大学（深圳）·先进运动控制技术与现代自动化装备重点实验室</v>
+        <v>广东工业大学·广东省智能决策与协同控制重点实验室</v>
       </c>
       <c r="D16" s="15" t="str">
-        <v>机器人运动控制、柔性操作及现代自动化装备</v>
+        <v>无人自主系统的深度/强化学习优化决策、状态估计与协同控制</v>
       </c>
       <c r="E16" s="15" t="str">
         <v>5—10万元</v>
@@ -32502,16 +34928,16 @@
         <v>已截止</v>
       </c>
       <c r="B17" s="13" t="d">
-        <v>2026-03-31T00:00:00.000Z</v>
+        <v>2026-01-05T00:00:00.000Z</v>
       </c>
       <c r="C17" s="14" t="str">
-        <v>人工智能与数字经济广东省实验室（深圳）·光明实验室2026年首轮开放课题</v>
+        <v>哈尔滨工业大学（深圳）·先进运动控制技术与现代自动化装备重点实验室</v>
       </c>
       <c r="D17" s="15" t="str">
-        <v>多模态世界模型、智能体感知交互、3D/4D重建及可交互场景；与M097第二批分别记录</v>
+        <v>机器人运动控制、柔性操作及现代自动化装备</v>
       </c>
       <c r="E17" s="15" t="str">
-        <v>30—100万元/项</v>
+        <v>5—10万元</v>
       </c>
       <c r="F17" s="16" t="str">
         <v>公告</v>
@@ -32522,17 +34948,16 @@
         <v>已截止</v>
       </c>
       <c r="B18" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C18" s="14" t="str">
-        <v>深圳市人工智能与机器人研究院AIRS·医疗机器人方向开放课题</v>
+        <v>人工智能与数字经济广东省实验室（深圳）·光明实验室2026年首轮开放课题</v>
       </c>
       <c r="D18" s="15" t="str">
-        <v>医疗机器人、内窥镜感知与导航</v>
+        <v>多模态世界模型、智能体感知交互、3D/4D重建及可交互场景；与M097第二批分别记录</v>
       </c>
       <c r="E18" s="15" t="str">
-        <v>原则10万元/项，不超过5项，实际按研究内容与评审意见；
-不限制各方向项目数量。</v>
+        <v>30—100万元/项</v>
       </c>
       <c r="F18" s="16" t="str">
         <v>公告</v>
@@ -32543,16 +34968,17 @@
         <v>已截止</v>
       </c>
       <c r="B19" s="13" t="d">
-        <v>2026-08-24T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C19" s="14" t="str">
-        <v>深圳光明实验室·人工智能与数字经济广东省实验室</v>
+        <v>深圳市人工智能与机器人研究院AIRS·医疗机器人方向开放课题</v>
       </c>
       <c r="D19" s="15" t="str">
-        <v>面向具身任务的世界模型、三维/四维交互与验证</v>
+        <v>医疗机器人、内窥镜感知与导航</v>
       </c>
       <c r="E19" s="15" t="str">
-        <v>一般60万元、重大100万元、开放30万元</v>
+        <v>原则10万元/项，不超过5项，实际按研究内容与评审意见；
+不限制各方向项目数量。</v>
       </c>
       <c r="F19" s="16" t="str">
         <v>公告</v>
@@ -32563,16 +34989,16 @@
         <v>已截止</v>
       </c>
       <c r="B20" s="13" t="d">
-        <v>2025-10-15T00:00:00.000Z</v>
+        <v>2026-08-24T00:00:00.000Z</v>
       </c>
       <c r="C20" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
+        <v>深圳光明实验室·人工智能与数字经济广东省实验室</v>
       </c>
       <c r="D20" s="15" t="str">
-        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
+        <v>面向具身任务的世界模型、三维/四维交互与验证</v>
       </c>
       <c r="E20" s="15" t="str">
-        <v>5—8万元</v>
+        <v>一般60万元、重大100万元、开放30万元</v>
       </c>
       <c r="F20" s="16" t="str">
         <v>公告</v>
@@ -32583,16 +35009,16 @@
         <v>已截止</v>
       </c>
       <c r="B21" s="13" t="d">
-        <v>2026-05-11T00:00:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C21" s="14" t="str">
-        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D21" s="15" t="str">
-        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
+        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
       </c>
       <c r="E21" s="15" t="str">
-        <v>10万元/项；每方向1项</v>
+        <v>5—8万元</v>
       </c>
       <c r="F21" s="16" t="str">
         <v>公告</v>
@@ -32603,16 +35029,16 @@
         <v>已截止</v>
       </c>
       <c r="B22" s="13" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-11T00:00:00.000Z</v>
       </c>
       <c r="C22" s="14" t="str">
-        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
+        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
       </c>
       <c r="D22" s="15" t="str">
-        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
+        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
       </c>
       <c r="E22" s="15" t="str">
-        <v>5—10万元</v>
+        <v>10万元/项；每方向1项</v>
       </c>
       <c r="F22" s="16" t="str">
         <v>公告</v>
@@ -32623,16 +35049,16 @@
         <v>已截止</v>
       </c>
       <c r="B23" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-05-29T00:00:00.000Z</v>
       </c>
       <c r="C23" s="14" t="str">
-        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
+        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
       </c>
       <c r="D23" s="15" t="str">
-        <v>地下空间具身智能感知、定位与点云建模</v>
+        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
       </c>
       <c r="E23" s="15" t="str">
-        <v>一般≥2万元；重点≥3万元</v>
+        <v>5—10万元</v>
       </c>
       <c r="F23" s="16" t="str">
         <v>公告</v>
@@ -32643,16 +35069,16 @@
         <v>已截止</v>
       </c>
       <c r="B24" s="13" t="d">
-        <v>2026-07-31T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C24" s="14" t="str">
-        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
+        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
       </c>
       <c r="D24" s="15" t="str">
-        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
+        <v>地下空间具身智能感知、定位与点云建模</v>
       </c>
       <c r="E24" s="15" t="str">
-        <v>30—90万元（无人机监视反制专项）</v>
+        <v>一般≥2万元；重点≥3万元</v>
       </c>
       <c r="F24" s="16" t="str">
         <v>公告</v>
@@ -32663,16 +35089,16 @@
         <v>已截止</v>
       </c>
       <c r="B25" s="13" t="d">
-        <v>2026-08-28T00:00:00.000Z</v>
+        <v>2026-07-31T00:00:00.000Z</v>
       </c>
       <c r="C25" s="14" t="str">
-        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
+        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
       </c>
       <c r="D25" s="15" t="str">
-        <v>机器人多接触规划、具身技能学习与运动行为</v>
+        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
       </c>
       <c r="E25" s="15" t="str">
-        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
+        <v>30—90万元（无人机监视反制专项）</v>
       </c>
       <c r="F25" s="16" t="str">
         <v>公告</v>
@@ -32683,57 +35109,57 @@
         <v>已截止</v>
       </c>
       <c r="B26" s="13" t="d">
-        <v>2025-08-10T00:00:00.000Z</v>
+        <v>2026-08-28T00:00:00.000Z</v>
       </c>
       <c r="C26" s="14" t="str">
-        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
       </c>
       <c r="D26" s="15" t="str">
-        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+        <v>机器人多接触规划、具身技能学习与运动行为</v>
       </c>
       <c r="E26" s="15" t="str">
-        <v>5—10万元/项</v>
+        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
       </c>
       <c r="F26" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="27" ht="79.5" customHeight="1">
+    <row r="27" ht="66" customHeight="1">
       <c r="A27" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B27" s="13" t="d">
+        <v>2025-08-10T00:00:00.000Z</v>
+      </c>
+      <c r="C27" s="14" t="str">
+        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="D27" s="15" t="str">
+        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+      </c>
+      <c r="E27" s="15" t="str">
+        <v>5—10万元/项</v>
+      </c>
+      <c r="F27" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="28" ht="79.5" customHeight="1">
+      <c r="A28" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B28" s="13" t="d">
         <v>2026-05-06T00:00:00.000Z</v>
       </c>
-      <c r="C27" s="14" t="str">
+      <c r="C28" s="14" t="str">
         <v>煤炭智能开采与岩层控制全国重点实验室（北京；具体依托机构待核，沈阳化工为转载单位）·煤炭智能开采与岩层控制全国重点实验室</v>
       </c>
-      <c r="D27" s="15" t="str">
+      <c r="D28" s="15" t="str">
         <v>机械臂—底座耦合振动、末端自适应定位（依托机构尚待确认）</v>
       </c>
-      <c r="E27" s="15" t="str">
+      <c r="E28" s="15" t="str">
         <v>2026年度实验室设开放基金项目共计40项，其中重点项目4项，每项资助研究金额为45-65万元；
 一般项目36项，每项资助研究金额为15-25万元。</v>
-      </c>
-      <c r="F27" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="28" ht="66" customHeight="1">
-      <c r="A28" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B28" s="13" t="d">
-        <v>2026-08-20T00:00:00.000Z</v>
-      </c>
-      <c r="C28" s="14" t="str">
-        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
-      </c>
-      <c r="D28" s="15" t="str">
-        <v>自主无人系统及机器人研究</v>
-      </c>
-      <c r="E28" s="15" t="str">
-        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F28" s="16" t="str">
         <v>公告</v>
@@ -32744,16 +35170,16 @@
         <v>已截止</v>
       </c>
       <c r="B29" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-08-20T00:00:00.000Z</v>
       </c>
       <c r="C29" s="14" t="str">
-        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
+        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D29" s="15" t="str">
-        <v>无人越野平台世界模型、具身感知与控制</v>
+        <v>自主无人系统及机器人研究</v>
       </c>
       <c r="E29" s="15" t="str">
-        <v>重点20—30万元、一般5—10万元</v>
+        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F29" s="16" t="str">
         <v>公告</v>
@@ -32764,16 +35190,16 @@
         <v>已截止</v>
       </c>
       <c r="B30" s="13" t="d">
-        <v>2026-09-20T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C30" s="14" t="str">
-        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
+        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
       </c>
       <c r="D30" s="15" t="str">
-        <v>平台具身智能与异构智能体协同</v>
+        <v>无人越野平台世界模型、具身感知与控制</v>
       </c>
       <c r="E30" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>重点20—30万元、一般5—10万元</v>
       </c>
       <c r="F30" s="16" t="str">
         <v>公告</v>
@@ -32784,16 +35210,16 @@
         <v>已截止</v>
       </c>
       <c r="B31" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2026-09-20T00:00:00.000Z</v>
       </c>
       <c r="C31" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室</v>
+        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
       </c>
       <c r="D31" s="15" t="str">
-        <v>工业机器人传动、机电耦合与高端装备传动</v>
+        <v>平台具身智能与异构智能体协同</v>
       </c>
       <c r="E31" s="15" t="str">
-        <v>面上5—8万元。</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F31" s="16" t="str">
         <v>公告</v>
@@ -32804,16 +35230,16 @@
         <v>已截止</v>
       </c>
       <c r="B32" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C32" s="14" t="str">
-        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室</v>
       </c>
       <c r="D32" s="15" t="str">
-        <v>具身智能世界模型与开放环境视觉感知</v>
+        <v>工业机器人传动、机电耦合与高端装备传动</v>
       </c>
       <c r="E32" s="15" t="str">
-        <v>3万元</v>
+        <v>面上5—8万元。</v>
       </c>
       <c r="F32" s="16" t="str">
         <v>公告</v>
@@ -32824,16 +35250,16 @@
         <v>已截止</v>
       </c>
       <c r="B33" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C33" s="14" t="str">
-        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
+        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
       </c>
       <c r="D33" s="15" t="str">
-        <v>山区建造装备及机器人</v>
+        <v>具身智能世界模型与开放环境视觉感知</v>
       </c>
       <c r="E33" s="15" t="str">
-        <v>每项6万元。</v>
+        <v>3万元</v>
       </c>
       <c r="F33" s="16" t="str">
         <v>公告</v>
@@ -32844,16 +35270,16 @@
         <v>已截止</v>
       </c>
       <c r="B34" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C34" s="14" t="str">
-        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
+        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
       </c>
       <c r="D34" s="15" t="str">
-        <v>桥梁检测机器人与无人巡检装备</v>
+        <v>山区建造装备及机器人</v>
       </c>
       <c r="E34" s="15" t="str">
-        <v>5—10万元</v>
+        <v>每项6万元。</v>
       </c>
       <c r="F34" s="16" t="str">
         <v>公告</v>
@@ -32864,17 +35290,16 @@
         <v>已截止</v>
       </c>
       <c r="B35" s="13" t="d">
-        <v>2026-09-01T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C35" s="14" t="str">
-        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
+        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
       </c>
       <c r="D35" s="15" t="str">
-        <v>工业机器人及智能产线运维、故障预测与控制</v>
+        <v>桥梁检测机器人与无人巡检装备</v>
       </c>
       <c r="E35" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F35" s="16" t="str">
         <v>公告</v>
@@ -32885,13 +35310,13 @@
         <v>已截止</v>
       </c>
       <c r="B36" s="13" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-09-01T00:00:00.000Z</v>
       </c>
       <c r="C36" s="14" t="str">
-        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
+        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
       </c>
       <c r="D36" s="15" t="str">
-        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
+        <v>工业机器人及智能产线运维、故障预测与控制</v>
       </c>
       <c r="E36" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -32906,13 +35331,13 @@
         <v>已截止</v>
       </c>
       <c r="B37" s="13" t="d">
-        <v>2025-02-28T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="C37" s="14" t="str">
-        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
+        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
       </c>
       <c r="D37" s="15" t="str">
-        <v>重载机器人减速器、直驱电机及关键部件</v>
+        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
       </c>
       <c r="E37" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -32927,16 +35352,17 @@
         <v>已截止</v>
       </c>
       <c r="B38" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-02-28T00:00:00.000Z</v>
       </c>
       <c r="C38" s="14" t="str">
-        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
+        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
       </c>
       <c r="D38" s="15" t="str">
-        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
+        <v>重载机器人减速器、直驱电机及关键部件</v>
       </c>
       <c r="E38" s="15" t="str">
-        <v>重点20万元；一般10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F38" s="16" t="str">
         <v>公告</v>
@@ -32947,16 +35373,16 @@
         <v>已截止</v>
       </c>
       <c r="B39" s="13" t="d">
-        <v>2026-06-14T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C39" s="14" t="str">
-        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
+        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
       </c>
       <c r="D39" s="15" t="str">
-        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
+        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
       </c>
       <c r="E39" s="15" t="str">
-        <v>10万元</v>
+        <v>重点20万元；一般10万元</v>
       </c>
       <c r="F39" s="16" t="str">
         <v>公告</v>
@@ -32967,16 +35393,16 @@
         <v>已截止</v>
       </c>
       <c r="B40" s="13" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2026-06-14T00:00:00.000Z</v>
       </c>
       <c r="C40" s="14" t="str">
-        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
+        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
       </c>
       <c r="D40" s="15" t="str">
-        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
+        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
       </c>
       <c r="E40" s="15" t="str">
-        <v>其他一般≤10万、重点≤15万</v>
+        <v>10万元</v>
       </c>
       <c r="F40" s="16" t="str">
         <v>公告</v>
@@ -32987,16 +35413,16 @@
         <v>已截止</v>
       </c>
       <c r="B41" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-09-24T00:00:00.000Z</v>
       </c>
       <c r="C41" s="14" t="str">
-        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
+        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
       </c>
       <c r="D41" s="15" t="str">
-        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
+        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
       </c>
       <c r="E41" s="15" t="str">
-        <v>10—15万元</v>
+        <v>其他一般≤10万、重点≤15万</v>
       </c>
       <c r="F41" s="16" t="str">
         <v>公告</v>
@@ -33007,16 +35433,16 @@
         <v>已截止</v>
       </c>
       <c r="B42" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C42" s="14" t="str">
-        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
+        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
       </c>
       <c r="D42" s="15" t="str">
-        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
+        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
       </c>
       <c r="E42" s="15" t="str">
-        <v>3万元（首拨1万元，中期2万元）</v>
+        <v>10—15万元</v>
       </c>
       <c r="F42" s="16" t="str">
         <v>公告</v>
@@ -33027,17 +35453,16 @@
         <v>已截止</v>
       </c>
       <c r="B43" s="13" t="d">
-        <v>2022-10-30T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C43" s="14" t="str">
-        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
+        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
       </c>
       <c r="D43" s="15" t="str">
-        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
+        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
       </c>
       <c r="E43" s="15" t="str">
-        <v>已核官方2022历史公告：5万元/项；
-未取得2026正式指南，不将历史额度视为当期额度。</v>
+        <v>3万元（首拨1万元，中期2万元）</v>
       </c>
       <c r="F43" s="16" t="str">
         <v>公告</v>
@@ -33048,16 +35473,17 @@
         <v>已截止</v>
       </c>
       <c r="B44" s="13" t="d">
-        <v>2022-11-04T00:00:00.000Z</v>
+        <v>2022-10-30T00:00:00.000Z</v>
       </c>
       <c r="C44" s="14" t="str">
-        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
+        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
       </c>
       <c r="D44" s="15" t="str">
-        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
+        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>一般2万元；重点4—6万元</v>
+        <v>已核官方2022历史公告：5万元/项；
+未取得2026正式指南，不将历史额度视为当期额度。</v>
       </c>
       <c r="F44" s="16" t="str">
         <v>公告</v>
@@ -33068,16 +35494,16 @@
         <v>已截止</v>
       </c>
       <c r="B45" s="13" t="d">
-        <v>2023-07-30T00:00:00.000Z</v>
+        <v>2022-11-04T00:00:00.000Z</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
+        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
+        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
       </c>
       <c r="E45" s="15" t="str">
-        <v>拟资助8—10项；单项金额未载</v>
+        <v>一般2万元；重点4—6万元</v>
       </c>
       <c r="F45" s="16" t="str">
         <v>公告</v>
@@ -33088,16 +35514,16 @@
         <v>已截止</v>
       </c>
       <c r="B46" s="13" t="d">
-        <v>2024-09-30T00:00:00.000Z</v>
+        <v>2023-07-30T00:00:00.000Z</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>南昌大学·智能机器人江西省重点实验室</v>
+        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>智能机器人机构、感知与控制</v>
+        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>重点3万元、一般2万元（2024年度）</v>
+        <v>拟资助8—10项；单项金额未载</v>
       </c>
       <c r="F46" s="16" t="str">
         <v>公告</v>
@@ -33108,16 +35534,16 @@
         <v>已截止</v>
       </c>
       <c r="B47" s="13" t="d">
-        <v>2025-03-31T00:00:00.000Z</v>
+        <v>2024-09-30T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
+        <v>南昌大学·智能机器人江西省重点实验室</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
+        <v>智能机器人机构、感知与控制</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>2—3万元/项左右</v>
+        <v>重点3万元、一般2万元（2024年度）</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
@@ -33128,16 +35554,16 @@
         <v>已截止</v>
       </c>
       <c r="B48" s="13" t="d">
-        <v>2025-04-25T00:00:00.000Z</v>
+        <v>2025-03-31T00:00:00.000Z</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>仿生机器人、新型驱动与感知及仿生装备</v>
+        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>5万元</v>
+        <v>2—3万元/项左右</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
@@ -33148,16 +35574,16 @@
         <v>已截止</v>
       </c>
       <c r="B49" s="13" t="d">
-        <v>2025-04-30T00:00:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>共融机器人控制、复杂智能体系统协同与控制</v>
+        <v>仿生机器人、新型驱动与感知及仿生装备</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>评审确定</v>
+        <v>5万元</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
@@ -33168,16 +35594,16 @@
         <v>已截止</v>
       </c>
       <c r="B50" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C50" s="14" t="str">
-        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
+        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
       </c>
       <c r="D50" s="15" t="str">
-        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
+        <v>共融机器人控制、复杂智能体系统协同与控制</v>
       </c>
       <c r="E50" s="15" t="str">
-        <v>5万元</v>
+        <v>评审确定</v>
       </c>
       <c r="F50" s="16" t="str">
         <v>公告</v>
@@ -33188,16 +35614,16 @@
         <v>已截止</v>
       </c>
       <c r="B51" s="13" t="d">
-        <v>2025-09-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C51" s="14" t="str">
-        <v>同济大学·自主智能无人系统全国重点实验室</v>
+        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
       </c>
       <c r="D51" s="15" t="str">
-        <v>自主智能无人系统与机器人感知、决策、控制</v>
+        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
       </c>
       <c r="E51" s="15" t="str">
-        <v>一般5—10万元、重点20—30万元</v>
+        <v>5万元</v>
       </c>
       <c r="F51" s="16" t="str">
         <v>公告</v>
@@ -33208,17 +35634,16 @@
         <v>已截止</v>
       </c>
       <c r="B52" s="13" t="d">
-        <v>2025-10-31T00:00:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C52" s="14" t="str">
-        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
+        <v>同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D52" s="15" t="str">
-        <v>机器人技术与系统、机器人学习、感知与控制</v>
+        <v>自主智能无人系统与机器人感知、决策、控制</v>
       </c>
       <c r="E52" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>一般5—10万元、重点20—30万元</v>
       </c>
       <c r="F52" s="16" t="str">
         <v>公告</v>
@@ -33229,17 +35654,17 @@
         <v>已截止</v>
       </c>
       <c r="B53" s="13" t="d">
-        <v>2025-11-03T00:00:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C53" s="14" t="str">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
+        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
       </c>
       <c r="D53" s="15" t="str">
-        <v>智能机器人感知、控制与系统</v>
+        <v>机器人技术与系统、机器人学习、感知与控制</v>
       </c>
       <c r="E53" s="15" t="str">
-        <v>校外开放基金1万元/项，拟5项；
-校内创新基金不同计划</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F53" s="16" t="str">
         <v>公告</v>
@@ -33250,16 +35675,17 @@
         <v>已截止</v>
       </c>
       <c r="B54" s="13" t="d">
-        <v>2025-11-07T00:00:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C54" s="14" t="str">
-        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D54" s="15" t="str">
-        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
+        <v>智能机器人感知、控制与系统</v>
       </c>
       <c r="E54" s="15" t="str">
-        <v>2万元</v>
+        <v>校外开放基金1万元/项，拟5项；
+校内创新基金不同计划</v>
       </c>
       <c r="F54" s="16" t="str">
         <v>公告</v>
@@ -33270,16 +35696,16 @@
         <v>已截止</v>
       </c>
       <c r="B55" s="13" t="d">
-        <v>2025-11-14T00:00:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C55" s="14" t="str">
-        <v>上海交通大学·机械系统与振动全国重点实验室</v>
+        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
       </c>
       <c r="D55" s="15" t="str">
-        <v>机器人设计、自主学习与神经接口</v>
+        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
       </c>
       <c r="E55" s="15" t="str">
-        <v>10—15万元</v>
+        <v>2万元</v>
       </c>
       <c r="F55" s="16" t="str">
         <v>公告</v>
@@ -33290,16 +35716,16 @@
         <v>已截止</v>
       </c>
       <c r="B56" s="13" t="d">
-        <v>2025-11-21T00:00:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C56" s="14" t="str">
-        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
+        <v>上海交通大学·机械系统与振动全国重点实验室</v>
       </c>
       <c r="D56" s="15" t="str">
-        <v>机器人视觉相关计算与随机数学方法</v>
+        <v>机器人设计、自主学习与神经接口</v>
       </c>
       <c r="E56" s="15" t="str">
-        <v>1—2万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F56" s="16" t="str">
         <v>公告</v>
@@ -33310,16 +35736,16 @@
         <v>已截止</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
+        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
+        <v>机器人视觉相关计算与随机数学方法</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>不超过3万元</v>
+        <v>1—2万元</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
@@ -33330,16 +35756,16 @@
         <v>已截止</v>
       </c>
       <c r="B58" s="13" t="d">
-        <v>2025-12-20T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C58" s="14" t="str">
-        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
+        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
       </c>
       <c r="D58" s="15" t="str">
-        <v>山地农业机器人、果实收获视觉与智能农机</v>
+        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
       </c>
       <c r="E58" s="15" t="str">
-        <v>不超过5万元</v>
+        <v>不超过3万元</v>
       </c>
       <c r="F58" s="16" t="str">
         <v>公告</v>
@@ -33350,16 +35776,16 @@
         <v>已截止</v>
       </c>
       <c r="B59" s="13" t="d">
-        <v>2025-12-31T00:00:00.000Z</v>
+        <v>2025-12-20T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
+        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
+        <v>山地农业机器人、果实收获视觉与智能农机</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>重点5万元、一般3万元</v>
+        <v>不超过5万元</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
@@ -33370,16 +35796,16 @@
         <v>已截止</v>
       </c>
       <c r="B60" s="13" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
+        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>深海无人潜航装备与智能控制</v>
+        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>不超过10万元</v>
+        <v>重点5万元、一般3万元</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
@@ -33390,16 +35816,16 @@
         <v>已截止</v>
       </c>
       <c r="B61" s="13" t="d">
-        <v>2026-01-31T00:00:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C61" s="14" t="str">
-        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
+        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
       </c>
       <c r="D61" s="15" t="str">
-        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
+        <v>深海无人潜航装备与智能控制</v>
       </c>
       <c r="E61" s="15" t="str">
-        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
+        <v>不超过10万元</v>
       </c>
       <c r="F61" s="16" t="str">
         <v>公告</v>
@@ -33410,16 +35836,16 @@
         <v>已截止</v>
       </c>
       <c r="B62" s="13" t="d">
-        <v>2026-03-10T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C62" s="14" t="str">
-        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
+        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
       </c>
       <c r="D62" s="15" t="str">
-        <v>工业机器人与柔性制造产线集成</v>
+        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
       </c>
       <c r="E62" s="15" t="str">
-        <v>4万元</v>
+        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
       </c>
       <c r="F62" s="16" t="str">
         <v>公告</v>
@@ -33430,16 +35856,16 @@
         <v>已截止</v>
       </c>
       <c r="B63" s="13" t="d">
-        <v>2026-03-20T00:00:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C63" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室</v>
+        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
       </c>
       <c r="D63" s="15" t="str">
-        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
+        <v>工业机器人与柔性制造产线集成</v>
       </c>
       <c r="E63" s="15" t="str">
-        <v>单项不超过10万元</v>
+        <v>4万元</v>
       </c>
       <c r="F63" s="16" t="str">
         <v>公告</v>
@@ -33450,16 +35876,16 @@
         <v>已截止</v>
       </c>
       <c r="B64" s="13" t="d">
-        <v>2026-04-10T00:00:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C64" s="14" t="str">
-        <v>新疆生产建设兵团相关单位·建筑钢结构智能制造技术兵团重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室</v>
       </c>
       <c r="D64" s="15" t="str">
-        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
+        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
       </c>
       <c r="E64" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>单项不超过10万元</v>
       </c>
       <c r="F64" s="16" t="str">
         <v>公告</v>
@@ -33470,16 +35896,16 @@
         <v>已截止</v>
       </c>
       <c r="B65" s="13" t="d">
-        <v>2026-04-15T00:00:00.000Z</v>
+        <v>2026-04-10T00:00:00.000Z</v>
       </c>
       <c r="C65" s="14" t="str">
-        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
+        <v>新疆生产建设兵团相关单位·建筑钢结构智能制造技术兵团重点实验室</v>
       </c>
       <c r="D65" s="15" t="str">
-        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
+        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
       </c>
       <c r="E65" s="15" t="str">
-        <v>一般5—8万元；重点20万元</v>
+        <v>不超过2万元</v>
       </c>
       <c r="F65" s="16" t="str">
         <v>公告</v>
@@ -33490,16 +35916,16 @@
         <v>已截止</v>
       </c>
       <c r="B66" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C66" s="14" t="str">
-        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
+        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
       </c>
       <c r="D66" s="15" t="str">
-        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
+        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
       </c>
       <c r="E66" s="15" t="str">
-        <v>5万元</v>
+        <v>一般5—8万元；重点20万元</v>
       </c>
       <c r="F66" s="16" t="str">
         <v>公告</v>
@@ -33513,14 +35939,13 @@
         <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C67" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
+        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
       </c>
       <c r="D67" s="15" t="str">
-        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
+        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
       </c>
       <c r="E67" s="15" t="str">
-        <v>单项原则上不超过10万元；
-100万元是本批次总额，不是单项额度。</v>
+        <v>5万元</v>
       </c>
       <c r="F67" s="16" t="str">
         <v>公告</v>
@@ -33531,16 +35956,17 @@
         <v>已截止</v>
       </c>
       <c r="B68" s="13" t="d">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C68" s="14" t="str">
-        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
       </c>
       <c r="D68" s="15" t="str">
-        <v>无人系统多源感知、导航与控制</v>
+        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
       </c>
       <c r="E68" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>单项原则上不超过10万元；
+100万元是本批次总额，不是单项额度。</v>
       </c>
       <c r="F68" s="16" t="str">
         <v>公告</v>
@@ -33551,16 +35977,16 @@
         <v>已截止</v>
       </c>
       <c r="B69" s="13" t="d">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C69" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
       </c>
       <c r="D69" s="15" t="str">
-        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
+        <v>无人系统多源感知、导航与控制</v>
       </c>
       <c r="E69" s="15" t="str">
-        <v>5万元/项；拟8项</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F69" s="16" t="str">
         <v>公告</v>
@@ -33571,16 +35997,16 @@
         <v>已截止</v>
       </c>
       <c r="B70" s="13" t="d">
-        <v>2026-04-30T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C70" s="14" t="str">
-        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D70" s="15" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
       </c>
       <c r="E70" s="15" t="str">
-        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
+        <v>5万元/项；拟8项</v>
       </c>
       <c r="F70" s="16" t="str">
         <v>公告</v>
@@ -33594,13 +36020,13 @@
         <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C71" s="14" t="str">
-        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
+        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
       </c>
       <c r="D71" s="15" t="str">
-        <v>警用智能机器人与协同任务</v>
+        <v>智能无人系统感知、规划与控制</v>
       </c>
       <c r="E71" s="15" t="str">
-        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
+        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="F71" s="16" t="str">
         <v>公告</v>
@@ -33611,16 +36037,16 @@
         <v>已截止</v>
       </c>
       <c r="B72" s="13" t="d">
-        <v>2026-05-06T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C72" s="14" t="str">
-        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
+        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
       </c>
       <c r="D72" s="15" t="str">
-        <v>具身智能（仅保留正式指南第7项方向）</v>
+        <v>警用智能机器人与协同任务</v>
       </c>
       <c r="E72" s="15" t="str">
-        <v>10—15万元</v>
+        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="F72" s="16" t="str">
         <v>公告</v>
@@ -33631,16 +36057,16 @@
         <v>已截止</v>
       </c>
       <c r="B73" s="13" t="d">
-        <v>2026-05-14T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C73" s="14" t="str">
-        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
+        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
       </c>
       <c r="D73" s="15" t="str">
-        <v>具身机器人磨削、抛光及加工技能</v>
+        <v>具身智能（仅保留正式指南第7项方向）</v>
       </c>
       <c r="E73" s="15" t="str">
-        <v>一般1—2万元、重点3—5万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F73" s="16" t="str">
         <v>公告</v>
@@ -33651,16 +36077,16 @@
         <v>已截止</v>
       </c>
       <c r="B74" s="13" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-14T00:00:00.000Z</v>
       </c>
       <c r="C74" s="14" t="str">
-        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
+        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
       </c>
       <c r="D74" s="15" t="str">
-        <v>前沿交叉方向中的手术机器人应用与验证</v>
+        <v>具身机器人磨削、抛光及加工技能</v>
       </c>
       <c r="E74" s="15" t="str">
-        <v>4万元</v>
+        <v>一般1—2万元、重点3—5万元</v>
       </c>
       <c r="F74" s="16" t="str">
         <v>公告</v>
@@ -33671,16 +36097,16 @@
         <v>已截止</v>
       </c>
       <c r="B75" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C75" s="14" t="str">
-        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
+        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
       </c>
       <c r="D75" s="15" t="str">
-        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
+        <v>前沿交叉方向中的手术机器人应用与验证</v>
       </c>
       <c r="E75" s="15" t="str">
-        <v>不超过1万元</v>
+        <v>4万元</v>
       </c>
       <c r="F75" s="16" t="str">
         <v>公告</v>
@@ -33691,16 +36117,16 @@
         <v>已截止</v>
       </c>
       <c r="B76" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C76" s="14" t="str">
-        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
+        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
       </c>
       <c r="D76" s="15" t="str">
-        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
+        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
       </c>
       <c r="E76" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>不超过1万元</v>
       </c>
       <c r="F76" s="16" t="str">
         <v>公告</v>
@@ -33711,16 +36137,16 @@
         <v>已截止</v>
       </c>
       <c r="B77" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C77" s="14" t="str">
-        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
+        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
       </c>
       <c r="D77" s="15" t="str">
-        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
+        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
       </c>
       <c r="E77" s="15" t="str">
-        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F77" s="16" t="str">
         <v>公告</v>
@@ -33734,13 +36160,13 @@
         <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C78" s="14" t="str">
-        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
+        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
       </c>
       <c r="D78" s="15" t="str">
-        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
+        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
       </c>
       <c r="E78" s="15" t="str">
-        <v>原则5万元/项；可按评审增加，上限未载</v>
+        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
       </c>
       <c r="F78" s="16" t="str">
         <v>公告</v>
@@ -33751,16 +36177,16 @@
         <v>已截止</v>
       </c>
       <c r="B79" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C79" s="14" t="str">
-        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
+        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
       </c>
       <c r="D79" s="15" t="str">
-        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
+        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
       </c>
       <c r="E79" s="15" t="str">
-        <v>5万元/项；专项拟2项</v>
+        <v>原则5万元/项；可按评审增加，上限未载</v>
       </c>
       <c r="F79" s="16" t="str">
         <v>公告</v>
@@ -33771,16 +36197,16 @@
         <v>已截止</v>
       </c>
       <c r="B80" s="13" t="d">
-        <v>2026-07-12T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C80" s="14" t="str">
-        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
+        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
       </c>
       <c r="D80" s="15" t="str">
-        <v>无人机轨迹与协同、自主采样探测装备</v>
+        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
       </c>
       <c r="E80" s="15" t="str">
-        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
+        <v>5万元/项；专项拟2项</v>
       </c>
       <c r="F80" s="16" t="str">
         <v>公告</v>
@@ -33791,16 +36217,16 @@
         <v>已截止</v>
       </c>
       <c r="B81" s="13" t="d">
-        <v>2026-07-19T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C81" s="14" t="str">
-        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
+        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
       </c>
       <c r="D81" s="15" t="str">
-        <v>具身智能传感、闭环感知与人机交互意图识别</v>
+        <v>无人机轨迹与协同、自主采样探测装备</v>
       </c>
       <c r="E81" s="15" t="str">
-        <v>10万元</v>
+        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
       </c>
       <c r="F81" s="16" t="str">
         <v>公告</v>
@@ -33811,16 +36237,16 @@
         <v>已截止</v>
       </c>
       <c r="B82" s="13" t="d">
-        <v>2026-07-25T00:00:00.000Z</v>
+        <v>2026-07-19T00:00:00.000Z</v>
       </c>
       <c r="C82" s="14" t="str">
-        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
+        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
       </c>
       <c r="D82" s="15" t="str">
-        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
+        <v>具身智能传感、闭环感知与人机交互意图识别</v>
       </c>
       <c r="E82" s="15" t="str">
-        <v>2—4万元</v>
+        <v>10万元</v>
       </c>
       <c r="F82" s="16" t="str">
         <v>公告</v>
@@ -33831,16 +36257,16 @@
         <v>已截止</v>
       </c>
       <c r="B83" s="13" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-07-25T00:00:00.000Z</v>
       </c>
       <c r="C83" s="14" t="str">
-        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
+        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
       </c>
       <c r="D83" s="15" t="str">
-        <v>智能机器人信息感知、多源融合与控制</v>
+        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
       </c>
       <c r="E83" s="15" t="str">
-        <v>约2万元</v>
+        <v>2—4万元</v>
       </c>
       <c r="F83" s="16" t="str">
         <v>公告</v>
@@ -33851,16 +36277,16 @@
         <v>已截止</v>
       </c>
       <c r="B84" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C84" s="14" t="str">
-        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
+        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
       </c>
       <c r="D84" s="15" t="str">
-        <v>机器人集成与医疗康复智能制造装备</v>
+        <v>智能机器人信息感知、多源融合与控制</v>
       </c>
       <c r="E84" s="15" t="str">
-        <v>一般2万元、重点3万元</v>
+        <v>约2万元</v>
       </c>
       <c r="F84" s="16" t="str">
         <v>公告</v>
@@ -33874,13 +36300,13 @@
         <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C85" s="14" t="str">
-        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
+        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
       </c>
       <c r="D85" s="15" t="str">
-        <v>桥梁与水下缺陷无人机器人检测</v>
+        <v>机器人集成与医疗康复智能制造装备</v>
       </c>
       <c r="E85" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>一般2万元、重点3万元</v>
       </c>
       <c r="F85" s="16" t="str">
         <v>公告</v>
@@ -33891,16 +36317,16 @@
         <v>已截止</v>
       </c>
       <c r="B86" s="13" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C86" s="14" t="str">
-        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
+        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
       </c>
       <c r="D86" s="15" t="str">
-        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
+        <v>桥梁与水下缺陷无人机器人检测</v>
       </c>
       <c r="E86" s="15" t="str">
-        <v>5万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F86" s="16" t="str">
         <v>公告</v>
@@ -33911,16 +36337,16 @@
         <v>已截止</v>
       </c>
       <c r="B87" s="13" t="d">
-        <v>2026-08-30T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C87" s="14" t="str">
-        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
+        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
       </c>
       <c r="D87" s="15" t="str">
-        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
+        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
       </c>
       <c r="E87" s="15" t="str">
-        <v>重点5万元；一般2万元；共6—8项</v>
+        <v>5万元</v>
       </c>
       <c r="F87" s="16" t="str">
         <v>公告</v>
@@ -33931,16 +36357,16 @@
         <v>已截止</v>
       </c>
       <c r="B88" s="13" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-30T00:00:00.000Z</v>
       </c>
       <c r="C88" s="14" t="str">
-        <v>四川警察学院·智能警务四川省重点实验室</v>
+        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
       </c>
       <c r="D88" s="15" t="str">
-        <v>无人机、车辆与机器狗异构协同及应急救援</v>
+        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
       </c>
       <c r="E88" s="15" t="str">
-        <v>重点15万元、一般10万元、青年5万元</v>
+        <v>重点5万元；一般2万元；共6—8项</v>
       </c>
       <c r="F88" s="16" t="str">
         <v>公告</v>
@@ -33951,17 +36377,16 @@
         <v>已截止</v>
       </c>
       <c r="B89" s="13" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C89" s="14" t="str">
-        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
+        <v>四川警察学院·智能警务四川省重点实验室</v>
       </c>
       <c r="D89" s="15" t="str">
-        <v>特种机器人多源感知、轨迹与动力学控制</v>
+        <v>无人机、车辆与机器狗异构协同及应急救援</v>
       </c>
       <c r="E89" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>重点15万元、一般10万元、青年5万元</v>
       </c>
       <c r="F89" s="16" t="str">
         <v>公告</v>
@@ -33972,16 +36397,17 @@
         <v>已截止</v>
       </c>
       <c r="B90" s="13" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C90" s="14" t="str">
-        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
       </c>
       <c r="D90" s="15" t="str">
-        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+        <v>特种机器人多源感知、轨迹与动力学控制</v>
       </c>
       <c r="E90" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F90" s="16" t="str">
         <v>公告</v>
@@ -33992,40 +36418,39 @@
         <v>已截止</v>
       </c>
       <c r="B91" s="13" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="C91" s="14" t="str">
+        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+      </c>
+      <c r="D91" s="15" t="str">
+        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+      </c>
+      <c r="E91" s="15" t="str">
+        <v>不超过2万元</v>
+      </c>
+      <c r="F91" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="92" ht="66" customHeight="1">
+      <c r="A92" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B92" s="13" t="d">
         <v>2026-09-27T00:00:00.000Z</v>
       </c>
-      <c r="C91" s="14" t="str">
+      <c r="C92" s="14" t="str">
         <v>云南大学·云南省智能系统与计算重点实验室</v>
       </c>
-      <c r="D91" s="15" t="str">
+      <c r="D92" s="15" t="str">
         <v>低空无人系统集群协同（仅保留具体无人装备方向）</v>
       </c>
-      <c r="E91" s="15" t="str">
+      <c r="E92" s="15" t="str">
         <v>重点≤8万元；
 一般≤2万元；
 定向1万元。</v>
       </c>
-      <c r="F91" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="92" ht="66" customHeight="1">
-      <c r="A92" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B92" s="13" t="d">
-        <v>2026-10-05T00:00:00.000Z</v>
-      </c>
-      <c r="C92" s="14" t="str">
-        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
-      </c>
-      <c r="D92" s="15" t="str">
-        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
-      </c>
-      <c r="E92" s="15" t="str">
-        <v>重点60—100万元；
-一般15—20万元</v>
-      </c>
       <c r="F92" s="16" t="str">
         <v>公告</v>
       </c>
@@ -34035,16 +36460,17 @@
         <v>已截止</v>
       </c>
       <c r="B93" s="13" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-05T00:00:00.000Z</v>
       </c>
       <c r="C93" s="14" t="str">
-        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
+        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
       </c>
       <c r="D93" s="15" t="str">
-        <v>机器人遥操作、双臂操作与人机协同</v>
+        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
       </c>
       <c r="E93" s="15" t="str">
-        <v>公告未公布统一金额，评审确定。</v>
+        <v>重点60—100万元；
+一般15—20万元</v>
       </c>
       <c r="F93" s="16" t="str">
         <v>公告</v>
@@ -34058,13 +36484,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C94" s="14" t="str">
-        <v>中北大学·微纳器件与系统教育部重点实验室</v>
+        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
       </c>
       <c r="D94" s="15" t="str">
-        <v>微型机器人及微纳执行器、精密定位</v>
+        <v>机器人遥操作、双臂操作与人机协同</v>
       </c>
       <c r="E94" s="15" t="str">
-        <v>2—4万元</v>
+        <v>公告未公布统一金额，评审确定。</v>
       </c>
       <c r="F94" s="16" t="str">
         <v>公告</v>
@@ -34078,13 +36504,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C95" s="14" t="str">
-        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
+        <v>中北大学·微纳器件与系统教育部重点实验室</v>
       </c>
       <c r="D95" s="15" t="str">
-        <v>机器人机械臂抓取、路径规划与自主导航</v>
+        <v>微型机器人及微纳执行器、精密定位</v>
       </c>
       <c r="E95" s="15" t="str">
-        <v>一般2万元；重点4万元（以评审为准）</v>
+        <v>2—4万元</v>
       </c>
       <c r="F95" s="16" t="str">
         <v>公告</v>
@@ -34098,13 +36524,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C96" s="14" t="str">
-        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
+        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
       </c>
       <c r="D96" s="15" t="str">
-        <v>无人平台智能探测与多源感知</v>
+        <v>机器人机械臂抓取、路径规划与自主导航</v>
       </c>
       <c r="E96" s="15" t="str">
-        <v>2—4万元/项，拟5—8项</v>
+        <v>一般2万元；重点4万元（以评审为准）</v>
       </c>
       <c r="F96" s="16" t="str">
         <v>公告</v>
@@ -34118,36 +36544,36 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C97" s="14" t="str">
-        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
       </c>
       <c r="D97" s="15" t="str">
-        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+        <v>无人平台智能探测与多源感知</v>
       </c>
       <c r="E97" s="15" t="str">
-        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+        <v>2—4万元/项，拟5—8项</v>
       </c>
       <c r="F97" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="98" ht="96" customHeight="1">
-      <c r="A98" t="str" s="18">
+    <row r="98" ht="66" customHeight="1">
+      <c r="A98" s="18" t="str">
         <v>已截止</v>
       </c>
-      <c r="B98" t="n" s="13">
-        <v>46295</v>
-      </c>
-      <c r="C98" t="str" s="14">
-        <v>上海交通大学·海洋工程全国重点实验室</v>
-      </c>
-      <c r="D98" t="str" s="15">
-        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
-      </c>
-      <c r="E98" t="str" s="15">
-        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
-      </c>
-      <c r="F98" t="str" s="16">
-        <v>官方公告</v>
+      <c r="B98" s="13" t="d">
+        <v>2026-10-08T00:00:00.000Z</v>
+      </c>
+      <c r="C98" s="14" t="str">
+        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+      </c>
+      <c r="D98" s="15" t="str">
+        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+      </c>
+      <c r="E98" s="15" t="str">
+        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+      </c>
+      <c r="F98" s="16" t="str">
+        <v>公告</v>
       </c>
     </row>
     <row r="99" ht="96" customHeight="1">
@@ -34155,16 +36581,16 @@
         <v>已截止</v>
       </c>
       <c r="B99" t="n" s="13">
-        <v>45503</v>
+        <v>46295</v>
       </c>
       <c r="C99" t="str" s="14">
-        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
+        <v>上海交通大学·海洋工程全国重点实验室</v>
       </c>
       <c r="D99" t="str" s="15">
-        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
+        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
       </c>
       <c r="E99" t="str" s="15">
-        <v>3万元/项；计划10项。</v>
+        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
       </c>
       <c r="F99" t="str" s="16">
         <v>官方公告</v>
@@ -34175,16 +36601,16 @@
         <v>已截止</v>
       </c>
       <c r="B100" t="n" s="13">
-        <v>46006</v>
+        <v>45503</v>
       </c>
       <c r="C100" t="str" s="14">
-        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
+        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
       </c>
       <c r="D100" t="str" s="15">
-        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
+        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
       </c>
       <c r="E100" t="str" s="15">
-        <v>正文未公开具体资助金额。</v>
+        <v>3万元/项；计划10项。</v>
       </c>
       <c r="F100" t="str" s="16">
         <v>官方公告</v>
@@ -34195,16 +36621,16 @@
         <v>已截止</v>
       </c>
       <c r="B101" t="n" s="13">
-        <v>46193</v>
+        <v>46006</v>
       </c>
       <c r="C101" t="str" s="14">
-        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
+        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
       <c r="D101" t="str" s="15">
-        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
+        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
       </c>
       <c r="E101" t="str" s="15">
-        <v>一般项目≤5万元/项；计划12项。</v>
+        <v>正文未公开具体资助金额。</v>
       </c>
       <c r="F101" t="str" s="16">
         <v>官方公告</v>
@@ -34215,16 +36641,16 @@
         <v>已截止</v>
       </c>
       <c r="B102" t="n" s="13">
-        <v>44434</v>
+        <v>46193</v>
       </c>
       <c r="C102" t="str" s="14">
-        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
       </c>
       <c r="D102" t="str" s="15">
-        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
       </c>
       <c r="E102" t="str" s="15">
-        <v>重点2万元/项；一般1万元/项。</v>
+        <v>一般项目≤5万元/项；计划12项。</v>
       </c>
       <c r="F102" t="str" s="16">
         <v>官方公告</v>
@@ -34235,16 +36661,16 @@
         <v>已截止</v>
       </c>
       <c r="B103" t="n" s="13">
-        <v>45163</v>
+        <v>44434</v>
       </c>
       <c r="C103" t="str" s="14">
-        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
       </c>
       <c r="D103" t="str" s="15">
-        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
       </c>
       <c r="E103" t="str" s="15">
-        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+        <v>重点2万元/项；一般1万元/项。</v>
       </c>
       <c r="F103" t="str" s="16">
         <v>官方公告</v>
@@ -34252,21 +36678,41 @@
     </row>
     <row r="104" ht="96" customHeight="1">
       <c r="A104" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B104" t="n" s="13">
+        <v>45163</v>
+      </c>
+      <c r="C104" t="str" s="14">
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+      </c>
+      <c r="D104" t="str" s="15">
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+      </c>
+      <c r="E104" t="str" s="15">
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+      </c>
+      <c r="F104" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="105" ht="96" customHeight="1">
+      <c r="A105" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B104" t="n" s="13">
+      <c r="B105" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C104" t="str" s="14">
+      <c r="C105" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D104" t="str" s="15">
+      <c r="D105" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E104" t="str" s="15">
+      <c r="E105" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F104" t="str" s="16">
+      <c r="F105" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -34282,8 +36728,8 @@
     <hyperlink ref="F5" ns1:id="Rff2d595907084ed9"/>
     <hyperlink ref="C6" location="'02项目完整详情'!A61"/>
     <hyperlink ref="F6" ns1:id="R840dfc7ac2ef4322"/>
-    <hyperlink ref="C36" location="'02项目完整详情'!A113"/>
-    <hyperlink ref="F36" ns1:id="Re902984ea1114a1f"/>
+    <hyperlink ref="C37" location="'02项目完整详情'!A113"/>
+    <hyperlink ref="F37" ns1:id="Re902984ea1114a1f"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A62"/>
     <hyperlink ref="F7" ns1:id="Ra6ff56d69fd14f0d"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A63"/>
@@ -34294,190 +36740,192 @@
     <hyperlink ref="F10" ns1:id="Ra45cae74f44f4c7f"/>
     <hyperlink ref="C12" location="'02项目完整详情'!A65"/>
     <hyperlink ref="F12" ns1:id="Rb60ba16ed31b49e2"/>
-    <hyperlink ref="C13" location="'02项目完整详情'!A140"/>
-    <hyperlink ref="F13" ns1:id="R54631d6f63ff4a84"/>
-    <hyperlink ref="C14" location="'02项目完整详情'!A82"/>
-    <hyperlink ref="F14" ns1:id="R5d6c0e16ca9148f1"/>
-    <hyperlink ref="C15" location="'02项目完整详情'!A141"/>
-    <hyperlink ref="F15" ns1:id="R29345038c30a4733"/>
-    <hyperlink ref="C37" location="'02项目完整详情'!A85"/>
-    <hyperlink ref="F37" ns1:id="R486c032b769d4524"/>
-    <hyperlink ref="C16" location="'02项目完整详情'!A99"/>
-    <hyperlink ref="F16" ns1:id="R19ee0f6cf8d14ed3"/>
-    <hyperlink ref="C17" location="'02项目完整详情'!A143"/>
-    <hyperlink ref="F17" ns1:id="R66d112d84a8644fb"/>
-    <hyperlink ref="C18" location="'02项目完整详情'!A122"/>
-    <hyperlink ref="F18" ns1:id="R83b69720fcfc4e60"/>
-    <hyperlink ref="C19" location="'02项目完整详情'!A127"/>
-    <hyperlink ref="F19" ns1:id="Ra979348b05084966"/>
-    <hyperlink ref="C20" location="'02项目完整详情'!A66"/>
-    <hyperlink ref="F20" ns1:id="R4dc201fc29cb4ab4"/>
-    <hyperlink ref="C38" location="'02项目完整详情'!A139"/>
-    <hyperlink ref="F38" ns1:id="Rf4dc98016cfb49fd"/>
-    <hyperlink ref="C21" location="'02项目完整详情'!A151"/>
-    <hyperlink ref="F21" ns1:id="R3d89872d06fd4b60"/>
-    <hyperlink ref="C22" location="'02项目完整详情'!A67"/>
-    <hyperlink ref="F22" ns1:id="R1e9b7d2bc63d4258"/>
-    <hyperlink ref="C39" location="'02项目完整详情'!A68"/>
-    <hyperlink ref="F39" ns1:id="R5d0261ffe45c4155"/>
-    <hyperlink ref="C23" location="'02项目完整详情'!A69"/>
-    <hyperlink ref="F23" ns1:id="Reeb11b878b934f2d"/>
-    <hyperlink ref="C24" location="'02项目完整详情'!A70"/>
-    <hyperlink ref="F24" ns1:id="R5b06defce5864a96"/>
-    <hyperlink ref="C25" location="'02项目完整详情'!A71"/>
-    <hyperlink ref="F25" ns1:id="Ra48afdb9842a4366"/>
-    <hyperlink ref="C40" location="'02项目完整详情'!A72"/>
-    <hyperlink ref="F40" ns1:id="Rb3b4681efcdd44d4"/>
-    <hyperlink ref="C41" location="'02项目完整详情'!A73"/>
-    <hyperlink ref="F41" ns1:id="R4f0b800598574b86"/>
-    <hyperlink ref="C42" location="'02项目完整详情'!A74"/>
-    <hyperlink ref="F42" ns1:id="R56697ca79cd54a14"/>
-    <hyperlink ref="C30" location="'02项目完整详情'!A75"/>
-    <hyperlink ref="F30" ns1:id="R0814a7680dde4f9a"/>
-    <hyperlink ref="C31" location="'02项目完整详情'!A76"/>
-    <hyperlink ref="F31" ns1:id="R3f222e6bf9fa46ec"/>
-    <hyperlink ref="C32" location="'02项目完整详情'!A77"/>
-    <hyperlink ref="F32" ns1:id="Rc66c2cf37bbc404d"/>
-    <hyperlink ref="C33" location="'02项目完整详情'!A78"/>
-    <hyperlink ref="F33" ns1:id="R90e03710dfe04e74"/>
-    <hyperlink ref="C34" location="'02项目完整详情'!A79"/>
-    <hyperlink ref="F34" ns1:id="R80f5129c1ee24096"/>
-    <hyperlink ref="C35" location="'02项目完整详情'!A80"/>
-    <hyperlink ref="F35" ns1:id="R6360db00742b45ec"/>
-    <hyperlink ref="C43" location="'02项目完整详情'!A81"/>
-    <hyperlink ref="F43" ns1:id="Rc4146f6376594d01"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A156"/>
-    <hyperlink ref="F44" ns1:id="R97ba6e4965084c76"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A155"/>
-    <hyperlink ref="F45" ns1:id="Rcbdc080795344925"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A83"/>
-    <hyperlink ref="F46" ns1:id="R9e6afd1b359743bb"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A154"/>
-    <hyperlink ref="F47" ns1:id="Rb320e0a5ad524836"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A86"/>
-    <hyperlink ref="F48" ns1:id="R42a660aaeb1d4c95"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A87"/>
-    <hyperlink ref="F49" ns1:id="R88784a2520864683"/>
-    <hyperlink ref="C26" location="'02项目完整详情'!A88"/>
-    <hyperlink ref="F26" ns1:id="Rcb8b33dae69a4731"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A89"/>
-    <hyperlink ref="F50" ns1:id="Rd5ea9c8442ca46ac"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A90"/>
-    <hyperlink ref="F51" ns1:id="R7734727212364cb2"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A91"/>
-    <hyperlink ref="F52" ns1:id="R78b8c8c0ca954ecb"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A92"/>
-    <hyperlink ref="F53" ns1:id="Rfdf5f46608d44776"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A93"/>
-    <hyperlink ref="F54" ns1:id="R82f06426c3d54976"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A94"/>
-    <hyperlink ref="F55" ns1:id="R3cae8e186c48414b"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A95"/>
-    <hyperlink ref="F56" ns1:id="Ra7f1aef2362a4a4a"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A96"/>
-    <hyperlink ref="F57" ns1:id="R8befa90ef3fc47c2"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A97"/>
-    <hyperlink ref="F58" ns1:id="Re7fdcbfdd1084572"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A98"/>
-    <hyperlink ref="F59" ns1:id="R65ca925ee60b42a7"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A100"/>
-    <hyperlink ref="F60" ns1:id="Reb76655df7374bc5"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A166"/>
-    <hyperlink ref="F61" ns1:id="R055caeb6a90642b5"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A102"/>
-    <hyperlink ref="F62" ns1:id="Rfff5ca38a0554ba3"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A103"/>
-    <hyperlink ref="F63" ns1:id="R0888add655cd4fba"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A104"/>
-    <hyperlink ref="F64" ns1:id="Rd9709f11bc9f4e83"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A163"/>
-    <hyperlink ref="F65" ns1:id="R20412a2edb1c448a"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A105"/>
-    <hyperlink ref="F66" ns1:id="R61772b79401a4268"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A106"/>
-    <hyperlink ref="F67" ns1:id="R987b8e6f52a74110"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A107"/>
-    <hyperlink ref="F68" ns1:id="R0c4396d550f2475f"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A162"/>
-    <hyperlink ref="F69" ns1:id="R4f11bd52ab71481c"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A108"/>
-    <hyperlink ref="F70" ns1:id="R4db82e37256244c2"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A109"/>
-    <hyperlink ref="F71" ns1:id="R4031c47a301e406d"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A110"/>
-    <hyperlink ref="F72" ns1:id="Raa160d321af04db8"/>
-    <hyperlink ref="C27" location="'02项目完整详情'!A111"/>
-    <hyperlink ref="F27" ns1:id="R769c1e9ff31b4410"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A112"/>
-    <hyperlink ref="F73" ns1:id="R4cdea66d1ef84e88"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A114"/>
-    <hyperlink ref="F74" ns1:id="Rfe9d4bacb83a4b3a"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A115"/>
-    <hyperlink ref="F75" ns1:id="Rdb52bb1fc14c4902"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A116"/>
-    <hyperlink ref="F76" ns1:id="Raea0cb8061aa4114"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A153"/>
-    <hyperlink ref="F77" ns1:id="Re209c4141aad4cc2"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A152"/>
-    <hyperlink ref="F78" ns1:id="R929ae2605c414e9f"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A165"/>
-    <hyperlink ref="F79" ns1:id="R1abe4cdaf9e34bae"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A117"/>
-    <hyperlink ref="F80" ns1:id="R0a10fce99c274f93"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A118"/>
-    <hyperlink ref="F81" ns1:id="R938383f864354c81"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A119"/>
-    <hyperlink ref="F82" ns1:id="Rf5654ce2b68c4be9"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A121"/>
-    <hyperlink ref="F83" ns1:id="Rcb7b406cd4eb4fbf"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A123"/>
-    <hyperlink ref="F84" ns1:id="R5815a7bd80814259"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A124"/>
-    <hyperlink ref="F85" ns1:id="R0c410df45d8a4e3d"/>
-    <hyperlink ref="C28" location="'02项目完整详情'!A125"/>
-    <hyperlink ref="F28" ns1:id="R431b21fd445f4abe"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A126"/>
-    <hyperlink ref="F86" ns1:id="R567091a279bf498d"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A164"/>
-    <hyperlink ref="F87" ns1:id="Re392bfd9b5274c72"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A128"/>
-    <hyperlink ref="F88" ns1:id="Re6cada6d8cc14329"/>
-    <hyperlink ref="C89" location="'02项目完整详情'!A129"/>
-    <hyperlink ref="F89" ns1:id="R8fc1cda8f3b6430e"/>
-    <hyperlink ref="C90" location="'02项目完整详情'!A130"/>
-    <hyperlink ref="F90" ns1:id="R27a55a96c3f24c5f"/>
-    <hyperlink ref="C91" location="'02项目完整详情'!A131"/>
-    <hyperlink ref="F91" ns1:id="R5e47895d5a614c2b"/>
-    <hyperlink ref="C29" location="'02项目完整详情'!A132"/>
-    <hyperlink ref="F29" ns1:id="R3b43825c6bac4d00"/>
-    <hyperlink ref="C92" location="'02项目完整详情'!A133"/>
-    <hyperlink ref="F92" ns1:id="R93e0d1bfa9de4923"/>
-    <hyperlink ref="C93" location="'02项目完整详情'!A40"/>
-    <hyperlink ref="F93" ns1:id="R8485fac45d264a2f"/>
-    <hyperlink ref="C94" location="'02项目完整详情'!A41"/>
-    <hyperlink ref="F94" ns1:id="R1c0f567749234b9c"/>
-    <hyperlink ref="C95" location="'02项目完整详情'!A42"/>
-    <hyperlink ref="F95" ns1:id="Rbf215fc93e064e7e"/>
-    <hyperlink ref="C96" location="'02项目完整详情'!A43"/>
-    <hyperlink ref="F96" ns1:id="R53db146b46f44f15"/>
-    <hyperlink ref="C97" location="'02项目完整详情'!A44"/>
-    <hyperlink ref="F97" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F104" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C104" location="'02项目完整详情'!A148"/>
-    <hyperlink ref="C98" location="'02项目完整详情'!A167" display="项目完整详情"/>
-    <hyperlink ref="F98" ns1:id="rIdSystematic98"/>
-    <hyperlink ref="C99" location="'02项目完整详情'!A168" display="项目完整详情"/>
-    <hyperlink ref="F99" ns1:id="rIdSystematic99"/>
-    <hyperlink ref="C100" location="'02项目完整详情'!A175" display="项目完整详情"/>
-    <hyperlink ref="F100" ns1:id="rIdSystematic100"/>
-    <hyperlink ref="C101" location="'02项目完整详情'!A176" display="项目完整详情"/>
-    <hyperlink ref="F101" ns1:id="rIdSystematic101"/>
+    <hyperlink ref="C14" location="'02项目完整详情'!A140"/>
+    <hyperlink ref="F14" ns1:id="R54631d6f63ff4a84"/>
+    <hyperlink ref="C15" location="'02项目完整详情'!A82"/>
+    <hyperlink ref="F15" ns1:id="R5d6c0e16ca9148f1"/>
+    <hyperlink ref="C16" location="'02项目完整详情'!A141"/>
+    <hyperlink ref="F16" ns1:id="R29345038c30a4733"/>
+    <hyperlink ref="C38" location="'02项目完整详情'!A85"/>
+    <hyperlink ref="F38" ns1:id="R486c032b769d4524"/>
+    <hyperlink ref="C17" location="'02项目完整详情'!A99"/>
+    <hyperlink ref="F17" ns1:id="R19ee0f6cf8d14ed3"/>
+    <hyperlink ref="C18" location="'02项目完整详情'!A143"/>
+    <hyperlink ref="F18" ns1:id="R66d112d84a8644fb"/>
+    <hyperlink ref="C19" location="'02项目完整详情'!A122"/>
+    <hyperlink ref="F19" ns1:id="R83b69720fcfc4e60"/>
+    <hyperlink ref="C20" location="'02项目完整详情'!A127"/>
+    <hyperlink ref="F20" ns1:id="Ra979348b05084966"/>
+    <hyperlink ref="C21" location="'02项目完整详情'!A66"/>
+    <hyperlink ref="F21" ns1:id="R4dc201fc29cb4ab4"/>
+    <hyperlink ref="C39" location="'02项目完整详情'!A139"/>
+    <hyperlink ref="F39" ns1:id="Rf4dc98016cfb49fd"/>
+    <hyperlink ref="C22" location="'02项目完整详情'!A151"/>
+    <hyperlink ref="F22" ns1:id="R3d89872d06fd4b60"/>
+    <hyperlink ref="C23" location="'02项目完整详情'!A67"/>
+    <hyperlink ref="F23" ns1:id="R1e9b7d2bc63d4258"/>
+    <hyperlink ref="C40" location="'02项目完整详情'!A68"/>
+    <hyperlink ref="F40" ns1:id="R5d0261ffe45c4155"/>
+    <hyperlink ref="C24" location="'02项目完整详情'!A69"/>
+    <hyperlink ref="F24" ns1:id="Reeb11b878b934f2d"/>
+    <hyperlink ref="C25" location="'02项目完整详情'!A70"/>
+    <hyperlink ref="F25" ns1:id="R5b06defce5864a96"/>
+    <hyperlink ref="C26" location="'02项目完整详情'!A71"/>
+    <hyperlink ref="F26" ns1:id="Ra48afdb9842a4366"/>
+    <hyperlink ref="C41" location="'02项目完整详情'!A72"/>
+    <hyperlink ref="F41" ns1:id="Rb3b4681efcdd44d4"/>
+    <hyperlink ref="C42" location="'02项目完整详情'!A73"/>
+    <hyperlink ref="F42" ns1:id="R4f0b800598574b86"/>
+    <hyperlink ref="C43" location="'02项目完整详情'!A74"/>
+    <hyperlink ref="F43" ns1:id="R56697ca79cd54a14"/>
+    <hyperlink ref="C31" location="'02项目完整详情'!A75"/>
+    <hyperlink ref="F31" ns1:id="R0814a7680dde4f9a"/>
+    <hyperlink ref="C32" location="'02项目完整详情'!A76"/>
+    <hyperlink ref="F32" ns1:id="R3f222e6bf9fa46ec"/>
+    <hyperlink ref="C33" location="'02项目完整详情'!A77"/>
+    <hyperlink ref="F33" ns1:id="Rc66c2cf37bbc404d"/>
+    <hyperlink ref="C34" location="'02项目完整详情'!A78"/>
+    <hyperlink ref="F34" ns1:id="R90e03710dfe04e74"/>
+    <hyperlink ref="C35" location="'02项目完整详情'!A79"/>
+    <hyperlink ref="F35" ns1:id="R80f5129c1ee24096"/>
+    <hyperlink ref="C36" location="'02项目完整详情'!A80"/>
+    <hyperlink ref="F36" ns1:id="R6360db00742b45ec"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A81"/>
+    <hyperlink ref="F44" ns1:id="Rc4146f6376594d01"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A156"/>
+    <hyperlink ref="F45" ns1:id="R97ba6e4965084c76"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A155"/>
+    <hyperlink ref="F46" ns1:id="Rcbdc080795344925"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A83"/>
+    <hyperlink ref="F47" ns1:id="R9e6afd1b359743bb"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A154"/>
+    <hyperlink ref="F48" ns1:id="Rb320e0a5ad524836"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A86"/>
+    <hyperlink ref="F49" ns1:id="R42a660aaeb1d4c95"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A87"/>
+    <hyperlink ref="F50" ns1:id="R88784a2520864683"/>
+    <hyperlink ref="C27" location="'02项目完整详情'!A88"/>
+    <hyperlink ref="F27" ns1:id="Rcb8b33dae69a4731"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A89"/>
+    <hyperlink ref="F51" ns1:id="Rd5ea9c8442ca46ac"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A90"/>
+    <hyperlink ref="F52" ns1:id="R7734727212364cb2"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A91"/>
+    <hyperlink ref="F53" ns1:id="R78b8c8c0ca954ecb"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A92"/>
+    <hyperlink ref="F54" ns1:id="Rfdf5f46608d44776"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A93"/>
+    <hyperlink ref="F55" ns1:id="R82f06426c3d54976"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A94"/>
+    <hyperlink ref="F56" ns1:id="R3cae8e186c48414b"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A95"/>
+    <hyperlink ref="F57" ns1:id="Ra7f1aef2362a4a4a"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A96"/>
+    <hyperlink ref="F58" ns1:id="R8befa90ef3fc47c2"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A97"/>
+    <hyperlink ref="F59" ns1:id="Re7fdcbfdd1084572"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A98"/>
+    <hyperlink ref="F60" ns1:id="R65ca925ee60b42a7"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A100"/>
+    <hyperlink ref="F61" ns1:id="Reb76655df7374bc5"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A166"/>
+    <hyperlink ref="F62" ns1:id="R055caeb6a90642b5"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A102"/>
+    <hyperlink ref="F63" ns1:id="Rfff5ca38a0554ba3"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A103"/>
+    <hyperlink ref="F64" ns1:id="R0888add655cd4fba"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A104"/>
+    <hyperlink ref="F65" ns1:id="Rd9709f11bc9f4e83"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A163"/>
+    <hyperlink ref="F66" ns1:id="R20412a2edb1c448a"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A105"/>
+    <hyperlink ref="F67" ns1:id="R61772b79401a4268"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A106"/>
+    <hyperlink ref="F68" ns1:id="R987b8e6f52a74110"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A107"/>
+    <hyperlink ref="F69" ns1:id="R0c4396d550f2475f"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A162"/>
+    <hyperlink ref="F70" ns1:id="R4f11bd52ab71481c"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A108"/>
+    <hyperlink ref="F71" ns1:id="R4db82e37256244c2"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A109"/>
+    <hyperlink ref="F72" ns1:id="R4031c47a301e406d"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A110"/>
+    <hyperlink ref="F73" ns1:id="Raa160d321af04db8"/>
+    <hyperlink ref="C28" location="'02项目完整详情'!A111"/>
+    <hyperlink ref="F28" ns1:id="R769c1e9ff31b4410"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A112"/>
+    <hyperlink ref="F74" ns1:id="R4cdea66d1ef84e88"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A114"/>
+    <hyperlink ref="F75" ns1:id="Rfe9d4bacb83a4b3a"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A115"/>
+    <hyperlink ref="F76" ns1:id="Rdb52bb1fc14c4902"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A116"/>
+    <hyperlink ref="F77" ns1:id="Raea0cb8061aa4114"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A153"/>
+    <hyperlink ref="F78" ns1:id="Re209c4141aad4cc2"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A152"/>
+    <hyperlink ref="F79" ns1:id="R929ae2605c414e9f"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A165"/>
+    <hyperlink ref="F80" ns1:id="R1abe4cdaf9e34bae"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A117"/>
+    <hyperlink ref="F81" ns1:id="R0a10fce99c274f93"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A118"/>
+    <hyperlink ref="F82" ns1:id="R938383f864354c81"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A119"/>
+    <hyperlink ref="F83" ns1:id="Rf5654ce2b68c4be9"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A121"/>
+    <hyperlink ref="F84" ns1:id="Rcb7b406cd4eb4fbf"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A123"/>
+    <hyperlink ref="F85" ns1:id="R5815a7bd80814259"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A124"/>
+    <hyperlink ref="F86" ns1:id="R0c410df45d8a4e3d"/>
+    <hyperlink ref="C29" location="'02项目完整详情'!A125"/>
+    <hyperlink ref="F29" ns1:id="R431b21fd445f4abe"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A126"/>
+    <hyperlink ref="F87" ns1:id="R567091a279bf498d"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A164"/>
+    <hyperlink ref="F88" ns1:id="Re392bfd9b5274c72"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A128"/>
+    <hyperlink ref="F89" ns1:id="Re6cada6d8cc14329"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A129"/>
+    <hyperlink ref="F90" ns1:id="R8fc1cda8f3b6430e"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A130"/>
+    <hyperlink ref="F91" ns1:id="R27a55a96c3f24c5f"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A131"/>
+    <hyperlink ref="F92" ns1:id="R5e47895d5a614c2b"/>
+    <hyperlink ref="C30" location="'02项目完整详情'!A132"/>
+    <hyperlink ref="F30" ns1:id="R3b43825c6bac4d00"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A133"/>
+    <hyperlink ref="F93" ns1:id="R93e0d1bfa9de4923"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A40"/>
+    <hyperlink ref="F94" ns1:id="R8485fac45d264a2f"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A41"/>
+    <hyperlink ref="F95" ns1:id="R1c0f567749234b9c"/>
+    <hyperlink ref="C96" location="'02项目完整详情'!A42"/>
+    <hyperlink ref="F96" ns1:id="Rbf215fc93e064e7e"/>
+    <hyperlink ref="C97" location="'02项目完整详情'!A43"/>
+    <hyperlink ref="F97" ns1:id="R53db146b46f44f15"/>
+    <hyperlink ref="C98" location="'02项目完整详情'!A44"/>
+    <hyperlink ref="F98" ns1:id="R188b27dcb5574282"/>
+    <hyperlink ref="F105" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="C99" location="'02项目完整详情'!A167" display="项目完整详情"/>
+    <hyperlink ref="F99" ns1:id="rIdSystematic98"/>
+    <hyperlink ref="C100" location="'02项目完整详情'!A168" display="项目完整详情"/>
+    <hyperlink ref="F100" ns1:id="rIdSystematic99"/>
+    <hyperlink ref="C101" location="'02项目完整详情'!A175" display="项目完整详情"/>
+    <hyperlink ref="F101" ns1:id="rIdSystematic100"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A176" display="项目完整详情"/>
+    <hyperlink ref="F102" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A182" display="项目完整详情"/>
-    <hyperlink ref="F102" ns1:id="rIdResume103"/>
-    <hyperlink ref="C103" location="'02项目完整详情'!A184" display="项目完整详情"/>
-    <hyperlink ref="F103" ns1:id="rIdResume104"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdResume103"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F104" ns1:id="rIdResume104"/>
+    <hyperlink ref="C13" location="'02项目完整详情'!A185" display="项目完整详情"/>
+    <hyperlink ref="F13" ns1:id="rIdResume105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -16921,6 +16921,171 @@
       </c>
       <c r="AA185" t="str" s="3"/>
     </row>
+    <row r="186" ht="79.5" customHeight="1">
+      <c r="A186" t="str" s="3">
+        <v>N037</v>
+      </c>
+      <c r="B186" t="str" s="3">
+        <v>2025—2026共享批次正式官方公告全文已核；管理经费页面2021版已核，当前适用待确认</v>
+      </c>
+      <c r="C186" t="str" s="3">
+        <v>长春理工大学</v>
+      </c>
+      <c r="D186" t="str" s="3">
+        <v>跨尺度微纳制造教育部重点实验室</v>
+      </c>
+      <c r="E186" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F186" t="str" s="3">
+        <v>2025—2026（共享轮次）</v>
+      </c>
+      <c r="G186" t="n" s="6">
+        <v>45991</v>
+      </c>
+      <c r="H186" t="str" s="3">
+        <v>17:00（公告未另列时区）</v>
+      </c>
+      <c r="I186" t="str" s="3">
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+      </c>
+      <c r="J186" t="str" s="3">
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+      </c>
+      <c r="K186" t="str" s="3">
+        <v>非长春理工的国内外高校/研究院研究人员；原则上国外著名高校、国内985/211大学或中科院研究所。博士或副高；否则两位副高专家推荐。主持+参与共≤2项；本人有本室未结题项目不可申报；须有团队成员。</v>
+      </c>
+      <c r="L186" t="str" s="3">
+        <v>必须有本实验室固定人员参加并作校内联系人，论文列该人为通讯作者之一；访问天数未载。</v>
+      </c>
+      <c r="M186" t="str" s="3">
+        <v>2025—2026公告未载拨付/外拨。官网2021经费管理：材料、小设备、仪器租用加工测试水电气等；客座交通住宿津贴≤开放经费30%，该部分可拨至负责人所在单位财务管理；其他开支由实验室审核校财务报销；结余/购置仪器材料留室。2021条款当前适用及拨付比例待确认，不把30%当整个项目可外拨比例。</v>
+      </c>
+      <c r="N186" t="str" s="3">
+        <v>一般不超过2年；申请起止填2025-12-01至2027-11-30，实际以下达为准。</v>
+      </c>
+      <c r="O186" t="str" s="3">
+        <v>一般：SCI中科院大类二区及以上1篇或SCI2篇；重点：大类一区1篇或大类二区及以上2篇或SCI3篇。实验室为完成单位之一、基金编号标注；固定联系人须通讯作者之一；实验室与负责人单位共同发表；成果报告归档。</v>
+      </c>
+      <c r="P186" t="str" s="3">
+        <v>年度公告明确实验室与负责人所在单位共同所有。</v>
+      </c>
+      <c r="Q186" t="str" s="3">
+        <v>申请书+个人简历合成1个PDF，附详细联系方式，截止前发送yangshen@cust.edu.cn；收到回复代表提交成功。附件2份DOCX首次超时。</v>
+      </c>
+      <c r="R186" t="str" s="3">
+        <v>本人博士满足学历门槛；现职单位是否满足公告原则上的985/211机构限制，需主办方明确；限项/固定合作者待本人确认。</v>
+      </c>
+      <c r="S186" t="str" s="3">
+        <v>已截止。须取得申请书/简历、开放合作机制及当年管理办法；确认非985/211依托单位是否受理、2021经费条款适用性、外拨范围/流程；2027新公告未取得。</v>
+      </c>
+      <c r="T186" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/kfyjl/kfkt/deeaacf5c4cd4a4c99d931f74f0fd8d9.htm</v>
+      </c>
+      <c r="U186" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/docs//2025-11/3b260bcd606e40549bd7b11fd8ff3d70.docx
+https://cmnm.cust.edu.cn/docs//2025-11/f971c8633e45462a8fb0cd60cd81c28a.docx
+https://cmnm.cust.edu.cn/yxgl/gzzd/79712.htm
+https://cmnm.cust.edu.cn/yxgl/gzzd/76199.htm</v>
+      </c>
+      <c r="V186" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W186" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X186" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y186" t="str" s="3">
+        <v>吉林·长春</v>
+      </c>
+      <c r="Z186" t="str" s="3">
+        <v>杨珅；yangshen@cust.edu.cn；0431-85582815；15764395100</v>
+      </c>
+      <c r="AA186" t="str" s="3"/>
+    </row>
+    <row r="187" ht="79.5" customHeight="1">
+      <c r="A187" t="str" s="3">
+        <v>N038</v>
+      </c>
+      <c r="B187" t="str" s="3">
+        <v>2026正式指南PDF已取得前5页文字，末页首次渲染超时；2026-04-14官方立项通知已核；非当前受理</v>
+      </c>
+      <c r="C187" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="D187" t="str" s="3">
+        <v>新能源系统高端装备和智慧运行教育部工程研究中心</v>
+      </c>
+      <c r="E187" t="str" s="3">
+        <v>历史批次·截止条款待核</v>
+      </c>
+      <c r="F187" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G187" t="str" s="6">
+        <v>具体截止日未取得（2026-04-14已发布立项通知）</v>
+      </c>
+      <c r="H187" t="str" s="3">
+        <v>资料未取得</v>
+      </c>
+      <c r="I187" t="str" s="3">
+        <v>年度方向四2明确新能源场站先进机器人、自动巡检、故障排查及维修、无人机巡检、自动化清洁维护、机器人与AI融合实现自主运维；其他能源调度/材料任务不扩充。</v>
+      </c>
+      <c r="J187" t="str" s="3">
+        <v>5万元/项；拟资助3项。</v>
+      </c>
+      <c r="K187" t="str" s="3">
+        <v>国内外符合中心方向、有研究基础的人员；博士或副高级以上职称；无高级职称青年需两名高级职称同行推荐。在校学生、研究生及博士后申请通常不受理。</v>
+      </c>
+      <c r="L187" t="str" s="3">
+        <v>必须同中心科研团队合作，明确合作计划；申报团队必须有中心科研人员和在读研究生；结题需青海大学学术报告1场。</v>
+      </c>
+      <c r="M187" t="str" s="3">
+        <v>明确不外拨，青海大学在岗教师协助报账；所有经费11月30日前支出完。允许论文版面、会议、技术服务、材料及相关差旅费；拨付比例未载。</v>
+      </c>
+      <c r="N187" t="str" s="3">
+        <v>资助周期1年；批准后1个月内签任务书；11月30支出期限与科研周期须确认。</v>
+      </c>
+      <c r="O187" t="str" s="3">
+        <v>论文1篇（北大核心/EI/SCI，青海大学第一单位）；青海大学学术报告1场；结题报告1份。</v>
+      </c>
+      <c r="P187" t="str" s="3">
+        <v>已取得前5页未载；末页/管理办法未取得。</v>
+      </c>
+      <c r="Q187" t="str" s="3">
+        <v>申请书采用国自然青年模板；电子邮件+双面纸质2份；收件邮箱、截止日期及末页具体材料要求未取得。立项后任务书1个月内确定。</v>
+      </c>
+      <c r="R187" t="str" s="3">
+        <v>本人博士已知；强制合作团队成员及限项须确认，未写可申请。</v>
+      </c>
+      <c r="S187" t="str" s="3">
+        <v>2026立项结果已发布，非当前申报项目；待补PDF第6页截止/联系人/知识产权等及管理办法，核研究期与11月30报账时间关系；2027公告未取得。</v>
+      </c>
+      <c r="T187" t="str" s="3">
+        <v>https://seee.qhu.edu.cn/docs/2026-03/030d356bfc944682adbfd3d82afac1e0.pdf</v>
+      </c>
+      <c r="U187" t="str" s="3">
+        <v>立项通知：https://seee.qhu.edu.cn/tzgg/5f84aa3029584f37ada867a1af4cae66.htm；正文图片名单未提取。</v>
+      </c>
+      <c r="V187" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W187" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X187" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y187" t="str" s="3">
+        <v>青海·西宁</v>
+      </c>
+      <c r="Z187" t="str" s="3">
+        <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
+      </c>
+      <c r="AA187" t="str" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -17326,6 +17491,8 @@
     <hyperlink ref="T183" ns1:id="rIdResume405"/>
     <hyperlink ref="T184" ns1:id="rIdResume406"/>
     <hyperlink ref="T185" ns1:id="rIdResume407"/>
+    <hyperlink ref="T186" ns1:id="rIdResume408"/>
+    <hyperlink ref="T187" ns1:id="rIdResume409"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -34575,6 +34742,1050 @@
       </c>
       <c r="I557" t="str" s="3">
         <v>resume_sources_20261009.json，官方正文与首次访问返回</v>
+      </c>
+    </row>
+    <row r="558" ht="52.5" customHeight="1">
+      <c r="A558" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B558" t="str" s="3">
+        <v>香港平台补漏</v>
+      </c>
+      <c r="C558" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D558" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E558" t="str" s="3">
+        <v>查询：Hong Kong robotics open research fund 2026 external applicants；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F558" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G558" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H558" t="str" s="3"/>
+      <c r="I558" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第172项</v>
+      </c>
+    </row>
+    <row r="559" ht="52.5" customHeight="1">
+      <c r="A559" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B559" t="str" s="3">
+        <v>南京地区平台补漏</v>
+      </c>
+      <c r="C559" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D559" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E559" t="str" s="3">
+        <v>查询：南京 开放课题 机器人 2026 实验室；定位：关于江苏省具身智能机器人技术重点实验室2026年开放课题申报工作的通知；警犬技术公安部重点实验室发布2026年度开放课题申请指南；江苏省具身智能工业机器人及其人机协作高校重点实验室开放课题管理办法-电气与自动化工程学院；2026年度开放课题申请公告；​江苏省工业人工智能重点实验室2026年度开放课题拟立项结果公示-- 中国科学院工业人工智能研究所；关于发布空间智能感知与大模型应用联合实验室2026年度开放基金课题申报指南的通知</v>
+      </c>
+      <c r="F559" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G559" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H559" t="str" s="3">
+        <v>https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
+https://www.njpu.edu.cn/2026/0420/c1693a102949/page.htm
+https://dqxylib.szut.edu.cn/info/1016/27682.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://iaii.cas.cn/kxyj/ptjs/202607/t20260729_8256776.html
+https://kyy.nuaa.edu.cn/2026/0604/c5817a400921/page.htm</v>
+      </c>
+      <c r="I559" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第173项</v>
+      </c>
+    </row>
+    <row r="560" ht="52.5" customHeight="1">
+      <c r="A560" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B560" t="str" s="3">
+        <v>省属高校平台补漏</v>
+      </c>
+      <c r="C560" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D560" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E560" t="str" s="3">
+        <v>查询：机器人 开放课题 2027 重点实验室 申请；定位：移动通信全国重点实验室 2027年度开放课题申请指南；申请表下载----机器人与智能系统全国重点实验室；2026年度开放课题申请公告；智能制造装备与技术全国重点实验室2027年度开放课题申请通知-智能制造装备与技术全国重点实验室；生命过程小分子调控全国重点实验室2027年度开放课题申请指南--生命过程小分子调控全国重点实验室；机器人与智能系统全国重点实验室 2025年度开放课题申请指南----机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="F560" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G560" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H560" t="str" s="3">
+        <v>https://ncrl.seu.edu.cn/2026/0803/c15598a578768/page.htm
+https://rlab.sia.cas.cn/kfjj/sqbxz/
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://imet.hust.edu.cn/info/1031/2870.htm
+https://sioc.cas.cn/sklcb/kfgx/kfkt/sqzn/202606/t20260630_8235628.html
+https://rlab.sia.cas.cn/gg/202507/t20250729_643573.html</v>
+      </c>
+      <c r="I560" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第174项</v>
+      </c>
+    </row>
+    <row r="561" ht="52.5" customHeight="1">
+      <c r="A561" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B561" t="str" s="3">
+        <v>澳门平台补漏</v>
+      </c>
+      <c r="C561" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D561" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E561" t="str" s="3">
+        <v>查询：澳门 开放基金 机器人 2026；定位：万家中证机器人交易型开放式指数证券投资基金更新招募说明书（2026年第2号）；关于同意东方证券股份有限公司为招商中证机器人交易型开放式指数证券投资基金提供主做市服务的公告 | 上海证券交易所；Microsoft Word - 鹏华国证机器人产业交易型开放式指数证券投资基金更新的招募说明书20260703.docx；嘉实中证机器人交易型开放式指数证券投资基金更新招募说明书（2026年03月27日更新）；国泰中证机器人交易型开放式指数证券</v>
+      </c>
+      <c r="F561" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G561" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H561" t="str" s="3">
+        <v>https://www.sse.com.cn/disclosure/fund/announcement/c/new/2026-03-31/560630_20260331_TM6L.pdf
+https://www.sse.com.cn/disclosure/announcement/general/jjzssgg/c/c_20260115_10805288.shtml
+https://static.cninfo.com.cn/finalpage/2026-07-03/1225407089.PDF
+https://notice.10jqka.com.cn/api/pdf/d75b9fc0034c0005.pdf
+https://pdf.dfcfw.com/pdf/H2_AN202603131820535353_1.pdf</v>
+      </c>
+      <c r="I561" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第175项</v>
+      </c>
+    </row>
+    <row r="562" ht="52.5" customHeight="1">
+      <c r="A562" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B562" t="str" s="3">
+        <v>重庆理工大学</v>
+      </c>
+      <c r="C562" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D562" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E562" t="str" s="3">
+        <v>查询：site:cqut.edu.cn "开放课题" "2026"；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F562" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G562" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H562" t="str" s="3"/>
+      <c r="I562" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第176项</v>
+      </c>
+    </row>
+    <row r="563" ht="52.5" customHeight="1">
+      <c r="A563" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B563" t="str" s="3">
+        <v>重庆邮电大学</v>
+      </c>
+      <c r="C563" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D563" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E563" t="str" s="3">
+        <v>查询：site:cqupt.edu.cn "开放基金" "2026"；定位：工业物联网与网络化控制教育部重点实验室</v>
+      </c>
+      <c r="F563" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G563" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H563" t="str" s="3">
+        <v>https://iot.cqupt.edu.cn/</v>
+      </c>
+      <c r="I563" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第177项</v>
+      </c>
+    </row>
+    <row r="564" ht="52.5" customHeight="1">
+      <c r="A564" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B564" t="str" s="3">
+        <v>南京理工大学</v>
+      </c>
+      <c r="C564" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D564" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E564" t="str" s="3">
+        <v>查询：site:njust.edu.cn "开放课题" "2026" 机器人；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F564" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G564" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H564" t="str" s="3"/>
+      <c r="I564" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第178项</v>
+      </c>
+    </row>
+    <row r="565" ht="52.5" customHeight="1">
+      <c r="A565" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B565" t="str" s="3">
+        <v>苏州科技大学</v>
+      </c>
+      <c r="C565" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D565" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E565" t="str" s="3">
+        <v>查询：site:usts.edu.cn "开放基金"；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F565" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G565" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H565" t="str" s="3"/>
+      <c r="I565" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第179项</v>
+      </c>
+    </row>
+    <row r="566" ht="52.5" customHeight="1">
+      <c r="A566" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B566" t="str" s="3">
+        <v>长春理工大学</v>
+      </c>
+      <c r="C566" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D566" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E566" t="str" s="3">
+        <v>查询：长春理工大学 开放课题 智能；定位：跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)</v>
+      </c>
+      <c r="F566" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G566" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H566" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/kfyjl/kfkt/deeaacf5c4cd4a4c99d931f74f0fd8d9.htm
+https://cmnm.cust.edu.cn/kfyjl/kfkt/index.htm</v>
+      </c>
+      <c r="I566" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第180项</v>
+      </c>
+    </row>
+    <row r="567" ht="52.5" customHeight="1">
+      <c r="A567" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B567" t="str" s="3">
+        <v>哈尔滨理工大学</v>
+      </c>
+      <c r="C567" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D567" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E567" t="str" s="3">
+        <v>查询：哈尔滨理工大学 开放基金 机器人；定位：2025年度开放基金申请公告；哈尔滨工业大学机器人技术与系统国家重点实验室；2026年度开放课题申请公告；2025年度开放基金评审结果公告；2023年度开放基金申请公告；机器人技术与系统国家重点实验室（哈尔滨工业大学）</v>
+      </c>
+      <c r="F567" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G567" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H567" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://robot.hit.edu.cn/_s11/main.psp
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://robot.hit.edu.cn/2024/1210/c338a360989/page.htm
+https://robot.hit.edu.cn/2022/1018/c338a282555/page.htm
+https://robot.hit.edu.cn/_upload/article/files/74/20/e1401e0a4bd58541639716dd275d/dcaff854-475c-4401-abd3-b25f7ac81081.pdf</v>
+      </c>
+      <c r="I567" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第181项</v>
+      </c>
+    </row>
+    <row r="568" ht="52.5" customHeight="1">
+      <c r="A568" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B568" t="str" s="3">
+        <v>浙江科技大学</v>
+      </c>
+      <c r="C568" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D568" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E568" t="str" s="3">
+        <v>查询：浙江科技大学 开放基金 2026；定位：先进纺织材料与制备技术教育部重点实验室 （浙江理工大学） 开放基金申请指南 （2026年度）-信息公开；2026 工控全重开放基金-湖控专项</v>
+      </c>
+      <c r="F568" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G568" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H568" t="str" s="3">
+        <v>https://xxgk.zstu.edu.cn/info/1107/4694.htm
+https://sklict.zju.edu.cn/_upload/article/files/78/0c/0e0b7cb64212855ad4d1fb5eaeb6/cffa0197-6de0-47f3-bf87-72beb7a06283.pdf</v>
+      </c>
+      <c r="I568" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第182项</v>
+      </c>
+    </row>
+    <row r="569" ht="52.5" customHeight="1">
+      <c r="A569" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B569" t="str" s="3">
+        <v>济南大学</v>
+      </c>
+      <c r="C569" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D569" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E569" t="str" s="3">
+        <v>查询：济南大学 开放课题 机器人；定位：2026年度开放课题申请公告；开放基金课题指南；近几年所承担的研究项目 | 云基智能机器人实验室；济南大学主页平台管理系统 Ai Changsheng--Home--Home；山东省无人系统智能技术与装备重点实验室2026年度开放课题申请指南；自主智能无人系统全国重点实验室2024年度开放课题申请指南</v>
+      </c>
+      <c r="F569" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G569" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H569" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://keysoftlab.nju.edu.cn/20/19/c1579a204825/page.htm
+https://www.cirobot.org/research/projects/
+https://faculty.ujn.edu.cn/aizhangsheng/en/index.htm
+https://slx.qlu.edu.cn/_t1249/2026/0409/c3946a275414/page.htm
+https://skl-ais.tongji.edu.cn/2c/f4/c32347a339188/page.htm</v>
+      </c>
+      <c r="I569" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第183项</v>
+      </c>
+    </row>
+    <row r="570" ht="52.5" customHeight="1">
+      <c r="A570" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B570" t="str" s="3">
+        <v>哈尔滨工业大学</v>
+      </c>
+      <c r="C570" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D570" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E570" t="str" s="3">
+        <v>查询：机器人技术与系统 高压作业机器人 专项 2026 申请；定位：机器人技术与系统全国重点实验室关于申报高压作业机器人专项的通知；机器人技术与系统全国重点实验室关于申报海上风电叶片检修机器人专项的通知；2026年度开放课题申请公告</v>
+      </c>
+      <c r="F570" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G570" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H570" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0917/c277a401682/page.htm
+https://robot.hit.edu.cn/2026/0917/c277a401687/page.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm</v>
+      </c>
+      <c r="I570" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第184项</v>
+      </c>
+    </row>
+    <row r="571" ht="52.5" customHeight="1">
+      <c r="A571" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B571" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="C571" t="str" s="3">
+        <v>青海</v>
+      </c>
+      <c r="D571" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E571" t="str" s="3">
+        <v>查询：青海大学 新能源 高端装备 开放课题；定位：新能源电力系统智慧运行教育部重点实验室2026年度开放课题申报指南 - 课题部落；教育部新能源系统高端装备和智慧运行工程研究中心；教育部新能源电力系统智慧运行重点实验室；关于“高端装备先进感知与智能控制教育部重点实验室”与“皖江高端装备制造协同创新中心”2025年度开放课题申请的通知；关于“高端装备先进感知与智能控制教育部重点实验室”2022年度开放基金项目申请的通知；关于“高端装备先进感知与智能控制”教育部重点实验室2020年度开放课题的申请通知</v>
+      </c>
+      <c r="F571" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G571" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H571" t="str" s="3">
+        <v>https://www.iktbl.com/?p=4981
+https://seee.qhu.edu.cn/docs/2024-11/1e5dc53ded204253ac27ede7c3c72671.pdf
+https://seee.qhu.edu.cn/docs/2024-11/578a4dec562644c298214a650c53919c.pdf
+https://cee.ahpu.edu.cn/lapic/2025/0827/c7174a253666/page.htm
+https://kjc.ahpu.edu.cn/_t41/2022/1123/c731a183627/page.psp
+https://cee.ahpu.edu.cn/lapic/2020/1021/c7174a143447/page.psp</v>
+      </c>
+      <c r="I571" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第185项</v>
+      </c>
+    </row>
+    <row r="572" ht="52.5" customHeight="1">
+      <c r="A572" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B572" t="str" s="3">
+        <v>哈尔滨工业大学</v>
+      </c>
+      <c r="C572" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D572" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E572" t="str" s="3">
+        <v>查询：机器人技术与系统 新能源运维机器人 专项 2025 申请；定位：机器人技术与系统全国重点实验室关于申报新能源运维机器人专项的通知；机器人技术与系统全国重点实验室 关于申报新能源运维机器人专项的通知；2025年度开放基金申请公告；机器人与智能系统全国重点实验室 2025年度开放课题申请指南----机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="F572" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G572" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H572" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2025/1106/c338a381201/page.htm
+https://robot.hit.edu.cn/2025/0812/c338a376279/page.htm
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://rlab.sia.cas.cn/gg/202507/t20250729_643573.html</v>
+      </c>
+      <c r="I572" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第186项</v>
+      </c>
+    </row>
+    <row r="573" ht="52.5" customHeight="1">
+      <c r="A573" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B573" t="str" s="3">
+        <v>哈尔滨工业大学</v>
+      </c>
+      <c r="C573" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D573" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E573" t="str" s="3">
+        <v>查询：机器人技术与系统 海上风电叶片检修 专项 2026 申请；定位：机器人技术与系统全国重点实验室关于申报海上风电叶片检修机器人专项的通知；中国三峡集团电子采购平台；中国三峡集团电子采购平台；机器人技术与系统全国重点实验室 关于申报新能源运维机器人专项的通知；中国三峡集团电子采购平台</v>
+      </c>
+      <c r="F573" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G573" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H573" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0917/c277a401687/page.htm
+https://eps.ctg.com.cn/cms/channel/2ywgg1/240639171.htm
+https://eps.ctg.com.cn/cms/channel/2ywgg1/240639607.htm
+https://robot.hit.edu.cn/2025/0812/c338a376279/page.htm
+https://eps.ctg.com.cn/cms/channel/2ywgg1/240631693.htm</v>
+      </c>
+      <c r="I573" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第187项</v>
+      </c>
+    </row>
+    <row r="574" ht="52.5" customHeight="1">
+      <c r="A574" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B574" t="str" s="3">
+        <v>长春理工大学</v>
+      </c>
+      <c r="C574" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D574" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E574" t="str" s="3">
+        <v>查询：site:cmnm.cust.edu.cn 开放课题 2026；定位：跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室2025-2026年度开放基金资助结果公示——跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)</v>
+      </c>
+      <c r="F574" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G574" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H574" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/kfyjl/kfkt/deeaacf5c4cd4a4c99d931f74f0fd8d9.htm
+https://cmnm.cust.edu.cn/kfyjl/kfkt/index.htm
+https://cmnm.cust.edu.cn/yxgl/gzzd/76198.htm
+https://cmnm.cust.edu.cn/xwdt/4d5276ea31864958966b8a08a60a7226.htm
+https://cmnm.cust.edu.cn/yxgl/gzzd/76199.htm
+https://cmnm.cust.edu.cn/xwdt/index.htm</v>
+      </c>
+      <c r="I574" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第188项</v>
+      </c>
+    </row>
+    <row r="575" ht="52.5" customHeight="1">
+      <c r="A575" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B575" t="str" s="3">
+        <v>哈尔滨理工大学</v>
+      </c>
+      <c r="C575" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D575" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E575" t="str" s="3">
+        <v>查询：site:hrbust.edu.cn 开放基金；定位：教育部工程研究中心年度报告；高等学校实验室工作规程-哈尔滨理工大学电工电子省级实验教学示范中心</v>
+      </c>
+      <c r="F575" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G575" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H575" t="str" s="3">
+        <v>https://kjc.hrbust.edu.cn/_upload/article/files/a7/5a/97f25693482693cb63edb27b402d/609b70a5-0622-47e2-b300-b596510b429a.pdf
+https://dgsxzx.cetong.hrbust.edu.cn/info/1057/1147.htm</v>
+      </c>
+      <c r="I575" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第189项</v>
+      </c>
+    </row>
+    <row r="576" ht="52.5" customHeight="1">
+      <c r="A576" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B576" t="str" s="3">
+        <v>济南大学</v>
+      </c>
+      <c r="C576" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D576" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E576" t="str" s="3">
+        <v>查询：site:ujn.edu.cn 科研平台 机器人 实验室；定位：重点实验室-济南大学自动化学院；采购公告-济南大学实验室与资产管理处；高水平学科平台-济南大学；采购结果公示-济南大学实验室与资产管理处</v>
+      </c>
+      <c r="F576" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G576" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H576" t="str" s="3">
+        <v>https://cse.ujn.edu.cn/kxyj/zdsys.htm
+https://sygz.ujn.edu.cn/cggg.htm
+https://www.ujn.edu.cn/kxyj/gspxkpt.htm
+https://sygz.ujn.edu.cn/cgjggs/33.htm</v>
+      </c>
+      <c r="I576" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第190项</v>
+      </c>
+    </row>
+    <row r="577" ht="52.5" customHeight="1">
+      <c r="A577" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B577" t="str" s="3">
+        <v>浙江科技大学</v>
+      </c>
+      <c r="C577" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D577" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E577" t="str" s="3">
+        <v>查询：site:zust.edu.cn 科研平台 机器人 实验室；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F577" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G577" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H577" t="str" s="3"/>
+      <c r="I577" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第191项</v>
+      </c>
+    </row>
+    <row r="578" ht="52.5" customHeight="1">
+      <c r="A578" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B578" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="C578" t="str" s="3">
+        <v>青海</v>
+      </c>
+      <c r="D578" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E578" t="str" s="3">
+        <v>查询：site:seee.qhu.edu.cn "开放课题指南（2026）"；定位：本次未取得新增正式入口</v>
+      </c>
+      <c r="F578" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G578" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H578" t="str" s="3"/>
+      <c r="I578" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第192项</v>
+      </c>
+    </row>
+    <row r="579" ht="52.5" customHeight="1">
+      <c r="A579" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B579" t="str" s="3">
+        <v>哈尔滨理工大学</v>
+      </c>
+      <c r="C579" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D579" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E579" t="str" s="3">
+        <v>查询："汽车电子驱动控制与系统集成" "开放基金"；定位：教育部工程研究中心年度报告；8个重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F579" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G579" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H579" t="str" s="3">
+        <v>https://kjc.hrbust.edu.cn/_upload/article/files/a7/5a/97f25693482693cb63edb27b402d/609b70a5-0622-47e2-b300-b596510b429a.pdf
+https://www.letpub.com.cn/index.php?article_id=1764&amp;page=grant_article_details</v>
+      </c>
+      <c r="I579" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第193项</v>
+      </c>
+    </row>
+    <row r="580" ht="52.5" customHeight="1">
+      <c r="A580" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B580" t="str" s="3">
+        <v>西藏大学</v>
+      </c>
+      <c r="C580" t="str" s="3">
+        <v>西藏</v>
+      </c>
+      <c r="D580" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E580" t="str" s="3">
+        <v>查询：site:utibet.edu.cn 开放课题 机器人；定位：青藏高原生物多样性与生态环境保护教育部重点实验室；青藏高原生物多样性与生态环境保护教育部重点实验室 2026年度开放课题申报通知-青藏高原生物多样性与生态环境保护教育部重点实验室；2026年青藏高原生物多样性与生态环境保护教育部重点实验室开放课题资助名单-青藏高原生物多样性与生态环境保护教育部重点实验室；青藏高原生物多样性与生态环境保护教育部重点实验室开放课题申报通知-青藏高原生物多样性与生态环境保护教育部重点实验室；2025年青藏高原生物多样性与生态环境保护教育部重点实验室开放课题资助名单-青藏高原生物多样性与生态环境保护教育部重点实验室；青藏高原生物多样性与生态环境保护教育部 重点实验2024年度开放课题资助名单-西藏大学生态环境学院</v>
+      </c>
+      <c r="F580" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G580" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H580" t="str" s="3">
+        <v>https://klbeqtp.utibet.edu.cn/
+https://klbeqtp.utibet.edu.cn/info/1025/1223.htm
+https://klbeqtp.utibet.edu.cn/info/1024/1244.htm
+https://klbeqtp.utibet.edu.cn/info/1025/1037.htm
+https://klbeqtp.utibet.edu.cn/info/1025/1115.htm
+https://ee.utibet.edu.cn/info/1064/2064.htm</v>
+      </c>
+      <c r="I580" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第194项</v>
+      </c>
+    </row>
+    <row r="581" ht="52.5" customHeight="1">
+      <c r="A581" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B581" t="str" s="3">
+        <v>济南大学</v>
+      </c>
+      <c r="C581" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D581" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E581" t="str" s="3">
+        <v>查询："智能感知与机器人应用" "开放"；定位：科沃斯八界具身智能开放社区 - 机器人·仿真·开发者生态；多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所；天津中德应用技术大学机关政府采购意向公告-巴彦淖尔今日招标-巴彦淖尔招标采购信息服务平台</v>
+      </c>
+      <c r="F581" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G581" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H581" t="str" s="3">
+        <v>https://www.ecovacs-tech.com/
+https://www.ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html
+https://byne.jrzb.com/purchases/2026-02-11.0f6a47607e84ae583aeb865c71b23084</v>
+      </c>
+      <c r="I581" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第195项</v>
+      </c>
+    </row>
+    <row r="582" ht="52.5" customHeight="1">
+      <c r="A582" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B582" t="str" s="3">
+        <v>中央高校基本科研业务费补漏</v>
+      </c>
+      <c r="C582" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D582" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E582" t="str" s="3">
+        <v>查询："重点平台开放基金" "2026"；定位：高速公路筑养装备与技术教育部工程研究中心2026年开放基金申请指南；道路施工技术与装备教育部重点实验室2026年开放基金申请指南；青海省盐湖资源化学重点实验室开放课题2026年度项目申请指南----中国科学院青海盐湖研究所；2026年安徽省实景地理环境重点实验室开放课题申报指南</v>
+      </c>
+      <c r="F582" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G582" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H582" t="str" s="3">
+        <v>https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261026/page.psp
+https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261025/page.psp
+https://www.isl.ac.cn/qt/tzgg/202603/t20260310_8153375.html
+https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm</v>
+      </c>
+      <c r="I582" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第196项</v>
+      </c>
+    </row>
+    <row r="583" ht="52.5" customHeight="1">
+      <c r="A583" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B583" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="C583" t="str" s="3">
+        <v>青海</v>
+      </c>
+      <c r="D583" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E583" t="str" s="3">
+        <v>查询：site:seee.qhu.edu.cn 开放课题 2027；定位：教育部新能源系统高端装备和智慧运行工程研究中心；教育部新能源电力系统智慧运行重点实验室；教育部新能源电力系统智慧运行重点实验室和</v>
+      </c>
+      <c r="F583" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G583" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H583" t="str" s="3">
+        <v>https://seee.qhu.edu.cn/docs/2024-11/1e5dc53ded204253ac27ede7c3c72671.pdf
+https://seee.qhu.edu.cn/docs/2024-11/578a4dec562644c298214a650c53919c.pdf
+https://seee.qhu.edu.cn/docs/2024-11/fc1904c969ca48d4b68259cb015bc1cc.pdf</v>
+      </c>
+      <c r="I583" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第197项</v>
+      </c>
+    </row>
+    <row r="584" ht="52.5" customHeight="1">
+      <c r="A584" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B584" t="str" s="3">
+        <v>长春理工大学</v>
+      </c>
+      <c r="C584" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D584" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E584" t="str" s="3">
+        <v>查询：site:cmnm.cust.edu.cn 开放基金 2027；定位：跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室2025-2026年度开放基金资助结果公示——跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)；跨尺度微纳制造教育部重点实验室(长春理工大学)</v>
+      </c>
+      <c r="F584" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G584" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H584" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/kfyjl/kfkt/deeaacf5c4cd4a4c99d931f74f0fd8d9.htm
+https://cmnm.cust.edu.cn/kfyjl/kfkt/78701.htm
+https://cmnm.cust.edu.cn/xwdt/4d5276ea31864958966b8a08a60a7226.htm
+https://cmnm.cust.edu.cn/kfyjl/kfkt/index.htm
+https://cmnm.cust.edu.cn/xwdt/index.htm
+https://cmnm.cust.edu.cn/</v>
+      </c>
+      <c r="I584" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第198项</v>
+      </c>
+    </row>
+    <row r="585" ht="52.5" customHeight="1">
+      <c r="A585" t="str" s="3">
+        <v>2026-10-09全国省属/平台交叉补漏</v>
+      </c>
+      <c r="B585" t="str" s="3">
+        <v>中央高校基本科研业务费补漏</v>
+      </c>
+      <c r="C585" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D585" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E585" t="str" s="3">
+        <v>查询："中央高校基本科研业务费" "开放基金" "机器人" "2026"；定位：博达主页平台管理系统 刘乐元--Home-- 中央高校基本科研业务费优秀青年团队项目，基于元宇宙的儿童孤独症干预与评估技术研究，45万元，2022/06~2025/05， 在研，主持；中国矿业大学主页平台系统 huadezheng--Home-- 磁流变仿生手驱动-传动一体化控制方法研究</v>
+      </c>
+      <c r="F585" t="str" s="3">
+        <v>检索结果可能为其他机构或获资助履历，先对账；不是逐平台完整覆盖，未命中不代表没有基金。</v>
+      </c>
+      <c r="G585" t="str" s="3">
+        <v>仅本行定向范围；新增项目/既有排除的核验结论见独立年度记录。</v>
+      </c>
+      <c r="H585" t="str" s="3">
+        <v>https://faculty.ccnu.edu.cn/liuleyuan/en/kyxm/216576/content/5668.htm
+https://faculty.cumt.edu.cn/huadezheng1/en/kyxm/240585/content/41685.htm</v>
+      </c>
+      <c r="I585" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第199项</v>
+      </c>
+    </row>
+    <row r="586" ht="52.5" customHeight="1">
+      <c r="A586" t="str" s="3">
+        <v>2026-10-09新增年度具体核验</v>
+      </c>
+      <c r="B586" t="str" s="3">
+        <v>长春理工大学</v>
+      </c>
+      <c r="C586" t="str" s="3">
+        <v>吉林·长春</v>
+      </c>
+      <c r="D586" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E586" t="str" s="3">
+        <v>跨尺度微纳制造教育部重点实验室；2025—2026（共享轮次）；N037；2025—2026共享批次正式官方公告全文已核；管理经费页面2021版已核，当前适用待确认</v>
+      </c>
+      <c r="F586" t="str" s="3">
+        <v>已截止。须取得申请书/简历、开放合作机制及当年管理办法；确认非985/211依托单位是否受理、2021经费条款适用性、外拨范围/流程；2027新公告未取得。</v>
+      </c>
+      <c r="G586" t="str" s="3">
+        <v>仅本平台所列批次资料已核，机构其他平台/2027仍继续。</v>
+      </c>
+      <c r="H586" t="str" s="3">
+        <v>https://cmnm.cust.edu.cn/kfyjl/kfkt/deeaacf5c4cd4a4c99d931f74f0fd8d9.htm</v>
+      </c>
+      <c r="I586" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="587" ht="52.5" customHeight="1">
+      <c r="A587" t="str" s="3">
+        <v>2026-10-09新增年度具体核验</v>
+      </c>
+      <c r="B587" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="C587" t="str" s="3">
+        <v>青海·西宁</v>
+      </c>
+      <c r="D587" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E587" t="str" s="3">
+        <v>新能源系统高端装备和智慧运行教育部工程研究中心；2026；N038；2026正式指南PDF已取得前5页文字，末页首次渲染超时；2026-04-14官方立项通知已核；非当前受理</v>
+      </c>
+      <c r="F587" t="str" s="3">
+        <v>2026立项结果已发布，非当前申报项目；待补PDF第6页截止/联系人/知识产权等及管理办法，核研究期与11月30报账时间关系；2027公告未取得。</v>
+      </c>
+      <c r="G587" t="str" s="3">
+        <v>仅本平台所列批次资料已核，机构其他平台/2027仍继续。</v>
+      </c>
+      <c r="H587" t="str" s="3">
+        <v>https://seee.qhu.edu.cn/docs/2026-03/030d356bfc944682adbfd3d82afac1e0.pdf</v>
+      </c>
+      <c r="I587" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="588" ht="52.5" customHeight="1">
+      <c r="A588" t="str" s="3">
+        <v>2026-10-09具体机制目录/去重核验</v>
+      </c>
+      <c r="B588" t="str" s="3">
+        <v>哈尔滨工业大学</v>
+      </c>
+      <c r="C588" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D588" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E588" t="str" s="3">
+        <v>2026海上风电叶片检修/高压操作专项复用已剔除E062/E063，本校全职教师限制不因高度相关技术任务撤销；2025新能源两次专项搜索亦明确校内负责人，未作为外部开放项目。</v>
+      </c>
+      <c r="F588" t="str" s="3">
+        <v>2027外部开放年度公告未取得，不能拿2025限校内专项替代外部基金。</v>
+      </c>
+      <c r="G588" t="str" s="3">
+        <v>已核所述具体机制，剩余范围继续。</v>
+      </c>
+      <c r="H588" t="str" s="3">
+        <v>https://robot.hit.edu.cn/xxdt/list.htm</v>
+      </c>
+      <c r="I588" t="str" s="3">
+        <v>resume_sources_20261009.json 官方正文/检索结果</v>
+      </c>
+    </row>
+    <row r="589" ht="52.5" customHeight="1">
+      <c r="A589" t="str" s="3">
+        <v>2026-10-09具体机制目录/去重核验</v>
+      </c>
+      <c r="B589" t="str" s="3">
+        <v>济南大学</v>
+      </c>
+      <c r="C589" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D589" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E589" t="str" s="3">
+        <v>官方自动化重点实验室/机器人工程专业资料定位过程控制平台及2022成立智能感知与机器人应用山东省工程中心；定向开放机制查询未定位正式指南。</v>
+      </c>
+      <c r="F589" t="str" s="3">
+        <v>全校及本中心2026/2027实际开放机制未确认。</v>
+      </c>
+      <c r="G589" t="str" s="3">
+        <v>已核所述具体机制，剩余范围继续。</v>
+      </c>
+      <c r="H589" t="str" s="3">
+        <v>https://cse.ujn.edu.cn/kxyj/zdsys.htm
+https://cse.ujn.edu.cn/info/1412/17081.htm</v>
+      </c>
+      <c r="I589" t="str" s="3">
+        <v>resume_sources_20261009.json 官方正文/检索结果</v>
+      </c>
+    </row>
+    <row r="590" ht="52.5" customHeight="1">
+      <c r="A590" t="str" s="3">
+        <v>2026-10-09具体机制目录/去重核验</v>
+      </c>
+      <c r="B590" t="str" s="3">
+        <v>哈尔滨理工大学</v>
+      </c>
+      <c r="C590" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D590" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E590" t="str" s="3">
+        <v>官方汽车电子驱动控制与系统集成教育部工程研究中心2022年度报告列向行业设开放基金；M047先进制造智能化2022原记录复用。</v>
+      </c>
+      <c r="F590" t="str" s="3">
+        <v>年度报告不能当2026受理公告，中心外部基金年度任务/条件未取得，继续查。</v>
+      </c>
+      <c r="G590" t="str" s="3">
+        <v>已核所述具体机制，剩余范围继续。</v>
+      </c>
+      <c r="H590" t="str" s="3">
+        <v>https://kjc.hrbust.edu.cn/_upload/article/files/a7/5a/97f25693482693cb63edb27b402d/609b70a5-0622-47e2-b300-b596510b429a.pdf</v>
+      </c>
+      <c r="I590" t="str" s="3">
+        <v>resume_sources_20261009.json 官方正文/检索结果</v>
+      </c>
+    </row>
+    <row r="591" ht="52.5" customHeight="1">
+      <c r="A591" t="str" s="3">
+        <v>2026-10-09具体机制目录/去重核验</v>
+      </c>
+      <c r="B591" t="str" s="3">
+        <v>青海大学</v>
+      </c>
+      <c r="C591" t="str" s="3">
+        <v>青海</v>
+      </c>
+      <c r="D591" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E591" t="str" s="3">
+        <v>能源学院2项教育部平台2026开放指南及工程中心立项通知定位，重点实验室M054复用、工程中心N038新增；学院科研平台目录另列压缩空气储能/先进材料两个省室。</v>
+      </c>
+      <c r="F591" t="str" s="3">
+        <v>工程中心6页PDF末页首次失败，期限、联系人及IP待人工；其他学院相关平台未全查。</v>
+      </c>
+      <c r="G591" t="str" s="3">
+        <v>已核所述具体机制，剩余范围继续。</v>
+      </c>
+      <c r="H591" t="str" s="3">
+        <v>https://seee.qhu.edu.cn/kxyj/sysgl/index.htm
+https://seee.qhu.edu.cn/tzgg/index.htm</v>
+      </c>
+      <c r="I591" t="str" s="3">
+        <v>resume_sources_20261009.json 官方正文/检索结果</v>
       </c>
     </row>
   </sheetData>
@@ -36698,21 +37909,41 @@
     </row>
     <row r="105" ht="96" customHeight="1">
       <c r="A105" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B105" t="n" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C105" t="str" s="14">
+        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+      </c>
+      <c r="D105" t="str" s="15">
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+      </c>
+      <c r="E105" t="str" s="15">
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+      </c>
+      <c r="F105" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="106" ht="96" customHeight="1">
+      <c r="A106" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B105" t="n" s="13">
+      <c r="B106" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C105" t="str" s="14">
+      <c r="C106" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D105" t="str" s="15">
+      <c r="D106" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E105" t="str" s="15">
+      <c r="E106" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F105" t="str" s="16">
+      <c r="F106" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -36908,8 +38139,8 @@
     <hyperlink ref="F97" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C98" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F98" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F105" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C105" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F106" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C106" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C99" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F99" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C100" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -36926,6 +38157,8 @@
     <hyperlink ref="F104" ns1:id="rIdResume104"/>
     <hyperlink ref="C13" location="'02项目完整详情'!A185" display="项目完整详情"/>
     <hyperlink ref="F13" ns1:id="rIdResume105"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A186" display="项目完整详情"/>
+    <hyperlink ref="F105" ns1:id="rIdResume106"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -38730,6 +39963,32 @@
       </c>
       <c r="H61" t="str" s="3">
         <v>李老师；18853318883；ligen@cdu.edu.cn</v>
+      </c>
+    </row>
+    <row r="62" ht="66" customHeight="1">
+      <c r="A62" t="str" s="20">
+        <v>历史批次·截止条款待核</v>
+      </c>
+      <c r="B62" t="str" s="13">
+        <v>具体截止日未取得（2026-04-14已发布立项通知）</v>
+      </c>
+      <c r="C62" t="str" s="14">
+        <v>青海大学·新能源系统高端装备和智慧运行教育部工程研究中心</v>
+      </c>
+      <c r="D62" t="str" s="15">
+        <v>年度方向四2明确新能源场站先进机器人、自动巡检、故障排查及维修、无人机巡检、自动化清洁维护、机器人与AI融合实现自主运维；其他能源调度/材料任务不扩充。</v>
+      </c>
+      <c r="E62" t="str" s="15">
+        <v>5万元/项；拟资助3项。</v>
+      </c>
+      <c r="F62" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G62" t="str" s="3">
+        <v>2026立项结果已发布，非当前申报项目；待补PDF第6页截止/联系人/知识产权等及管理办法，核研究期与11月30报账时间关系；2027公告未取得。</v>
+      </c>
+      <c r="H62" t="str" s="3">
+        <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
       </c>
     </row>
   </sheetData>
@@ -38854,6 +40113,8 @@
     <hyperlink ref="F54" ns1:id="rIdResume62"/>
     <hyperlink ref="C55" location="'02项目完整详情'!A181" display="项目完整详情"/>
     <hyperlink ref="F55" ns1:id="rIdResume63"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A187" display="项目完整详情"/>
+    <hyperlink ref="F62" ns1:id="rIdResume64"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -17086,6 +17086,169 @@
       </c>
       <c r="AA187" t="str" s="3"/>
     </row>
+    <row r="188" ht="79.5" customHeight="1">
+      <c r="A188" t="str" s="3">
+        <v>N039</v>
+      </c>
+      <c r="B188" t="str" s="3">
+        <v>官方2024年度公告正文已核；附件RAR首次读取失败</v>
+      </c>
+      <c r="C188" t="str" s="3">
+        <v>江西科技师范大学</v>
+      </c>
+      <c r="D188" t="str" s="3">
+        <v>江西省无人感知系统与人工智能技术工程研究中心</v>
+      </c>
+      <c r="E188" t="str" s="3">
+        <v>历史批次·截止年份冲突待核</v>
+      </c>
+      <c r="F188" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G188" t="str" s="6">
+        <v>原文2024-07-15至2023-07-20；年份冲突</v>
+      </c>
+      <c r="H188" t="str" s="3">
+        <v>未载截止时点，日期年份冲突不能推定</v>
+      </c>
+      <c r="I188" t="str" s="3">
+        <v>三维重建；目标感知与识别；无人移动载体自主导航及智能控制；无人移动载体协同工作控制；人工智能感知方法。</v>
+      </c>
+      <c r="J188" t="str" s="3">
+        <v>一般课题不超过3万元/项</v>
+      </c>
+      <c r="K188" t="str" s="3">
+        <v>具有博士学位或中级以上职称；面向校内外科研人员；主持申请不超过1项。</v>
+      </c>
+      <c r="L188" t="str" s="3">
+        <v>必须至少1名固定人员作为课题组成员及联系人；正文称“本省重点实验室”，与工程中心标题不一致，需确认人员归属。访问要求未取得。</v>
+      </c>
+      <c r="M188" t="str" s="3">
+        <v>经费使用范围、外拨或校内报销规则待附件管理办法核实。</v>
+      </c>
+      <c r="N188" t="str" s="3">
+        <v>2024年8月起执行，1—2年；确切起止以任务书为准。</v>
+      </c>
+      <c r="O188" t="str" s="3">
+        <v>正文未列成果数量及署名要求，待管理办法及任务书。</v>
+      </c>
+      <c r="P188" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q188" t="str" s="3">
+        <v>申请书纸质3份A4双面左装订，单位或科研部门盖章；同时PDF电子版1份；收件人刘老师；地址南昌市学府大道569号行政楼423，330038；邮箱20423232@qq.com。</v>
+      </c>
+      <c r="R188" t="str" s="3">
+        <v>本人博士背景已知；固定合作人员、在研限项、单位签章及准确截止条件未确认。</v>
+      </c>
+      <c r="S188" t="str" s="3">
+        <v>截止原文“2023年度”及2024-07-15—2023-07-20互相矛盾，不改写为2024-07-20；下载RAR中的申请指南、管理办法、申请书，补金额类别、经费/外拨、成果/IP、合作要求。2026—2027公告未定位，不能当当前窗口。</v>
+      </c>
+      <c r="T188" t="str" s="3">
+        <v>https://xxgc.jxstnu.edu.cn/info/1010/1188.htm</v>
+      </c>
+      <c r="U188" t="str" s="3">
+        <v>https://xxgc.jxstnu.edu.cn/__local/1/07/46/BA21BFD52EC6B95DECC63AE06E8_0839008E_1C11A.rar?e=.rar</v>
+      </c>
+      <c r="V188" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W188" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X188" t="str" s="3">
+        <v>历史开放机制；机器人相关具体任务已核，截止年份及附件条款待核。</v>
+      </c>
+      <c r="Y188" t="str" s="3">
+        <v>江西·南昌</v>
+      </c>
+      <c r="Z188" t="str" s="3">
+        <v>刘老师13576931367；20423232@qq.com</v>
+      </c>
+      <c r="AA188" t="str" s="3"/>
+    </row>
+    <row r="189" ht="79.5" customHeight="1">
+      <c r="A189" t="str" s="3">
+        <v>N040</v>
+      </c>
+      <c r="B189" t="str" s="3">
+        <v>官方2026公告正文已核；DOCX指南及DOC申请书首次读取失败</v>
+      </c>
+      <c r="C189" t="str" s="3">
+        <v>南昌航空大学</v>
+      </c>
+      <c r="D189" t="str" s="3">
+        <v>江西省智慧建筑工程研究中心等联署四个平台</v>
+      </c>
+      <c r="E189" t="str" s="3">
+        <v>任务证据待核·窗口未截止</v>
+      </c>
+      <c r="F189" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G189" t="n" s="6">
+        <v>46305</v>
+      </c>
+      <c r="H189" t="str" s="3">
+        <v>截止时点及时区未明示</v>
+      </c>
+      <c r="I189" t="str" s="3">
+        <v>公告列低空基础设施风险防控、韧性建造与智能运维、安全监测预警应急、智慧建筑绿色低碳、建筑及低空基础设施数字化智能系统、自主相关方向；未明确机器人感知、规划、控制等具体任务，须核附件，不因“低空”“智能”直接保留首页。</v>
+      </c>
+      <c r="J189" t="str" s="3">
+        <v>不超过2万元/项</v>
+      </c>
+      <c r="K189" t="str" s="3">
+        <v>国内外高级专业技术职务或博士及其他认可情形；课题须紧扣平台研究范围。</v>
+      </c>
+      <c r="L189" t="str" s="3">
+        <v>可在中心或申请者单位独立或合作研究；未列必须固定合作者及访问条款。</v>
+      </c>
+      <c r="M189" t="str" s="3">
+        <v>依据相关平台开放基金管理规定，正文未给经费范围及外拨/报销规则。</v>
+      </c>
+      <c r="N189" t="str" s="3">
+        <v>正文称一年，执行2026年12月至2027年12月；起止细节以任务书为准。</v>
+      </c>
+      <c r="O189" t="str" s="3">
+        <v>按时提交研究计划、进展及结题总结；论文数量、署名、单位排序未载。</v>
+      </c>
+      <c r="P189" t="str" s="3">
+        <v>正文未载知识产权条款，待附件/管理规定。</v>
+      </c>
+      <c r="Q189" t="str" s="3">
+        <v>开放基金申请书发71291@nchu.edu.cn，备注“开放基金+姓名+联系方式”；获准名单邮件通知；纸质签章要求待附件。</v>
+      </c>
+      <c r="R189" t="str" s="3">
+        <v>本人博士背景已知；具体机器人任务适用性、申请限项及合作要求未确认，未入首页。</v>
+      </c>
+      <c r="S189" t="str" s="3">
+        <v>取得DOCX指南与DOC申请书，先核是否有实际机器人/自主装备相关任务；若无则剔除。金额上限/窗口已核，成果、IP、经费外拨、合作与签章条件待核。四个平台联合一轮，非四条独立项目。</v>
+      </c>
+      <c r="T189" t="str" s="3">
+        <v>https://zhjz.nchu.edu.cn/tzgg/content_196076</v>
+      </c>
+      <c r="U189" t="str" s="3">
+        <v>https://zhjz.nchu.edu.cn/upload/zhjz/contentmanage/article/file/2026/09/22/2026%E5%BC%80%E6%94%BE%E5%9F%BA%E9%87%91%E8%AF%BE%E9%A2%98%E7%94%B3%E8%AF%B7%E6%8C%87%E5%8D%97.docx?t=1790052165233
+https://zhjz.nchu.edu.cn/upload/zhjz/contentmanage/article/file/2026/09/20/%E7%94%B3%E8%AF%B7%E4%B9%A62026.doc?t=1789902048581</v>
+      </c>
+      <c r="V189" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W189" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X189" t="str" s="3">
+        <v>任务证据不足，暂列待核；公告窗口2026-09-15—10-10。联合平台：智慧建筑工程中心、低空基础设施安全与韧性重点实验室、低空交通基础设施韧性建造与安全产业技术工程化中心、智慧建筑产业技术工程化中心。</v>
+      </c>
+      <c r="Y189" t="str" s="3">
+        <v>江西·南昌</v>
+      </c>
+      <c r="Z189" t="str" s="3">
+        <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
+      </c>
+      <c r="AA189" t="str" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -17493,6 +17656,8 @@
     <hyperlink ref="T185" ns1:id="rIdResume407"/>
     <hyperlink ref="T186" ns1:id="rIdResume408"/>
     <hyperlink ref="T187" ns1:id="rIdResume409"/>
+    <hyperlink ref="T188" ns1:id="rIdResume410"/>
+    <hyperlink ref="T189" ns1:id="rIdResume411"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -17967,7 +18132,7 @@
       </c>
       <c r="E21" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sklmqcm.um.edu.mo/skl-orpp/?lang=zh-hant
 https://skl-ammp.pku.edu.cn/info/1055/6288.htm
 https://iapme.um.edu.mo/orp-2026-guidelines/?lang=zh-hant
@@ -17978,10 +18143,10 @@
 https://www.ece.pku.edu.cn/info/1008/3124.htm</v>
       </c>
       <c r="F21" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G21" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H21" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18005,7 +18170,7 @@
       </c>
       <c r="E22" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.shanghaitech.edu.cn/2021/0816/c1482a70448/page.htm
 https://misc.sdu.edu.cn/info/1003/1438.htm
 https://www.shanghaitech.edu.cn/2026/0907/c1482a1126842/page.htm
@@ -18016,10 +18181,10 @@
 https://mae.shu.edu.cn/info/1013/1423.htm</v>
       </c>
       <c r="F22" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G22" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H22" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18076,7 +18241,7 @@
       </c>
       <c r="E24" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
 https://mip.ecnu.edu.cn/6a/ae/c2117a682670/page.htm
 https://shklmi.sumhs.edu.cn/74/98/c5705a291992/page.htm
@@ -18086,10 +18251,10 @@
 https://shkhrem.shanghaitech.edu.cn/_upload/article/files/ca/c3/de76c14241c58b966265ea227a22/41cc51cd-f516-4705-a198-2a23988ef022.pdf</v>
       </c>
       <c r="F24" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G24" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H24" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18113,7 +18278,7 @@
       </c>
       <c r="E25" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://imr.sjtu.edu.cn/
 https://www.shsmu.edu.cn/irm/
 https://www.shsmu.edu.cn/irm/info/1015/1801.htm
@@ -18124,10 +18289,10 @@
 https://imr.sjtu.edu.cn/kx_lwzl/3961.html</v>
       </c>
       <c r="F25" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G25" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H25" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18151,7 +18316,7 @@
       </c>
       <c r="E26" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://gmis.shu.edu.cn/ZSJZ/BS/2026/ShowMajor.php-ID%3D468.htm
 https://medicine.shu.edu.cn/info/1054/18157.htm
 https://www.control.sdu.edu.cn/info/1055/7158.htm
@@ -18162,10 +18327,10 @@
 https://gmis.shu.edu.cn/ZSJZ/BS/2022/ShowMajor.php-ID%3D241.htm</v>
       </c>
       <c r="F26" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G26" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H26" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18189,7 +18354,7 @@
       </c>
       <c r="E27" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://openinfo.shanghaitech.edu.cn/2025/0428/c158a1110564/page.htm
 https://www.shsmu.edu.cn/irm/info/1015/1801.htm
 https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
@@ -18200,10 +18365,10 @@
 https://www.shmtu.edu.cn/2025/1013/c12271a271820/page.htm</v>
       </c>
       <c r="F27" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G27" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H27" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18227,7 +18392,7 @@
       </c>
       <c r="E28" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.shanghaitech.edu.cn/2021/0816/c1482a70448/page.htm
 https://www.shanghaitech.edu.cn/2026/0907/c1482a1126842/page.htm
 https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
@@ -18238,10 +18403,10 @@
 https://www.shanghaitech.edu.cn/2025/0428/c1482a1110564/page.htm</v>
       </c>
       <c r="F28" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G28" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H28" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18362,7 +18527,7 @@
       </c>
       <c r="E32" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dgut.edu.cn/info/1023/67382.htm
 https://des.dgut.edu.cn/info/1072/1912.htm
 https://sail.dlut.edu.cn/kfjj/kfjjsqs.htm
@@ -18373,10 +18538,10 @@
 https://cas.dgut.edu.cn/home/Oauth/getToken/appid/kyxt.html）进行在线填报（纵向项目-项目申报-东莞市新型城镇融合发展研究院2020年度开放课题），如实填写项目的有关情况，不得弄虚作假，同时上传有关附件（申请书以及相关附件合并为一个PDF文件上传）。</v>
       </c>
       <c r="F32" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G32" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H32" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18458,7 +18623,7 @@
       </c>
       <c r="E35" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.sitp.ac.cn/ggtz/202605/t20260525_8209379.html
 https://www.sitp.ac.cn/ggtz/
 https://www.sitp.ac.cn/
@@ -18467,10 +18632,10 @@
 https://www.sitp.ac.cn/pic/dntdyys/</v>
       </c>
       <c r="F35" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G35" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H35" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18494,16 +18659,16 @@
       </c>
       <c r="E36" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sioc.cas.cn/sklcb/kfgx/kfkt/sqzn/202606/t20260630_8235628.html
 https://sioc.cas.cn/sklcb/kfgx/kfkt/sqzn/202507/t20250709_7883283.html
 https://www.sioc.cas.cn/sklcb/</v>
       </c>
       <c r="F36" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G36" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H36" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18527,14 +18692,14 @@
       </c>
       <c r="E37" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.sic.ac.cn/kybm/kybm2/kfjj/sqzn/</v>
       </c>
       <c r="F37" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G37" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H37" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18558,16 +18723,16 @@
       </c>
       <c r="E38" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.issas.ac.cn/
 https://www.issas.ac.cn/ydhz/ysjs/202405/P020240520520308613325.pdf
 https://www.issas.ac.cn/ydhz/ysjs/202307/P020230727571743371521.pdf</v>
       </c>
       <c r="F38" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G38" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H38" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18591,17 +18756,17 @@
       </c>
       <c r="E39" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.niglas.ac.cn/xwdt_1_1/zhxw/202205/t20220524_6453052.html
 https://niglas.ac.cn/jgsz2020/sys_2025/
 http://skl.niglas.ac.cn/
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm</v>
       </c>
       <c r="F39" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G39" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H39" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18625,16 +18790,16 @@
       </c>
       <c r="E40" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://rlab.sia.cas.cn/kfjj/glbf/
 https://rlab.sia.cas.cn/kfjj/sqbxz/
 https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html</v>
       </c>
       <c r="F40" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G40" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H40" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18658,15 +18823,15 @@
       </c>
       <c r="E41" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://www.niaot.ac.cn/czjf/ysjs/202508/P020250820629352136656.pdf</v>
       </c>
       <c r="F41" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G41" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H41" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18690,7 +18855,7 @@
       </c>
       <c r="E42" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.hfcas.ac.cn/lmjx/glbm/kyghc/kyc_kyghc/tzgg/202411/t20241106_7430643.html
 https://www.hfcas.ac.cn/tzygs/tzgg/index_2.html
 https://www.hfuu.edu.cn/kjc/74/ff/c11997a161023/page.htm
@@ -18701,10 +18866,10 @@
 https://wuli.iphy.ac.cn/en/article/pdf/preview/10.7693/wl20220208.pdf</v>
       </c>
       <c r="F42" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G42" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H42" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18728,17 +18893,17 @@
       </c>
       <c r="E43" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.ia.ac.cn/qtgn/tzgg/202505/t20250520_7788773.html
 https://www.sia.ac.cn/xwzx/tzgg/202507/t20250711_7884994.html
 https://www.ia.ac.cn/qtgn/tzgg/202404/t20240418_7122705.html
 https://www.ia.ac.cn/qtgn/tzgg/202305/t20230530_6765024.html</v>
       </c>
       <c r="F43" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G43" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H43" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18822,17 +18987,17 @@
       </c>
       <c r="E46" s="3" t="str">
         <v>已发现部分证据（仍非逐平台完成）：类器官2026历史指南
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.sinano.ac.cn/
 https://www.sinano.ac.cn/newsite/
 https://www.sinano.ac.cn/infogk/gkm/
 https://www.sinano.ac.cn/infogk/gkm/202512/P020250520608233397662.pdf</v>
       </c>
       <c r="F46" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G46" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H46" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18856,7 +19021,7 @@
       </c>
       <c r="E47" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sklnm.cpu.edu.cn/aa/f3/c13452a240371/page.htm
 https://gjc.cpu.edu.cn/_upload/article/files/de/ea/acc2b668422691f3caa22074fe53/88658561-c367-4995-965a-c76fb283c028.pdf
 https://sklnm.cpu.edu.cn/13452/listm.htm
@@ -18867,10 +19032,10 @@
 https://ist.cpu.edu.cn/tzgg/gjzrkxjj.htm</v>
       </c>
       <c r="F47" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G47" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H47" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18894,7 +19059,7 @@
       </c>
       <c r="E48" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://zssom.sysu.edu.cn/stemcells/sites/default/files/2025-09/2025%E5%B9%B4%E5%BA%A6%E5%BC%80%E6%94%BE%E7%A0%94%E7%A9%B6%E5%9F%BA%E9%87%91%E8%AF%BE%E9%A2%98%E7%94%B3%E8%AF%B7%E6%8C%87%E5%8D%97.pdf
 https://mse.sysu.edu.cn/article/3421
 https://cse.sysu.edu.cn/compsci/cn/cn02/36642.htm
@@ -18905,10 +19070,10 @@
 https://www.zdkqyy.com/sites/kqyy.prod.sysucloud1.sysu.edu.cn/files/2023-10/%EF%BC%882023%E7%89%88%EF%BC%89%E9%99%84%E4%BB%B61%EF%BC%9A2023%E5%B9%B4%E5%B9%BF%E4%B8%9C%E7%9C%81%E5%8F%A3%E8%85%94%E5%8C%BB%E5%AD%A6%E9%87%8D%E7%82%B9%E5%AE%9E%E9%AA%8C%E5%AE%A4%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98%E8%AF%A6%E7%BB%86%E7%94%B3%E6%8A%A5%E6%8C%87%E5%8D%97.pdf</v>
       </c>
       <c r="F48" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G48" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H48" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -18961,7 +19126,7 @@
       </c>
       <c r="E50" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://fo.bnbu.edu.cn/announcements.htm
 https://sjc.bnu.edu.cn/xwdt/xctt/d466817b66434b23bd913d5d1b542474.html
 https://sjc.bnu.edu.cn/xwdt/tzgg/1bf78b7b139f401eb6143be36618e787.html
@@ -18972,10 +19137,10 @@
 https://ctl.bnbu.edu.cn/virtual_attach_file.vsb?afc=DMzfsRnzCaLNWfnZ7UPnN78oR6RnR9bZL7CanNliM77PLNC0gihFp2hmCIa0M1yDMYyZL1hkL8lbnRLDLNUDLlVRnmUioRvYLR-iLzT7L8MFLN-ZL8laMRQFMzWRLR9Jv2nto4OPg1RTmWFNJ%2F4TJ-mwm-uTXHFTKqCxEqqQbK10bKIZbgYqbqSjbqDtE-2lbQk-bQJhEQtVbqDtEQt1bEYObg%2Flbp2HbXIQbp1-bXIQbqDtbC1pbXqabqSjEgIpbeJ2bC1Q547PLR9YMkbaQ2CeoDM8pkhXptQ0g47Poz-0LmL4MYbw62E8c&amp;e=.pdf&amp;nid=2337&amp;oid=1730746372&amp;tid=1192</v>
       </c>
       <c r="F50" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G50" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H50" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19057,7 +19222,7 @@
       </c>
       <c r="E53" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://kxyjy.scnu.edu.cn/a/20250507/164.html
 https://bchd.scnu.edu.cn/xueshuhuodong/kaifangketi/
 https://pfm.jxnu.edu.cn/kfjj/list.htm
@@ -19068,10 +19233,10 @@
 https://gis.ecnu.edu.cn/49484/list.htm</v>
       </c>
       <c r="F53" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G53" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H53" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19095,7 +19260,7 @@
       </c>
       <c r="E54" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://yxy.njucm.edu.cn/2026/0430/c2989a168259/page.htm
 https://wyxy.njucm.edu.cn/2025/1009/c1579a162069/page.htm
 https://kjc.njucm.edu.cn/2026/0603/c3816a169399/page.htm
@@ -19105,10 +19270,10 @@
 https://gra.njucm.edu.cn/_upload/article/files/ba/cd/5ce2b140491aba738020d3e46c45/b2fa0f2f-ba53-4a2f-b19c-e5306395b3bb.pdf</v>
       </c>
       <c r="F54" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G54" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H54" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19132,7 +19297,7 @@
       </c>
       <c r="E55" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.nsi.edu.cn/jw/63/b3/c583a91059/page.htm
 https://keysoftlab.nju.edu.cn/20/19/c1579a204825/page.htm
 https://keysoftlab.nju.edu.cn/1573/list.htm）下载并据实填写开放课题基金申请表，由所在单位审批同意、领导签署意见并加盖公章后，请于2025年4月30日前将申请表寄回南京大学计算机软件新技术全国重点实验室（电子版1份、纸质版2份）。
@@ -19143,10 +19308,10 @@
 https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm</v>
       </c>
       <c r="F55" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G55" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H55" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19170,7 +19335,7 @@
       </c>
       <c r="E56" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://ai.njau.edu.cn/info/1010/4407.htm
 https://graschgzb.njau.edu.cn/info/1152/9273.htm
 https://coe.njau.edu.cn/info/1019/5581.htm
@@ -19181,10 +19346,10 @@
 https://ai.njau.edu.cn/info/1134/2528.htm</v>
       </c>
       <c r="F56" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G56" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H56" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19273,7 +19438,7 @@
       </c>
       <c r="E59" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.naujsc.edu.cn/2023/0625/c293a12894/page.htm
 https://jlsf.nau.edu.cn/2025/0902/c11247a147134/page.htm
 https://www.nau.edu.cn/2026/0827/c5728a161022/page.htm
@@ -19284,10 +19449,10 @@
 https://cse.seu.edu.cn/edulab/22981/list.htm</v>
       </c>
       <c r="F59" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G59" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H59" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19340,7 +19505,7 @@
       </c>
       <c r="E61" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.njit.edu.cn/info/1043/21696.htm
 https://www.njit.edu.cn/info/1043/19187.htm
 https://www.njit.edu.cn/info/1043/18230.htm
@@ -19351,10 +19516,10 @@
 https://sie.njit.edu.cn/__local/2/37/E3/E48E2CE34448DA175460A9F233C_B887BE63_26EE4D.pdf</v>
       </c>
       <c r="F61" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G61" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H61" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19378,7 +19543,7 @@
       </c>
       <c r="E62" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://automation.seu.edu.cn/mccse/2021/0604/c33959a373840/page.htm
 https://cee.ahpu.edu.cn/lapic/kfkt/list.htm
 https://lib.njnu.edu.cn/f/yxbkbylw/%E5%8D%97%E4%BA%AC%E5%B8%88%E8%8C%83%E5%A4%A7%E5%AD%A6%E6%9C%AC%E7%A7%91%E7%94%9F%E7%9C%81%E7%BA%A7%E4%BC%98%E7%A7%80%E6%AF%95%E4%B8%9A%E4%BD%9C%E5%93%81%E6%B1%87%E7%BC%96%EF%BC%882024%E5%8D%B7%EF%BC%89.pdf
@@ -19389,10 +19554,10 @@
 https://sklcc.nju.edu.cn/kfjl/zzkt/20250126/i308478.html</v>
       </c>
       <c r="F62" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G62" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H62" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19416,7 +19581,7 @@
       </c>
       <c r="E63" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://automation.seu.edu.cn/mccse/2021/0605/c33989a373924/page.psp
 https://xxgk.njfu.edu.cn/DFS/file/2018/09/30/20180930092751426izgmbx.pdf
 https://jidian.njfu.edu.cn/szdw/js2617/20250901/i343071.html
@@ -19427,10 +19592,10 @@
 https://jidian.njfu.edu.cn/szdw/fjs/20211104/i244357.html</v>
       </c>
       <c r="F63" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G63" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H63" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19454,7 +19619,7 @@
       </c>
       <c r="E64" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sie.njust.edu.cn/_upload/article/files/2a/9e/b929e7634d7d9bdbf8cdb7782ffc/d76527b9-c71c-4e28-a8c9-8035a83090d2.pdf
 https://sie.njust.edu.cn/_upload/article/files/f6/25/315a06784d12bc99b43538a29d6b/a1c730c2-043c-42fd-aa71-d488884aba74.pdf
 https://teacher.njust.edu.cn/zdh/zh/list.htm
@@ -19465,10 +19630,10 @@
 https://teacher.njust.edu.cn/jxgc/zxl/list.htm</v>
       </c>
       <c r="F64" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G64" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H64" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19554,7 +19719,7 @@
       </c>
       <c r="E67" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://jwc.nufe.edu.cn/info/1031/18286.htm
 https://jwc.nufe.edu.cn/info/1024/18183.htm
 https://jwc.nufe.edu.cn/info/1024/18329.htm
@@ -19565,10 +19730,10 @@
 https://www.nufe.edu.cn/info/1057/15871.htm</v>
       </c>
       <c r="F67" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G67" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H67" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19621,7 +19786,7 @@
       </c>
       <c r="E69" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sklmcb.nankai.edu.cn/kfkt1/list5.htm
 https://jwc.gpnu.edu.cn/__local/9/C9/F1/4D4EFB64F94C0B5213889DB5F9E_D5C04A25_534DB9.pdf
 https://ahmu-derm.ahmu.edu.cn/kfkt/list.htm
@@ -19632,10 +19797,10 @@
 https://mt.njmu.edu.cn/16032/list.htm</v>
       </c>
       <c r="F69" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G69" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H69" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19688,7 +19853,7 @@
       </c>
       <c r="E71" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://faculty.hfut.edu.cn/index.jsp
 https://faculty.hfut.edu.cn/yj1234/zh_CN/index.htm
 https://sail.dlut.edu.cn/info/1361/8331.htm
@@ -19699,10 +19864,10 @@
 https://www.hfut.edu.cn/znhlahssys/info/1017/1191.htm</v>
       </c>
       <c r="F71" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G71" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H71" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19726,17 +19891,17 @@
       </c>
       <c r="E72" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.iim.ac.cn/xxzx/xmtz/index_4.html
 https://www.iim.ac.cn/
 https://www.iim.ac.cn/cgzh/
 https://kjc.ahpu.edu.cn/_t41/2025/0728/c731a252845/page.psp</v>
       </c>
       <c r="F72" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G72" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H72" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19884,7 +20049,7 @@
       </c>
       <c r="E77" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://aimlab.ahmu.edu.cn/2026/0908/c6737a203817/page.htm
 https://aimlab.ahmu.edu.cn/4027/list.htm
 https://biopreserv.ahmu.edu.cn/2025/0823/c9513a189925/page.htm
@@ -19895,10 +20060,10 @@
 https://jjh.ahmu.edu.cn/upload/file/20230610012552_84c0a279-c5a8-4cf2-a793-418c089670b8.pdf</v>
       </c>
       <c r="F77" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G77" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H77" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19922,7 +20087,7 @@
       </c>
       <c r="E78" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.hfuu.edu.cn/kjc/74/ff/c11997a161023/page.htm
 https://sai.ahu.edu.cn/kfkt/list.htm
 https://sai.ahu.edu.cn/kfjl/list.htm
@@ -19933,10 +20098,10 @@
 https://dnzlgczx.ahu.edu.cn/_upload/article/files/9d/80/08689d4c4aceba2750f7b4dea85e/54935d47-22a1-4275-8935-40315afcf86d.pdf</v>
       </c>
       <c r="F78" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G78" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H78" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -19960,7 +20125,7 @@
       </c>
       <c r="E79" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://keysoftlab.nju.edu.cn/1573/list.htm
 https://keysoftlab.nju.edu.cn/1611/list.htm）下载并据实填写开放课题基金申请表，由所在单位审批同意、领导签署意见并加盖公章后，请于2026年4月30日前将申请表寄回南京大学计算机软件新技术全国重点实验室（电子版1份、纸质版2份）。
 https://soillab.zju.edu.cn/2026/0810/c86548a3194243/page.htm
@@ -19971,10 +20136,10 @@
 https://kyy.nuaa.edu.cn/2026/0604/c5817a400921/page.htm</v>
       </c>
       <c r="F79" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G79" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H79" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20027,7 +20192,7 @@
       </c>
       <c r="E81" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://iimt.cczu.edu.cn/2026/0519/c22023a415871/page.htm
 https://automation.seu.edu.cn/2022/0215/c24460a398708/page.htm
@@ -20036,10 +20201,10 @@
 https://iimt.cczu.edu.cn/_upload/article/files/66/cf/d34982dd443fadb6643895fc49a6/fa8ee5aa-6fe2-479c-9f00-98c2fcb0d0b0.pdf</v>
       </c>
       <c r="F81" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G81" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H81" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20063,7 +20228,7 @@
       </c>
       <c r="E82" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
 https://automation.seu.edu.cn/mccse/2021/0605/c33989a373924/page.htm
 https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
@@ -20074,10 +20239,10 @@
 https://dqxylib.szut.edu.cn/info/1016/27682.htm</v>
       </c>
       <c r="F82" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G82" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H82" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20101,7 +20266,7 @@
       </c>
       <c r="E83" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://teacher.gdut.edu.cn/zhang_hao/en/kyxm/216002/list/index.htm
 https://teacher.gdut.edu.cn/huangguoheng/zh_CN/kyxm/130673/list/index.htm
 https://jdgcxy.gdut.edu.cn/info/1086/4035.htm
@@ -20112,10 +20277,10 @@
 https://jdis.gdut.edu.cn/wdzweb/newslist.aspx?ctx=D3A2BB5708F1AD9028B1F36CBD048A37</v>
       </c>
       <c r="F83" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G83" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H83" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20139,7 +20304,7 @@
       </c>
       <c r="E84" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://znfs.siat.ac.cn/index.php?id=257&amp;r=mobile%2Fpage%2Fshow&amp;type=5
 https://znfs.siat.ac.cn/index.php?category_id=0&amp;id=280&amp;r=page%2Fshow&amp;type=5
 https://znfs.siat.ac.cn/index.php?category_id=0&amp;id=269&amp;r=page%2Fshow&amp;type=5
@@ -20150,10 +20315,10 @@
 https://www.gml.ac.cn/xxgs/973.html</v>
       </c>
       <c r="F84" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G84" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H84" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20177,7 +20342,7 @@
       </c>
       <c r="E85" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.giec.ac.cn/tzgg2016/202411/t20241115_7440542.html
 https://sites.gtiit.edu.cn/matec/open-fund/
 https://ipt.jnu.edu.cn/ofsc/36317/list.htm
@@ -20188,10 +20353,10 @@
 https://irads.bnbu.edu.cn/project_application/open_funding/pro.htm</v>
       </c>
       <c r="F85" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G85" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H85" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20215,7 +20380,7 @@
       </c>
       <c r="E86" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://stemlab.gibh.ac.cn/hzjl/kfkt/
 https://yxy.gzhmu.edu.cn/info/1052/8545.htm
 https://yxy.gzhmu.edu.cn/info/1052/3965.htm
@@ -20226,10 +20391,10 @@
 https://yxy.gzhmu.edu.cn/info/1051/8595.htm</v>
       </c>
       <c r="F86" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G86" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H86" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20253,7 +20418,7 @@
       </c>
       <c r="E87" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://eertc.gzhu.edu.cn/info/1192/8809.htm
 https://fcc.gzu.edu.cn/2026/0320/c4450a266319/page.htm
 https://ai.gzhu.edu.cn/info/1200/1742.htm
@@ -20264,10 +20429,10 @@
 https://yjsy.gzhu.edu.cn/info/1038/109201.htm</v>
       </c>
       <c r="F87" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G87" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H87" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20291,7 +20456,7 @@
       </c>
       <c r="E88" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cee.ahpu.edu.cn/lapic/kfkt/list.htm
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://digimed.seu.edu.cn/2025/0226/c18440a519564/page.htm
@@ -20302,10 +20467,10 @@
 https://aiia.seu.edu.cn/2023/1016/c50239a468618/page.htm</v>
       </c>
       <c r="F88" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G88" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H88" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20329,7 +20494,7 @@
       </c>
       <c r="E89" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://robot.hit.edu.cn/2022/1018/c338a282555/page.htm
@@ -20340,10 +20505,10 @@
 https://www.control.sdu.edu.cn/info/1055/7158.htm</v>
       </c>
       <c r="F89" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G89" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H89" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20367,7 +20532,7 @@
       </c>
       <c r="E90" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://automation.seu.edu.cn/2022/0215/c24460a398708/page.htm
@@ -20378,10 +20543,10 @@
 https://zdhxy.cwxu.edu.cn/info/1162/2676.htm</v>
       </c>
       <c r="F90" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G90" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H90" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20405,7 +20570,7 @@
       </c>
       <c r="E91" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cse.seu.edu.cn/edulab/22981/list.htm
 https://keysoftlab.nju.edu.cn/1573/list.htm
 https://keysoftlab.nju.edu.cn/1611/list.htm）下载并据实填写开放课题基金申请表，由所在单位审批同意、领导签署意见并加盖公章后，请于2026年4月30日前将申请表寄回南京大学计算机软件新技术全国重点实验室（电子版1份、纸质版2份）。
@@ -20416,10 +20581,10 @@
 https://jnumed.jnu.edu.cn/2025/0710/c7380a840301/page.htm</v>
       </c>
       <c r="F91" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G91" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H91" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20443,7 +20608,7 @@
       </c>
       <c r="E92" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://kyc.hznu.edu.cn/c/2026-04-03/3186880.shtml
 https://zjyjg.hznu.edu.cn/c/2017-04-05/1659180.shtml
 https://kyc.hznu.edu.cn/xbwz/xmsb/rwsk/index_3.shtml
@@ -20454,10 +20619,10 @@
 https://yjg.hznu.edu.cn/c/2017-04-05/1659205.shtml</v>
       </c>
       <c r="F92" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G92" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H92" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20481,7 +20646,7 @@
       </c>
       <c r="E93" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cabri.hdu.edu.cn/main.htm
 https://cs.seu.edu.cn/edulab/2026/0507/c68203a566776/page.htm
 https://cs.seu.edu.cn/edulab/main.htm）下载并填写开放基金课题申请书，由所在单位签署意见并加盖公章后，将申请表寄回东南大学计算机网络和信息集成教育部重点实验室（需提交一份电子版，三份纸质版本）。
@@ -20492,10 +20657,10 @@
 https://www.htu.edu.cn/hnsgdcgjcyy/kfkt/list.psp</v>
       </c>
       <c r="F93" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G93" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H93" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20519,16 +20684,16 @@
       </c>
       <c r="E94" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sslab.org.cn/uploads/%E9%80%9A%E7%9F%A5%E5%85%AC%E5%91%8A/2024/%E6%98%BE%E5%BE%AE%E7%A7%91%E5%AD%A6%E6%8A%80%E6%9C%AF%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98%E7%94%B3%E8%AF%B7%E6%8C%87%E5%8D%97/%E9%99%84%E4%BB%B63%E6%9D%BE%E5%B1%B1%E6%B9%96%E7%A7%91%E5%AD%A6%E5%9F%8E%E6%98%BE%E5%BE%AE%E7%A7%91%E5%AD%A6%E4%B8%8E%E6%8A%80%E6%9C%AF%E5%BC%80%E6%94%BE%E5%9F%BA%E9%87%91%E8%AF%BE%E9%A2%98%E7%AE%A1%E7%90%86%E5%8A%9E%E6%B3%95%EF%BC%88%E8%AF%95%E8%A1%8C%EF%BC%89.pdf
 https://www.sslab.org.cn/news/noticedetail?id=24101115263846816E759E69C
 https://www.sslab.org.cn/uploads/%E6%96%B0%E9%97%BB%E5%8A%A8%E6%80%81/2022%E5%B9%B4%E9%83%BD%E6%94%BE%E8%BF%99%E9%87%8C%EF%BC%81%EF%BC%81%EF%BC%81/20220630%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98/%E9%99%84%E4%BB%B6-%E6%9D%BE%E5%B1%B1%E6%B9%96%E6%9D%90%E6%96%99%E5%AE%9E%E9%AA%8C%E5%AE%A42022%E5%B9%B4%E5%BA%A6%E6%8B%9F%E7%AB%8B%E9%A1%B9%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98%E6%B8%85%E5%8D%95.pdf</v>
       </c>
       <c r="F94" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G94" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H94" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20583,7 +20748,7 @@
       </c>
       <c r="E96" s="3" t="str">
         <v>已发现部分证据（仍非逐平台完成）：检验医学重点实验室2026项目公布记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://automation.seu.edu.cn/_upload/article/files/e3/73/0e15ce584036a5f4e0ae7a3e8245/b46125c5-7868-4c52-99f9-f5ad9a961721.pdf
@@ -20594,10 +20759,10 @@
 https://scit.nju.edu.cn/35/a9/c10916a538025/page.htm</v>
       </c>
       <c r="F96" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G96" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H96" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20621,7 +20786,7 @@
       </c>
       <c r="E97" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://automation.seu.edu.cn/mccse/2021/0605/c33989a373924/page.psp
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://kjc.squ.edu.cn/info/1008/2302.htm
@@ -20632,10 +20797,10 @@
 https://automation.seu.edu.cn/_upload/article/files/e3/73/0e15ce584036a5f4e0ae7a3e8245/b46125c5-7868-4c52-99f9-f5ad9a961721.pdf</v>
       </c>
       <c r="F97" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G97" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H97" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20659,7 +20824,7 @@
       </c>
       <c r="E98" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://kjc.squ.edu.cn/info/1008/2141.htm
 https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
@@ -20669,10 +20834,10 @@
 https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm</v>
       </c>
       <c r="F98" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G98" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H98" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20696,7 +20861,7 @@
       </c>
       <c r="E99" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://kjc.squ.edu.cn/info/1008/2302.htm
 https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
@@ -20704,10 +20869,10 @@
 https://mps.seu.edu.cn/2024/0820/c54962a500192/page.htm</v>
       </c>
       <c r="F99" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G99" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H99" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20731,7 +20896,7 @@
       </c>
       <c r="E100" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://automation.seu.edu.cn/mccse/2021/0605/c33989a373924/page.htm
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://kjc.squ.edu.cn/info/1008/2302.htm
@@ -20742,10 +20907,10 @@
 https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp</v>
       </c>
       <c r="F100" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G100" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H100" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20769,7 +20934,7 @@
       </c>
       <c r="E101" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://water-center.hhu.edu.cn/_upload/article/files/0b/82/0241efcb4f94afddd0d5a2f8d300/1b6af828-a98f-4824-803f-abae698a6abf.pdf
 https://jidian.hhu.edu.cn/zzjg_18302/list.htm
 https://hhusz.hhu.edu.cn/2026/0506/c26542a326097/page.htm
@@ -20780,10 +20945,10 @@
 https://hydro-lab.hhu.edu.cn/jin.asp</v>
       </c>
       <c r="F101" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G101" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H101" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20840,7 +21005,7 @@
       </c>
       <c r="E103" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sklict.zju.edu.cn/_upload/article/files/5d/0a/a43000ae4b8a8628f03f2bdc8307/be490fc1-e1fe-45ae-b0ec-33ac7019d56f.pdf
 https://enr.zust.edu.cn/info/1048/4312.htm
 https://enr.zust.edu.cn/info/1048/3923.htm
@@ -20851,10 +21016,10 @@
 https://ie.zjut.edu.cn/xxgcxy/ueditor/jsp/upload/file/20230217/1676614625458053991.pdf</v>
       </c>
       <c r="F103" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G103" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H103" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -20907,7 +21072,7 @@
       </c>
       <c r="E105" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://medimaging.siat.ac.cn/
 https://imm.ac.cn/tz/tzgg/4b39a8ea6dbf4029af869ff966ad5aab.htm
 https://medimaging.siat.ac.cn/cxqjzx/bianlab/research/
@@ -20915,10 +21080,10 @@
 https://phs.sysu.edu.cn/sites/default/files/2024-09/2.%20%E6%B7%B1%E5%9C%B3%E5%8C%BB%E5%AD%A6%E7%A7%91%E5%AD%A6%E9%99%A2%E5%85%B3%E4%BA%8E%E5%85%AC%E5%BC%802023%E5%B9%B4%E5%BA%A6%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8C%BB%E5%AD%A6%E7%A0%94%E7%A9%B6%E4%B8%93%E9%A1%B9%E8%B5%84%E9%87%91%E8%B5%84%E5%8A%A9%E9%A1%B9%E7%9B%AE%E7%9A%84%E9%80%9A%E7%9F%A5.pdf</v>
       </c>
       <c r="F105" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G105" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H105" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21000,7 +21165,7 @@
       </c>
       <c r="E108" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://liff-lab.szbl.ac.cn/
 https://zhouyq-lab.szbl.ac.cn/
 https://www.szbl.ac.cn/
@@ -21011,10 +21176,10 @@
 https://huangkai-lab.szbl.ac.cn/</v>
       </c>
       <c r="F108" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G108" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H108" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21038,7 +21203,7 @@
       </c>
       <c r="E109" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.csust.edu.cn/rwshkx/info/1116/11290.htm
 https://media-sec.szu.edu.cn/kfjj/a2025nkfjjktsqzn.htm
 https://science.sustech.edu.cn/portal/article/index/id/1573
@@ -21049,10 +21214,10 @@
 https://media-sec.szu.edu.cn/kfjj/a2022nkfjjktsqzn.htm</v>
       </c>
       <c r="F109" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G109" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H109" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21076,7 +21241,7 @@
       </c>
       <c r="E110" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://bm.cugb.edu.cn/gpmr/c/2026-05-29/851486.shtml
 https://ofcl.pku.edu.cn/info/1006/3502.htm
 https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261025/page.psp
@@ -21087,10 +21252,10 @@
 https://sklmqcm.um.edu.mo/wp-content/uploads/2024/02/%E4%B8%AD%E8%97%A5%E8%B3%AA%E9%87%8F%E7%A0%94%E7%A9%B6%E5%9C%8B%E5%AE%B6%E9%87%8D%E9%BB%9E%E5%AF%A6%E9%A9%97%E5%AE%A4%E9%96%8B%E6%94%BE%E8%AA%B2%E9%A1%8C%E7%94%B3%E8%AB%8B%E6%8C%87%E5%8D%972024.pdf</v>
       </c>
       <c r="F110" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G110" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H110" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21114,7 +21279,7 @@
       </c>
       <c r="E111" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://iapme.um.edu.mo/orp-2026-guidelines/?lang=zh-hant
 https://iapme.um.edu.mo/orp-2026-management/?lang=zh-hant
 https://www.polyu.edu.hk/sklumt/open-research-project/call-for-application/?sc_lang=tc
@@ -21122,10 +21287,10 @@
 https://www.csust.edu.cn/rwshkx/info/1116/11290.htm</v>
       </c>
       <c r="F111" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G111" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H111" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21178,17 +21343,17 @@
       </c>
       <c r="E113" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://ofcl.pku.edu.cn/info/1006/3502.htm
 https://sklmrsi.apm.ac.cn/kfjl/kfkt/202604/t20260424_835102.html
 https://klais.ict.ac.cn/tzgg/xmzj/202609/t20260908_856264.html
 https://imet.hust.edu.cn/info/1031/2733.htm</v>
       </c>
       <c r="F113" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G113" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H113" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21272,7 +21437,7 @@
       </c>
       <c r="E116" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
 https://automation.seu.edu.cn/2024/0320/c24460a484504/page.htm
@@ -21282,10 +21447,10 @@
 https://www.lit.edu.cn/kyc/info/1074/16874.htm</v>
       </c>
       <c r="F116" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G116" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H116" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21338,7 +21503,7 @@
       </c>
       <c r="E118" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://dqxylib.szut.edu.cn/info/1016/27682.htm
 https://automation.seu.edu.cn/mccse/2021/0605/c33989a373924/page.htm
 https://www.control.sdu.edu.cn/info/1055/7158.htm
@@ -21349,10 +21514,10 @@
 https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp</v>
       </c>
       <c r="F118" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G118" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H118" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21376,7 +21541,7 @@
       </c>
       <c r="E119" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://soillab.zju.edu.cn/kfjj/list.htm
 https://klab.xhu.edu.cn/9e/eb/c2100a237291/page.htm
 https://klab.xhu.edu.cn/64/20/c2100a222240/page.htm
@@ -21387,10 +21552,10 @@
 https://cidr.westlake.edu.cn/NewsEvents/News/202507/t20250717_56778.html</v>
       </c>
       <c r="F119" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G119" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H119" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21414,7 +21579,7 @@
       </c>
       <c r="E120" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cuhk.edu.cn/zh-hans/article/15611
 https://cuhk.edu.cn/zh-hans/article/17530
 https://pts.jhun.edu.cn/73/e8/c5452a226280/pagem.htm
@@ -21423,10 +21588,10 @@
 https://aia.hust.edu.cn/info/1174/11568.htm</v>
       </c>
       <c r="F120" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G120" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H120" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21450,16 +21615,16 @@
       </c>
       <c r="E121" s="3" t="str">
         <v>已发现部分证据（仍非逐平台完成）：关联AIRS医疗机器人2026历史开放
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cuhk.edu.cn/zh-hans/article/17530
 https://cuhk.edu.cn/zh-hans/article/15611
 https://math4ai.cuhk.edu.cn/page/24</v>
       </c>
       <c r="F121" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G121" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H121" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21483,7 +21648,7 @@
       </c>
       <c r="E122" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261025/page.psp
 https://ofcl.pku.edu.cn/info/1006/3502.htm
 https://www.hgu.edu.cn/info/1050/11853.htm
@@ -21491,10 +21656,10 @@
 https://bigdata.ecnu.edu.cn/ee/2e/c43524a781870/page.htm</v>
       </c>
       <c r="F122" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G122" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H122" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21518,7 +21683,7 @@
       </c>
       <c r="E123" s="3" t="str">
         <v>已发现部分证据（仍非逐平台完成）：合成化学全重公开合作机制，2026结果已出
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://aia.hust.edu.cn/info/1174/11568.htm
 https://pts.jhun.edu.cn/73/e8/c5452a226280/pagem.htm
 https://jdcad.jhun.edu.cn/8e/7b/c7392a233083/page.htm
@@ -21529,10 +21694,10 @@
 https://civil.hit.edu.cn/2026/0828/c8439a400176/page.htm</v>
       </c>
       <c r="F123" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G123" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H123" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21556,16 +21721,16 @@
       </c>
       <c r="E124" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.astri.org/sc
 https://www.astri.org/tc
 https://www.astri.org/</v>
       </c>
       <c r="F124" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G124" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H124" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21589,16 +21754,16 @@
       </c>
       <c r="E125" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cs.seu.edu.cn/edulab/2026/0507/c68203a566776/page.htm
 https://etcc.seu.edu.cn/2026/0428/c7052a566005/page.htm
 https://fao.shiep.edu.cn/_upload/article/files/9e/68/9ffc7bb64c86a0c1d3c7c4ca67e0/a4420a94-2b8d-4604-87cb-c022818240fd.pdf</v>
       </c>
       <c r="F125" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G125" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H125" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21622,7 +21787,7 @@
       </c>
       <c r="E126" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://aia.hust.edu.cn/info/1174/11568.htm
 https://ihperrl.hbut.edu.cn/kfjj/kfktzn.htm
 https://pts.jhun.edu.cn/73/e8/c5452a226280/pagem.htm
@@ -21630,10 +21795,10 @@
 https://jdcad.jhun.edu.cn/8e/7b/c7392a233083/page.htm</v>
       </c>
       <c r="F126" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G126" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H126" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21657,16 +21822,16 @@
       </c>
       <c r="E127" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.polyu.edu.hk/sklumt/open-research-project/call-for-application/?sc_lang=tc
 https://www.polyu.edu.hk/kteo/entrepreneurship/funding_investment/polyu-micro-fund-scheme/?sc_lang=sc
 https://www.polyu.edu.hk/kteo/about-kteo/news-and-events/events/2026/09/micro-fund-briefing/?sc_lang=sc</v>
       </c>
       <c r="F127" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G127" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H127" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21690,7 +21855,7 @@
       </c>
       <c r="E128" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://klais.ict.ac.cn/tzgg/xmzj/202609/t20260908_856264.html
 https://aia.hust.edu.cn/info/1174/11568.htm
 https://enr.zust.edu.cn/info/1048/4312.htm
@@ -21698,10 +21863,10 @@
 https://ncms.ustb.edu.cn/kycx/zxxx/a97d75e5a5fa4ccb9746953d07fdc287.htm</v>
       </c>
       <c r="F128" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G128" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H128" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21725,7 +21890,7 @@
       </c>
       <c r="E129" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.hkust-gz.edu.cn/zh/2026/03/20/%E6%95%99%E8%82%B2%E9%83%A8%E7%AE%80%E6%8A%A5%EF%BC%9A%E9%A6%99%E6%B8%AF%E7%A7%91%E6%8A%80%E5%A4%A7%E5%AD%A6%EF%BC%88%E5%B9%BF%E5%B7%9E%EF%BC%89%E4%BB%A5%E8%9E%8D%E5%90%88%E5%88%9B%E6%96%B0%E7%94%9F/
 https://www.gml.ac.cn/xxgs/973.html
 https://rd.hkust-gz.edu.cn/2023/10/%E9%A6%99%E6%B8%AF%E7%A7%91%E6%8A%80%E5%A4%A7%E5%AD%A6-%E9%A6%99%E6%B8%AF%E7%A7%91%E6%8A%80%E5%A4%A7%E5%AD%A6%EF%BC%88%E5%B9%BF%E5%B7%9E%EF%BC%8920-20%E4%B8%A4%E6%A0%A1%E8%81%94%E5%90%88%E7%A0%94/
@@ -21733,10 +21898,10 @@
 https://science.sustech.edu.cn/portal/article/index/id/1573</v>
       </c>
       <c r="F129" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G129" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H129" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21760,7 +21925,7 @@
       </c>
       <c r="E130" s="3" t="str">
         <v>待逐平台核查；不得标记为无公开项目
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://www.pcl.ac.cn/html/943/2024-10-23/content-4517.html
 https://pcl.ac.cn/
 https://pcl.ac.cn/html/935/
@@ -21771,10 +21936,10 @@
 https://www.pkusz.edu.cn/info/1058/6435.htm</v>
       </c>
       <c r="F130" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G130" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H130" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21798,7 +21963,7 @@
       </c>
       <c r="E131" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sail.dlut.edu.cn/info/1361/9202.htm
 https://faculty.neu.edu.cn/niudapeng/en/kyxm/30582/list/index.htm
 https://idme.neu.edu.cn/2026/0416/c10682a452524/page.htm
@@ -21809,10 +21974,10 @@
 https://www.ral.neu.edu.cn/4389/listm.htm</v>
       </c>
       <c r="F131" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G131" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H131" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21836,7 +22001,7 @@
       </c>
       <c r="E132" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://sklpm.csu.edu.cn/info/1028/1442.htm
 https://gip.csu.edu.cn/info/1381/8673.htm
 https://bs.csu.edu.cn/info/1045/27017.htm
@@ -21847,10 +22012,10 @@
 https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261025/page.psp</v>
       </c>
       <c r="F132" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G132" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H132" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21874,7 +22039,7 @@
       </c>
       <c r="E133" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://se-office.ruc.edu.cn/xwdt/830f65554d20442f8054e1d9bc50f283.htm
 https://se-office.ruc.edu.cn/xwdt/c8181f7ee330421fb73a39c1e56f52c0.htm
 https://bm.cugb.edu.cn/gpmr/c/2026-05-29/851486.shtml
@@ -21885,10 +22050,10 @@
 https://blasting.jhun.edu.cn/7a/87/c5648a227975/pagem.htm</v>
       </c>
       <c r="F133" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G133" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H133" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21912,7 +22077,7 @@
       </c>
       <c r="E134" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://cvm.cau.edu.cn/art/2026/1/26/art_41943_1097971.html
 https://cbs.cau.edu.cn/art/2026/4/13/art_21772_1107390.html
 https://scxy.ouc.edu.cn/lanf/2026/0828/c18906a536068/page.htm
@@ -21923,10 +22088,10 @@
 https://cvm.cau.edu.cn/art/2025/11/3/art_41942_1087868.html</v>
       </c>
       <c r="F134" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G134" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H134" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21950,7 +22115,7 @@
       </c>
       <c r="E135" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://scxy.ouc.edu.cn/lanf/2026/0828/c18906a536068/page.htm
 https://slcoe.dlut.edu.cn/info/1076/4892.htm
 https://www.qdhhc.edu.cn/mb/4/p_detail.aspx?id=63080&amp;wsId=28
@@ -21961,10 +22126,10 @@
 https://ocean.upc.edu.cn/2026/0424/c15098a488720/page.htm</v>
       </c>
       <c r="F135" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G135" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H135" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -21988,7 +22153,7 @@
       </c>
       <c r="E136" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://yxy.muc.edu.cn/zdsys/kfjl1.htm
 https://mzyy.muc.edu.cn/info/1091/3027.htm
 https://pupc.ccnu.edu.cn/info/1010/1125.htm
@@ -21999,10 +22164,10 @@
 https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261025/page.psp</v>
       </c>
       <c r="F136" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G136" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H136" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22026,7 +22191,7 @@
       </c>
       <c r="E137" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://vphs.cau.edu.cn/art/2026/1/26/art_54622_1110903.html
 https://cwc.lzu.edu.cn/cwcnew/upload/files/20260423/85a60ff6a43045e09cc73b442c391f91.pdf
 https://keylab.lzu.edu.cn/keylab/upload/files/20251218/d047823df7ee4789b8d971410f961627.pdf
@@ -22037,10 +22202,10 @@
 https://keylab.lzu.edu.cn/keylab/upload/files/20251224/f23379faa7124f35a1064d7f9bcbaf30.pdf</v>
       </c>
       <c r="F137" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G137" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H137" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22093,7 +22258,7 @@
       </c>
       <c r="E139" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://bsee.bnu.edu.cn/xwzx/tzgg/ea9d567283c44f0da77b671189b4cfd4.htm
 https://espdrr.bnu.edu.cn/kfjl/kfkt/index.htm
 https://aic-fe.bnu.edu.cn/xwdt/ztdtrky/szhzkt/zktkfsqzn/index.html
@@ -22104,10 +22269,10 @@
 https://jsgzb.bnu.edu.cn/tzgg/43626a012b08411dac6cc8c990e6fa81.html</v>
       </c>
       <c r="F139" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G139" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H139" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22224,7 +22389,7 @@
       </c>
       <c r="E143" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://env.nankai.edu.cn/ppe/2026/0413/c15695a592863/page.htm
 https://sklmcb.nankai.edu.cn/kfkt1/list.htm
 https://skleoc.nankai.edu.cn/kfjj.htm
@@ -22235,10 +22400,10 @@
 https://std.nankai.edu.cn/37965/list.htm</v>
       </c>
       <c r="F143" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G143" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H143" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22388,7 +22553,7 @@
       </c>
       <c r="E148" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://research.dhu.edu.cn/2025/0715/c6973a363885/page.htm
 https://ncms.ustb.edu.cn/kycx/zxxx/a97d75e5a5fa4ccb9746953d07fdc287.htm
 https://www.nudt.edu.cn/press/gywm/fd21dd4caee548b9b37c082de20fa8ef.htm
@@ -22399,10 +22564,10 @@
 https://klais.ict.ac.cn/tzgg/xmzj/202609/t20260908_856264.html</v>
       </c>
       <c r="F148" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G148" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H148" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22484,7 +22649,7 @@
       </c>
       <c r="E151" s="3" t="str">
         <v>已发现至少一条历史公告线索；仍未完成校内全部相关平台检查
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://irsmp.sdu.edu.cn/info/1057/1917.htm
 https://www.huanke.sdu.edu.cn/info/1152/7395.htm
 https://mbtechinst.qd.sdu.edu.cn/info/1075/11213.htm
@@ -22495,10 +22660,10 @@
 https://sklcm.sdu.edu.cn/</v>
       </c>
       <c r="F151" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G151" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H151" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22522,7 +22687,7 @@
       </c>
       <c r="E152" s="3" t="str">
         <v>本轮仅作限定关键词定向网站搜索，未找到可确认当期开放基金；仍未完成平台检查
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://pole.whu.edu.cn/cn/news/139270.html
 https://aia.hust.edu.cn/info/1174/11568.htm
 https://wnlo.hust.edu.cn/kxyj/kfkt.htm
@@ -22533,10 +22698,10 @@
 https://mse.xhu.edu.cn/_t316/b6/b3/c810a243379/page.htm</v>
       </c>
       <c r="F152" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G152" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H152" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -22651,7 +22816,7 @@
       </c>
       <c r="E156" s="3" t="str">
         <v>尚未建立逐平台检索记录
-2026-10-08：本轮完成机构名及官网域名定向检索。证据入口：
+2026-10-08：原始批量发现结果（包含跨机构链接；仅作线索，不作为本机构已查证明）。入口：
 https://zhxy.nwsuaf.edu.cn/klpnanc/kfjl/kfkt/8d857779d3a548bb972ab1817f1932db.htm
 https://ppc.nwafu.edu.cn/tzgg/abefcb02e4f747a6870e7c408c9b7e4a.htm
 https://pplab.nwsuaf.edu.cn/kfyjl/gjhzxm/dce83bb8ee81426a81c058f177a7e67f.htm
@@ -22662,10 +22827,10 @@
 https://pplab.nwsuaf.edu.cn/kfyjl/gjhzxm/index.htm</v>
       </c>
       <c r="F156" s="3" t="str">
-        <v>尚无实验室及公告年度逐项证据，需核官网平台目录后列明。</v>
+        <v>原母表未具备本机构平台目录及年度逐室完整证据；跨机构结果须归属核验，后续独立行记录实际已查范围。</v>
       </c>
       <c r="G156" s="3" t="str">
-        <v>部分已查（历史线索）</v>
+        <v>机构母表/批量线索；本行不计机构完成。</v>
       </c>
       <c r="H156" s="3" t="str">
         <v>v0.8地区机构样本清单或39所原985母表；检索记录保留，按官网证据确认。</v>
@@ -35786,6 +35951,839 @@
       </c>
       <c r="I591" t="str" s="3">
         <v>resume_sources_20261009.json 官方正文/检索结果</v>
+      </c>
+    </row>
+    <row r="592" ht="52.5" customHeight="1">
+      <c r="A592" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B592" t="str" s="3">
+        <v>湖北文理学院</v>
+      </c>
+      <c r="C592" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D592" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E592" t="str" s="3">
+        <v>查询：湖北文理学院 智能机器人 开放基金；定位：关于2020年学科开放基金项目申报的通知；2026年度开放基金课题申报通知-智能机器人湖北省重点实验室；2026年度开放研究基金拟立项项目公示-数字教育湖北省重点实验室；2025年度开放/创新基金课题申报通知-智能机器人湖北省重点实验室；警用智能机器人达州市重点实验室2026年度开放基金申报公告-警用智能机器人达州市重点实验室；2026年度开放基金申请指南-现代制造质量工程湖北省重点实验室</v>
+      </c>
+      <c r="F592" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G592" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H592" t="str" s="3">
+        <v>https://yjsc.hbuas.edu.cn/__local/F/A0/08/3EABCB32BBE2AC185BB6342FAA7_CB35719B_2BA6B.pdf
+https://robot.wit.edu.cn/info/1017/1552.htm
+https://hrcei.ccnu.edu.cn/info/1203/3485.htm
+https://robot.wit.edu.cn/info/1017/1532.htm
+https://jqr.sasu.edu.cn/info/1009/1061.htm
+https://mmqe.hbut.edu.cn/info/1047/2232.htm</v>
+      </c>
+      <c r="I592" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第200项</v>
+      </c>
+    </row>
+    <row r="593" ht="52.5" customHeight="1">
+      <c r="A593" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B593" t="str" s="3">
+        <v>宁波大学</v>
+      </c>
+      <c r="C593" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D593" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E593" t="str" s="3">
+        <v>查询：宁波大学 机器人 开放基金；定位：2026年度开放基金评审结果公告；2025年度开放基金申请公告；2025年度开放基金评审结果公告；开放课题基金指南；关于2026年宁波市空间智能与数字衍生重点实验室开放基金资助名单资助名单公布的通知-宁波数字孪生（东方理工）研究院</v>
+      </c>
+      <c r="F593" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G593" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H593" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://robot.hit.edu.cn/2024/1210/c338a360989/page.htm
+https://keysoftlab.nju.edu.cn/1573/list.htm
+https://idt.eitech.edu.cn/2650.html</v>
+      </c>
+      <c r="I593" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第201项</v>
+      </c>
+    </row>
+    <row r="594" ht="52.5" customHeight="1">
+      <c r="A594" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B594" t="str" s="3">
+        <v>福州大学</v>
+      </c>
+      <c r="C594" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D594" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E594" t="str" s="3">
+        <v>查询：福州大学 机器视觉 开放基金 2026；定位：关于申请2027年“福州大学福建省高校测试中心贵重仪器设备开放测试基金”的通知-福州大学福建省高校测试中心；福州外语外贸学院数据科学与智能计算重点实验室2026年度开放课题申请指南-福州外语外贸学院-大数据学院；重点实验室开放课题申请指南（2026年度）；关于2025年“福州大学福建省高校测试中心贵重仪器设备开放测试基金”课题小结的通知-福州大学福建省高校测试中心；福州大学关于公布2023年本科生开放探索性实验项目（课程）评选结果的通知-福州大学教务处；关于2026年“福州大学福建省高校测试中心贵重仪器设备开放测试基金”资助项目的公示-福州大学福建省高校测试中心</v>
+      </c>
+      <c r="F594" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G594" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H594" t="str" s="3">
+        <v>https://iamc.fzu.edu.cn/info/1103/5770.htm
+https://www.fzfu.edu.cn/bigdata/info/1171/4977.htm
+https://www.sspu.edu.cn/_t156/2026/0420/c3089a169274/page.htm
+https://iamc.fzu.edu.cn/info/1103/5718.htm
+https://jwch.fzu.edu.cn/info/1039/12923.htm
+https://iamc.fzu.edu.cn/info/1103/5558.htm</v>
+      </c>
+      <c r="I594" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第202项</v>
+      </c>
+    </row>
+    <row r="595" ht="52.5" customHeight="1">
+      <c r="A595" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B595" t="str" s="3">
+        <v>杭州电子科技大学</v>
+      </c>
+      <c r="C595" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D595" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E595" t="str" s="3">
+        <v>查询：杭州电子科技大学 机器人 开放课题 2026；定位：2026年度开放课题申请公告；智能制造装备与技术全国重点实验室 2026年度开放课题申请通知-智能制造装备与技术全国重点实验室；2026年度开放基金评审结果公告</v>
+      </c>
+      <c r="F595" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G595" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H595" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://imet.hust.edu.cn/info/1031/2733.htm
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm</v>
+      </c>
+      <c r="I595" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第203项</v>
+      </c>
+    </row>
+    <row r="596" ht="52.5" customHeight="1">
+      <c r="A596" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B596" t="str" s="3">
+        <v>江西科技师范大学</v>
+      </c>
+      <c r="C596" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D596" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E596" t="str" s="3">
+        <v>查询：江西科技师范大学 机器视觉 开放课题；定位：关于组织申报江西省无人感知系统与人工智能技术工程 研究中心2024年度开放基金项目的通知-江西科技师范大学信息工程学院；关于提交2016年立项教改课题和精品在线开放课程经费预算的通知-江西科技师范大学教务处；多维感知与控制江西省重点实验室-稀土与技术卓越创新中心（稀土与制造学部）；氟硅能源材料与化学教育部重点实验室（江西师范大学）2026年度开放课题基金申请通知</v>
+      </c>
+      <c r="F596" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G596" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H596" t="str" s="3">
+        <v>https://xxgc.jxstnu.edu.cn/info/1010/1188.htm
+https://jwc.jxstnu.edu.cn/info/1020/13061.htm
+https://www.jxust.edu.cn/xtyzzxb2026/zxpt/dwgzykzjxszdsys.htm
+https://iasr.jxnu.edu.cn/2026/0701/c13498a295940/page.htm</v>
+      </c>
+      <c r="I596" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第204项</v>
+      </c>
+    </row>
+    <row r="597" ht="52.5" customHeight="1">
+      <c r="A597" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B597" t="str" s="3">
+        <v>河北工程大学</v>
+      </c>
+      <c r="C597" t="str" s="3">
+        <v>河北</v>
+      </c>
+      <c r="D597" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E597" t="str" s="3">
+        <v>查询：河北工程大学 机器人 开放基金；定位：2026年度开放基金评审结果公告；2025年度开放基金申请公告；管理办法----机器人与智能系统全国重点实验室；2025年度开放基金评审结果公告；2023年度开放基金申请公告；2023年度开放基金评审结果公告</v>
+      </c>
+      <c r="F597" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G597" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H597" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://robot.hit.edu.cn/2024/1210/c338a360989/page.htm
+https://robot.hit.edu.cn/2022/1018/c338a282555/page.htm
+https://robot.hit.edu.cn/2023/0116/c277a287815/page.htm</v>
+      </c>
+      <c r="I597" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第205项</v>
+      </c>
+    </row>
+    <row r="598" ht="52.5" customHeight="1">
+      <c r="A598" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B598" t="str" s="3">
+        <v>辽宁工业大学</v>
+      </c>
+      <c r="C598" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D598" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E598" t="str" s="3">
+        <v>查询：辽宁工业大学 机器人 开放基金；定位：管理办法----机器人与智能系统全国重点实验室；开放基金-工业装备结构分析优化与CAE 软件全国重点实验室；2025年度开放基金申请公告；基金简介----机器人与智能系统全国重点实验室；慧鱼机器人创新实验室-辽宁工业大学机械工程与自动化学院；2023年度开放基金申请公告</v>
+      </c>
+      <c r="F598" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G598" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H598" t="str" s="3">
+        <v>https://rlab.sia.cas.cn/kfjj/glbf/
+https://sail.dlut.edu.cn/kfjj.htm
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://rlab.sia.cas.cn/kfjj/jjjj/
+https://jxxy.lnut.edu.cn/info/14164/179978.htm
+https://robot.hit.edu.cn/2022/1018/c338a282555/page.htm</v>
+      </c>
+      <c r="I598" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第206项</v>
+      </c>
+    </row>
+    <row r="599" ht="52.5" customHeight="1">
+      <c r="A599" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B599" t="str" s="3">
+        <v>湖南工程学院</v>
+      </c>
+      <c r="C599" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D599" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E599" t="str" s="3">
+        <v>查询：湖南工程学院 机器人 开放基金；定位：2026年度开放基金评审结果公告；管理办法----机器人与智能系统全国重点实验室；2025年度开放基金申请公告；水利工程智能巡检与数字化养护湖南省工程研究中心2025年度开放基金申请指南-管理制度-科研处；2025年度开放基金评审结果公告；智能制造与机械工程学院关于2026年度科技创新平台开放课题（汽车零部件产业链产教融合项目专项）评审结果暨拟推荐立项课题的公示-湖南工学院智能制造与机械工程学院欢迎您</v>
+      </c>
+      <c r="F599" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G599" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H599" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://www.hnslsdxy.com/kyc/page/contentshow.aspx?id=202601051120397521
+https://robot.hit.edu.cn/2024/1210/c338a360989/page.htm
+https://www.hnit.edu.cn/jxxy/info/1040/11713.htm</v>
+      </c>
+      <c r="I599" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第207项</v>
+      </c>
+    </row>
+    <row r="600" ht="52.5" customHeight="1">
+      <c r="A600" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B600" t="str" s="3">
+        <v>江西科技师范大学</v>
+      </c>
+      <c r="C600" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D600" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E600" t="str" s="3">
+        <v>查询：江西省无人感知系统与人工智能技术工程研究中心 开放基金 2026 2027；定位：关于组织申报江西省无人感知系统与人工智能技术工程 研究中心2024年度开放基金项目的通知-江西科技师范大学信息工程学院；江西省机载系统智能检测技术产业技术工程化中心、南昌市航空软件共性技术研发重点实验室开放基金指南_校内公告_新闻中心_南昌航空大学；关于组织开展省技术创新中心2027年度平台类研发项目申报工作的通知；安全生产风险监测预警与防控江西省重点实验室2026年开放基金项目征集指南 - 科策云；2026江西省智慧建筑工程研究中心开放基金课题申请指南_通知公告_江西省智慧建筑工程研究中心 - 南昌航空大学；安全生产风险监测预警与防控江西省重点实验室2026年开放基金拟立项项目公示 - 科策云</v>
+      </c>
+      <c r="F600" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G600" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H600" t="str" s="3">
+        <v>https://xxgc.jxstnu.edu.cn/info/1010/1188.htm
+https://www.nchu.edu.cn/xwzx/xngg/content_196002
+https://kyc.jxufe.edu.cn/news-show-9063.html
+https://www.keceyun.com/policy/newsdetail/661658.html
+https://zhjz.nchu.edu.cn/tzgg/content_196076
+https://www.keceyun.com/policy/newsdetail/712559.html</v>
+      </c>
+      <c r="I600" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第208项</v>
+      </c>
+    </row>
+    <row r="601" ht="52.5" customHeight="1">
+      <c r="A601" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B601" t="str" s="3">
+        <v>湖北文理学院</v>
+      </c>
+      <c r="C601" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D601" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E601" t="str" s="3">
+        <v>查询：site:hbuas.edu.cn 学科开放基金 2026；定位：开放基金-湖北文理学院功能材料研究院；关于2020年学科开放基金项目申报的通知；湖北文理学院学科开放基金项目暂行管理办法-数学与统计学院</v>
+      </c>
+      <c r="F601" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G601" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H601" t="str" s="3">
+        <v>https://gncl.hbuas.edu.cn/kfjj.htm
+https://yjsc.hbuas.edu.cn/__local/F/A0/08/3EABCB32BBE2AC185BB6342FAA7_CB35719B_2BA6B.pdf
+https://stxy.hbuas.edu.cn/info/1030/1191.htm</v>
+      </c>
+      <c r="I601" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第209项</v>
+      </c>
+    </row>
+    <row r="602" ht="52.5" customHeight="1">
+      <c r="A602" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B602" t="str" s="3">
+        <v>福州大学</v>
+      </c>
+      <c r="C602" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D602" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E602" t="str" s="3">
+        <v>查询：site:fzu.edu.cn 机器视觉 重点实验室 开放课题；定位：张立伟-福建省太赫兹功能器件与智能传感重点实验室；福建省国土空间分析与模拟数字技术重点实验室项目及经费管理办法（试行-福州大学-建筑与城乡规划学院；钟剑锋-福建省太赫兹功能器件与智能传感重点实验室；数字能源福建省高校重点实验室2026年度开放课题评审结果公示-福州大学电气工程与自动化学院；关于申请2025年开放课题的通知-福州大学离散数学与理论计算机科学研究中心；空间数据挖掘与信息共享教育部重点实验室（福州大学）2023年开放课题申请指南-数字中国研究院（福建）</v>
+      </c>
+      <c r="F602" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G602" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H602" t="str" s="3">
+        <v>https://thz.fzu.edu.cn/info/1029/1149.htm
+https://jzxy.fzu.edu.cn/info/1116/2784.htm
+https://thz.fzu.edu.cn/info/1029/1140.htm
+https://dqxy.fzu.edu.cn/info/1034/8195.htm
+https://dimacs.fzu.edu.cn/info/1039/1912.htm
+https://adc.fzu.edu.cn/info/1014/2573.htm</v>
+      </c>
+      <c r="I602" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第210项</v>
+      </c>
+    </row>
+    <row r="603" ht="52.5" customHeight="1">
+      <c r="A603" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B603" t="str" s="3">
+        <v>杭州电子科技大学</v>
+      </c>
+      <c r="C603" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D603" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E603" t="str" s="3">
+        <v>查询：site:hdu.edu.cn 开放基金 机器人；定位：浙江省“脑机协同智能”重点实验室开放研究基金申报通知</v>
+      </c>
+      <c r="F603" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G603" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H603" t="str" s="3">
+        <v>https://bmci.hdu.edu.cn/2020/1216/c7485a156839/page.htm</v>
+      </c>
+      <c r="I603" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第211项</v>
+      </c>
+    </row>
+    <row r="604" ht="52.5" customHeight="1">
+      <c r="A604" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B604" t="str" s="3">
+        <v>宁波大学</v>
+      </c>
+      <c r="C604" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D604" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E604" t="str" s="3">
+        <v>查询：宁波大学 智能制造与机器人研究中心 开放基金；定位：实验室介绍 - 浙江省机器人与智能装备技术重点实验室 - robotics-lab.nimte.ac.cn；2024年度开放基金课题申请通知-宁波研究院；宁波市空间智能与数字衍生重点实验室 2026年度开放基金申请指南-宁波数字孪生（东方理工）研究院；关于2026年宁波市空间智能与数字衍生重点实验室开放基金资助名单资助名单公布的通知-宁波数字孪生（东方理工）研究院；关于征集2026年度浙江省重点实验室开放课题的通知-宁波研究院；关于申报2021年度江苏省工业感知及智能制造装备工程研究中心开放基金项目的通知</v>
+      </c>
+      <c r="F604" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G604" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H604" t="str" s="3">
+        <v>https://robotics-lab.nimte.ac.cn/view-13552.html
+https://ningbo.nwpu.edu.cn/info/1013/3539.htm
+https://idt.eitech.edu.cn/2411.html
+https://idt.eitech.edu.cn/2650.html
+https://ningbo.nwpu.edu.cn/info/1013/5119.htm
+https://kjc.niit.edu.cn/91/70/c1361a37232/page.htm</v>
+      </c>
+      <c r="I604" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第212项</v>
+      </c>
+    </row>
+    <row r="605" ht="52.5" customHeight="1">
+      <c r="A605" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B605" t="str" s="3">
+        <v>上海航天平台</v>
+      </c>
+      <c r="C605" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D605" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E605" t="str" s="3">
+        <v>查询：上海市空间飞行器机构重点实验室 开放基金 2026；定位：智能感知与人机协同教育部重点实验室2026年度开放课题申请指南；上海市空间导航与定位技术重点实验室2025年度开放课题指南--中国科学院上海天文台；特种环境复合材料技术国家级重点实验室开放基金指南（2026年度）；自然资源部超大城市自然资源时空大数据分析应用重点实验室2026年度开放基金课题申请指南；〖上海市〗上海市空间导航与定位技术重点实验室2025年度开放课题指南 -- 上海天文台；上海市科学技术委员会关于发布2025年度高水平机构建设运行计划“重点实验室”项目申报指南的通知</v>
+      </c>
+      <c r="F605" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G605" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H605" t="str" s="3">
+        <v>https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
+https://shao.cas.cn/lnpt/release/202507/t20250730_7899184.html
+https://ccms.hit.edu.cn/2026/0918/c13809a401763/page.htm
+https://bigdata.ecnu.edu.cn/ee/2e/c43524a781870/page.htm
+https://shao.cas.cn/2020Ver/xwdt/tzzn/202509/t20250909_7963929.html
+https://www.shanghai.gov.cn/gwk/search/content/e7829b61c89e4b1d8f15fb492dbded49</v>
+      </c>
+      <c r="I605" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第213项</v>
+      </c>
+    </row>
+    <row r="606" ht="52.5" customHeight="1">
+      <c r="A606" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B606" t="str" s="3">
+        <v>杭州电子科技大学</v>
+      </c>
+      <c r="C606" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D606" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E606" t="str" s="3">
+        <v>查询：脑机协同智能 开放基金 2026；定位：2026年度脑认知与类脑智能全国重点实验室开放课题申请指南--中国科学院脑科学与智能技术卓越创新中心；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；开放课题----中国科学院脑科学与智能技术卓越创新中心；国家高性能医疗器械创新中心关于发布2026年开放基金-国家高性能医疗器械创新中心；智能算法安全全国重点实验室2026年度开放课题申请指南--智能算法安全全国重点实验室</v>
+      </c>
+      <c r="F606" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G606" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H606" t="str" s="3">
+        <v>https://www.cebsit.cas.cn/nrzylnznzdsys/kfkt/202604/t20260407_8182418.html
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://www.cebsit.cas.cn/nrzylnznzdsys/kfkt/
+https://www.nmed.org.cn/Content/xwzx/gg/2026-03/147291_1.html
+https://klais.ict.ac.cn/tzgg/xmzj/202609/t20260908_856264.html</v>
+      </c>
+      <c r="I606" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第214项</v>
+      </c>
+    </row>
+    <row r="607" ht="52.5" customHeight="1">
+      <c r="A607" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B607" t="str" s="3">
+        <v>福州大学</v>
+      </c>
+      <c r="C607" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D607" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E607" t="str" s="3">
+        <v>查询：福州大学 数字能源 2026 开放课题 申请；定位：数字能源福建省高校重点实验室开放课题指南-福州大学电气工程与自动化学院；数字能源福建省高校重点实验室2026年度开放课题评审结果公示-福州大学电气工程与自动化学院；能源与环境光催化国家重点实验室；光能利用与减污降碳教育部工程研究中心2026年开放课题申请通知-光能利用与减污降碳教育部工程研究中心；省部共建能源与环境光催化国家重点实验室；能源与环境光催化国家重点实验室</v>
+      </c>
+      <c r="F607" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G607" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H607" t="str" s="3">
+        <v>https://dqxy.fzu.edu.cn/info/1034/8270.htm
+https://dqxy.fzu.edu.cn/info/1034/8195.htm
+https://sklpee.fzu.edu.cn/__local/D/0A/43/44C0B3E68978756ADE4B46C2B33_4E0A31F0_2583B.pdf?e=.pdf
+https://pupc.ccnu.edu.cn/info/1010/1125.htm
+https://kjc.fzu.edu.cn/__local/3/73/8F/F6FFBF2882A214DEB0C9BD6245E_92A84832_2E005.pdf?e=.pdf
+https://kjc.fzu.edu.cn/__local/F/CF/10/67DDF34CC56CC0B560D75BD9778_B0F7475F_257A1.pdf?e=.pdf</v>
+      </c>
+      <c r="I607" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第215项</v>
+      </c>
+    </row>
+    <row r="608" ht="52.5" customHeight="1">
+      <c r="A608" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B608" t="str" s="3">
+        <v>南昌航空大学</v>
+      </c>
+      <c r="C608" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D608" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E608" t="str" s="3">
+        <v>查询：site:zhjz.nchu.edu.cn 开放 2026；定位：2026江西省智慧建筑工程研究中心开放基金课题申请指南_通知公告_江西省智慧建筑工程研究中心 - 南昌航空大学；李克强总理在庆祝中华人民共和国成立七十一周年招待会上致辞_科研动态_江西省智慧建筑工程研究中心 - 南昌航空大学；发改委 科技部 工信部 财政部│推行绿色建造 大力发展钢结构 加快节能环保产业试点示范_学术预告_科学研究_江西省智慧建筑工程研究中心 - 南昌航空大学；江西省智慧建筑工程研究中心 - 南昌航空大学；通知公告_江西省智慧建筑工程研究中心 - 南昌航空大学；江西省智慧建筑工程研究中心2021 年开放基金课题申请指南</v>
+      </c>
+      <c r="F608" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G608" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H608" t="str" s="3">
+        <v>https://zhjz.nchu.edu.cn/tzgg/content_196076
+https://zhjz.nchu.edu.cn/kydt/content_92757
+https://zhjz.nchu.edu.cn/kxyj/kyxm/content_92754
+https://zhjz.nchu.edu.cn/
+https://zhjz.nchu.edu.cn/tzgg
+https://zhjz.nchu.edu.cn/upload/zhjz/pdf/2021/11/12/%E6%B1%9F%E8%A5%BF%E7%9C%81%E6%99%BA%E6%85%A7%E5%BB%BA%E7%AD%91%E5%B7%A5%E7%A8%8B%E7%A0%94%E7%A9%B6%E4%B8%AD%E5%BF%83%E5%BC%80%E6%94%BE%E5%9F%BA%E9%87%9120211020%281%29.pdf</v>
+      </c>
+      <c r="I608" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第216项</v>
+      </c>
+    </row>
+    <row r="609" ht="52.5" customHeight="1">
+      <c r="A609" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B609" t="str" s="3">
+        <v>湖北文理学院</v>
+      </c>
+      <c r="C609" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D609" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E609" t="str" s="3">
+        <v>查询：湖北文理学院 2026 开放基金 机器人；定位：开放基金-湖北文理学院功能材料研究院；2026年度开放研究基金拟立项项目公示-数字教育湖北省重点实验室；2026年度开放研究基金申请指南-数字教育湖北省重点实验室；2026年度开放基金申请指南-现代制造质量工程湖北省重点实验室；2026年度开放基金课题申报通知-智能机器人湖北省重点实验室；智能无人系统技术四川省高等学校重点实验室2026年度开放基金申报公告-智能无人系统技术四川省高等学校重点实验室</v>
+      </c>
+      <c r="F609" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G609" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H609" t="str" s="3">
+        <v>https://gncl.hbuas.edu.cn/kfjj.htm
+https://hrcei.ccnu.edu.cn/info/1203/3485.htm
+https://hrcei.ccnu.edu.cn/info/1203/3415.htm
+https://mmqe.hbut.edu.cn/info/1047/2232.htm
+https://robot.wit.edu.cn/info/1017/1552.htm
+https://znwrxt.sasu.edu.cn/info/1009/1062.htm</v>
+      </c>
+      <c r="I609" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第217项</v>
+      </c>
+    </row>
+    <row r="610" ht="52.5" customHeight="1">
+      <c r="A610" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B610" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C610" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D610" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E610" t="str" s="3">
+        <v>查询：site:jsj.nwpu.edu.cn 科研概况 研究机构；定位：智能感知与计算工业和信息化部重点实验室-计算机学院；空天地海一体化大数据应用技术国家工程实验室​-计算机学院</v>
+      </c>
+      <c r="F610" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G610" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H610" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1658/7529.htm
+https://jsj.nwpu.edu.cn/info/1658/7531.htm</v>
+      </c>
+      <c r="I610" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第218项</v>
+      </c>
+    </row>
+    <row r="611" ht="52.5" customHeight="1">
+      <c r="A611" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B611" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C611" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D611" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E611" t="str" s="3">
+        <v>查询：site:ia.cas.cn 2026 开放基金 紫东 太初 模式识别；定位：紫东太初大模型研究中心----中国科学院自动化研究所；工业视觉智能装备技术工程实验室----中国科学院自动化研究所；复杂系统认知与决策国家级重点实验室----中国科学院自动化研究所；分子影像实验室----中国科学院自动化研究所</v>
+      </c>
+      <c r="F611" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G611" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H611" t="str" s="3">
+        <v>https://ia.cas.cn/jgsz/kyxt/zztc/
+https://ia.cas.cn/jgsz/kyxt/gysj/
+https://ia.cas.cn/jgsz/kyxt/fzxtrz/
+https://ia.cas.cn/jgsz/kyxt/bm9/</v>
+      </c>
+      <c r="I611" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第219项</v>
+      </c>
+    </row>
+    <row r="612" ht="52.5" customHeight="1">
+      <c r="A612" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B612" t="str" s="3">
+        <v>江西科技师范大学</v>
+      </c>
+      <c r="C612" t="str" s="3">
+        <v>江西·南昌</v>
+      </c>
+      <c r="D612" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E612" t="str" s="3">
+        <v>江西省无人感知系统与人工智能技术工程研究中心；2024；N039；官方2024年度公告正文已核；附件RAR首次读取失败</v>
+      </c>
+      <c r="F612" t="str" s="3">
+        <v>截止原文“2023年度”及2024-07-15—2023-07-20互相矛盾，不改写为2024-07-20；下载RAR中的申请指南、管理办法、申请书，补金额类别、经费/外拨、成果/IP、合作要求。2026—2027公告未定位，不能当当前窗口。</v>
+      </c>
+      <c r="G612" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H612" t="str" s="3">
+        <v>https://xxgc.jxstnu.edu.cn/info/1010/1188.htm</v>
+      </c>
+      <c r="I612" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="613" ht="52.5" customHeight="1">
+      <c r="A613" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B613" t="str" s="3">
+        <v>南昌航空大学</v>
+      </c>
+      <c r="C613" t="str" s="3">
+        <v>江西·南昌</v>
+      </c>
+      <c r="D613" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E613" t="str" s="3">
+        <v>江西省智慧建筑工程研究中心等联署四个平台；2026；N040；官方2026公告正文已核；DOCX指南及DOC申请书首次读取失败</v>
+      </c>
+      <c r="F613" t="str" s="3">
+        <v>取得DOCX指南与DOC申请书，先核是否有实际机器人/自主装备相关任务；若无则剔除。金额上限/窗口已核，成果、IP、经费外拨、合作与签章条件待核。四个平台联合一轮，非四条独立项目。</v>
+      </c>
+      <c r="G613" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H613" t="str" s="3">
+        <v>https://zhjz.nchu.edu.cn/tzgg/content_196076</v>
+      </c>
+      <c r="I613" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="614" ht="52.5" customHeight="1">
+      <c r="A614" t="str" s="3">
+        <v>2026-10-09具体平台核验</v>
+      </c>
+      <c r="B614" t="str" s="3">
+        <v>杭州电子科技大学</v>
+      </c>
+      <c r="C614" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D614" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E614" t="str" s="3">
+        <v>浙江省脑机协同智能重点实验室：网页标题称开放基金，正文却为IFIP IIP2020学术会议报道，未获正式基金任务或条款，不新增项目。</v>
+      </c>
+      <c r="F614" t="str" s="3">
+        <v>另需真实年度指南和2026—2027开放机制，不能以标题替代正文证据。</v>
+      </c>
+      <c r="G614" t="str" s="3">
+        <v>只限本行证据范围；剩余检索继续。</v>
+      </c>
+      <c r="H614" t="str" s="3">
+        <v>https://bmci.hdu.edu.cn/2020/1216/c7485a156839/page.htm</v>
+      </c>
+      <c r="I614" t="str" s="3">
+        <v>resume_sources_20261009.json 正文/首次失败</v>
+      </c>
+    </row>
+    <row r="615" ht="52.5" customHeight="1">
+      <c r="A615" t="str" s="3">
+        <v>2026-10-09具体平台核验</v>
+      </c>
+      <c r="B615" t="str" s="3">
+        <v>福州大学</v>
+      </c>
+      <c r="C615" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D615" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E615" t="str" s="3">
+        <v>数字能源福建省高校重点实验室2026指南：任务为能源系统状态估计、电能变换电机驱动、多能协同低碳运行、能源弹性；未发现机器人具体任务，排除本年度。</v>
+      </c>
+      <c r="F615" t="str" s="3">
+        <v>其他机器人相关实验室及2027逐平台查询仍需补齐。</v>
+      </c>
+      <c r="G615" t="str" s="3">
+        <v>只限本行证据范围；剩余检索继续。</v>
+      </c>
+      <c r="H615" t="str" s="3">
+        <v>https://dqxy.fzu.edu.cn/info/1034/8270.htm</v>
+      </c>
+      <c r="I615" t="str" s="3">
+        <v>resume_sources_20261009.json 正文/首次失败</v>
+      </c>
+    </row>
+    <row r="616" ht="52.5" customHeight="1">
+      <c r="A616" t="str" s="3">
+        <v>2026-10-09具体平台核验</v>
+      </c>
+      <c r="B616" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C616" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D616" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E616" t="str" s="3">
+        <v>计算机学院2025-11-23科研概况：主建空天地海一体化大数据国家工程实验室、移动平台环境感知及空天应用国际联合中心、无人航行实时智能感知与计算引智基地、云计算应用国家地方工程中心；8省部级平台未逐名列出。</v>
+      </c>
+      <c r="F616" t="str" s="3">
+        <v>名单包含待查新平台；学院全目录及各平台2026—2027开放机制仍须逐一查。</v>
+      </c>
+      <c r="G616" t="str" s="3">
+        <v>只限本行证据范围；剩余检索继续。</v>
+      </c>
+      <c r="H616" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1556/7722.htm</v>
+      </c>
+      <c r="I616" t="str" s="3">
+        <v>resume_sources_20261009.json 正文/首次失败</v>
+      </c>
+    </row>
+    <row r="617" ht="52.5" customHeight="1">
+      <c r="A617" t="str" s="3">
+        <v>2026-10-09具体平台核验</v>
+      </c>
+      <c r="B617" t="str" s="3">
+        <v>湖北文理学院</v>
+      </c>
+      <c r="C617" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D617" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E617" t="str" s="3">
+        <v>2021学科开放基金PDF首次无法读取，2026机器人开放基金查询未定位同校正式新指南；他校搜索命中不算本校成果。</v>
+      </c>
+      <c r="F617" t="str" s="3">
+        <v>覆盖-HBUAS：人工下载2021PDF核任务、金额、资格及条款，历史发现线索不是当前受理。</v>
+      </c>
+      <c r="G617" t="str" s="3">
+        <v>只限本行证据范围；剩余检索继续。</v>
+      </c>
+      <c r="H617" t="str" s="3">
+        <v>https://yjsc.hbuas.edu.cn/__local/1/68/63/7346D44F94C168A2F221006C73C_3B23A756_24843.pdf</v>
+      </c>
+      <c r="I617" t="str" s="3">
+        <v>resume_sources_20261009.json 正文/首次失败</v>
       </c>
     </row>
   </sheetData>
@@ -39991,6 +40989,58 @@
         <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
       </c>
     </row>
+    <row r="63" ht="66" customHeight="1">
+      <c r="A63" t="str" s="20">
+        <v>历史批次·截止年份冲突待核</v>
+      </c>
+      <c r="B63" t="str" s="13">
+        <v>原文2024-07-15至2023-07-20；年份冲突</v>
+      </c>
+      <c r="C63" t="str" s="14">
+        <v>江西科技师范大学·江西省无人感知系统与人工智能技术工程研究中心</v>
+      </c>
+      <c r="D63" t="str" s="15">
+        <v>三维重建；目标感知与识别；无人移动载体自主导航及智能控制；无人移动载体协同工作控制；人工智能感知方法。</v>
+      </c>
+      <c r="E63" t="str" s="15">
+        <v>一般课题不超过3万元/项</v>
+      </c>
+      <c r="F63" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G63" t="str" s="3">
+        <v>截止原文“2023年度”及2024-07-15—2023-07-20互相矛盾，不改写为2024-07-20；下载RAR中的申请指南、管理办法、申请书，补金额类别、经费/外拨、成果/IP、合作要求。2026—2027公告未定位，不能当当前窗口。</v>
+      </c>
+      <c r="H63" t="str" s="3">
+        <v>刘老师13576931367；20423232@qq.com</v>
+      </c>
+    </row>
+    <row r="64" ht="66" customHeight="1">
+      <c r="A64" t="str" s="20">
+        <v>任务证据待核·窗口未截止</v>
+      </c>
+      <c r="B64" t="n" s="13">
+        <v>46305</v>
+      </c>
+      <c r="C64" t="str" s="14">
+        <v>南昌航空大学·江西省智慧建筑工程研究中心等联署四个平台</v>
+      </c>
+      <c r="D64" t="str" s="15">
+        <v>公告列低空基础设施风险防控、韧性建造与智能运维、安全监测预警应急、智慧建筑绿色低碳、建筑及低空基础设施数字化智能系统、自主相关方向；未明确机器人感知、规划、控制等具体任务，须核附件，不因“低空”“智能”直接保留首页。</v>
+      </c>
+      <c r="E64" t="str" s="15">
+        <v>不超过2万元/项</v>
+      </c>
+      <c r="F64" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G64" t="str" s="3">
+        <v>取得DOCX指南与DOC申请书，先核是否有实际机器人/自主装备相关任务；若无则剔除。金额上限/窗口已核，成果、IP、经费外拨、合作与签章条件待核。四个平台联合一轮，非四条独立项目。</v>
+      </c>
+      <c r="H64" t="str" s="3">
+        <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" location="'02项目完整详情'!A14"/>
@@ -40115,6 +41165,10 @@
     <hyperlink ref="F55" ns1:id="rIdResume63"/>
     <hyperlink ref="C62" location="'02项目完整详情'!A187" display="项目完整详情"/>
     <hyperlink ref="F62" ns1:id="rIdResume64"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A188" display="项目完整详情"/>
+    <hyperlink ref="F63" ns1:id="rIdResume65"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A189" display="项目完整详情"/>
+    <hyperlink ref="F64" ns1:id="rIdResume66"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -10066,7 +10066,7 @@
         <v>正式开放课题公告</v>
       </c>
       <c r="C104" s="3" t="str">
-        <v>新疆生产建设兵团相关单位</v>
+        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）</v>
       </c>
       <c r="D104" s="3" t="str">
         <v>建筑钢结构智能制造技术兵团重点实验室</v>
@@ -10092,13 +10092,13 @@
 已离退休的科研人员、申请单位的兼职科研人员不得作为申请项目的负责人提出申请，但可作为项目组成员参加研究。</v>
       </c>
       <c r="L104" s="3" t="str">
-        <v>官方明确｜依据《兵团重点实验室建设与运行管理办法》和《建筑钢结构智能制造技术兵团重点实验室章程》等文件规定，为贯彻兵团重点实验室“开放、流动、联合、竞争”的方针，促进新疆生产建设兵团建筑钢结构智能制造领域的基础理论研究和应用基础研究，加强科研合作与学术交流，围绕兵团生产问题和科学难题，吸引国内外优秀人才来实验室工作与合作交流，建筑钢结构智能制造技术兵团重点实验室（以下简称：重点实验室）特设立开放课题研究基金，热忱欢迎和邀请相关领域的广大科研人员申报。</v>
+        <v>优先与实验室团队合作；成果论文通讯作者须为实验室固定人员。访问天数未载。</v>
       </c>
       <c r="M104" s="3" t="str">
         <v>官方明确｜资助项目的经费使用一律采用“报账制”，受资助项目经费不下拨，需到重点实验室依托单位财务处报账。</v>
       </c>
       <c r="N104" s="3" t="str">
-        <v>官方明确｜如需变动，必须由申请人在课题研究期限的一半时间前提出书面报告申请，由实验室学术委员会讨论决定。</v>
+        <v>每项只能延期一次，含延期总执行时间不超过1年；确切起止及正常期限以任务书确认。</v>
       </c>
       <c r="O104" s="3" t="str">
         <v>官方明确｜课题考核指标为发表1篇及以上与项目直接相关的EI或SCI刊物论文（主持人为第一作者，“建筑钢结构智能制造技术兵团重点实验室”为第一署名单位），论文的通讯作者需为本重点实验室固定人员，课题负责人应完成约定的研究任务并明确知识产权共享方式，全部由重点实验室资助的课题研究成果，其知识产权为重点实验室所有。
@@ -10117,7 +10117,7 @@
         <v>已知背景：南京信息工程大学现职、博士。个人条件、在研限项及实际合作人尚未逐项确认；须按公告条款核对，受理窗口状态不代表可申请。</v>
       </c>
       <c r="S104" s="3" t="str">
-        <v>本轮复读的公开公告/已取得附件中未发现新增条款缺口；个人资格及合作条件仍须逐项确认。</v>
+        <v>周期不得仅摘录项目变更条款：正文给出含延期总执行时间≤1年，确切起止待任务书；费用不下拨、校内报账；固定人员通讯作者要求已核。</v>
       </c>
       <c r="T104" s="3" t="str">
         <v>https://kjj.xjbt.gov.cn/c/2026-04-01/8477891.shtml</v>
@@ -10138,7 +10138,7 @@
         <v>P2 新疆</v>
       </c>
       <c r="Z104" s="3" t="str">
-        <v>btzdsysfutai@163.com</v>
+        <v>何静15352668022；btzdsysfutai@163.com</v>
       </c>
       <c r="AA104" s="3" t="str"/>
     </row>
@@ -17248,6 +17248,411 @@
         <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
       </c>
       <c r="AA189" t="str" s="3"/>
+    </row>
+    <row r="190" ht="79.5" customHeight="1">
+      <c r="A190" t="str" s="3">
+        <v>N041</v>
+      </c>
+      <c r="B190" t="str" s="3">
+        <v>官方2019公告已读；具体任务附件首次读取失败</v>
+      </c>
+      <c r="C190" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="D190" t="str" s="3">
+        <v>宁夏智能装备CAE重点实验室</v>
+      </c>
+      <c r="E190" t="str" s="3">
+        <v>历史批次·具体任务待核</v>
+      </c>
+      <c r="F190" t="str" s="3">
+        <v>2019</v>
+      </c>
+      <c r="G190" t="n" s="6">
+        <v>43808</v>
+      </c>
+      <c r="H190" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I190" t="str" s="3">
+        <v>公告正文介绍多目标优化、多物理场、材料本构、复杂机电耦合；具体资助方向仅称见附件。不得以智能装备名称/优化关键词判定机器人相关，须核《开放课题设置.pdf》。</v>
+      </c>
+      <c r="J190" t="str" s="3">
+        <v>3万元/项；成果突出可追加，追加额未载</v>
+      </c>
+      <c r="K190" t="str" s="3">
+        <v>国外知名高校及国内211、985高校、科研机构中级以上职称或博士科研人员；南京信息工程大学是否符合科研机构口径需主办方确认，不能默认符合限定高校范围。</v>
+      </c>
+      <c r="L190" t="str" s="3">
+        <v>固定合作人员及访问要求正文未载。</v>
+      </c>
+      <c r="M190" t="str" s="3">
+        <v>经费科目、外拨及报销规则未取得，不能推定可外拨。</v>
+      </c>
+      <c r="N190" t="str" s="3">
+        <v>1年，正文2019.12—2020.12；旧批次不套作2026—2027机制。</v>
+      </c>
+      <c r="O190" t="str" s="3">
+        <v>具体成果数量及署名要求需管理条例/任务设置。</v>
+      </c>
+      <c r="P190" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q190" t="str" s="3">
+        <v>申请书原件3份，单位审查盖章，邮寄宁夏大学实验室办公室；无评审费用；电子提交未载。</v>
+      </c>
+      <c r="R190" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；个人年龄、限项、单位资格及合作人员尚未逐项确认。</v>
+      </c>
+      <c r="S190" t="str" s="3">
+        <v>年度任务PDF首次无法读取；补机器人/自主装备具体任务证据，若无则剔除；另核管理条例、成果/IP、经费外拨及限定单位。2026—2027定向搜索未定位新公告。此前误用nu.edu.cn的空结果不作宁夏大学证据，正确域名nxu.edu.cn。</v>
+      </c>
+      <c r="T190" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/info/1262/4078.htm</v>
+      </c>
+      <c r="U190" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/system/_content/download.jsp?owner=1884047012&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=11910680</v>
+      </c>
+      <c r="V190" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W190" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X190" t="str" s="3">
+        <v>客观保留公告任务及条件；未知条款明确待核。</v>
+      </c>
+      <c r="Y190" t="str" s="3">
+        <v>宁夏·银川</v>
+      </c>
+      <c r="Z190" t="str" s="3">
+        <v>王老师13895189949；cae@nxu.edu.cn；2019收件：贺兰山西路539号宁大C区机械工程学院750021</v>
+      </c>
+      <c r="AA190" t="str" s="3"/>
+    </row>
+    <row r="191" ht="79.5" customHeight="1">
+      <c r="A191" t="str" s="3">
+        <v>N042</v>
+      </c>
+      <c r="B191" t="str" s="3">
+        <v>官方2024年度正式公告正文已核；模板首次读取失败</v>
+      </c>
+      <c r="C191" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="D191" t="str" s="3">
+        <v>脑机智能技术教育部重点实验室</v>
+      </c>
+      <c r="E191" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F191" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G191" t="n" s="6">
+        <v>45412</v>
+      </c>
+      <c r="H191" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I191" t="str" s="3">
+        <v>脑机接口、脑机融合智能、脑信号感知传输、脑机控制交互技术；并列多模态融合、鲁棒机器学习等方向。</v>
+      </c>
+      <c r="J191" t="str" s="3">
+        <v>3—5万元/项；拟15—20项</v>
+      </c>
+      <c r="K191" t="str" s="3">
+        <v>人工智能、脑科学、计算机、电子、自动化等相关专业背景，年龄不超过40岁；每人主持1项，课题组人员不得同时参加两个以上项目申请；单位同意盖章。</v>
+      </c>
+      <c r="L191" t="str" s="3">
+        <v>鼓励联合固定成员制定计划开展合作，未写强制；访问期限未载。</v>
+      </c>
+      <c r="M191" t="str" s="3">
+        <v>经费科目、外拨及报销规则未取得，不能推定可外拨。</v>
+      </c>
+      <c r="N191" t="str" s="3">
+        <v>2年，自收到资助通知起，一个月内提交实施计划。</v>
+      </c>
+      <c r="O191" t="str" s="3">
+        <v>期限内至少1篇中科院二区及以上SCI/CCF A会议论文，须共同署名实验室、标注资助，不能仅脚注致谢；结题提交总结、论文、报告及原始资料。实验室第一单位/通讯作者要求未载，不能附加。</v>
+      </c>
+      <c r="P191" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q191" t="str" s="3">
+        <v>个人申报单位推荐，申请书纸质2份单位盖章邮寄，完全一致电子版发sunl@nuaa.edu.cn；邮寄细地址公告未列。</v>
+      </c>
+      <c r="R191" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；个人年龄、限项、单位资格及合作人员尚未逐项确认。</v>
+      </c>
+      <c r="S191" t="str" s="3">
+        <v>正文资金、年龄、限项、合作、成果已核；2024模板DOC首次失败（页面显示DOCX名但链接实际DOC），经费外拨、IP、邮寄地址待补。2026—2027查询仅定位2024，不能当当前窗口。</v>
+      </c>
+      <c r="T191" t="str" s="3">
+        <v>https://bmi.nuaa.edu.cn/article/417830/content/1334.htm</v>
+      </c>
+      <c r="U191" t="str" s="3">
+        <v>https://ai.nuaa.edu.cn/_upload/article/files/d8/9f/74c2bc0346ad98bb32e5b59fa8b0/61acea59-408a-4f0d-bddc-097d0c5eb3fe.doc</v>
+      </c>
+      <c r="V191" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W191" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X191" t="str" s="3">
+        <v>客观保留公告任务及条件；未知条款明确待核。</v>
+      </c>
+      <c r="Y191" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="Z191" t="str" s="3">
+        <v>孙亮025-84896885；sunl@nuaa.edu.cn</v>
+      </c>
+      <c r="AA191" t="str" s="3"/>
+    </row>
+    <row r="192" ht="79.5" customHeight="1">
+      <c r="A192" t="str" s="3">
+        <v>N043</v>
+      </c>
+      <c r="B192" t="str" s="3">
+        <v>官方公告搜索摘要及缓存片段；直接访问首次超时</v>
+      </c>
+      <c r="C192" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="D192" t="str" s="3">
+        <v>模式分析与机器智能工业和信息化部重点实验室</v>
+      </c>
+      <c r="E192" t="str" s="3">
+        <v>历史批次·公告全文待核</v>
+      </c>
+      <c r="F192" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G192" t="str" s="6">
+        <v>未取得2024准确截止</v>
+      </c>
+      <c r="H192" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I192" t="str" s="3">
+        <v>官方缓存列面向交互的视觉识别理解、复杂场景多模态感知、人机融合智能交互；并列特征表示、鲁棒学习、弱监督模式识别。须核全文，未限定医疗超声。</v>
+      </c>
+      <c r="J192" t="str" s="3">
+        <v>官方缓存：3—5万元/项，拟4—5项；全文待核</v>
+      </c>
+      <c r="K192" t="str" s="3">
+        <v>缓存：人工智能、脑科学、计算机、电子、自动化等背景，年龄≤40；主持1项，成员不得同时参加两个以上申请；单位同意盖章。全文待核。</v>
+      </c>
+      <c r="L192" t="str" s="3">
+        <v>缓存鼓励联合实验室成员，不据此写强制；访问待核。</v>
+      </c>
+      <c r="M192" t="str" s="3">
+        <v>经费科目、外拨及报销规则未取得，不能推定可外拨。</v>
+      </c>
+      <c r="N192" t="str" s="3">
+        <v>缓存为2年，准确起止待全文。</v>
+      </c>
+      <c r="O192" t="str" s="3">
+        <v>缓存未取得完整成果指标、署名与单位排序。</v>
+      </c>
+      <c r="P192" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q192" t="str" s="3">
+        <v>申报材料、份数、邮箱、邮寄地址需全文及模板。</v>
+      </c>
+      <c r="R192" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；个人年龄、限项、单位资格及合作人员尚未逐项确认。</v>
+      </c>
+      <c r="S192" t="str" s="3">
+        <v>首次网页超时，不反复访问；需完整公告文字/网页PDF及全部附件，补准确截止、成果署名、经费外拨、IP、提交。2026—2027搜索仅定位2024批次，不当当前正式公告。</v>
+      </c>
+      <c r="T192" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0420/c10849a336622/page.psp</v>
+      </c>
+      <c r="U192" t="str" s="3">
+        <v>附件具体下载地址未取得，请从公告下载</v>
+      </c>
+      <c r="V192" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W192" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X192" t="str" s="3">
+        <v>客观保留公告任务及条件；未知条款明确待核。</v>
+      </c>
+      <c r="Y192" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="Z192" t="str" s="3">
+        <v>联系人邮箱未取得</v>
+      </c>
+      <c r="AA192" t="str" s="3"/>
+    </row>
+    <row r="193" ht="79.5" customHeight="1">
+      <c r="A193" t="str" s="3">
+        <v>N044</v>
+      </c>
+      <c r="B193" t="str" s="3">
+        <v>官方公告搜索缓存部分正文；直接访问首次超时</v>
+      </c>
+      <c r="C193" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="D193" t="str" s="3">
+        <v>高安全系统的软件开发与验证技术工业和信息化部重点实验室</v>
+      </c>
+      <c r="E193" t="str" s="3">
+        <v>历史批次·年度任务全文待核</v>
+      </c>
+      <c r="F193" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G193" t="n" s="6">
+        <v>45402</v>
+      </c>
+      <c r="H193" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I193" t="str" s="3">
+        <v>平台介绍含无人自主智能系统安全分析；已见年度方向片段仅高安全软件需求、建模及形式化验证，未取得完整年度任务。须确认当年是否支持无人自主系统，不能用平台简介代替年度任务。</v>
+      </c>
+      <c r="J193" t="str" s="3">
+        <v>缓存：2—4万元/项，拟5—10项；全文待核</v>
+      </c>
+      <c r="K193" t="str" s="3">
+        <v>缓存：主持1项，成员不得同时参加两个以上申请，单位同意盖章；学历、职称、年龄全文未取得。</v>
+      </c>
+      <c r="L193" t="str" s="3">
+        <v>固定合作与访问全文待核。</v>
+      </c>
+      <c r="M193" t="str" s="3">
+        <v>经费科目、外拨及报销规则未取得，不能推定可外拨。</v>
+      </c>
+      <c r="N193" t="str" s="3">
+        <v>缓存为2年，起止待全文。</v>
+      </c>
+      <c r="O193" t="str" s="3">
+        <v>未取得完整年度成果数量及署名。</v>
+      </c>
+      <c r="P193" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q193" t="str" s="3">
+        <v>缓存：个人申报、单位推荐，申请书纸质2份单位盖章邮寄，同时发一致电子版；具体联系人和地址未取得。</v>
+      </c>
+      <c r="R193" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；个人年龄、限项、单位资格及合作人员尚未逐项确认。</v>
+      </c>
+      <c r="S193" t="str" s="3">
+        <v>年度完整方向/任务证据不足，若仅软件验证而无无人自主机器人任务则剔除；获取全文和申请模板，补资格、成果/IP、经费外拨、联系与窗口。2026—2027未定位新正式公告。</v>
+      </c>
+      <c r="T193" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0412/c10849a335982/page.psp</v>
+      </c>
+      <c r="U193" t="str" s="3">
+        <v>附件具体下载地址未取得，请从公告下载</v>
+      </c>
+      <c r="V193" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W193" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X193" t="str" s="3">
+        <v>客观保留公告任务及条件；未知条款明确待核。</v>
+      </c>
+      <c r="Y193" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="Z193" t="str" s="3">
+        <v>联系人邮箱未取得</v>
+      </c>
+      <c r="AA193" t="str" s="3"/>
+    </row>
+    <row r="194" ht="79.5" customHeight="1">
+      <c r="A194" t="str" s="3">
+        <v>N045</v>
+      </c>
+      <c r="B194" t="str" s="3">
+        <v>官方2026通知搜索摘要，直接网页首次483受阻</v>
+      </c>
+      <c r="C194" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="D194" t="str" s="3">
+        <v>民航飞机健康监测与智能维护重点实验室（基本科研业务费自主课题）</v>
+      </c>
+      <c r="E194" t="str" s="3">
+        <v>公告及具体任务待核</v>
+      </c>
+      <c r="F194" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G194" t="str" s="6">
+        <v>2026准确截止未取得</v>
+      </c>
+      <c r="H194" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I194" t="str" s="3">
+        <v>现仅确认民航飞机健康监测与智能维护课题，年度机器人/自主装备相关研究任务尚未取得，不能仅智能维护名称保留首页。</v>
+      </c>
+      <c r="J194" t="str" s="3">
+        <v>资助金额未取得</v>
+      </c>
+      <c r="K194" t="str" s="3">
+        <v>官方摘要提到校外负责人经费路径，但校外申请范围、职称学历、年龄及限项未取得，不直接认定本人可申报。</v>
+      </c>
+      <c r="L194" t="str" s="3">
+        <v>合作成员、驻室及访问要求未取得。</v>
+      </c>
+      <c r="M194" t="str" s="3">
+        <v>官方摘要明确：校内负责人列子账号，校外负责人通过合同外协转至校外；资金实际接收单位、比例、费用范围待全文，不推定转个人账户。</v>
+      </c>
+      <c r="N194" t="str" s="3">
+        <v>周期和起止未取得。</v>
+      </c>
+      <c r="O194" t="str" s="3">
+        <v>成果数量、论文与单位署名要求未取得。</v>
+      </c>
+      <c r="P194" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q194" t="str" s="3">
+        <v>提交份数、格式、盖章、邮箱、时间未取得。</v>
+      </c>
+      <c r="R194" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；个人年龄、限项、单位资格及合作人员尚未逐项确认。</v>
+      </c>
+      <c r="S194" t="str" s="3">
+        <v>首次483，不再尝试；下载或复制完整2026公告及全部附件，先核真实机器人任务与外部资格；再补金额、截止、周期、成果、IP、合作、外协接收单位及提交。未进入首页。</v>
+      </c>
+      <c r="T194" t="str" s="3">
+        <v>https://cca.nuaa.edu.cn/_t862/2026/0627/c15585a402933/page.htm</v>
+      </c>
+      <c r="U194" t="str" s="3">
+        <v>请从公告页面下载全部附件，具体直链未取得</v>
+      </c>
+      <c r="V194" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W194" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X194" t="str" s="3">
+        <v>客观保留公告任务及条件；未知条款明确待核。</v>
+      </c>
+      <c r="Y194" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="Z194" t="str" s="3">
+        <v>申报联系人及邮箱未取得</v>
+      </c>
+      <c r="AA194" t="str" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17658,6 +18063,11 @@
     <hyperlink ref="T187" ns1:id="rIdResume409"/>
     <hyperlink ref="T188" ns1:id="rIdResume410"/>
     <hyperlink ref="T189" ns1:id="rIdResume411"/>
+    <hyperlink ref="T190" ns1:id="rIdResume412"/>
+    <hyperlink ref="T191" ns1:id="rIdResume413"/>
+    <hyperlink ref="T192" ns1:id="rIdResume414"/>
+    <hyperlink ref="T193" ns1:id="rIdResume415"/>
+    <hyperlink ref="T194" ns1:id="rIdResume416"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -36784,6 +37194,1494 @@
       </c>
       <c r="I617" t="str" s="3">
         <v>resume_sources_20261009.json 正文/首次失败</v>
+      </c>
+    </row>
+    <row r="618" ht="52.5" customHeight="1">
+      <c r="A618" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B618" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C618" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D618" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E618" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "移动平台环境感知" "开放" 基金；定位：西北工业大学计算机学院2026年暑期校园开放日活动方案-计算机学院；2025年西北工业大学计算机学院暑期校园开放日暨研究生招生宣传日活动方案-计算机学院</v>
+      </c>
+      <c r="F618" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G618" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H618" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1599/29795.htm
+https://jsj.nwpu.edu.cn/info/1599/26125.htm</v>
+      </c>
+      <c r="I618" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第220项</v>
+      </c>
+    </row>
+    <row r="619" ht="52.5" customHeight="1">
+      <c r="A619" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B619" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C619" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D619" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E619" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "智能感知与计算" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F619" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G619" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H619" t="str" s="3"/>
+      <c r="I619" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第221项</v>
+      </c>
+    </row>
+    <row r="620" ht="52.5" customHeight="1">
+      <c r="A620" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B620" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C620" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D620" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E620" t="str" s="3">
+        <v>查询：site:ia.cas.cn "模式识别实验室" "开放基金"；定位：多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所；多模态人工智能系统全国重点实验室副主任招聘启事----中国科学院自动化研究所</v>
+      </c>
+      <c r="F620" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G620" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H620" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html
+https://www.ia.cas.cn/qtgn/tzgg/202510/t20251030_7999657.html</v>
+      </c>
+      <c r="I620" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第222项</v>
+      </c>
+    </row>
+    <row r="621" ht="52.5" customHeight="1">
+      <c r="A621" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B621" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C621" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D621" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E621" t="str" s="3">
+        <v>查询：site:ia.cas.cn "国家专用集成电路" "开放" 基金；定位：为所长助理；徐波、卢汉清为模式识别国家重点实验室副主任，易建强为复杂系统与智能科学开放实验室副主任，彭思龙为国家专用集成电路设计工程技术研究中心副主任，刘迎建为文字识别工程中心主任，张立清为文字识别工程中心副主任，孙敦圣为综合自动化技术工程中心主任，邹益仁、林红权为综合自动化技术工程中心副主任，王飞跃为智能控制与系统工程中心主任，杨一平为互联网研究发展中心主任，王晓功为互联网研究发展中心副主任，房自正为所综合办公室副主任。任期自 2002 年 2 月 27 日起至研究所本届领导班子届满。；紫东太初大模型研究中心----中国科学院自动化研究所；多模态人工智能系统全国重点实验室----中国科学院自动化研究所；复杂系统认知与决策国家级重点实验室----中国科学院自动化研究所</v>
+      </c>
+      <c r="F621" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G621" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H621" t="str" s="3">
+        <v>https://www.ia.cas.cn/60zhsq/sqlsyg/202005/W020200518639608854729.pdf
+https://ia.cas.cn/jgsz/kyxt/zztc/
+https://ia.cas.cn/jgsz/kyxt/dmtrgzn/
+https://www.ia.cas.cn/jgsz/kyxt/fzxtrz/</v>
+      </c>
+      <c r="I621" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第223项</v>
+      </c>
+    </row>
+    <row r="622" ht="52.5" customHeight="1">
+      <c r="A622" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B622" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C622" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D622" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E622" t="str" s="3">
+        <v>查询：site:um.edu.mo "robot" "open" "fund" 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F622" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G622" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H622" t="str" s="3"/>
+      <c r="I622" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第224项</v>
+      </c>
+    </row>
+    <row r="623" ht="52.5" customHeight="1">
+      <c r="A623" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B623" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C623" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D623" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E623" t="str" s="3">
+        <v>查询：site:um.edu.mo "laboratories" "Intelligent" "Unmanned"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F623" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G623" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H623" t="str" s="3"/>
+      <c r="I623" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第225项</v>
+      </c>
+    </row>
+    <row r="624" ht="52.5" customHeight="1">
+      <c r="A624" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B624" t="str" s="3">
+        <v>香港理工大学南京/无锡研究院</v>
+      </c>
+      <c r="C624" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D624" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E624" t="str" s="3">
+        <v>查询：site:polyu.edu.hk 南京 无锡 开放 基金 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F624" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G624" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H624" t="str" s="3"/>
+      <c r="I624" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第226项</v>
+      </c>
+    </row>
+    <row r="625" ht="52.5" customHeight="1">
+      <c r="A625" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B625" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C625" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D625" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E625" t="str" s="3">
+        <v>查询：site:cqu.edu.cn "机器人" "开放基金" 2026 2027；定位：山区土木工程安全与韧性全国重点实验室 2025年度开放基金申请指南-重庆大学土木工程学院；重庆大学高端装备机械传动全国重点实验室2024年度开放基金课题申请指南-高端装备机械传动全国重点实验室（测试版）；重庆大学机械传动国家重点实验室2023年度开放基金课题申请指南-高端装备机械传动全国重点实验室（测试版）；邹莱/教授-高端装备机械传动全国重点实验室（测试版）；信息物理社会可信服务计算教育部重点实验室_重庆大学CPS实验室</v>
+      </c>
+      <c r="F625" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G625" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H625" t="str" s="3">
+        <v>https://civil.cqu.edu.cn/info/1327/17713.htm
+https://slmt.cqu.edu.cn/info/10663/89470.htm
+https://slmt.cqu.edu.cn/info/10447/89244.htm
+https://slmt.cqu.edu.cn/info/10513/86893.htm
+https://cps.cqu.edu.cn/</v>
+      </c>
+      <c r="I625" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第227项</v>
+      </c>
+    </row>
+    <row r="626" ht="52.5" customHeight="1">
+      <c r="A626" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B626" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C626" t="str" s="3">
+        <v>广东</v>
+      </c>
+      <c r="D626" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E626" t="str" s="3">
+        <v>查询：site:scut.edu.cn "人机共生" 开放基金；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F626" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G626" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H626" t="str" s="3"/>
+      <c r="I626" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第228项</v>
+      </c>
+    </row>
+    <row r="627" ht="52.5" customHeight="1">
+      <c r="A627" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B627" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C627" t="str" s="3">
+        <v>广东</v>
+      </c>
+      <c r="D627" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E627" t="str" s="3">
+        <v>查询：site:scut.edu.cn "智能无人船" 开放基金；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F627" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G627" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H627" t="str" s="3"/>
+      <c r="I627" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第229项</v>
+      </c>
+    </row>
+    <row r="628" ht="52.5" customHeight="1">
+      <c r="A628" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B628" t="str" s="3">
+        <v>南京/苏州/无锡/常州/镇江/扬州高校</v>
+      </c>
+      <c r="C628" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D628" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E628" t="str" s="3">
+        <v>查询：2027 开放基金 机器人 江苏 苏州 常州 镇江 扬州；定位：江苏省人民政府 今日江苏 江苏积极建设省级具身智能创新平台 七个获省级资金支持项目加速落地</v>
+      </c>
+      <c r="F628" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G628" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H628" t="str" s="3">
+        <v>https://www.jiangsu.gov.cn/art/2026/3/27/art_60095_11750391.html</v>
+      </c>
+      <c r="I628" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第230项</v>
+      </c>
+    </row>
+    <row r="629" ht="52.5" customHeight="1">
+      <c r="A629" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B629" t="str" s="3">
+        <v>中科院自动化所</v>
+      </c>
+      <c r="C629" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D629" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E629" t="str" s="3">
+        <v>查询：site:ia.cas.cn "分子影像实验室" 开放课题 2026 2027；定位：分子影像实验室----中国科学院自动化研究所；工业视觉智能装备技术工程实验室----中国科学院自动化研究所；模式识别实验室----中国科学院自动化研究所；多模态人工智能系统全国重点实验室----中国科学院自动化研究所</v>
+      </c>
+      <c r="F629" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G629" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H629" t="str" s="3">
+        <v>https://www.ia.cas.cn/jgsz/kyxt/bm9/
+https://ia.cas.cn/jgsz/kyxt/gysj/
+https://www.ia.cas.cn/jgsz/kyxt/ZNGZ/
+https://ia.cas.cn/jgsz/kyxt/dmtrgzn/</v>
+      </c>
+      <c r="I629" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第231项</v>
+      </c>
+    </row>
+    <row r="630" ht="52.5" customHeight="1">
+      <c r="A630" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B630" t="str" s="3">
+        <v>甘肃省高校/科研平台</v>
+      </c>
+      <c r="C630" t="str" s="3">
+        <v>甘肃</v>
+      </c>
+      <c r="D630" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E630" t="str" s="3">
+        <v>查询：甘肃 机器人 重点实验室 开放基金 2026；定位：2026年度开放基金评审结果公告；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；2026年度开放课题申请公告；&lt;p style="color: rgb(0, 0, 0); font-size: 24px; font-weight: bold; text-align: center; padding: 0px 4px 0px 0px; margin: 0px 0px 10px; border-width: medium; border-style: none; border-color: currentcolor; border-image: initial; line-height: normal;"&gt;&lt;span data-index="7"&gt;&lt;strong&gt;&lt;span data-index="6" style="font-family: 宋体, SimSun;"&gt;西北生态环境资源研究院油气资源研究中心/甘肃省油气资源勘探与评价重点实验室2026年开放基金申请指南&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;_中国科学院西北生态环境资源研究院油气资源研究中心；机器人工程与智能制造南充市重点实验室-油气装备教育部重点实验室2026年度联合开放基金评审结果公示-西南石油大学机电工程学院；管理办法----机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="F630" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G630" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H630" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://lig.cas.cn/xwzx/zhxw/202606/t20260615_841862.html
+https://www.swpu.edu.cn/jdy/info/1040/32450.htm
+https://rlab.sia.cas.cn/kfjj/glbf/</v>
+      </c>
+      <c r="I630" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第232项</v>
+      </c>
+    </row>
+    <row r="631" ht="52.5" customHeight="1">
+      <c r="A631" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B631" t="str" s="3">
+        <v>宁夏高校/科研平台</v>
+      </c>
+      <c r="C631" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D631" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E631" t="str" s="3">
+        <v>查询：宁夏 智能 机器人 实验室 开放基金 2026；定位：多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；警用智能机器人达州市重点实验室2026年度开放基金拟立项项目公示-警用智能机器人达州市重点实验室；管理办法----机器人与智能系统全国重点实验室；警用智能机器人达州市重点实验室2026年度开放基金申报公告-警用智能机器人达州市重点实验室；智能算法安全全国重点实验室2026年度开放课题申请指南--智能算法安全全国重点实验室；关于2026年宁波市空间智能与数字衍生重点实验室开放基金资助名单资助名单公布的通知-宁波数字孪生（东方理工）研究院</v>
+      </c>
+      <c r="F631" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G631" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H631" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://jqr.sasu.edu.cn/info/1009/1063.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://jqr.sasu.edu.cn/info/1009/1061.htm
+https://klais.ict.ac.cn/tzgg/xmzj/202609/t20260908_856264.html
+https://idt.eitech.edu.cn/2650.html</v>
+      </c>
+      <c r="I631" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第233项</v>
+      </c>
+    </row>
+    <row r="632" ht="52.5" customHeight="1">
+      <c r="A632" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B632" t="str" s="3">
+        <v>新疆高校/科研平台</v>
+      </c>
+      <c r="C632" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D632" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E632" t="str" s="3">
+        <v>查询：新疆 机器人 控制 实验室 开放基金 2026；定位：2026年度开放基金评审结果公告；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；中国石油大学(北京)克拉玛依校区新疆油气智能勘探与开发重点实验室；智能感知与人机协同教育部重点实验室2026年度开放课题申请指南；管理办法----机器人与智能系统全国重点实验室；警用智能机器人达州市重点实验室2026年度开放基金拟立项项目公示-警用智能机器人达州市重点实验室</v>
+      </c>
+      <c r="F632" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G632" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H632" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://www.cupk.edu.cn/olgas/c/2026-05-30/534544.shtml
+https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://jqr.sasu.edu.cn/info/1009/1063.htm</v>
+      </c>
+      <c r="I632" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第234项</v>
+      </c>
+    </row>
+    <row r="633" ht="52.5" customHeight="1">
+      <c r="A633" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B633" t="str" s="3">
+        <v>西藏高校/科研平台</v>
+      </c>
+      <c r="C633" t="str" s="3">
+        <v>西藏</v>
+      </c>
+      <c r="D633" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E633" t="str" s="3">
+        <v>查询：西藏 智能 感知 实验室 开放基金 2026；定位：高原智慧农业联合实验室在拉萨揭牌_西藏自治区人民政府；智能感知与人机协同教育部重点实验室2026年度开放课题申请指南；关于发布空间智能感知与大模型应用联合实验室2026年度开放基金课题申报指南的通知；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；高原智慧农业联合实验室在拉萨揭牌；青藏高原生物多样性与生态环境保护教育部重点实验室 2026年度开放课题申报通知-青藏高原生物多样性与生态环境保护教育部重点实验室</v>
+      </c>
+      <c r="F633" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G633" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H633" t="str" s="3">
+        <v>https://www.xizang.gov.cn/xwzx_406/dsdt/202608/t20260819_554342.html
+https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
+https://kyy.nuaa.edu.cn/2026/0604/c5817a400921/page.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://xz.people.com.cn/n2/2026/0819/c138901-41671553.html
+https://klbeqtp.utibet.edu.cn/info/1025/1223.htm</v>
+      </c>
+      <c r="I633" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第235项</v>
+      </c>
+    </row>
+    <row r="634" ht="52.5" customHeight="1">
+      <c r="A634" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B634" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C634" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D634" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E634" t="str" s="3">
+        <v>查询：site:nu.edu.cn 实验室 "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F634" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G634" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H634" t="str" s="3"/>
+      <c r="I634" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第236项</v>
+      </c>
+    </row>
+    <row r="635" ht="52.5" customHeight="1">
+      <c r="A635" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B635" t="str" s="3">
+        <v>西藏大学/农牧科学院</v>
+      </c>
+      <c r="C635" t="str" s="3">
+        <v>西藏</v>
+      </c>
+      <c r="D635" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E635" t="str" s="3">
+        <v>查询：site:utibet.edu.cn "开放" "智能" 基金；定位：国家开放大学西藏分部2026年春季学期期末考试致考生的一封信-国家开放大学西藏分部；国家开放大学致全体考生的一封信-国家开放大学西藏分部；关于我院组织开展“体验科技魅力”开放日活动-西藏大学信息科学技术学院；国家开放大学西藏分部</v>
+      </c>
+      <c r="F635" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G635" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H635" t="str" s="3">
+        <v>https://gkxzfb.utibet.edu.cn/info/1014/1261.htm
+https://gkxzfb.utibet.edu.cn/info/1014/1199.htm
+https://it.utibet.edu.cn/info/1030/1036.htm
+https://gkxzfb.utibet.edu.cn/</v>
+      </c>
+      <c r="I635" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第237项</v>
+      </c>
+    </row>
+    <row r="636" ht="52.5" customHeight="1">
+      <c r="A636" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B636" t="str" s="3">
+        <v>甘肃省高校/研究所</v>
+      </c>
+      <c r="C636" t="str" s="3">
+        <v>甘肃</v>
+      </c>
+      <c r="D636" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E636" t="str" s="3">
+        <v>查询：site:gs.gov.cn "智能" "重点实验室" 名单；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F636" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G636" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H636" t="str" s="3"/>
+      <c r="I636" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第238项</v>
+      </c>
+    </row>
+    <row r="637" ht="52.5" customHeight="1">
+      <c r="A637" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B637" t="str" s="3">
+        <v>新疆高校/兵团科研平台</v>
+      </c>
+      <c r="C637" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D637" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E637" t="str" s="3">
+        <v>查询：site:kjj.xjbt.gov.cn "钢结构智能制造" 开放课题 2026；定位：科学技术局、科协--通知公告--建筑钢结构智能制造技术兵团重点实验室2026年开放课题申报指南</v>
+      </c>
+      <c r="F637" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G637" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H637" t="str" s="3">
+        <v>https://kjj.xjbt.gov.cn/c/2026-04-01/8477891.shtml</v>
+      </c>
+      <c r="I637" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第239项</v>
+      </c>
+    </row>
+    <row r="638" ht="52.5" customHeight="1">
+      <c r="A638" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B638" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C638" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D638" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E638" t="str" s="3">
+        <v>查询：site:nu.edu.cn "重点实验室" "机器人"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F638" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G638" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H638" t="str" s="3"/>
+      <c r="I638" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第240项</v>
+      </c>
+    </row>
+    <row r="639" ht="52.5" customHeight="1">
+      <c r="A639" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B639" t="str" s="3">
+        <v>兰州理工大学</v>
+      </c>
+      <c r="C639" t="str" s="3">
+        <v>甘肃</v>
+      </c>
+      <c r="D639" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E639" t="str" s="3">
+        <v>查询：site:lut.edu.cn "机器人" "开放基金" 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F639" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G639" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H639" t="str" s="3"/>
+      <c r="I639" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第241项</v>
+      </c>
+    </row>
+    <row r="640" ht="52.5" customHeight="1">
+      <c r="A640" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B640" t="str" s="3">
+        <v>西藏自治区农牧科学院</v>
+      </c>
+      <c r="C640" t="str" s="3">
+        <v>西藏</v>
+      </c>
+      <c r="D640" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E640" t="str" s="3">
+        <v>查询："高原智慧农业联合实验室" "开放基金"；定位：水土保持与荒漠化整治全国重点实验室2026年度实验室开放基金项目申报指南----水土保持与荒漠化整治全国重点实验室</v>
+      </c>
+      <c r="F640" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G640" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H640" t="str" s="3">
+        <v>https://skl.iswc.cas.cn/tzgg/202512/t20251204_803767.html</v>
+      </c>
+      <c r="I640" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第242项</v>
+      </c>
+    </row>
+    <row r="641" ht="52.5" customHeight="1">
+      <c r="A641" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B641" t="str" s="3">
+        <v>新疆工程学院/新疆大学</v>
+      </c>
+      <c r="C641" t="str" s="3">
+        <v>新疆</v>
+      </c>
+      <c r="D641" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E641" t="str" s="3">
+        <v>查询：新疆工程学院 新疆大学 智能控制 开放基金 2026；定位：智能空地融合载具及管控教育部工程研究中心2026年度开放基金项目申报通知；新疆煤炭资源绿色开采教育部重点实验室开放课题指南（2026年）-新疆工程学院；煤炭精细勘探与智能开发全国重点实验室-新疆工程学院联合基金管理办法（2025）-煤炭精细勘探与智能开发全国重点实验室；GK2026-172（3） 新疆工程学院煤炭绿色智能开发实验教学示范中心—专业实验教学平台采购项目（三次）公开招标公告_新疆维吾尔自治区_</v>
+      </c>
+      <c r="F641" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G641" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H641" t="str" s="3">
+        <v>https://jybgczx.xhu.edu.cn/aa/a4/c11041a240292/page.htm
+https://www.xjie.edu.cn/info/1061/15798.htm
+https://skl.cumt.edu.cn/info/1149/3767.htm
+https://yzb.caigou2003.com/detail/2097311761790402560</v>
+      </c>
+      <c r="I641" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第243项</v>
+      </c>
+    </row>
+    <row r="642" ht="52.5" customHeight="1">
+      <c r="A642" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B642" t="str" s="3">
+        <v>教育部科研平台名录</v>
+      </c>
+      <c r="C642" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D642" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E642" t="str" s="3">
+        <v>查询：site:moe.gov.cn 重点实验室 名单 机器人 感知 2025；定位：教育部关于部分国家重点实验室主任和学术委员会主任聘任的通知 - 中华人民共和国教育部政府门户网站</v>
+      </c>
+      <c r="F642" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G642" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H642" t="str" s="3">
+        <v>https://www.moe.gov.cn/jyb_xxgk/gk_gbgg/moe_0/moe_1133/moe_1147/tnull_14506.html</v>
+      </c>
+      <c r="I642" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第244项</v>
+      </c>
+    </row>
+    <row r="643" ht="52.5" customHeight="1">
+      <c r="A643" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B643" t="str" s="3">
+        <v>教育部工程研究中心名录</v>
+      </c>
+      <c r="C643" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D643" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E643" t="str" s="3">
+        <v>查询：site:moe.gov.cn 工程研究中心 名单 机器人 智能 2025；定位：直属高校国家实验室、国家重点实验室、国家工程研究中心、国家工程技术研究中心、国家人文社科基地情况 - 中华人民共和国教育部政府门户网站；关于聘任部分教育部工程研究中心主任的通知 - 中华人民共和国教育部政府门户网站</v>
+      </c>
+      <c r="F643" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G643" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H643" t="str" s="3">
+        <v>https://www.moe.gov.cn/srcsite/A14/A14_other/200602/t20060219_75852.html
+https://www.moe.gov.cn/srcsite/A16/s3336/200512/t20051231_82265.html</v>
+      </c>
+      <c r="I643" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第245项</v>
+      </c>
+    </row>
+    <row r="644" ht="52.5" customHeight="1">
+      <c r="A644" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B644" t="str" s="3">
+        <v>省属高校重点实验室名录</v>
+      </c>
+      <c r="C644" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D644" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E644" t="str" s="3">
+        <v>查询：省属高校 重点实验室 机器人 开放基金 2026 2027；定位：关于征集安徽省人形机器人重点实验室2026年度开放基金指南建议的通知 - 江淮实验室；2026年度开放基金课题申报通知-智能机器人湖北省重点实验室；安徽省特种重载机器人重点实验室2026年度开放基金申请指南 -特种重载机器人安徽省重点实验室；江苏省具身智能工业机器人及其人机协作高校重点实验室开放课题管理办法-电气与自动化工程学院；关于江苏省具身智能机器人技术重点实验室2026年开放课题申报工作的通知；2026年度开放研究基金申请指南-数字教育湖北省重点实验室</v>
+      </c>
+      <c r="F644" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G644" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H644" t="str" s="3">
+        <v>https://www.jhatc.cn/html/mobile/kexue/pingtaichanpin/2098331115939979266.html
+https://robot.wit.edu.cn/info/1017/1552.htm
+https://robotlab.ahut.edu.cn/info/1549/1412.htm
+https://dqxylib.szut.edu.cn/info/1016/27682.htm
+https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
+https://hrcei.ccnu.edu.cn/info/1203/3415.htm</v>
+      </c>
+      <c r="I644" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第246项</v>
+      </c>
+    </row>
+    <row r="645" ht="52.5" customHeight="1">
+      <c r="A645" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B645" t="str" s="3">
+        <v>宁夏大学科研平台</v>
+      </c>
+      <c r="C645" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D645" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E645" t="str" s="3">
+        <v>查询：宁夏大学 科研平台 重点实验室 机械 人工智能；定位：机械工程学院科研实验室基本情况简介-宁夏大学机械工程学院；宁夏智能装备CAE重点实验室简介-宁夏大学机械工程学院；脑机智能技术教育部重点实验室；宁夏智能装备CAE重点实验室学术委员会第一次会议召开-宁夏大学机械工程学院；关于印发《宁夏大学科技创新平台建设与；宁夏“东数西算”人工智能与信息安全重点实验室揭牌仪式在我校举行-宁夏大学</v>
+      </c>
+      <c r="F645" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G645" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H645" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/info/1262/6093.htm
+https://jxgc.nxu.edu.cn/info/1262/5535.htm
+https://ai.nuaa.edu.cn/2026/0322/c19394a395058/page.htm
+https://jxgc.nxu.edu.cn/info/1262/4083.htm
+https://nxy.nxu.edu.cn/__local/C/F5/02/7FF0B933EE7AA97E48FA71AF85D_7441B8C3_57882.pdf
+https://www.nxu.edu.cn/info/1569/31334.htm</v>
+      </c>
+      <c r="I645" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第247项</v>
+      </c>
+    </row>
+    <row r="646" ht="52.5" customHeight="1">
+      <c r="A646" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B646" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C646" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D646" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E646" t="str" s="3">
+        <v>查询：site:nxu.edu.cn 开放基金 智能装备 CAE；定位：机械工程学院科研实验室基本情况简介-宁夏大学机械工程学院；宁夏智能装备CAE重点实验室学术委员会第一次会议召开-宁夏大学机械工程学院；2019年度宁夏智能装备CAE重点实验室开放基金申请通知-宁夏大学机械工程学院；宁夏智能装备CAE重点实验室仪器设备开放使用管理办法（试行）-宁夏大学机械工程学院；宁夏智能装备CAE重点实验室简介-宁夏大学机械工程学院</v>
+      </c>
+      <c r="F646" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G646" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H646" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/info/1262/6093.htm
+https://jxgc.nxu.edu.cn/info/1262/4083.htm
+https://jxgc.nxu.edu.cn/info/1262/4078.htm
+https://jxgc.nxu.edu.cn/info/1262/4151.htm
+https://jxgc.nxu.edu.cn/info/1262/5535.htm</v>
+      </c>
+      <c r="I646" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第248项</v>
+      </c>
+    </row>
+    <row r="647" ht="52.5" customHeight="1">
+      <c r="A647" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B647" t="str" s="3">
+        <v>宁夏大学/六盘山实验室</v>
+      </c>
+      <c r="C647" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D647" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E647" t="str" s="3">
+        <v>查询：六盘山实验室 开放基金 2026 2027；定位：关于生态环境部危险废物鉴别与风险控制重点实验室2026年度开放基金申请的通知_中国环境科学研究院；2026年实验室开放课题基金申请指南-光子传输与通信全国重点实验室官方网站-Powered by PageAdmin 博达；中国标准化研究院2026年度省部级重点&lt;br&gt;实验室开放基金项目申报指南；2027年精密大地测量与定位全国重点实验室开放研究基金指南----精密大地测量与定位全国重点实验室；中药资源与中药化学湖北省重点实验室2026~2027年度 开放基金申请指南-中药资源与中药化学湖北省重点实验室；粒子天体物理全国重点实验室开放基金课题申请指南----粒子天体物理全国重点实验室</v>
+      </c>
+      <c r="F647" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G647" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H647" t="str" s="3">
+        <v>https://www.craes.cn/tzgg/tz/xxgk/202608/t20260810_1163824.shtml
+https://ofcl.pku.edu.cn/info/1006/3502.htm
+https://www.cnis.ac.cn/tzgg/202609/t20260904_63600.html
+https://sklpg.apm.ac.cn/jlyhz/jfkt/202609/t20260928_858526.html
+https://klrccm.hbucm.edu.cn/info/1006/1613.htm
+https://www.ihep.ac.cn/astro/kxyj/xwdt/2026/202609/t20260901_8276232.html</v>
+      </c>
+      <c r="I647" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第249项</v>
+      </c>
+    </row>
+    <row r="648" ht="52.5" customHeight="1">
+      <c r="A648" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B648" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C648" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D648" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E648" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "脑机智能技术" 开放基金；定位：南京航空航天大学主页平台管理系统 脑机智能技术教育部重点实验室--中文主页--关于组织脑机智能技术教育部重点实验室2024年度开放课题申报通知；南京航空航天大学主页平台管理系统 秦杰--中文主页--首页；南京航空航天大学主页平台管理系统 wanghaibo--Home--Home；南京航空航天大学主页平台管理系统 Qin Jie--Home--Research Field；南京航空航天大学主页平台管理系统 脑机智能技术教育部重点实验室--中文主页--首页；南京航空航天大学主页平台管理系统 Qin Jie--Home--Paper Publications</v>
+      </c>
+      <c r="F648" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G648" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H648" t="str" s="3">
+        <v>https://bmi.nuaa.edu.cn/article/417830/content/1334.htm
+https://faculty.nuaa.edu.cn/qinjie/zh_CN/index.htm
+https://faculty.nuaa.edu.cn/wanghaibo/en/index.htm
+https://faculty.nuaa.edu.cn/qinjie/en/yjgk/383498/list/index.htm
+https://bmi.nuaa.edu.cn/
+https://faculty.nuaa.edu.cn/qinjie/en/lwcg/383499/list/index.htm</v>
+      </c>
+      <c r="I648" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第250项</v>
+      </c>
+    </row>
+    <row r="649" ht="52.5" customHeight="1">
+      <c r="A649" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B649" t="str" s="3">
+        <v>江淮实验室</v>
+      </c>
+      <c r="C649" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D649" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E649" t="str" s="3">
+        <v>查询：site:jhatc.cn "2026" "开放基金" 申请；定位：关于征集安徽省人形机器人重点实验室2026年度开放基金指南建议的通知 - 江淮实验室；江淮实验室；江淮实验室；江淮实验室；江淮实验室-科研进展；江淮实验室</v>
+      </c>
+      <c r="F649" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G649" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H649" t="str" s="3">
+        <v>https://www.jhatc.cn/html/mobile/kexue/pingtaichanpin/2098331115939979266.html
+https://www.jhatc.cn/
+https://www.jhatc.cn/html/mobile/kexue/index.html
+https://www.jhatc.cn/html/web/
+https://www.jhatc.cn/html/web/kexue/pingtaichanpin/index.html
+https://www.jhatc.cn/html/mobile/news/xingyedongtai/2046492958026493953.html</v>
+      </c>
+      <c r="I649" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第251项</v>
+      </c>
+    </row>
+    <row r="650" ht="52.5" customHeight="1">
+      <c r="A650" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B650" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C650" t="str" s="3">
+        <v>宁夏</v>
+      </c>
+      <c r="D650" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E650" t="str" s="3">
+        <v>查询：site:nxu.edu.cn "CAE" "开放基金" 2026 2027；定位：机械工程学院科研实验室基本情况简介-宁夏大学机械工程学院；宁夏智能装备CAE重点实验室学术委员会第一次会议召开-宁夏大学机械工程学院；2019年度宁夏智能装备CAE重点实验室开放基金申请通知-宁夏大学机械工程学院</v>
+      </c>
+      <c r="F650" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G650" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H650" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/info/1262/6093.htm
+https://jxgc.nxu.edu.cn/info/1262/4083.htm
+https://jxgc.nxu.edu.cn/info/1262/4078.htm</v>
+      </c>
+      <c r="I650" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第252项</v>
+      </c>
+    </row>
+    <row r="651" ht="52.5" customHeight="1">
+      <c r="A651" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B651" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C651" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D651" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E651" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "脑机智能技术" "2026" "开放课题"；定位：南京航空航天大学主页平台管理系统 wanghaibo--Home--Home；南京航空航天大学主页平台管理系统 张玉哲--中文主页--首页</v>
+      </c>
+      <c r="F651" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G651" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H651" t="str" s="3">
+        <v>https://faculty.nuaa.edu.cn/wanghaibo/en/index.htm
+https://faculty.nuaa.edu.cn/zhangyuzhe/zh_CN/index/422112/list/index.htm</v>
+      </c>
+      <c r="I651" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第253项</v>
+      </c>
+    </row>
+    <row r="652" ht="52.5" customHeight="1">
+      <c r="A652" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B652" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C652" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D652" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E652" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "脑机智能技术" "2027" "开放课题"；定位：南京航空航天大学主页平台管理系统 Zhang Yuzhe--Home--Home</v>
+      </c>
+      <c r="F652" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G652" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H652" t="str" s="3">
+        <v>https://faculty.nuaa.edu.cn/zhangyuzhe/en/more/422127/jsjjgd/index.htm</v>
+      </c>
+      <c r="I652" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第254项</v>
+      </c>
+    </row>
+    <row r="653" ht="52.5" customHeight="1">
+      <c r="A653" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B653" t="str" s="3">
+        <v>中央高校外部开放项目</v>
+      </c>
+      <c r="C653" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D653" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E653" t="str" s="3">
+        <v>查询："基本科研业务费" "校外" "开放课题" 2026 机器人；定位：图像信息处理与智能控制教育部重点实验室2026年度开放课题指南；关于申请2026年度南京航空航天大学基本科研业务费民航飞机健康监测与智能维护重点实验室自主课题的通知；关于征集“风能太阳能利用关键技术研究”项目开放课题的通知-风能太阳能利用技术教育部重点实验室；贵州省生态特色食品新质化加工与贮藏 全省重点实验室开放课题申请指南；东南大学“复杂工程系统测量与控制”教育部重点实验室2024年度开放课题指南；2026年行星地质与深空探测湖北省重点实验室 开放基金申请指南-地球科学学院</v>
+      </c>
+      <c r="F653" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G653" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H653" t="str" s="3">
+        <v>https://aia.hust.edu.cn/info/1174/11568.htm
+https://cca.nuaa.edu.cn/_t862/2026/0627/c15585a402933/page.htm
+https://fntyn.imut.edu.cn/info/1011/1412.htm
+https://st.gzu.edu.cn/2026/0316/c17883a265809/page.htm
+https://automation.seu.edu.cn/2024/0320/c24460a484504/page.htm
+https://dxy.cug.edu.cn/info/1035/9306.htm</v>
+      </c>
+      <c r="I653" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第255项</v>
+      </c>
+    </row>
+    <row r="654" ht="52.5" customHeight="1">
+      <c r="A654" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B654" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C654" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D654" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E654" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "高安全系统" "2024" "开放课题"；定位：关于组织高安全系统的软件开发与验证技术工业和信息化部重点实验室2024年度开放课题申报通知；南京航空航天大学主页平台管理系统 杨志斌--中文主页--首页；南京航空航天大学主页平台管理系统 Yang Zhibin--Home--Home</v>
+      </c>
+      <c r="F654" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G654" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H654" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0412/c10849a335982/page.psp
+https://faculty.nuaa.edu.cn/yangzhibin/zh_CN/index.htm
+https://faculty.nuaa.edu.cn/yangzhibin/en/index/162516/list/index.htm</v>
+      </c>
+      <c r="I654" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第256项</v>
+      </c>
+    </row>
+    <row r="655" ht="52.5" customHeight="1">
+      <c r="A655" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B655" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C655" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D655" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E655" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "模式分析与机器智能" "2024" "开放课题"；定位：关于组织模式分析与机器智能工业和信息化部重点实验室2024年度开放课题申报通知；南京航空航天大学主页平台管理系统 陈想--中文主页--首页；南京航空航天大学主页平台管理系统 Chen Xiang--Home--Home</v>
+      </c>
+      <c r="F655" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G655" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H655" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0420/c10849a336622/page.psp
+https://faculty.nuaa.edu.cn/ChenXiang/zh_CN/index/413113/list/index.htm
+https://faculty.nuaa.edu.cn/chenxiang1/en/more/413128/jsjjgd/index.htm</v>
+      </c>
+      <c r="I655" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第257项</v>
+      </c>
+    </row>
+    <row r="656" ht="52.5" customHeight="1">
+      <c r="A656" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B656" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C656" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D656" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E656" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "高安全系统" "2026" "开放课题"；定位：南京航空航天大学主页平台管理系统 杨志斌--中文主页--首页；南京航空航天大学主页平台管理系统 Yang Zhibin--Home--Home</v>
+      </c>
+      <c r="F656" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G656" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H656" t="str" s="3">
+        <v>https://faculty.nuaa.edu.cn/yangzhibin/zh_CN/index/162501/list/index.htm
+https://faculty.nuaa.edu.cn/yangzhibin/en/index/162516/list/index.htm</v>
+      </c>
+      <c r="I656" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第258项</v>
+      </c>
+    </row>
+    <row r="657" ht="52.5" customHeight="1">
+      <c r="A657" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B657" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C657" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D657" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E657" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "模式分析与机器智能" "2026" "开放课题"；定位：南京航空航天大学主页平台管理系统 陈想--中文主页--首页</v>
+      </c>
+      <c r="F657" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G657" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H657" t="str" s="3">
+        <v>https://faculty.nuaa.edu.cn/ChenXiang/zh_CN/index.htm</v>
+      </c>
+      <c r="I657" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第259项</v>
+      </c>
+    </row>
+    <row r="658" ht="52.5" customHeight="1">
+      <c r="A658" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B658" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C658" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D658" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E658" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "高安全系统" "2027" "开放课题"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F658" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G658" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H658" t="str" s="3"/>
+      <c r="I658" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第260项</v>
+      </c>
+    </row>
+    <row r="659" ht="52.5" customHeight="1">
+      <c r="A659" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B659" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C659" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D659" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E659" t="str" s="3">
+        <v>查询：site:nuaa.edu.cn "模式分析与机器智能" "2027" "开放课题"；定位：南京航空航天大学主页平台管理系统 陈想--中文主页--首页；南京航空航天大学主页平台管理系统 陈想--中文主页--首页；南京航空航天大学主页平台管理系统 Chen Xiang--Home--Home</v>
+      </c>
+      <c r="F659" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G659" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H659" t="str" s="3">
+        <v>https://faculty.nuaa.edu.cn/ChenXiang/zh_CN/index.htm
+https://faculty.nuaa.edu.cn/ChenXiang/zh_CN/index/413113/list/index.htm
+https://faculty.nuaa.edu.cn/chenxiang1/en/more/413128/jsjjgd/index.htm</v>
+      </c>
+      <c r="I659" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第261项</v>
+      </c>
+    </row>
+    <row r="660" ht="52.5" customHeight="1">
+      <c r="A660" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B660" t="str" s="3">
+        <v>扬州大学</v>
+      </c>
+      <c r="C660" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D660" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E660" t="str" s="3">
+        <v>查询：site:yzu.edu.cn 科研平台 机器人 重点实验室 开放基金；定位：扬州大学江苏省重点实验室；化学化工学院发展基金-扬州大学教育发展基金会捐赠平台</v>
+      </c>
+      <c r="F660" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G660" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H660" t="str" s="3">
+        <v>https://sjxy.yzu.edu.cn/__local/E/BB/8C/8CDF21785A7954A24B8CC2A0313_7EEBF50C_3292A.pdf?e=.pdf
+https://giving.yzu.edu.cn/project.action?id=500</v>
+      </c>
+      <c r="I660" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第262项</v>
+      </c>
+    </row>
+    <row r="661" ht="52.5" customHeight="1">
+      <c r="A661" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B661" t="str" s="3">
+        <v>江苏科技大学/常州大学</v>
+      </c>
+      <c r="C661" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D661" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E661" t="str" s="3">
+        <v>查询：江苏科技大学 常州大学 机器人 实验室 开放基金 2026；定位：江苏省具身智能工业机器人及其人机协作高校重点实验室开放课题管理办法-电气与自动化工程学院；关于组织申报2026年常州市科技项目-智能制造龙城实验室开放课题的通知；关于江苏省具身智能机器人技术重点实验室2026年开放课题申报工作的通知；智能感知与人机协同教育部重点实验室2026年度开放课题申请指南；2026年度开放课题申请公告；图像信息处理与智能控制教育部重点实验室2026年度开放课题指南</v>
+      </c>
+      <c r="F661" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G661" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H661" t="str" s="3">
+        <v>https://dqxylib.szut.edu.cn/info/1016/27682.htm
+https://iimt.cczu.edu.cn/2026/0519/c22023a415871/page.htm
+https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
+https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://aia.hust.edu.cn/info/1174/11568.htm</v>
+      </c>
+      <c r="I661" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第263项</v>
+      </c>
+    </row>
+    <row r="662" ht="52.5" customHeight="1">
+      <c r="A662" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B662" t="str" s="3">
+        <v>宁夏大学</v>
+      </c>
+      <c r="C662" t="str" s="3">
+        <v>宁夏·银川</v>
+      </c>
+      <c r="D662" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E662" t="str" s="3">
+        <v>宁夏智能装备CAE重点实验室；2019；N041；官方2019公告已读；具体任务附件首次读取失败</v>
+      </c>
+      <c r="F662" t="str" s="3">
+        <v>年度任务PDF首次无法读取；补机器人/自主装备具体任务证据，若无则剔除；另核管理条例、成果/IP、经费外拨及限定单位。2026—2027定向搜索未定位新公告。此前误用nu.edu.cn的空结果不作宁夏大学证据，正确域名nxu.edu.cn。</v>
+      </c>
+      <c r="G662" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H662" t="str" s="3">
+        <v>https://jxgc.nxu.edu.cn/info/1262/4078.htm</v>
+      </c>
+      <c r="I662" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="663" ht="52.5" customHeight="1">
+      <c r="A663" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B663" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C663" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D663" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E663" t="str" s="3">
+        <v>脑机智能技术教育部重点实验室；2024；N042；官方2024年度正式公告正文已核；模板首次读取失败</v>
+      </c>
+      <c r="F663" t="str" s="3">
+        <v>正文资金、年龄、限项、合作、成果已核；2024模板DOC首次失败（页面显示DOCX名但链接实际DOC），经费外拨、IP、邮寄地址待补。2026—2027查询仅定位2024，不能当当前窗口。</v>
+      </c>
+      <c r="G663" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H663" t="str" s="3">
+        <v>https://bmi.nuaa.edu.cn/article/417830/content/1334.htm</v>
+      </c>
+      <c r="I663" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="664" ht="52.5" customHeight="1">
+      <c r="A664" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B664" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C664" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D664" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E664" t="str" s="3">
+        <v>模式分析与机器智能工业和信息化部重点实验室；2024；N043；官方公告搜索摘要及缓存片段；直接访问首次超时</v>
+      </c>
+      <c r="F664" t="str" s="3">
+        <v>首次网页超时，不反复访问；需完整公告文字/网页PDF及全部附件，补准确截止、成果署名、经费外拨、IP、提交。2026—2027搜索仅定位2024批次，不当当前正式公告。</v>
+      </c>
+      <c r="G664" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H664" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0420/c10849a336622/page.psp</v>
+      </c>
+      <c r="I664" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="665" ht="52.5" customHeight="1">
+      <c r="A665" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B665" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C665" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D665" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E665" t="str" s="3">
+        <v>高安全系统的软件开发与验证技术工业和信息化部重点实验室；2024；N044；官方公告搜索缓存部分正文；直接访问首次超时</v>
+      </c>
+      <c r="F665" t="str" s="3">
+        <v>年度完整方向/任务证据不足，若仅软件验证而无无人自主机器人任务则剔除；获取全文和申请模板，补资格、成果/IP、经费外拨、联系与窗口。2026—2027未定位新正式公告。</v>
+      </c>
+      <c r="G665" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H665" t="str" s="3">
+        <v>https://cs.nuaa.edu.cn/_t2321/2024/0412/c10849a335982/page.psp</v>
+      </c>
+      <c r="I665" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="666" ht="52.5" customHeight="1">
+      <c r="A666" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B666" t="str" s="3">
+        <v>南京航空航天大学</v>
+      </c>
+      <c r="C666" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D666" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E666" t="str" s="3">
+        <v>民航飞机健康监测与智能维护重点实验室（基本科研业务费自主课题）；2026；N045；官方2026通知搜索摘要，直接网页首次483受阻</v>
+      </c>
+      <c r="F666" t="str" s="3">
+        <v>首次483，不再尝试；下载或复制完整2026公告及全部附件，先核真实机器人任务与外部资格；再补金额、截止、周期、成果、IP、合作、外协接收单位及提交。未进入首页。</v>
+      </c>
+      <c r="G666" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H666" t="str" s="3">
+        <v>https://cca.nuaa.edu.cn/_t862/2026/0627/c15585a402933/page.htm</v>
+      </c>
+      <c r="I666" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
       </c>
     </row>
   </sheetData>
@@ -37032,64 +38930,64 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="18" t="str">
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B12" s="13" t="d">
+      <c r="B12" t="n" s="13">
+        <v>45412</v>
+      </c>
+      <c r="C12" t="str" s="14">
+        <v>南京航空航天大学·脑机智能技术教育部重点实验室</v>
+      </c>
+      <c r="D12" t="str" s="15">
+        <v>脑机接口、脑机融合智能、脑信号感知传输、脑机控制交互技术；并列多模态融合、鲁棒机器学习等方向。</v>
+      </c>
+      <c r="E12" t="str" s="15">
+        <v>3—5万元/项；拟15—20项</v>
+      </c>
+      <c r="F12" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B13" s="13" t="d">
         <v>2026-01-19T00:00:00.000Z</v>
       </c>
-      <c r="C12" s="14" t="str">
+      <c r="C13" s="14" t="str">
         <v>香港理工大学·超精密加工技术全国重点实验室</v>
       </c>
-      <c r="D12" s="15" t="str">
+      <c r="D13" s="15" t="str">
         <v>新一代超精密加工技术及智能化装备</v>
       </c>
-      <c r="E12" s="15" t="str">
+      <c r="E13" s="15" t="str">
         <v>每项6—8万港元（不能写人民币）。</v>
       </c>
-      <c r="F12" s="16" t="str">
+      <c r="F13" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="13" ht="96" customHeight="1">
-      <c r="A13" t="str" s="18">
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B13" t="n" s="13">
+      <c r="B14" t="n" s="13">
         <v>45775</v>
       </c>
-      <c r="C13" t="str" s="14">
+      <c r="C14" t="str" s="14">
         <v>香港理工大学·Research Centre for Low Altitude Economy（低空经济研究中心）</v>
       </c>
-      <c r="D13" t="str" s="15">
+      <c r="D14" t="str" s="15">
         <v>明确可靠感知、鲁棒控制、应急安全飞行及无人机应用；须关联低空经济。</v>
       </c>
-      <c r="E13" t="str" s="15">
+      <c r="E14" t="str" s="15">
         <v>平台/应用≤50万港币；基础≤30万港币；探索15万港币</v>
       </c>
-      <c r="F13" t="str" s="16">
+      <c r="F14" t="str" s="16">
         <v>正式指南</v>
-      </c>
-    </row>
-    <row r="14" ht="66" customHeight="1">
-      <c r="A14" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B14" s="13" t="d">
-        <v>2018-06-30T00:00:00.000Z</v>
-      </c>
-      <c r="C14" s="14" t="str">
-        <v>广东工业大学·微电子精密制造技术与装备教育部重点实验室（现网站名：电子精密制造装备及技术）</v>
-      </c>
-      <c r="D14" s="15" t="str">
-        <v>精密操作机器人机构优化、复杂机电系统精密运动控制、视觉定位、少自由度精密操作机器人</v>
-      </c>
-      <c r="E14" s="15" t="str">
-        <v>平均2—3万元</v>
-      </c>
-      <c r="F14" s="16" t="str">
-        <v>公告</v>
       </c>
     </row>
     <row r="15" ht="66" customHeight="1">
@@ -37097,16 +38995,16 @@
         <v>已截止</v>
       </c>
       <c r="B15" s="13" t="d">
-        <v>2023-10-15T00:00:00.000Z</v>
+        <v>2018-06-30T00:00:00.000Z</v>
       </c>
       <c r="C15" s="14" t="str">
-        <v>中国科学院深圳先进技术研究院·广东省机器人与智能系统重点实验室（智能仿生研究中心）</v>
+        <v>广东工业大学·微电子精密制造技术与装备教育部重点实验室（现网站名：电子精密制造装备及技术）</v>
       </c>
       <c r="D15" s="15" t="str">
-        <v>穿戴、工业、软体及康复机器人</v>
+        <v>精密操作机器人机构优化、复杂机电系统精密运动控制、视觉定位、少自由度精密操作机器人</v>
       </c>
       <c r="E15" s="15" t="str">
-        <v>5—10万元（2023年度）</v>
+        <v>平均2—3万元</v>
       </c>
       <c r="F15" s="16" t="str">
         <v>公告</v>
@@ -37117,16 +39015,16 @@
         <v>已截止</v>
       </c>
       <c r="B16" s="13" t="d">
-        <v>2024-11-29T00:00:00.000Z</v>
+        <v>2023-10-15T00:00:00.000Z</v>
       </c>
       <c r="C16" s="14" t="str">
-        <v>广东工业大学·广东省智能决策与协同控制重点实验室</v>
+        <v>中国科学院深圳先进技术研究院·广东省机器人与智能系统重点实验室（智能仿生研究中心）</v>
       </c>
       <c r="D16" s="15" t="str">
-        <v>无人自主系统的深度/强化学习优化决策、状态估计与协同控制</v>
+        <v>穿戴、工业、软体及康复机器人</v>
       </c>
       <c r="E16" s="15" t="str">
-        <v>5—10万元</v>
+        <v>5—10万元（2023年度）</v>
       </c>
       <c r="F16" s="16" t="str">
         <v>公告</v>
@@ -37137,13 +39035,13 @@
         <v>已截止</v>
       </c>
       <c r="B17" s="13" t="d">
-        <v>2026-01-05T00:00:00.000Z</v>
+        <v>2024-11-29T00:00:00.000Z</v>
       </c>
       <c r="C17" s="14" t="str">
-        <v>哈尔滨工业大学（深圳）·先进运动控制技术与现代自动化装备重点实验室</v>
+        <v>广东工业大学·广东省智能决策与协同控制重点实验室</v>
       </c>
       <c r="D17" s="15" t="str">
-        <v>机器人运动控制、柔性操作及现代自动化装备</v>
+        <v>无人自主系统的深度/强化学习优化决策、状态估计与协同控制</v>
       </c>
       <c r="E17" s="15" t="str">
         <v>5—10万元</v>
@@ -37157,16 +39055,16 @@
         <v>已截止</v>
       </c>
       <c r="B18" s="13" t="d">
-        <v>2026-03-31T00:00:00.000Z</v>
+        <v>2026-01-05T00:00:00.000Z</v>
       </c>
       <c r="C18" s="14" t="str">
-        <v>人工智能与数字经济广东省实验室（深圳）·光明实验室2026年首轮开放课题</v>
+        <v>哈尔滨工业大学（深圳）·先进运动控制技术与现代自动化装备重点实验室</v>
       </c>
       <c r="D18" s="15" t="str">
-        <v>多模态世界模型、智能体感知交互、3D/4D重建及可交互场景；与M097第二批分别记录</v>
+        <v>机器人运动控制、柔性操作及现代自动化装备</v>
       </c>
       <c r="E18" s="15" t="str">
-        <v>30—100万元/项</v>
+        <v>5—10万元</v>
       </c>
       <c r="F18" s="16" t="str">
         <v>公告</v>
@@ -37177,17 +39075,16 @@
         <v>已截止</v>
       </c>
       <c r="B19" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C19" s="14" t="str">
-        <v>深圳市人工智能与机器人研究院AIRS·医疗机器人方向开放课题</v>
+        <v>人工智能与数字经济广东省实验室（深圳）·光明实验室2026年首轮开放课题</v>
       </c>
       <c r="D19" s="15" t="str">
-        <v>医疗机器人、内窥镜感知与导航</v>
+        <v>多模态世界模型、智能体感知交互、3D/4D重建及可交互场景；与M097第二批分别记录</v>
       </c>
       <c r="E19" s="15" t="str">
-        <v>原则10万元/项，不超过5项，实际按研究内容与评审意见；
-不限制各方向项目数量。</v>
+        <v>30—100万元/项</v>
       </c>
       <c r="F19" s="16" t="str">
         <v>公告</v>
@@ -37198,16 +39095,17 @@
         <v>已截止</v>
       </c>
       <c r="B20" s="13" t="d">
-        <v>2026-08-24T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C20" s="14" t="str">
-        <v>深圳光明实验室·人工智能与数字经济广东省实验室</v>
+        <v>深圳市人工智能与机器人研究院AIRS·医疗机器人方向开放课题</v>
       </c>
       <c r="D20" s="15" t="str">
-        <v>面向具身任务的世界模型、三维/四维交互与验证</v>
+        <v>医疗机器人、内窥镜感知与导航</v>
       </c>
       <c r="E20" s="15" t="str">
-        <v>一般60万元、重大100万元、开放30万元</v>
+        <v>原则10万元/项，不超过5项，实际按研究内容与评审意见；
+不限制各方向项目数量。</v>
       </c>
       <c r="F20" s="16" t="str">
         <v>公告</v>
@@ -37218,16 +39116,16 @@
         <v>已截止</v>
       </c>
       <c r="B21" s="13" t="d">
-        <v>2025-10-15T00:00:00.000Z</v>
+        <v>2026-08-24T00:00:00.000Z</v>
       </c>
       <c r="C21" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
+        <v>深圳光明实验室·人工智能与数字经济广东省实验室</v>
       </c>
       <c r="D21" s="15" t="str">
-        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
+        <v>面向具身任务的世界模型、三维/四维交互与验证</v>
       </c>
       <c r="E21" s="15" t="str">
-        <v>5—8万元</v>
+        <v>一般60万元、重大100万元、开放30万元</v>
       </c>
       <c r="F21" s="16" t="str">
         <v>公告</v>
@@ -37238,16 +39136,16 @@
         <v>已截止</v>
       </c>
       <c r="B22" s="13" t="d">
-        <v>2026-05-11T00:00:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C22" s="14" t="str">
-        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D22" s="15" t="str">
-        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
+        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
       </c>
       <c r="E22" s="15" t="str">
-        <v>10万元/项；每方向1项</v>
+        <v>5—8万元</v>
       </c>
       <c r="F22" s="16" t="str">
         <v>公告</v>
@@ -37258,16 +39156,16 @@
         <v>已截止</v>
       </c>
       <c r="B23" s="13" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-11T00:00:00.000Z</v>
       </c>
       <c r="C23" s="14" t="str">
-        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
+        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
       </c>
       <c r="D23" s="15" t="str">
-        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
+        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
       </c>
       <c r="E23" s="15" t="str">
-        <v>5—10万元</v>
+        <v>10万元/项；每方向1项</v>
       </c>
       <c r="F23" s="16" t="str">
         <v>公告</v>
@@ -37278,16 +39176,16 @@
         <v>已截止</v>
       </c>
       <c r="B24" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-05-29T00:00:00.000Z</v>
       </c>
       <c r="C24" s="14" t="str">
-        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
+        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
       </c>
       <c r="D24" s="15" t="str">
-        <v>地下空间具身智能感知、定位与点云建模</v>
+        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
       </c>
       <c r="E24" s="15" t="str">
-        <v>一般≥2万元；重点≥3万元</v>
+        <v>5—10万元</v>
       </c>
       <c r="F24" s="16" t="str">
         <v>公告</v>
@@ -37298,16 +39196,16 @@
         <v>已截止</v>
       </c>
       <c r="B25" s="13" t="d">
-        <v>2026-07-31T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C25" s="14" t="str">
-        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
+        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
       </c>
       <c r="D25" s="15" t="str">
-        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
+        <v>地下空间具身智能感知、定位与点云建模</v>
       </c>
       <c r="E25" s="15" t="str">
-        <v>30—90万元（无人机监视反制专项）</v>
+        <v>一般≥2万元；重点≥3万元</v>
       </c>
       <c r="F25" s="16" t="str">
         <v>公告</v>
@@ -37318,16 +39216,16 @@
         <v>已截止</v>
       </c>
       <c r="B26" s="13" t="d">
-        <v>2026-08-28T00:00:00.000Z</v>
+        <v>2026-07-31T00:00:00.000Z</v>
       </c>
       <c r="C26" s="14" t="str">
-        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
+        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
       </c>
       <c r="D26" s="15" t="str">
-        <v>机器人多接触规划、具身技能学习与运动行为</v>
+        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
       </c>
       <c r="E26" s="15" t="str">
-        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
+        <v>30—90万元（无人机监视反制专项）</v>
       </c>
       <c r="F26" s="16" t="str">
         <v>公告</v>
@@ -37338,57 +39236,57 @@
         <v>已截止</v>
       </c>
       <c r="B27" s="13" t="d">
-        <v>2025-08-10T00:00:00.000Z</v>
+        <v>2026-08-28T00:00:00.000Z</v>
       </c>
       <c r="C27" s="14" t="str">
-        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
       </c>
       <c r="D27" s="15" t="str">
-        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+        <v>机器人多接触规划、具身技能学习与运动行为</v>
       </c>
       <c r="E27" s="15" t="str">
-        <v>5—10万元/项</v>
+        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
       </c>
       <c r="F27" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="28" ht="79.5" customHeight="1">
+    <row r="28" ht="66" customHeight="1">
       <c r="A28" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B28" s="13" t="d">
+        <v>2025-08-10T00:00:00.000Z</v>
+      </c>
+      <c r="C28" s="14" t="str">
+        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="D28" s="15" t="str">
+        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+      </c>
+      <c r="E28" s="15" t="str">
+        <v>5—10万元/项</v>
+      </c>
+      <c r="F28" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="29" ht="79.5" customHeight="1">
+      <c r="A29" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B29" s="13" t="d">
         <v>2026-05-06T00:00:00.000Z</v>
       </c>
-      <c r="C28" s="14" t="str">
+      <c r="C29" s="14" t="str">
         <v>煤炭智能开采与岩层控制全国重点实验室（北京；具体依托机构待核，沈阳化工为转载单位）·煤炭智能开采与岩层控制全国重点实验室</v>
       </c>
-      <c r="D28" s="15" t="str">
+      <c r="D29" s="15" t="str">
         <v>机械臂—底座耦合振动、末端自适应定位（依托机构尚待确认）</v>
       </c>
-      <c r="E28" s="15" t="str">
+      <c r="E29" s="15" t="str">
         <v>2026年度实验室设开放基金项目共计40项，其中重点项目4项，每项资助研究金额为45-65万元；
 一般项目36项，每项资助研究金额为15-25万元。</v>
-      </c>
-      <c r="F28" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="29" ht="66" customHeight="1">
-      <c r="A29" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B29" s="13" t="d">
-        <v>2026-08-20T00:00:00.000Z</v>
-      </c>
-      <c r="C29" s="14" t="str">
-        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
-      </c>
-      <c r="D29" s="15" t="str">
-        <v>自主无人系统及机器人研究</v>
-      </c>
-      <c r="E29" s="15" t="str">
-        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F29" s="16" t="str">
         <v>公告</v>
@@ -37399,16 +39297,16 @@
         <v>已截止</v>
       </c>
       <c r="B30" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-08-20T00:00:00.000Z</v>
       </c>
       <c r="C30" s="14" t="str">
-        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
+        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D30" s="15" t="str">
-        <v>无人越野平台世界模型、具身感知与控制</v>
+        <v>自主无人系统及机器人研究</v>
       </c>
       <c r="E30" s="15" t="str">
-        <v>重点20—30万元、一般5—10万元</v>
+        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F30" s="16" t="str">
         <v>公告</v>
@@ -37419,16 +39317,16 @@
         <v>已截止</v>
       </c>
       <c r="B31" s="13" t="d">
-        <v>2026-09-20T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C31" s="14" t="str">
-        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
+        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
       </c>
       <c r="D31" s="15" t="str">
-        <v>平台具身智能与异构智能体协同</v>
+        <v>无人越野平台世界模型、具身感知与控制</v>
       </c>
       <c r="E31" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>重点20—30万元、一般5—10万元</v>
       </c>
       <c r="F31" s="16" t="str">
         <v>公告</v>
@@ -37439,16 +39337,16 @@
         <v>已截止</v>
       </c>
       <c r="B32" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2026-04-10T00:00:00.000Z</v>
       </c>
       <c r="C32" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室</v>
+        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）·建筑钢结构智能制造技术兵团重点实验室</v>
       </c>
       <c r="D32" s="15" t="str">
-        <v>工业机器人传动、机电耦合与高端装备传动</v>
+        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
       </c>
       <c r="E32" s="15" t="str">
-        <v>面上5—8万元。</v>
+        <v>不超过2万元</v>
       </c>
       <c r="F32" s="16" t="str">
         <v>公告</v>
@@ -37459,16 +39357,16 @@
         <v>已截止</v>
       </c>
       <c r="B33" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-09-20T00:00:00.000Z</v>
       </c>
       <c r="C33" s="14" t="str">
-        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
+        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
       </c>
       <c r="D33" s="15" t="str">
-        <v>具身智能世界模型与开放环境视觉感知</v>
+        <v>平台具身智能与异构智能体协同</v>
       </c>
       <c r="E33" s="15" t="str">
-        <v>3万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F33" s="16" t="str">
         <v>公告</v>
@@ -37479,16 +39377,16 @@
         <v>已截止</v>
       </c>
       <c r="B34" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C34" s="14" t="str">
-        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室</v>
       </c>
       <c r="D34" s="15" t="str">
-        <v>山区建造装备及机器人</v>
+        <v>工业机器人传动、机电耦合与高端装备传动</v>
       </c>
       <c r="E34" s="15" t="str">
-        <v>每项6万元。</v>
+        <v>面上5—8万元。</v>
       </c>
       <c r="F34" s="16" t="str">
         <v>公告</v>
@@ -37499,16 +39397,16 @@
         <v>已截止</v>
       </c>
       <c r="B35" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C35" s="14" t="str">
-        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
+        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
       </c>
       <c r="D35" s="15" t="str">
-        <v>桥梁检测机器人与无人巡检装备</v>
+        <v>具身智能世界模型与开放环境视觉感知</v>
       </c>
       <c r="E35" s="15" t="str">
-        <v>5—10万元</v>
+        <v>3万元</v>
       </c>
       <c r="F35" s="16" t="str">
         <v>公告</v>
@@ -37519,17 +39417,16 @@
         <v>已截止</v>
       </c>
       <c r="B36" s="13" t="d">
-        <v>2026-09-01T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C36" s="14" t="str">
-        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
+        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
       </c>
       <c r="D36" s="15" t="str">
-        <v>工业机器人及智能产线运维、故障预测与控制</v>
+        <v>山区建造装备及机器人</v>
       </c>
       <c r="E36" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>每项6万元。</v>
       </c>
       <c r="F36" s="16" t="str">
         <v>公告</v>
@@ -37540,17 +39437,16 @@
         <v>已截止</v>
       </c>
       <c r="B37" s="13" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C37" s="14" t="str">
-        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
+        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
       </c>
       <c r="D37" s="15" t="str">
-        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
+        <v>桥梁检测机器人与无人巡检装备</v>
       </c>
       <c r="E37" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F37" s="16" t="str">
         <v>公告</v>
@@ -37561,13 +39457,13 @@
         <v>已截止</v>
       </c>
       <c r="B38" s="13" t="d">
-        <v>2025-02-28T00:00:00.000Z</v>
+        <v>2026-09-01T00:00:00.000Z</v>
       </c>
       <c r="C38" s="14" t="str">
-        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
+        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
       </c>
       <c r="D38" s="15" t="str">
-        <v>重载机器人减速器、直驱电机及关键部件</v>
+        <v>工业机器人及智能产线运维、故障预测与控制</v>
       </c>
       <c r="E38" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -37582,16 +39478,17 @@
         <v>已截止</v>
       </c>
       <c r="B39" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="C39" s="14" t="str">
-        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
+        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
       </c>
       <c r="D39" s="15" t="str">
-        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
+        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
       </c>
       <c r="E39" s="15" t="str">
-        <v>重点20万元；一般10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F39" s="16" t="str">
         <v>公告</v>
@@ -37602,16 +39499,17 @@
         <v>已截止</v>
       </c>
       <c r="B40" s="13" t="d">
-        <v>2026-06-14T00:00:00.000Z</v>
+        <v>2025-02-28T00:00:00.000Z</v>
       </c>
       <c r="C40" s="14" t="str">
-        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
+        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
       </c>
       <c r="D40" s="15" t="str">
-        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
+        <v>重载机器人减速器、直驱电机及关键部件</v>
       </c>
       <c r="E40" s="15" t="str">
-        <v>10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F40" s="16" t="str">
         <v>公告</v>
@@ -37622,16 +39520,16 @@
         <v>已截止</v>
       </c>
       <c r="B41" s="13" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C41" s="14" t="str">
-        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
+        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
       </c>
       <c r="D41" s="15" t="str">
-        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
+        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
       </c>
       <c r="E41" s="15" t="str">
-        <v>其他一般≤10万、重点≤15万</v>
+        <v>重点20万元；一般10万元</v>
       </c>
       <c r="F41" s="16" t="str">
         <v>公告</v>
@@ -37642,16 +39540,16 @@
         <v>已截止</v>
       </c>
       <c r="B42" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-06-14T00:00:00.000Z</v>
       </c>
       <c r="C42" s="14" t="str">
-        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
+        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
       </c>
       <c r="D42" s="15" t="str">
-        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
+        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
       </c>
       <c r="E42" s="15" t="str">
-        <v>10—15万元</v>
+        <v>10万元</v>
       </c>
       <c r="F42" s="16" t="str">
         <v>公告</v>
@@ -37662,16 +39560,16 @@
         <v>已截止</v>
       </c>
       <c r="B43" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-09-24T00:00:00.000Z</v>
       </c>
       <c r="C43" s="14" t="str">
-        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
+        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
       </c>
       <c r="D43" s="15" t="str">
-        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
+        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
       </c>
       <c r="E43" s="15" t="str">
-        <v>3万元（首拨1万元，中期2万元）</v>
+        <v>其他一般≤10万、重点≤15万</v>
       </c>
       <c r="F43" s="16" t="str">
         <v>公告</v>
@@ -37682,17 +39580,16 @@
         <v>已截止</v>
       </c>
       <c r="B44" s="13" t="d">
-        <v>2022-10-30T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C44" s="14" t="str">
-        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
+        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
       </c>
       <c r="D44" s="15" t="str">
-        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
+        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>已核官方2022历史公告：5万元/项；
-未取得2026正式指南，不将历史额度视为当期额度。</v>
+        <v>10—15万元</v>
       </c>
       <c r="F44" s="16" t="str">
         <v>公告</v>
@@ -37703,16 +39600,16 @@
         <v>已截止</v>
       </c>
       <c r="B45" s="13" t="d">
-        <v>2022-11-04T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
+        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
+        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
       </c>
       <c r="E45" s="15" t="str">
-        <v>一般2万元；重点4—6万元</v>
+        <v>3万元（首拨1万元，中期2万元）</v>
       </c>
       <c r="F45" s="16" t="str">
         <v>公告</v>
@@ -37723,16 +39620,17 @@
         <v>已截止</v>
       </c>
       <c r="B46" s="13" t="d">
-        <v>2023-07-30T00:00:00.000Z</v>
+        <v>2022-10-30T00:00:00.000Z</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
+        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
+        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>拟资助8—10项；单项金额未载</v>
+        <v>已核官方2022历史公告：5万元/项；
+未取得2026正式指南，不将历史额度视为当期额度。</v>
       </c>
       <c r="F46" s="16" t="str">
         <v>公告</v>
@@ -37743,16 +39641,16 @@
         <v>已截止</v>
       </c>
       <c r="B47" s="13" t="d">
-        <v>2024-09-30T00:00:00.000Z</v>
+        <v>2022-11-04T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>南昌大学·智能机器人江西省重点实验室</v>
+        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>智能机器人机构、感知与控制</v>
+        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>重点3万元、一般2万元（2024年度）</v>
+        <v>一般2万元；重点4—6万元</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
@@ -37763,16 +39661,16 @@
         <v>已截止</v>
       </c>
       <c r="B48" s="13" t="d">
-        <v>2025-03-31T00:00:00.000Z</v>
+        <v>2023-07-30T00:00:00.000Z</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
+        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
+        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>2—3万元/项左右</v>
+        <v>拟资助8—10项；单项金额未载</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
@@ -37783,16 +39681,16 @@
         <v>已截止</v>
       </c>
       <c r="B49" s="13" t="d">
-        <v>2025-04-25T00:00:00.000Z</v>
+        <v>2024-09-30T00:00:00.000Z</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>南昌大学·智能机器人江西省重点实验室</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>仿生机器人、新型驱动与感知及仿生装备</v>
+        <v>智能机器人机构、感知与控制</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>5万元</v>
+        <v>重点3万元、一般2万元（2024年度）</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
@@ -37803,16 +39701,16 @@
         <v>已截止</v>
       </c>
       <c r="B50" s="13" t="d">
-        <v>2025-04-30T00:00:00.000Z</v>
+        <v>2025-03-31T00:00:00.000Z</v>
       </c>
       <c r="C50" s="14" t="str">
-        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
+        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
       </c>
       <c r="D50" s="15" t="str">
-        <v>共融机器人控制、复杂智能体系统协同与控制</v>
+        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
       </c>
       <c r="E50" s="15" t="str">
-        <v>评审确定</v>
+        <v>2—3万元/项左右</v>
       </c>
       <c r="F50" s="16" t="str">
         <v>公告</v>
@@ -37823,13 +39721,13 @@
         <v>已截止</v>
       </c>
       <c r="B51" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C51" s="14" t="str">
-        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D51" s="15" t="str">
-        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
+        <v>仿生机器人、新型驱动与感知及仿生装备</v>
       </c>
       <c r="E51" s="15" t="str">
         <v>5万元</v>
@@ -37843,16 +39741,16 @@
         <v>已截止</v>
       </c>
       <c r="B52" s="13" t="d">
-        <v>2025-09-20T00:00:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C52" s="14" t="str">
-        <v>同济大学·自主智能无人系统全国重点实验室</v>
+        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
       </c>
       <c r="D52" s="15" t="str">
-        <v>自主智能无人系统与机器人感知、决策、控制</v>
+        <v>共融机器人控制、复杂智能体系统协同与控制</v>
       </c>
       <c r="E52" s="15" t="str">
-        <v>一般5—10万元、重点20—30万元</v>
+        <v>评审确定</v>
       </c>
       <c r="F52" s="16" t="str">
         <v>公告</v>
@@ -37863,17 +39761,16 @@
         <v>已截止</v>
       </c>
       <c r="B53" s="13" t="d">
-        <v>2025-10-31T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C53" s="14" t="str">
-        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
+        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
       </c>
       <c r="D53" s="15" t="str">
-        <v>机器人技术与系统、机器人学习、感知与控制</v>
+        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
       </c>
       <c r="E53" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5万元</v>
       </c>
       <c r="F53" s="16" t="str">
         <v>公告</v>
@@ -37884,17 +39781,16 @@
         <v>已截止</v>
       </c>
       <c r="B54" s="13" t="d">
-        <v>2025-11-03T00:00:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C54" s="14" t="str">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
+        <v>同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D54" s="15" t="str">
-        <v>智能机器人感知、控制与系统</v>
+        <v>自主智能无人系统与机器人感知、决策、控制</v>
       </c>
       <c r="E54" s="15" t="str">
-        <v>校外开放基金1万元/项，拟5项；
-校内创新基金不同计划</v>
+        <v>一般5—10万元、重点20—30万元</v>
       </c>
       <c r="F54" s="16" t="str">
         <v>公告</v>
@@ -37905,16 +39801,17 @@
         <v>已截止</v>
       </c>
       <c r="B55" s="13" t="d">
-        <v>2025-11-07T00:00:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C55" s="14" t="str">
-        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
+        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
       </c>
       <c r="D55" s="15" t="str">
-        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
+        <v>机器人技术与系统、机器人学习、感知与控制</v>
       </c>
       <c r="E55" s="15" t="str">
-        <v>2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F55" s="16" t="str">
         <v>公告</v>
@@ -37925,16 +39822,17 @@
         <v>已截止</v>
       </c>
       <c r="B56" s="13" t="d">
-        <v>2025-11-14T00:00:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C56" s="14" t="str">
-        <v>上海交通大学·机械系统与振动全国重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D56" s="15" t="str">
-        <v>机器人设计、自主学习与神经接口</v>
+        <v>智能机器人感知、控制与系统</v>
       </c>
       <c r="E56" s="15" t="str">
-        <v>10—15万元</v>
+        <v>校外开放基金1万元/项，拟5项；
+校内创新基金不同计划</v>
       </c>
       <c r="F56" s="16" t="str">
         <v>公告</v>
@@ -37945,16 +39843,16 @@
         <v>已截止</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2025-11-21T00:00:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
+        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>机器人视觉相关计算与随机数学方法</v>
+        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>1—2万元</v>
+        <v>2万元</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
@@ -37965,16 +39863,16 @@
         <v>已截止</v>
       </c>
       <c r="B58" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C58" s="14" t="str">
-        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
+        <v>上海交通大学·机械系统与振动全国重点实验室</v>
       </c>
       <c r="D58" s="15" t="str">
-        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
+        <v>机器人设计、自主学习与神经接口</v>
       </c>
       <c r="E58" s="15" t="str">
-        <v>不超过3万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F58" s="16" t="str">
         <v>公告</v>
@@ -37985,16 +39883,16 @@
         <v>已截止</v>
       </c>
       <c r="B59" s="13" t="d">
-        <v>2025-12-20T00:00:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
+        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>山地农业机器人、果实收获视觉与智能农机</v>
+        <v>机器人视觉相关计算与随机数学方法</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>不超过5万元</v>
+        <v>1—2万元</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
@@ -38005,16 +39903,16 @@
         <v>已截止</v>
       </c>
       <c r="B60" s="13" t="d">
-        <v>2025-12-31T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
+        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
+        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>重点5万元、一般3万元</v>
+        <v>不超过3万元</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
@@ -38025,16 +39923,16 @@
         <v>已截止</v>
       </c>
       <c r="B61" s="13" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2025-12-20T00:00:00.000Z</v>
       </c>
       <c r="C61" s="14" t="str">
-        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
+        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
       </c>
       <c r="D61" s="15" t="str">
-        <v>深海无人潜航装备与智能控制</v>
+        <v>山地农业机器人、果实收获视觉与智能农机</v>
       </c>
       <c r="E61" s="15" t="str">
-        <v>不超过10万元</v>
+        <v>不超过5万元</v>
       </c>
       <c r="F61" s="16" t="str">
         <v>公告</v>
@@ -38045,16 +39943,16 @@
         <v>已截止</v>
       </c>
       <c r="B62" s="13" t="d">
-        <v>2026-01-31T00:00:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C62" s="14" t="str">
-        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
+        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
       </c>
       <c r="D62" s="15" t="str">
-        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
+        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
       </c>
       <c r="E62" s="15" t="str">
-        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
+        <v>重点5万元、一般3万元</v>
       </c>
       <c r="F62" s="16" t="str">
         <v>公告</v>
@@ -38065,16 +39963,16 @@
         <v>已截止</v>
       </c>
       <c r="B63" s="13" t="d">
-        <v>2026-03-10T00:00:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C63" s="14" t="str">
-        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
+        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
       </c>
       <c r="D63" s="15" t="str">
-        <v>工业机器人与柔性制造产线集成</v>
+        <v>深海无人潜航装备与智能控制</v>
       </c>
       <c r="E63" s="15" t="str">
-        <v>4万元</v>
+        <v>不超过10万元</v>
       </c>
       <c r="F63" s="16" t="str">
         <v>公告</v>
@@ -38085,16 +39983,16 @@
         <v>已截止</v>
       </c>
       <c r="B64" s="13" t="d">
-        <v>2026-03-20T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C64" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室</v>
+        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
       </c>
       <c r="D64" s="15" t="str">
-        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
+        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
       </c>
       <c r="E64" s="15" t="str">
-        <v>单项不超过10万元</v>
+        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
       </c>
       <c r="F64" s="16" t="str">
         <v>公告</v>
@@ -38105,16 +40003,16 @@
         <v>已截止</v>
       </c>
       <c r="B65" s="13" t="d">
-        <v>2026-04-10T00:00:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C65" s="14" t="str">
-        <v>新疆生产建设兵团相关单位·建筑钢结构智能制造技术兵团重点实验室</v>
+        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
       </c>
       <c r="D65" s="15" t="str">
-        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
+        <v>工业机器人与柔性制造产线集成</v>
       </c>
       <c r="E65" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>4万元</v>
       </c>
       <c r="F65" s="16" t="str">
         <v>公告</v>
@@ -38125,16 +40023,16 @@
         <v>已截止</v>
       </c>
       <c r="B66" s="13" t="d">
-        <v>2026-04-15T00:00:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C66" s="14" t="str">
-        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室</v>
       </c>
       <c r="D66" s="15" t="str">
-        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
+        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
       </c>
       <c r="E66" s="15" t="str">
-        <v>一般5—8万元；重点20万元</v>
+        <v>单项不超过10万元</v>
       </c>
       <c r="F66" s="16" t="str">
         <v>公告</v>
@@ -38145,16 +40043,16 @@
         <v>已截止</v>
       </c>
       <c r="B67" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C67" s="14" t="str">
-        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
+        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
       </c>
       <c r="D67" s="15" t="str">
-        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
+        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
       </c>
       <c r="E67" s="15" t="str">
-        <v>5万元</v>
+        <v>一般5—8万元；重点20万元</v>
       </c>
       <c r="F67" s="16" t="str">
         <v>公告</v>
@@ -38168,14 +40066,13 @@
         <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C68" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
+        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
       </c>
       <c r="D68" s="15" t="str">
-        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
+        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
       </c>
       <c r="E68" s="15" t="str">
-        <v>单项原则上不超过10万元；
-100万元是本批次总额，不是单项额度。</v>
+        <v>5万元</v>
       </c>
       <c r="F68" s="16" t="str">
         <v>公告</v>
@@ -38186,16 +40083,17 @@
         <v>已截止</v>
       </c>
       <c r="B69" s="13" t="d">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C69" s="14" t="str">
-        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
       </c>
       <c r="D69" s="15" t="str">
-        <v>无人系统多源感知、导航与控制</v>
+        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
       </c>
       <c r="E69" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>单项原则上不超过10万元；
+100万元是本批次总额，不是单项额度。</v>
       </c>
       <c r="F69" s="16" t="str">
         <v>公告</v>
@@ -38206,16 +40104,16 @@
         <v>已截止</v>
       </c>
       <c r="B70" s="13" t="d">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C70" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
       </c>
       <c r="D70" s="15" t="str">
-        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
+        <v>无人系统多源感知、导航与控制</v>
       </c>
       <c r="E70" s="15" t="str">
-        <v>5万元/项；拟8项</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F70" s="16" t="str">
         <v>公告</v>
@@ -38226,16 +40124,16 @@
         <v>已截止</v>
       </c>
       <c r="B71" s="13" t="d">
-        <v>2026-04-30T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C71" s="14" t="str">
-        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D71" s="15" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
       </c>
       <c r="E71" s="15" t="str">
-        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
+        <v>5万元/项；拟8项</v>
       </c>
       <c r="F71" s="16" t="str">
         <v>公告</v>
@@ -38249,13 +40147,13 @@
         <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C72" s="14" t="str">
-        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
+        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
       </c>
       <c r="D72" s="15" t="str">
-        <v>警用智能机器人与协同任务</v>
+        <v>智能无人系统感知、规划与控制</v>
       </c>
       <c r="E72" s="15" t="str">
-        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
+        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="F72" s="16" t="str">
         <v>公告</v>
@@ -38266,16 +40164,16 @@
         <v>已截止</v>
       </c>
       <c r="B73" s="13" t="d">
-        <v>2026-05-06T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C73" s="14" t="str">
-        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
+        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
       </c>
       <c r="D73" s="15" t="str">
-        <v>具身智能（仅保留正式指南第7项方向）</v>
+        <v>警用智能机器人与协同任务</v>
       </c>
       <c r="E73" s="15" t="str">
-        <v>10—15万元</v>
+        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="F73" s="16" t="str">
         <v>公告</v>
@@ -38286,16 +40184,16 @@
         <v>已截止</v>
       </c>
       <c r="B74" s="13" t="d">
-        <v>2026-05-14T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C74" s="14" t="str">
-        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
+        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
       </c>
       <c r="D74" s="15" t="str">
-        <v>具身机器人磨削、抛光及加工技能</v>
+        <v>具身智能（仅保留正式指南第7项方向）</v>
       </c>
       <c r="E74" s="15" t="str">
-        <v>一般1—2万元、重点3—5万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F74" s="16" t="str">
         <v>公告</v>
@@ -38306,16 +40204,16 @@
         <v>已截止</v>
       </c>
       <c r="B75" s="13" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-14T00:00:00.000Z</v>
       </c>
       <c r="C75" s="14" t="str">
-        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
+        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
       </c>
       <c r="D75" s="15" t="str">
-        <v>前沿交叉方向中的手术机器人应用与验证</v>
+        <v>具身机器人磨削、抛光及加工技能</v>
       </c>
       <c r="E75" s="15" t="str">
-        <v>4万元</v>
+        <v>一般1—2万元、重点3—5万元</v>
       </c>
       <c r="F75" s="16" t="str">
         <v>公告</v>
@@ -38326,16 +40224,16 @@
         <v>已截止</v>
       </c>
       <c r="B76" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C76" s="14" t="str">
-        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
+        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
       </c>
       <c r="D76" s="15" t="str">
-        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
+        <v>前沿交叉方向中的手术机器人应用与验证</v>
       </c>
       <c r="E76" s="15" t="str">
-        <v>不超过1万元</v>
+        <v>4万元</v>
       </c>
       <c r="F76" s="16" t="str">
         <v>公告</v>
@@ -38346,16 +40244,16 @@
         <v>已截止</v>
       </c>
       <c r="B77" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C77" s="14" t="str">
-        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
+        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
       </c>
       <c r="D77" s="15" t="str">
-        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
+        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
       </c>
       <c r="E77" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>不超过1万元</v>
       </c>
       <c r="F77" s="16" t="str">
         <v>公告</v>
@@ -38366,16 +40264,16 @@
         <v>已截止</v>
       </c>
       <c r="B78" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C78" s="14" t="str">
-        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
+        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
       </c>
       <c r="D78" s="15" t="str">
-        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
+        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
       </c>
       <c r="E78" s="15" t="str">
-        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F78" s="16" t="str">
         <v>公告</v>
@@ -38389,13 +40287,13 @@
         <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C79" s="14" t="str">
-        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
+        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
       </c>
       <c r="D79" s="15" t="str">
-        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
+        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
       </c>
       <c r="E79" s="15" t="str">
-        <v>原则5万元/项；可按评审增加，上限未载</v>
+        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
       </c>
       <c r="F79" s="16" t="str">
         <v>公告</v>
@@ -38406,16 +40304,16 @@
         <v>已截止</v>
       </c>
       <c r="B80" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C80" s="14" t="str">
-        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
+        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
       </c>
       <c r="D80" s="15" t="str">
-        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
+        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
       </c>
       <c r="E80" s="15" t="str">
-        <v>5万元/项；专项拟2项</v>
+        <v>原则5万元/项；可按评审增加，上限未载</v>
       </c>
       <c r="F80" s="16" t="str">
         <v>公告</v>
@@ -38426,16 +40324,16 @@
         <v>已截止</v>
       </c>
       <c r="B81" s="13" t="d">
-        <v>2026-07-12T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C81" s="14" t="str">
-        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
+        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
       </c>
       <c r="D81" s="15" t="str">
-        <v>无人机轨迹与协同、自主采样探测装备</v>
+        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
       </c>
       <c r="E81" s="15" t="str">
-        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
+        <v>5万元/项；专项拟2项</v>
       </c>
       <c r="F81" s="16" t="str">
         <v>公告</v>
@@ -38446,16 +40344,16 @@
         <v>已截止</v>
       </c>
       <c r="B82" s="13" t="d">
-        <v>2026-07-19T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C82" s="14" t="str">
-        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
+        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
       </c>
       <c r="D82" s="15" t="str">
-        <v>具身智能传感、闭环感知与人机交互意图识别</v>
+        <v>无人机轨迹与协同、自主采样探测装备</v>
       </c>
       <c r="E82" s="15" t="str">
-        <v>10万元</v>
+        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
       </c>
       <c r="F82" s="16" t="str">
         <v>公告</v>
@@ -38466,16 +40364,16 @@
         <v>已截止</v>
       </c>
       <c r="B83" s="13" t="d">
-        <v>2026-07-25T00:00:00.000Z</v>
+        <v>2026-07-19T00:00:00.000Z</v>
       </c>
       <c r="C83" s="14" t="str">
-        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
+        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
       </c>
       <c r="D83" s="15" t="str">
-        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
+        <v>具身智能传感、闭环感知与人机交互意图识别</v>
       </c>
       <c r="E83" s="15" t="str">
-        <v>2—4万元</v>
+        <v>10万元</v>
       </c>
       <c r="F83" s="16" t="str">
         <v>公告</v>
@@ -38486,16 +40384,16 @@
         <v>已截止</v>
       </c>
       <c r="B84" s="13" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-07-25T00:00:00.000Z</v>
       </c>
       <c r="C84" s="14" t="str">
-        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
+        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
       </c>
       <c r="D84" s="15" t="str">
-        <v>智能机器人信息感知、多源融合与控制</v>
+        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
       </c>
       <c r="E84" s="15" t="str">
-        <v>约2万元</v>
+        <v>2—4万元</v>
       </c>
       <c r="F84" s="16" t="str">
         <v>公告</v>
@@ -38506,16 +40404,16 @@
         <v>已截止</v>
       </c>
       <c r="B85" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C85" s="14" t="str">
-        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
+        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
       </c>
       <c r="D85" s="15" t="str">
-        <v>机器人集成与医疗康复智能制造装备</v>
+        <v>智能机器人信息感知、多源融合与控制</v>
       </c>
       <c r="E85" s="15" t="str">
-        <v>一般2万元、重点3万元</v>
+        <v>约2万元</v>
       </c>
       <c r="F85" s="16" t="str">
         <v>公告</v>
@@ -38529,13 +40427,13 @@
         <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C86" s="14" t="str">
-        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
+        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
       </c>
       <c r="D86" s="15" t="str">
-        <v>桥梁与水下缺陷无人机器人检测</v>
+        <v>机器人集成与医疗康复智能制造装备</v>
       </c>
       <c r="E86" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>一般2万元、重点3万元</v>
       </c>
       <c r="F86" s="16" t="str">
         <v>公告</v>
@@ -38546,16 +40444,16 @@
         <v>已截止</v>
       </c>
       <c r="B87" s="13" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C87" s="14" t="str">
-        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
+        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
       </c>
       <c r="D87" s="15" t="str">
-        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
+        <v>桥梁与水下缺陷无人机器人检测</v>
       </c>
       <c r="E87" s="15" t="str">
-        <v>5万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F87" s="16" t="str">
         <v>公告</v>
@@ -38566,16 +40464,16 @@
         <v>已截止</v>
       </c>
       <c r="B88" s="13" t="d">
-        <v>2026-08-30T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C88" s="14" t="str">
-        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
+        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
       </c>
       <c r="D88" s="15" t="str">
-        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
+        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
       </c>
       <c r="E88" s="15" t="str">
-        <v>重点5万元；一般2万元；共6—8项</v>
+        <v>5万元</v>
       </c>
       <c r="F88" s="16" t="str">
         <v>公告</v>
@@ -38586,16 +40484,16 @@
         <v>已截止</v>
       </c>
       <c r="B89" s="13" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-30T00:00:00.000Z</v>
       </c>
       <c r="C89" s="14" t="str">
-        <v>四川警察学院·智能警务四川省重点实验室</v>
+        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
       </c>
       <c r="D89" s="15" t="str">
-        <v>无人机、车辆与机器狗异构协同及应急救援</v>
+        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
       </c>
       <c r="E89" s="15" t="str">
-        <v>重点15万元、一般10万元、青年5万元</v>
+        <v>重点5万元；一般2万元；共6—8项</v>
       </c>
       <c r="F89" s="16" t="str">
         <v>公告</v>
@@ -38606,17 +40504,16 @@
         <v>已截止</v>
       </c>
       <c r="B90" s="13" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C90" s="14" t="str">
-        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
+        <v>四川警察学院·智能警务四川省重点实验室</v>
       </c>
       <c r="D90" s="15" t="str">
-        <v>特种机器人多源感知、轨迹与动力学控制</v>
+        <v>无人机、车辆与机器狗异构协同及应急救援</v>
       </c>
       <c r="E90" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>重点15万元、一般10万元、青年5万元</v>
       </c>
       <c r="F90" s="16" t="str">
         <v>公告</v>
@@ -38627,16 +40524,17 @@
         <v>已截止</v>
       </c>
       <c r="B91" s="13" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C91" s="14" t="str">
-        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
       </c>
       <c r="D91" s="15" t="str">
-        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+        <v>特种机器人多源感知、轨迹与动力学控制</v>
       </c>
       <c r="E91" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F91" s="16" t="str">
         <v>公告</v>
@@ -38647,40 +40545,39 @@
         <v>已截止</v>
       </c>
       <c r="B92" s="13" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="C92" s="14" t="str">
+        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+      </c>
+      <c r="D92" s="15" t="str">
+        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+      </c>
+      <c r="E92" s="15" t="str">
+        <v>不超过2万元</v>
+      </c>
+      <c r="F92" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="93" ht="66" customHeight="1">
+      <c r="A93" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B93" s="13" t="d">
         <v>2026-09-27T00:00:00.000Z</v>
       </c>
-      <c r="C92" s="14" t="str">
+      <c r="C93" s="14" t="str">
         <v>云南大学·云南省智能系统与计算重点实验室</v>
       </c>
-      <c r="D92" s="15" t="str">
+      <c r="D93" s="15" t="str">
         <v>低空无人系统集群协同（仅保留具体无人装备方向）</v>
       </c>
-      <c r="E92" s="15" t="str">
+      <c r="E93" s="15" t="str">
         <v>重点≤8万元；
 一般≤2万元；
 定向1万元。</v>
       </c>
-      <c r="F92" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="93" ht="66" customHeight="1">
-      <c r="A93" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B93" s="13" t="d">
-        <v>2026-10-05T00:00:00.000Z</v>
-      </c>
-      <c r="C93" s="14" t="str">
-        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
-      </c>
-      <c r="D93" s="15" t="str">
-        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
-      </c>
-      <c r="E93" s="15" t="str">
-        <v>重点60—100万元；
-一般15—20万元</v>
-      </c>
       <c r="F93" s="16" t="str">
         <v>公告</v>
       </c>
@@ -38690,16 +40587,17 @@
         <v>已截止</v>
       </c>
       <c r="B94" s="13" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-05T00:00:00.000Z</v>
       </c>
       <c r="C94" s="14" t="str">
-        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
+        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
       </c>
       <c r="D94" s="15" t="str">
-        <v>机器人遥操作、双臂操作与人机协同</v>
+        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
       </c>
       <c r="E94" s="15" t="str">
-        <v>公告未公布统一金额，评审确定。</v>
+        <v>重点60—100万元；
+一般15—20万元</v>
       </c>
       <c r="F94" s="16" t="str">
         <v>公告</v>
@@ -38713,13 +40611,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C95" s="14" t="str">
-        <v>中北大学·微纳器件与系统教育部重点实验室</v>
+        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
       </c>
       <c r="D95" s="15" t="str">
-        <v>微型机器人及微纳执行器、精密定位</v>
+        <v>机器人遥操作、双臂操作与人机协同</v>
       </c>
       <c r="E95" s="15" t="str">
-        <v>2—4万元</v>
+        <v>公告未公布统一金额，评审确定。</v>
       </c>
       <c r="F95" s="16" t="str">
         <v>公告</v>
@@ -38733,13 +40631,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C96" s="14" t="str">
-        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
+        <v>中北大学·微纳器件与系统教育部重点实验室</v>
       </c>
       <c r="D96" s="15" t="str">
-        <v>机器人机械臂抓取、路径规划与自主导航</v>
+        <v>微型机器人及微纳执行器、精密定位</v>
       </c>
       <c r="E96" s="15" t="str">
-        <v>一般2万元；重点4万元（以评审为准）</v>
+        <v>2—4万元</v>
       </c>
       <c r="F96" s="16" t="str">
         <v>公告</v>
@@ -38753,13 +40651,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C97" s="14" t="str">
-        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
+        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
       </c>
       <c r="D97" s="15" t="str">
-        <v>无人平台智能探测与多源感知</v>
+        <v>机器人机械臂抓取、路径规划与自主导航</v>
       </c>
       <c r="E97" s="15" t="str">
-        <v>2—4万元/项，拟5—8项</v>
+        <v>一般2万元；重点4万元（以评审为准）</v>
       </c>
       <c r="F97" s="16" t="str">
         <v>公告</v>
@@ -38773,36 +40671,36 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C98" s="14" t="str">
-        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
       </c>
       <c r="D98" s="15" t="str">
-        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+        <v>无人平台智能探测与多源感知</v>
       </c>
       <c r="E98" s="15" t="str">
-        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+        <v>2—4万元/项，拟5—8项</v>
       </c>
       <c r="F98" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="99" ht="96" customHeight="1">
-      <c r="A99" t="str" s="18">
+    <row r="99" ht="66" customHeight="1">
+      <c r="A99" s="18" t="str">
         <v>已截止</v>
       </c>
-      <c r="B99" t="n" s="13">
-        <v>46295</v>
-      </c>
-      <c r="C99" t="str" s="14">
-        <v>上海交通大学·海洋工程全国重点实验室</v>
-      </c>
-      <c r="D99" t="str" s="15">
-        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
-      </c>
-      <c r="E99" t="str" s="15">
-        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
-      </c>
-      <c r="F99" t="str" s="16">
-        <v>官方公告</v>
+      <c r="B99" s="13" t="d">
+        <v>2026-10-08T00:00:00.000Z</v>
+      </c>
+      <c r="C99" s="14" t="str">
+        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+      </c>
+      <c r="D99" s="15" t="str">
+        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+      </c>
+      <c r="E99" s="15" t="str">
+        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+      </c>
+      <c r="F99" s="16" t="str">
+        <v>公告</v>
       </c>
     </row>
     <row r="100" ht="96" customHeight="1">
@@ -38810,16 +40708,16 @@
         <v>已截止</v>
       </c>
       <c r="B100" t="n" s="13">
-        <v>45503</v>
+        <v>46295</v>
       </c>
       <c r="C100" t="str" s="14">
-        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
+        <v>上海交通大学·海洋工程全国重点实验室</v>
       </c>
       <c r="D100" t="str" s="15">
-        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
+        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
       </c>
       <c r="E100" t="str" s="15">
-        <v>3万元/项；计划10项。</v>
+        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
       </c>
       <c r="F100" t="str" s="16">
         <v>官方公告</v>
@@ -38830,16 +40728,16 @@
         <v>已截止</v>
       </c>
       <c r="B101" t="n" s="13">
-        <v>46006</v>
+        <v>45503</v>
       </c>
       <c r="C101" t="str" s="14">
-        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
+        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
       </c>
       <c r="D101" t="str" s="15">
-        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
+        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
       </c>
       <c r="E101" t="str" s="15">
-        <v>正文未公开具体资助金额。</v>
+        <v>3万元/项；计划10项。</v>
       </c>
       <c r="F101" t="str" s="16">
         <v>官方公告</v>
@@ -38850,16 +40748,16 @@
         <v>已截止</v>
       </c>
       <c r="B102" t="n" s="13">
-        <v>46193</v>
+        <v>46006</v>
       </c>
       <c r="C102" t="str" s="14">
-        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
+        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
       <c r="D102" t="str" s="15">
-        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
+        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
       </c>
       <c r="E102" t="str" s="15">
-        <v>一般项目≤5万元/项；计划12项。</v>
+        <v>正文未公开具体资助金额。</v>
       </c>
       <c r="F102" t="str" s="16">
         <v>官方公告</v>
@@ -38870,16 +40768,16 @@
         <v>已截止</v>
       </c>
       <c r="B103" t="n" s="13">
-        <v>44434</v>
+        <v>46193</v>
       </c>
       <c r="C103" t="str" s="14">
-        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
       </c>
       <c r="D103" t="str" s="15">
-        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
       </c>
       <c r="E103" t="str" s="15">
-        <v>重点2万元/项；一般1万元/项。</v>
+        <v>一般项目≤5万元/项；计划12项。</v>
       </c>
       <c r="F103" t="str" s="16">
         <v>官方公告</v>
@@ -38890,16 +40788,16 @@
         <v>已截止</v>
       </c>
       <c r="B104" t="n" s="13">
-        <v>45163</v>
+        <v>44434</v>
       </c>
       <c r="C104" t="str" s="14">
-        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
       </c>
       <c r="D104" t="str" s="15">
-        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
       </c>
       <c r="E104" t="str" s="15">
-        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+        <v>重点2万元/项；一般1万元/项。</v>
       </c>
       <c r="F104" t="str" s="16">
         <v>官方公告</v>
@@ -38910,16 +40808,16 @@
         <v>已截止</v>
       </c>
       <c r="B105" t="n" s="13">
-        <v>45991</v>
+        <v>45163</v>
       </c>
       <c r="C105" t="str" s="14">
-        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
       </c>
       <c r="D105" t="str" s="15">
-        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
       </c>
       <c r="E105" t="str" s="15">
-        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
       </c>
       <c r="F105" t="str" s="16">
         <v>官方公告</v>
@@ -38927,21 +40825,41 @@
     </row>
     <row r="106" ht="96" customHeight="1">
       <c r="A106" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B106" t="n" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C106" t="str" s="14">
+        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+      </c>
+      <c r="D106" t="str" s="15">
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+      </c>
+      <c r="E106" t="str" s="15">
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+      </c>
+      <c r="F106" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="107" ht="96" customHeight="1">
+      <c r="A107" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B106" t="n" s="13">
+      <c r="B107" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C106" t="str" s="14">
+      <c r="C107" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D106" t="str" s="15">
+      <c r="D107" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E106" t="str" s="15">
+      <c r="E107" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F106" t="str" s="16">
+      <c r="F107" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -38957,8 +40875,8 @@
     <hyperlink ref="F5" ns1:id="Rff2d595907084ed9"/>
     <hyperlink ref="C6" location="'02项目完整详情'!A61"/>
     <hyperlink ref="F6" ns1:id="R840dfc7ac2ef4322"/>
-    <hyperlink ref="C37" location="'02项目完整详情'!A113"/>
-    <hyperlink ref="F37" ns1:id="Re902984ea1114a1f"/>
+    <hyperlink ref="C39" location="'02项目完整详情'!A113"/>
+    <hyperlink ref="F39" ns1:id="Re902984ea1114a1f"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A62"/>
     <hyperlink ref="F7" ns1:id="Ra6ff56d69fd14f0d"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A63"/>
@@ -38967,196 +40885,198 @@
     <hyperlink ref="F9" ns1:id="R0efd7513d55943ed"/>
     <hyperlink ref="C10" location="'02项目完整详情'!A64"/>
     <hyperlink ref="F10" ns1:id="Ra45cae74f44f4c7f"/>
-    <hyperlink ref="C12" location="'02项目完整详情'!A65"/>
-    <hyperlink ref="F12" ns1:id="Rb60ba16ed31b49e2"/>
-    <hyperlink ref="C14" location="'02项目完整详情'!A140"/>
-    <hyperlink ref="F14" ns1:id="R54631d6f63ff4a84"/>
-    <hyperlink ref="C15" location="'02项目完整详情'!A82"/>
-    <hyperlink ref="F15" ns1:id="R5d6c0e16ca9148f1"/>
-    <hyperlink ref="C16" location="'02项目完整详情'!A141"/>
-    <hyperlink ref="F16" ns1:id="R29345038c30a4733"/>
-    <hyperlink ref="C38" location="'02项目完整详情'!A85"/>
-    <hyperlink ref="F38" ns1:id="R486c032b769d4524"/>
-    <hyperlink ref="C17" location="'02项目完整详情'!A99"/>
-    <hyperlink ref="F17" ns1:id="R19ee0f6cf8d14ed3"/>
-    <hyperlink ref="C18" location="'02项目完整详情'!A143"/>
-    <hyperlink ref="F18" ns1:id="R66d112d84a8644fb"/>
-    <hyperlink ref="C19" location="'02项目完整详情'!A122"/>
-    <hyperlink ref="F19" ns1:id="R83b69720fcfc4e60"/>
-    <hyperlink ref="C20" location="'02项目完整详情'!A127"/>
-    <hyperlink ref="F20" ns1:id="Ra979348b05084966"/>
-    <hyperlink ref="C21" location="'02项目完整详情'!A66"/>
-    <hyperlink ref="F21" ns1:id="R4dc201fc29cb4ab4"/>
-    <hyperlink ref="C39" location="'02项目完整详情'!A139"/>
-    <hyperlink ref="F39" ns1:id="Rf4dc98016cfb49fd"/>
-    <hyperlink ref="C22" location="'02项目完整详情'!A151"/>
-    <hyperlink ref="F22" ns1:id="R3d89872d06fd4b60"/>
-    <hyperlink ref="C23" location="'02项目完整详情'!A67"/>
-    <hyperlink ref="F23" ns1:id="R1e9b7d2bc63d4258"/>
-    <hyperlink ref="C40" location="'02项目完整详情'!A68"/>
-    <hyperlink ref="F40" ns1:id="R5d0261ffe45c4155"/>
-    <hyperlink ref="C24" location="'02项目完整详情'!A69"/>
-    <hyperlink ref="F24" ns1:id="Reeb11b878b934f2d"/>
-    <hyperlink ref="C25" location="'02项目完整详情'!A70"/>
-    <hyperlink ref="F25" ns1:id="R5b06defce5864a96"/>
-    <hyperlink ref="C26" location="'02项目完整详情'!A71"/>
-    <hyperlink ref="F26" ns1:id="Ra48afdb9842a4366"/>
-    <hyperlink ref="C41" location="'02项目完整详情'!A72"/>
-    <hyperlink ref="F41" ns1:id="Rb3b4681efcdd44d4"/>
-    <hyperlink ref="C42" location="'02项目完整详情'!A73"/>
-    <hyperlink ref="F42" ns1:id="R4f0b800598574b86"/>
-    <hyperlink ref="C43" location="'02项目完整详情'!A74"/>
-    <hyperlink ref="F43" ns1:id="R56697ca79cd54a14"/>
-    <hyperlink ref="C31" location="'02项目完整详情'!A75"/>
-    <hyperlink ref="F31" ns1:id="R0814a7680dde4f9a"/>
-    <hyperlink ref="C32" location="'02项目完整详情'!A76"/>
-    <hyperlink ref="F32" ns1:id="R3f222e6bf9fa46ec"/>
-    <hyperlink ref="C33" location="'02项目完整详情'!A77"/>
-    <hyperlink ref="F33" ns1:id="Rc66c2cf37bbc404d"/>
-    <hyperlink ref="C34" location="'02项目完整详情'!A78"/>
-    <hyperlink ref="F34" ns1:id="R90e03710dfe04e74"/>
-    <hyperlink ref="C35" location="'02项目完整详情'!A79"/>
-    <hyperlink ref="F35" ns1:id="R80f5129c1ee24096"/>
-    <hyperlink ref="C36" location="'02项目完整详情'!A80"/>
-    <hyperlink ref="F36" ns1:id="R6360db00742b45ec"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A81"/>
-    <hyperlink ref="F44" ns1:id="Rc4146f6376594d01"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A156"/>
-    <hyperlink ref="F45" ns1:id="R97ba6e4965084c76"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A155"/>
-    <hyperlink ref="F46" ns1:id="Rcbdc080795344925"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A83"/>
-    <hyperlink ref="F47" ns1:id="R9e6afd1b359743bb"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A154"/>
-    <hyperlink ref="F48" ns1:id="Rb320e0a5ad524836"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A86"/>
-    <hyperlink ref="F49" ns1:id="R42a660aaeb1d4c95"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A87"/>
-    <hyperlink ref="F50" ns1:id="R88784a2520864683"/>
-    <hyperlink ref="C27" location="'02项目完整详情'!A88"/>
-    <hyperlink ref="F27" ns1:id="Rcb8b33dae69a4731"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A89"/>
-    <hyperlink ref="F51" ns1:id="Rd5ea9c8442ca46ac"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A90"/>
-    <hyperlink ref="F52" ns1:id="R7734727212364cb2"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A91"/>
-    <hyperlink ref="F53" ns1:id="R78b8c8c0ca954ecb"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A92"/>
-    <hyperlink ref="F54" ns1:id="Rfdf5f46608d44776"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A93"/>
-    <hyperlink ref="F55" ns1:id="R82f06426c3d54976"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A94"/>
-    <hyperlink ref="F56" ns1:id="R3cae8e186c48414b"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A95"/>
-    <hyperlink ref="F57" ns1:id="Ra7f1aef2362a4a4a"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A96"/>
-    <hyperlink ref="F58" ns1:id="R8befa90ef3fc47c2"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A97"/>
-    <hyperlink ref="F59" ns1:id="Re7fdcbfdd1084572"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A98"/>
-    <hyperlink ref="F60" ns1:id="R65ca925ee60b42a7"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A100"/>
-    <hyperlink ref="F61" ns1:id="Reb76655df7374bc5"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A166"/>
-    <hyperlink ref="F62" ns1:id="R055caeb6a90642b5"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A102"/>
-    <hyperlink ref="F63" ns1:id="Rfff5ca38a0554ba3"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A103"/>
-    <hyperlink ref="F64" ns1:id="R0888add655cd4fba"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A104"/>
-    <hyperlink ref="F65" ns1:id="Rd9709f11bc9f4e83"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A163"/>
-    <hyperlink ref="F66" ns1:id="R20412a2edb1c448a"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A105"/>
-    <hyperlink ref="F67" ns1:id="R61772b79401a4268"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A106"/>
-    <hyperlink ref="F68" ns1:id="R987b8e6f52a74110"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A107"/>
-    <hyperlink ref="F69" ns1:id="R0c4396d550f2475f"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A162"/>
-    <hyperlink ref="F70" ns1:id="R4f11bd52ab71481c"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A108"/>
-    <hyperlink ref="F71" ns1:id="R4db82e37256244c2"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A109"/>
-    <hyperlink ref="F72" ns1:id="R4031c47a301e406d"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A110"/>
-    <hyperlink ref="F73" ns1:id="Raa160d321af04db8"/>
-    <hyperlink ref="C28" location="'02项目完整详情'!A111"/>
-    <hyperlink ref="F28" ns1:id="R769c1e9ff31b4410"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A112"/>
-    <hyperlink ref="F74" ns1:id="R4cdea66d1ef84e88"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A114"/>
-    <hyperlink ref="F75" ns1:id="Rfe9d4bacb83a4b3a"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A115"/>
-    <hyperlink ref="F76" ns1:id="Rdb52bb1fc14c4902"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A116"/>
-    <hyperlink ref="F77" ns1:id="Raea0cb8061aa4114"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A153"/>
-    <hyperlink ref="F78" ns1:id="Re209c4141aad4cc2"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A152"/>
-    <hyperlink ref="F79" ns1:id="R929ae2605c414e9f"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A165"/>
-    <hyperlink ref="F80" ns1:id="R1abe4cdaf9e34bae"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A117"/>
-    <hyperlink ref="F81" ns1:id="R0a10fce99c274f93"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A118"/>
-    <hyperlink ref="F82" ns1:id="R938383f864354c81"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A119"/>
-    <hyperlink ref="F83" ns1:id="Rf5654ce2b68c4be9"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A121"/>
-    <hyperlink ref="F84" ns1:id="Rcb7b406cd4eb4fbf"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A123"/>
-    <hyperlink ref="F85" ns1:id="R5815a7bd80814259"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A124"/>
-    <hyperlink ref="F86" ns1:id="R0c410df45d8a4e3d"/>
-    <hyperlink ref="C29" location="'02项目完整详情'!A125"/>
-    <hyperlink ref="F29" ns1:id="R431b21fd445f4abe"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A126"/>
-    <hyperlink ref="F87" ns1:id="R567091a279bf498d"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A164"/>
-    <hyperlink ref="F88" ns1:id="Re392bfd9b5274c72"/>
-    <hyperlink ref="C89" location="'02项目完整详情'!A128"/>
-    <hyperlink ref="F89" ns1:id="Re6cada6d8cc14329"/>
-    <hyperlink ref="C90" location="'02项目完整详情'!A129"/>
-    <hyperlink ref="F90" ns1:id="R8fc1cda8f3b6430e"/>
-    <hyperlink ref="C91" location="'02项目完整详情'!A130"/>
-    <hyperlink ref="F91" ns1:id="R27a55a96c3f24c5f"/>
-    <hyperlink ref="C92" location="'02项目完整详情'!A131"/>
-    <hyperlink ref="F92" ns1:id="R5e47895d5a614c2b"/>
-    <hyperlink ref="C30" location="'02项目完整详情'!A132"/>
-    <hyperlink ref="F30" ns1:id="R3b43825c6bac4d00"/>
-    <hyperlink ref="C93" location="'02项目完整详情'!A133"/>
-    <hyperlink ref="F93" ns1:id="R93e0d1bfa9de4923"/>
-    <hyperlink ref="C94" location="'02项目完整详情'!A40"/>
-    <hyperlink ref="F94" ns1:id="R8485fac45d264a2f"/>
-    <hyperlink ref="C95" location="'02项目完整详情'!A41"/>
-    <hyperlink ref="F95" ns1:id="R1c0f567749234b9c"/>
-    <hyperlink ref="C96" location="'02项目完整详情'!A42"/>
-    <hyperlink ref="F96" ns1:id="Rbf215fc93e064e7e"/>
-    <hyperlink ref="C97" location="'02项目完整详情'!A43"/>
-    <hyperlink ref="F97" ns1:id="R53db146b46f44f15"/>
-    <hyperlink ref="C98" location="'02项目完整详情'!A44"/>
-    <hyperlink ref="F98" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F106" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C106" location="'02项目完整详情'!A148"/>
-    <hyperlink ref="C99" location="'02项目完整详情'!A167" display="项目完整详情"/>
-    <hyperlink ref="F99" ns1:id="rIdSystematic98"/>
-    <hyperlink ref="C100" location="'02项目完整详情'!A168" display="项目完整详情"/>
-    <hyperlink ref="F100" ns1:id="rIdSystematic99"/>
-    <hyperlink ref="C101" location="'02项目完整详情'!A175" display="项目完整详情"/>
-    <hyperlink ref="F101" ns1:id="rIdSystematic100"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A176" display="项目完整详情"/>
-    <hyperlink ref="F102" ns1:id="rIdSystematic101"/>
+    <hyperlink ref="C13" location="'02项目完整详情'!A65"/>
+    <hyperlink ref="F13" ns1:id="Rb60ba16ed31b49e2"/>
+    <hyperlink ref="C15" location="'02项目完整详情'!A140"/>
+    <hyperlink ref="F15" ns1:id="R54631d6f63ff4a84"/>
+    <hyperlink ref="C16" location="'02项目完整详情'!A82"/>
+    <hyperlink ref="F16" ns1:id="R5d6c0e16ca9148f1"/>
+    <hyperlink ref="C17" location="'02项目完整详情'!A141"/>
+    <hyperlink ref="F17" ns1:id="R29345038c30a4733"/>
+    <hyperlink ref="C40" location="'02项目完整详情'!A85"/>
+    <hyperlink ref="F40" ns1:id="R486c032b769d4524"/>
+    <hyperlink ref="C18" location="'02项目完整详情'!A99"/>
+    <hyperlink ref="F18" ns1:id="R19ee0f6cf8d14ed3"/>
+    <hyperlink ref="C19" location="'02项目完整详情'!A143"/>
+    <hyperlink ref="F19" ns1:id="R66d112d84a8644fb"/>
+    <hyperlink ref="C20" location="'02项目完整详情'!A122"/>
+    <hyperlink ref="F20" ns1:id="R83b69720fcfc4e60"/>
+    <hyperlink ref="C21" location="'02项目完整详情'!A127"/>
+    <hyperlink ref="F21" ns1:id="Ra979348b05084966"/>
+    <hyperlink ref="C22" location="'02项目完整详情'!A66"/>
+    <hyperlink ref="F22" ns1:id="R4dc201fc29cb4ab4"/>
+    <hyperlink ref="C41" location="'02项目完整详情'!A139"/>
+    <hyperlink ref="F41" ns1:id="Rf4dc98016cfb49fd"/>
+    <hyperlink ref="C23" location="'02项目完整详情'!A151"/>
+    <hyperlink ref="F23" ns1:id="R3d89872d06fd4b60"/>
+    <hyperlink ref="C24" location="'02项目完整详情'!A67"/>
+    <hyperlink ref="F24" ns1:id="R1e9b7d2bc63d4258"/>
+    <hyperlink ref="C42" location="'02项目完整详情'!A68"/>
+    <hyperlink ref="F42" ns1:id="R5d0261ffe45c4155"/>
+    <hyperlink ref="C25" location="'02项目完整详情'!A69"/>
+    <hyperlink ref="F25" ns1:id="Reeb11b878b934f2d"/>
+    <hyperlink ref="C26" location="'02项目完整详情'!A70"/>
+    <hyperlink ref="F26" ns1:id="R5b06defce5864a96"/>
+    <hyperlink ref="C27" location="'02项目完整详情'!A71"/>
+    <hyperlink ref="F27" ns1:id="Ra48afdb9842a4366"/>
+    <hyperlink ref="C43" location="'02项目完整详情'!A72"/>
+    <hyperlink ref="F43" ns1:id="Rb3b4681efcdd44d4"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A73"/>
+    <hyperlink ref="F44" ns1:id="R4f0b800598574b86"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A74"/>
+    <hyperlink ref="F45" ns1:id="R56697ca79cd54a14"/>
+    <hyperlink ref="C33" location="'02项目完整详情'!A75"/>
+    <hyperlink ref="F33" ns1:id="R0814a7680dde4f9a"/>
+    <hyperlink ref="C34" location="'02项目完整详情'!A76"/>
+    <hyperlink ref="F34" ns1:id="R3f222e6bf9fa46ec"/>
+    <hyperlink ref="C35" location="'02项目完整详情'!A77"/>
+    <hyperlink ref="F35" ns1:id="Rc66c2cf37bbc404d"/>
+    <hyperlink ref="C36" location="'02项目完整详情'!A78"/>
+    <hyperlink ref="F36" ns1:id="R90e03710dfe04e74"/>
+    <hyperlink ref="C37" location="'02项目完整详情'!A79"/>
+    <hyperlink ref="F37" ns1:id="R80f5129c1ee24096"/>
+    <hyperlink ref="C38" location="'02项目完整详情'!A80"/>
+    <hyperlink ref="F38" ns1:id="R6360db00742b45ec"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A81"/>
+    <hyperlink ref="F46" ns1:id="Rc4146f6376594d01"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A156"/>
+    <hyperlink ref="F47" ns1:id="R97ba6e4965084c76"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A155"/>
+    <hyperlink ref="F48" ns1:id="Rcbdc080795344925"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A83"/>
+    <hyperlink ref="F49" ns1:id="R9e6afd1b359743bb"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A154"/>
+    <hyperlink ref="F50" ns1:id="Rb320e0a5ad524836"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A86"/>
+    <hyperlink ref="F51" ns1:id="R42a660aaeb1d4c95"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A87"/>
+    <hyperlink ref="F52" ns1:id="R88784a2520864683"/>
+    <hyperlink ref="C28" location="'02项目完整详情'!A88"/>
+    <hyperlink ref="F28" ns1:id="Rcb8b33dae69a4731"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A89"/>
+    <hyperlink ref="F53" ns1:id="Rd5ea9c8442ca46ac"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A90"/>
+    <hyperlink ref="F54" ns1:id="R7734727212364cb2"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A91"/>
+    <hyperlink ref="F55" ns1:id="R78b8c8c0ca954ecb"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A92"/>
+    <hyperlink ref="F56" ns1:id="Rfdf5f46608d44776"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A93"/>
+    <hyperlink ref="F57" ns1:id="R82f06426c3d54976"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A94"/>
+    <hyperlink ref="F58" ns1:id="R3cae8e186c48414b"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A95"/>
+    <hyperlink ref="F59" ns1:id="Ra7f1aef2362a4a4a"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A96"/>
+    <hyperlink ref="F60" ns1:id="R8befa90ef3fc47c2"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A97"/>
+    <hyperlink ref="F61" ns1:id="Re7fdcbfdd1084572"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A98"/>
+    <hyperlink ref="F62" ns1:id="R65ca925ee60b42a7"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A100"/>
+    <hyperlink ref="F63" ns1:id="Reb76655df7374bc5"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A166"/>
+    <hyperlink ref="F64" ns1:id="R055caeb6a90642b5"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A102"/>
+    <hyperlink ref="F65" ns1:id="Rfff5ca38a0554ba3"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A103"/>
+    <hyperlink ref="F66" ns1:id="R0888add655cd4fba"/>
+    <hyperlink ref="C32" location="'02项目完整详情'!A104"/>
+    <hyperlink ref="F32" ns1:id="Rd9709f11bc9f4e83"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A163"/>
+    <hyperlink ref="F67" ns1:id="R20412a2edb1c448a"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A105"/>
+    <hyperlink ref="F68" ns1:id="R61772b79401a4268"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A106"/>
+    <hyperlink ref="F69" ns1:id="R987b8e6f52a74110"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A107"/>
+    <hyperlink ref="F70" ns1:id="R0c4396d550f2475f"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A162"/>
+    <hyperlink ref="F71" ns1:id="R4f11bd52ab71481c"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A108"/>
+    <hyperlink ref="F72" ns1:id="R4db82e37256244c2"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A109"/>
+    <hyperlink ref="F73" ns1:id="R4031c47a301e406d"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A110"/>
+    <hyperlink ref="F74" ns1:id="Raa160d321af04db8"/>
+    <hyperlink ref="C29" location="'02项目完整详情'!A111"/>
+    <hyperlink ref="F29" ns1:id="R769c1e9ff31b4410"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A112"/>
+    <hyperlink ref="F75" ns1:id="R4cdea66d1ef84e88"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A114"/>
+    <hyperlink ref="F76" ns1:id="Rfe9d4bacb83a4b3a"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A115"/>
+    <hyperlink ref="F77" ns1:id="Rdb52bb1fc14c4902"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A116"/>
+    <hyperlink ref="F78" ns1:id="Raea0cb8061aa4114"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A153"/>
+    <hyperlink ref="F79" ns1:id="Re209c4141aad4cc2"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A152"/>
+    <hyperlink ref="F80" ns1:id="R929ae2605c414e9f"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A165"/>
+    <hyperlink ref="F81" ns1:id="R1abe4cdaf9e34bae"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A117"/>
+    <hyperlink ref="F82" ns1:id="R0a10fce99c274f93"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A118"/>
+    <hyperlink ref="F83" ns1:id="R938383f864354c81"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A119"/>
+    <hyperlink ref="F84" ns1:id="Rf5654ce2b68c4be9"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A121"/>
+    <hyperlink ref="F85" ns1:id="Rcb7b406cd4eb4fbf"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A123"/>
+    <hyperlink ref="F86" ns1:id="R5815a7bd80814259"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A124"/>
+    <hyperlink ref="F87" ns1:id="R0c410df45d8a4e3d"/>
+    <hyperlink ref="C30" location="'02项目完整详情'!A125"/>
+    <hyperlink ref="F30" ns1:id="R431b21fd445f4abe"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A126"/>
+    <hyperlink ref="F88" ns1:id="R567091a279bf498d"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A164"/>
+    <hyperlink ref="F89" ns1:id="Re392bfd9b5274c72"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A128"/>
+    <hyperlink ref="F90" ns1:id="Re6cada6d8cc14329"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A129"/>
+    <hyperlink ref="F91" ns1:id="R8fc1cda8f3b6430e"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A130"/>
+    <hyperlink ref="F92" ns1:id="R27a55a96c3f24c5f"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A131"/>
+    <hyperlink ref="F93" ns1:id="R5e47895d5a614c2b"/>
+    <hyperlink ref="C31" location="'02项目完整详情'!A132"/>
+    <hyperlink ref="F31" ns1:id="R3b43825c6bac4d00"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A133"/>
+    <hyperlink ref="F94" ns1:id="R93e0d1bfa9de4923"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A40"/>
+    <hyperlink ref="F95" ns1:id="R8485fac45d264a2f"/>
+    <hyperlink ref="C96" location="'02项目完整详情'!A41"/>
+    <hyperlink ref="F96" ns1:id="R1c0f567749234b9c"/>
+    <hyperlink ref="C97" location="'02项目完整详情'!A42"/>
+    <hyperlink ref="F97" ns1:id="Rbf215fc93e064e7e"/>
+    <hyperlink ref="C98" location="'02项目完整详情'!A43"/>
+    <hyperlink ref="F98" ns1:id="R53db146b46f44f15"/>
+    <hyperlink ref="C99" location="'02项目完整详情'!A44"/>
+    <hyperlink ref="F99" ns1:id="R188b27dcb5574282"/>
+    <hyperlink ref="F107" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C107" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="C100" location="'02项目完整详情'!A167" display="项目完整详情"/>
+    <hyperlink ref="F100" ns1:id="rIdSystematic98"/>
+    <hyperlink ref="C101" location="'02项目完整详情'!A168" display="项目完整详情"/>
+    <hyperlink ref="F101" ns1:id="rIdSystematic99"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A175" display="项目完整详情"/>
+    <hyperlink ref="F102" ns1:id="rIdSystematic100"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A176" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
-    <hyperlink ref="C103" location="'02项目完整详情'!A182" display="项目完整详情"/>
-    <hyperlink ref="F103" ns1:id="rIdResume103"/>
-    <hyperlink ref="C104" location="'02项目完整详情'!A184" display="项目完整详情"/>
-    <hyperlink ref="F104" ns1:id="rIdResume104"/>
-    <hyperlink ref="C13" location="'02项目完整详情'!A185" display="项目完整详情"/>
-    <hyperlink ref="F13" ns1:id="rIdResume105"/>
-    <hyperlink ref="C105" location="'02项目完整详情'!A186" display="项目完整详情"/>
-    <hyperlink ref="F105" ns1:id="rIdResume106"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F104" ns1:id="rIdResume103"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F105" ns1:id="rIdResume104"/>
+    <hyperlink ref="C14" location="'02项目完整详情'!A185" display="项目完整详情"/>
+    <hyperlink ref="F14" ns1:id="rIdResume105"/>
+    <hyperlink ref="C106" location="'02项目完整详情'!A186" display="项目完整详情"/>
+    <hyperlink ref="F106" ns1:id="rIdResume106"/>
+    <hyperlink ref="C12" location="'02项目完整详情'!A191" display="项目完整详情"/>
+    <hyperlink ref="F12" ns1:id="rIdResume107"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -41039,6 +42959,110 @@
       </c>
       <c r="H64" t="str" s="3">
         <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
+      </c>
+    </row>
+    <row r="65" ht="66" customHeight="1">
+      <c r="A65" t="str" s="20">
+        <v>历史批次·具体任务待核</v>
+      </c>
+      <c r="B65" t="n" s="13">
+        <v>43808</v>
+      </c>
+      <c r="C65" t="str" s="14">
+        <v>宁夏大学·宁夏智能装备CAE重点实验室</v>
+      </c>
+      <c r="D65" t="str" s="15">
+        <v>公告正文介绍多目标优化、多物理场、材料本构、复杂机电耦合；具体资助方向仅称见附件。不得以智能装备名称/优化关键词判定机器人相关，须核《开放课题设置.pdf》。</v>
+      </c>
+      <c r="E65" t="str" s="15">
+        <v>3万元/项；成果突出可追加，追加额未载</v>
+      </c>
+      <c r="F65" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G65" t="str" s="3">
+        <v>年度任务PDF首次无法读取；补机器人/自主装备具体任务证据，若无则剔除；另核管理条例、成果/IP、经费外拨及限定单位。2026—2027定向搜索未定位新公告。此前误用nu.edu.cn的空结果不作宁夏大学证据，正确域名nxu.edu.cn。</v>
+      </c>
+      <c r="H65" t="str" s="3">
+        <v>王老师13895189949；cae@nxu.edu.cn；2019收件：贺兰山西路539号宁大C区机械工程学院750021</v>
+      </c>
+    </row>
+    <row r="66" ht="66" customHeight="1">
+      <c r="A66" t="str" s="20">
+        <v>历史批次·公告全文待核</v>
+      </c>
+      <c r="B66" t="str" s="13">
+        <v>未取得2024准确截止</v>
+      </c>
+      <c r="C66" t="str" s="14">
+        <v>南京航空航天大学·模式分析与机器智能工业和信息化部重点实验室</v>
+      </c>
+      <c r="D66" t="str" s="15">
+        <v>官方缓存列面向交互的视觉识别理解、复杂场景多模态感知、人机融合智能交互；并列特征表示、鲁棒学习、弱监督模式识别。须核全文，未限定医疗超声。</v>
+      </c>
+      <c r="E66" t="str" s="15">
+        <v>官方缓存：3—5万元/项，拟4—5项；全文待核</v>
+      </c>
+      <c r="F66" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G66" t="str" s="3">
+        <v>首次网页超时，不反复访问；需完整公告文字/网页PDF及全部附件，补准确截止、成果署名、经费外拨、IP、提交。2026—2027搜索仅定位2024批次，不当当前正式公告。</v>
+      </c>
+      <c r="H66" t="str" s="3">
+        <v>联系人邮箱未取得</v>
+      </c>
+    </row>
+    <row r="67" ht="66" customHeight="1">
+      <c r="A67" t="str" s="20">
+        <v>历史批次·年度任务全文待核</v>
+      </c>
+      <c r="B67" t="n" s="13">
+        <v>45402</v>
+      </c>
+      <c r="C67" t="str" s="14">
+        <v>南京航空航天大学·高安全系统的软件开发与验证技术工业和信息化部重点实验室</v>
+      </c>
+      <c r="D67" t="str" s="15">
+        <v>平台介绍含无人自主智能系统安全分析；已见年度方向片段仅高安全软件需求、建模及形式化验证，未取得完整年度任务。须确认当年是否支持无人自主系统，不能用平台简介代替年度任务。</v>
+      </c>
+      <c r="E67" t="str" s="15">
+        <v>缓存：2—4万元/项，拟5—10项；全文待核</v>
+      </c>
+      <c r="F67" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G67" t="str" s="3">
+        <v>年度完整方向/任务证据不足，若仅软件验证而无无人自主机器人任务则剔除；获取全文和申请模板，补资格、成果/IP、经费外拨、联系与窗口。2026—2027未定位新正式公告。</v>
+      </c>
+      <c r="H67" t="str" s="3">
+        <v>联系人邮箱未取得</v>
+      </c>
+    </row>
+    <row r="68" ht="66" customHeight="1">
+      <c r="A68" t="str" s="20">
+        <v>公告及具体任务待核</v>
+      </c>
+      <c r="B68" t="str" s="13">
+        <v>2026准确截止未取得</v>
+      </c>
+      <c r="C68" t="str" s="14">
+        <v>南京航空航天大学·民航飞机健康监测与智能维护重点实验室（基本科研业务费自主课题）</v>
+      </c>
+      <c r="D68" t="str" s="15">
+        <v>现仅确认民航飞机健康监测与智能维护课题，年度机器人/自主装备相关研究任务尚未取得，不能仅智能维护名称保留首页。</v>
+      </c>
+      <c r="E68" t="str" s="15">
+        <v>资助金额未取得</v>
+      </c>
+      <c r="F68" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G68" t="str" s="3">
+        <v>首次483，不再尝试；下载或复制完整2026公告及全部附件，先核真实机器人任务与外部资格；再补金额、截止、周期、成果、IP、合作、外协接收单位及提交。未进入首页。</v>
+      </c>
+      <c r="H68" t="str" s="3">
+        <v>申报联系人及邮箱未取得</v>
       </c>
     </row>
   </sheetData>
@@ -41169,6 +43193,14 @@
     <hyperlink ref="F63" ns1:id="rIdResume65"/>
     <hyperlink ref="C64" location="'02项目完整详情'!A189" display="项目完整详情"/>
     <hyperlink ref="F64" ns1:id="rIdResume66"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A190" display="项目完整详情"/>
+    <hyperlink ref="F65" ns1:id="rIdResume67"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A192" display="项目完整详情"/>
+    <hyperlink ref="F66" ns1:id="rIdResume68"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A193" display="项目完整详情"/>
+    <hyperlink ref="F67" ns1:id="rIdResume69"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A194" display="项目完整详情"/>
+    <hyperlink ref="F68" ns1:id="rIdResume70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -17654,6 +17654,87 @@
       </c>
       <c r="AA194" t="str" s="3"/>
     </row>
+    <row r="195" ht="79.5" customHeight="1">
+      <c r="A195" t="str" s="3">
+        <v>N046</v>
+      </c>
+      <c r="B195" t="str" s="3">
+        <v>官方2026公告全文已核；申请表首次访问要求验证码</v>
+      </c>
+      <c r="C195" t="str" s="3">
+        <v>中北大学</v>
+      </c>
+      <c r="D195" t="str" s="3">
+        <v>半导体超精密加工技术与智能装备山西省重点实验室</v>
+      </c>
+      <c r="E195" t="str" s="3">
+        <v>年度具体任务待核</v>
+      </c>
+      <c r="F195" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G195" t="n" s="6">
+        <v>46311</v>
+      </c>
+      <c r="H195" t="str" s="3">
+        <v>截止时点未明示</v>
+      </c>
+      <c r="I195" t="str" s="3">
+        <v>年度方向：超精密加工理论与装备制造；多能场复合加工；半导体产业链核心装备及零部件；产线AI+智造基础理论与应用。尚未明确机器人感知、规划、控制或自主装备具体任务；不能凭AI/智能装备名称进入首页。</v>
+      </c>
+      <c r="J195" t="str" s="3">
+        <v>2—4万元/项，拟4—8项</v>
+      </c>
+      <c r="K195" t="str" s="3">
+        <v>国内外相关领域博士或副高及以上；原则年龄≤45周岁；主持本实验室基金未结题验收者不得申报；单位同意签字盖章。</v>
+      </c>
+      <c r="L195" t="str" s="3">
+        <v>论文成果必须署名实验室固定科研人员；未指定其担任通讯作者；访问天数未载。</v>
+      </c>
+      <c r="M195" t="str" s="3">
+        <v>经费使用须实验室审核，实验室主任及负责人双方签字方可报销；外拨是否允许及支出范围未明示，不能推断禁止或允许。</v>
+      </c>
+      <c r="N195" t="str" s="3">
+        <v>2年，2026年10月至2028年9月。</v>
+      </c>
+      <c r="O195" t="str" s="3">
+        <v>相关SCI≥2篇，其中≥1篇满足中北大学论文分类A2及以上（不是SCI二区）；年度报告和下一年度计划、中期学术报告、结题报告及答辩。实验室第一单位、固定研究人员署名；须同时标建设计划基金202504010932044及开放课题号，未标不计入验收。</v>
+      </c>
+      <c r="P195" t="str" s="3">
+        <v>知识产权归属及转化条款未载，需管理办法确认。</v>
+      </c>
+      <c r="Q195" t="str" s="3">
+        <v>纸质3份单位同意签章，提交学院路3号中北大学实验室；电子版songtjarvin@nuc.edu.cn；正文另并列yuruien@nuc.edu.cn，是否同时提交需确认。</v>
+      </c>
+      <c r="R195" t="str" s="3">
+        <v>本人博士满足学历选项；年龄、实验室在研限项、固定合作署名尚待本人/主办方确认。</v>
+      </c>
+      <c r="S195" t="str" s="3">
+        <v>先取得申请表及管理办法，核有无实际机器人/自主装备任务；无则剔除。附件验证码；经费外拨、IP、具体截止时点及第二邮箱用途未明示；不因日期未过直接写可申请。</v>
+      </c>
+      <c r="T195" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/63023.htm</v>
+      </c>
+      <c r="U195" t="str" s="3">
+        <v>https://www.nuc.edu.cn/system/_content/download.jsp?owner=1472165184&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=BBFEEDA971110196880E465484B14C3F</v>
+      </c>
+      <c r="V195" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W195" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X195" t="str" s="3">
+        <v>年度任务相关性证据不足，保持待核；不作能力评分或推荐。</v>
+      </c>
+      <c r="Y195" t="str" s="3">
+        <v>山西·太原</v>
+      </c>
+      <c r="Z195" t="str" s="3">
+        <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
+      </c>
+      <c r="AA195" t="str" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -18068,6 +18149,7 @@
     <hyperlink ref="T192" ns1:id="rIdResume414"/>
     <hyperlink ref="T193" ns1:id="rIdResume415"/>
     <hyperlink ref="T194" ns1:id="rIdResume416"/>
+    <hyperlink ref="T195" ns1:id="rIdResume417"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -38682,6 +38764,906 @@
       </c>
       <c r="I666" t="str" s="3">
         <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="667" ht="52.5" customHeight="1">
+      <c r="A667" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B667" t="str" s="3">
+        <v>上海大学/上海理工大学</v>
+      </c>
+      <c r="C667" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D667" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E667" t="str" s="3">
+        <v>查询：上海大学 上海理工大学 科研平台 机器人 开放基金 2026；定位：2026年度开放基金评审结果公告；智能感知与人机协同教育部重点实验室2026年度开放课题申请指南；科研平台；上海理工大学科研基地平台建设管理办法</v>
+      </c>
+      <c r="F667" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G667" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H667" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://klip-humaco.sist.shanghaitech.edu.cn/2026/0914/c14914a1126983/page.htm
+https://www.usst.edu.cn/kypt/list.htm
+https://xxgk.usst.edu.cn/2013/1225/c8490a194399/page.htm</v>
+      </c>
+      <c r="I667" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第264项</v>
+      </c>
+    </row>
+    <row r="668" ht="52.5" customHeight="1">
+      <c r="A668" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B668" t="str" s="3">
+        <v>河北工业大学/河北科技大学</v>
+      </c>
+      <c r="C668" t="str" s="3">
+        <v>河北</v>
+      </c>
+      <c r="D668" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E668" t="str" s="3">
+        <v>查询：河北 机器人 实验室 开放基金 2026 2027；定位：河北省地质环境智能感知与数据处理重点实验室2026年开放基金申请通知-河北地质大学；管理办法----机器人与智能系统全国重点实验室；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；2026年度开放基金评审结果公告；河北省战略性关键矿产资源重点实验室2026年度校内开放基金申请通知-河北地质大学；自然资源部京津冀城市群地下空间智能探测与装备重点实验室2026年度开放基金课题申请指南-河北地质大学</v>
+      </c>
+      <c r="F668" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G668" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H668" t="str" s="3">
+        <v>https://www.hgu.edu.cn/info/1050/11863.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://www.hgu.edu.cn/info/1050/11446.htm
+https://www.hgu.edu.cn/info/1050/11853.htm</v>
+      </c>
+      <c r="I668" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第265项</v>
+      </c>
+    </row>
+    <row r="669" ht="52.5" customHeight="1">
+      <c r="A669" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B669" t="str" s="3">
+        <v>河南省相关高校</v>
+      </c>
+      <c r="C669" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D669" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E669" t="str" s="3">
+        <v>查询：河南 机器人 重点实验室 开放基金 2026；定位：2026年度开放基金评审结果公告；全国重点实验室开放基金申请指南（2026年7月）-橡塑模具国家工程研究中心；河南省水体污染防治与修复重点实验室2026年度开放基金申报指南-河南省水体污染防治与修复重点实验室；2026年度郑州航院科研平台开放基金拟立项公示-郑州航空工业管理学院科技处；2026年度开放课题申请公告；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所</v>
+      </c>
+      <c r="F669" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G669" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H669" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://www5.zzu.edu.cn/nerc/info/1073/3205.htm
+https://keylab.huuc.edu.cn/info/1047/1335.htm
+https://kjc.zua.edu.cn/info/1202/3138.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html</v>
+      </c>
+      <c r="I669" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第266项</v>
+      </c>
+    </row>
+    <row r="670" ht="52.5" customHeight="1">
+      <c r="A670" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B670" t="str" s="3">
+        <v>山西省相关高校</v>
+      </c>
+      <c r="C670" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D670" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E670" t="str" s="3">
+        <v>查询：山西 机器人 重点实验室 开放基金 2026 2027；定位：机器视觉与虚拟现实山西省重点实验室 2026年度开放基金申请指南-中北大学；智能探测技术与装备山西省重点实验室2026年度开放基金课题申请指南-中北大学；机器视觉与虚拟现实山西省重点实验室2026年度开放基金申请指南 - 科研项目申报 - 泛研网；半导体超精密加工技术与智能装备山西省重点实验室2026年度开放基金申请指南-中北大学；管理办法----机器人与智能系统全国重点实验室；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所</v>
+      </c>
+      <c r="F670" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G670" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H670" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/62433.htm
+https://www.nuc.edu.cn/info/1014/62583.htm
+https://www.funresearch.cn/grant/YjBkMWE1NGEtNTRjOC00NWE0LWE4MTUtZjJlNmVhZmUzYWE2
+https://www.nuc.edu.cn/info/1014/63023.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html</v>
+      </c>
+      <c r="I670" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第267项</v>
+      </c>
+    </row>
+    <row r="671" ht="52.5" customHeight="1">
+      <c r="A671" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B671" t="str" s="3">
+        <v>上海大学</v>
+      </c>
+      <c r="C671" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D671" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E671" t="str" s="3">
+        <v>查询：site:shu.edu.cn "重点实验室" "机器人" "开放" 基金；定位：腿足机构测试实验室-上海市智能制造及机器人重点实验室</v>
+      </c>
+      <c r="F671" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G671" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H671" t="str" s="3">
+        <v>https://imrobot.shu.edu.cn/zysys/tzjgcssys.htm</v>
+      </c>
+      <c r="I671" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第268项</v>
+      </c>
+    </row>
+    <row r="672" ht="52.5" customHeight="1">
+      <c r="A672" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B672" t="str" s="3">
+        <v>上海理工大学</v>
+      </c>
+      <c r="C672" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D672" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E672" t="str" s="3">
+        <v>查询：site:usst.edu.cn "机器人" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F672" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G672" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H672" t="str" s="3"/>
+      <c r="I672" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第269项</v>
+      </c>
+    </row>
+    <row r="673" ht="52.5" customHeight="1">
+      <c r="A673" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B673" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C673" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D673" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E673" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "机器人" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F673" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G673" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H673" t="str" s="3"/>
+      <c r="I673" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第270项</v>
+      </c>
+    </row>
+    <row r="674" ht="52.5" customHeight="1">
+      <c r="A674" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B674" t="str" s="3">
+        <v>河南省高校平台</v>
+      </c>
+      <c r="C674" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D674" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E674" t="str" s="3">
+        <v>查询："河南省" "机器人" "开放课题" 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F674" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G674" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H674" t="str" s="3"/>
+      <c r="I674" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第271项</v>
+      </c>
+    </row>
+    <row r="675" ht="52.5" customHeight="1">
+      <c r="A675" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B675" t="str" s="3">
+        <v>中原工学院</v>
+      </c>
+      <c r="C675" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D675" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E675" t="str" s="3">
+        <v>查询：site:zut.edu.cn "现代制造装备与仪器" "开放"；定位：性制造系统实验室等38个专业实验室，拥有柔性生产线制造系统、精密减速器综合性能测量仪、立式加工机床等机械相关仪器设备，实验室面积达到4300m²，实验仪器设备价值超过6970万元。拥有研究生教室2个，研究生工作室8个，总面积1000余m²。学校购置了中国知网、万方数据知识服务平台、爱思唯尔SD数据库等中外文数据库32个，拥有本学科纸质图书资料7.8万册，订阅国内外本学科纸质专业期刊53种，均可服务于本学位点研究生教育。目前机械工程科学学位授权点市厅级及以上教学、学科与科研平台12个，其中省级及以上平台8个，市厅级平台4个。</v>
+      </c>
+      <c r="F675" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G675" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H675" t="str" s="3">
+        <v>https://yjsc.zut.edu.cn/__local/E/AB/15/BCE05A03050AC8241B7C96E3732_CDA67BDD_5A0476.pdf</v>
+      </c>
+      <c r="I675" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第272项</v>
+      </c>
+    </row>
+    <row r="676" ht="52.5" customHeight="1">
+      <c r="A676" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B676" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C676" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D676" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E676" t="str" s="3">
+        <v>查询：site:hebut.edu.cn 科研平台 机器人 重点实验室；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F676" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G676" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H676" t="str" s="3"/>
+      <c r="I676" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第273项</v>
+      </c>
+    </row>
+    <row r="677" ht="52.5" customHeight="1">
+      <c r="A677" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B677" t="str" s="3">
+        <v>上海大学</v>
+      </c>
+      <c r="C677" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D677" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E677" t="str" s="3">
+        <v>查询：site:imrobot.shu.edu.cn 开放课题 2026 2027；定位：腿足机构测试实验室-上海市智能制造及机器人重点实验室；2026年科技周预约通道-上海市智能制造及机器人重点实验室；上海市智能制造及机器人重点实验室；智能化数控装备及工艺实验室-上海市智能制造及机器人重点实验室；上海市智能制造及机器人重点实验室；综合新闻-上海市智能制造及机器人重点实验室</v>
+      </c>
+      <c r="F677" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G677" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H677" t="str" s="3">
+        <v>https://imrobot.shu.edu.cn/zysys/tzjgcssys.htm
+https://imrobot.shu.edu.cn/info/1002/1111.htm
+https://imrobot.shu.edu.cn/
+https://imrobot.shu.edu.cn/zysys/znhskzbjgysys.htm
+https://imrobot.shu.edu.cn/index.htm
+https://imrobot.shu.edu.cn/zhxw.htm</v>
+      </c>
+      <c r="I677" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第274项</v>
+      </c>
+    </row>
+    <row r="678" ht="52.5" customHeight="1">
+      <c r="A678" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B678" t="str" s="3">
+        <v>上海理工大学</v>
+      </c>
+      <c r="C678" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D678" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E678" t="str" s="3">
+        <v>查询：site:usst.edu.cn "医疗器械" "开放基金" 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F678" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G678" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H678" t="str" s="3"/>
+      <c r="I678" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第275项</v>
+      </c>
+    </row>
+    <row r="679" ht="52.5" customHeight="1">
+      <c r="A679" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B679" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C679" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D679" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E679" t="str" s="3">
+        <v>查询："河北省机器人感知与人机融合重点实验室" "开放"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F679" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G679" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H679" t="str" s="3"/>
+      <c r="I679" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第276项</v>
+      </c>
+    </row>
+    <row r="680" ht="52.5" customHeight="1">
+      <c r="A680" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B680" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C680" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D680" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E680" t="str" s="3">
+        <v>查询："智能康复装置与检测技术" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F680" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G680" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H680" t="str" s="3"/>
+      <c r="I680" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第277项</v>
+      </c>
+    </row>
+    <row r="681" ht="52.5" customHeight="1">
+      <c r="A681" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B681" t="str" s="3">
+        <v>中原工学院</v>
+      </c>
+      <c r="C681" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D681" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E681" t="str" s="3">
+        <v>查询："现代制造装备与仪器" "开放基金" 2026 2027；定位：2026年度开放基金申请指南-现代制造质量工程湖北省重点实验室；副教授，博士生导师 | Open FIESTA｜清华大学国际开放创新教育中心</v>
+      </c>
+      <c r="F681" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G681" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H681" t="str" s="3">
+        <v>https://mmqe.hbut.edu.cn/info/1047/2232.htm
+https://openfiesta.sigs.tsinghua.edu.cn/cn/pi/3/30</v>
+      </c>
+      <c r="I681" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第278项</v>
+      </c>
+    </row>
+    <row r="682" ht="52.5" customHeight="1">
+      <c r="A682" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B682" t="str" s="3">
+        <v>中原工学院</v>
+      </c>
+      <c r="C682" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D682" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E682" t="str" s="3">
+        <v>查询：site:jdxy.zut.edu.cn "2015-12-29" 开放实验室 申请；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F682" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G682" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H682" t="str" s="3"/>
+      <c r="I682" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第279项</v>
+      </c>
+    </row>
+    <row r="683" ht="52.5" customHeight="1">
+      <c r="A683" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B683" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C683" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D683" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E683" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "智能化建筑施工装备" 开放基金 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F683" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G683" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H683" t="str" s="3"/>
+      <c r="I683" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第280项</v>
+      </c>
+    </row>
+    <row r="684" ht="52.5" customHeight="1">
+      <c r="A684" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B684" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C684" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D684" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E684" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "机电一体化" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F684" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G684" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H684" t="str" s="3"/>
+      <c r="I684" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第281项</v>
+      </c>
+    </row>
+    <row r="685" ht="52.5" customHeight="1">
+      <c r="A685" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B685" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C685" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D685" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E685" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "跨尺度智能装备" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F685" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G685" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H685" t="str" s="3"/>
+      <c r="I685" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第282项</v>
+      </c>
+    </row>
+    <row r="686" ht="52.5" customHeight="1">
+      <c r="A686" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B686" t="str" s="3">
+        <v>河北工业大学</v>
+      </c>
+      <c r="C686" t="str" s="3">
+        <v>天津/河北</v>
+      </c>
+      <c r="D686" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E686" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "智能防护装备" 开放课题 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F686" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G686" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H686" t="str" s="3"/>
+      <c r="I686" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第283项</v>
+      </c>
+    </row>
+    <row r="687" ht="52.5" customHeight="1">
+      <c r="A687" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B687" t="str" s="3">
+        <v>河北工业大学其他相关平台</v>
+      </c>
+      <c r="C687" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D687" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E687" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "生物电磁" "开放基金" / site:hebut.edu.cn "交通基础设施" "开放课题" / site:hebut.edu.cn "大数据计算" "开放基金" / site:hebut.edu.cn "激光" "开放基金" 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F687" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G687" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H687" t="str" s="3"/>
+      <c r="I687" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第284项</v>
+      </c>
+    </row>
+    <row r="688" ht="52.5" customHeight="1">
+      <c r="A688" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B688" t="str" s="3">
+        <v>上海大学机器人重点实验室</v>
+      </c>
+      <c r="C688" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D688" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E688" t="str" s="3">
+        <v>查询：site:imrobot.shu.edu.cn "开放基金" / site:imrobot.shu.edu.cn "开放课题" / site:shu.edu.cn "机器人" "开放基金" 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F688" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G688" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H688" t="str" s="3"/>
+      <c r="I688" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第285项</v>
+      </c>
+    </row>
+    <row r="689" ht="52.5" customHeight="1">
+      <c r="A689" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B689" t="str" s="3">
+        <v>上海理工大学科研平台</v>
+      </c>
+      <c r="C689" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D689" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E689" t="str" s="3">
+        <v>查询：site:usst.edu.cn 科研平台 机器人 重点实验室 开放 / site:usst.edu.cn "开放基金" 2026 2027 机器人 / site:usst.edu.cn "开放课题" 康复 医疗器械；定位：科研平台；关于发布上海市2024年度“科技创新行动计划”重点实验室（第一批）申报指南的通知；上海理工大学科研基地平台建设管理办法；科研平台；关于印发《上海市重点实验室建设与运行管理办法》的通知；&lt;tr&gt;&lt;th colspan="3"&gt;国家级科研平台&lt;</v>
+      </c>
+      <c r="F689" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G689" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H689" t="str" s="3">
+        <v>https://ndxy.usst.edu.cn/kypt/list.htm
+https://xxgk.usst.edu.cn/2024/1111/c8884a329754/page.htm
+https://xxgk.usst.edu.cn/2013/1225/c8490a194399/page.htm
+https://www.usst.edu.cn/_t32/kypt/list.htm
+https://xxgk.usst.edu.cn/2019/1012/c8701a192311/page.htm
+https://yz.usst.edu.cn/_upload/article/files/3f/c3/eef5d17549c78dd7aac6bb0831f2/2a83a1bb-c47b-4c87-be36-88d83fa73b0c.pdf</v>
+      </c>
+      <c r="I689" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第286项</v>
+      </c>
+    </row>
+    <row r="690" ht="52.5" customHeight="1">
+      <c r="A690" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B690" t="str" s="3">
+        <v>河北工业大学复杂工程平台</v>
+      </c>
+      <c r="C690" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D690" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E690" t="str" s="3">
+        <v>查询：site:hebut.edu.cn "复杂工程" "开放基金" / site:hebut.edu.cn "康复" "开放课题" 2026 2027 / site:hebut.edu.cn "机器人感知" "开放基金" 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F690" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G690" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H690" t="str" s="3"/>
+      <c r="I690" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第287项</v>
+      </c>
+    </row>
+    <row r="691" ht="52.5" customHeight="1">
+      <c r="A691" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B691" t="str" s="3">
+        <v>中北大学</v>
+      </c>
+      <c r="C691" t="str" s="3">
+        <v>山西·太原</v>
+      </c>
+      <c r="D691" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E691" t="str" s="3">
+        <v>半导体超精密加工技术与智能装备山西省重点实验室；2026；N046；官方2026公告全文已核；申请表首次访问要求验证码</v>
+      </c>
+      <c r="F691" t="str" s="3">
+        <v>先取得申请表及管理办法，核有无实际机器人/自主装备任务；无则剔除。附件验证码；经费外拨、IP、具体截止时点及第二邮箱用途未明示；不因日期未过直接写可申请。</v>
+      </c>
+      <c r="G691" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H691" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/63023.htm</v>
+      </c>
+      <c r="I691" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="692" ht="52.5" customHeight="1">
+      <c r="A692" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B692" t="str" s="3">
+        <v>中北大学</v>
+      </c>
+      <c r="C692" t="str" s="3">
+        <v>山西·太原</v>
+      </c>
+      <c r="D692" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E692" t="str" s="3">
+        <v>2026半导体超精密加工N046；机器视觉M068、智能探测M106、微纳M043、电子测试M107等复用，不重复计数</v>
+      </c>
+      <c r="F692" t="str" s="3">
+        <v>N046年度任务未明确机器人；验证码模板待补；2027未见新正式公告</v>
+      </c>
+      <c r="G692" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H692" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/63023.htm</v>
+      </c>
+      <c r="I692" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="693" ht="52.5" customHeight="1">
+      <c r="A693" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B693" t="str" s="3">
+        <v>河北地质大学</v>
+      </c>
+      <c r="C693" t="str" s="3">
+        <v>河北·石家庄</v>
+      </c>
+      <c r="D693" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E693" t="str" s="3">
+        <v>地下智能探测2026年度正文已核；E079剔除。地质环境AI2026复用M079剔除。</v>
+      </c>
+      <c r="F693" t="str" s="3">
+        <v>实际为地球物理探测、面波微动、光纤地球物理监测、地球物理仪器和城市灾害地质评价，无机器人具体任务；额度2万仅3000—6000现金，其余仪器租赁，不作全额现金基金。</v>
+      </c>
+      <c r="G693" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H693" t="str" s="3">
+        <v>https://www.hgu.edu.cn/info/1050/11853.htm</v>
+      </c>
+      <c r="I693" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="694" ht="52.5" customHeight="1">
+      <c r="A694" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B694" t="str" s="3">
+        <v>河北工业大学机械学院</v>
+      </c>
+      <c r="C694" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D694" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E694" t="str" s="3">
+        <v>2026-05-29官方机械平台目录：康复装置/机器人感知人机融合、机电一体化、先进智能防护、跨尺度装备、智能建筑施工装备等；逐名开放基金/课题2026—2027及历史机制搜索。</v>
+      </c>
+      <c r="F694" t="str" s="3">
+        <v>未定位本校相关平台正式对外基金公告；教师获外校开放基金不当本校主办。省级目录生物电磁神经、交通智能建造、大数据、先进激光、复杂工程平台亦查询；年度管理机制仍未取得。</v>
+      </c>
+      <c r="G694" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H694" t="str" s="3">
+        <v>https://mes.hebut.edu.cn/kxyj/kypt/index.htm
+https://www.hebut.edu.cn/kxyj/kyjg/106311.htm</v>
+      </c>
+      <c r="I694" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="695" ht="52.5" customHeight="1">
+      <c r="A695" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B695" t="str" s="3">
+        <v>上海大学</v>
+      </c>
+      <c r="C695" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D695" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E695" t="str" s="3">
+        <v>智能制造及机器人重点实验室7子室：离散制造、智能制造系统、共融机器人、腿足机构、精密测量、机器人图像学习、数控装备；2026—2027及历史基金定向搜索、官网科研政策栏目已核。</v>
+      </c>
+      <c r="F695" t="str" s="3">
+        <v>未获正式年度对外资助公告；开放交流/预约不作资助机制；政策栏仅市级运行经费2018和校实验队伍专项2015，未据此认定外部申请资格。其他校级目录/年度仍有缺口。</v>
+      </c>
+      <c r="G695" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H695" t="str" s="3">
+        <v>https://imrobot.shu.edu.cn/
+https://imrobot.shu.edu.cn/gzzd/kyzc.htm</v>
+      </c>
+      <c r="I695" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="696" ht="52.5" customHeight="1">
+      <c r="A696" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B696" t="str" s="3">
+        <v>中原工学院</v>
+      </c>
+      <c r="C696" t="str" s="3">
+        <v>河南·郑州</v>
+      </c>
+      <c r="D696" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E696" t="str" s="3">
+        <v>机械科研团队官方索引见2015-12-29河南高校现代制造装备与仪器重点学科开放实验室项目申请条目；2026—2027和历史机制已定向搜索。</v>
+      </c>
+      <c r="F696" t="str" s="3">
+        <v>目录正文首次超时；须人工点开2015申请条目保存完整公告附件，年度金额任务未知，不生成正式项目；全校其他相关平台待继续。</v>
+      </c>
+      <c r="G696" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H696" t="str" s="3">
+        <v>https://jdxy.zut.edu.cn/kxyj/kytd.htm</v>
+      </c>
+      <c r="I696" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="697" ht="52.5" customHeight="1">
+      <c r="A697" t="str" s="3">
+        <v>2026-10-09目录及年度核验</v>
+      </c>
+      <c r="B697" t="str" s="3">
+        <v>上海理工大学</v>
+      </c>
+      <c r="C697" t="str" s="3">
+        <v>上海</v>
+      </c>
+      <c r="D697" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E697" t="str" s="3">
+        <v>官方科研平台搜索缓存列医用光学、神经形态光计算边缘智能、光电测试、数控机床等平台；开放基金/课题2026—2027查询。</v>
+      </c>
+      <c r="F697" t="str" s="3">
+        <v>官网目录首次超时，交人工确认完整平台名单；教师履历及论文中的外校基金不作本校正式公告。具体平台年度仍需逐项核。</v>
+      </c>
+      <c r="G697" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H697" t="str" s="3">
+        <v>https://www.usst.edu.cn/_t32/kypt/list.htm</v>
+      </c>
+      <c r="I697" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
       </c>
     </row>
   </sheetData>
@@ -43065,6 +44047,32 @@
         <v>申报联系人及邮箱未取得</v>
       </c>
     </row>
+    <row r="69" ht="66" customHeight="1">
+      <c r="A69" t="str" s="20">
+        <v>年度具体任务待核</v>
+      </c>
+      <c r="B69" t="n" s="13">
+        <v>46311</v>
+      </c>
+      <c r="C69" t="str" s="14">
+        <v>中北大学·半导体超精密加工技术与智能装备山西省重点实验室</v>
+      </c>
+      <c r="D69" t="str" s="15">
+        <v>年度方向：超精密加工理论与装备制造；多能场复合加工；半导体产业链核心装备及零部件；产线AI+智造基础理论与应用。尚未明确机器人感知、规划、控制或自主装备具体任务；不能凭AI/智能装备名称进入首页。</v>
+      </c>
+      <c r="E69" t="str" s="15">
+        <v>2—4万元/项，拟4—8项</v>
+      </c>
+      <c r="F69" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G69" t="str" s="3">
+        <v>先取得申请表及管理办法，核有无实际机器人/自主装备任务；无则剔除。附件验证码；经费外拨、IP、具体截止时点及第二邮箱用途未明示；不因日期未过直接写可申请。</v>
+      </c>
+      <c r="H69" t="str" s="3">
+        <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" location="'02项目完整详情'!A14"/>
@@ -43201,6 +44209,8 @@
     <hyperlink ref="F67" ns1:id="rIdResume69"/>
     <hyperlink ref="C68" location="'02项目完整详情'!A194" display="项目完整详情"/>
     <hyperlink ref="F68" ns1:id="rIdResume70"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A195" display="项目完整详情"/>
+    <hyperlink ref="F69" ns1:id="rIdResume71"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -17735,6 +17735,249 @@
       </c>
       <c r="AA195" t="str" s="3"/>
     </row>
+    <row r="196" ht="79.5" customHeight="1">
+      <c r="A196" t="str" s="3">
+        <v>N047</v>
+      </c>
+      <c r="B196" t="str" s="3">
+        <v>官方公告搜索缓存及摘要；正文首次500失败</v>
+      </c>
+      <c r="C196" t="str" s="3">
+        <v>山东科技大学</v>
+      </c>
+      <c r="D196" t="str" s="3">
+        <v>山东省智慧矿山信息技术重点实验室</v>
+      </c>
+      <c r="E196" t="str" s="3">
+        <v>历史批次·公告附件待核</v>
+      </c>
+      <c r="F196" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G196" t="n" s="6">
+        <v>46296</v>
+      </c>
+      <c r="H196" t="str" s="3">
+        <v>寄出时间须在2026年10月01日之前，具体时点未取得</v>
+      </c>
+      <c r="I196" t="str" s="3">
+        <v>官方摘要明确煤矿全场景视觉感知、恶劣条件多模态增强感知与鲁棒分析、复杂矿山环境感知与设备自适应控制、智能巡检设备、矿山具身智能装备。其他地质/矿山大模型方向不代替机器人具体任务。</v>
+      </c>
+      <c r="J196" t="str" s="3">
+        <v>资助金额及项数尚未取得</v>
+      </c>
+      <c r="K196" t="str" s="3">
+        <v>官方缓存欢迎国内外人才利用实验室条件开展基础研究；学历职称、年龄、限项具体条款未取得，不能代为确认可申报。</v>
+      </c>
+      <c r="L196" t="str" s="3">
+        <v>固定合作者、共同署名及驻室要求未取得。</v>
+      </c>
+      <c r="M196" t="str" s="3">
+        <v>费用范围、外拨及报销条件未取得。</v>
+      </c>
+      <c r="N196" t="str" s="3">
+        <v>周期及起止尚未取得。</v>
+      </c>
+      <c r="O196" t="str" s="3">
+        <v>成果数量、第一单位、指定作者及结题要求未取得。</v>
+      </c>
+      <c r="P196" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q196" t="str" s="3">
+        <v>官方摘要第8条：申请书纸质2份，2026-10-01之前（寄出时间）邮寄实验室，并将电子版发指定邮箱；地址、邮箱、盖章格式未取得。</v>
+      </c>
+      <c r="R196" t="str" s="3">
+        <v>本人博士；具体资格全文未取得，年龄/限项及合作需按完整公告核实。</v>
+      </c>
+      <c r="S196" t="str" s="3">
+        <v>正文首次500，保存完整2026公告和附件；补金额、资格、合作、经费外拨、周期、成果/IP、联系方式及时点。截止已过，非当前申报项目；2027年度未取得。</v>
+      </c>
+      <c r="T196" t="str" s="3">
+        <v>https://cise.sdust.edu.cn/home/page/details/catId/18/id/999001273.html</v>
+      </c>
+      <c r="U196" t="str" s="3">
+        <v>完整公告附件入口未取得，请从网页下载全部当年指南/管理办法/申请书</v>
+      </c>
+      <c r="V196" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W196" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X196" t="str" s="3">
+        <v>官方摘要存在机器人实际任务证据，历史轮次正文及附件仍待核。</v>
+      </c>
+      <c r="Y196" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="Z196" t="str" s="3">
+        <v>指定邮箱、收件地址及联系人未取得</v>
+      </c>
+      <c r="AA196" t="str" s="3"/>
+    </row>
+    <row r="197" ht="79.5" customHeight="1">
+      <c r="A197" t="str" s="3">
+        <v>N048</v>
+      </c>
+      <c r="B197" t="str" s="3">
+        <v>第三方2026-01-20转载及本校教师履历机制线索；候选官方路径首次受阻，非已核正式公告</v>
+      </c>
+      <c r="C197" t="str" s="3">
+        <v>潍坊学院（机构与年度公告尚待官方核验）</v>
+      </c>
+      <c r="D197" t="str" s="3">
+        <v>山东省先进动力装备智能制造技术重点实验室</v>
+      </c>
+      <c r="E197" t="str" s="3">
+        <v>历史线索·官方公告待核</v>
+      </c>
+      <c r="F197" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G197" t="n" s="6">
+        <v>46087</v>
+      </c>
+      <c r="H197" t="str" s="3">
+        <v>转载为16:00，须官方原件确认</v>
+      </c>
+      <c r="I197" t="str" s="3">
+        <v>转载方向含多维制造信息融合感知与控制、非结构动态环境下人机协同制造、制造系统集成与智能运维、数字孪生建模、智能测试标定等。浙江工业教师主页另记2026多机械臂协同感知控制获本实验室基金，证明机制线索，不能代替完整年度正式任务及条款。</v>
+      </c>
+      <c r="J197" t="str" s="3">
+        <v>转载每项2—3万元，未取得官方确认</v>
+      </c>
+      <c r="K197" t="str" s="3">
+        <v>转载：国内外高校/科研院所科研人员，博士或副高以上；本年度限1项，实验室在研负责人不得参与；实际需官方核验。</v>
+      </c>
+      <c r="L197" t="str" s="3">
+        <v>固定合作人员及访问要求转载未載，待官方。</v>
+      </c>
+      <c r="M197" t="str" s="3">
+        <v>支出、外拨报销规则未取得。</v>
+      </c>
+      <c r="N197" t="str" s="3">
+        <v>项目期限及起止未取得，不按教师项目起止推断。</v>
+      </c>
+      <c r="O197" t="str" s="3">
+        <v>转载：期限内≥3篇SCI/EI期刊，标实验室中文/英文资助及课题号；第一单位、指定作者需官方确认。</v>
+      </c>
+      <c r="P197" t="str" s="3">
+        <v>IP未取得管理办法。</v>
+      </c>
+      <c r="Q197" t="str" s="3">
+        <v>转载：2026-03-06 16:00前申请书发20220051@wfu.edu.cn，评审立项签技术合同；份数、签章等待原件。</v>
+      </c>
+      <c r="R197" t="str" s="3">
+        <v>本人博士；待官方明确真实资格、限项及合作，无推荐判断。</v>
+      </c>
+      <c r="S197" t="str" s="3">
+        <v>第三方不是正式凭据；候选官方URL无法读取且真实性未确认，需人工从学校机械学院官网定位2026指南及附件、管理办法。转载电话区号0356与潍坊所在地不同，原样保留待核不自行改为0536；日期/金额不得当作已核。</v>
+      </c>
+      <c r="T197" t="str" s="3">
+        <v>https://www.10100.com/article/115636790</v>
+      </c>
+      <c r="U197" t="str" s="3">
+        <v>候选路径（未确认）：https://jid.wfu.edu.cn/2026/0119/c1036a258486/page.htm；学校学院入口https://jid.wfu.edu.cn/</v>
+      </c>
+      <c r="V197" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W197" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X197" t="str" s="3">
+        <v>历史机制线索；所有转载条款均未获官方验证，不进入正式受理页。</v>
+      </c>
+      <c r="Y197" t="str" s="3">
+        <v>山东·潍坊</v>
+      </c>
+      <c r="Z197" t="str" s="3">
+        <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
+      </c>
+      <c r="AA197" t="str" s="3"/>
+    </row>
+    <row r="198" ht="79.5" customHeight="1">
+      <c r="A198" t="str" s="3">
+        <v>N049</v>
+      </c>
+      <c r="B198" t="str" s="3">
+        <v>官方2023公告搜索缓存全文已取得；网页首次直接访问不可达</v>
+      </c>
+      <c r="C198" t="str" s="3">
+        <v>广东工业大学</v>
+      </c>
+      <c r="D198" t="str" s="3">
+        <v>省部共建精密电子制造技术与装备国家重点实验室</v>
+      </c>
+      <c r="E198" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F198" t="str" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G198" t="n" s="6">
+        <v>45261</v>
+      </c>
+      <c r="H198" t="str" s="3">
+        <v>当年截止时点未明示；常年收材料描述不替代当年截止</v>
+      </c>
+      <c r="I198" t="str" s="3">
+        <v>高速精密运动机构/平台、宏微协同精密运动控制、非线性响应运动规划、多模三维显微成像、大视场高速视觉检测、精密电子制造智能装备（含3C机器人）关键技术、柔性产线快速定制设计。仅相关条款入方向，材料制备不凭关键词延伸。</v>
+      </c>
+      <c r="J198" t="str" s="3">
+        <v>一般约5万元/项；重点约10万元/项</v>
+      </c>
+      <c r="K198" t="str" s="3">
+        <v>在职博士或副高以上；其他需2名正高书面推荐；35岁以下优先而非年龄硬限制；负责人不能同期承担≥2项开放课题；国内外学者。</v>
+      </c>
+      <c r="L198" t="str" s="3">
+        <v>鼓励固定研究人员联合申报，未列强制；客座访问天数未明示。</v>
+      </c>
+      <c r="M198" t="str" s="3">
+        <v>资金来源中央财政及学校实验室拨款；具体科目、外拨和报销办法未取得。</v>
+      </c>
+      <c r="N198" t="str" s="3">
+        <v>3年，确切执行起止待任务书。</v>
+      </c>
+      <c r="O198" t="str" s="3">
+        <v>一般≥1篇、重点≥2篇广工国际TOP目录高质量论文；另验收条款要求成果至少发表或录用2篇高质量论文，两段数量差异保留待确认。论文第一/通讯作者完成单位含实验室；全部成果实验室第一完成单位。结题报告成果原件复印件验收。</v>
+      </c>
+      <c r="P198" t="str" s="3">
+        <v>成果由实验室、研究者单位及其他资助单位共享；具体专利/转化处置未载。</v>
+      </c>
+      <c r="Q198" t="str" s="3">
+        <v>按附件申请书申请，专家评审后任务书再合同；合同双方单位签署盖章2份寄实验室。常年收材料但2023年度截止2023-12-01，不能视当前受理；初始申请份数及提交途径应核附件。</v>
+      </c>
+      <c r="R198" t="str" s="3">
+        <v>本人博士满足学历选项；在职、同期开放限项可按本人实际确认；合作鼓励非强制。</v>
+      </c>
+      <c r="S198" t="str" s="3">
+        <v>直接网页首次不可达；人工保存2023完整公告及附件1申请书，补经费外拨、初始申请提交格式，确认一般1篇与验收至少2篇的口径；2026—2027新指南未取得。不同于R003教育部平台2018年度，不合并年度/不同平台。</v>
+      </c>
+      <c r="T198" t="str" s="3">
+        <v>https://jdgcxy.gdut.edu.cn/info/1086/4035.htm</v>
+      </c>
+      <c r="U198" t="str" s="3">
+        <v>附件1《省部共建精密电子制造技术与装备国家重点实验室开放课题申请书（2023年）》DOC，具体下载直链未取得</v>
+      </c>
+      <c r="V198" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W198" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X198" t="str" s="3">
+        <v>3C机器人与运动规划实际任务明确；2023历史项目，不因常年收材料进入当前首页。</v>
+      </c>
+      <c r="Y198" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="Z198" t="str" s="3">
+        <v>刘金花；jmdz_gz@gdut.edu.cn；020-39325372、15013234272；广州市番禺区大学城外环西路100号工学二号馆301室510006</v>
+      </c>
+      <c r="AA198" t="str" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -18150,6 +18393,9 @@
     <hyperlink ref="T193" ns1:id="rIdResume415"/>
     <hyperlink ref="T194" ns1:id="rIdResume416"/>
     <hyperlink ref="T195" ns1:id="rIdResume417"/>
+    <hyperlink ref="T196" ns1:id="rIdResume418"/>
+    <hyperlink ref="T197" ns1:id="rIdResume419"/>
+    <hyperlink ref="T198" ns1:id="rIdResume420"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -39663,6 +39909,524 @@
         <v>https://www.usst.edu.cn/_t32/kypt/list.htm</v>
       </c>
       <c r="I697" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="698" ht="52.5" customHeight="1">
+      <c r="A698" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B698" t="str" s="3">
+        <v>西北工业大学计算机学院平台逐名补齐</v>
+      </c>
+      <c r="C698" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D698" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E698" t="str" s="3">
+        <v>查询：site:jsj.nwpu.edu.cn 科研平台 重点实验室 移动平台 智能感知 / site:nwpu.edu.cn "无人航行" "开放基金" 2026 2027 / site:nwpu.edu.cn "移动平台" "开放课题" 2026 2027；定位：智能感知与计算工业和信息化部重点实验室-计算机学院</v>
+      </c>
+      <c r="F698" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G698" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H698" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/info/1658/7529.htm</v>
+      </c>
+      <c r="I698" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第288项</v>
+      </c>
+    </row>
+    <row r="699" ht="52.5" customHeight="1">
+      <c r="A699" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B699" t="str" s="3">
+        <v>西北工业大学人机物融合/智能感知平台</v>
+      </c>
+      <c r="C699" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D699" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E699" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn "人机物融合群智计算" "开放" 基金 / site:nwpu.edu.cn "智能感知与计算" "开放课题" / site:nwpu.edu.cn "语音与图像" "开放基金" 2026 2027 / site:nwpu.edu.cn "嵌入式系统技术" "开放基金"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F699" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G699" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H699" t="str" s="3"/>
+      <c r="I699" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第289项</v>
+      </c>
+    </row>
+    <row r="700" ht="52.5" customHeight="1">
+      <c r="A700" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B700" t="str" s="3">
+        <v>华南理工大学自动化及机械科研平台</v>
+      </c>
+      <c r="C700" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D700" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E700" t="str" s="3">
+        <v>查询：site:scut.edu.cn 自动化 科研平台 重点实验室 机器人 / site:scut.edu.cn 机械 科研平台 机器人 重点实验室 / site:scut.edu.cn "人机共生" "开放基金" 2026 2027 / site:scut.edu.cn "机器人" "开放课题" 2026 2027；定位：数智赋能设计创新　华南理工新增一文科省重点实验室</v>
+      </c>
+      <c r="F700" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G700" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H700" t="str" s="3">
+        <v>https://news.scut.edu.cn/2023/0928/c160a47573/page.htm</v>
+      </c>
+      <c r="I700" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第290项</v>
+      </c>
+    </row>
+    <row r="701" ht="52.5" customHeight="1">
+      <c r="A701" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B701" t="str" s="3">
+        <v>重庆大学自动化与机械平台目录缺口</v>
+      </c>
+      <c r="C701" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D701" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E701" t="str" s="3">
+        <v>查询：site:cqu.edu.cn 自动化 科研平台 机器人 重点实验室 / site:cqu.edu.cn 机械 科研平台 重点实验室 2026 / site:cqu.edu.cn "自主无人系统" "开放基金" 2026 2027 / site:cqu.edu.cn "人机" "开放课题" 2026 2027；定位：薛方正-信息物理社会可信服务计算教育部重点实验室_重庆大学CPS实验室；科研平台-重庆大学；高端装备机械传动全国重点实验室（测试版）；程森林-信息物理社会可信服务计算教育部重点实验室_重庆大学CPS实验室；机器人与智能系统-信息物理社会可信服务计算教育部重点实验室_重庆大学CPS实验室；特种作业具身智能安全与应用实验室签约仪式在校举行-计算机学院主页</v>
+      </c>
+      <c r="F701" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G701" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H701" t="str" s="3">
+        <v>https://cps.cqu.edu.cn/info/1006/1599.htm
+https://www.cqu.edu.cn/kxyj/kypt.htm
+https://slmt.cqu.edu.cn/
+https://cps.cqu.edu.cn/info/1006/1605.htm
+https://cps.cqu.edu.cn/info/1020/1748.htm
+https://cs.cqu.edu.cn/info/1540/12035.htm</v>
+      </c>
+      <c r="I701" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第291项</v>
+      </c>
+    </row>
+    <row r="702" ht="52.5" customHeight="1">
+      <c r="A702" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B702" t="str" s="3">
+        <v>中科院自动化所尚未核平台开放机制</v>
+      </c>
+      <c r="C702" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D702" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E702" t="str" s="3">
+        <v>查询：site:ia.cas.cn "脑图谱" "开放基金" 2026 2027 / site:ia.cas.cn "工业视觉" "开放基金" 2026 2027 / site:ia.cas.cn "复杂系统" "开放课题" 2026 2027 / site:ia.cas.cn "分子影像" "开放课题" 2026 2027；定位：多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所；多模态人工智能系统全国重点实验室2024年度开放课题申请指南----中国科学院自动化研究所；复杂系统认知与决策国家级重点实验室----中国科学院自动化研究所；多模态人工智能系统全国重点实验室2023年度开放课题申请指南----中国科学院自动化研究所</v>
+      </c>
+      <c r="F702" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G702" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H702" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html
+https://www.ia.cas.cn/qtgn/tzgg/202404/t20240418_7122705.html
+https://ia.cas.cn/jgsz/kyxt/fzxtrz/
+https://www.ia.cas.cn/qtgn/tzgg/202305/t20230530_6765024.html</v>
+      </c>
+      <c r="I702" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第292项</v>
+      </c>
+    </row>
+    <row r="703" ht="52.5" customHeight="1">
+      <c r="A703" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B703" t="str" s="3">
+        <v>浙江工业大学省级机器人平台目录</v>
+      </c>
+      <c r="C703" t="str" s="3">
+        <v>浙江·杭州</v>
+      </c>
+      <c r="D703" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E703" t="str" s="3">
+        <v>查询：site:zjut.edu.cn "科研平台" "机器人" / site:zjut.edu.cn "开放基金" 2026 2027 机器人 / site:zjut.edu.cn "开放课题" 智能 制造 控制 2026；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F703" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G703" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H703" t="str" s="3"/>
+      <c r="I703" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第293项</v>
+      </c>
+    </row>
+    <row r="704" ht="52.5" customHeight="1">
+      <c r="A704" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B704" t="str" s="3">
+        <v>广东工业大学省级机器人平台目录</v>
+      </c>
+      <c r="C704" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D704" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E704" t="str" s="3">
+        <v>查询：site:gdut.edu.cn 科研平台 机器人 重点实验室 / site:gdut.edu.cn "开放基金" 2026 2027 机器人 / site:gdut.edu.cn "开放课题" 2026 2027 智能；定位：广东工业大学教师主页平台管理系统 Zhigang Ren--Home--Home；广东工业大学教师主页平台管理系统 liuyonghua--Home--Research Field；广东工业大学-电子精密制造装备及技术教育部重点实验室；广东工业大学教师主页平台管理系统 任志刚--中文主页--首页；南方海洋科学与工程广东省实验室（湛江）2027年科研人员校园招聘公告；广东工业大学教师主页平台管理系统 Jiewu Leng--Home-- 广东省重点领域研发计划，智能机器人与装备制造专项，面向3C行业的机器人生产线智能化三维设计与仿真优化系统（2019B090916002），2019.01-2021.12，1000万元，核心成员</v>
+      </c>
+      <c r="F704" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G704" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H704" t="str" s="3">
+        <v>https://teacher.gdut.edu.cn/renzhigang/en/1
+https://teacher.gdut.edu.cn/liuyonghua/en/more/148541/jsjjgd/index.htm
+https://jdis.gdut.edu.cn/wdzweb/newslist.aspx?ctx=4B4811F135C116514FDB179F7C97391B
+https://teacher.gdut.edu.cn/renzhigang/zh_CN/index.htm
+https://career.gdut.edu.cn/campus/view/id/1021147
+https://teacher.gdut.edu.cn/lengjiewu/en/kyxm/130241/content/3198.htm</v>
+      </c>
+      <c r="I704" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第294项</v>
+      </c>
+    </row>
+    <row r="705" ht="52.5" customHeight="1">
+      <c r="A705" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B705" t="str" s="3">
+        <v>湖南科技大学省级机器人平台目录</v>
+      </c>
+      <c r="C705" t="str" s="3">
+        <v>湖南·湘潭</v>
+      </c>
+      <c r="D705" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E705" t="str" s="3">
+        <v>查询：site:hnust.edu.cn "科研平台" "机器人" / site:hnust.edu.cn "开放基金" 2026 2027 / site:hnust.edu.cn "开放课题" 机器人；定位：王宪_湖南科技大学海洋实验室；功能膜材料湖南省工程研究中心承担政府科研课题表</v>
+      </c>
+      <c r="F705" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G705" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H705" t="str" s="3">
+        <v>https://marinelab.hnust.edu.cn/yjdw/hdzywhtzbyjsyjry/ee29ac13743f42b9a77fd52abc673da9.htm
+https://chem.hnust.edu.cn/docs/2025-07/eda84b6c99154da1aa0ad73c44df4155.pdf</v>
+      </c>
+      <c r="I705" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第295项</v>
+      </c>
+    </row>
+    <row r="706" ht="52.5" customHeight="1">
+      <c r="A706" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B706" t="str" s="3">
+        <v>山东科技大学省级机器人平台目录</v>
+      </c>
+      <c r="C706" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D706" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E706" t="str" s="3">
+        <v>查询：site:sdust.edu.cn "科研平台" 机器人 重点实验室 / site:sdust.edu.cn "开放基金" 2026 2027 机器人 / site:sdust.edu.cn "开放课题" 2026 智能控制；定位：机器人与智能技术重点实验室、控制科学与智能技术山东省高等学校实验室、山东省智能无人系统技术创新中心、山东省机器人省级示范工程技术研究中心、山东省机器人与智能技术示范协同创新中心、铝离子动力和储能技术协同创新中心、山东省高校矿山安全监测技术与系统强化建设重点实验室、山东省安全监测监控与智能控制重点实验室、青岛市智能控制与机器人技术重点实验室、青岛市机器人与智能制造技术工程研究中心等科研平台。；科研平台；成果依托的教科研平台-自动化学院；山东省智能感知与自主控制重点实验室2026年开放基金申请指南-自动化学院；关于进一步加强学校山东省重点实验室建设和管理的通知-山东科技大学科技处；数学学院2个实验室获批青岛市重点实验室筹建-数学与系统科学学院网站</v>
+      </c>
+      <c r="F706" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G706" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H706" t="str" s="3">
+        <v>https://cfasta2023.sdust.edu.cn/__local/1/37/5E/98C3E4D507D3E0B59DD1FBBB88D_F2E51080_276393.pdf
+https://keyan.sdust.edu.cn/home/page/detail.html?id=50
+https://xindian.sdust.edu.cn/sjjxcgj_yjs_/cgytdjkypt/2.htm
+https://xindian.sdust.edu.cn/info/1008/7407.htm
+https://keyan.sdust.edu.cn/info/1034/1646.htm
+https://sxy.sdust.edu.cn/info/1221/9227.htm</v>
+      </c>
+      <c r="I706" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第296项</v>
+      </c>
+    </row>
+    <row r="707" ht="52.5" customHeight="1">
+      <c r="A707" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B707" t="str" s="3">
+        <v>山东先进动力装备/重庆隧道开放机制</v>
+      </c>
+      <c r="C707" t="str" s="3">
+        <v>山东·重庆</v>
+      </c>
+      <c r="D707" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E707" t="str" s="3">
+        <v>查询："山东省先进动力装备智能制造技术重点实验室" "开放" 2026 / "重庆市工程实验室" "开放课题" "隧道" 2025 2026 / site:jdgcxy.gdut.edu.cn "精密电子制造" "开放课题" 2026 2027；定位：先进动力装备智能制造技术重点实验室 2026年度开放课题申报指南- 大数跨境；交通工程应用机器人重庆市工程实验室 2026年度开放基金申报指南与中期、结题通知-重庆交通大学新闻网；省部共建精密电子制造技术与装备国家重点实验室开放课题申请指南（2023年）-机电工程学院；重庆交通大学召开交通工程应用机器人重庆市工程实验室技术委员会2024年会议-重庆交通大学新闻网；国家山区公路工程技术研究中心_百度百科</v>
+      </c>
+      <c r="F707" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G707" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H707" t="str" s="3">
+        <v>https://www.10100.com/article/115636790
+https://news.cqjtu.edu.cn/info/1024/68220.htm
+https://jdgcxy.gdut.edu.cn/info/1086/4035.htm
+https://news.cqjtu.edu.cn/info/1027/60452.htm
+https://bkso.baidu.com/item/%E5%9B%BD%E5%AE%B6%E5%B1%B1%E5%8C%BA%E5%85%AC%E8%B7%AF%E5%B7%A5%E7%A8%8B%E6%8A%80%E6%9C%AF%E7%A0%94%E7%A9%B6%E4%B8%AD%E5%BF%83/10986293?fromModule=lemma_inlink</v>
+      </c>
+      <c r="I707" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第297项</v>
+      </c>
+    </row>
+    <row r="708" ht="52.5" customHeight="1">
+      <c r="A708" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B708" t="str" s="3">
+        <v>潍坊学院先进动力装备2026正式源定位</v>
+      </c>
+      <c r="C708" t="str" s="3">
+        <v>山东·潍坊</v>
+      </c>
+      <c r="D708" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E708" t="str" s="3">
+        <v>查询：site:wfu.edu.cn "先进动力装备" "2026" "开放" / site:wfu.edu.cn "20220051" "开放" / "先进动力装备智能制造技术" "2026年度" 申请 指南；定位：山东省先进动力装备智能制造技术重点实验室2026年度开放课题申报指南 - taptap点点体育在线；先进动力装备智能制造技术重点实验室 2026年度开放课题申报指南- 大数跨境；智能制造装备与技术全国重点实验室 2026年度开放课题申请通知-智能制造装备与技术全国重点实验室；申请！一批次重点实验室课题基金申请指南 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F708" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G708" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H708" t="str" s="3">
+        <v>https://m.yumehaniito.com/jid/2026/0119/c1036a258486/page.htm
+https://www.10100.com/article/115636790
+https://imet.hust.edu.cn/info/1031/2733.htm
+https://www.letpub.com.cn/index.php?article_id=3242&amp;page=grant_article_details</v>
+      </c>
+      <c r="I708" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第298项</v>
+      </c>
+    </row>
+    <row r="709" ht="52.5" customHeight="1">
+      <c r="A709" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B709" t="str" s="3">
+        <v>山东科技大学</v>
+      </c>
+      <c r="C709" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D709" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E709" t="str" s="3">
+        <v>山东省智慧矿山信息技术重点实验室；2026；N047；官方公告搜索缓存及摘要；正文首次500失败</v>
+      </c>
+      <c r="F709" t="str" s="3">
+        <v>正文首次500，保存完整2026公告和附件；补金额、资格、合作、经费外拨、周期、成果/IP、联系方式及时点。截止已过，非当前申报项目；2027年度未取得。</v>
+      </c>
+      <c r="G709" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H709" t="str" s="3">
+        <v>https://cise.sdust.edu.cn/home/page/details/catId/18/id/999001273.html</v>
+      </c>
+      <c r="I709" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="710" ht="52.5" customHeight="1">
+      <c r="A710" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B710" t="str" s="3">
+        <v>潍坊学院（机构与年度公告尚待官方核验）</v>
+      </c>
+      <c r="C710" t="str" s="3">
+        <v>山东·潍坊</v>
+      </c>
+      <c r="D710" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E710" t="str" s="3">
+        <v>山东省先进动力装备智能制造技术重点实验室；2026；N048；第三方2026-01-20转载及本校教师履历机制线索；候选官方路径首次受阻，非已核正式公告</v>
+      </c>
+      <c r="F710" t="str" s="3">
+        <v>第三方不是正式凭据；候选官方URL无法读取且真实性未确认，需人工从学校机械学院官网定位2026指南及附件、管理办法。转载电话区号0356与潍坊所在地不同，原样保留待核不自行改为0536；日期/金额不得当作已核。</v>
+      </c>
+      <c r="G710" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H710" t="str" s="3">
+        <v>https://www.10100.com/article/115636790</v>
+      </c>
+      <c r="I710" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="711" ht="52.5" customHeight="1">
+      <c r="A711" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B711" t="str" s="3">
+        <v>广东工业大学</v>
+      </c>
+      <c r="C711" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D711" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E711" t="str" s="3">
+        <v>省部共建精密电子制造技术与装备国家重点实验室；2023；N049；官方2023公告搜索缓存全文已取得；网页首次直接访问不可达</v>
+      </c>
+      <c r="F711" t="str" s="3">
+        <v>直接网页首次不可达；人工保存2023完整公告及附件1申请书，补经费外拨、初始申请提交格式，确认一般1篇与验收至少2篇的口径；2026—2027新指南未取得。不同于R003教育部平台2018年度，不合并年度/不同平台。</v>
+      </c>
+      <c r="G711" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H711" t="str" s="3">
+        <v>https://jdgcxy.gdut.edu.cn/info/1086/4035.htm</v>
+      </c>
+      <c r="I711" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="712" ht="52.5" customHeight="1">
+      <c r="A712" t="str" s="3">
+        <v>2026-10-09核心平台机制</v>
+      </c>
+      <c r="B712" t="str" s="3">
+        <v>西北工业大学计算机相关平台</v>
+      </c>
+      <c r="C712" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D712" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E712" t="str" s="3">
+        <v>复用官方研究机构目录（实际仅1个简介条目，未列8省部平台全名）；计算机信息系、智能系统系介绍列移动感知、无人航行感知、人机物融合群智、语音图像、嵌入式及工信部智能感知；本次逐名基金/课题搜索。</v>
+      </c>
+      <c r="F712" t="str" s="3">
+        <v>尚未定位这些平台2026—2027正式对外基金；8个平台名称未完整列出仍缺口，不把7学科方向当7实验室。</v>
+      </c>
+      <c r="G712" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H712" t="str" s="3">
+        <v>https://jsj.nwpu.edu.cn/snew/list.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1556
+https://jsj.nwpu.edu.cn/info/1657/7521.htm
+https://jsj.nwpu.edu.cn/info/1657/10601.htm</v>
+      </c>
+      <c r="I712" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="713" ht="52.5" customHeight="1">
+      <c r="A713" t="str" s="3">
+        <v>2026-10-09核心平台机制</v>
+      </c>
+      <c r="B713" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C713" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D713" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E713" t="str" s="3">
+        <v>复杂系统认知决策官方简介全文首次核：明确“部署开放课题”，联系方式c2dl@ia.ac.cn、010-82544562；脑图谱、工业视觉、复杂系统、分子影像2026—2027机制定向查询。</v>
+      </c>
+      <c r="F713" t="str" s="3">
+        <v>平台部署机制不等同已获年度受理公告；经费/资格/期限需年度正式通知。多模态2026/2025等已有条目复用。</v>
+      </c>
+      <c r="G713" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H713" t="str" s="3">
+        <v>https://ia.cas.cn/jgsz/kyxt/fzxtrz/</v>
+      </c>
+      <c r="I713" t="str" s="3">
+        <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="714" ht="52.5" customHeight="1">
+      <c r="A714" t="str" s="3">
+        <v>2026-10-09核心平台机制</v>
+      </c>
+      <c r="B714" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C714" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D714" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E714" t="str" s="3">
+        <v>信息物理社会可信服务实验室机器人与智能系统分组官方入口首次412；智慧无人、自动化学院平台及人机课题定向搜索，已有项目不重复。</v>
+      </c>
+      <c r="F714" t="str" s="3">
+        <v>机器人与智能系统分组需人工网页原件；平台介绍不是新增基金。全校未查范围仍按原机构记录继续。</v>
+      </c>
+      <c r="G714" t="str" s="3">
+        <v>仅所列目录/年度与查询已查，非机构查全。</v>
+      </c>
+      <c r="H714" t="str" s="3">
+        <v>https://cps.cqu.edu.cn/info/1020/1748.htm</v>
+      </c>
+      <c r="I714" t="str" s="3">
         <v>resume_sources_20261009.json 末组正文/查询</v>
       </c>
     </row>
@@ -40113,24 +40877,24 @@
         <v>公告</v>
       </c>
     </row>
-    <row r="22" ht="66" customHeight="1">
-      <c r="A22" s="18" t="str">
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B22" s="13" t="d">
-        <v>2025-10-15T00:00:00.000Z</v>
-      </c>
-      <c r="C22" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
-      </c>
-      <c r="D22" s="15" t="str">
-        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
-      </c>
-      <c r="E22" s="15" t="str">
-        <v>5—8万元</v>
-      </c>
-      <c r="F22" s="16" t="str">
-        <v>公告</v>
+      <c r="B22" t="n" s="13">
+        <v>45261</v>
+      </c>
+      <c r="C22" t="str" s="14">
+        <v>广东工业大学·省部共建精密电子制造技术与装备国家重点实验室</v>
+      </c>
+      <c r="D22" t="str" s="15">
+        <v>高速精密运动机构/平台、宏微协同精密运动控制、非线性响应运动规划、多模三维显微成像、大视场高速视觉检测、精密电子制造智能装备（含3C机器人）关键技术、柔性产线快速定制设计。仅相关条款入方向，材料制备不凭关键词延伸。</v>
+      </c>
+      <c r="E22" t="str" s="15">
+        <v>一般约5万元/项；重点约10万元/项</v>
+      </c>
+      <c r="F22" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="23" ht="66" customHeight="1">
@@ -40138,16 +40902,16 @@
         <v>已截止</v>
       </c>
       <c r="B23" s="13" t="d">
-        <v>2026-05-11T00:00:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C23" s="14" t="str">
-        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D23" s="15" t="str">
-        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
+        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
       </c>
       <c r="E23" s="15" t="str">
-        <v>10万元/项；每方向1项</v>
+        <v>5—8万元</v>
       </c>
       <c r="F23" s="16" t="str">
         <v>公告</v>
@@ -40158,16 +40922,16 @@
         <v>已截止</v>
       </c>
       <c r="B24" s="13" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-11T00:00:00.000Z</v>
       </c>
       <c r="C24" s="14" t="str">
-        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
+        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
       </c>
       <c r="D24" s="15" t="str">
-        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
+        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
       </c>
       <c r="E24" s="15" t="str">
-        <v>5—10万元</v>
+        <v>10万元/项；每方向1项</v>
       </c>
       <c r="F24" s="16" t="str">
         <v>公告</v>
@@ -40178,16 +40942,16 @@
         <v>已截止</v>
       </c>
       <c r="B25" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-05-29T00:00:00.000Z</v>
       </c>
       <c r="C25" s="14" t="str">
-        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
+        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
       </c>
       <c r="D25" s="15" t="str">
-        <v>地下空间具身智能感知、定位与点云建模</v>
+        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
       </c>
       <c r="E25" s="15" t="str">
-        <v>一般≥2万元；重点≥3万元</v>
+        <v>5—10万元</v>
       </c>
       <c r="F25" s="16" t="str">
         <v>公告</v>
@@ -40198,16 +40962,16 @@
         <v>已截止</v>
       </c>
       <c r="B26" s="13" t="d">
-        <v>2026-07-31T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C26" s="14" t="str">
-        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
+        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
       </c>
       <c r="D26" s="15" t="str">
-        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
+        <v>地下空间具身智能感知、定位与点云建模</v>
       </c>
       <c r="E26" s="15" t="str">
-        <v>30—90万元（无人机监视反制专项）</v>
+        <v>一般≥2万元；重点≥3万元</v>
       </c>
       <c r="F26" s="16" t="str">
         <v>公告</v>
@@ -40218,16 +40982,16 @@
         <v>已截止</v>
       </c>
       <c r="B27" s="13" t="d">
-        <v>2026-08-28T00:00:00.000Z</v>
+        <v>2026-07-31T00:00:00.000Z</v>
       </c>
       <c r="C27" s="14" t="str">
-        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
+        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
       </c>
       <c r="D27" s="15" t="str">
-        <v>机器人多接触规划、具身技能学习与运动行为</v>
+        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
       </c>
       <c r="E27" s="15" t="str">
-        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
+        <v>30—90万元（无人机监视反制专项）</v>
       </c>
       <c r="F27" s="16" t="str">
         <v>公告</v>
@@ -40238,57 +41002,57 @@
         <v>已截止</v>
       </c>
       <c r="B28" s="13" t="d">
-        <v>2025-08-10T00:00:00.000Z</v>
+        <v>2026-08-28T00:00:00.000Z</v>
       </c>
       <c r="C28" s="14" t="str">
-        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
       </c>
       <c r="D28" s="15" t="str">
-        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+        <v>机器人多接触规划、具身技能学习与运动行为</v>
       </c>
       <c r="E28" s="15" t="str">
-        <v>5—10万元/项</v>
+        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
       </c>
       <c r="F28" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="29" ht="79.5" customHeight="1">
+    <row r="29" ht="66" customHeight="1">
       <c r="A29" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B29" s="13" t="d">
+        <v>2025-08-10T00:00:00.000Z</v>
+      </c>
+      <c r="C29" s="14" t="str">
+        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="D29" s="15" t="str">
+        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+      </c>
+      <c r="E29" s="15" t="str">
+        <v>5—10万元/项</v>
+      </c>
+      <c r="F29" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="30" ht="79.5" customHeight="1">
+      <c r="A30" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B30" s="13" t="d">
         <v>2026-05-06T00:00:00.000Z</v>
       </c>
-      <c r="C29" s="14" t="str">
+      <c r="C30" s="14" t="str">
         <v>煤炭智能开采与岩层控制全国重点实验室（北京；具体依托机构待核，沈阳化工为转载单位）·煤炭智能开采与岩层控制全国重点实验室</v>
       </c>
-      <c r="D29" s="15" t="str">
+      <c r="D30" s="15" t="str">
         <v>机械臂—底座耦合振动、末端自适应定位（依托机构尚待确认）</v>
       </c>
-      <c r="E29" s="15" t="str">
+      <c r="E30" s="15" t="str">
         <v>2026年度实验室设开放基金项目共计40项，其中重点项目4项，每项资助研究金额为45-65万元；
 一般项目36项，每项资助研究金额为15-25万元。</v>
-      </c>
-      <c r="F29" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="30" ht="66" customHeight="1">
-      <c r="A30" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B30" s="13" t="d">
-        <v>2026-08-20T00:00:00.000Z</v>
-      </c>
-      <c r="C30" s="14" t="str">
-        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
-      </c>
-      <c r="D30" s="15" t="str">
-        <v>自主无人系统及机器人研究</v>
-      </c>
-      <c r="E30" s="15" t="str">
-        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F30" s="16" t="str">
         <v>公告</v>
@@ -40299,16 +41063,16 @@
         <v>已截止</v>
       </c>
       <c r="B31" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-08-20T00:00:00.000Z</v>
       </c>
       <c r="C31" s="14" t="str">
-        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
+        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D31" s="15" t="str">
-        <v>无人越野平台世界模型、具身感知与控制</v>
+        <v>自主无人系统及机器人研究</v>
       </c>
       <c r="E31" s="15" t="str">
-        <v>重点20—30万元、一般5—10万元</v>
+        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F31" s="16" t="str">
         <v>公告</v>
@@ -40319,16 +41083,16 @@
         <v>已截止</v>
       </c>
       <c r="B32" s="13" t="d">
-        <v>2026-04-10T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C32" s="14" t="str">
-        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）·建筑钢结构智能制造技术兵团重点实验室</v>
+        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
       </c>
       <c r="D32" s="15" t="str">
-        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
+        <v>无人越野平台世界模型、具身感知与控制</v>
       </c>
       <c r="E32" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>重点20—30万元、一般5—10万元</v>
       </c>
       <c r="F32" s="16" t="str">
         <v>公告</v>
@@ -40339,16 +41103,16 @@
         <v>已截止</v>
       </c>
       <c r="B33" s="13" t="d">
-        <v>2026-09-20T00:00:00.000Z</v>
+        <v>2026-04-10T00:00:00.000Z</v>
       </c>
       <c r="C33" s="14" t="str">
-        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
+        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）·建筑钢结构智能制造技术兵团重点实验室</v>
       </c>
       <c r="D33" s="15" t="str">
-        <v>平台具身智能与异构智能体协同</v>
+        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
       </c>
       <c r="E33" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>不超过2万元</v>
       </c>
       <c r="F33" s="16" t="str">
         <v>公告</v>
@@ -40359,16 +41123,16 @@
         <v>已截止</v>
       </c>
       <c r="B34" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2026-09-20T00:00:00.000Z</v>
       </c>
       <c r="C34" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室</v>
+        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
       </c>
       <c r="D34" s="15" t="str">
-        <v>工业机器人传动、机电耦合与高端装备传动</v>
+        <v>平台具身智能与异构智能体协同</v>
       </c>
       <c r="E34" s="15" t="str">
-        <v>面上5—8万元。</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F34" s="16" t="str">
         <v>公告</v>
@@ -40379,16 +41143,16 @@
         <v>已截止</v>
       </c>
       <c r="B35" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C35" s="14" t="str">
-        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室</v>
       </c>
       <c r="D35" s="15" t="str">
-        <v>具身智能世界模型与开放环境视觉感知</v>
+        <v>工业机器人传动、机电耦合与高端装备传动</v>
       </c>
       <c r="E35" s="15" t="str">
-        <v>3万元</v>
+        <v>面上5—8万元。</v>
       </c>
       <c r="F35" s="16" t="str">
         <v>公告</v>
@@ -40399,16 +41163,16 @@
         <v>已截止</v>
       </c>
       <c r="B36" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C36" s="14" t="str">
-        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
+        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
       </c>
       <c r="D36" s="15" t="str">
-        <v>山区建造装备及机器人</v>
+        <v>具身智能世界模型与开放环境视觉感知</v>
       </c>
       <c r="E36" s="15" t="str">
-        <v>每项6万元。</v>
+        <v>3万元</v>
       </c>
       <c r="F36" s="16" t="str">
         <v>公告</v>
@@ -40419,16 +41183,16 @@
         <v>已截止</v>
       </c>
       <c r="B37" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C37" s="14" t="str">
-        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
+        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
       </c>
       <c r="D37" s="15" t="str">
-        <v>桥梁检测机器人与无人巡检装备</v>
+        <v>山区建造装备及机器人</v>
       </c>
       <c r="E37" s="15" t="str">
-        <v>5—10万元</v>
+        <v>每项6万元。</v>
       </c>
       <c r="F37" s="16" t="str">
         <v>公告</v>
@@ -40439,17 +41203,16 @@
         <v>已截止</v>
       </c>
       <c r="B38" s="13" t="d">
-        <v>2026-09-01T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C38" s="14" t="str">
-        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
+        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
       </c>
       <c r="D38" s="15" t="str">
-        <v>工业机器人及智能产线运维、故障预测与控制</v>
+        <v>桥梁检测机器人与无人巡检装备</v>
       </c>
       <c r="E38" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F38" s="16" t="str">
         <v>公告</v>
@@ -40460,13 +41223,13 @@
         <v>已截止</v>
       </c>
       <c r="B39" s="13" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-09-01T00:00:00.000Z</v>
       </c>
       <c r="C39" s="14" t="str">
-        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
+        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
       </c>
       <c r="D39" s="15" t="str">
-        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
+        <v>工业机器人及智能产线运维、故障预测与控制</v>
       </c>
       <c r="E39" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -40481,13 +41244,13 @@
         <v>已截止</v>
       </c>
       <c r="B40" s="13" t="d">
-        <v>2025-02-28T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="C40" s="14" t="str">
-        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
+        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
       </c>
       <c r="D40" s="15" t="str">
-        <v>重载机器人减速器、直驱电机及关键部件</v>
+        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
       </c>
       <c r="E40" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -40502,16 +41265,17 @@
         <v>已截止</v>
       </c>
       <c r="B41" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-02-28T00:00:00.000Z</v>
       </c>
       <c r="C41" s="14" t="str">
-        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
+        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
       </c>
       <c r="D41" s="15" t="str">
-        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
+        <v>重载机器人减速器、直驱电机及关键部件</v>
       </c>
       <c r="E41" s="15" t="str">
-        <v>重点20万元；一般10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F41" s="16" t="str">
         <v>公告</v>
@@ -40522,16 +41286,16 @@
         <v>已截止</v>
       </c>
       <c r="B42" s="13" t="d">
-        <v>2026-06-14T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C42" s="14" t="str">
-        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
+        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
       </c>
       <c r="D42" s="15" t="str">
-        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
+        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
       </c>
       <c r="E42" s="15" t="str">
-        <v>10万元</v>
+        <v>重点20万元；一般10万元</v>
       </c>
       <c r="F42" s="16" t="str">
         <v>公告</v>
@@ -40542,16 +41306,16 @@
         <v>已截止</v>
       </c>
       <c r="B43" s="13" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2026-06-14T00:00:00.000Z</v>
       </c>
       <c r="C43" s="14" t="str">
-        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
+        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
       </c>
       <c r="D43" s="15" t="str">
-        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
+        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
       </c>
       <c r="E43" s="15" t="str">
-        <v>其他一般≤10万、重点≤15万</v>
+        <v>10万元</v>
       </c>
       <c r="F43" s="16" t="str">
         <v>公告</v>
@@ -40562,16 +41326,16 @@
         <v>已截止</v>
       </c>
       <c r="B44" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-09-24T00:00:00.000Z</v>
       </c>
       <c r="C44" s="14" t="str">
-        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
+        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
       </c>
       <c r="D44" s="15" t="str">
-        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
+        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>10—15万元</v>
+        <v>其他一般≤10万、重点≤15万</v>
       </c>
       <c r="F44" s="16" t="str">
         <v>公告</v>
@@ -40582,16 +41346,16 @@
         <v>已截止</v>
       </c>
       <c r="B45" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
+        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
+        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
       </c>
       <c r="E45" s="15" t="str">
-        <v>3万元（首拨1万元，中期2万元）</v>
+        <v>10—15万元</v>
       </c>
       <c r="F45" s="16" t="str">
         <v>公告</v>
@@ -40602,17 +41366,16 @@
         <v>已截止</v>
       </c>
       <c r="B46" s="13" t="d">
-        <v>2022-10-30T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
+        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
+        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>已核官方2022历史公告：5万元/项；
-未取得2026正式指南，不将历史额度视为当期额度。</v>
+        <v>3万元（首拨1万元，中期2万元）</v>
       </c>
       <c r="F46" s="16" t="str">
         <v>公告</v>
@@ -40623,16 +41386,17 @@
         <v>已截止</v>
       </c>
       <c r="B47" s="13" t="d">
-        <v>2022-11-04T00:00:00.000Z</v>
+        <v>2022-10-30T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
+        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
+        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>一般2万元；重点4—6万元</v>
+        <v>已核官方2022历史公告：5万元/项；
+未取得2026正式指南，不将历史额度视为当期额度。</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
@@ -40643,16 +41407,16 @@
         <v>已截止</v>
       </c>
       <c r="B48" s="13" t="d">
-        <v>2023-07-30T00:00:00.000Z</v>
+        <v>2022-11-04T00:00:00.000Z</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
+        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
+        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>拟资助8—10项；单项金额未载</v>
+        <v>一般2万元；重点4—6万元</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
@@ -40663,16 +41427,16 @@
         <v>已截止</v>
       </c>
       <c r="B49" s="13" t="d">
-        <v>2024-09-30T00:00:00.000Z</v>
+        <v>2023-07-30T00:00:00.000Z</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>南昌大学·智能机器人江西省重点实验室</v>
+        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>智能机器人机构、感知与控制</v>
+        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>重点3万元、一般2万元（2024年度）</v>
+        <v>拟资助8—10项；单项金额未载</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
@@ -40683,16 +41447,16 @@
         <v>已截止</v>
       </c>
       <c r="B50" s="13" t="d">
-        <v>2025-03-31T00:00:00.000Z</v>
+        <v>2024-09-30T00:00:00.000Z</v>
       </c>
       <c r="C50" s="14" t="str">
-        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
+        <v>南昌大学·智能机器人江西省重点实验室</v>
       </c>
       <c r="D50" s="15" t="str">
-        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
+        <v>智能机器人机构、感知与控制</v>
       </c>
       <c r="E50" s="15" t="str">
-        <v>2—3万元/项左右</v>
+        <v>重点3万元、一般2万元（2024年度）</v>
       </c>
       <c r="F50" s="16" t="str">
         <v>公告</v>
@@ -40703,16 +41467,16 @@
         <v>已截止</v>
       </c>
       <c r="B51" s="13" t="d">
-        <v>2025-04-25T00:00:00.000Z</v>
+        <v>2025-03-31T00:00:00.000Z</v>
       </c>
       <c r="C51" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
       </c>
       <c r="D51" s="15" t="str">
-        <v>仿生机器人、新型驱动与感知及仿生装备</v>
+        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
       </c>
       <c r="E51" s="15" t="str">
-        <v>5万元</v>
+        <v>2—3万元/项左右</v>
       </c>
       <c r="F51" s="16" t="str">
         <v>公告</v>
@@ -40723,16 +41487,16 @@
         <v>已截止</v>
       </c>
       <c r="B52" s="13" t="d">
-        <v>2025-04-30T00:00:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C52" s="14" t="str">
-        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D52" s="15" t="str">
-        <v>共融机器人控制、复杂智能体系统协同与控制</v>
+        <v>仿生机器人、新型驱动与感知及仿生装备</v>
       </c>
       <c r="E52" s="15" t="str">
-        <v>评审确定</v>
+        <v>5万元</v>
       </c>
       <c r="F52" s="16" t="str">
         <v>公告</v>
@@ -40743,16 +41507,16 @@
         <v>已截止</v>
       </c>
       <c r="B53" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C53" s="14" t="str">
-        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
+        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
       </c>
       <c r="D53" s="15" t="str">
-        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
+        <v>共融机器人控制、复杂智能体系统协同与控制</v>
       </c>
       <c r="E53" s="15" t="str">
-        <v>5万元</v>
+        <v>评审确定</v>
       </c>
       <c r="F53" s="16" t="str">
         <v>公告</v>
@@ -40763,16 +41527,16 @@
         <v>已截止</v>
       </c>
       <c r="B54" s="13" t="d">
-        <v>2025-09-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C54" s="14" t="str">
-        <v>同济大学·自主智能无人系统全国重点实验室</v>
+        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
       </c>
       <c r="D54" s="15" t="str">
-        <v>自主智能无人系统与机器人感知、决策、控制</v>
+        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
       </c>
       <c r="E54" s="15" t="str">
-        <v>一般5—10万元、重点20—30万元</v>
+        <v>5万元</v>
       </c>
       <c r="F54" s="16" t="str">
         <v>公告</v>
@@ -40783,17 +41547,16 @@
         <v>已截止</v>
       </c>
       <c r="B55" s="13" t="d">
-        <v>2025-10-31T00:00:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C55" s="14" t="str">
-        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
+        <v>同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D55" s="15" t="str">
-        <v>机器人技术与系统、机器人学习、感知与控制</v>
+        <v>自主智能无人系统与机器人感知、决策、控制</v>
       </c>
       <c r="E55" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>一般5—10万元、重点20—30万元</v>
       </c>
       <c r="F55" s="16" t="str">
         <v>公告</v>
@@ -40804,17 +41567,17 @@
         <v>已截止</v>
       </c>
       <c r="B56" s="13" t="d">
-        <v>2025-11-03T00:00:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C56" s="14" t="str">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
+        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
       </c>
       <c r="D56" s="15" t="str">
-        <v>智能机器人感知、控制与系统</v>
+        <v>机器人技术与系统、机器人学习、感知与控制</v>
       </c>
       <c r="E56" s="15" t="str">
-        <v>校外开放基金1万元/项，拟5项；
-校内创新基金不同计划</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F56" s="16" t="str">
         <v>公告</v>
@@ -40825,16 +41588,17 @@
         <v>已截止</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2025-11-07T00:00:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
+        <v>智能机器人感知、控制与系统</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>2万元</v>
+        <v>校外开放基金1万元/项，拟5项；
+校内创新基金不同计划</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
@@ -40845,16 +41609,16 @@
         <v>已截止</v>
       </c>
       <c r="B58" s="13" t="d">
-        <v>2025-11-14T00:00:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C58" s="14" t="str">
-        <v>上海交通大学·机械系统与振动全国重点实验室</v>
+        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
       </c>
       <c r="D58" s="15" t="str">
-        <v>机器人设计、自主学习与神经接口</v>
+        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
       </c>
       <c r="E58" s="15" t="str">
-        <v>10—15万元</v>
+        <v>2万元</v>
       </c>
       <c r="F58" s="16" t="str">
         <v>公告</v>
@@ -40865,16 +41629,16 @@
         <v>已截止</v>
       </c>
       <c r="B59" s="13" t="d">
-        <v>2025-11-21T00:00:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
+        <v>上海交通大学·机械系统与振动全国重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>机器人视觉相关计算与随机数学方法</v>
+        <v>机器人设计、自主学习与神经接口</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>1—2万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
@@ -40885,16 +41649,16 @@
         <v>已截止</v>
       </c>
       <c r="B60" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
+        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
+        <v>机器人视觉相关计算与随机数学方法</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>不超过3万元</v>
+        <v>1—2万元</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
@@ -40905,16 +41669,16 @@
         <v>已截止</v>
       </c>
       <c r="B61" s="13" t="d">
-        <v>2025-12-20T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C61" s="14" t="str">
-        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
+        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
       </c>
       <c r="D61" s="15" t="str">
-        <v>山地农业机器人、果实收获视觉与智能农机</v>
+        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
       </c>
       <c r="E61" s="15" t="str">
-        <v>不超过5万元</v>
+        <v>不超过3万元</v>
       </c>
       <c r="F61" s="16" t="str">
         <v>公告</v>
@@ -40925,16 +41689,16 @@
         <v>已截止</v>
       </c>
       <c r="B62" s="13" t="d">
-        <v>2025-12-31T00:00:00.000Z</v>
+        <v>2025-12-20T00:00:00.000Z</v>
       </c>
       <c r="C62" s="14" t="str">
-        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
+        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
       </c>
       <c r="D62" s="15" t="str">
-        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
+        <v>山地农业机器人、果实收获视觉与智能农机</v>
       </c>
       <c r="E62" s="15" t="str">
-        <v>重点5万元、一般3万元</v>
+        <v>不超过5万元</v>
       </c>
       <c r="F62" s="16" t="str">
         <v>公告</v>
@@ -40945,16 +41709,16 @@
         <v>已截止</v>
       </c>
       <c r="B63" s="13" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C63" s="14" t="str">
-        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
+        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
       </c>
       <c r="D63" s="15" t="str">
-        <v>深海无人潜航装备与智能控制</v>
+        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
       </c>
       <c r="E63" s="15" t="str">
-        <v>不超过10万元</v>
+        <v>重点5万元、一般3万元</v>
       </c>
       <c r="F63" s="16" t="str">
         <v>公告</v>
@@ -40965,16 +41729,16 @@
         <v>已截止</v>
       </c>
       <c r="B64" s="13" t="d">
-        <v>2026-01-31T00:00:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C64" s="14" t="str">
-        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
+        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
       </c>
       <c r="D64" s="15" t="str">
-        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
+        <v>深海无人潜航装备与智能控制</v>
       </c>
       <c r="E64" s="15" t="str">
-        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
+        <v>不超过10万元</v>
       </c>
       <c r="F64" s="16" t="str">
         <v>公告</v>
@@ -40985,16 +41749,16 @@
         <v>已截止</v>
       </c>
       <c r="B65" s="13" t="d">
-        <v>2026-03-10T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C65" s="14" t="str">
-        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
+        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
       </c>
       <c r="D65" s="15" t="str">
-        <v>工业机器人与柔性制造产线集成</v>
+        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
       </c>
       <c r="E65" s="15" t="str">
-        <v>4万元</v>
+        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
       </c>
       <c r="F65" s="16" t="str">
         <v>公告</v>
@@ -41005,16 +41769,16 @@
         <v>已截止</v>
       </c>
       <c r="B66" s="13" t="d">
-        <v>2026-03-20T00:00:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C66" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室</v>
+        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
       </c>
       <c r="D66" s="15" t="str">
-        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
+        <v>工业机器人与柔性制造产线集成</v>
       </c>
       <c r="E66" s="15" t="str">
-        <v>单项不超过10万元</v>
+        <v>4万元</v>
       </c>
       <c r="F66" s="16" t="str">
         <v>公告</v>
@@ -41025,16 +41789,16 @@
         <v>已截止</v>
       </c>
       <c r="B67" s="13" t="d">
-        <v>2026-04-15T00:00:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C67" s="14" t="str">
-        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室</v>
       </c>
       <c r="D67" s="15" t="str">
-        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
+        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
       </c>
       <c r="E67" s="15" t="str">
-        <v>一般5—8万元；重点20万元</v>
+        <v>单项不超过10万元</v>
       </c>
       <c r="F67" s="16" t="str">
         <v>公告</v>
@@ -41045,16 +41809,16 @@
         <v>已截止</v>
       </c>
       <c r="B68" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C68" s="14" t="str">
-        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
+        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
       </c>
       <c r="D68" s="15" t="str">
-        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
+        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
       </c>
       <c r="E68" s="15" t="str">
-        <v>5万元</v>
+        <v>一般5—8万元；重点20万元</v>
       </c>
       <c r="F68" s="16" t="str">
         <v>公告</v>
@@ -41068,14 +41832,13 @@
         <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C69" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
+        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
       </c>
       <c r="D69" s="15" t="str">
-        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
+        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
       </c>
       <c r="E69" s="15" t="str">
-        <v>单项原则上不超过10万元；
-100万元是本批次总额，不是单项额度。</v>
+        <v>5万元</v>
       </c>
       <c r="F69" s="16" t="str">
         <v>公告</v>
@@ -41086,16 +41849,17 @@
         <v>已截止</v>
       </c>
       <c r="B70" s="13" t="d">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C70" s="14" t="str">
-        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
       </c>
       <c r="D70" s="15" t="str">
-        <v>无人系统多源感知、导航与控制</v>
+        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
       </c>
       <c r="E70" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>单项原则上不超过10万元；
+100万元是本批次总额，不是单项额度。</v>
       </c>
       <c r="F70" s="16" t="str">
         <v>公告</v>
@@ -41106,16 +41870,16 @@
         <v>已截止</v>
       </c>
       <c r="B71" s="13" t="d">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C71" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
       </c>
       <c r="D71" s="15" t="str">
-        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
+        <v>无人系统多源感知、导航与控制</v>
       </c>
       <c r="E71" s="15" t="str">
-        <v>5万元/项；拟8项</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F71" s="16" t="str">
         <v>公告</v>
@@ -41126,16 +41890,16 @@
         <v>已截止</v>
       </c>
       <c r="B72" s="13" t="d">
-        <v>2026-04-30T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C72" s="14" t="str">
-        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D72" s="15" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
       </c>
       <c r="E72" s="15" t="str">
-        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
+        <v>5万元/项；拟8项</v>
       </c>
       <c r="F72" s="16" t="str">
         <v>公告</v>
@@ -41149,13 +41913,13 @@
         <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C73" s="14" t="str">
-        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
+        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
       </c>
       <c r="D73" s="15" t="str">
-        <v>警用智能机器人与协同任务</v>
+        <v>智能无人系统感知、规划与控制</v>
       </c>
       <c r="E73" s="15" t="str">
-        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
+        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="F73" s="16" t="str">
         <v>公告</v>
@@ -41166,16 +41930,16 @@
         <v>已截止</v>
       </c>
       <c r="B74" s="13" t="d">
-        <v>2026-05-06T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C74" s="14" t="str">
-        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
+        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
       </c>
       <c r="D74" s="15" t="str">
-        <v>具身智能（仅保留正式指南第7项方向）</v>
+        <v>警用智能机器人与协同任务</v>
       </c>
       <c r="E74" s="15" t="str">
-        <v>10—15万元</v>
+        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="F74" s="16" t="str">
         <v>公告</v>
@@ -41186,16 +41950,16 @@
         <v>已截止</v>
       </c>
       <c r="B75" s="13" t="d">
-        <v>2026-05-14T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C75" s="14" t="str">
-        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
+        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
       </c>
       <c r="D75" s="15" t="str">
-        <v>具身机器人磨削、抛光及加工技能</v>
+        <v>具身智能（仅保留正式指南第7项方向）</v>
       </c>
       <c r="E75" s="15" t="str">
-        <v>一般1—2万元、重点3—5万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F75" s="16" t="str">
         <v>公告</v>
@@ -41206,16 +41970,16 @@
         <v>已截止</v>
       </c>
       <c r="B76" s="13" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-14T00:00:00.000Z</v>
       </c>
       <c r="C76" s="14" t="str">
-        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
+        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
       </c>
       <c r="D76" s="15" t="str">
-        <v>前沿交叉方向中的手术机器人应用与验证</v>
+        <v>具身机器人磨削、抛光及加工技能</v>
       </c>
       <c r="E76" s="15" t="str">
-        <v>4万元</v>
+        <v>一般1—2万元、重点3—5万元</v>
       </c>
       <c r="F76" s="16" t="str">
         <v>公告</v>
@@ -41226,16 +41990,16 @@
         <v>已截止</v>
       </c>
       <c r="B77" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C77" s="14" t="str">
-        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
+        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
       </c>
       <c r="D77" s="15" t="str">
-        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
+        <v>前沿交叉方向中的手术机器人应用与验证</v>
       </c>
       <c r="E77" s="15" t="str">
-        <v>不超过1万元</v>
+        <v>4万元</v>
       </c>
       <c r="F77" s="16" t="str">
         <v>公告</v>
@@ -41246,16 +42010,16 @@
         <v>已截止</v>
       </c>
       <c r="B78" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C78" s="14" t="str">
-        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
+        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
       </c>
       <c r="D78" s="15" t="str">
-        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
+        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
       </c>
       <c r="E78" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>不超过1万元</v>
       </c>
       <c r="F78" s="16" t="str">
         <v>公告</v>
@@ -41266,16 +42030,16 @@
         <v>已截止</v>
       </c>
       <c r="B79" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C79" s="14" t="str">
-        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
+        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
       </c>
       <c r="D79" s="15" t="str">
-        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
+        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
       </c>
       <c r="E79" s="15" t="str">
-        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F79" s="16" t="str">
         <v>公告</v>
@@ -41289,13 +42053,13 @@
         <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C80" s="14" t="str">
-        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
+        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
       </c>
       <c r="D80" s="15" t="str">
-        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
+        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
       </c>
       <c r="E80" s="15" t="str">
-        <v>原则5万元/项；可按评审增加，上限未载</v>
+        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
       </c>
       <c r="F80" s="16" t="str">
         <v>公告</v>
@@ -41306,16 +42070,16 @@
         <v>已截止</v>
       </c>
       <c r="B81" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C81" s="14" t="str">
-        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
+        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
       </c>
       <c r="D81" s="15" t="str">
-        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
+        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
       </c>
       <c r="E81" s="15" t="str">
-        <v>5万元/项；专项拟2项</v>
+        <v>原则5万元/项；可按评审增加，上限未载</v>
       </c>
       <c r="F81" s="16" t="str">
         <v>公告</v>
@@ -41326,16 +42090,16 @@
         <v>已截止</v>
       </c>
       <c r="B82" s="13" t="d">
-        <v>2026-07-12T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C82" s="14" t="str">
-        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
+        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
       </c>
       <c r="D82" s="15" t="str">
-        <v>无人机轨迹与协同、自主采样探测装备</v>
+        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
       </c>
       <c r="E82" s="15" t="str">
-        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
+        <v>5万元/项；专项拟2项</v>
       </c>
       <c r="F82" s="16" t="str">
         <v>公告</v>
@@ -41346,16 +42110,16 @@
         <v>已截止</v>
       </c>
       <c r="B83" s="13" t="d">
-        <v>2026-07-19T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C83" s="14" t="str">
-        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
+        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
       </c>
       <c r="D83" s="15" t="str">
-        <v>具身智能传感、闭环感知与人机交互意图识别</v>
+        <v>无人机轨迹与协同、自主采样探测装备</v>
       </c>
       <c r="E83" s="15" t="str">
-        <v>10万元</v>
+        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
       </c>
       <c r="F83" s="16" t="str">
         <v>公告</v>
@@ -41366,16 +42130,16 @@
         <v>已截止</v>
       </c>
       <c r="B84" s="13" t="d">
-        <v>2026-07-25T00:00:00.000Z</v>
+        <v>2026-07-19T00:00:00.000Z</v>
       </c>
       <c r="C84" s="14" t="str">
-        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
+        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
       </c>
       <c r="D84" s="15" t="str">
-        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
+        <v>具身智能传感、闭环感知与人机交互意图识别</v>
       </c>
       <c r="E84" s="15" t="str">
-        <v>2—4万元</v>
+        <v>10万元</v>
       </c>
       <c r="F84" s="16" t="str">
         <v>公告</v>
@@ -41386,16 +42150,16 @@
         <v>已截止</v>
       </c>
       <c r="B85" s="13" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-07-25T00:00:00.000Z</v>
       </c>
       <c r="C85" s="14" t="str">
-        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
+        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
       </c>
       <c r="D85" s="15" t="str">
-        <v>智能机器人信息感知、多源融合与控制</v>
+        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
       </c>
       <c r="E85" s="15" t="str">
-        <v>约2万元</v>
+        <v>2—4万元</v>
       </c>
       <c r="F85" s="16" t="str">
         <v>公告</v>
@@ -41406,16 +42170,16 @@
         <v>已截止</v>
       </c>
       <c r="B86" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C86" s="14" t="str">
-        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
+        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
       </c>
       <c r="D86" s="15" t="str">
-        <v>机器人集成与医疗康复智能制造装备</v>
+        <v>智能机器人信息感知、多源融合与控制</v>
       </c>
       <c r="E86" s="15" t="str">
-        <v>一般2万元、重点3万元</v>
+        <v>约2万元</v>
       </c>
       <c r="F86" s="16" t="str">
         <v>公告</v>
@@ -41429,13 +42193,13 @@
         <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C87" s="14" t="str">
-        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
+        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
       </c>
       <c r="D87" s="15" t="str">
-        <v>桥梁与水下缺陷无人机器人检测</v>
+        <v>机器人集成与医疗康复智能制造装备</v>
       </c>
       <c r="E87" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>一般2万元、重点3万元</v>
       </c>
       <c r="F87" s="16" t="str">
         <v>公告</v>
@@ -41446,16 +42210,16 @@
         <v>已截止</v>
       </c>
       <c r="B88" s="13" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C88" s="14" t="str">
-        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
+        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
       </c>
       <c r="D88" s="15" t="str">
-        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
+        <v>桥梁与水下缺陷无人机器人检测</v>
       </c>
       <c r="E88" s="15" t="str">
-        <v>5万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F88" s="16" t="str">
         <v>公告</v>
@@ -41466,16 +42230,16 @@
         <v>已截止</v>
       </c>
       <c r="B89" s="13" t="d">
-        <v>2026-08-30T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C89" s="14" t="str">
-        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
+        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
       </c>
       <c r="D89" s="15" t="str">
-        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
+        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
       </c>
       <c r="E89" s="15" t="str">
-        <v>重点5万元；一般2万元；共6—8项</v>
+        <v>5万元</v>
       </c>
       <c r="F89" s="16" t="str">
         <v>公告</v>
@@ -41486,16 +42250,16 @@
         <v>已截止</v>
       </c>
       <c r="B90" s="13" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-30T00:00:00.000Z</v>
       </c>
       <c r="C90" s="14" t="str">
-        <v>四川警察学院·智能警务四川省重点实验室</v>
+        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
       </c>
       <c r="D90" s="15" t="str">
-        <v>无人机、车辆与机器狗异构协同及应急救援</v>
+        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
       </c>
       <c r="E90" s="15" t="str">
-        <v>重点15万元、一般10万元、青年5万元</v>
+        <v>重点5万元；一般2万元；共6—8项</v>
       </c>
       <c r="F90" s="16" t="str">
         <v>公告</v>
@@ -41506,17 +42270,16 @@
         <v>已截止</v>
       </c>
       <c r="B91" s="13" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C91" s="14" t="str">
-        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
+        <v>四川警察学院·智能警务四川省重点实验室</v>
       </c>
       <c r="D91" s="15" t="str">
-        <v>特种机器人多源感知、轨迹与动力学控制</v>
+        <v>无人机、车辆与机器狗异构协同及应急救援</v>
       </c>
       <c r="E91" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>重点15万元、一般10万元、青年5万元</v>
       </c>
       <c r="F91" s="16" t="str">
         <v>公告</v>
@@ -41527,16 +42290,17 @@
         <v>已截止</v>
       </c>
       <c r="B92" s="13" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C92" s="14" t="str">
-        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
       </c>
       <c r="D92" s="15" t="str">
-        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+        <v>特种机器人多源感知、轨迹与动力学控制</v>
       </c>
       <c r="E92" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F92" s="16" t="str">
         <v>公告</v>
@@ -41547,40 +42311,39 @@
         <v>已截止</v>
       </c>
       <c r="B93" s="13" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="C93" s="14" t="str">
+        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+      </c>
+      <c r="D93" s="15" t="str">
+        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+      </c>
+      <c r="E93" s="15" t="str">
+        <v>不超过2万元</v>
+      </c>
+      <c r="F93" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="94" ht="66" customHeight="1">
+      <c r="A94" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B94" s="13" t="d">
         <v>2026-09-27T00:00:00.000Z</v>
       </c>
-      <c r="C93" s="14" t="str">
+      <c r="C94" s="14" t="str">
         <v>云南大学·云南省智能系统与计算重点实验室</v>
       </c>
-      <c r="D93" s="15" t="str">
+      <c r="D94" s="15" t="str">
         <v>低空无人系统集群协同（仅保留具体无人装备方向）</v>
       </c>
-      <c r="E93" s="15" t="str">
+      <c r="E94" s="15" t="str">
         <v>重点≤8万元；
 一般≤2万元；
 定向1万元。</v>
       </c>
-      <c r="F93" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="94" ht="66" customHeight="1">
-      <c r="A94" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B94" s="13" t="d">
-        <v>2026-10-05T00:00:00.000Z</v>
-      </c>
-      <c r="C94" s="14" t="str">
-        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
-      </c>
-      <c r="D94" s="15" t="str">
-        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
-      </c>
-      <c r="E94" s="15" t="str">
-        <v>重点60—100万元；
-一般15—20万元</v>
-      </c>
       <c r="F94" s="16" t="str">
         <v>公告</v>
       </c>
@@ -41590,16 +42353,17 @@
         <v>已截止</v>
       </c>
       <c r="B95" s="13" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-05T00:00:00.000Z</v>
       </c>
       <c r="C95" s="14" t="str">
-        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
+        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
       </c>
       <c r="D95" s="15" t="str">
-        <v>机器人遥操作、双臂操作与人机协同</v>
+        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
       </c>
       <c r="E95" s="15" t="str">
-        <v>公告未公布统一金额，评审确定。</v>
+        <v>重点60—100万元；
+一般15—20万元</v>
       </c>
       <c r="F95" s="16" t="str">
         <v>公告</v>
@@ -41613,13 +42377,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C96" s="14" t="str">
-        <v>中北大学·微纳器件与系统教育部重点实验室</v>
+        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
       </c>
       <c r="D96" s="15" t="str">
-        <v>微型机器人及微纳执行器、精密定位</v>
+        <v>机器人遥操作、双臂操作与人机协同</v>
       </c>
       <c r="E96" s="15" t="str">
-        <v>2—4万元</v>
+        <v>公告未公布统一金额，评审确定。</v>
       </c>
       <c r="F96" s="16" t="str">
         <v>公告</v>
@@ -41633,13 +42397,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C97" s="14" t="str">
-        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
+        <v>中北大学·微纳器件与系统教育部重点实验室</v>
       </c>
       <c r="D97" s="15" t="str">
-        <v>机器人机械臂抓取、路径规划与自主导航</v>
+        <v>微型机器人及微纳执行器、精密定位</v>
       </c>
       <c r="E97" s="15" t="str">
-        <v>一般2万元；重点4万元（以评审为准）</v>
+        <v>2—4万元</v>
       </c>
       <c r="F97" s="16" t="str">
         <v>公告</v>
@@ -41653,13 +42417,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C98" s="14" t="str">
-        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
+        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
       </c>
       <c r="D98" s="15" t="str">
-        <v>无人平台智能探测与多源感知</v>
+        <v>机器人机械臂抓取、路径规划与自主导航</v>
       </c>
       <c r="E98" s="15" t="str">
-        <v>2—4万元/项，拟5—8项</v>
+        <v>一般2万元；重点4万元（以评审为准）</v>
       </c>
       <c r="F98" s="16" t="str">
         <v>公告</v>
@@ -41673,36 +42437,36 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C99" s="14" t="str">
-        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
       </c>
       <c r="D99" s="15" t="str">
-        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+        <v>无人平台智能探测与多源感知</v>
       </c>
       <c r="E99" s="15" t="str">
-        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+        <v>2—4万元/项，拟5—8项</v>
       </c>
       <c r="F99" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="100" ht="96" customHeight="1">
-      <c r="A100" t="str" s="18">
+    <row r="100" ht="66" customHeight="1">
+      <c r="A100" s="18" t="str">
         <v>已截止</v>
       </c>
-      <c r="B100" t="n" s="13">
-        <v>46295</v>
-      </c>
-      <c r="C100" t="str" s="14">
-        <v>上海交通大学·海洋工程全国重点实验室</v>
-      </c>
-      <c r="D100" t="str" s="15">
-        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
-      </c>
-      <c r="E100" t="str" s="15">
-        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
-      </c>
-      <c r="F100" t="str" s="16">
-        <v>官方公告</v>
+      <c r="B100" s="13" t="d">
+        <v>2026-10-08T00:00:00.000Z</v>
+      </c>
+      <c r="C100" s="14" t="str">
+        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+      </c>
+      <c r="D100" s="15" t="str">
+        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+      </c>
+      <c r="E100" s="15" t="str">
+        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+      </c>
+      <c r="F100" s="16" t="str">
+        <v>公告</v>
       </c>
     </row>
     <row r="101" ht="96" customHeight="1">
@@ -41710,16 +42474,16 @@
         <v>已截止</v>
       </c>
       <c r="B101" t="n" s="13">
-        <v>45503</v>
+        <v>46295</v>
       </c>
       <c r="C101" t="str" s="14">
-        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
+        <v>上海交通大学·海洋工程全国重点实验室</v>
       </c>
       <c r="D101" t="str" s="15">
-        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
+        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
       </c>
       <c r="E101" t="str" s="15">
-        <v>3万元/项；计划10项。</v>
+        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
       </c>
       <c r="F101" t="str" s="16">
         <v>官方公告</v>
@@ -41730,16 +42494,16 @@
         <v>已截止</v>
       </c>
       <c r="B102" t="n" s="13">
-        <v>46006</v>
+        <v>45503</v>
       </c>
       <c r="C102" t="str" s="14">
-        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
+        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
       </c>
       <c r="D102" t="str" s="15">
-        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
+        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
       </c>
       <c r="E102" t="str" s="15">
-        <v>正文未公开具体资助金额。</v>
+        <v>3万元/项；计划10项。</v>
       </c>
       <c r="F102" t="str" s="16">
         <v>官方公告</v>
@@ -41750,16 +42514,16 @@
         <v>已截止</v>
       </c>
       <c r="B103" t="n" s="13">
-        <v>46193</v>
+        <v>46006</v>
       </c>
       <c r="C103" t="str" s="14">
-        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
+        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
       <c r="D103" t="str" s="15">
-        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
+        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
       </c>
       <c r="E103" t="str" s="15">
-        <v>一般项目≤5万元/项；计划12项。</v>
+        <v>正文未公开具体资助金额。</v>
       </c>
       <c r="F103" t="str" s="16">
         <v>官方公告</v>
@@ -41770,16 +42534,16 @@
         <v>已截止</v>
       </c>
       <c r="B104" t="n" s="13">
-        <v>44434</v>
+        <v>46193</v>
       </c>
       <c r="C104" t="str" s="14">
-        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
       </c>
       <c r="D104" t="str" s="15">
-        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
       </c>
       <c r="E104" t="str" s="15">
-        <v>重点2万元/项；一般1万元/项。</v>
+        <v>一般项目≤5万元/项；计划12项。</v>
       </c>
       <c r="F104" t="str" s="16">
         <v>官方公告</v>
@@ -41790,16 +42554,16 @@
         <v>已截止</v>
       </c>
       <c r="B105" t="n" s="13">
-        <v>45163</v>
+        <v>44434</v>
       </c>
       <c r="C105" t="str" s="14">
-        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
       </c>
       <c r="D105" t="str" s="15">
-        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
       </c>
       <c r="E105" t="str" s="15">
-        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+        <v>重点2万元/项；一般1万元/项。</v>
       </c>
       <c r="F105" t="str" s="16">
         <v>官方公告</v>
@@ -41810,16 +42574,16 @@
         <v>已截止</v>
       </c>
       <c r="B106" t="n" s="13">
-        <v>45991</v>
+        <v>45163</v>
       </c>
       <c r="C106" t="str" s="14">
-        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
       </c>
       <c r="D106" t="str" s="15">
-        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
       </c>
       <c r="E106" t="str" s="15">
-        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
       </c>
       <c r="F106" t="str" s="16">
         <v>官方公告</v>
@@ -41827,21 +42591,41 @@
     </row>
     <row r="107" ht="96" customHeight="1">
       <c r="A107" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B107" t="n" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C107" t="str" s="14">
+        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+      </c>
+      <c r="D107" t="str" s="15">
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+      </c>
+      <c r="E107" t="str" s="15">
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+      </c>
+      <c r="F107" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="108" ht="96" customHeight="1">
+      <c r="A108" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B107" t="n" s="13">
+      <c r="B108" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C107" t="str" s="14">
+      <c r="C108" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D107" t="str" s="15">
+      <c r="D108" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E107" t="str" s="15">
+      <c r="E108" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F107" t="str" s="16">
+      <c r="F108" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -41857,8 +42641,8 @@
     <hyperlink ref="F5" ns1:id="Rff2d595907084ed9"/>
     <hyperlink ref="C6" location="'02项目完整详情'!A61"/>
     <hyperlink ref="F6" ns1:id="R840dfc7ac2ef4322"/>
-    <hyperlink ref="C39" location="'02项目完整详情'!A113"/>
-    <hyperlink ref="F39" ns1:id="Re902984ea1114a1f"/>
+    <hyperlink ref="C40" location="'02项目完整详情'!A113"/>
+    <hyperlink ref="F40" ns1:id="Re902984ea1114a1f"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A62"/>
     <hyperlink ref="F7" ns1:id="Ra6ff56d69fd14f0d"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A63"/>
@@ -41875,8 +42659,8 @@
     <hyperlink ref="F16" ns1:id="R5d6c0e16ca9148f1"/>
     <hyperlink ref="C17" location="'02项目完整详情'!A141"/>
     <hyperlink ref="F17" ns1:id="R29345038c30a4733"/>
-    <hyperlink ref="C40" location="'02项目完整详情'!A85"/>
-    <hyperlink ref="F40" ns1:id="R486c032b769d4524"/>
+    <hyperlink ref="C41" location="'02项目完整详情'!A85"/>
+    <hyperlink ref="F41" ns1:id="R486c032b769d4524"/>
     <hyperlink ref="C18" location="'02项目完整详情'!A99"/>
     <hyperlink ref="F18" ns1:id="R19ee0f6cf8d14ed3"/>
     <hyperlink ref="C19" location="'02项目完整详情'!A143"/>
@@ -41885,180 +42669,182 @@
     <hyperlink ref="F20" ns1:id="R83b69720fcfc4e60"/>
     <hyperlink ref="C21" location="'02项目完整详情'!A127"/>
     <hyperlink ref="F21" ns1:id="Ra979348b05084966"/>
-    <hyperlink ref="C22" location="'02项目完整详情'!A66"/>
-    <hyperlink ref="F22" ns1:id="R4dc201fc29cb4ab4"/>
-    <hyperlink ref="C41" location="'02项目完整详情'!A139"/>
-    <hyperlink ref="F41" ns1:id="Rf4dc98016cfb49fd"/>
-    <hyperlink ref="C23" location="'02项目完整详情'!A151"/>
-    <hyperlink ref="F23" ns1:id="R3d89872d06fd4b60"/>
-    <hyperlink ref="C24" location="'02项目完整详情'!A67"/>
-    <hyperlink ref="F24" ns1:id="R1e9b7d2bc63d4258"/>
-    <hyperlink ref="C42" location="'02项目完整详情'!A68"/>
-    <hyperlink ref="F42" ns1:id="R5d0261ffe45c4155"/>
-    <hyperlink ref="C25" location="'02项目完整详情'!A69"/>
-    <hyperlink ref="F25" ns1:id="Reeb11b878b934f2d"/>
-    <hyperlink ref="C26" location="'02项目完整详情'!A70"/>
-    <hyperlink ref="F26" ns1:id="R5b06defce5864a96"/>
-    <hyperlink ref="C27" location="'02项目完整详情'!A71"/>
-    <hyperlink ref="F27" ns1:id="Ra48afdb9842a4366"/>
-    <hyperlink ref="C43" location="'02项目完整详情'!A72"/>
-    <hyperlink ref="F43" ns1:id="Rb3b4681efcdd44d4"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A73"/>
-    <hyperlink ref="F44" ns1:id="R4f0b800598574b86"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A74"/>
-    <hyperlink ref="F45" ns1:id="R56697ca79cd54a14"/>
-    <hyperlink ref="C33" location="'02项目完整详情'!A75"/>
-    <hyperlink ref="F33" ns1:id="R0814a7680dde4f9a"/>
-    <hyperlink ref="C34" location="'02项目完整详情'!A76"/>
-    <hyperlink ref="F34" ns1:id="R3f222e6bf9fa46ec"/>
-    <hyperlink ref="C35" location="'02项目完整详情'!A77"/>
-    <hyperlink ref="F35" ns1:id="Rc66c2cf37bbc404d"/>
-    <hyperlink ref="C36" location="'02项目完整详情'!A78"/>
-    <hyperlink ref="F36" ns1:id="R90e03710dfe04e74"/>
-    <hyperlink ref="C37" location="'02项目完整详情'!A79"/>
-    <hyperlink ref="F37" ns1:id="R80f5129c1ee24096"/>
-    <hyperlink ref="C38" location="'02项目完整详情'!A80"/>
-    <hyperlink ref="F38" ns1:id="R6360db00742b45ec"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A81"/>
-    <hyperlink ref="F46" ns1:id="Rc4146f6376594d01"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A156"/>
-    <hyperlink ref="F47" ns1:id="R97ba6e4965084c76"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A155"/>
-    <hyperlink ref="F48" ns1:id="Rcbdc080795344925"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A83"/>
-    <hyperlink ref="F49" ns1:id="R9e6afd1b359743bb"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A154"/>
-    <hyperlink ref="F50" ns1:id="Rb320e0a5ad524836"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A86"/>
-    <hyperlink ref="F51" ns1:id="R42a660aaeb1d4c95"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A87"/>
-    <hyperlink ref="F52" ns1:id="R88784a2520864683"/>
-    <hyperlink ref="C28" location="'02项目完整详情'!A88"/>
-    <hyperlink ref="F28" ns1:id="Rcb8b33dae69a4731"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A89"/>
-    <hyperlink ref="F53" ns1:id="Rd5ea9c8442ca46ac"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A90"/>
-    <hyperlink ref="F54" ns1:id="R7734727212364cb2"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A91"/>
-    <hyperlink ref="F55" ns1:id="R78b8c8c0ca954ecb"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A92"/>
-    <hyperlink ref="F56" ns1:id="Rfdf5f46608d44776"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A93"/>
-    <hyperlink ref="F57" ns1:id="R82f06426c3d54976"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A94"/>
-    <hyperlink ref="F58" ns1:id="R3cae8e186c48414b"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A95"/>
-    <hyperlink ref="F59" ns1:id="Ra7f1aef2362a4a4a"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A96"/>
-    <hyperlink ref="F60" ns1:id="R8befa90ef3fc47c2"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A97"/>
-    <hyperlink ref="F61" ns1:id="Re7fdcbfdd1084572"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A98"/>
-    <hyperlink ref="F62" ns1:id="R65ca925ee60b42a7"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A100"/>
-    <hyperlink ref="F63" ns1:id="Reb76655df7374bc5"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A166"/>
-    <hyperlink ref="F64" ns1:id="R055caeb6a90642b5"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A102"/>
-    <hyperlink ref="F65" ns1:id="Rfff5ca38a0554ba3"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A103"/>
-    <hyperlink ref="F66" ns1:id="R0888add655cd4fba"/>
-    <hyperlink ref="C32" location="'02项目完整详情'!A104"/>
-    <hyperlink ref="F32" ns1:id="Rd9709f11bc9f4e83"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A163"/>
-    <hyperlink ref="F67" ns1:id="R20412a2edb1c448a"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A105"/>
-    <hyperlink ref="F68" ns1:id="R61772b79401a4268"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A106"/>
-    <hyperlink ref="F69" ns1:id="R987b8e6f52a74110"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A107"/>
-    <hyperlink ref="F70" ns1:id="R0c4396d550f2475f"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A162"/>
-    <hyperlink ref="F71" ns1:id="R4f11bd52ab71481c"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A108"/>
-    <hyperlink ref="F72" ns1:id="R4db82e37256244c2"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A109"/>
-    <hyperlink ref="F73" ns1:id="R4031c47a301e406d"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A110"/>
-    <hyperlink ref="F74" ns1:id="Raa160d321af04db8"/>
-    <hyperlink ref="C29" location="'02项目完整详情'!A111"/>
-    <hyperlink ref="F29" ns1:id="R769c1e9ff31b4410"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A112"/>
-    <hyperlink ref="F75" ns1:id="R4cdea66d1ef84e88"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A114"/>
-    <hyperlink ref="F76" ns1:id="Rfe9d4bacb83a4b3a"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A115"/>
-    <hyperlink ref="F77" ns1:id="Rdb52bb1fc14c4902"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A116"/>
-    <hyperlink ref="F78" ns1:id="Raea0cb8061aa4114"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A153"/>
-    <hyperlink ref="F79" ns1:id="Re209c4141aad4cc2"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A152"/>
-    <hyperlink ref="F80" ns1:id="R929ae2605c414e9f"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A165"/>
-    <hyperlink ref="F81" ns1:id="R1abe4cdaf9e34bae"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A117"/>
-    <hyperlink ref="F82" ns1:id="R0a10fce99c274f93"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A118"/>
-    <hyperlink ref="F83" ns1:id="R938383f864354c81"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A119"/>
-    <hyperlink ref="F84" ns1:id="Rf5654ce2b68c4be9"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A121"/>
-    <hyperlink ref="F85" ns1:id="Rcb7b406cd4eb4fbf"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A123"/>
-    <hyperlink ref="F86" ns1:id="R5815a7bd80814259"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A124"/>
-    <hyperlink ref="F87" ns1:id="R0c410df45d8a4e3d"/>
-    <hyperlink ref="C30" location="'02项目完整详情'!A125"/>
-    <hyperlink ref="F30" ns1:id="R431b21fd445f4abe"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A126"/>
-    <hyperlink ref="F88" ns1:id="R567091a279bf498d"/>
-    <hyperlink ref="C89" location="'02项目完整详情'!A164"/>
-    <hyperlink ref="F89" ns1:id="Re392bfd9b5274c72"/>
-    <hyperlink ref="C90" location="'02项目完整详情'!A128"/>
-    <hyperlink ref="F90" ns1:id="Re6cada6d8cc14329"/>
-    <hyperlink ref="C91" location="'02项目完整详情'!A129"/>
-    <hyperlink ref="F91" ns1:id="R8fc1cda8f3b6430e"/>
-    <hyperlink ref="C92" location="'02项目完整详情'!A130"/>
-    <hyperlink ref="F92" ns1:id="R27a55a96c3f24c5f"/>
-    <hyperlink ref="C93" location="'02项目完整详情'!A131"/>
-    <hyperlink ref="F93" ns1:id="R5e47895d5a614c2b"/>
-    <hyperlink ref="C31" location="'02项目完整详情'!A132"/>
-    <hyperlink ref="F31" ns1:id="R3b43825c6bac4d00"/>
-    <hyperlink ref="C94" location="'02项目完整详情'!A133"/>
-    <hyperlink ref="F94" ns1:id="R93e0d1bfa9de4923"/>
-    <hyperlink ref="C95" location="'02项目完整详情'!A40"/>
-    <hyperlink ref="F95" ns1:id="R8485fac45d264a2f"/>
-    <hyperlink ref="C96" location="'02项目完整详情'!A41"/>
-    <hyperlink ref="F96" ns1:id="R1c0f567749234b9c"/>
-    <hyperlink ref="C97" location="'02项目完整详情'!A42"/>
-    <hyperlink ref="F97" ns1:id="Rbf215fc93e064e7e"/>
-    <hyperlink ref="C98" location="'02项目完整详情'!A43"/>
-    <hyperlink ref="F98" ns1:id="R53db146b46f44f15"/>
-    <hyperlink ref="C99" location="'02项目完整详情'!A44"/>
-    <hyperlink ref="F99" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F107" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C107" location="'02项目完整详情'!A148"/>
-    <hyperlink ref="C100" location="'02项目完整详情'!A167" display="项目完整详情"/>
-    <hyperlink ref="F100" ns1:id="rIdSystematic98"/>
-    <hyperlink ref="C101" location="'02项目完整详情'!A168" display="项目完整详情"/>
-    <hyperlink ref="F101" ns1:id="rIdSystematic99"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A175" display="项目完整详情"/>
-    <hyperlink ref="F102" ns1:id="rIdSystematic100"/>
-    <hyperlink ref="C103" location="'02项目完整详情'!A176" display="项目完整详情"/>
-    <hyperlink ref="F103" ns1:id="rIdSystematic101"/>
+    <hyperlink ref="C23" location="'02项目完整详情'!A66"/>
+    <hyperlink ref="F23" ns1:id="R4dc201fc29cb4ab4"/>
+    <hyperlink ref="C42" location="'02项目完整详情'!A139"/>
+    <hyperlink ref="F42" ns1:id="Rf4dc98016cfb49fd"/>
+    <hyperlink ref="C24" location="'02项目完整详情'!A151"/>
+    <hyperlink ref="F24" ns1:id="R3d89872d06fd4b60"/>
+    <hyperlink ref="C25" location="'02项目完整详情'!A67"/>
+    <hyperlink ref="F25" ns1:id="R1e9b7d2bc63d4258"/>
+    <hyperlink ref="C43" location="'02项目完整详情'!A68"/>
+    <hyperlink ref="F43" ns1:id="R5d0261ffe45c4155"/>
+    <hyperlink ref="C26" location="'02项目完整详情'!A69"/>
+    <hyperlink ref="F26" ns1:id="Reeb11b878b934f2d"/>
+    <hyperlink ref="C27" location="'02项目完整详情'!A70"/>
+    <hyperlink ref="F27" ns1:id="R5b06defce5864a96"/>
+    <hyperlink ref="C28" location="'02项目完整详情'!A71"/>
+    <hyperlink ref="F28" ns1:id="Ra48afdb9842a4366"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A72"/>
+    <hyperlink ref="F44" ns1:id="Rb3b4681efcdd44d4"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A73"/>
+    <hyperlink ref="F45" ns1:id="R4f0b800598574b86"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A74"/>
+    <hyperlink ref="F46" ns1:id="R56697ca79cd54a14"/>
+    <hyperlink ref="C34" location="'02项目完整详情'!A75"/>
+    <hyperlink ref="F34" ns1:id="R0814a7680dde4f9a"/>
+    <hyperlink ref="C35" location="'02项目完整详情'!A76"/>
+    <hyperlink ref="F35" ns1:id="R3f222e6bf9fa46ec"/>
+    <hyperlink ref="C36" location="'02项目完整详情'!A77"/>
+    <hyperlink ref="F36" ns1:id="Rc66c2cf37bbc404d"/>
+    <hyperlink ref="C37" location="'02项目完整详情'!A78"/>
+    <hyperlink ref="F37" ns1:id="R90e03710dfe04e74"/>
+    <hyperlink ref="C38" location="'02项目完整详情'!A79"/>
+    <hyperlink ref="F38" ns1:id="R80f5129c1ee24096"/>
+    <hyperlink ref="C39" location="'02项目完整详情'!A80"/>
+    <hyperlink ref="F39" ns1:id="R6360db00742b45ec"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A81"/>
+    <hyperlink ref="F47" ns1:id="Rc4146f6376594d01"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A156"/>
+    <hyperlink ref="F48" ns1:id="R97ba6e4965084c76"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A155"/>
+    <hyperlink ref="F49" ns1:id="Rcbdc080795344925"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A83"/>
+    <hyperlink ref="F50" ns1:id="R9e6afd1b359743bb"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A154"/>
+    <hyperlink ref="F51" ns1:id="Rb320e0a5ad524836"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A86"/>
+    <hyperlink ref="F52" ns1:id="R42a660aaeb1d4c95"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A87"/>
+    <hyperlink ref="F53" ns1:id="R88784a2520864683"/>
+    <hyperlink ref="C29" location="'02项目完整详情'!A88"/>
+    <hyperlink ref="F29" ns1:id="Rcb8b33dae69a4731"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A89"/>
+    <hyperlink ref="F54" ns1:id="Rd5ea9c8442ca46ac"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A90"/>
+    <hyperlink ref="F55" ns1:id="R7734727212364cb2"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A91"/>
+    <hyperlink ref="F56" ns1:id="R78b8c8c0ca954ecb"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A92"/>
+    <hyperlink ref="F57" ns1:id="Rfdf5f46608d44776"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A93"/>
+    <hyperlink ref="F58" ns1:id="R82f06426c3d54976"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A94"/>
+    <hyperlink ref="F59" ns1:id="R3cae8e186c48414b"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A95"/>
+    <hyperlink ref="F60" ns1:id="Ra7f1aef2362a4a4a"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A96"/>
+    <hyperlink ref="F61" ns1:id="R8befa90ef3fc47c2"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A97"/>
+    <hyperlink ref="F62" ns1:id="Re7fdcbfdd1084572"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A98"/>
+    <hyperlink ref="F63" ns1:id="R65ca925ee60b42a7"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A100"/>
+    <hyperlink ref="F64" ns1:id="Reb76655df7374bc5"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A166"/>
+    <hyperlink ref="F65" ns1:id="R055caeb6a90642b5"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A102"/>
+    <hyperlink ref="F66" ns1:id="Rfff5ca38a0554ba3"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A103"/>
+    <hyperlink ref="F67" ns1:id="R0888add655cd4fba"/>
+    <hyperlink ref="C33" location="'02项目完整详情'!A104"/>
+    <hyperlink ref="F33" ns1:id="Rd9709f11bc9f4e83"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A163"/>
+    <hyperlink ref="F68" ns1:id="R20412a2edb1c448a"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A105"/>
+    <hyperlink ref="F69" ns1:id="R61772b79401a4268"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A106"/>
+    <hyperlink ref="F70" ns1:id="R987b8e6f52a74110"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A107"/>
+    <hyperlink ref="F71" ns1:id="R0c4396d550f2475f"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A162"/>
+    <hyperlink ref="F72" ns1:id="R4f11bd52ab71481c"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A108"/>
+    <hyperlink ref="F73" ns1:id="R4db82e37256244c2"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A109"/>
+    <hyperlink ref="F74" ns1:id="R4031c47a301e406d"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A110"/>
+    <hyperlink ref="F75" ns1:id="Raa160d321af04db8"/>
+    <hyperlink ref="C30" location="'02项目完整详情'!A111"/>
+    <hyperlink ref="F30" ns1:id="R769c1e9ff31b4410"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A112"/>
+    <hyperlink ref="F76" ns1:id="R4cdea66d1ef84e88"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A114"/>
+    <hyperlink ref="F77" ns1:id="Rfe9d4bacb83a4b3a"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A115"/>
+    <hyperlink ref="F78" ns1:id="Rdb52bb1fc14c4902"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A116"/>
+    <hyperlink ref="F79" ns1:id="Raea0cb8061aa4114"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A153"/>
+    <hyperlink ref="F80" ns1:id="Re209c4141aad4cc2"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A152"/>
+    <hyperlink ref="F81" ns1:id="R929ae2605c414e9f"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A165"/>
+    <hyperlink ref="F82" ns1:id="R1abe4cdaf9e34bae"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A117"/>
+    <hyperlink ref="F83" ns1:id="R0a10fce99c274f93"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A118"/>
+    <hyperlink ref="F84" ns1:id="R938383f864354c81"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A119"/>
+    <hyperlink ref="F85" ns1:id="Rf5654ce2b68c4be9"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A121"/>
+    <hyperlink ref="F86" ns1:id="Rcb7b406cd4eb4fbf"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A123"/>
+    <hyperlink ref="F87" ns1:id="R5815a7bd80814259"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A124"/>
+    <hyperlink ref="F88" ns1:id="R0c410df45d8a4e3d"/>
+    <hyperlink ref="C31" location="'02项目完整详情'!A125"/>
+    <hyperlink ref="F31" ns1:id="R431b21fd445f4abe"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A126"/>
+    <hyperlink ref="F89" ns1:id="R567091a279bf498d"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A164"/>
+    <hyperlink ref="F90" ns1:id="Re392bfd9b5274c72"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A128"/>
+    <hyperlink ref="F91" ns1:id="Re6cada6d8cc14329"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A129"/>
+    <hyperlink ref="F92" ns1:id="R8fc1cda8f3b6430e"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A130"/>
+    <hyperlink ref="F93" ns1:id="R27a55a96c3f24c5f"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A131"/>
+    <hyperlink ref="F94" ns1:id="R5e47895d5a614c2b"/>
+    <hyperlink ref="C32" location="'02项目完整详情'!A132"/>
+    <hyperlink ref="F32" ns1:id="R3b43825c6bac4d00"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A133"/>
+    <hyperlink ref="F95" ns1:id="R93e0d1bfa9de4923"/>
+    <hyperlink ref="C96" location="'02项目完整详情'!A40"/>
+    <hyperlink ref="F96" ns1:id="R8485fac45d264a2f"/>
+    <hyperlink ref="C97" location="'02项目完整详情'!A41"/>
+    <hyperlink ref="F97" ns1:id="R1c0f567749234b9c"/>
+    <hyperlink ref="C98" location="'02项目完整详情'!A42"/>
+    <hyperlink ref="F98" ns1:id="Rbf215fc93e064e7e"/>
+    <hyperlink ref="C99" location="'02项目完整详情'!A43"/>
+    <hyperlink ref="F99" ns1:id="R53db146b46f44f15"/>
+    <hyperlink ref="C100" location="'02项目完整详情'!A44"/>
+    <hyperlink ref="F100" ns1:id="R188b27dcb5574282"/>
+    <hyperlink ref="F108" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C108" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="C101" location="'02项目完整详情'!A167" display="项目完整详情"/>
+    <hyperlink ref="F101" ns1:id="rIdSystematic98"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A168" display="项目完整详情"/>
+    <hyperlink ref="F102" ns1:id="rIdSystematic99"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A175" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdSystematic100"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A176" display="项目完整详情"/>
+    <hyperlink ref="F104" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
-    <hyperlink ref="C104" location="'02项目完整详情'!A182" display="项目完整详情"/>
-    <hyperlink ref="F104" ns1:id="rIdResume103"/>
-    <hyperlink ref="C105" location="'02项目完整详情'!A184" display="项目完整详情"/>
-    <hyperlink ref="F105" ns1:id="rIdResume104"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F105" ns1:id="rIdResume103"/>
+    <hyperlink ref="C106" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F106" ns1:id="rIdResume104"/>
     <hyperlink ref="C14" location="'02项目完整详情'!A185" display="项目完整详情"/>
     <hyperlink ref="F14" ns1:id="rIdResume105"/>
-    <hyperlink ref="C106" location="'02项目完整详情'!A186" display="项目完整详情"/>
-    <hyperlink ref="F106" ns1:id="rIdResume106"/>
+    <hyperlink ref="C107" location="'02项目完整详情'!A186" display="项目完整详情"/>
+    <hyperlink ref="F107" ns1:id="rIdResume106"/>
     <hyperlink ref="C12" location="'02项目完整详情'!A191" display="项目完整详情"/>
     <hyperlink ref="F12" ns1:id="rIdResume107"/>
+    <hyperlink ref="C22" location="'02项目完整详情'!A198" display="项目完整详情"/>
+    <hyperlink ref="F22" ns1:id="rIdResume108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -44071,6 +44857,58 @@
       </c>
       <c r="H69" t="str" s="3">
         <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
+      </c>
+    </row>
+    <row r="70" ht="66" customHeight="1">
+      <c r="A70" t="str" s="20">
+        <v>历史批次·公告附件待核</v>
+      </c>
+      <c r="B70" t="n" s="13">
+        <v>46296</v>
+      </c>
+      <c r="C70" t="str" s="14">
+        <v>山东科技大学·山东省智慧矿山信息技术重点实验室</v>
+      </c>
+      <c r="D70" t="str" s="15">
+        <v>官方摘要明确煤矿全场景视觉感知、恶劣条件多模态增强感知与鲁棒分析、复杂矿山环境感知与设备自适应控制、智能巡检设备、矿山具身智能装备。其他地质/矿山大模型方向不代替机器人具体任务。</v>
+      </c>
+      <c r="E70" t="str" s="15">
+        <v>资助金额及项数尚未取得</v>
+      </c>
+      <c r="F70" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G70" t="str" s="3">
+        <v>正文首次500，保存完整2026公告和附件；补金额、资格、合作、经费外拨、周期、成果/IP、联系方式及时点。截止已过，非当前申报项目；2027年度未取得。</v>
+      </c>
+      <c r="H70" t="str" s="3">
+        <v>指定邮箱、收件地址及联系人未取得</v>
+      </c>
+    </row>
+    <row r="71" ht="66" customHeight="1">
+      <c r="A71" t="str" s="20">
+        <v>历史线索·官方公告待核</v>
+      </c>
+      <c r="B71" t="n" s="13">
+        <v>46087</v>
+      </c>
+      <c r="C71" t="str" s="14">
+        <v>潍坊学院（机构与年度公告尚待官方核验）·山东省先进动力装备智能制造技术重点实验室</v>
+      </c>
+      <c r="D71" t="str" s="15">
+        <v>转载方向含多维制造信息融合感知与控制、非结构动态环境下人机协同制造、制造系统集成与智能运维、数字孪生建模、智能测试标定等。浙江工业教师主页另记2026多机械臂协同感知控制获本实验室基金，证明机制线索，不能代替完整年度正式任务及条款。</v>
+      </c>
+      <c r="E71" t="str" s="15">
+        <v>转载每项2—3万元，未取得官方确认</v>
+      </c>
+      <c r="F71" t="str" s="16">
+        <v>线索来源（非官方）</v>
+      </c>
+      <c r="G71" t="str" s="3">
+        <v>第三方不是正式凭据；候选官方URL无法读取且真实性未确认，需人工从学校机械学院官网定位2026指南及附件、管理办法。转载电话区号0356与潍坊所在地不同，原样保留待核不自行改为0536；日期/金额不得当作已核。</v>
+      </c>
+      <c r="H71" t="str" s="3">
+        <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
       </c>
     </row>
   </sheetData>
@@ -44211,6 +45049,10 @@
     <hyperlink ref="F68" ns1:id="rIdResume70"/>
     <hyperlink ref="C69" location="'02项目完整详情'!A195" display="项目完整详情"/>
     <hyperlink ref="F69" ns1:id="rIdResume71"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A196" display="项目完整详情"/>
+    <hyperlink ref="F70" ns1:id="rIdResume72"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A197" display="项目完整详情"/>
+    <hyperlink ref="F71" ns1:id="rIdResume73"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -1548,16 +1548,17 @@
       </c>
       <c r="W7" s="3" t="str"/>
       <c r="X7" s="3" t="str">
-        <v>完整经费条款见M列，成果要求见O列，知识产权见P列。
-待核：经费使用及外拨、知识产权</v>
+        <v>完整经费条款见M列，成果O列，IP在P列；经费外拨和IP仍待核。同一2027批次补充官方通知：https://rvl.swjtu.edu.cn/info/1071/20938.htm；不另立项目。</v>
       </c>
       <c r="Y7" s="3" t="str">
         <v>P2 四川·成都</v>
       </c>
       <c r="Z7" s="3" t="str">
-        <v>qybgky@swjtu.edu.cn</v>
-      </c>
-      <c r="AA7" s="3" t="str"/>
+        <v>姜老师028-87600869；qybgky@swjtu.edu.cn；成都市二环路北一段111号实验室，610031</v>
+      </c>
+      <c r="AA7" s="3" t="str">
+        <v>同一2027申报批次官方公告：20938（原已核20948保留），非新增项目。</v>
+      </c>
     </row>
     <row r="8" ht="160.5" customHeight="1">
       <c r="A8" s="3" t="str">
@@ -10424,16 +10425,16 @@
       </c>
       <c r="H108" s="3" t="str"/>
       <c r="I108" s="3" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>无人系统多源传感融合/环境适配、轻量化目标识别跟踪、无卫星定位地图构建、机载边缘感知、高精运动控制轨迹规划、多导航融合、异构无人集群分布式协同、空地任务调度、数字孪生协同仿真、容错控制及无人系统协同安全。</v>
       </c>
       <c r="J108" s="3" t="str">
         <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="K108" s="3" t="str">
-        <v>官方明确｜1.高等院校、科研院所、机关企事业单位具有中级以上专业技术职称或具有正科职级或具有硕士学位的科研人员（不具有以上条件的应提供两名同领域的高级职称专家的推荐意见），均可在开放课题指南范围内向实验室提出申请；</v>
+        <v>高校、科研院所、机关企事业单位中级以上或正科职级或硕士学位；否则2名同领域高级职称推荐。每人申报主持1项，未结题开放课题负责人不能参与当年申请；校内主持≤1、参与≤2。</v>
       </c>
       <c r="L108" s="3" t="str">
-        <v>公开资料未载明｜已取得公开资料未载明合作及访问的完整条款。</v>
+        <v>必须指定1名四川文理学院固定人员联系人；论文专利须含1名实验室固定人员；产学研联合鼓励，驻室/访问天数未载。</v>
       </c>
       <c r="M108" s="3" t="str">
         <v>官方明确｜本实验室采取后资助模式，开放基金资助经费在课题结项后一次性划拨，其中校内人员作为课题负责人的经费，由发布平台将汇总表报科技处审核后，交计划财务处直接划拨至课题负责人相应账号；
@@ -10441,21 +10442,10 @@
 开放课题经费的开支及标准，按我校校级科研项目经费管理相关办法或校外负责人所在单位相关办法执行。</v>
       </c>
       <c r="N108" s="3" t="str">
-        <v>官方明确｜1.重点课题：资助额度2万—3万元/项，资助期限为2年，被资助的每个课题研发技术或样机需在工程实际中进行技术应用或推广，工程应用效果良好并获技术应用企业提供的工程应用证明，还须满足下列条件之二：①研发工程样机或应用系统一台/套（提供研制报告和实物）；
-2.一般课题：资助额度1万—2万元/项，资助期限为2年，被资助的每个课题研发技术或样机需在工程实际中进行技术应用或推广，工程应用效果良好并获技术应用企业提供的工程应用证明，还须满足下列条件之一：①研发工程样机或应用系统一台/套（提供研制报告和实物）；
-3.自筹课题：无经费资助，实验室提供平台、设备、数据支持，资助期限为2年，结题须满足下列条件之一：①完成技术验证、场景测试并提交总结报告；
-1.项目的研究周期一般为两年，执行时间以下达时为准。
-为规范项目管理，申报书中项目起止时间应填写为2026年01月01日至2027年12月31日。</v>
+        <v>一般2年，执行以下达为准；申报书统一填写2026-01-01至2027-12-31。</v>
       </c>
       <c r="O108" s="3" t="str">
-        <v>官方明确｜③发表EI/SCI检索论文1篇或其他核心期刊论文2篇（授权专利可折合核心期刊）；
-③发表核心期刊论文1篇（授权专利可折合核心期刊）或普通期刊论文2篇；
-3.自筹课题：无经费资助，实验室提供平台、设备、数据支持，资助期限为2年，结题须满足下列条件之一：①完成技术验证、场景测试并提交总结报告；
-②发表期刊论文1篇或申请知识产权1项；
-2.由本实验室资助的开放基金课题，其研究成果归本实验室与申请人单位共有，转让收益按协议共享。
-所发表论文、专利本实验室或四川文理学院必须作为第一或第二单位，同时包含1名本实验室固定研究人员。
-研究成果必须注明“智能无人系统技术四川省高等学校重点实验室资助项目（编号：xxx）”（英文：Supported by Open Fund(No.xxx) of Sichuan Provincial University Key Laboratory of Intelligent Unmanned System Technology），标注成果作为验收的重要参考依据。
-本人承诺在项目实施（包括项目评估、检查、项目执行、资源汇交、验收等过程）中，遵守科学道德和诚信要求，严格执行项目任务书的规定，按计划进度完成预期研究目标，及时与相关其它部门进行协调，保证项目的顺利完成。</v>
+        <v>重点和一般均须工程实际应用推广、效果良好及企业工程应用证明；重点另满足5类中的2项，一般另满足1项：样机/系统1台套、省部级及行业学会奖、论文（重点SCI/EI1或核心2；一般核心1或普刊2，授权专利可折核心）、省部级首台套、同水平其他成果。自筹无现金，验证测试报告/期刊1或IP1/同水平三者选1。论文专利实验室或学校第一/第二单位并含1名固定人员、标资助课题号；结题总结、应用及各类成果证明。不把论文单项替代工程应用要求。</v>
       </c>
       <c r="P108" s="3" t="str">
         <v>官方明确｜2.由本实验室资助的开放基金课题，其研究成果归本实验室与申请人单位共有，转让收益按协议共享。</v>
@@ -10472,7 +10462,7 @@
         <v>已知背景：南京信息工程大学现职、博士。个人条件、在研限项及实际合作人尚未逐项确认；须按公告条款核对，受理窗口状态不代表可申请。</v>
       </c>
       <c r="S108" s="3" t="str">
-        <v>合作及访问：已取得公开资料未载明合作及访问的完整条款。</v>
+        <v>固定人员联系人及署名已由现有2026正文核实；驻室天数未载，是否另有合同访问要求待主办方确认。2026-07-18首页索引与旧档拟立项标题不同，需核其公告性质/是否新轮，不能当新申报批次。</v>
       </c>
       <c r="T108" s="3" t="str">
         <v>https://jqr.sasu.edu.cn/info/1009/1062.htm</v>
@@ -10495,7 +10485,7 @@
         <v>P2 四川·达州</v>
       </c>
       <c r="Z108" s="3" t="str">
-        <v>3282644598@qq.com</v>
+        <v>熊浩18111791715；3282644598@qq.com；达州市达川区南坝路四川文理学院南坝校区二教楼604，635000</v>
       </c>
       <c r="AA108" s="3" t="str"/>
     </row>
@@ -10529,10 +10519,10 @@
         <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="K109" s="3" t="str">
-        <v>官方明确｜1.高等院校、科研院所、机关企事业单位具有中级以上专业技术职称（包括中级以上警务技术职称）或具有正科职级或具有硕士学位的科研人员（不具有以上条件的应提供两名同领域的高级职称专家的推荐意见），均可在开放课题指南范围内向实验室提出申请；</v>
+        <v>高校、科研院所、机关企事业单位中级以上（含警务技术）或正科或硕士；否则2名同领域高级职称推荐。每人申报主持1项，未结题开放课题负责人不能参与当年申请；校内主持≤1、参与≤2。</v>
       </c>
       <c r="L109" s="3" t="str">
-        <v>公开资料未载明｜已取得公开资料未载明合作及访问的完整条款。</v>
+        <v>必须指定1名四川文理学院固定人员联系人；论文专利须含1名实验室固定人员；鼓励与公安实战单位/产学研联合；驻室天数未载。</v>
       </c>
       <c r="M109" s="3" t="str">
         <v>官方明确｜本实验室采取后资助模式，开放基金资助经费在课题结项后一次性划拨，其中校内人员作为课题负责人的经费，由发布平台将汇总表报科技处审核后，交计划财务处直接划拨至课题负责人相应账号；
@@ -10540,21 +10530,10 @@
 开放课题经费的开支及标准，按我校校级科研项目经费管理相关办法或校外负责人所在单位相关办法执行。</v>
       </c>
       <c r="N109" s="3" t="str">
-        <v>官方明确｜1.重点课题：资助额度1万—2万元/项，资助期限为2年，被资助的每个课题研发技术或样机需在工程实际中进行技术应用或推广，工程应用效果良好并获技术应用企业提供的工程应用证明，还须满足下列条件之二：①研发工程样机或应用系统一台/套（提供研制报告和实物）；
-2.一般课题：资助额度0.5万—1万元/项，资助期限为2年，被资助的每个课题研发技术或样机需在工程实际中进行技术应用或推广，工程应用效果良好并获技术应用企业提供的工程应用证明，还须满足下列条件之一：①研发工程样机或应用系统一台/套（提供研制报告和实物）；
-3.自筹课题：无经费资助，实验室提供平台、设备、数据支持，资助期限为2年，结题须满足下列条件之一：①完成技术验证、场景测试并提交总结报告；
-1.项目的研究周期一般为两年，执行时间以下达时为准。
-为规范项目管理，申报书中项目起止时间应填写为2026年01月01日至2027年12月31日。</v>
+        <v>一般2年，执行以下达为准；申报书统一填写2026-01-01至2027-12-31。</v>
       </c>
       <c r="O109" s="3" t="str">
-        <v>官方明确｜③发表EI/SCI检索论文1篇或其他核心期刊论文2篇（授权专利可折合核心期刊）；
-③发表核心期刊论文1篇（授权专利可折合核心期刊）或普通期刊论文2篇；
-3.自筹课题：无经费资助，实验室提供平台、设备、数据支持，资助期限为2年，结题须满足下列条件之一：①完成技术验证、场景测试并提交总结报告；
-②发表期刊论文1篇或申请知识产权1项；
-2026年，本实验室开放基金紧扣公安巡逻防控、应急处突、侦查办案、安全防护等实战需求，聚焦警用智能机器人“卡脖子”技术与应用痛点，在以下方向或与警用智能机器人技术相关的其他方向自由选题，要注重技术实用性、可转化性，推动研究成果服务公安实战、形成知识产权与示范应用。
-2.由本实验室资助的开放基金课题，其研究成果归本实验室与申请人单位共有，转让收益按协议共享。
-所发表论文、专利等成果本实验室或四川文理学院必须作为第一或第二单位，同时包含1名本实验室固定研究人员。
-研究成果必须注明“警用智能机器人达州市重点实验室资助项目（编号：xxx）”（英文：Supported by Open Fund(No.xxx) of Dazhou Key Laboratory of Police Intelligent Robotics），标注成果作为验收的重要参考依据。</v>
+        <v>重点和一般均须工程实际应用推广、效果良好及企业工程应用证明；重点另满足5类中的2项，一般另满足1项：样机/系统1台套、省部级及行业学会奖、论文（重点SCI/EI1或核心2；一般核心1或普刊2，授权专利可折核心）、省部级首台套、同水平其他成果。自筹无现金，验证测试报告/期刊1或IP1/同水平三者选1。论文专利实验室或学校第一/第二单位并含1名固定人员、标资助课题号；结题总结、应用及各类成果证明。不把论文单项替代工程应用要求。</v>
       </c>
       <c r="P109" s="3" t="str">
         <v>官方明确｜2.由本实验室资助的开放基金课题，其研究成果归本实验室与申请人单位共有，转让收益按协议共享。</v>
@@ -10570,7 +10549,7 @@
         <v>已知背景：南京信息工程大学现职、博士。个人条件、在研限项及实际合作人尚未逐项确认；须按公告条款核对，受理窗口状态不代表可申请。</v>
       </c>
       <c r="S109" s="3" t="str">
-        <v>合作及访问：已取得公开资料未载明合作及访问的完整条款。</v>
+        <v>固定人员联系人、论文署名和工程应用证明已从现有年度原文补齐；驻室天数未载，需按主办方合同确认。</v>
       </c>
       <c r="T109" s="3" t="str">
         <v>https://jqr.sasu.edu.cn/info/1009/1061.htm</v>
@@ -10593,7 +10572,7 @@
         <v>P2 四川·达州</v>
       </c>
       <c r="Z109" s="3" t="str">
-        <v>3282644598@qq.com</v>
+        <v>熊浩18111791715；3282644598@qq.com；达州市达川区南坝路四川文理学院南坝校区二教楼604，635000</v>
       </c>
       <c r="AA109" s="3" t="str"/>
     </row>
@@ -17977,6 +17956,87 @@
         <v>刘金花；jmdz_gz@gdut.edu.cn；020-39325372、15013234272；广州市番禺区大学城外环西路100号工学二号馆301室510006</v>
       </c>
       <c r="AA198" t="str" s="3"/>
+    </row>
+    <row r="199" ht="79.5" customHeight="1">
+      <c r="A199" t="str" s="3">
+        <v>N050</v>
+      </c>
+      <c r="B199" t="str" s="3">
+        <v>官方2024首批正文前段已读，续读末段首次超时</v>
+      </c>
+      <c r="C199" t="str" s="3">
+        <v>中国石油大学（华东）</v>
+      </c>
+      <c r="D199" t="str" s="3">
+        <v>自然资源部海上丝路海洋资源环境组网观测技术创新中心</v>
+      </c>
+      <c r="E199" t="str" s="3">
+        <v>历史批次·公告末段附件待核</v>
+      </c>
+      <c r="F199" t="str" s="3">
+        <v>2024（首批）</v>
+      </c>
+      <c r="G199" t="str" s="6">
+        <v>2024申报截止原文未取得；研究期已结束</v>
+      </c>
+      <c r="H199" t="str" s="3">
+        <v>具体截止时点未取得</v>
+      </c>
+      <c r="I199" t="str" s="3">
+        <v>1.2运动船载雷达目标检测与测向；1.4海雾/AIS碰撞风险建模及航行路径规划；2.1复杂地形动态气象下无人机集群组网观测；2.3声传播折射下水下航行器非线性卡尔曼定位；2.4水上/水下一体化导航。其他土壤/温盐反演和地质任务不凭关键词扩展。</v>
+      </c>
+      <c r="J199" t="str" s="3">
+        <v>正文已见部分未给金额，需管理办法确认；不是确认零资助</v>
+      </c>
+      <c r="K199" t="str" s="3">
+        <v>国内外相关研发人员，原则年龄≤40；中级或博士或中心直接聘任客座/访问学者；申请人不得为中心固定人员；同年1项、前项未结题不申请。</v>
+      </c>
+      <c r="L199" t="str" s="3">
+        <v>必须与依托单位正式工作人员合作，对方协同研究并负责经费报销；是否驻室及天数未载。</v>
+      </c>
+      <c r="M199" t="str" s="3">
+        <v>依托中央高校基本科研业务费自主创新科研计划平台专项，由校内人员负责报销；外拨是否允许、科目比例待管理办法，不根据报销描述推定外拨禁止。</v>
+      </c>
+      <c r="N199" t="str" s="3">
+        <v>2年，2024-01-01—2025-12-31；非当前受理。</v>
+      </c>
+      <c r="O199" t="str" s="3">
+        <v>每项至少1个仪器装备样机或数据集，加1篇SCI/EI期刊论文；须同时标中央高校基本科研业务费及专项号、创新中心开放课题资助，未标成果不认可；第一单位及指定作者要求待办法。</v>
+      </c>
+      <c r="P199" t="str" s="3">
+        <v>知识产权条款未取得。</v>
+      </c>
+      <c r="Q199" t="str" s="3">
+        <v>填附件2申请书提交中心、形式审查及专家评审；公告末段未取得，准确截止、份数、签章、收件邮箱地址尚未核。</v>
+      </c>
+      <c r="R199" t="str" s="3">
+        <v>本人博士满足学历选项；年龄、中心固定身份/限项及合作人需按本人实际确认，尚未落实固定合作者。</v>
+      </c>
+      <c r="S199" t="str" s="3">
+        <v>首次正文前段可读，续读末段超时即停止；人工保存完整2024公告及附件1管理办法、附件2申请书，补截止、金额、提交、经费外拨/IP。2025第二批和2026第三批实为海洋流场/遥感环境任务，按各年任务独立剔除，不覆盖2024相关结论。</v>
+      </c>
+      <c r="T199" t="str" s="3">
+        <v>https://imeie.upc.edu.cn/2024/0612/c10897a460865/page.htm</v>
+      </c>
+      <c r="U199" t="str" s="3">
+        <v>正文称附件1开放基金管理办法（试行）、附件2申请书；末段具体下载链接未取得</v>
+      </c>
+      <c r="V199" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W199" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X199" t="str" s="3">
+        <v>2024明确自主装备实际任务，历史批次末段及附件待核；不同年度按具体任务筛选。</v>
+      </c>
+      <c r="Y199" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="Z199" t="str" s="3">
+        <v>研究方向联系人：1.2纪永刚jiyonggang@upc.edu.cn、崔学荣cxr@upc.edu.cn；1.4刘善伟20110052@upc.edu.cn；2.1罗偲luo_cai@upc.edu.cn；2.3余相20240018@upc.edu.cn；2.4贺凯飞kfhe@upc.edu.cn。受理联系人及提交地址待末段，不能套2026联系信息。</v>
+      </c>
+      <c r="AA199" t="str" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18396,6 +18456,7 @@
     <hyperlink ref="T196" ns1:id="rIdResume418"/>
     <hyperlink ref="T197" ns1:id="rIdResume419"/>
     <hyperlink ref="T198" ns1:id="rIdResume420"/>
+    <hyperlink ref="T199" ns1:id="rIdResume421"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -40428,6 +40489,723 @@
       </c>
       <c r="I714" t="str" s="3">
         <v>resume_sources_20261009.json 末组正文/查询</v>
+      </c>
+    </row>
+    <row r="715" ht="52.5" customHeight="1">
+      <c r="A715" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B715" t="str" s="3">
+        <v>苏州大学机器人相关平台目录及年度机制</v>
+      </c>
+      <c r="C715" t="str" s="3">
+        <v>江苏·苏州</v>
+      </c>
+      <c r="D715" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E715" t="str" s="3">
+        <v>查询：site:suda.edu.cn 科研平台 机器人 重点实验室 / site:suda.edu.cn "开放基金" 2026 2027 机器人 / site:suda.edu.cn "开放课题" 人机交互 控制 / site:suda.edu.cn "机器人" "重点实验室" "基金"；定位：关于江苏省具身智能机器人技术重点实验室2026年开放课题申报工作的通知；江苏省高校通用人工智能与大模型重点实验室开放课题申报指南；科研平台；国家级平台；江苏省重大脑疾病创新药物研发及转化重点实验室2025年开放课题申请指南</v>
+      </c>
+      <c r="F715" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G715" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H715" t="str" s="3">
+        <v>https://jdxy.suda.edu.cn/_t1815/be/36/c12042a704054/page.psp
+https://future.suda.edu.cn/e8/2a/c30836a714794/page.htm
+https://cicrm.suda.edu.cn/9032/list.htm
+https://scit.suda.edu.cn/32734/list.htm
+https://jskeylab.suda.edu.cn/5a/06/c14681a678406/page.htm</v>
+      </c>
+      <c r="I715" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第299项</v>
+      </c>
+    </row>
+    <row r="716" ht="52.5" customHeight="1">
+      <c r="A716" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B716" t="str" s="3">
+        <v>扬州大学机器人相关平台目录及年度机制</v>
+      </c>
+      <c r="C716" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D716" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E716" t="str" s="3">
+        <v>查询：site:yzu.edu.cn "科研平台" 机器人 控制 / site:yzu.edu.cn "开放课题" 2026 2027 机器人 / site:yzu.edu.cn "开放基金" 2026 2027 智能 / site:yzu.edu.cn "智能装备" "重点实验室" 开放；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F716" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G716" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H716" t="str" s="3"/>
+      <c r="I716" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第300项</v>
+      </c>
+    </row>
+    <row r="717" ht="52.5" customHeight="1">
+      <c r="A717" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B717" t="str" s="3">
+        <v>江苏科技大学自主装备平台目录及年度机制</v>
+      </c>
+      <c r="C717" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D717" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E717" t="str" s="3">
+        <v>查询：site:just.edu.cn "科研平台" 机器人 / site:just.edu.cn "开放基金" 2026 2027 智能 / site:just.edu.cn "开放课题" 2026 2027 无人 / site:just.edu.cn "水下机器人" "开放" 基金；定位：农业农村部蚕桑遗传改良重点实验室与蚕桑与畜禽生物技术省高校重点实验室（江苏科技大学）2026年度学术委员会会议召开；江苏科技大学科研平台建设与管理办法（修订）；科研平台</v>
+      </c>
+      <c r="F717" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G717" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H717" t="str" s="3">
+        <v>https://swjs.just.edu.cn/2026/0715/c4706a375502/page.htm
+https://kjc.just.edu.cn/_upload/article/files/cc/84/18d197874b67be296c0f200f367a/80309204-debb-4143-8850-ac8f46eb94a5.pdf
+https://swjs.just.edu.cn/4685/listm.htm</v>
+      </c>
+      <c r="I717" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第301项</v>
+      </c>
+    </row>
+    <row r="718" ht="52.5" customHeight="1">
+      <c r="A718" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B718" t="str" s="3">
+        <v>南京邮电大学感知人机平台目录及年度机制</v>
+      </c>
+      <c r="C718" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D718" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E718" t="str" s="3">
+        <v>查询：site:njupt.edu.cn "科研平台" 机器人 / site:njupt.edu.cn "开放基金" 2026 2027 智能 / site:njupt.edu.cn "开放课题" 2026 2027 控制 / site:njupt.edu.cn "智能传感" "开放基金"；定位：江苏省物联网智能机器人工程实验室学术委员会成立暨第一次学术委员会会议召开；科研平台；科技基础条件平台；四、科研平台和条件支撑；江苏省集成电路先进封测工程研究中心</v>
+      </c>
+      <c r="F718" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G718" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H718" t="str" s="3">
+        <v>https://iotrobot.njupt.edu.cn/2018/0306/c9947a122565/page.htm
+https://coa.njupt.edu.cn/kypt/list.htm
+https://www.njupt.edu.cn/_t44/44/listm.psp
+https://rsc.njupt.edu.cn/_upload/article/files/67/10/5ba9911848ba960851c8951c58de/d8a75e30-9e61-4952-a18b-e4e06ab0f1f1.pdf
+https://ntyjy.njupt.edu.cn/_upload/article/files/ea/83/0922224a4dbe88b0d6a04e2d3a16/5c65a220-ce4a-4050-be3f-c14349e416e6.pdf</v>
+      </c>
+      <c r="I718" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第302项</v>
+      </c>
+    </row>
+    <row r="719" ht="52.5" customHeight="1">
+      <c r="A719" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B719" t="str" s="3">
+        <v>江苏科技大学自动化船舶机器人平台补漏</v>
+      </c>
+      <c r="C719" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D719" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E719" t="str" s="3">
+        <v>查询：site:zidonghua.just.edu.cn 科研平台 实验室 水下机器人 / site:just.edu.cn "江苏省" "机器人" "实验室" 开放 / site:just.edu.cn "船舶" "开放基金" 2026 2027；定位：学科实验室；实验室管理处；物流工程与管理实验室；练在平时 防患未然 —— 自动化学院开展实验室安全应急实战演练；船海学院调研组赴沪调研船舶智能制造实验室建设；管理单位科研设施与仪器开放服务信息公示表</v>
+      </c>
+      <c r="F719" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G719" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H719" t="str" s="3">
+        <v>https://zidonghua.just.edu.cn/5965/list.htm
+https://lmd.just.edu.cn/
+https://sem.just.edu.cn/2025/0512/c11908a362171/page.htm
+https://zidonghua.just.edu.cn/2025/1205/c5947a369716/page.htm
+https://www.just.edu.cn/2025/0314/c11144a359241/page.htm
+https://lmd.just.edu.cn/_upload/article/files/d3/b1/0e0c929147aba891fe990a621647/ad1722fd-177e-4563-bbbd-125f16530e70.pdf</v>
+      </c>
+      <c r="I719" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第303项</v>
+      </c>
+    </row>
+    <row r="720" ht="52.5" customHeight="1">
+      <c r="A720" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B720" t="str" s="3">
+        <v>扬州大学机械科研平台逐名发现</v>
+      </c>
+      <c r="C720" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D720" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E720" t="str" s="3">
+        <v>查询：site:me.yzu.edu.cn 科研平台 实验室 / site:me.yzu.edu.cn "开放" 基金 课题 / site:yzu.edu.cn "智能制造" "重点实验室" 科研 平台；定位：校级虚拟仿真实验管理平台</v>
+      </c>
+      <c r="F720" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G720" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H720" t="str" s="3">
+        <v>https://xnfzgxpt.yzu.edu.cn/project/list</v>
+      </c>
+      <c r="I720" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第304项</v>
+      </c>
+    </row>
+    <row r="721" ht="52.5" customHeight="1">
+      <c r="A721" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B721" t="str" s="3">
+        <v>南京邮电物联网智能机器人开放机制</v>
+      </c>
+      <c r="C721" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D721" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E721" t="str" s="3">
+        <v>查询：site:iotrobot.njupt.edu.cn 开放基金 / site:iotrobot.njupt.edu.cn 开放课题 / "物联网智能机器人工程实验室" "开放基金" 2026 2027；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F721" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G721" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H721" t="str" s="3"/>
+      <c r="I721" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第305项</v>
+      </c>
+    </row>
+    <row r="722" ht="52.5" customHeight="1">
+      <c r="A722" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B722" t="str" s="3">
+        <v>南京邮电具身智能高校实验室年度</v>
+      </c>
+      <c r="C722" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D722" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E722" t="str" s="3">
+        <v>查询：site:njupt.edu.cn "具身智能与装备控制" "开放" / site:njupt.edu.cn "物联网智能感知与计算" "开放基金" 2026 2027 / site:njupt.edu.cn "物联网智能感知与计算" "开放课题"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F722" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G722" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H722" t="str" s="3"/>
+      <c r="I722" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第306项</v>
+      </c>
+    </row>
+    <row r="723" ht="52.5" customHeight="1">
+      <c r="A723" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B723" t="str" s="3">
+        <v>扬州大学机械院正确官网与平台</v>
+      </c>
+      <c r="C723" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D723" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E723" t="str" s="3">
+        <v>查询：扬州大学 机械工程学院 科研平台 官网 / site:yzu.edu.cn "机械工程学院" "重点实验室" / site:yzu.edu.cn "机械工程学院" "开放课题"；定位：科研平台-机械工程学院；&lt;tr&gt;&lt;th colspan="3"&gt;国家级科研平台&lt;</v>
+      </c>
+      <c r="F723" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G723" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H723" t="str" s="3">
+        <v>https://mec.ysu.edu.cn/yqgl/jgsz/kypt.htm
+https://yz.usst.edu.cn/_upload/article/files/3f/c3/eef5d17549c78dd7aac6bb0831f2/2a83a1bb-c47b-4c87-be36-88d83fa73b0c.pdf</v>
+      </c>
+      <c r="I723" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第307项</v>
+      </c>
+    </row>
+    <row r="724" ht="52.5" customHeight="1">
+      <c r="A724" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B724" t="str" s="3">
+        <v>江苏科技船舶与海工自动化逐平台开放机制</v>
+      </c>
+      <c r="C724" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D724" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E724" t="str" s="3">
+        <v>查询："江苏省船舶与海工装备自动化" "开放基金" / "船舶综合控制与保障" "开放课题" / site:just.edu.cn "水下机器人实验室" "开放课题" 2026 2027；定位：怀柔实验室2026年校园招聘 - 吉林大学就业网</v>
+      </c>
+      <c r="F724" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G724" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H724" t="str" s="3">
+        <v>https://jdjyw.jlu.edu.cn/mportal/recruit/details?id=76e52e4086a64d4caba974693f0554f1</v>
+      </c>
+      <c r="I724" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第308项</v>
+      </c>
+    </row>
+    <row r="725" ht="52.5" customHeight="1">
+      <c r="A725" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B725" t="str" s="3">
+        <v>扬州大学机械官方域名平台机制</v>
+      </c>
+      <c r="C725" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D725" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E725" t="str" s="3">
+        <v>查询：site:jxgcxy.yzu.edu.cn "科研机构" / site:jxgcxy.yzu.edu.cn "重点实验室" / site:jxgcxy.yzu.edu.cn "开放基金" 2026 2027 / site:jxgcxy.yzu.edu.cn "开放课题"；定位：本次未定位新增正式入口</v>
+      </c>
+      <c r="F725" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G725" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H725" t="str" s="3"/>
+      <c r="I725" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第309项</v>
+      </c>
+    </row>
+    <row r="726" ht="52.5" customHeight="1">
+      <c r="A726" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B726" t="str" s="3">
+        <v>全国省高校重点实验室2026—2027机器人交叉补漏</v>
+      </c>
+      <c r="C726" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D726" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E726" t="str" s="3">
+        <v>查询："高校重点实验室" "开放基金" "机器人" 2026 / "省重点实验室" "开放课题" "机器人" 2027 / "开放基金" "具身智能" 2027 / "开放课题" "人机协同" 2027；定位：智能无人系统技术四川省高等学校重点实验室2026年度开放基金申报公告-智能无人系统技术四川省高等学校重点实验室；江苏省具身智能工业机器人及其人机协作高校重点实验室开放课题管理办法-电气与自动化工程学院；关于申报轨道交通运载系统全国重点实验室2027年度开放课题的通知-西南交通大学轨道交通运载系统全国重点实验室；江苏省工业人工智能重点实验室2026年度开放课题申请通知-- 中国科学院工业人工智能研究所；智能无人系统技术四川省高等学校重点实验室；人工智能实验室招标信息-人工智能实验室招标采购-采招网</v>
+      </c>
+      <c r="F726" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G726" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H726" t="str" s="3">
+        <v>https://znwrxt.sasu.edu.cn/info/1009/1062.htm
+https://dqxylib.szut.edu.cn/info/1016/27682.htm
+https://rvl.swjtu.edu.cn/info/1071/20938.htm
+https://iaii.cas.cn/hzjl/kjhz/202607/t20260715_8248969.html
+https://znwrxt.sasu.edu.cn/
+https://www.bidcenter.com.cn/zhaobiao/zbkeyw-75010.html</v>
+      </c>
+      <c r="I726" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第310项</v>
+      </c>
+    </row>
+    <row r="727" ht="52.5" customHeight="1">
+      <c r="A727" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B727" t="str" s="3">
+        <v>中央高校校外负责人机器人课题交叉补漏</v>
+      </c>
+      <c r="C727" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D727" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E727" t="str" s="3">
+        <v>查询："基本科研业务费" "校外" "开放" "机器人" 2026 2027 / "重点科研平台开放基金" 2026 "校外" / "基本科研业务费" "开放课题" "自主" 2026 / "中央高校" "开放基金" "规划" 2027；定位：关于申请“先进核技术与辐射防护”工信部重点实验室；国家重点实验室专项经费管理办法-北京航空航天大学计划财务部；杂交水稻全国重点实验室；关于中央高校基本科研业务费重点科研平台水；自然资源部海上丝路海洋资源环境组网观测技术创新中心开放基金课题申请指南；申请！一批次重点实验室课题基金申请指南_搜狐网</v>
+      </c>
+      <c r="F727" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G727" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H727" t="str" s="3">
+        <v>https://iint.nuaa.edu.cn/_upload/article/files/3c/c6/adf3d30e4636b707f714a4499f3d/d601b93c-364c-4d66-b937-1ae640bf1048.pdf
+https://jhcwb.buaa.edu.cn/info/1084/1913.htm
+https://sklhr.whu.edu.cn/portal/article/about_article/id/1156.html
+https://jtxny.chd.edu.cn/_upload/article/files/92/b2/8288fd8245f887a6f450e6bd7015/7a8f38fd-f1a6-49ff-8a90-5c812b8a6004.pdf
+https://imeie.upc.edu.cn/2024/0612/c10897a460865/page.htm
+https://m.sohu.com/a/1018268396_120343587</v>
+      </c>
+      <c r="I727" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第311项</v>
+      </c>
+    </row>
+    <row r="728" ht="52.5" customHeight="1">
+      <c r="A728" t="str" s="3">
+        <v>2026-10-09接续平台查漏</v>
+      </c>
+      <c r="B728" t="str" s="3">
+        <v>海上丝路组网观测平台2026—2027任务筛选</v>
+      </c>
+      <c r="C728" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D728" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E728" t="str" s="3">
+        <v>查询：site:upc.edu.cn "海上丝路" "开放基金" 2026 2027 / site:imeie.upc.edu.cn "组网观测" "开放" 机器人 自主；定位：自然资源部海上丝路海洋资源环境组网观测技术创新中心开放基金课题(第三批)申请指南；自然资源部海上丝路海洋资源环境组网观测技术创新中心开放基金课题(第二批)申请指南；自然资源部海上丝路海洋资源环境组网观测技术创新中心开放基金课题申请指南</v>
+      </c>
+      <c r="F728" t="str" s="3">
+        <v>搜索结果含跨机构内容，须对账；未命中不代表无开放基金；平台目录及年度须继续逐项确认。</v>
+      </c>
+      <c r="G728" t="str" s="3">
+        <v>仅本查询完成，不代表机构查全。</v>
+      </c>
+      <c r="H728" t="str" s="3">
+        <v>https://ocean.upc.edu.cn/2026/0424/c15098a488720/page.htm
+https://ocean.upc.edu.cn/2025/0922/c18017a471570/page.htm
+https://imeie.upc.edu.cn/2024/0612/c10897a460865/page.htm</v>
+      </c>
+      <c r="I728" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第312项</v>
+      </c>
+    </row>
+    <row r="729" ht="52.5" customHeight="1">
+      <c r="A729" t="str" s="3">
+        <v>2026-10-09年度正文核验</v>
+      </c>
+      <c r="B729" t="str" s="3">
+        <v>中国石油大学（华东）</v>
+      </c>
+      <c r="C729" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D729" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E729" t="str" s="3">
+        <v>自然资源部海上丝路海洋资源环境组网观测技术创新中心；2024（首批）；N050；官方2024首批正文前段已读，续读末段首次超时</v>
+      </c>
+      <c r="F729" t="str" s="3">
+        <v>首次正文前段可读，续读末段超时即停止；人工保存完整2024公告及附件1管理办法、附件2申请书，补截止、金额、提交、经费外拨/IP。2025第二批和2026第三批实为海洋流场/遥感环境任务，按各年任务独立剔除，不覆盖2024相关结论。</v>
+      </c>
+      <c r="G729" t="str" s="3">
+        <v>仅本年度公告已核正文；附件/年度条款待核，不计机构完整覆盖。</v>
+      </c>
+      <c r="H729" t="str" s="3">
+        <v>https://imeie.upc.edu.cn/2024/0612/c10897a460865/page.htm</v>
+      </c>
+      <c r="I729" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="730" ht="52.5" customHeight="1">
+      <c r="A730" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B730" t="str" s="3">
+        <v>南京邮电大学</v>
+      </c>
+      <c r="C730" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D730" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E730" t="str" s="3">
+        <v>官方自动化目录搜索缓存明确3个平台：具身智能与装备控制省高校重点实验室、物联网智能机器人工程研究中心、主动配电网零碳运行中心；计算机目录含物联网智能感知计算/大数据平台，逐名历史及2026—2027基金检索。</v>
+      </c>
+      <c r="F730" t="str" s="3">
+        <v>自动化目录首次403，需人工全文；机器人两平台未获正式资助通知，计算机大数据2017复用M181；未用学院科研成果当基金。</v>
+      </c>
+      <c r="G730" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H730" t="str" s="3">
+        <v>https://coa.njupt.edu.cn/kypt/list.htm
+https://cs.njupt.edu.cn/18753/list.htm</v>
+      </c>
+      <c r="I730" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="731" ht="52.5" customHeight="1">
+      <c r="A731" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B731" t="str" s="3">
+        <v>江苏科技大学自动化学院</v>
+      </c>
+      <c r="C731" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D731" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E731" t="str" s="3">
+        <v>已读完整学科实验室目录：罗克韦尔、船舶综合电站、船舶综合控制保障（自主航行）、省船舶海工自动化、省船海电气自动化（机器人/无人船）、水下机器人（控制/导航/路径跟踪）；逐名基金及2026—2027查询。</v>
+      </c>
+      <c r="F731" t="str" s="3">
+        <v>目录兼教学实验，不作已设对外资助机制；尚未定位这些实验室正式基金；其他学院/研究平台仍未齐。</v>
+      </c>
+      <c r="G731" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H731" t="str" s="3">
+        <v>https://zidonghua.just.edu.cn/5965/list.htm</v>
+      </c>
+      <c r="I731" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="732" ht="52.5" customHeight="1">
+      <c r="A732" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B732" t="str" s="3">
+        <v>江苏科技大学计算机学院</v>
+      </c>
+      <c r="C732" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D732" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E732" t="str" s="3">
+        <v>官方简介完整读：5团队、1省级工程中心/5产学研基地/2培养基地、船舶海工信息资源共享工程实验室、船舶工业软件学院。</v>
+      </c>
+      <c r="F732" t="str" s="3">
+        <v>简介未列全部平台具体名称及开放机制；开放实验室栏目是教学线索，未作开放资助。</v>
+      </c>
+      <c r="G732" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H732" t="str" s="3">
+        <v>https://jisuanji.just.edu.cn/xyjj/list.htm</v>
+      </c>
+      <c r="I732" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="733" ht="52.5" customHeight="1">
+      <c r="A733" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B733" t="str" s="3">
+        <v>扬州大学</v>
+      </c>
+      <c r="C733" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D733" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E733" t="str" s="3">
+        <v>机械学院正确域名jxgcxy.yzu.edu.cn由2026官方调剂PDF确认；改正先前me.yzu.edu.cn空查询，正确域名逐名检索。</v>
+      </c>
+      <c r="F733" t="str" s="3">
+        <v>正确机械学院首页首次412，交人工目录；me.yzu.edu.cn空结果不作没有基金证据。搜索出现燕山/长江/东南机械学院不当扬州平台。</v>
+      </c>
+      <c r="G733" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H733" t="str" s="3">
+        <v>https://jxgcxy.yzu.edu.cn/</v>
+      </c>
+      <c r="I733" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="734" ht="52.5" customHeight="1">
+      <c r="A734" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B734" t="str" s="3">
+        <v>苏州大学</v>
+      </c>
+      <c r="C734" t="str" s="3">
+        <v>江苏·苏州</v>
+      </c>
+      <c r="D734" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E734" t="str" s="3">
+        <v>机器人相关2026M076、通用AI2026M077对账复用；本次科研平台搜索结果cicrm目录全文核实实际为放射医学协同创新中心，含其他依托单位。</v>
+      </c>
+      <c r="F734" t="str" s="3">
+        <v>放射医学目录非机器人目录，也非全校名单，不将中国辐射防护研究院等平台归属苏大；其他机械/机器人目录仍待完整核验。</v>
+      </c>
+      <c r="G734" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H734" t="str" s="3">
+        <v>https://cicrm.suda.edu.cn/9032/list.htm</v>
+      </c>
+      <c r="I734" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="735" ht="52.5" customHeight="1">
+      <c r="A735" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B735" t="str" s="3">
+        <v>中国石油大学（华东）</v>
+      </c>
+      <c r="C735" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D735" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E735" t="str" s="3">
+        <v>海上丝路2026第三批年度完整正文2任务：内孤立波声传播影响、水质光学遥感反演，E080排除；2027未获正式指南。</v>
+      </c>
+      <c r="F735" t="str" s="3">
+        <v>限定当年任务无机器人，不由平台水下组网简介反推本轮相关；年度金额未必要深入，因为已快速排除。</v>
+      </c>
+      <c r="G735" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H735" t="str" s="3">
+        <v>https://ocean.upc.edu.cn/2026/0424/c15098a488720/page.htm</v>
+      </c>
+      <c r="I735" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="736" ht="52.5" customHeight="1">
+      <c r="A736" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B736" t="str" s="3">
+        <v>中国石油大学（华东）</v>
+      </c>
+      <c r="C736" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D736" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E736" t="str" s="3">
+        <v>海上丝路2025第二批全文5任务：油气数据挖掘、溢油风险、水色水深遥感、中尺度涡反演重构、海洋流场反演，E081排除。</v>
+      </c>
+      <c r="F736" t="str" s="3">
+        <v>实际海洋环境/资源建模，不用三维重构、AI、定位章节名称假定机器人任务；2024首批另核N050，不以本轮排除整个平台。</v>
+      </c>
+      <c r="G736" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H736" t="str" s="3">
+        <v>https://ocean.upc.edu.cn/2025/0922/c18017a471570/page.htm</v>
+      </c>
+      <c r="I736" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="737" ht="52.5" customHeight="1">
+      <c r="A737" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B737" t="str" s="3">
+        <v>四川文理学院</v>
+      </c>
+      <c r="C737" t="str" s="3">
+        <v>四川·达州</v>
+      </c>
+      <c r="D737" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E737" t="str" s="3">
+        <v>M059/M060官方原文及附件源复用，从同一归档补齐固定联系人、工程应用证明和成果分类，前期已取得条款不因本次网页失败退回待核。</v>
+      </c>
+      <c r="F737" t="str" s="3">
+        <v>新域名首页首次超时；2026-07-18索引与原档拟立项题不同，需人工确认公告性质，未当新增项目；其余平台仍未完整。</v>
+      </c>
+      <c r="G737" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H737" t="str" s="3">
+        <v>https://znwrxt.sasu.edu.cn/</v>
+      </c>
+      <c r="I737" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
+      </c>
+    </row>
+    <row r="738" ht="52.5" customHeight="1">
+      <c r="A738" t="str" s="3">
+        <v>2026-10-09周边与年度补漏</v>
+      </c>
+      <c r="B738" t="str" s="3">
+        <v>西南交通大学</v>
+      </c>
+      <c r="C738" t="str" s="3">
+        <v>四川·成都</v>
+      </c>
+      <c r="D738" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E738" t="str" s="3">
+        <v>官方2027轮次搜索缓存20938正文与原M105（20948）逐项对应：8—10万、2026-10-26、校外负责人+联络人、2年、论文2/第一单位/到室1次。</v>
+      </c>
+      <c r="F738" t="str" s="3">
+        <v>同批公告异URL非新增项目，补联系人与别名来源；经费外拨/IP仍未载，不能按日期表示本人可申请。</v>
+      </c>
+      <c r="G738" t="str" s="3">
+        <v>仅所列目录/年度已查，不是机构全覆盖。</v>
+      </c>
+      <c r="H738" t="str" s="3">
+        <v>https://rvl.swjtu.edu.cn/info/1071/20938.htm</v>
+      </c>
+      <c r="I738" t="str" s="3">
+        <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
       </c>
     </row>
   </sheetData>
@@ -44911,6 +45689,32 @@
         <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
       </c>
     </row>
+    <row r="72" ht="66" customHeight="1">
+      <c r="A72" t="str" s="20">
+        <v>历史批次·公告末段附件待核</v>
+      </c>
+      <c r="B72" t="str" s="13">
+        <v>2024申报截止原文未取得；研究期已结束</v>
+      </c>
+      <c r="C72" t="str" s="14">
+        <v>中国石油大学（华东）·自然资源部海上丝路海洋资源环境组网观测技术创新中心</v>
+      </c>
+      <c r="D72" t="str" s="15">
+        <v>1.2运动船载雷达目标检测与测向；1.4海雾/AIS碰撞风险建模及航行路径规划；2.1复杂地形动态气象下无人机集群组网观测；2.3声传播折射下水下航行器非线性卡尔曼定位；2.4水上/水下一体化导航。其他土壤/温盐反演和地质任务不凭关键词扩展。</v>
+      </c>
+      <c r="E72" t="str" s="15">
+        <v>正文已见部分未给金额，需管理办法确认；不是确认零资助</v>
+      </c>
+      <c r="F72" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G72" t="str" s="3">
+        <v>首次正文前段可读，续读末段超时即停止；人工保存完整2024公告及附件1管理办法、附件2申请书，补截止、金额、提交、经费外拨/IP。2025第二批和2026第三批实为海洋流场/遥感环境任务，按各年任务独立剔除，不覆盖2024相关结论。</v>
+      </c>
+      <c r="H72" t="str" s="3">
+        <v>研究方向联系人：1.2纪永刚jiyonggang@upc.edu.cn、崔学荣cxr@upc.edu.cn；1.4刘善伟20110052@upc.edu.cn；2.1罗偲luo_cai@upc.edu.cn；2.3余相20240018@upc.edu.cn；2.4贺凯飞kfhe@upc.edu.cn。受理联系人及提交地址待末段，不能套2026联系信息。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" location="'02项目完整详情'!A14"/>
@@ -45053,6 +45857,8 @@
     <hyperlink ref="F70" ns1:id="rIdResume72"/>
     <hyperlink ref="C71" location="'02项目完整详情'!A197" display="项目完整详情"/>
     <hyperlink ref="F71" ns1:id="rIdResume73"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A199" display="项目完整详情"/>
+    <hyperlink ref="F72" ns1:id="rIdResume74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AA150" s="3" t="str"/>
     </row>
-    <row r="151" ht="106.5" customHeight="1">
+    <row r="151" ht="117" customHeight="1">
       <c r="A151" s="3" t="str">
         <v>N001</v>
       </c>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="AA151" s="3" t="str"/>
     </row>
-    <row r="152" ht="66" customHeight="1">
+    <row r="152" ht="72" customHeight="1">
       <c r="A152" s="3" t="str">
         <v>N002</v>
       </c>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AA152" s="3" t="str"/>
     </row>
-    <row r="153" ht="66" customHeight="1">
+    <row r="153" ht="72" customHeight="1">
       <c r="A153" s="3" t="str">
         <v>N003</v>
       </c>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AA155" s="3" t="str"/>
     </row>
-    <row r="156" ht="66" customHeight="1">
+    <row r="156" ht="72" customHeight="1">
       <c r="A156" s="3" t="str">
         <v>N006</v>
       </c>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AA156" s="3" t="str"/>
     </row>
-    <row r="157" ht="48" customHeight="1">
+    <row r="157" ht="57" customHeight="1">
       <c r="A157" s="3" t="str">
         <v>N007</v>
       </c>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AA158" s="3" t="str"/>
     </row>
-    <row r="159" ht="48" customHeight="1">
+    <row r="159" ht="57" customHeight="1">
       <c r="A159" s="3" t="str">
         <v>N009</v>
       </c>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="AA159" s="3" t="str"/>
     </row>
-    <row r="160" ht="52.5" customHeight="1">
+    <row r="160" ht="57" customHeight="1">
       <c r="A160" s="3" t="str">
         <v>N010</v>
       </c>
@@ -14886,7 +14886,7 @@
       <c r="Z160" s="3" t="str"/>
       <c r="AA160" s="3" t="str"/>
     </row>
-    <row r="161" ht="52.5" customHeight="1">
+    <row r="161" ht="87" customHeight="1">
       <c r="A161" s="3" t="str">
         <v>N011</v>
       </c>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="AA161" s="3" t="str"/>
     </row>
-    <row r="162" ht="66" customHeight="1">
+    <row r="162" ht="102" customHeight="1">
       <c r="A162" s="3" t="str">
         <v>N012</v>
       </c>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="AA163" s="3" t="str"/>
     </row>
-    <row r="164" ht="79.5" customHeight="1">
+    <row r="164" ht="102" customHeight="1">
       <c r="A164" s="3" t="str">
         <v>N014</v>
       </c>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="AA164" s="3" t="str"/>
     </row>
-    <row r="165" ht="79.5" customHeight="1">
+    <row r="165" ht="117" customHeight="1">
       <c r="A165" s="3" t="str">
         <v>N015</v>
       </c>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="AA165" s="3" t="str"/>
     </row>
-    <row r="166" ht="79.5" customHeight="1">
+    <row r="166" ht="102" customHeight="1">
       <c r="A166" s="3" t="str">
         <v>N016</v>
       </c>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="AA169" t="str" s="3"/>
     </row>
-    <row r="170" ht="79.5" customHeight="1">
+    <row r="170" ht="132" customHeight="1">
       <c r="A170" t="str" s="3">
         <v>N020</v>
       </c>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AA175" t="str" s="3"/>
     </row>
-    <row r="176" ht="79.5" customHeight="1">
+    <row r="176" ht="102" customHeight="1">
       <c r="A176" t="str" s="3">
         <v>N026</v>
       </c>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="AA184" t="str" s="3"/>
     </row>
-    <row r="185" ht="79.5" customHeight="1">
+    <row r="185" ht="102" customHeight="1">
       <c r="A185" t="str" s="3">
         <v>N036</v>
       </c>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="AA185" t="str" s="3"/>
     </row>
-    <row r="186" ht="79.5" customHeight="1">
+    <row r="186" ht="162" customHeight="1">
       <c r="A186" t="str" s="3">
         <v>N037</v>
       </c>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="AA186" t="str" s="3"/>
     </row>
-    <row r="187" ht="79.5" customHeight="1">
+    <row r="187" ht="87" customHeight="1">
       <c r="A187" t="str" s="3">
         <v>N038</v>
       </c>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="AA188" t="str" s="3"/>
     </row>
-    <row r="189" ht="79.5" customHeight="1">
+    <row r="189" ht="162" customHeight="1">
       <c r="A189" t="str" s="3">
         <v>N040</v>
       </c>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="AA189" t="str" s="3"/>
     </row>
-    <row r="190" ht="79.5" customHeight="1">
+    <row r="190" ht="87" customHeight="1">
       <c r="A190" t="str" s="3">
         <v>N041</v>
       </c>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="AA192" t="str" s="3"/>
     </row>
-    <row r="193" ht="79.5" customHeight="1">
+    <row r="193" ht="87" customHeight="1">
       <c r="A193" t="str" s="3">
         <v>N044</v>
       </c>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="AA194" t="str" s="3"/>
     </row>
-    <row r="195" ht="79.5" customHeight="1">
+    <row r="195" ht="102" customHeight="1">
       <c r="A195" t="str" s="3">
         <v>N046</v>
       </c>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="AA195" t="str" s="3"/>
     </row>
-    <row r="196" ht="79.5" customHeight="1">
+    <row r="196" ht="87" customHeight="1">
       <c r="A196" t="str" s="3">
         <v>N047</v>
       </c>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="AA196" t="str" s="3"/>
     </row>
-    <row r="197" ht="79.5" customHeight="1">
+    <row r="197" ht="117" customHeight="1">
       <c r="A197" t="str" s="3">
         <v>N048</v>
       </c>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="AA197" t="str" s="3"/>
     </row>
-    <row r="198" ht="79.5" customHeight="1">
+    <row r="198" ht="102" customHeight="1">
       <c r="A198" t="str" s="3">
         <v>N049</v>
       </c>
@@ -17957,7 +17957,7 @@
       </c>
       <c r="AA198" t="str" s="3"/>
     </row>
-    <row r="199" ht="79.5" customHeight="1">
+    <row r="199" ht="132" customHeight="1">
       <c r="A199" t="str" s="3">
         <v>N050</v>
       </c>
@@ -41655,7 +41655,7 @@
         <v>公告</v>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1">
+    <row r="22" ht="117" customHeight="1">
       <c r="A22" t="str" s="18">
         <v>已截止</v>
       </c>
@@ -42823,7 +42823,7 @@
         <v>公告</v>
       </c>
     </row>
-    <row r="80" ht="66" customHeight="1">
+    <row r="80" ht="72" customHeight="1">
       <c r="A80" s="18" t="str">
         <v>已截止</v>
       </c>
@@ -43367,7 +43367,7 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="107" ht="96" customHeight="1">
+    <row r="107" ht="102" customHeight="1">
       <c r="A107" t="str" s="18">
         <v>已截止</v>
       </c>
@@ -44310,7 +44310,7 @@
         <v>184092@hainanu.edu.cn；BME@hainanu.edu.cn</v>
       </c>
     </row>
-    <row r="24" ht="52.5" customHeight="1">
+    <row r="24" ht="57" customHeight="1">
       <c r="A24" s="20" t="str">
         <v>方向待核·已截止</v>
       </c>
@@ -45040,7 +45040,7 @@
         <v>江老师；jfjiang6@iflytek.com</v>
       </c>
     </row>
-    <row r="47" ht="52.5" customHeight="1">
+    <row r="47" ht="57" customHeight="1">
       <c r="A47" s="20" t="str">
         <v>线索待核</v>
       </c>
@@ -45090,7 +45090,7 @@
       </c>
       <c r="H48" s="3" t="str"/>
     </row>
-    <row r="49" ht="48" customHeight="1">
+    <row r="49" ht="57" customHeight="1">
       <c r="A49" s="20" t="str">
         <v>线索待核</v>
       </c>
@@ -45429,7 +45429,7 @@
         <v>李老师；18853318883；ligen@cdu.edu.cn</v>
       </c>
     </row>
-    <row r="62" ht="66" customHeight="1">
+    <row r="62" ht="87" customHeight="1">
       <c r="A62" t="str" s="20">
         <v>历史批次·截止条款待核</v>
       </c>
@@ -45455,7 +45455,7 @@
         <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
       </c>
     </row>
-    <row r="63" ht="66" customHeight="1">
+    <row r="63" ht="72" customHeight="1">
       <c r="A63" t="str" s="20">
         <v>历史批次·截止年份冲突待核</v>
       </c>
@@ -45481,7 +45481,7 @@
         <v>刘老师13576931367；20423232@qq.com</v>
       </c>
     </row>
-    <row r="64" ht="66" customHeight="1">
+    <row r="64" ht="117" customHeight="1">
       <c r="A64" t="str" s="20">
         <v>任务证据待核·窗口未截止</v>
       </c>
@@ -45507,7 +45507,7 @@
         <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
       </c>
     </row>
-    <row r="65" ht="66" customHeight="1">
+    <row r="65" ht="87" customHeight="1">
       <c r="A65" t="str" s="20">
         <v>历史批次·具体任务待核</v>
       </c>
@@ -45533,7 +45533,7 @@
         <v>王老师13895189949；cae@nxu.edu.cn；2019收件：贺兰山西路539号宁大C区机械工程学院750021</v>
       </c>
     </row>
-    <row r="66" ht="66" customHeight="1">
+    <row r="66" ht="87" customHeight="1">
       <c r="A66" t="str" s="20">
         <v>历史批次·公告全文待核</v>
       </c>
@@ -45559,7 +45559,7 @@
         <v>联系人邮箱未取得</v>
       </c>
     </row>
-    <row r="67" ht="66" customHeight="1">
+    <row r="67" ht="102" customHeight="1">
       <c r="A67" t="str" s="20">
         <v>历史批次·年度任务全文待核</v>
       </c>
@@ -45585,7 +45585,7 @@
         <v>联系人邮箱未取得</v>
       </c>
     </row>
-    <row r="68" ht="66" customHeight="1">
+    <row r="68" ht="72" customHeight="1">
       <c r="A68" t="str" s="20">
         <v>公告及具体任务待核</v>
       </c>
@@ -45611,7 +45611,7 @@
         <v>申报联系人及邮箱未取得</v>
       </c>
     </row>
-    <row r="69" ht="66" customHeight="1">
+    <row r="69" ht="117" customHeight="1">
       <c r="A69" t="str" s="20">
         <v>年度具体任务待核</v>
       </c>
@@ -45637,7 +45637,7 @@
         <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
       </c>
     </row>
-    <row r="70" ht="66" customHeight="1">
+    <row r="70" ht="102" customHeight="1">
       <c r="A70" t="str" s="20">
         <v>历史批次·公告附件待核</v>
       </c>
@@ -45663,7 +45663,7 @@
         <v>指定邮箱、收件地址及联系人未取得</v>
       </c>
     </row>
-    <row r="71" ht="66" customHeight="1">
+    <row r="71" ht="132" customHeight="1">
       <c r="A71" t="str" s="20">
         <v>历史线索·官方公告待核</v>
       </c>
@@ -45689,7 +45689,7 @@
         <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
       </c>
     </row>
-    <row r="72" ht="66" customHeight="1">
+    <row r="72" ht="132" customHeight="1">
       <c r="A72" t="str" s="20">
         <v>历史批次·公告末段附件待核</v>
       </c>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -41208,6 +41208,646 @@
         <v>resume_sources_20261009.json；M059/M060既有sources归档</v>
       </c>
     </row>
+    <row r="739" ht="52.5" customHeight="1">
+      <c r="A739" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B739" t="str" s="3">
+        <v>澳门大学珠海研究院及澳门实验室开放机制补漏</v>
+      </c>
+      <c r="C739" t="str" s="3">
+        <v>澳门·珠海</v>
+      </c>
+      <c r="D739" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E739" t="str" s="3">
+        <v>查询："澳门大学珠海研究院" "开放课题" 2026 2027 / "澳门大学" "开放基金" "机器人" / "澳门" "重点实验室" "开放课题" 2026 / "澳门" "开放研究" "基金" 机器人；线索：Microsoft Word - SKL开放课题管理办法.doc；Microsoft Word - 中药质量研究国家重点实验室开放课题申请表.doc；东南大学新一代人工智能技术与交叉应用教育部重点实验室；省部共建复杂有色金属资源清洁利用国家重点实验室2025年度开放基金申请指南-澳门娱乐城；澳大智慧城市物联网全国重点实验室举行学术委员会会议　加速推进智慧城市技术的科创发展 – 澳门特别行政区政府入口网站；中国-葡萄牙文化遗产保护科学"一带一路"联合实验室</v>
+      </c>
+      <c r="F739" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G739" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H739" t="str" s="3">
+        <v>https://www.must.edu.mo/images/SKL/files/SKL%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98%E7%AE%A1%E7%90%86%E5%8A%9E%E6%B3%95.pdf
+https://www.must.edu.mo/images/SKL/files/%E4%B8%AD%E8%8D%AF%E8%B4%A8%E9%87%8F%E7%A0%94%E7%A9%B6%E5%9B%BD%E5%AE%B6%E9%87%8D%E7%82%B9%E5%AE%9E%E9%AA%8C%E5%AE%A4%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98%E7%94%B3%E8%AF%B7%E8%A1%A8.pdf
+https://aiia.seu.edu.cn/
+https://www.macauylc.com/info/1060/4724.htm
+https://www.gov.mo/zh-hans/news/%E6%BE%B3%E5%A4%A7%E6%99%BA%E6%85%A7%E5%9F%8E%E5%B8%82%E7%89%A9%E8%81%94%E7%BD%91%E5%85%A8%E5%9B%BD%E9%87%8D%E7%82%B9%E5%AE%9E%E9%AA%8C%E5%AE%A4%E4%B8%BE%E8%A1%8C%E5%AD%A6%E6%9C%AF%E5%A7%94%E5%91%98/
+https://sinolab-femmfqe7.manus.space/</v>
+      </c>
+      <c r="I739" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第313项</v>
+      </c>
+    </row>
+    <row r="740" ht="52.5" customHeight="1">
+      <c r="A740" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B740" t="str" s="3">
+        <v>香港理工内地研究院对外开放课题</v>
+      </c>
+      <c r="C740" t="str" s="3">
+        <v>香港·珠三角</v>
+      </c>
+      <c r="D740" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E740" t="str" s="3">
+        <v>查询："香港理工大学深圳研究院" "开放课题" / "香港理工大学" "开放基金" "机器人" 2026 2027 / "香港理工大学" "开放课题" 广州 江门 / "香港" "联合实验室" "开放基金" 2026 2027 机器人；线索：先进环境装备与污染防治技术全国重点实验室2025年度开放课题立项通知----先进环境装备与污染防治技术全国重点实验室；2026年度开放基金公示-现代制造质量工程湖北省重点实验室；关于组织申报人工智能与数字经济广东省实验室（深圳） 2026年度第二批开放课题的通知-天津大学香港理工大学深圳未来技术学院；地震动力学国家重点实验室·２０１０年度报告；华南理工大学亚热带建筑科学国家重点实验室；实验室2024年度开放基金申请通知-深圳大学地理空间信息研究团队</v>
+      </c>
+      <c r="F740" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G740" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H740" t="str" s="3">
+        <v>https://sklaet.gig.ac.cn/kydt/qt/202509/t20250910_768300.html
+https://mmqe.hbut.edu.cn/info/1047/2282.htm
+https://sz.tju.edu.cn/info/1711/5661.htm
+https://www.eqlab.ac.cn/upload/b66458e7-221f-4767-b42e-d9c645a398cd/2010.pdf
+https://www2.scut.edu.cn/_upload/article/files/20/94/1575e0de41c7871586ec9e43d70a/5976d8a1-a8f4-4d0d-97e6-f6819a86d687.pdf
+https://geospatial.szu.edu.cn/info/1052/6662.htm</v>
+      </c>
+      <c r="I740" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第314项</v>
+      </c>
+    </row>
+    <row r="741" ht="52.5" customHeight="1">
+      <c r="A741" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B741" t="str" s="3">
+        <v>香港其他高校及广州研究平台开放课题</v>
+      </c>
+      <c r="C741" t="str" s="3">
+        <v>香港·广州</v>
+      </c>
+      <c r="D741" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E741" t="str" s="3">
+        <v>查询："香港科技大学" "开放课题" 2026 2027 / "香港中文大学" "开放基金" 2026 2027 机器人 / "香港城市大学" "开放课题" 2026 2027 / "香港大学" "开放基金" 2026 2027 机器人；线索：&lt;span class="rich_media_title " id="activity-name"&gt;智能算法安全全国重点实验室2025年度开放课题立项公告&lt;/span&gt;--智能算法安全全国重点实验室；〖公告〗2025-2026年度工业控制技术全国重点实验室开放课题立项结果公告；广东省未来智联网络重点实验室2024年度开放课题申请指南 | 未来智联网络研究院；肖华 广东海洋大学副教授，硕导，湛江市 B 类高层次 | --- | --- 肖华 人才 Email: oliviaxh@gdou.edu.cn | 肖华 研究方向: | 肖华 纳米光电材料、半导体发光器、可见光通信、光电 | 肖华 器件失效分析研究、光谱优化算法 | 肖华 硕士招生专业： | 肖华 095136 农业工程与信息技术（专业学位型硕士） | 肖华 教育经历: | 肖华 2015-09 至 2020-02， 香港城市大学，机电工程系，博士 | 肖华 2011-09 至 2014-06， 厦门大学，电子科学系，硕士 | 肖华 2007-09 至 2011-06， 湖南师范大学，物理与电子科学学院，学士 | 肖华 工作经历： |2014/07-2015/07 湖南师范大学，物理与信息科学学院，行政管理；2003年开放课题评审意见；神经信息教育部重点实验室</v>
+      </c>
+      <c r="F741" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G741" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H741" t="str" s="3">
+        <v>https://klais.ict.ac.cn/tzgg/xmzj/202511/t20251120_798577.html
+https://sklict.zju.edu.cn/2025/0624/c85587a3064115/page.htm
+https://fnii.cuhk.edu.cn/node/154
+https://dxxy.gdou.edu.cn/__local/E/B0/EB/E99A1050C31A7B824C52FB96AC1_F3A19351_2E6F4.pdf
+https://pcoss.xmu.edu.cn/2019-5.pdf
+https://neuro.uestc.edu.cn/neuro/html/Lab%20paper/Lab2014.pdf</v>
+      </c>
+      <c r="I741" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第315项</v>
+      </c>
+    </row>
+    <row r="742" ht="52.5" customHeight="1">
+      <c r="A742" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B742" t="str" s="3">
+        <v>深圳先进技术研究院机器人平台开放基金机制</v>
+      </c>
+      <c r="C742" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="D742" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E742" t="str" s="3">
+        <v>查询：site:siat.ac.cn "科研平台" 机器人 重点实验室 / site:siat.ac.cn "开放基金" 2026 2027 / site:siat.ac.cn "开放课题" 2026 2027 / site:siat.ac.cn "人机" "开放基金"；线索：中国科学院香港中文大学深圳先进集成技术研究所2025年优秀大学生夏令营招生简章；市级科研平台；省级科研平台；中国科学院深圳先进技术研究院科学仪器研究所（筹）周寿军团队招聘公告；媒体报道----劳特伯生物医学成像研究中心；中国科学院深圳先进技术研究院</v>
+      </c>
+      <c r="F742" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G742" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H742" t="str" s="3">
+        <v>https://cxqjzx.siat.ac.cn/siat/iait/rczp/2025053017375065876/index.html
+https://szs.siat.ac.cn/siat/iacde/yjsgk/tj_pt/sjkypt28/index.html
+https://szs.siat.ac.cn/siat/iacde/yjsgk/tj_pt/sjkypt/index.html
+https://insci.siat.ac.cn/siat/2026-04/13/article_2026041318224725302.html
+https://lauterbur.siat.ac.cn/xwdt/mtbd/info/2023/587.html
+https://www.siat.ac.cn/?from=websitedict.com</v>
+      </c>
+      <c r="I742" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第316项</v>
+      </c>
+    </row>
+    <row r="743" ht="52.5" customHeight="1">
+      <c r="A743" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B743" t="str" s="3">
+        <v>香港大学及城大港科大开放实验室资金英文补漏</v>
+      </c>
+      <c r="C743" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D743" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E743" t="str" s="3">
+        <v>查询：site:hku.hk robotics "open fund" 2026 / site:cityu.edu.hk robotics "open research" "fund" / site:hkust.edu.hk robotics laboratory "open call" 2026 2027；线索：RESEARCH ARTICLE</v>
+      </c>
+      <c r="F743" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G743" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H743" t="str" s="3">
+        <v>https://www.cityu.edu.hk/phy/appkchu/Publications/2024/24.57.pdf</v>
+      </c>
+      <c r="I743" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第317项</v>
+      </c>
+    </row>
+    <row r="744" ht="52.5" customHeight="1">
+      <c r="A744" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B744" t="str" s="3">
+        <v>澳门及香港理工科研中心外部申请英文机制</v>
+      </c>
+      <c r="C744" t="str" s="3">
+        <v>澳门·香港</v>
+      </c>
+      <c r="D744" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E744" t="str" s="3">
+        <v>查询：site:um.edu.mo robotics laboratory "open fund" / site:um.edu.mo "open research" "2026" / site:polyu.edu.hk robotics "open fund" 2026 2027 / site:polyu.edu.hk "open call" "external researchers" laboratory；线索：Out-of-order execution enabled deep reinforcement learning for dynamic additive manufacturing scheduling | PolyU Institutional Research Archive；Open Research Project of Centre for Innovation and Entrepreneurship Now Open for Application (Deadline: 26/03/2026) – UM E-bulletin board；Open Research Project - State Key Laboratory of Internet of Things for Smart City | University of Macau；Hydrogel-engineered interface suppressing water activity by hydrogen bonds and regulated solvation for stable Zn metal anodes | PolyU Institutional Research Archive</v>
+      </c>
+      <c r="F744" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G744" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H744" t="str" s="3">
+        <v>https://ira.lib.polyu.edu.hk/handle/10397/115393?mode=full
+https://e-bulletin.um.edu.mo/notice/500662/
+https://skliotsc.um.edu.mo/_collaboration/open-research-project/
+https://ira.lib.polyu.edu.hk/handle/10397/121319?mode=full</v>
+      </c>
+      <c r="I744" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第318项</v>
+      </c>
+    </row>
+    <row r="745" ht="52.5" customHeight="1">
+      <c r="A745" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B745" t="str" s="3">
+        <v>深圳先进技术研究院机器视觉与虚拟现实及人机协同平台</v>
+      </c>
+      <c r="C745" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="D745" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E745" t="str" s="3">
+        <v>查询：深圳先进技术研究院 "机器视觉与虚拟现实" "开放" 基金 / 深圳 "机器视觉与模式识别" "开放课题" / "人机智能协同" "开放基金" 2026 2027 / 深圳先进技术研究院 "可视计算" "开放基金"；线索：安徽省工业互联网智能应用与安全工程研究中心2022年度开放基金项目评审结果公示-欢迎访问安徽工业大学门户网站！；特聘序列-深圳理工大学人工智能研究院；机器视觉与虚拟现实山西省重点实验室2026年度开放基金申请指南 - 科研项目申报 - 泛研网；煤炭无人化开采数智技术全国重点实验室2026年度开放基金课题（第一批）申请指南-煤炭无人化开采数智技术全国重点实验室；多模态人工智能系统全国重点实验室2025年度开放课题申请指南----中国科学院自动化研究所</v>
+      </c>
+      <c r="F745" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G745" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H745" t="str" s="3">
+        <v>https://www.ahut.edu.cn/info/1103/22250.htm
+https://airi.suat-sz.edu.cn/gywm/szdw/tpxl.htm
+https://www.funresearch.cn/grant/YjBkMWE1NGEtNTRjOC00NWE0LWE4MTUtZjJlNmVhZmUzYWE2
+https://cdsys.aust.edu.cn/info/1021/2502.htm
+https://www.ia.cas.cn/qtgn/tzgg/202505/t20250520_7788773.html</v>
+      </c>
+      <c r="I745" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第319项</v>
+      </c>
+    </row>
+    <row r="746" ht="52.5" customHeight="1">
+      <c r="A746" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B746" t="str" s="3">
+        <v>深圳先进技术研究院医疗机器人触觉及位置服务平台</v>
+      </c>
+      <c r="C746" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="D746" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E746" t="str" s="3">
+        <v>查询：深圳先进技术研究院 "微创" "开放基金" 机器人 / 深圳先进技术研究院 "触觉" "开放课题" / 深圳 "北斗" "工程实验室" "开放基金" / 深圳先进技术研究院 "机器人" "开放课题" 2027 2026；线索：Search | 深圳市人工智能与机器人研究院；神经工程研究中心；在研课题-微纳操作机器人实验室；中国科学院 深圳智能仿生研究中心；副教授，博士生导师 | Open FIESTA｜清华大学国际开放创新教育中心；安徽省北斗精准农业信息工程研究中心</v>
+      </c>
+      <c r="F746" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G746" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H746" t="str" s="3">
+        <v>https://airs.cuhk.edu.cn/search
+https://neural.siat.ac.cn/
+https://romiol.nankai.edu.cn/ktsb/zykt.htm
+https://znfs.siat.ac.cn/
+https://openfiesta.sigs.tsinghua.edu.cn/cn/pi/3/30
+https://www.aielab.net/</v>
+      </c>
+      <c r="I746" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第320项</v>
+      </c>
+    </row>
+    <row r="747" ht="52.5" customHeight="1">
+      <c r="A747" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B747" t="str" s="3">
+        <v>中北大学机器视觉与虚拟现实及安徽工业工业互联网年度对账</v>
+      </c>
+      <c r="C747" t="str" s="3">
+        <v>山西·太原/安徽·马鞍山</v>
+      </c>
+      <c r="D747" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E747" t="str" s="3">
+        <v>查询：site:nuc.edu.cn "机器视觉与虚拟现实" "2026" "开放" / site:ahut.edu.cn "工业互联网智能应用与安全" "2026" "开放基金" / site:ahut.edu.cn "工业互联网智能应用与安全" "开放基金" "指南" / site:siat.ac.cn "开放基金" "2026" "机器人"；线索：机器视觉与虚拟现实山西省重点实验室 2026年度开放基金申请指南-中北大学；安徽省工业互联网智能应用与安全工程研究中心2025年度开放基金申请指南-欢迎访问安徽工业大学门户网站！；安徽省工业互联网智能应用与安全工程研究中心开放基金课题申报指南（2024年度）-欢迎访问安徽工业大学门户网站！；安徽省工业互联网智能应用与安全工程研究中心2025年度开放基金项目评审结果公示-欢迎访问安徽工业大学门户网站！；安徽省工业互联网智能应用与安全工程研究中心2022年度开放基金项目评审结果公示-欢迎访问安徽工业大学门户网站！；医学成像科学与技术系统全国重点实验室2026年度开放基金拟立项课题公示</v>
+      </c>
+      <c r="F747" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G747" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H747" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/62433.htm
+https://www.ahut.edu.cn/info/1022/25764.htm
+https://www.ahut.edu.cn/info/1022/23642.htm
+https://www.ahut.edu.cn/info/1103/26046.htm
+https://www.ahut.edu.cn/info/1103/22250.htm
+https://isynbio.siat.ac.cn/cxqjzx/medimaging/zxgg/2026041511424879183/index.html</v>
+      </c>
+      <c r="I747" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第321项</v>
+      </c>
+    </row>
+    <row r="748" ht="52.5" customHeight="1">
+      <c r="A748" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B748" t="str" s="3">
+        <v>西北省属高校机器人重点平台目录补漏</v>
+      </c>
+      <c r="C748" t="str" s="3">
+        <v>甘肃/宁夏/内蒙古</v>
+      </c>
+      <c r="D748" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E748" t="str" s="3">
+        <v>查询：兰州理工大学 机器人 科研平台 开放基金 2026 / 兰州交通大学 人工智能 自动化 重点实验室 开放课题 2026 / 宁夏大学 机器人 重点实验室 开放基金 2026 / 内蒙古工业大学 机器人 智能装备 重点实验室 开放基金 2026 2027；线索：关于公布交通智能运维技术与装备教育部重点实验室2025年度开放课题评审结果的通知-交通智能运维技术与装备教育部重点实验室；2026年度开放课题申请公告；内蒙古自治区机器人与智能装备技术重点实验室介绍-机械工程学院；内蒙古工业大学新能源学院机械电子专业实验室采购项目（机器人与智能装备技术实验的教学设备）中标（成交）结果公告；重点实验室-兰州交通大学；管理办法----机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="F748" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G748" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H748" t="str" s="3">
+        <v>https://tiom.ecjtu.edu.cn/info/1047/3632.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://jixiexy.imut.edu.cn/info/1107/5834.htm
+https://www.ccgp.gov.cn/cggg/dfgg/zbgg/202607/t20260716_26949519.htm
+https://www.lzjtu.edu.cn/kxyj/zdsys.htm
+https://rlab.sia.cas.cn/kfjj/glbf/</v>
+      </c>
+      <c r="I748" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第322项</v>
+      </c>
+    </row>
+    <row r="749" ht="52.5" customHeight="1">
+      <c r="A749" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B749" t="str" s="3">
+        <v>澳门高校及横琴研究平台开放课题机制补漏</v>
+      </c>
+      <c r="C749" t="str" s="3">
+        <v>澳门/广东·珠海</v>
+      </c>
+      <c r="D749" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E749" t="str" s="3">
+        <v>查询：site:must.edu.mo 机器人 开放基金 / site:cityu.edu.mo 开放课题 智能 / 澳门大学 横琴 研究院 开放课题 2026 2027 / 澳门 "机器人" "开放基金" 2026 2027；线索：澳大加强研究院建设　助力澳门产业多元 – 澳门特别行政区政府入口网站；2026年度开放基金评审结果公告；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；澳门新葡京平台 “复杂工程系统测量与控制”教育部重点实验室2022年度开放课题申请指南；关于发布“空间智能控制技术全国重点实验室2026年度开放基金指南”的通知 - 课题部落；澳门博士申请窗口延长，研究计划要和横琴实习场景接上_吕励勤的博客-新东方前途出国</v>
+      </c>
+      <c r="F749" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G749" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H749" t="str" s="3">
+        <v>https://www.gov.mo/zh-hans/news/917258/?noredirect=zh_hans
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://www.xpjplat.com/mccse/2022/0215/c33959a398676/page.htm
+https://www.iktbl.com/?p=4907
+https://liuxue.xdf.cn/blog/blog_7993888.shtml</v>
+      </c>
+      <c r="I749" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第323项</v>
+      </c>
+    </row>
+    <row r="750" ht="52.5" customHeight="1">
+      <c r="A750" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B750" t="str" s="3">
+        <v>香港高校机器人研究平台对外课题机制核查</v>
+      </c>
+      <c r="C750" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D750" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E750" t="str" s="3">
+        <v>查询：site.polyu.edu.hk "robotics" "open fund" / site:hkust.edu.hk "robotics" "open research fund" / site:cuhk.edu.hk "robotics" "open project" funding / site:hku.hk "robotics" "open fund"；线索：警用智能机器人达州市重点实验室2026年度开放基金申报公告-警用智能机器人达州市重点实验室；一种多运动模式的仿生软体爬行机器人设计与性能研究</v>
+      </c>
+      <c r="F750" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G750" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H750" t="str" s="3">
+        <v>https://jqr.sasu.edu.cn/info/1009/1061.htm
+https://aas.net.cn/cn/article/doi/10.16383/j.aas.c250680</v>
+      </c>
+      <c r="I750" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第324项</v>
+      </c>
+    </row>
+    <row r="751" ht="52.5" customHeight="1">
+      <c r="A751" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B751" t="str" s="3">
+        <v>香港理工大学机器人研究中心及内地研究院目录</v>
+      </c>
+      <c r="C751" t="str" s="3">
+        <v>香港/珠三角</v>
+      </c>
+      <c r="D751" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E751" t="str" s="3">
+        <v>查询：site:polyu.edu.hk robotics research centres institutes open funding external / site:polyu.edu.hk "开放课题" 2026 / site:polyu.edu.hk "开放基金" / 香港理工大学 深圳研究院 机器人 开放课题；线索：Chief Editor’s Corner | PolyU Academy for Interdisciplinary Research (PAIR)；Search | 深圳市人工智能与机器人研究院；External Partnership Opportunities | Research and Innovation Office；Research Centres；Interdisciplinary Research for Excellence；开放项目 | 深圳市人工智能与机器人研究院</v>
+      </c>
+      <c r="F751" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G751" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H751" t="str" s="3">
+        <v>https://www.polyu.edu.hk/pair/publications/issue-3/chief-editors-corner/
+https://airs.cuhk.edu.cn/search
+https://www.polyu.edu.hk/rio/for-researcher/external-partnership-opportunities/?sc_lang=en
+https://www.polyu.edu.hk/bre/research/research-centres
+https://www.polyu.edu.hk/pair/-/media/department/pair/publication/pair-annual-reoport/pair-annual-report-2023.pdf
+https://airs.cuhk.edu.cn/page/372</v>
+      </c>
+      <c r="I751" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第325项</v>
+      </c>
+    </row>
+    <row r="752" ht="52.5" customHeight="1">
+      <c r="A752" t="str" s="3">
+        <v>2026-10-09港澳及平台补漏</v>
+      </c>
+      <c r="B752" t="str" s="3">
+        <v>澳门科技大学机器人研究平台及对外资助机制</v>
+      </c>
+      <c r="C752" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D752" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E752" t="str" s="3">
+        <v>查询：site:must.edu.mo 机器人 实验室 科研平台 / site:must.edu.mo "开放基金" / site:must.edu.mo "开放课题" / site:cityu.edu.mo "开放基金"；线索：开放课题（已完成）/ Opening Research Projects（Finished）；6.胡国平，陈珂，李青侠，郭伟，“月球表面微波亮温时变趋势研究”，华中科技大学（自然科学版），vol.41(5), 2013.；研究小组：天体化学；澳门建筑与城市规划研究院；研究小组：天体生物学；研究小组：行星表面环境与小天体</v>
+      </c>
+      <c r="F752" t="str" s="3">
+        <v>查询结果须逐项确认归属和年度；无命中不证明没有基金；论文基金致谢、教学开放、招聘、外部一般项目转发不当本地开放基金。</v>
+      </c>
+      <c r="G752" t="str" s="3">
+        <v>仅本查询已执行，未计机构完成。</v>
+      </c>
+      <c r="H752" t="str" s="3">
+        <v>https://www.must.edu.mo/images/SKL/files/%E5%BC%80%E6%94%BE%E8%AF%BE%E9%A2%98_%E5%B7%B2%E5%AE%8C%E6%88%90.pdf
+https://www.must.edu.mo/images/SSI/cv/Website_Teachers_CV_Form-GPHU_20160930_%E7%B0%A1%E9%AB%94%E4%B8%AD%E6%96%87.pdf
+https://www.must.edu.mo/cn/ssi/cosmochemistry
+https://www.must.edu.mo/cn/ssi/course/1128-research/yjs/maupi
+https://www.must.edu.mo/cn/ssi/astrobiology
+https://www.must.edu.mo/cn/ssi/environment</v>
+      </c>
+      <c r="I752" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第326项</v>
+      </c>
+    </row>
+    <row r="753" ht="52.5" customHeight="1">
+      <c r="A753" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B753" t="str" s="3">
+        <v>香港浸会大学深圳研究院</v>
+      </c>
+      <c r="C753" t="str" s="3">
+        <v>香港/广东·深圳</v>
+      </c>
+      <c r="D753" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E753" t="str" s="3">
+        <v>已读iRACE Call for Applications完整栏目；2026—2027内容主要转发国家及省市通用项目。</v>
+      </c>
+      <c r="F753" t="str" s="3">
+        <v>栏目不是研究院机器人实验室自主开放课题；其他平台目录及外部资格未全查。</v>
+      </c>
+      <c r="G753" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H753" t="str" s="3">
+        <v>https://irace.hkbu.edu.hk/research/call-for-applications.html</v>
+      </c>
+      <c r="I753" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="754" ht="52.5" customHeight="1">
+      <c r="A754" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B754" t="str" s="3">
+        <v>深圳先进技术研究院先进计算与数字工程研究所</v>
+      </c>
+      <c r="C754" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="D754" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E754" t="str" s="3">
+        <v>省、市平台目录缓存定位机器视觉与虚拟现实、机器视觉模式识别、可视计算可视分析、北斗位置服务等；后续逐名基金/2026—2027/长期机制查询未获新增正式通知。</v>
+      </c>
+      <c r="F754" t="str" s="3">
+        <v>目录续读首次超时交人工；仅该研究所子目录，不代表全院目录；机器人M186、医学成像M020复用。</v>
+      </c>
+      <c r="G754" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H754" t="str" s="3">
+        <v>https://szs.siat.ac.cn/siat/iacde/yjsgk/tj_pt/sjkypt/index.html
+https://szs.siat.ac.cn/siat/iacde/yjsgk/tj_pt/sjkypt28/index.html</v>
+      </c>
+      <c r="I754" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="755" ht="52.5" customHeight="1">
+      <c r="A755" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B755" t="str" s="3">
+        <v>澳门大学智慧城市物联网国家重点实验室</v>
+      </c>
+      <c r="C755" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D755" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E755" t="str" s="3">
+        <v>2026—2027指南既有M165复用；另定位2025—2026历史指南官方PDF，缓存年份/页脚Applications2024不一致。</v>
+      </c>
+      <c r="F755" t="str" s="3">
+        <v>历史PDF首次403，任务和条款未核不新建正式项目；需人工确认实际年度。M123/M150/M151/M164既有剔除不重复收录。</v>
+      </c>
+      <c r="G755" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H755" t="str" s="3">
+        <v>https://skliotsc.um.edu.mo/wp-content/uploads/2024/07/Guidelines-for-IOTSC-ORP-2025-2026-2.pdf</v>
+      </c>
+      <c r="I755" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="756" ht="52.5" customHeight="1">
+      <c r="A756" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B756" t="str" s="3">
+        <v>内蒙古工业大学机器人与智能装备技术重点实验室</v>
+      </c>
+      <c r="C756" t="str" s="3">
+        <v>内蒙古·呼和浩特</v>
+      </c>
+      <c r="D756" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E756" t="str" s="3">
+        <v>完整官方2024介绍确认由先进制造2011与特殊服役智能机器人2020平台重组；特殊环境巡检、新能源智能运维、极端环境机电装备任务明确，2026—2027基金机制查询。</v>
+      </c>
+      <c r="F756" t="str" s="3">
+        <v>开放性平台是科研合作介绍，未获面向校外资助公告/金额；不推定长期受理。机械学院及其他学院完整名单未齐。</v>
+      </c>
+      <c r="G756" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H756" t="str" s="3">
+        <v>https://jixiexy.imut.edu.cn/info/1107/5834.htm</v>
+      </c>
+      <c r="I756" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="757" ht="52.5" customHeight="1">
+      <c r="A757" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B757" t="str" s="3">
+        <v>兰州交通大学</v>
+      </c>
+      <c r="C757" t="str" s="3">
+        <v>甘肃·兰州</v>
+      </c>
+      <c r="D757" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E757" t="str" s="3">
+        <v>重点实验室目录定位；2026—2027机器人/自动化及长期机制检索。</v>
+      </c>
+      <c r="F757" t="str" s="3">
+        <v>完整目录第一次超时，交人工；教学开放实验项目不当校外资助。</v>
+      </c>
+      <c r="G757" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H757" t="str" s="3">
+        <v>https://www.lzjtu.edu.cn/kxyj/zdsys.htm</v>
+      </c>
+      <c r="I757" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="758" ht="52.5" customHeight="1">
+      <c r="A758" t="str" s="3">
+        <v>2026-10-09目录及机制核验</v>
+      </c>
+      <c r="B758" t="str" s="3">
+        <v>安徽工业大学工业互联网智能应用与安全工程研究中心</v>
+      </c>
+      <c r="C758" t="str" s="3">
+        <v>安徽·马鞍山</v>
+      </c>
+      <c r="D758" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E758" t="str" s="3">
+        <v>官方2024/2025指南搜索正文及2022/2025立项公示发现长期校外资助机制；1—3万、2年、固定第一合作人及报账、2025合作人须通讯/共同通讯；2026未获指南。</v>
+      </c>
+      <c r="F758" t="str" s="3">
+        <v>当年六项主要网络、数据、边缘计算、安全和工业缺陷故障诊断，未明确机器人任务，不因人机协同论文/立项标题推定指南相关；暂存机制证据而不新增正式相关项目。</v>
+      </c>
+      <c r="G758" t="str" s="3">
+        <v>仅所列范围核验；机构整体未查全。</v>
+      </c>
+      <c r="H758" t="str" s="3">
+        <v>https://www.ahut.edu.cn/info/1022/25764.htm
+https://www.ahut.edu.cn/info/1022/23642.htm</v>
+      </c>
+      <c r="I758" t="str" s="3">
+        <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -18038,6 +18038,172 @@
       </c>
       <c r="AA199" t="str" s="3"/>
     </row>
+    <row r="200" ht="132" customHeight="1">
+      <c r="A200" t="str" s="3">
+        <v>N051</v>
+      </c>
+      <c r="B200" t="str" s="3">
+        <v>正式历史公告完整正文已读；两类申请模板首次超时</v>
+      </c>
+      <c r="C200" t="str" s="3">
+        <v>深圳市人工智能与机器人研究院</v>
+      </c>
+      <c r="D200" t="str" s="3">
+        <v>AIRS开放项目（探索/重点）</v>
+      </c>
+      <c r="E200" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F200" t="str" s="3">
+        <v>2020</v>
+      </c>
+      <c r="G200" t="n" s="6">
+        <v>43868</v>
+      </c>
+      <c r="H200" t="str" s="3">
+        <v>电子版2020-02-07之前；盖章纸质版2020-02-14前；均未列具体时点</v>
+      </c>
+      <c r="I200" t="str" s="3">
+        <v>探索：机器学习、计算机视觉、群体智能、智能云物联网、机器人设计理论/系统及应用。重点当年6项：可信学习、联邦强化学习、工业机器学习、机器人与AI教育素养测评、大型机翼内部检测机器人、5G智能网联调度规划；按实际任务选择，不把2020任务套2026。</v>
+      </c>
+      <c r="J200" t="str" s="3">
+        <v>探索20—50万元/年；重点≤150万元/年；周期1—2年，最终立项额度由评审决定；未给统一两年总额。</v>
+      </c>
+      <c r="K200" t="str" s="3">
+        <v>境内高校、科研机构、国家高新技术企业等为依托；港澳高校/公营科研机构通过深圳设立单位申请。负责人全职聘用获单位书面同意；港澳单位深圳项目可由港澳全职且具PI经历者主持。探索博士/中级以上/高企主要技术负责人，或1名同领域高级推荐；重点高级/高企主要技术负责人，或2名同领域高级推荐。执行期内负责人或参与者合计≤1项（AIRS合作人例外）；AIRS人员/分院在研项目负责人不能主持。</v>
+      </c>
+      <c r="L200" t="str" s="3">
+        <v>探索需参与研究院学术交流，研究院额外资助差旅；重点须至少1名AIRS副研究员及以上合作人，提交前签合作协议，约定任务、经费分配、IP及成果转化收益。访问天数未载。</v>
+      </c>
+      <c r="M200" t="str" s="3">
+        <v>探索经费拨到申请人依托单位；重点部分外拨依托单位、部分留AIRS，比例须预先合作协议约定。首批50%依市政府经费到位拨付，中期通过后1个月内拨尾款。按深圳科技研发资金及各单位财务制度报账；结题需指定清单会计所专项审计，审计费用列项目预算。</v>
+      </c>
+      <c r="N200" t="str" s="3">
+        <v>1—2年；具体起止日期公开正文未载。</v>
+      </c>
+      <c r="O200" t="str" s="3">
+        <v>项目结束经费决算+指定会计所专项审计；正文未公开论文/专利/样机数量、第一单位或作者指标，不能推定仅凭论文结题。</v>
+      </c>
+      <c r="P200" t="str" s="3">
+        <v>重点提交前协议约定IP及转化收益；探索具体IP归属正文未载，须管理办法/任务书确认。</v>
+      </c>
+      <c r="Q200" t="str" s="3">
+        <v>电子版2020-02-07前发openproj-airs@cuhk.edu.cn，主题单位+姓名+开放项目申请；盖章纸质2020-02-14前邮寄深圳龙岗坂田雅宝路1号星河WORLD G2-15层，518172，鄢老师。两类表为公告附件。</v>
+      </c>
+      <c r="R200" t="str" s="3">
+        <v>本人博士及南京信息工程大学现职可对应探索学历及境内高校条件；本轮已截止。重点职称/推荐、执行期其他项目限项及合作协议须按后续年度实核，不认熟人已落实。</v>
+      </c>
+      <c r="S200" t="str" s="3">
+        <v>2020已截止，仅历史机制参考。两份DOC模板首次超时；数量成果/署名/探索IP、当年管理办法未取得；不得套用2020金额和外拨到2026。M098已记录2026另轮不重复。</v>
+      </c>
+      <c r="T200" t="str" s="3">
+        <v>https://airs.cuhk.edu.cn/page/372</v>
+      </c>
+      <c r="U200" t="str" s="3">
+        <v>公告附件1探索申请模板、2重点模板：各首次TimeoutError；原精确URL见原始访问记录及人工N051。</v>
+      </c>
+      <c r="V200" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W200" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X200" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y200" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="Z200" t="str" s="3">
+        <v>鄢老师，（86）755-23518016；openproj-airs@cuhk.edu.cn；深圳龙岗坂田雅宝路1号星河WORLD G2-15层518172（2020提交地址）；页尾现办公G2-14层不是替换历史申报地址。</v>
+      </c>
+      <c r="AA200" t="str" s="3">
+        <v>M098为2026独立轮次；本网页栏目正文明确2020，不按访问日当当前公告。</v>
+      </c>
+    </row>
+    <row r="201" ht="132" customHeight="1">
+      <c r="A201" t="str" s="3">
+        <v>N052</v>
+      </c>
+      <c r="B201" t="str" s="3">
+        <v>正式2026联合公告完整正文已读；机器人任务证据未够，申请附件需验证码</v>
+      </c>
+      <c r="C201" t="str" s="3">
+        <v>沈阳航空航天大学</v>
+      </c>
+      <c r="D201" t="str" s="3">
+        <v>飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+      </c>
+      <c r="E201" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F201" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G201" t="n" s="6">
+        <v>46249</v>
+      </c>
+      <c r="H201" t="str" s="3">
+        <v>具体截止时点未载</v>
+      </c>
+      <c r="I201" t="str" s="3">
+        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+      </c>
+      <c r="J201" t="str" s="3">
+        <v>合同金额2万元/项；计划≤10项。</v>
+      </c>
+      <c r="K201" t="str" s="3">
+        <v>一般副高以上或博士；项目必须由沈航及其他高校/研究院所/企业等人员共同承担；年龄/限项正文未载。</v>
+      </c>
+      <c r="L201" t="str" s="3">
+        <v>必须沈航+校外共同承担；执行期至少参加1次教育部实验室学术交流并作汇报；没有在本公告指定合作人级别/驻室天数。</v>
+      </c>
+      <c r="M201" t="str" s="3">
+        <v>须按申请书研究计划/经费预算执行、提交进展和支出说明；外拨比例、报账地点、开支细项正文未载，不推断2万可全拨南信大。</v>
+      </c>
+      <c r="N201" t="str" s="3">
+        <v>研究期限2年；起止日期未载。</v>
+      </c>
+      <c r="O201" t="str" s="3">
+        <v>负责人第一或通讯作者且与非沈航参研人共同：公开SCI≥1篇，或EI/一级学报≥2篇，或授权发明专利≥1项；至少1次交流汇报；进展、支出说明、结题报告。论文及其他成果须基金标注，第一单位顺序未载。</v>
+      </c>
+      <c r="P201" t="str" s="3">
+        <v>开放基金成果归飞行器快速试制技术研究教育部重点实验室、航空制造技术国防重点学科与技术研究中心共有；正文未明确校外单位共有比例，须协议确认。</v>
+      </c>
+      <c r="Q201" t="str" s="3">
+        <v>填写联合申请书，附研究基础佐证；课题名称（研究方向）+申请人+单位命名；申请书与佐证合并PDF，2026-08-15前发136478034@qq.com。纸质份数/盖章正文未載，附件待取。</v>
+      </c>
+      <c r="R201" t="str" s="3">
+        <v>本人博士/高校现职已知；与沈航合作人尚未落实。年度任务是否涵盖实际机器人或相关装备算法待核，本轮已截止。</v>
+      </c>
+      <c r="S201" t="str" s="3">
+        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+      </c>
+      <c r="T201" t="str" s="3">
+        <v>https://kjc.sau.edu.cn/info/1074/2420.htm</v>
+      </c>
+      <c r="U201" t="str" s="3">
+        <v>申请DOC验证码：https://kjc.sau.edu.cn/system/_content/download.jsp?owner=2133624617&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=18212205</v>
+      </c>
+      <c r="V201" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W201" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X201" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y201" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="Z201" t="str" s="3">
+        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
+      </c>
+      <c r="AA201" t="str" s="3">
+        <v>同一联合公告两平台合并为1独立轮次，不拆成两笔基金；2025/2024另有索引但未核不套条款。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -18457,6 +18623,8 @@
     <hyperlink ref="T197" ns1:id="rIdResume419"/>
     <hyperlink ref="T198" ns1:id="rIdResume420"/>
     <hyperlink ref="T199" ns1:id="rIdResume421"/>
+    <hyperlink ref="T200" ns1:id="rIdResume422"/>
+    <hyperlink ref="T201" ns1:id="rIdResume423"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -41846,6 +42014,471 @@
       </c>
       <c r="I758" t="str" s="3">
         <v>resume_sources_20261009.json本轮原文/搜索缓存</v>
+      </c>
+    </row>
+    <row r="759" ht="52.5" customHeight="1">
+      <c r="A759" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B759" t="str" s="3">
+        <v>香港理工机器人相关平台自主外部资助逐名检索</v>
+      </c>
+      <c r="C759" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D759" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E759" t="str" s="3">
+        <v>查询：site:polyu.edu.hk "RCUAS" "fund" "application" / site:polyu.edu.hk "RIAM" "open" "fund" / site:polyu.edu.hk "RIAIoT" "fund" "external" / site:polyu.edu.hk "RISUD" "Interdisciplinary Research Scheme" eligibility；线索：Projects | RCUAS；Interdisciplinary Research Scheme | Research Institute for Sustainable Urban Development；Multi-disciplinary Research | Research Institute for Sustainable Urban Development；Interdisciplinary Research Scheme | Research Institute for Sustainable Urban Development；Hydrogel-engineered interface suppressing water activity by hydrogen bonds and regulated solvation for stable Zn metal anodes | PolyU Institutional Research Archive；Achieving excellent elevated-temperature mechanical properties in dual-phase high-entropy alloys via nanoscale co-precipitation and heterostructure engineering | PolyU Institutional Research Archive</v>
+      </c>
+      <c r="F759" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G759" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H759" t="str" s="3">
+        <v>https://www.polyu.edu.hk/rcuas/research/projects/
+https://www.polyu.edu.hk/en/risud/research/multi-disciplinary-research-in-focus-areas/interdisciplinary-research-scheme
+https://www.polyu.edu.hk/risud/Research/Multi-Disciplinary-Research-in-Focus-Areas?sc_lang=en
+https://www.polyu.edu.hk/risud/Research/Multi-Disciplinary-Research-in-Focus-Areas/Interdisciplinary-Research-Scheme?sc_lang=en
+https://ira.lib.polyu.edu.hk/handle/10397/121319?mode=full
+https://ira.lib.polyu.edu.hk/handle/10397/114306?mode=full</v>
+      </c>
+      <c r="I759" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第327项</v>
+      </c>
+    </row>
+    <row r="760" ht="52.5" customHeight="1">
+      <c r="A760" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B760" t="str" s="3">
+        <v>澳门科大已确认科研实验室逐名开放机制查询</v>
+      </c>
+      <c r="C760" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D760" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E760" t="str" s="3">
+        <v>查询：site:must.edu.mo "人工智能及机器学习" "开放" 基金 / site:must.edu.mo "图形图像及视频处理" "开放" 课题 / site:must.edu.mo "传感器系统实验室" "开放" 基金 / site:must.edu.mo "智能航空仿真" "课题" 2026 2027；线索：创新工程学院 - 学术单位/学系 - 计算机科学与工程学院 - 实验室 - 科研实验室；研究生院 - 更多 - 最新消息 - 校生动态</v>
+      </c>
+      <c r="F760" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G760" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H760" t="str" s="3">
+        <v>https://fie.must.edu.mo/id-1458/article/view/id-557.html?locale=zh_CN
+https://sgs.must.edu.mo/news.school.news/article/view/id-39098.html?locale=zh_CN</v>
+      </c>
+      <c r="I760" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第328项</v>
+      </c>
+    </row>
+    <row r="761" ht="52.5" customHeight="1">
+      <c r="A761" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B761" t="str" s="3">
+        <v>东北省属高校机器人平台批量发现B</v>
+      </c>
+      <c r="C761" t="str" s="3">
+        <v>吉林/黑龙江</v>
+      </c>
+      <c r="D761" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E761" t="str" s="3">
+        <v>查询：长春理工大学 科研平台 机器人 开放课题 2026 2027 / 哈尔滨理工大学 重点实验室 机器人 开放基金 2026 / 黑龙江科技大学 开放课题 智能装备 2026 / 东北电力大学 机器人 实验室 开放基金 2026；线索：2026年度开放课题申请公告；关于公布黑龙江科技大学2026年教学研究项目立项结果的通知-黑龙江科技大学-教务处；哈尔滨工业大学机器人技术与系统国家重点实验室；机器人技术与系统国家重点实验室（哈尔滨工业大学）；黑龙江科技大学2026年学术学位硕士研究生招生目录；SIELab｜智能基础设施工程创新研究团队- 黑龙江科技大学</v>
+      </c>
+      <c r="F761" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G761" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H761" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://jwc.usth.edu.cn/info/1003/2498.htm
+https://robot.hit.edu.cn/
+https://robot.hit.edu.cn/_upload/article/files/74/20/e1401e0a4bd58541639716dd275d/dcaff854-475c-4401-abd3-b25f7ac81081.pdf
+https://gs.usth.edu.cn/__local/3/29/31/4982B19CBDB66DDDEF3E4F79F80_972A79E8_2C815.pdf
+https://ibridgelab.com/</v>
+      </c>
+      <c r="I761" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第329项</v>
+      </c>
+    </row>
+    <row r="762" ht="52.5" customHeight="1">
+      <c r="A762" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B762" t="str" s="3">
+        <v>东北省属高校机器人平台批量发现A</v>
+      </c>
+      <c r="C762" t="str" s="3">
+        <v>辽宁/吉林</v>
+      </c>
+      <c r="D762" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E762" t="str" s="3">
+        <v>查询：沈阳工业大学 科研平台 机器人 开放基金 2026 2027 / 沈阳航空航天大学 重点实验室 无人机 开放课题 2026 2027 / 辽宁科技大学 重点实验室 机器人 开放基金 / 长春工业大学 重点实验室 智能装备 开放基金 2026；线索：关于2026年度教育部重点实验室/重点学科与技术研究中心联合开放基金课题申请的通知-沈阳航空航天大学-科学技术研究院；管理办法----机器人与智能系统全国重点实验室；基金简介----机器人与智能系统全国重点实验室；沈阳航空航天大学-科学技术研究院；关于申报辽宁省桥梁安全工程重点实验室2026年度开放基金项目的通知-科技处；梁宵-沈阳航空航天大学研究生院</v>
+      </c>
+      <c r="F762" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G762" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H762" t="str" s="3">
+        <v>https://kjc.sau.edu.cn/info/1074/2420.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://rlab.sia.cas.cn/kfjj/jjjj/
+https://kjc.sau.edu.cn/
+https://www.lncc.edu.cn/kjc/info/1015/3316.htm
+https://yjs.sau.edu.cn/info/1035/1410.htm</v>
+      </c>
+      <c r="I762" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第330项</v>
+      </c>
+    </row>
+    <row r="763" ht="52.5" customHeight="1">
+      <c r="A763" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B763" t="str" s="3">
+        <v>沈阳航空已确认机器人与飞控省级平台逐名基金查漏</v>
+      </c>
+      <c r="C763" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D763" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E763" t="str" s="3">
+        <v>查询："航空航天装备与机器人技术" "开放" 基金 2026 2027 / "飞行器测试与控制技术" "开放课题" / "先进飞行控制与仿真技术" "开放" 基金 / "农用无人机专业技术创新中心" "开放课题"；线索：孟光磊-沈阳航空航天大学研究生院；装发年底又放招，1.6亿等你拿 | 国防科技重点实验室基金公开指南条目全收录_采购；复杂系统控制与智能协同技术重点实验室开放研究基金课题指南；诚聘英才|智能测试与控制技术研究所招聘公告；〖招聘信息〗全球空海精英计划｜艾美依航空博士后工作站开放申请（内附福利待遇）_中国复合材料工业协会官网；浣江实验室</v>
+      </c>
+      <c r="F763" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G763" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H763" t="str" s="3">
+        <v>https://yjs.sau.edu.cn/info/1035/1399.htm
+https://www.sohu.com/a/276231860_465915
+https://webs.nuist.edu.cn/_s13/2021/1125/c83a186321/page.psp
+https://zri.hit.edu.cn/2022/1029/c14156a283289/page.htm
+https://www.ccia.xin/mingxingqiyedanwei/2643.html
+https://huanjianglab.zju.edu.cn/product.aspx</v>
+      </c>
+      <c r="I763" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第331项</v>
+      </c>
+    </row>
+    <row r="764" ht="52.5" customHeight="1">
+      <c r="A764" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B764" t="str" s="3">
+        <v>沈阳航空感知交互及加工检测省级平台逐名基金查漏</v>
+      </c>
+      <c r="C764" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D764" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E764" t="str" s="3">
+        <v>查询："知识工程与人机交互" "开放基金" / "空天信息感知与智能处理" "开放课题" / "航空发动机结构件数控加工与检测" "开放" 基金 / site:kjc.sau.edu.cn 开放基金 2027 2026；线索：2015年度山东计算机学会省重点实验室联合开放基金申请指南 -山东工商学院计算机科学与技术学院；2010年信息系新获国家自然科学基金项目3项，省部级科研项目4项，各类校内研究项目7项，企；申请！一批次重点实验室课题基金申请指南 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F764" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G764" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H764" t="str" s="3">
+        <v>https://jsj.sdtbu.edu.cn/info/1999/2341.htm
+https://idke.ruc.edu.cn/school/2010.pdf
+https://www.letpub.com.cn/index.php?article_id=3190&amp;page=grant_article_details</v>
+      </c>
+      <c r="I764" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第332项</v>
+      </c>
+    </row>
+    <row r="765" ht="52.5" customHeight="1">
+      <c r="A765" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B765" t="str" s="3">
+        <v>深圳市人工智能与机器人研究院</v>
+      </c>
+      <c r="C765" t="str" s="3">
+        <v>广东·深圳</v>
+      </c>
+      <c r="D765" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E765" t="str" s="3">
+        <v>AIRS开放项目（探索/重点）；2020；N051；正式历史公告完整正文已读；两类申请模板首次超时</v>
+      </c>
+      <c r="F765" t="str" s="3">
+        <v>2020已截止，仅历史机制参考。两份DOC模板首次超时；数量成果/署名/探索IP、当年管理办法未取得；不得套用2020金额和外拨到2026。M098已记录2026另轮不重复。</v>
+      </c>
+      <c r="G765" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H765" t="str" s="3">
+        <v>https://airs.cuhk.edu.cn/page/372</v>
+      </c>
+      <c r="I765" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="766" ht="52.5" customHeight="1">
+      <c r="A766" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B766" t="str" s="3">
+        <v>沈阳航空航天大学</v>
+      </c>
+      <c r="C766" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D766" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E766" t="str" s="3">
+        <v>飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金；2026；N052；正式2026联合公告完整正文已读；机器人任务证据未够，申请附件需验证码</v>
+      </c>
+      <c r="F766" t="str" s="3">
+        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+      </c>
+      <c r="G766" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H766" t="str" s="3">
+        <v>https://kjc.sau.edu.cn/info/1074/2420.htm</v>
+      </c>
+      <c r="I766" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="767" ht="52.5" customHeight="1">
+      <c r="A767" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B767" t="str" s="3">
+        <v>香港理工大学RCUAS</v>
+      </c>
+      <c r="C767" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D767" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E767" t="str" s="3">
+        <v>完整研究中心介绍：无人机/无人车/水下航行器、导航感知、人形及外骨骼；外部合作页全文只是政府及企业合作名单，项目列表是已获资助项目；RIAM/RIAIoT/RISUD逐名机制查询。</v>
+      </c>
+      <c r="F767" t="str" s="3">
+        <v>外部合作名单和已获种子资金不是校外可申请通知；各研究院年度指南及完整资格仍有缺口。</v>
+      </c>
+      <c r="G767" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H767" t="str" s="3">
+        <v>https://www.polyu.edu.hk/rcuas/about-rcuas/about-rcuas/
+https://www.polyu.edu.hk/rcuas/about-rcuas/external-collaboration/
+https://www.polyu.edu.hk/rcuas/research/projects/</v>
+      </c>
+      <c r="I767" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="768" ht="52.5" customHeight="1">
+      <c r="A768" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B768" t="str" s="3">
+        <v>香港理工大学RISUD</v>
+      </c>
+      <c r="C768" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D768" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E768" t="str" s="3">
+        <v>官方机制总页全文分别明确内部Interdisciplinary Research Scheme、面向RISUD成员与本地/海外高校合作的Joint Research Fund。</v>
+      </c>
+      <c r="F768" t="str" s="3">
+        <v>JRF独立页第一次超时；金额/期限/校外PI资格及机器人具体任务不明，交人工，未加当前正式基金。</v>
+      </c>
+      <c r="G768" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H768" t="str" s="3">
+        <v>https://www.polyu.edu.hk/risud/research/multi-disciplinary-research-in-focus-areas/?sc_lang=en
+https://www.polyu.edu.hk/en/risud/Research/Multi-Disciplinary-Research-in-Focus-Areas/Joint-Research-Fund</v>
+      </c>
+      <c r="I768" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="769" ht="52.5" customHeight="1">
+      <c r="A769" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B769" t="str" s="3">
+        <v>香港理工大学科研创新处</v>
+      </c>
+      <c r="C769" t="str" s="3">
+        <v>香港</v>
+      </c>
+      <c r="D769" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E769" t="str" s="3">
+        <v>官方External Partnership Opportunities全文：国内外政府/企业一般项目、JITRI合作资金针对PolyU PI，与本地实验室基金区分。</v>
+      </c>
+      <c r="F769" t="str" s="3">
+        <v>页面多个2020—2022旧机制，不用网页当前可访问推断2026受理；其他收入渠道留后阶段，不扩散当前开放课题任务。</v>
+      </c>
+      <c r="G769" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H769" t="str" s="3">
+        <v>https://www.polyu.edu.hk/rio/for-researcher/external-partnership-opportunities/?sc_lang=en</v>
+      </c>
+      <c r="I769" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="770" ht="52.5" customHeight="1">
+      <c r="A770" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B770" t="str" s="3">
+        <v>澳门科技大学创新工程学院</v>
+      </c>
+      <c r="C770" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D770" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E770" t="str" s="3">
+        <v>工程科学科研目录1项传感器系统；计算机科研目录7项：计算机中心、通讯网络、电力电子、AI机器学习、图形图像视频、物联网通讯、智能航空仿真；教学自动化控制小车实验室另核只是课程平台；逐名基金机制查询。</v>
+      </c>
+      <c r="F770" t="str" s="3">
+        <v>实际研究平台介绍/已有项目不当外部资助，2026—2027未获正式开放通知；全校/太空等平台完整目录未齐。</v>
+      </c>
+      <c r="G770" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H770" t="str" s="3">
+        <v>https://fie.must.edu.mo/article/research-labs.html?locale=zh_CN
+https://fie.must.edu.mo/article/id-1458.html?locale=zh_CN
+https://fie.must.edu.mo/id-1458/article/view/id-557.html?locale=zh_CN</v>
+      </c>
+      <c r="I770" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="771" ht="52.5" customHeight="1">
+      <c r="A771" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B771" t="str" s="3">
+        <v>澳门大学</v>
+      </c>
+      <c r="C771" t="str" s="3">
+        <v>澳门</v>
+      </c>
+      <c r="D771" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E771" t="str" s="3">
+        <v>附属研究实体官方目录入口已定位；2026—2027机器人相关物联网M165及其他机制复用。</v>
+      </c>
+      <c r="F771" t="str" s="3">
+        <v>目录首503交人工；不因研究院新闻认定所有附属平台查全。</v>
+      </c>
+      <c r="G771" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H771" t="str" s="3">
+        <v>https://www.um.edu.mo/zh-hant/research/affiliated-entities-units/</v>
+      </c>
+      <c r="I771" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="772" ht="52.5" customHeight="1">
+      <c r="A772" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B772" t="str" s="3">
+        <v>沈阳航空航天大学</v>
+      </c>
+      <c r="C772" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D772" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E772" t="str" s="3">
+        <v>官方完整科研平台汇总44项已读；机器人装备、飞行测试控制、飞控仿真、知识工程人机交互、空天感知、农用无人机、数控加工检测逐名机制查询；2026联合公告N052。</v>
+      </c>
+      <c r="F772" t="str" s="3">
+        <v>所列7项逐名未获新增通知；2026联合实际智能装备任务待附件细化；2025/2024开放索引尚未读取不算完成。目录之外学院省属平台变化未确认。</v>
+      </c>
+      <c r="G772" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H772" t="str" s="3">
+        <v>https://kjc.sau.edu.cn/kypt.htm
+https://kjc.sau.edu.cn/info/1074/2420.htm</v>
+      </c>
+      <c r="I772" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="773" ht="52.5" customHeight="1">
+      <c r="A773" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B773" t="str" s="3">
+        <v>东北电力大学电气工程学院</v>
+      </c>
+      <c r="C773" t="str" s="3">
+        <v>吉林·吉林</v>
+      </c>
+      <c r="D773" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E773" t="str" s="3">
+        <v>完整科研平台9项均电网/新能源/电力电子等；现代电力仿真控制2026年度完整实际4项电气任务，E082快速剔除。</v>
+      </c>
+      <c r="F773" t="str" s="3">
+        <v>不凭智能/控制保留电力基金；机械机器人实验室已发现，机械学院完整名单及资助机制未齐。</v>
+      </c>
+      <c r="G773" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H773" t="str" s="3">
+        <v>https://ee.neepu.edu.cn/kxyj/kypt1.htm
+https://ee.neepu.edu.cn/info/1055/40177.htm</v>
+      </c>
+      <c r="I773" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
       </c>
     </row>
   </sheetData>
@@ -42315,24 +42948,24 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="23" ht="66" customHeight="1">
-      <c r="A23" s="18" t="str">
+    <row r="23" ht="96" customHeight="1">
+      <c r="A23" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B23" s="13" t="d">
-        <v>2025-10-15T00:00:00.000Z</v>
-      </c>
-      <c r="C23" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
-      </c>
-      <c r="D23" s="15" t="str">
-        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
-      </c>
-      <c r="E23" s="15" t="str">
-        <v>5—8万元</v>
-      </c>
-      <c r="F23" s="16" t="str">
-        <v>公告</v>
+      <c r="B23" t="n" s="13">
+        <v>43868</v>
+      </c>
+      <c r="C23" t="str" s="14">
+        <v>深圳市人工智能与机器人研究院·AIRS开放项目（探索/重点）</v>
+      </c>
+      <c r="D23" t="str" s="15">
+        <v>探索：机器学习、计算机视觉、群体智能、智能云物联网、机器人设计理论/系统及应用。重点当年6项：可信学习、联邦强化学习、工业机器学习、机器人与AI教育素养测评、大型机翼内部检测机器人、5G智能网联调度规划；按实际任务选择，不把2020任务套2026。</v>
+      </c>
+      <c r="E23" t="str" s="15">
+        <v>探索20—50万元/年；重点≤150万元/年；周期1—2年，最终立项额度由评审决定；未给统一两年总额。</v>
+      </c>
+      <c r="F23" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="24" ht="66" customHeight="1">
@@ -42340,16 +42973,16 @@
         <v>已截止</v>
       </c>
       <c r="B24" s="13" t="d">
-        <v>2026-05-11T00:00:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C24" s="14" t="str">
-        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D24" s="15" t="str">
-        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
+        <v>轨道交通自主运行、多源感知与车地协同控制（自主运行装备方向）</v>
       </c>
       <c r="E24" s="15" t="str">
-        <v>10万元/项；每方向1项</v>
+        <v>5—8万元</v>
       </c>
       <c r="F24" s="16" t="str">
         <v>公告</v>
@@ -42360,16 +42993,16 @@
         <v>已截止</v>
       </c>
       <c r="B25" s="13" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-11T00:00:00.000Z</v>
       </c>
       <c r="C25" s="14" t="str">
-        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
+        <v>清华大学·北京信息科学与技术国家研究中心2026年度开放课题</v>
       </c>
       <c r="D25" s="15" t="str">
-        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
+        <v>方向6：类脑物理智能体跨场景感知、认知、决策、执行；小样本迁移适配及平台验证</v>
       </c>
       <c r="E25" s="15" t="str">
-        <v>5—10万元</v>
+        <v>10万元/项；每方向1项</v>
       </c>
       <c r="F25" s="16" t="str">
         <v>公告</v>
@@ -42380,16 +43013,16 @@
         <v>已截止</v>
       </c>
       <c r="B26" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-05-29T00:00:00.000Z</v>
       </c>
       <c r="C26" s="14" t="str">
-        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
+        <v>中国科学院自动化研究所·多模态人工智能系统全国重点实验室</v>
       </c>
       <c r="D26" s="15" t="str">
-        <v>地下空间具身智能感知、定位与点云建模</v>
+        <v>多模态机器人感知、医疗与农业机器人、具身决策控制</v>
       </c>
       <c r="E26" s="15" t="str">
-        <v>一般≥2万元；重点≥3万元</v>
+        <v>5—10万元</v>
       </c>
       <c r="F26" s="16" t="str">
         <v>公告</v>
@@ -42400,16 +43033,16 @@
         <v>已截止</v>
       </c>
       <c r="B27" s="13" t="d">
-        <v>2026-07-31T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C27" s="14" t="str">
-        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
+        <v>北京市测绘设计研究院·城市空间智能感知与数字治理北京市重点实验室</v>
       </c>
       <c r="D27" s="15" t="str">
-        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
+        <v>地下空间具身智能感知、定位与点云建模</v>
       </c>
       <c r="E27" s="15" t="str">
-        <v>30—90万元（无人机监视反制专项）</v>
+        <v>一般≥2万元；重点≥3万元</v>
       </c>
       <c r="F27" s="16" t="str">
         <v>公告</v>
@@ -42420,16 +43053,16 @@
         <v>已截止</v>
       </c>
       <c r="B28" s="13" t="d">
-        <v>2026-08-28T00:00:00.000Z</v>
+        <v>2026-07-31T00:00:00.000Z</v>
       </c>
       <c r="C28" s="14" t="str">
-        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
+        <v>中国科学院自动化研究所·复杂系统认知与决策国家级重点实验室</v>
       </c>
       <c r="D28" s="15" t="str">
-        <v>机器人多接触规划、具身技能学习与运动行为</v>
+        <v>无人机监视反制平台关键技术（详细研究内容与指标须向联系人索取）</v>
       </c>
       <c r="E28" s="15" t="str">
-        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
+        <v>30—90万元（无人机监视反制专项）</v>
       </c>
       <c r="F28" s="16" t="str">
         <v>公告</v>
@@ -42440,57 +43073,57 @@
         <v>已截止</v>
       </c>
       <c r="B29" s="13" t="d">
-        <v>2025-08-10T00:00:00.000Z</v>
+        <v>2026-08-28T00:00:00.000Z</v>
       </c>
       <c r="C29" s="14" t="str">
-        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+        <v>北京大学·跨媒体通用人工智能全国重点实验室</v>
       </c>
       <c r="D29" s="15" t="str">
-        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+        <v>机器人多接触规划、具身技能学习与运动行为</v>
       </c>
       <c r="E29" s="15" t="str">
-        <v>5—10万元/项</v>
+        <v>官方明确｜2026年度单项开放课题资助上限20万元，最终核准额度以批复为准。</v>
       </c>
       <c r="F29" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="30" ht="79.5" customHeight="1">
+    <row r="30" ht="66" customHeight="1">
       <c r="A30" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B30" s="13" t="d">
+        <v>2025-08-10T00:00:00.000Z</v>
+      </c>
+      <c r="C30" s="14" t="str">
+        <v>中国科学院沈阳自动化研究所·机器人与智能系统全国重点实验室</v>
+      </c>
+      <c r="D30" s="15" t="str">
+        <v>医疗、柔性与协作机器人；机器人感知、学习及控制</v>
+      </c>
+      <c r="E30" s="15" t="str">
+        <v>5—10万元/项</v>
+      </c>
+      <c r="F30" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="31" ht="79.5" customHeight="1">
+      <c r="A31" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B31" s="13" t="d">
         <v>2026-05-06T00:00:00.000Z</v>
       </c>
-      <c r="C30" s="14" t="str">
+      <c r="C31" s="14" t="str">
         <v>煤炭智能开采与岩层控制全国重点实验室（北京；具体依托机构待核，沈阳化工为转载单位）·煤炭智能开采与岩层控制全国重点实验室</v>
       </c>
-      <c r="D30" s="15" t="str">
+      <c r="D31" s="15" t="str">
         <v>机械臂—底座耦合振动、末端自适应定位（依托机构尚待确认）</v>
       </c>
-      <c r="E30" s="15" t="str">
+      <c r="E31" s="15" t="str">
         <v>2026年度实验室设开放基金项目共计40项，其中重点项目4项，每项资助研究金额为45-65万元；
 一般项目36项，每项资助研究金额为15-25万元。</v>
-      </c>
-      <c r="F30" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="31" ht="66" customHeight="1">
-      <c r="A31" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B31" s="13" t="d">
-        <v>2026-08-20T00:00:00.000Z</v>
-      </c>
-      <c r="C31" s="14" t="str">
-        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
-      </c>
-      <c r="D31" s="15" t="str">
-        <v>自主无人系统及机器人研究</v>
-      </c>
-      <c r="E31" s="15" t="str">
-        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F31" s="16" t="str">
         <v>公告</v>
@@ -42501,16 +43134,16 @@
         <v>已截止</v>
       </c>
       <c r="B32" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-08-20T00:00:00.000Z</v>
       </c>
       <c r="C32" s="14" t="str">
-        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
+        <v>北京理工大学、同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D32" s="15" t="str">
-        <v>无人越野平台世界模型、具身感知与控制</v>
+        <v>自主无人系统及机器人研究</v>
       </c>
       <c r="E32" s="15" t="str">
-        <v>重点20—30万元、一般5—10万元</v>
+        <v>一般5—10万元、重点10—20万元</v>
       </c>
       <c r="F32" s="16" t="str">
         <v>公告</v>
@@ -42521,16 +43154,16 @@
         <v>已截止</v>
       </c>
       <c r="B33" s="13" t="d">
-        <v>2026-04-10T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C33" s="14" t="str">
-        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）·建筑钢结构智能制造技术兵团重点实验室</v>
+        <v>北京·先进越野系统技术全国重点实验室·2026年度对外开放基金</v>
       </c>
       <c r="D33" s="15" t="str">
-        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
+        <v>无人越野平台世界模型、具身感知与控制</v>
       </c>
       <c r="E33" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>重点20—30万元、一般5—10万元</v>
       </c>
       <c r="F33" s="16" t="str">
         <v>公告</v>
@@ -42541,16 +43174,16 @@
         <v>已截止</v>
       </c>
       <c r="B34" s="13" t="d">
-        <v>2026-09-20T00:00:00.000Z</v>
+        <v>2026-04-10T00:00:00.000Z</v>
       </c>
       <c r="C34" s="14" t="str">
-        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
+        <v>新疆天福泰钢结构有限公司（与北京化工大学联合共建）·建筑钢结构智能制造技术兵团重点实验室</v>
       </c>
       <c r="D34" s="15" t="str">
-        <v>平台具身智能与异构智能体协同</v>
+        <v>钢结构制造机器人喷涂、焊接与自适应装配</v>
       </c>
       <c r="E34" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>不超过2万元</v>
       </c>
       <c r="F34" s="16" t="str">
         <v>公告</v>
@@ -42561,16 +43194,16 @@
         <v>已截止</v>
       </c>
       <c r="B35" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2026-09-20T00:00:00.000Z</v>
       </c>
       <c r="C35" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室</v>
+        <v>西北工业大学·空天地海一体化大数据应用技术国家工程实验室</v>
       </c>
       <c r="D35" s="15" t="str">
-        <v>工业机器人传动、机电耦合与高端装备传动</v>
+        <v>平台具身智能与异构智能体协同</v>
       </c>
       <c r="E35" s="15" t="str">
-        <v>面上5—8万元。</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F35" s="16" t="str">
         <v>公告</v>
@@ -42581,16 +43214,16 @@
         <v>已截止</v>
       </c>
       <c r="B36" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C36" s="14" t="str">
-        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室</v>
       </c>
       <c r="D36" s="15" t="str">
-        <v>具身智能世界模型与开放环境视觉感知</v>
+        <v>工业机器人传动、机电耦合与高端装备传动</v>
       </c>
       <c r="E36" s="15" t="str">
-        <v>3万元</v>
+        <v>面上5—8万元。</v>
       </c>
       <c r="F36" s="16" t="str">
         <v>公告</v>
@@ -42601,16 +43234,16 @@
         <v>已截止</v>
       </c>
       <c r="B37" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C37" s="14" t="str">
-        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
+        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
       </c>
       <c r="D37" s="15" t="str">
-        <v>山区建造装备及机器人</v>
+        <v>具身智能世界模型与开放环境视觉感知</v>
       </c>
       <c r="E37" s="15" t="str">
-        <v>每项6万元。</v>
+        <v>3万元</v>
       </c>
       <c r="F37" s="16" t="str">
         <v>公告</v>
@@ -42621,16 +43254,16 @@
         <v>已截止</v>
       </c>
       <c r="B38" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C38" s="14" t="str">
-        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
+        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
       </c>
       <c r="D38" s="15" t="str">
-        <v>桥梁检测机器人与无人巡检装备</v>
+        <v>山区建造装备及机器人</v>
       </c>
       <c r="E38" s="15" t="str">
-        <v>5—10万元</v>
+        <v>每项6万元。</v>
       </c>
       <c r="F38" s="16" t="str">
         <v>公告</v>
@@ -42641,17 +43274,16 @@
         <v>已截止</v>
       </c>
       <c r="B39" s="13" t="d">
-        <v>2026-09-01T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C39" s="14" t="str">
-        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
+        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
       </c>
       <c r="D39" s="15" t="str">
-        <v>工业机器人及智能产线运维、故障预测与控制</v>
+        <v>桥梁检测机器人与无人巡检装备</v>
       </c>
       <c r="E39" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F39" s="16" t="str">
         <v>公告</v>
@@ -42662,13 +43294,13 @@
         <v>已截止</v>
       </c>
       <c r="B40" s="13" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-09-01T00:00:00.000Z</v>
       </c>
       <c r="C40" s="14" t="str">
-        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
+        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
       </c>
       <c r="D40" s="15" t="str">
-        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
+        <v>工业机器人及智能产线运维、故障预测与控制</v>
       </c>
       <c r="E40" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -42683,13 +43315,13 @@
         <v>已截止</v>
       </c>
       <c r="B41" s="13" t="d">
-        <v>2025-02-28T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="C41" s="14" t="str">
-        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
+        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
       </c>
       <c r="D41" s="15" t="str">
-        <v>重载机器人减速器、直驱电机及关键部件</v>
+        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
       </c>
       <c r="E41" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -42704,16 +43336,17 @@
         <v>已截止</v>
       </c>
       <c r="B42" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-02-28T00:00:00.000Z</v>
       </c>
       <c r="C42" s="14" t="str">
-        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
+        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
       </c>
       <c r="D42" s="15" t="str">
-        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
+        <v>重载机器人减速器、直驱电机及关键部件</v>
       </c>
       <c r="E42" s="15" t="str">
-        <v>重点20万元；一般10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F42" s="16" t="str">
         <v>公告</v>
@@ -42724,16 +43357,16 @@
         <v>已截止</v>
       </c>
       <c r="B43" s="13" t="d">
-        <v>2026-06-14T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C43" s="14" t="str">
-        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
+        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
       </c>
       <c r="D43" s="15" t="str">
-        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
+        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
       </c>
       <c r="E43" s="15" t="str">
-        <v>10万元</v>
+        <v>重点20万元；一般10万元</v>
       </c>
       <c r="F43" s="16" t="str">
         <v>公告</v>
@@ -42744,16 +43377,16 @@
         <v>已截止</v>
       </c>
       <c r="B44" s="13" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2026-06-14T00:00:00.000Z</v>
       </c>
       <c r="C44" s="14" t="str">
-        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
+        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
       </c>
       <c r="D44" s="15" t="str">
-        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
+        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>其他一般≤10万、重点≤15万</v>
+        <v>10万元</v>
       </c>
       <c r="F44" s="16" t="str">
         <v>公告</v>
@@ -42764,16 +43397,16 @@
         <v>已截止</v>
       </c>
       <c r="B45" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-09-24T00:00:00.000Z</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
+        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
+        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
       </c>
       <c r="E45" s="15" t="str">
-        <v>10—15万元</v>
+        <v>其他一般≤10万、重点≤15万</v>
       </c>
       <c r="F45" s="16" t="str">
         <v>公告</v>
@@ -42784,16 +43417,16 @@
         <v>已截止</v>
       </c>
       <c r="B46" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
+        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
+        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>3万元（首拨1万元，中期2万元）</v>
+        <v>10—15万元</v>
       </c>
       <c r="F46" s="16" t="str">
         <v>公告</v>
@@ -42804,17 +43437,16 @@
         <v>已截止</v>
       </c>
       <c r="B47" s="13" t="d">
-        <v>2022-10-30T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
+        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
+        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>已核官方2022历史公告：5万元/项；
-未取得2026正式指南，不将历史额度视为当期额度。</v>
+        <v>3万元（首拨1万元，中期2万元）</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
@@ -42825,16 +43457,17 @@
         <v>已截止</v>
       </c>
       <c r="B48" s="13" t="d">
-        <v>2022-11-04T00:00:00.000Z</v>
+        <v>2022-10-30T00:00:00.000Z</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
+        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
+        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>一般2万元；重点4—6万元</v>
+        <v>已核官方2022历史公告：5万元/项；
+未取得2026正式指南，不将历史额度视为当期额度。</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
@@ -42845,16 +43478,16 @@
         <v>已截止</v>
       </c>
       <c r="B49" s="13" t="d">
-        <v>2023-07-30T00:00:00.000Z</v>
+        <v>2022-11-04T00:00:00.000Z</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
+        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
+        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>拟资助8—10项；单项金额未载</v>
+        <v>一般2万元；重点4—6万元</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
@@ -42865,16 +43498,16 @@
         <v>已截止</v>
       </c>
       <c r="B50" s="13" t="d">
-        <v>2024-09-30T00:00:00.000Z</v>
+        <v>2023-07-30T00:00:00.000Z</v>
       </c>
       <c r="C50" s="14" t="str">
-        <v>南昌大学·智能机器人江西省重点实验室</v>
+        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
       </c>
       <c r="D50" s="15" t="str">
-        <v>智能机器人机构、感知与控制</v>
+        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
       </c>
       <c r="E50" s="15" t="str">
-        <v>重点3万元、一般2万元（2024年度）</v>
+        <v>拟资助8—10项；单项金额未载</v>
       </c>
       <c r="F50" s="16" t="str">
         <v>公告</v>
@@ -42885,16 +43518,16 @@
         <v>已截止</v>
       </c>
       <c r="B51" s="13" t="d">
-        <v>2025-03-31T00:00:00.000Z</v>
+        <v>2024-09-30T00:00:00.000Z</v>
       </c>
       <c r="C51" s="14" t="str">
-        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
+        <v>南昌大学·智能机器人江西省重点实验室</v>
       </c>
       <c r="D51" s="15" t="str">
-        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
+        <v>智能机器人机构、感知与控制</v>
       </c>
       <c r="E51" s="15" t="str">
-        <v>2—3万元/项左右</v>
+        <v>重点3万元、一般2万元（2024年度）</v>
       </c>
       <c r="F51" s="16" t="str">
         <v>公告</v>
@@ -42905,16 +43538,16 @@
         <v>已截止</v>
       </c>
       <c r="B52" s="13" t="d">
-        <v>2025-04-25T00:00:00.000Z</v>
+        <v>2025-03-31T00:00:00.000Z</v>
       </c>
       <c r="C52" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
       </c>
       <c r="D52" s="15" t="str">
-        <v>仿生机器人、新型驱动与感知及仿生装备</v>
+        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
       </c>
       <c r="E52" s="15" t="str">
-        <v>5万元</v>
+        <v>2—3万元/项左右</v>
       </c>
       <c r="F52" s="16" t="str">
         <v>公告</v>
@@ -42925,16 +43558,16 @@
         <v>已截止</v>
       </c>
       <c r="B53" s="13" t="d">
-        <v>2025-04-30T00:00:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C53" s="14" t="str">
-        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D53" s="15" t="str">
-        <v>共融机器人控制、复杂智能体系统协同与控制</v>
+        <v>仿生机器人、新型驱动与感知及仿生装备</v>
       </c>
       <c r="E53" s="15" t="str">
-        <v>评审确定</v>
+        <v>5万元</v>
       </c>
       <c r="F53" s="16" t="str">
         <v>公告</v>
@@ -42945,16 +43578,16 @@
         <v>已截止</v>
       </c>
       <c r="B54" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C54" s="14" t="str">
-        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
+        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
       </c>
       <c r="D54" s="15" t="str">
-        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
+        <v>共融机器人控制、复杂智能体系统协同与控制</v>
       </c>
       <c r="E54" s="15" t="str">
-        <v>5万元</v>
+        <v>评审确定</v>
       </c>
       <c r="F54" s="16" t="str">
         <v>公告</v>
@@ -42965,16 +43598,16 @@
         <v>已截止</v>
       </c>
       <c r="B55" s="13" t="d">
-        <v>2025-09-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C55" s="14" t="str">
-        <v>同济大学·自主智能无人系统全国重点实验室</v>
+        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
       </c>
       <c r="D55" s="15" t="str">
-        <v>自主智能无人系统与机器人感知、决策、控制</v>
+        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
       </c>
       <c r="E55" s="15" t="str">
-        <v>一般5—10万元、重点20—30万元</v>
+        <v>5万元</v>
       </c>
       <c r="F55" s="16" t="str">
         <v>公告</v>
@@ -42985,17 +43618,16 @@
         <v>已截止</v>
       </c>
       <c r="B56" s="13" t="d">
-        <v>2025-10-31T00:00:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C56" s="14" t="str">
-        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
+        <v>同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D56" s="15" t="str">
-        <v>机器人技术与系统、机器人学习、感知与控制</v>
+        <v>自主智能无人系统与机器人感知、决策、控制</v>
       </c>
       <c r="E56" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>一般5—10万元、重点20—30万元</v>
       </c>
       <c r="F56" s="16" t="str">
         <v>公告</v>
@@ -43006,17 +43638,17 @@
         <v>已截止</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2025-11-03T00:00:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
+        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>智能机器人感知、控制与系统</v>
+        <v>机器人技术与系统、机器人学习、感知与控制</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>校外开放基金1万元/项，拟5项；
-校内创新基金不同计划</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
@@ -43027,16 +43659,17 @@
         <v>已截止</v>
       </c>
       <c r="B58" s="13" t="d">
-        <v>2025-11-07T00:00:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C58" s="14" t="str">
-        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D58" s="15" t="str">
-        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
+        <v>智能机器人感知、控制与系统</v>
       </c>
       <c r="E58" s="15" t="str">
-        <v>2万元</v>
+        <v>校外开放基金1万元/项，拟5项；
+校内创新基金不同计划</v>
       </c>
       <c r="F58" s="16" t="str">
         <v>公告</v>
@@ -43047,16 +43680,16 @@
         <v>已截止</v>
       </c>
       <c r="B59" s="13" t="d">
-        <v>2025-11-14T00:00:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>上海交通大学·机械系统与振动全国重点实验室</v>
+        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>机器人设计、自主学习与神经接口</v>
+        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>10—15万元</v>
+        <v>2万元</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
@@ -43067,16 +43700,16 @@
         <v>已截止</v>
       </c>
       <c r="B60" s="13" t="d">
-        <v>2025-11-21T00:00:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
+        <v>上海交通大学·机械系统与振动全国重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>机器人视觉相关计算与随机数学方法</v>
+        <v>机器人设计、自主学习与神经接口</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>1—2万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
@@ -43087,16 +43720,16 @@
         <v>已截止</v>
       </c>
       <c r="B61" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C61" s="14" t="str">
-        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
+        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
       </c>
       <c r="D61" s="15" t="str">
-        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
+        <v>机器人视觉相关计算与随机数学方法</v>
       </c>
       <c r="E61" s="15" t="str">
-        <v>不超过3万元</v>
+        <v>1—2万元</v>
       </c>
       <c r="F61" s="16" t="str">
         <v>公告</v>
@@ -43107,16 +43740,16 @@
         <v>已截止</v>
       </c>
       <c r="B62" s="13" t="d">
-        <v>2025-12-20T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C62" s="14" t="str">
-        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
+        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
       </c>
       <c r="D62" s="15" t="str">
-        <v>山地农业机器人、果实收获视觉与智能农机</v>
+        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
       </c>
       <c r="E62" s="15" t="str">
-        <v>不超过5万元</v>
+        <v>不超过3万元</v>
       </c>
       <c r="F62" s="16" t="str">
         <v>公告</v>
@@ -43127,16 +43760,16 @@
         <v>已截止</v>
       </c>
       <c r="B63" s="13" t="d">
-        <v>2025-12-31T00:00:00.000Z</v>
+        <v>2025-12-20T00:00:00.000Z</v>
       </c>
       <c r="C63" s="14" t="str">
-        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
+        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
       </c>
       <c r="D63" s="15" t="str">
-        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
+        <v>山地农业机器人、果实收获视觉与智能农机</v>
       </c>
       <c r="E63" s="15" t="str">
-        <v>重点5万元、一般3万元</v>
+        <v>不超过5万元</v>
       </c>
       <c r="F63" s="16" t="str">
         <v>公告</v>
@@ -43147,16 +43780,16 @@
         <v>已截止</v>
       </c>
       <c r="B64" s="13" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C64" s="14" t="str">
-        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
+        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
       </c>
       <c r="D64" s="15" t="str">
-        <v>深海无人潜航装备与智能控制</v>
+        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
       </c>
       <c r="E64" s="15" t="str">
-        <v>不超过10万元</v>
+        <v>重点5万元、一般3万元</v>
       </c>
       <c r="F64" s="16" t="str">
         <v>公告</v>
@@ -43167,16 +43800,16 @@
         <v>已截止</v>
       </c>
       <c r="B65" s="13" t="d">
-        <v>2026-01-31T00:00:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C65" s="14" t="str">
-        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
+        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
       </c>
       <c r="D65" s="15" t="str">
-        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
+        <v>深海无人潜航装备与智能控制</v>
       </c>
       <c r="E65" s="15" t="str">
-        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
+        <v>不超过10万元</v>
       </c>
       <c r="F65" s="16" t="str">
         <v>公告</v>
@@ -43187,16 +43820,16 @@
         <v>已截止</v>
       </c>
       <c r="B66" s="13" t="d">
-        <v>2026-03-10T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C66" s="14" t="str">
-        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
+        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
       </c>
       <c r="D66" s="15" t="str">
-        <v>工业机器人与柔性制造产线集成</v>
+        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
       </c>
       <c r="E66" s="15" t="str">
-        <v>4万元</v>
+        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
       </c>
       <c r="F66" s="16" t="str">
         <v>公告</v>
@@ -43207,16 +43840,16 @@
         <v>已截止</v>
       </c>
       <c r="B67" s="13" t="d">
-        <v>2026-03-20T00:00:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C67" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室</v>
+        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
       </c>
       <c r="D67" s="15" t="str">
-        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
+        <v>工业机器人与柔性制造产线集成</v>
       </c>
       <c r="E67" s="15" t="str">
-        <v>单项不超过10万元</v>
+        <v>4万元</v>
       </c>
       <c r="F67" s="16" t="str">
         <v>公告</v>
@@ -43227,16 +43860,16 @@
         <v>已截止</v>
       </c>
       <c r="B68" s="13" t="d">
-        <v>2026-04-15T00:00:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C68" s="14" t="str">
-        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室</v>
       </c>
       <c r="D68" s="15" t="str">
-        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
+        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
       </c>
       <c r="E68" s="15" t="str">
-        <v>一般5—8万元；重点20万元</v>
+        <v>单项不超过10万元</v>
       </c>
       <c r="F68" s="16" t="str">
         <v>公告</v>
@@ -43247,16 +43880,16 @@
         <v>已截止</v>
       </c>
       <c r="B69" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C69" s="14" t="str">
-        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
+        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
       </c>
       <c r="D69" s="15" t="str">
-        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
+        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
       </c>
       <c r="E69" s="15" t="str">
-        <v>5万元</v>
+        <v>一般5—8万元；重点20万元</v>
       </c>
       <c r="F69" s="16" t="str">
         <v>公告</v>
@@ -43270,14 +43903,13 @@
         <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C70" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
+        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
       </c>
       <c r="D70" s="15" t="str">
-        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
+        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
       </c>
       <c r="E70" s="15" t="str">
-        <v>单项原则上不超过10万元；
-100万元是本批次总额，不是单项额度。</v>
+        <v>5万元</v>
       </c>
       <c r="F70" s="16" t="str">
         <v>公告</v>
@@ -43288,16 +43920,17 @@
         <v>已截止</v>
       </c>
       <c r="B71" s="13" t="d">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C71" s="14" t="str">
-        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
       </c>
       <c r="D71" s="15" t="str">
-        <v>无人系统多源感知、导航与控制</v>
+        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
       </c>
       <c r="E71" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>单项原则上不超过10万元；
+100万元是本批次总额，不是单项额度。</v>
       </c>
       <c r="F71" s="16" t="str">
         <v>公告</v>
@@ -43308,16 +43941,16 @@
         <v>已截止</v>
       </c>
       <c r="B72" s="13" t="d">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C72" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
       </c>
       <c r="D72" s="15" t="str">
-        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
+        <v>无人系统多源感知、导航与控制</v>
       </c>
       <c r="E72" s="15" t="str">
-        <v>5万元/项；拟8项</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F72" s="16" t="str">
         <v>公告</v>
@@ -43328,16 +43961,16 @@
         <v>已截止</v>
       </c>
       <c r="B73" s="13" t="d">
-        <v>2026-04-30T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C73" s="14" t="str">
-        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D73" s="15" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
       </c>
       <c r="E73" s="15" t="str">
-        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
+        <v>5万元/项；拟8项</v>
       </c>
       <c r="F73" s="16" t="str">
         <v>公告</v>
@@ -43351,13 +43984,13 @@
         <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C74" s="14" t="str">
-        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
+        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
       </c>
       <c r="D74" s="15" t="str">
-        <v>警用智能机器人与协同任务</v>
+        <v>智能无人系统感知、规划与控制</v>
       </c>
       <c r="E74" s="15" t="str">
-        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
+        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="F74" s="16" t="str">
         <v>公告</v>
@@ -43368,16 +44001,16 @@
         <v>已截止</v>
       </c>
       <c r="B75" s="13" t="d">
-        <v>2026-05-06T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C75" s="14" t="str">
-        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
+        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
       </c>
       <c r="D75" s="15" t="str">
-        <v>具身智能（仅保留正式指南第7项方向）</v>
+        <v>警用智能机器人与协同任务</v>
       </c>
       <c r="E75" s="15" t="str">
-        <v>10—15万元</v>
+        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="F75" s="16" t="str">
         <v>公告</v>
@@ -43388,16 +44021,16 @@
         <v>已截止</v>
       </c>
       <c r="B76" s="13" t="d">
-        <v>2026-05-14T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C76" s="14" t="str">
-        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
+        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
       </c>
       <c r="D76" s="15" t="str">
-        <v>具身机器人磨削、抛光及加工技能</v>
+        <v>具身智能（仅保留正式指南第7项方向）</v>
       </c>
       <c r="E76" s="15" t="str">
-        <v>一般1—2万元、重点3—5万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F76" s="16" t="str">
         <v>公告</v>
@@ -43408,16 +44041,16 @@
         <v>已截止</v>
       </c>
       <c r="B77" s="13" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-14T00:00:00.000Z</v>
       </c>
       <c r="C77" s="14" t="str">
-        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
+        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
       </c>
       <c r="D77" s="15" t="str">
-        <v>前沿交叉方向中的手术机器人应用与验证</v>
+        <v>具身机器人磨削、抛光及加工技能</v>
       </c>
       <c r="E77" s="15" t="str">
-        <v>4万元</v>
+        <v>一般1—2万元、重点3—5万元</v>
       </c>
       <c r="F77" s="16" t="str">
         <v>公告</v>
@@ -43428,16 +44061,16 @@
         <v>已截止</v>
       </c>
       <c r="B78" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C78" s="14" t="str">
-        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
+        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
       </c>
       <c r="D78" s="15" t="str">
-        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
+        <v>前沿交叉方向中的手术机器人应用与验证</v>
       </c>
       <c r="E78" s="15" t="str">
-        <v>不超过1万元</v>
+        <v>4万元</v>
       </c>
       <c r="F78" s="16" t="str">
         <v>公告</v>
@@ -43448,42 +44081,42 @@
         <v>已截止</v>
       </c>
       <c r="B79" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C79" s="14" t="str">
-        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
+        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
       </c>
       <c r="D79" s="15" t="str">
-        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
+        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
       </c>
       <c r="E79" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>不超过1万元</v>
       </c>
       <c r="F79" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="80" ht="72" customHeight="1">
+    <row r="80" ht="66" customHeight="1">
       <c r="A80" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B80" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C80" s="14" t="str">
-        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
+        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
       </c>
       <c r="D80" s="15" t="str">
-        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
+        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
       </c>
       <c r="E80" s="15" t="str">
-        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F80" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="81" ht="66" customHeight="1">
+    <row r="81" ht="72" customHeight="1">
       <c r="A81" s="18" t="str">
         <v>已截止</v>
       </c>
@@ -43491,13 +44124,13 @@
         <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C81" s="14" t="str">
-        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
+        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
       </c>
       <c r="D81" s="15" t="str">
-        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
+        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
       </c>
       <c r="E81" s="15" t="str">
-        <v>原则5万元/项；可按评审增加，上限未载</v>
+        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
       </c>
       <c r="F81" s="16" t="str">
         <v>公告</v>
@@ -43508,16 +44141,16 @@
         <v>已截止</v>
       </c>
       <c r="B82" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C82" s="14" t="str">
-        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
+        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
       </c>
       <c r="D82" s="15" t="str">
-        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
+        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
       </c>
       <c r="E82" s="15" t="str">
-        <v>5万元/项；专项拟2项</v>
+        <v>原则5万元/项；可按评审增加，上限未载</v>
       </c>
       <c r="F82" s="16" t="str">
         <v>公告</v>
@@ -43528,16 +44161,16 @@
         <v>已截止</v>
       </c>
       <c r="B83" s="13" t="d">
-        <v>2026-07-12T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C83" s="14" t="str">
-        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
+        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
       </c>
       <c r="D83" s="15" t="str">
-        <v>无人机轨迹与协同、自主采样探测装备</v>
+        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
       </c>
       <c r="E83" s="15" t="str">
-        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
+        <v>5万元/项；专项拟2项</v>
       </c>
       <c r="F83" s="16" t="str">
         <v>公告</v>
@@ -43548,16 +44181,16 @@
         <v>已截止</v>
       </c>
       <c r="B84" s="13" t="d">
-        <v>2026-07-19T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C84" s="14" t="str">
-        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
+        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
       </c>
       <c r="D84" s="15" t="str">
-        <v>具身智能传感、闭环感知与人机交互意图识别</v>
+        <v>无人机轨迹与协同、自主采样探测装备</v>
       </c>
       <c r="E84" s="15" t="str">
-        <v>10万元</v>
+        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
       </c>
       <c r="F84" s="16" t="str">
         <v>公告</v>
@@ -43568,16 +44201,16 @@
         <v>已截止</v>
       </c>
       <c r="B85" s="13" t="d">
-        <v>2026-07-25T00:00:00.000Z</v>
+        <v>2026-07-19T00:00:00.000Z</v>
       </c>
       <c r="C85" s="14" t="str">
-        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
+        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
       </c>
       <c r="D85" s="15" t="str">
-        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
+        <v>具身智能传感、闭环感知与人机交互意图识别</v>
       </c>
       <c r="E85" s="15" t="str">
-        <v>2—4万元</v>
+        <v>10万元</v>
       </c>
       <c r="F85" s="16" t="str">
         <v>公告</v>
@@ -43588,16 +44221,16 @@
         <v>已截止</v>
       </c>
       <c r="B86" s="13" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-07-25T00:00:00.000Z</v>
       </c>
       <c r="C86" s="14" t="str">
-        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
+        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
       </c>
       <c r="D86" s="15" t="str">
-        <v>智能机器人信息感知、多源融合与控制</v>
+        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
       </c>
       <c r="E86" s="15" t="str">
-        <v>约2万元</v>
+        <v>2—4万元</v>
       </c>
       <c r="F86" s="16" t="str">
         <v>公告</v>
@@ -43608,16 +44241,16 @@
         <v>已截止</v>
       </c>
       <c r="B87" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C87" s="14" t="str">
-        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
+        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
       </c>
       <c r="D87" s="15" t="str">
-        <v>机器人集成与医疗康复智能制造装备</v>
+        <v>智能机器人信息感知、多源融合与控制</v>
       </c>
       <c r="E87" s="15" t="str">
-        <v>一般2万元、重点3万元</v>
+        <v>约2万元</v>
       </c>
       <c r="F87" s="16" t="str">
         <v>公告</v>
@@ -43631,13 +44264,13 @@
         <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C88" s="14" t="str">
-        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
+        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
       </c>
       <c r="D88" s="15" t="str">
-        <v>桥梁与水下缺陷无人机器人检测</v>
+        <v>机器人集成与医疗康复智能制造装备</v>
       </c>
       <c r="E88" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>一般2万元、重点3万元</v>
       </c>
       <c r="F88" s="16" t="str">
         <v>公告</v>
@@ -43648,16 +44281,16 @@
         <v>已截止</v>
       </c>
       <c r="B89" s="13" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C89" s="14" t="str">
-        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
+        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
       </c>
       <c r="D89" s="15" t="str">
-        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
+        <v>桥梁与水下缺陷无人机器人检测</v>
       </c>
       <c r="E89" s="15" t="str">
-        <v>5万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F89" s="16" t="str">
         <v>公告</v>
@@ -43668,16 +44301,16 @@
         <v>已截止</v>
       </c>
       <c r="B90" s="13" t="d">
-        <v>2026-08-30T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C90" s="14" t="str">
-        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
+        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
       </c>
       <c r="D90" s="15" t="str">
-        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
+        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
       </c>
       <c r="E90" s="15" t="str">
-        <v>重点5万元；一般2万元；共6—8项</v>
+        <v>5万元</v>
       </c>
       <c r="F90" s="16" t="str">
         <v>公告</v>
@@ -43688,16 +44321,16 @@
         <v>已截止</v>
       </c>
       <c r="B91" s="13" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-30T00:00:00.000Z</v>
       </c>
       <c r="C91" s="14" t="str">
-        <v>四川警察学院·智能警务四川省重点实验室</v>
+        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
       </c>
       <c r="D91" s="15" t="str">
-        <v>无人机、车辆与机器狗异构协同及应急救援</v>
+        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
       </c>
       <c r="E91" s="15" t="str">
-        <v>重点15万元、一般10万元、青年5万元</v>
+        <v>重点5万元；一般2万元；共6—8项</v>
       </c>
       <c r="F91" s="16" t="str">
         <v>公告</v>
@@ -43708,17 +44341,16 @@
         <v>已截止</v>
       </c>
       <c r="B92" s="13" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C92" s="14" t="str">
-        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
+        <v>四川警察学院·智能警务四川省重点实验室</v>
       </c>
       <c r="D92" s="15" t="str">
-        <v>特种机器人多源感知、轨迹与动力学控制</v>
+        <v>无人机、车辆与机器狗异构协同及应急救援</v>
       </c>
       <c r="E92" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>重点15万元、一般10万元、青年5万元</v>
       </c>
       <c r="F92" s="16" t="str">
         <v>公告</v>
@@ -43729,16 +44361,17 @@
         <v>已截止</v>
       </c>
       <c r="B93" s="13" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C93" s="14" t="str">
-        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
       </c>
       <c r="D93" s="15" t="str">
-        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+        <v>特种机器人多源感知、轨迹与动力学控制</v>
       </c>
       <c r="E93" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F93" s="16" t="str">
         <v>公告</v>
@@ -43749,40 +44382,39 @@
         <v>已截止</v>
       </c>
       <c r="B94" s="13" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="C94" s="14" t="str">
+        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+      </c>
+      <c r="D94" s="15" t="str">
+        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+      </c>
+      <c r="E94" s="15" t="str">
+        <v>不超过2万元</v>
+      </c>
+      <c r="F94" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="95" ht="66" customHeight="1">
+      <c r="A95" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B95" s="13" t="d">
         <v>2026-09-27T00:00:00.000Z</v>
       </c>
-      <c r="C94" s="14" t="str">
+      <c r="C95" s="14" t="str">
         <v>云南大学·云南省智能系统与计算重点实验室</v>
       </c>
-      <c r="D94" s="15" t="str">
+      <c r="D95" s="15" t="str">
         <v>低空无人系统集群协同（仅保留具体无人装备方向）</v>
       </c>
-      <c r="E94" s="15" t="str">
+      <c r="E95" s="15" t="str">
         <v>重点≤8万元；
 一般≤2万元；
 定向1万元。</v>
       </c>
-      <c r="F94" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="95" ht="66" customHeight="1">
-      <c r="A95" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B95" s="13" t="d">
-        <v>2026-10-05T00:00:00.000Z</v>
-      </c>
-      <c r="C95" s="14" t="str">
-        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
-      </c>
-      <c r="D95" s="15" t="str">
-        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
-      </c>
-      <c r="E95" s="15" t="str">
-        <v>重点60—100万元；
-一般15—20万元</v>
-      </c>
       <c r="F95" s="16" t="str">
         <v>公告</v>
       </c>
@@ -43792,16 +44424,17 @@
         <v>已截止</v>
       </c>
       <c r="B96" s="13" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-05T00:00:00.000Z</v>
       </c>
       <c r="C96" s="14" t="str">
-        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
+        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
       </c>
       <c r="D96" s="15" t="str">
-        <v>机器人遥操作、双臂操作与人机协同</v>
+        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
       </c>
       <c r="E96" s="15" t="str">
-        <v>公告未公布统一金额，评审确定。</v>
+        <v>重点60—100万元；
+一般15—20万元</v>
       </c>
       <c r="F96" s="16" t="str">
         <v>公告</v>
@@ -43815,13 +44448,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C97" s="14" t="str">
-        <v>中北大学·微纳器件与系统教育部重点实验室</v>
+        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
       </c>
       <c r="D97" s="15" t="str">
-        <v>微型机器人及微纳执行器、精密定位</v>
+        <v>机器人遥操作、双臂操作与人机协同</v>
       </c>
       <c r="E97" s="15" t="str">
-        <v>2—4万元</v>
+        <v>公告未公布统一金额，评审确定。</v>
       </c>
       <c r="F97" s="16" t="str">
         <v>公告</v>
@@ -43835,13 +44468,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C98" s="14" t="str">
-        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
+        <v>中北大学·微纳器件与系统教育部重点实验室</v>
       </c>
       <c r="D98" s="15" t="str">
-        <v>机器人机械臂抓取、路径规划与自主导航</v>
+        <v>微型机器人及微纳执行器、精密定位</v>
       </c>
       <c r="E98" s="15" t="str">
-        <v>一般2万元；重点4万元（以评审为准）</v>
+        <v>2—4万元</v>
       </c>
       <c r="F98" s="16" t="str">
         <v>公告</v>
@@ -43855,13 +44488,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C99" s="14" t="str">
-        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
+        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
       </c>
       <c r="D99" s="15" t="str">
-        <v>无人平台智能探测与多源感知</v>
+        <v>机器人机械臂抓取、路径规划与自主导航</v>
       </c>
       <c r="E99" s="15" t="str">
-        <v>2—4万元/项，拟5—8项</v>
+        <v>一般2万元；重点4万元（以评审为准）</v>
       </c>
       <c r="F99" s="16" t="str">
         <v>公告</v>
@@ -43875,36 +44508,36 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C100" s="14" t="str">
-        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
       </c>
       <c r="D100" s="15" t="str">
-        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+        <v>无人平台智能探测与多源感知</v>
       </c>
       <c r="E100" s="15" t="str">
-        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+        <v>2—4万元/项，拟5—8项</v>
       </c>
       <c r="F100" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="101" ht="96" customHeight="1">
-      <c r="A101" t="str" s="18">
+    <row r="101" ht="66" customHeight="1">
+      <c r="A101" s="18" t="str">
         <v>已截止</v>
       </c>
-      <c r="B101" t="n" s="13">
-        <v>46295</v>
-      </c>
-      <c r="C101" t="str" s="14">
-        <v>上海交通大学·海洋工程全国重点实验室</v>
-      </c>
-      <c r="D101" t="str" s="15">
-        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
-      </c>
-      <c r="E101" t="str" s="15">
-        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
-      </c>
-      <c r="F101" t="str" s="16">
-        <v>官方公告</v>
+      <c r="B101" s="13" t="d">
+        <v>2026-10-08T00:00:00.000Z</v>
+      </c>
+      <c r="C101" s="14" t="str">
+        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+      </c>
+      <c r="D101" s="15" t="str">
+        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+      </c>
+      <c r="E101" s="15" t="str">
+        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+      </c>
+      <c r="F101" s="16" t="str">
+        <v>公告</v>
       </c>
     </row>
     <row r="102" ht="96" customHeight="1">
@@ -43912,16 +44545,16 @@
         <v>已截止</v>
       </c>
       <c r="B102" t="n" s="13">
-        <v>45503</v>
+        <v>46295</v>
       </c>
       <c r="C102" t="str" s="14">
-        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
+        <v>上海交通大学·海洋工程全国重点实验室</v>
       </c>
       <c r="D102" t="str" s="15">
-        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
+        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
       </c>
       <c r="E102" t="str" s="15">
-        <v>3万元/项；计划10项。</v>
+        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
       </c>
       <c r="F102" t="str" s="16">
         <v>官方公告</v>
@@ -43932,16 +44565,16 @@
         <v>已截止</v>
       </c>
       <c r="B103" t="n" s="13">
-        <v>46006</v>
+        <v>45503</v>
       </c>
       <c r="C103" t="str" s="14">
-        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
+        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
       </c>
       <c r="D103" t="str" s="15">
-        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
+        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
       </c>
       <c r="E103" t="str" s="15">
-        <v>正文未公开具体资助金额。</v>
+        <v>3万元/项；计划10项。</v>
       </c>
       <c r="F103" t="str" s="16">
         <v>官方公告</v>
@@ -43952,16 +44585,16 @@
         <v>已截止</v>
       </c>
       <c r="B104" t="n" s="13">
-        <v>46193</v>
+        <v>46006</v>
       </c>
       <c r="C104" t="str" s="14">
-        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
+        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
       <c r="D104" t="str" s="15">
-        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
+        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
       </c>
       <c r="E104" t="str" s="15">
-        <v>一般项目≤5万元/项；计划12项。</v>
+        <v>正文未公开具体资助金额。</v>
       </c>
       <c r="F104" t="str" s="16">
         <v>官方公告</v>
@@ -43972,16 +44605,16 @@
         <v>已截止</v>
       </c>
       <c r="B105" t="n" s="13">
-        <v>44434</v>
+        <v>46193</v>
       </c>
       <c r="C105" t="str" s="14">
-        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
       </c>
       <c r="D105" t="str" s="15">
-        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
       </c>
       <c r="E105" t="str" s="15">
-        <v>重点2万元/项；一般1万元/项。</v>
+        <v>一般项目≤5万元/项；计划12项。</v>
       </c>
       <c r="F105" t="str" s="16">
         <v>官方公告</v>
@@ -43992,58 +44625,78 @@
         <v>已截止</v>
       </c>
       <c r="B106" t="n" s="13">
-        <v>45163</v>
+        <v>44434</v>
       </c>
       <c r="C106" t="str" s="14">
-        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
       </c>
       <c r="D106" t="str" s="15">
-        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
       </c>
       <c r="E106" t="str" s="15">
-        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+        <v>重点2万元/项；一般1万元/项。</v>
       </c>
       <c r="F106" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="107" ht="102" customHeight="1">
+    <row r="107" ht="96" customHeight="1">
       <c r="A107" t="str" s="18">
         <v>已截止</v>
       </c>
       <c r="B107" t="n" s="13">
-        <v>45991</v>
+        <v>45163</v>
       </c>
       <c r="C107" t="str" s="14">
-        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
       </c>
       <c r="D107" t="str" s="15">
-        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
       </c>
       <c r="E107" t="str" s="15">
-        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
       </c>
       <c r="F107" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="108" ht="96" customHeight="1">
+    <row r="108" ht="102" customHeight="1">
       <c r="A108" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B108" t="n" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C108" t="str" s="14">
+        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+      </c>
+      <c r="D108" t="str" s="15">
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+      </c>
+      <c r="E108" t="str" s="15">
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+      </c>
+      <c r="F108" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="109" ht="96" customHeight="1">
+      <c r="A109" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B108" t="n" s="13">
+      <c r="B109" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C108" t="str" s="14">
+      <c r="C109" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D108" t="str" s="15">
+      <c r="D109" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E108" t="str" s="15">
+      <c r="E109" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F108" t="str" s="16">
+      <c r="F109" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -44059,8 +44712,8 @@
     <hyperlink ref="F5" ns1:id="Rff2d595907084ed9"/>
     <hyperlink ref="C6" location="'02项目完整详情'!A61"/>
     <hyperlink ref="F6" ns1:id="R840dfc7ac2ef4322"/>
-    <hyperlink ref="C40" location="'02项目完整详情'!A113"/>
-    <hyperlink ref="F40" ns1:id="Re902984ea1114a1f"/>
+    <hyperlink ref="C41" location="'02项目完整详情'!A113"/>
+    <hyperlink ref="F41" ns1:id="Re902984ea1114a1f"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A62"/>
     <hyperlink ref="F7" ns1:id="Ra6ff56d69fd14f0d"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A63"/>
@@ -44077,8 +44730,8 @@
     <hyperlink ref="F16" ns1:id="R5d6c0e16ca9148f1"/>
     <hyperlink ref="C17" location="'02项目完整详情'!A141"/>
     <hyperlink ref="F17" ns1:id="R29345038c30a4733"/>
-    <hyperlink ref="C41" location="'02项目完整详情'!A85"/>
-    <hyperlink ref="F41" ns1:id="R486c032b769d4524"/>
+    <hyperlink ref="C42" location="'02项目完整详情'!A85"/>
+    <hyperlink ref="F42" ns1:id="R486c032b769d4524"/>
     <hyperlink ref="C18" location="'02项目完整详情'!A99"/>
     <hyperlink ref="F18" ns1:id="R19ee0f6cf8d14ed3"/>
     <hyperlink ref="C19" location="'02项目完整详情'!A143"/>
@@ -44087,182 +44740,184 @@
     <hyperlink ref="F20" ns1:id="R83b69720fcfc4e60"/>
     <hyperlink ref="C21" location="'02项目完整详情'!A127"/>
     <hyperlink ref="F21" ns1:id="Ra979348b05084966"/>
-    <hyperlink ref="C23" location="'02项目完整详情'!A66"/>
-    <hyperlink ref="F23" ns1:id="R4dc201fc29cb4ab4"/>
-    <hyperlink ref="C42" location="'02项目完整详情'!A139"/>
-    <hyperlink ref="F42" ns1:id="Rf4dc98016cfb49fd"/>
-    <hyperlink ref="C24" location="'02项目完整详情'!A151"/>
-    <hyperlink ref="F24" ns1:id="R3d89872d06fd4b60"/>
-    <hyperlink ref="C25" location="'02项目完整详情'!A67"/>
-    <hyperlink ref="F25" ns1:id="R1e9b7d2bc63d4258"/>
-    <hyperlink ref="C43" location="'02项目完整详情'!A68"/>
-    <hyperlink ref="F43" ns1:id="R5d0261ffe45c4155"/>
-    <hyperlink ref="C26" location="'02项目完整详情'!A69"/>
-    <hyperlink ref="F26" ns1:id="Reeb11b878b934f2d"/>
-    <hyperlink ref="C27" location="'02项目完整详情'!A70"/>
-    <hyperlink ref="F27" ns1:id="R5b06defce5864a96"/>
-    <hyperlink ref="C28" location="'02项目完整详情'!A71"/>
-    <hyperlink ref="F28" ns1:id="Ra48afdb9842a4366"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A72"/>
-    <hyperlink ref="F44" ns1:id="Rb3b4681efcdd44d4"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A73"/>
-    <hyperlink ref="F45" ns1:id="R4f0b800598574b86"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A74"/>
-    <hyperlink ref="F46" ns1:id="R56697ca79cd54a14"/>
-    <hyperlink ref="C34" location="'02项目完整详情'!A75"/>
-    <hyperlink ref="F34" ns1:id="R0814a7680dde4f9a"/>
-    <hyperlink ref="C35" location="'02项目完整详情'!A76"/>
-    <hyperlink ref="F35" ns1:id="R3f222e6bf9fa46ec"/>
-    <hyperlink ref="C36" location="'02项目完整详情'!A77"/>
-    <hyperlink ref="F36" ns1:id="Rc66c2cf37bbc404d"/>
-    <hyperlink ref="C37" location="'02项目完整详情'!A78"/>
-    <hyperlink ref="F37" ns1:id="R90e03710dfe04e74"/>
-    <hyperlink ref="C38" location="'02项目完整详情'!A79"/>
-    <hyperlink ref="F38" ns1:id="R80f5129c1ee24096"/>
-    <hyperlink ref="C39" location="'02项目完整详情'!A80"/>
-    <hyperlink ref="F39" ns1:id="R6360db00742b45ec"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A81"/>
-    <hyperlink ref="F47" ns1:id="Rc4146f6376594d01"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A156"/>
-    <hyperlink ref="F48" ns1:id="R97ba6e4965084c76"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A155"/>
-    <hyperlink ref="F49" ns1:id="Rcbdc080795344925"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A83"/>
-    <hyperlink ref="F50" ns1:id="R9e6afd1b359743bb"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A154"/>
-    <hyperlink ref="F51" ns1:id="Rb320e0a5ad524836"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A86"/>
-    <hyperlink ref="F52" ns1:id="R42a660aaeb1d4c95"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A87"/>
-    <hyperlink ref="F53" ns1:id="R88784a2520864683"/>
-    <hyperlink ref="C29" location="'02项目完整详情'!A88"/>
-    <hyperlink ref="F29" ns1:id="Rcb8b33dae69a4731"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A89"/>
-    <hyperlink ref="F54" ns1:id="Rd5ea9c8442ca46ac"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A90"/>
-    <hyperlink ref="F55" ns1:id="R7734727212364cb2"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A91"/>
-    <hyperlink ref="F56" ns1:id="R78b8c8c0ca954ecb"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A92"/>
-    <hyperlink ref="F57" ns1:id="Rfdf5f46608d44776"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A93"/>
-    <hyperlink ref="F58" ns1:id="R82f06426c3d54976"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A94"/>
-    <hyperlink ref="F59" ns1:id="R3cae8e186c48414b"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A95"/>
-    <hyperlink ref="F60" ns1:id="Ra7f1aef2362a4a4a"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A96"/>
-    <hyperlink ref="F61" ns1:id="R8befa90ef3fc47c2"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A97"/>
-    <hyperlink ref="F62" ns1:id="Re7fdcbfdd1084572"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A98"/>
-    <hyperlink ref="F63" ns1:id="R65ca925ee60b42a7"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A100"/>
-    <hyperlink ref="F64" ns1:id="Reb76655df7374bc5"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A166"/>
-    <hyperlink ref="F65" ns1:id="R055caeb6a90642b5"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A102"/>
-    <hyperlink ref="F66" ns1:id="Rfff5ca38a0554ba3"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A103"/>
-    <hyperlink ref="F67" ns1:id="R0888add655cd4fba"/>
-    <hyperlink ref="C33" location="'02项目完整详情'!A104"/>
-    <hyperlink ref="F33" ns1:id="Rd9709f11bc9f4e83"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A163"/>
-    <hyperlink ref="F68" ns1:id="R20412a2edb1c448a"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A105"/>
-    <hyperlink ref="F69" ns1:id="R61772b79401a4268"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A106"/>
-    <hyperlink ref="F70" ns1:id="R987b8e6f52a74110"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A107"/>
-    <hyperlink ref="F71" ns1:id="R0c4396d550f2475f"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A162"/>
-    <hyperlink ref="F72" ns1:id="R4f11bd52ab71481c"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A108"/>
-    <hyperlink ref="F73" ns1:id="R4db82e37256244c2"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A109"/>
-    <hyperlink ref="F74" ns1:id="R4031c47a301e406d"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A110"/>
-    <hyperlink ref="F75" ns1:id="Raa160d321af04db8"/>
-    <hyperlink ref="C30" location="'02项目完整详情'!A111"/>
-    <hyperlink ref="F30" ns1:id="R769c1e9ff31b4410"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A112"/>
-    <hyperlink ref="F76" ns1:id="R4cdea66d1ef84e88"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A114"/>
-    <hyperlink ref="F77" ns1:id="Rfe9d4bacb83a4b3a"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A115"/>
-    <hyperlink ref="F78" ns1:id="Rdb52bb1fc14c4902"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A116"/>
-    <hyperlink ref="F79" ns1:id="Raea0cb8061aa4114"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A153"/>
-    <hyperlink ref="F80" ns1:id="Re209c4141aad4cc2"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A152"/>
-    <hyperlink ref="F81" ns1:id="R929ae2605c414e9f"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A165"/>
-    <hyperlink ref="F82" ns1:id="R1abe4cdaf9e34bae"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A117"/>
-    <hyperlink ref="F83" ns1:id="R0a10fce99c274f93"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A118"/>
-    <hyperlink ref="F84" ns1:id="R938383f864354c81"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A119"/>
-    <hyperlink ref="F85" ns1:id="Rf5654ce2b68c4be9"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A121"/>
-    <hyperlink ref="F86" ns1:id="Rcb7b406cd4eb4fbf"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A123"/>
-    <hyperlink ref="F87" ns1:id="R5815a7bd80814259"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A124"/>
-    <hyperlink ref="F88" ns1:id="R0c410df45d8a4e3d"/>
-    <hyperlink ref="C31" location="'02项目完整详情'!A125"/>
-    <hyperlink ref="F31" ns1:id="R431b21fd445f4abe"/>
-    <hyperlink ref="C89" location="'02项目完整详情'!A126"/>
-    <hyperlink ref="F89" ns1:id="R567091a279bf498d"/>
-    <hyperlink ref="C90" location="'02项目完整详情'!A164"/>
-    <hyperlink ref="F90" ns1:id="Re392bfd9b5274c72"/>
-    <hyperlink ref="C91" location="'02项目完整详情'!A128"/>
-    <hyperlink ref="F91" ns1:id="Re6cada6d8cc14329"/>
-    <hyperlink ref="C92" location="'02项目完整详情'!A129"/>
-    <hyperlink ref="F92" ns1:id="R8fc1cda8f3b6430e"/>
-    <hyperlink ref="C93" location="'02项目完整详情'!A130"/>
-    <hyperlink ref="F93" ns1:id="R27a55a96c3f24c5f"/>
-    <hyperlink ref="C94" location="'02项目完整详情'!A131"/>
-    <hyperlink ref="F94" ns1:id="R5e47895d5a614c2b"/>
-    <hyperlink ref="C32" location="'02项目完整详情'!A132"/>
-    <hyperlink ref="F32" ns1:id="R3b43825c6bac4d00"/>
-    <hyperlink ref="C95" location="'02项目完整详情'!A133"/>
-    <hyperlink ref="F95" ns1:id="R93e0d1bfa9de4923"/>
-    <hyperlink ref="C96" location="'02项目完整详情'!A40"/>
-    <hyperlink ref="F96" ns1:id="R8485fac45d264a2f"/>
-    <hyperlink ref="C97" location="'02项目完整详情'!A41"/>
-    <hyperlink ref="F97" ns1:id="R1c0f567749234b9c"/>
-    <hyperlink ref="C98" location="'02项目完整详情'!A42"/>
-    <hyperlink ref="F98" ns1:id="Rbf215fc93e064e7e"/>
-    <hyperlink ref="C99" location="'02项目完整详情'!A43"/>
-    <hyperlink ref="F99" ns1:id="R53db146b46f44f15"/>
-    <hyperlink ref="C100" location="'02项目完整详情'!A44"/>
-    <hyperlink ref="F100" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F108" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C108" location="'02项目完整详情'!A148"/>
-    <hyperlink ref="C101" location="'02项目完整详情'!A167" display="项目完整详情"/>
-    <hyperlink ref="F101" ns1:id="rIdSystematic98"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A168" display="项目完整详情"/>
-    <hyperlink ref="F102" ns1:id="rIdSystematic99"/>
-    <hyperlink ref="C103" location="'02项目完整详情'!A175" display="项目完整详情"/>
-    <hyperlink ref="F103" ns1:id="rIdSystematic100"/>
-    <hyperlink ref="C104" location="'02项目完整详情'!A176" display="项目完整详情"/>
-    <hyperlink ref="F104" ns1:id="rIdSystematic101"/>
+    <hyperlink ref="C24" location="'02项目完整详情'!A66"/>
+    <hyperlink ref="F24" ns1:id="R4dc201fc29cb4ab4"/>
+    <hyperlink ref="C43" location="'02项目完整详情'!A139"/>
+    <hyperlink ref="F43" ns1:id="Rf4dc98016cfb49fd"/>
+    <hyperlink ref="C25" location="'02项目完整详情'!A151"/>
+    <hyperlink ref="F25" ns1:id="R3d89872d06fd4b60"/>
+    <hyperlink ref="C26" location="'02项目完整详情'!A67"/>
+    <hyperlink ref="F26" ns1:id="R1e9b7d2bc63d4258"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A68"/>
+    <hyperlink ref="F44" ns1:id="R5d0261ffe45c4155"/>
+    <hyperlink ref="C27" location="'02项目完整详情'!A69"/>
+    <hyperlink ref="F27" ns1:id="Reeb11b878b934f2d"/>
+    <hyperlink ref="C28" location="'02项目完整详情'!A70"/>
+    <hyperlink ref="F28" ns1:id="R5b06defce5864a96"/>
+    <hyperlink ref="C29" location="'02项目完整详情'!A71"/>
+    <hyperlink ref="F29" ns1:id="Ra48afdb9842a4366"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A72"/>
+    <hyperlink ref="F45" ns1:id="Rb3b4681efcdd44d4"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A73"/>
+    <hyperlink ref="F46" ns1:id="R4f0b800598574b86"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A74"/>
+    <hyperlink ref="F47" ns1:id="R56697ca79cd54a14"/>
+    <hyperlink ref="C35" location="'02项目完整详情'!A75"/>
+    <hyperlink ref="F35" ns1:id="R0814a7680dde4f9a"/>
+    <hyperlink ref="C36" location="'02项目完整详情'!A76"/>
+    <hyperlink ref="F36" ns1:id="R3f222e6bf9fa46ec"/>
+    <hyperlink ref="C37" location="'02项目完整详情'!A77"/>
+    <hyperlink ref="F37" ns1:id="Rc66c2cf37bbc404d"/>
+    <hyperlink ref="C38" location="'02项目完整详情'!A78"/>
+    <hyperlink ref="F38" ns1:id="R90e03710dfe04e74"/>
+    <hyperlink ref="C39" location="'02项目完整详情'!A79"/>
+    <hyperlink ref="F39" ns1:id="R80f5129c1ee24096"/>
+    <hyperlink ref="C40" location="'02项目完整详情'!A80"/>
+    <hyperlink ref="F40" ns1:id="R6360db00742b45ec"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A81"/>
+    <hyperlink ref="F48" ns1:id="Rc4146f6376594d01"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A156"/>
+    <hyperlink ref="F49" ns1:id="R97ba6e4965084c76"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A155"/>
+    <hyperlink ref="F50" ns1:id="Rcbdc080795344925"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A83"/>
+    <hyperlink ref="F51" ns1:id="R9e6afd1b359743bb"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A154"/>
+    <hyperlink ref="F52" ns1:id="Rb320e0a5ad524836"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A86"/>
+    <hyperlink ref="F53" ns1:id="R42a660aaeb1d4c95"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A87"/>
+    <hyperlink ref="F54" ns1:id="R88784a2520864683"/>
+    <hyperlink ref="C30" location="'02项目完整详情'!A88"/>
+    <hyperlink ref="F30" ns1:id="Rcb8b33dae69a4731"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A89"/>
+    <hyperlink ref="F55" ns1:id="Rd5ea9c8442ca46ac"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A90"/>
+    <hyperlink ref="F56" ns1:id="R7734727212364cb2"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A91"/>
+    <hyperlink ref="F57" ns1:id="R78b8c8c0ca954ecb"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A92"/>
+    <hyperlink ref="F58" ns1:id="Rfdf5f46608d44776"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A93"/>
+    <hyperlink ref="F59" ns1:id="R82f06426c3d54976"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A94"/>
+    <hyperlink ref="F60" ns1:id="R3cae8e186c48414b"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A95"/>
+    <hyperlink ref="F61" ns1:id="Ra7f1aef2362a4a4a"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A96"/>
+    <hyperlink ref="F62" ns1:id="R8befa90ef3fc47c2"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A97"/>
+    <hyperlink ref="F63" ns1:id="Re7fdcbfdd1084572"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A98"/>
+    <hyperlink ref="F64" ns1:id="R65ca925ee60b42a7"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A100"/>
+    <hyperlink ref="F65" ns1:id="Reb76655df7374bc5"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A166"/>
+    <hyperlink ref="F66" ns1:id="R055caeb6a90642b5"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A102"/>
+    <hyperlink ref="F67" ns1:id="Rfff5ca38a0554ba3"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A103"/>
+    <hyperlink ref="F68" ns1:id="R0888add655cd4fba"/>
+    <hyperlink ref="C34" location="'02项目完整详情'!A104"/>
+    <hyperlink ref="F34" ns1:id="Rd9709f11bc9f4e83"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A163"/>
+    <hyperlink ref="F69" ns1:id="R20412a2edb1c448a"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A105"/>
+    <hyperlink ref="F70" ns1:id="R61772b79401a4268"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A106"/>
+    <hyperlink ref="F71" ns1:id="R987b8e6f52a74110"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A107"/>
+    <hyperlink ref="F72" ns1:id="R0c4396d550f2475f"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A162"/>
+    <hyperlink ref="F73" ns1:id="R4f11bd52ab71481c"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A108"/>
+    <hyperlink ref="F74" ns1:id="R4db82e37256244c2"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A109"/>
+    <hyperlink ref="F75" ns1:id="R4031c47a301e406d"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A110"/>
+    <hyperlink ref="F76" ns1:id="Raa160d321af04db8"/>
+    <hyperlink ref="C31" location="'02项目完整详情'!A111"/>
+    <hyperlink ref="F31" ns1:id="R769c1e9ff31b4410"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A112"/>
+    <hyperlink ref="F77" ns1:id="R4cdea66d1ef84e88"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A114"/>
+    <hyperlink ref="F78" ns1:id="Rfe9d4bacb83a4b3a"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A115"/>
+    <hyperlink ref="F79" ns1:id="Rdb52bb1fc14c4902"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A116"/>
+    <hyperlink ref="F80" ns1:id="Raea0cb8061aa4114"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A153"/>
+    <hyperlink ref="F81" ns1:id="Re209c4141aad4cc2"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A152"/>
+    <hyperlink ref="F82" ns1:id="R929ae2605c414e9f"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A165"/>
+    <hyperlink ref="F83" ns1:id="R1abe4cdaf9e34bae"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A117"/>
+    <hyperlink ref="F84" ns1:id="R0a10fce99c274f93"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A118"/>
+    <hyperlink ref="F85" ns1:id="R938383f864354c81"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A119"/>
+    <hyperlink ref="F86" ns1:id="Rf5654ce2b68c4be9"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A121"/>
+    <hyperlink ref="F87" ns1:id="Rcb7b406cd4eb4fbf"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A123"/>
+    <hyperlink ref="F88" ns1:id="R5815a7bd80814259"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A124"/>
+    <hyperlink ref="F89" ns1:id="R0c410df45d8a4e3d"/>
+    <hyperlink ref="C32" location="'02项目完整详情'!A125"/>
+    <hyperlink ref="F32" ns1:id="R431b21fd445f4abe"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A126"/>
+    <hyperlink ref="F90" ns1:id="R567091a279bf498d"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A164"/>
+    <hyperlink ref="F91" ns1:id="Re392bfd9b5274c72"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A128"/>
+    <hyperlink ref="F92" ns1:id="Re6cada6d8cc14329"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A129"/>
+    <hyperlink ref="F93" ns1:id="R8fc1cda8f3b6430e"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A130"/>
+    <hyperlink ref="F94" ns1:id="R27a55a96c3f24c5f"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A131"/>
+    <hyperlink ref="F95" ns1:id="R5e47895d5a614c2b"/>
+    <hyperlink ref="C33" location="'02项目完整详情'!A132"/>
+    <hyperlink ref="F33" ns1:id="R3b43825c6bac4d00"/>
+    <hyperlink ref="C96" location="'02项目完整详情'!A133"/>
+    <hyperlink ref="F96" ns1:id="R93e0d1bfa9de4923"/>
+    <hyperlink ref="C97" location="'02项目完整详情'!A40"/>
+    <hyperlink ref="F97" ns1:id="R8485fac45d264a2f"/>
+    <hyperlink ref="C98" location="'02项目完整详情'!A41"/>
+    <hyperlink ref="F98" ns1:id="R1c0f567749234b9c"/>
+    <hyperlink ref="C99" location="'02项目完整详情'!A42"/>
+    <hyperlink ref="F99" ns1:id="Rbf215fc93e064e7e"/>
+    <hyperlink ref="C100" location="'02项目完整详情'!A43"/>
+    <hyperlink ref="F100" ns1:id="R53db146b46f44f15"/>
+    <hyperlink ref="C101" location="'02项目完整详情'!A44"/>
+    <hyperlink ref="F101" ns1:id="R188b27dcb5574282"/>
+    <hyperlink ref="F109" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C109" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A167" display="项目完整详情"/>
+    <hyperlink ref="F102" ns1:id="rIdSystematic98"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A168" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdSystematic99"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A175" display="项目完整详情"/>
+    <hyperlink ref="F104" ns1:id="rIdSystematic100"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A176" display="项目完整详情"/>
+    <hyperlink ref="F105" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
-    <hyperlink ref="C105" location="'02项目完整详情'!A182" display="项目完整详情"/>
-    <hyperlink ref="F105" ns1:id="rIdResume103"/>
-    <hyperlink ref="C106" location="'02项目完整详情'!A184" display="项目完整详情"/>
-    <hyperlink ref="F106" ns1:id="rIdResume104"/>
+    <hyperlink ref="C106" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F106" ns1:id="rIdResume103"/>
+    <hyperlink ref="C107" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F107" ns1:id="rIdResume104"/>
     <hyperlink ref="C14" location="'02项目完整详情'!A185" display="项目完整详情"/>
     <hyperlink ref="F14" ns1:id="rIdResume105"/>
-    <hyperlink ref="C107" location="'02项目完整详情'!A186" display="项目完整详情"/>
-    <hyperlink ref="F107" ns1:id="rIdResume106"/>
+    <hyperlink ref="C108" location="'02项目完整详情'!A186" display="项目完整详情"/>
+    <hyperlink ref="F108" ns1:id="rIdResume106"/>
     <hyperlink ref="C12" location="'02项目完整详情'!A191" display="项目完整详情"/>
     <hyperlink ref="F12" ns1:id="rIdResume107"/>
     <hyperlink ref="C22" location="'02项目完整详情'!A198" display="项目完整详情"/>
     <hyperlink ref="F22" ns1:id="rIdResume108"/>
+    <hyperlink ref="C23" location="'02项目完整详情'!A200" display="项目完整详情"/>
+    <hyperlink ref="F23" ns1:id="rIdResume109"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -46353,6 +47008,32 @@
       </c>
       <c r="H72" t="str" s="3">
         <v>研究方向联系人：1.2纪永刚jiyonggang@upc.edu.cn、崔学荣cxr@upc.edu.cn；1.4刘善伟20110052@upc.edu.cn；2.1罗偲luo_cai@upc.edu.cn；2.3余相20240018@upc.edu.cn；2.4贺凯飞kfhe@upc.edu.cn。受理联系人及提交地址待末段，不能套2026联系信息。</v>
+      </c>
+    </row>
+    <row r="73" ht="132" customHeight="1">
+      <c r="A73" t="str" s="20">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B73" t="n" s="13">
+        <v>46249</v>
+      </c>
+      <c r="C73" t="str" s="14">
+        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+      </c>
+      <c r="D73" t="str" s="15">
+        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+      </c>
+      <c r="E73" t="str" s="15">
+        <v>合同金额2万元/项；计划≤10项。</v>
+      </c>
+      <c r="F73" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G73" t="str" s="3">
+        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+      </c>
+      <c r="H73" t="str" s="3">
+        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
       </c>
     </row>
   </sheetData>
@@ -46499,6 +47180,8 @@
     <hyperlink ref="F71" ns1:id="rIdResume73"/>
     <hyperlink ref="C72" location="'02项目完整详情'!A199" display="项目完整详情"/>
     <hyperlink ref="F72" ns1:id="rIdResume74"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A201" display="项目完整详情"/>
+    <hyperlink ref="F73" ns1:id="rIdResume75"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -18204,6 +18204,255 @@
         <v>同一联合公告两平台合并为1独立轮次，不拆成两笔基金；2025/2024另有索引但未核不套条款。</v>
       </c>
     </row>
+    <row r="202" ht="132" customHeight="1">
+      <c r="A202" t="str" s="3">
+        <v>N053</v>
+      </c>
+      <c r="B202" t="str" s="3">
+        <v>官方2026完整正文已读；智能可穿戴任务未细化，办法/申请表验证码</v>
+      </c>
+      <c r="C202" t="str" s="3">
+        <v>西安工程大学</v>
+      </c>
+      <c r="D202" t="str" s="3">
+        <v>功能性纺织材料及制品教育部重点实验室</v>
+      </c>
+      <c r="E202" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F202" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G202" t="n" s="6">
+        <v>46158</v>
+      </c>
+      <c r="H202" t="str" s="3">
+        <v>具体时点未载</v>
+      </c>
+      <c r="I202" t="str" s="3">
+        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
+      </c>
+      <c r="J202" t="str" s="3">
+        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
+      </c>
+      <c r="K202" t="str" s="3">
+        <v>在职教学/科研人员，相关功能性纺织材料研究，副教授以上或博士；否则由该领域高级专家推荐（人数未载）。优先校外，校外申请人作为负责人；同年申报1项可参与1项，年龄未载。</v>
+      </c>
+      <c r="L202" t="str" s="3">
+        <v>必须与实验室固定科研人员联合申请；鼓励利用设备/科研交流，驻室天数未载。</v>
+      </c>
+      <c r="M202" t="str" s="3">
+        <v>经费主要设备费、业务费、劳务费；是否外拨及比例、报账地点/支付时点正文未载，办法验证码未取。</v>
+      </c>
+      <c r="N202" t="str" s="3">
+        <v>2年；起止日期未載；2027-07-01前须中检报告，进展不佳可终止。</v>
+      </c>
+      <c r="O202" t="str" s="3">
+        <v>重点：研究报告1篇+SCI中科院一区≥1或二区≥2+可展示产品1件；一般：报告1篇+SCI二区及以上≥1+产品1件；报告须有显示度/可量化指标/应用示范。论文第一单位或第一通讯单位为实验室，成果基金编号标注；在实验室开展测试须交测试报告。</v>
+      </c>
+      <c r="P202" t="str" s="3">
+        <v>授权专利/软著等：西安工程大学为第一专利权人/完成单位；成果转化经济效益双方共享比例另议；全面IP归属/合作单位权益须办法确认。</v>
+      </c>
+      <c r="Q202" t="str" s="3">
+        <v>纸质1份负责人签字、单位盖章，邮实验室；电子含盖章页扫描发jybzdsys@xpu.edu.cn；截止2026-05-16，材料不齐不受理。西安碑林金花南路19号。</v>
+      </c>
+      <c r="R202" t="str" s="3">
+        <v>已知本人博士和高校现职；机器人具体任务证据不足且本轮已截止；固定合作、限项及材料领域具体任务待核，不推断不能做。</v>
+      </c>
+      <c r="S202" t="str" s="3">
+        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
+      </c>
+      <c r="T202" t="str" s="3">
+        <v>https://klftpme.xpu.edu.cn/info/1042/1495.htm</v>
+      </c>
+      <c r="U202" t="str" s="3">
+        <v>管理办法PDF wbfileid=16491081；申请DOC wbfileid=16491080；owner=1869563533；两附件首次验证码未取，链接见人工N053。</v>
+      </c>
+      <c r="V202" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W202" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X202" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y202" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="Z202" t="str" s="3">
+        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
+      </c>
+      <c r="AA202" t="str" s="3">
+        <v>申请条件、产品指标和优先外部已确认，但任务证据不足保持待核；不以平台简介智能加工装备判断本轮已相关。</v>
+      </c>
+    </row>
+    <row r="203" ht="132" customHeight="1">
+      <c r="A203" t="str" s="3">
+        <v>N054</v>
+      </c>
+      <c r="B203" t="str" s="3">
+        <v>正式2015完整公告及成果额度对照表已读；2个DOC首次不可解析</v>
+      </c>
+      <c r="C203" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="D203" t="str" s="3">
+        <v>广西高校无人机遥测重点实验室开放课题（主任基金仅内部，未纳入）</v>
+      </c>
+      <c r="E203" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F203" t="str" s="3">
+        <v>2015</v>
+      </c>
+      <c r="G203" t="n" s="6">
+        <v>42175</v>
+      </c>
+      <c r="H203" t="str" s="3">
+        <v>具体截止时点未载</v>
+      </c>
+      <c r="I203" t="str" s="3">
+        <v>实际14项无人机任务：飞控模型、航迹规划、姿态控制、影像匹配、多用途系统/载荷设计、数传图传二次开发、行业应用、多机多任务协作、目标识别跟踪、特殊用途无人机、遥感系统、北斗飞控及无人机热点。</v>
+      </c>
+      <c r="J203" t="str" s="3">
+        <v>校外开放1—5万元/项拟2—3项；结题按实际成果折算增减资助，不承诺固定到账。主任基金3—6/3—4万元面向固定人员，不计本人对外资助金额。</v>
+      </c>
+      <c r="K203" t="str" s="3">
+        <v>国内外科研教学人员、博士后、产业科技人员；邀请参与研究人员/博士硕士、自带课题经费来室人员/短期测试人员亦列。学历职称/年龄统一门槛和限项未載。主任课题固定人员专属，分开不纳。</v>
+      </c>
+      <c r="L203" t="str" s="3">
+        <v>申请人原则上需与固定研究人员联合申请，保留原则上限定；到室交流具体天数未载。</v>
+      </c>
+      <c r="M203" t="str" s="3">
+        <v>实验室统一管理、专款专用由受资助人掌握使用；原/辅材料、分析测试、出版文献信息知识产权事务、差旅、会议费（国际会议特别说明）；结余归实验室；外拨到申请人单位未明确。结题按成果增减资金，支付节点未载。</v>
+      </c>
+      <c r="N203" t="str" s="3">
+        <v>一般2年；2015-07-01—2017-07-01。</v>
+      </c>
+      <c r="O203" t="str" s="3">
+        <v>年度汇报/论文报告或阶段小结；结题/终止交总结、论文报告、原始资料实验数据及档案目录、完成指标。成果折算额度≥实际资助额才完成，结题按实际增减钱。Top论文3万、IF&gt;2非Top2万、其他SCI/指定电子学报通信学报电子信息学报宇航学报系统工程与电子技术1万、中文期刊EI.5万、会议EI/中文核心表列.2万；中文核心须一级学会主办。博士毕业1万、硕士.5万（本课题并致谢）；国家奖一等10/二等6万，省部奖一等5/二等4/三等3万；授权发明表列1.5万、申请发明.5万、实用专利.5万、科技厅鉴定.5万。实验室第一/第二单位及基金编号标注；第二单位折半、第三1/3；其他EI/中文核心又要求实验室第一单位才计，按具体类别不能泛化第二单位都能计。</v>
+      </c>
+      <c r="P203" t="str" s="3">
+        <v>成果归实验室与研究者所在单位共有；实验室组织鉴定、双方联报奖励；转让获利共享比例另议，专利依法办理，外籍按国家规定。</v>
+      </c>
+      <c r="Q203" t="str" s="3">
+        <v>开放申请表3份、所在单位主管领导同意，2015-06-20前交实验室。广西桂林金鸡路2号桂林航天工业学院电子工程系541004；正文邮箱联络，未明确电子邮件可替3份纸质。</v>
+      </c>
+      <c r="R203" t="str" s="3">
+        <v>本人博士、高校现职对应科研教学类别，本历史轮已截止；未来实际限项/合作及支付机制需新年度，不据熟人判断已落实。</v>
+      </c>
+      <c r="S203" t="str" s="3">
+        <v>2015历史机制；2 DOC首次工具不可解析/返回异常，需人工下载；Top范围、专利折算正文“授权含申请1.5万（申请.5+授权1）”与表“授权发明1.5万”不完全一致须确认；外拨/支付节点未载。现平台名称是否重组为目录无人机系统与技术应用未证实，不直接合并年度。</v>
+      </c>
+      <c r="T203" t="str" s="3">
+        <v>https://kjc.guat.edu.cn/info/1088/1539.htm</v>
+      </c>
+      <c r="U203" t="str" s="3">
+        <v>开放表：https://kjc.guat.edu.cn/__local/C/C7/37/EDFAC45A52A5B0FD648F0A2BA53_6367132E_11800.doc?e=.doc；指南：https://kjc.guat.edu.cn/__local/7/67/22/FE6152A9B835F5C6A46F53DA719_BA2C6462_DA00.doc?e=.doc；均首次不可解析不重试；主任表无需本人下载。</v>
+      </c>
+      <c r="V203" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W203" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X203" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y203" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="Z203" t="str" s="3">
+        <v>张文凯15078326608；zwklxt@126.com；桂林金鸡路2号电子工程系541004（2015公告联系，不保证现任）。</v>
+      </c>
+      <c r="AA203" t="str" s="3">
+        <v>仅2015对外开放部分；同页主任基金内部资格分离；具体成果货币折算不能套用现年SCI分区或当期资金。</v>
+      </c>
+    </row>
+    <row r="204" ht="132" customHeight="1">
+      <c r="A204" t="str" s="3">
+        <v>N055</v>
+      </c>
+      <c r="B204" t="str" s="3">
+        <v>正式2024年度完整公告已核；管理办法与申请书首次验证码</v>
+      </c>
+      <c r="C204" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="D204" t="str" s="3">
+        <v>广西特种工程装备与控制重点实验室</v>
+      </c>
+      <c r="E204" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F204" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G204" t="n" s="6">
+        <v>45442</v>
+      </c>
+      <c r="H204" t="str" s="3">
+        <v>具体时点未载；官网2024-04-30发布，落款04-28，不混作截止</v>
+      </c>
+      <c r="I204" t="str" s="3">
+        <v>2024方向二明确特种工程机器人：矿山/隧道/电力线路/抢险救灾/危险环境，姿态和受力检测、运动反馈控制、环境认知定位；非结构环境移动平台行走路径与机械臂关节实时协同规划。方向一含机构动力建模、工作状态辨识控制；材料方向并非凭实验室名称收录。</v>
+      </c>
+      <c r="J204" t="str" s="3">
+        <v>3—6万元/项；计划8—10项，各方向2—3项。</v>
+      </c>
+      <c r="K204" t="str" s="3">
+        <v>博士或中级及以上技术职称科技人员可依办法申请；年龄、单位具体范围及限项正文未載，办法待取。</v>
+      </c>
+      <c r="L204" t="str" s="3">
+        <v>年度正文提联合攻关，未明确强制固定合作人及驻室频次，须2024管理办法确认。</v>
+      </c>
+      <c r="M204" t="str" s="3">
+        <v>立项部分拨课题负责人单位、部分留实验室按实际支出报账；比例/节点未载。材料、测试化验加工、差旅、会议、出版文献信息/IP事务、科研助理劳务；劳务≤总额20%；专款专用。</v>
+      </c>
+      <c r="N204" t="str" s="3">
+        <v>2年，自批准之日起算，未列统一起止。</v>
+      </c>
+      <c r="O204" t="str" s="3">
+        <v>公告明确成果管理/结题按2024管理办法执行；具体论文/专利/样机数量、第一单位/指定作者及报告要求未取得，不套2015无人机或2026主任基金。</v>
+      </c>
+      <c r="P204" t="str" s="3">
+        <v>公告正文未载，须2024管理办法确认IP及转化收益。</v>
+      </c>
+      <c r="Q204" t="str" s="3">
+        <v>参考2024管理办法/申请指南填写2024申报书，电子发xzglsl2013@163.com；发布日起至2024-05-30，初审后学术委员会评审；纸质份数/盖章正文未载。</v>
+      </c>
+      <c r="R204" t="str" s="3">
+        <v>本人博士对应学历；本轮已截止。年龄/限项/固定合作人规则需办法或后续年新公告；不判定本人可当前申请。</v>
+      </c>
+      <c r="S204" t="str" s="3">
+        <v>2附件验证码；2024办法成果/署名/IP/资格细则及外拨比例未核。2026已有主任基金E069只限本校，不能由第三方2026开放标题或2024外拨机制认当期对外受理。</v>
+      </c>
+      <c r="T204" t="str" s="3">
+        <v>https://seec.guat.edu.cn/info/1133/1103.htm</v>
+      </c>
+      <c r="U204" t="str" s="3">
+        <v>2024办法PDF wbfileid=14337059、2024表DOC wbfileid=14337058，owner1976671854；均首次验证码，原URL人工N055。</v>
+      </c>
+      <c r="V204" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W204" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X204" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y204" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="Z204" t="str" s="3">
+        <v>熊中刚13788579056、赵宏旺13877391885；xzglsl2013@163.com；桂林七星区金鸡路2号541004；实验室办公0773-2253031。</v>
+      </c>
+      <c r="AA204" t="str" s="3">
+        <v>2024对外批次与2026内部主任E069分别处理；网页上一篇2024立项不能当申请窗口仍开。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -18625,6 +18874,9 @@
     <hyperlink ref="T199" ns1:id="rIdResume421"/>
     <hyperlink ref="T200" ns1:id="rIdResume422"/>
     <hyperlink ref="T201" ns1:id="rIdResume423"/>
+    <hyperlink ref="T202" ns1:id="rIdResume424"/>
+    <hyperlink ref="T203" ns1:id="rIdResume425"/>
+    <hyperlink ref="T204" ns1:id="rIdResume426"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -42478,6 +42730,814 @@
 https://ee.neepu.edu.cn/info/1055/40177.htm</v>
       </c>
       <c r="I773" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="774" ht="52.5" customHeight="1">
+      <c r="A774" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B774" t="str" s="3">
+        <v>福建省属高校机器人研究平台目录补漏</v>
+      </c>
+      <c r="C774" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D774" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E774" t="str" s="3">
+        <v>查询：福建理工大学 机器人 重点实验室 开放基金 2026 2027 / 福建工程学院 数字化 装备 开放基金 / 厦门理工学院 机器人 重点实验室 开放课题 2026 / 闽南科技学院 闽江学院 智能制造 开放基金 2026；线索：2026“柔性制造装备集成福建省高校重点实验室”开放课题研究基金申报指南；功能晶体与器件全国重点实验室开放基金课题申请指南（2026年度）&lt;br/&gt;--功能晶体与器件全国重点实验室；关于做好2026年度福建理工大学重点科研创新平台开放基金项目结题验收工作的通知；2026年度开放课题申请公告；煤炭无人化开采数智技术全国重点实验室2026年度开放基金课题（第一批）申请指南-煤炭无人化开采数智技术全国重点实验室；我院姚俊峰教授团队获2026年度文化和旅游部重点实验室资助项目-厦门大学数字媒体计算中心</v>
+      </c>
+      <c r="F774" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G774" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H774" t="str" s="3">
+        <v>https://www.xit.edu.cn/kxyj/2026/0206/c1174a83598/page.htm
+https://www.fjirsm.ac.cn/sklfcd/tzgg/202605/t20260508_8197508.html
+https://kyc.fjut.edu.cn/2026/0512/c6400a267638/page.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://cdsys.aust.edu.cn/info/1021/2502.htm
+https://cdmc.xmu.edu.cn/info/1002/5644.htm</v>
+      </c>
+      <c r="I774" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第333项</v>
+      </c>
+    </row>
+    <row r="775" ht="52.5" customHeight="1">
+      <c r="A775" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B775" t="str" s="3">
+        <v>江西省属高校机器人平台及开放机制补漏</v>
+      </c>
+      <c r="C775" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D775" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E775" t="str" s="3">
+        <v>查询：江西理工大学 智能装备 重点实验室 开放基金 2026 2027 / 南昌航空大学 机器人 重点实验室 开放基金 2026 / 景德镇陶瓷大学 机器人 智能装备 开放课题 2026 / 江西科技师范大学 机器人 重点实验室 开放基金；线索：江西省机载系统智能检测技术产业技术工程化中心、南昌市航空软件共性技术研发重点实验室开放基金指南_校内公告_新闻中心_南昌航空大学；关于拟立项建设2026年景德镇陶瓷大学研究生层次AI课程建设的公示-景德镇陶瓷大学-研究生院；关于开展2026年度开放性实验项目申报工作的通知-景德镇陶瓷大学-教务处；关于江西陶瓷文物遗存保护暨御窑研究协同创新中心2026年度拟立项及有关课题拟撤项的公示-景德镇陶瓷大学官方网站；机械电子工程学院2026届硕士研究生学位论文答辩公告-景德镇陶瓷大学机械电子工程学院；赣南实验室2026年高层次人才招聘公告-江西理工大学人事处网站</v>
+      </c>
+      <c r="F775" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G775" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H775" t="str" s="3">
+        <v>https://www.nchu.edu.cn/xwzx/xngg/content_196002
+https://yjsy.jcu.edu.cn/info/1042/6115.htm
+https://jwc.jci.edu.cn/info/1067/5649.htm
+https://www.jci.edu.cn/info/1055/51920.htm
+https://jdxy.jci.edu.cn/info/1041/5710.htm
+https://www.jxust.edu.cn/dwjsgzbrsc/info/1024/1206.htm</v>
+      </c>
+      <c r="I775" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第334项</v>
+      </c>
+    </row>
+    <row r="776" ht="52.5" customHeight="1">
+      <c r="A776" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B776" t="str" s="3">
+        <v>西安工程及重庆理工省属机器人平台目录补漏</v>
+      </c>
+      <c r="C776" t="str" s="3">
+        <v>陕西·西安/重庆</v>
+      </c>
+      <c r="D776" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E776" t="str" s="3">
+        <v>查询：site:xpu.edu.cn 科研平台 机器人 重点实验室 / site:xpu.edu.cn 开放基金 2026 2027 / site:cqut.edu.cn 科研平台 机器人 重点实验室 / site:cqut.edu.cn 开放基金 2027 2026 机器人；线索：科研项目-西安工程大学“陕西省服装设计智能化重点实验室”；科研平台-西安工程大学机电工程学院；科大讯飞陕西大区一行来我校座谈共建陕西省人工智能联合重点实验室工作-西安工程大学招生办</v>
+      </c>
+      <c r="F776" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G776" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H776" t="str" s="3">
+        <v>https://ci.xpu.edu.cn/kycg/kyxm.htm
+https://jidianxy.xpu.edu.cn/Subject_research/kypt.htm
+https://zsb.xpu.edu.cn/info/1105/1473.htm</v>
+      </c>
+      <c r="I776" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第335项</v>
+      </c>
+    </row>
+    <row r="777" ht="52.5" customHeight="1">
+      <c r="A777" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B777" t="str" s="3">
+        <v>北京信息科技大学机器人相关平台目录发现</v>
+      </c>
+      <c r="C777" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D777" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E777" t="str" s="3">
+        <v>查询：site:bistu.edu.cn 科研平台 机器人 重点实验室 / site:bistu.edu.cn 开放基金 2026 2027 / site:bistu.edu.cn 重点实验室 开放课题 智能感知 / site:bistu.edu.cn "开放基金" 机器人；线索：基地主任王红军教授负责的国家重点实验室重点开放课题结题验收_基地新闻_高端装备智能感知与控制北京市国际科技合作基地；重点实验室开放课题情况 2020年度_开放课题_北京信息科技大学现代测控技术教育部重点实验室；北京信息科技大学 - 焦点关注-我校获批惯性与声学传感技术北京市工程研究中心；人工智能实验室_北京信息科技大学机器人大工程平台</v>
+      </c>
+      <c r="F777" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G777" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H777" t="str" s="3">
+        <v>https://gdzbjd.bistu.edu.cn/jdxw/1434bf1df7434937a26dbab67622ef07.htm
+https://labmct.bistu.edu.cn/hzjl/syskfkt/f8dba308307a405d80344dc70e417d8f.html
+https://www.bistu.edu.cn/jdgz/395994.html
+https://ai-r-teach.bistu.edu.cn/sjjx/cxsys/48802e479920446ba64f92146bf90c9b.htm</v>
+      </c>
+      <c r="I777" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第336项</v>
+      </c>
+    </row>
+    <row r="778" ht="52.5" customHeight="1">
+      <c r="A778" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B778" t="str" s="3">
+        <v>南京周边尚缺完整名单的科研平台目录发现</v>
+      </c>
+      <c r="C778" t="str" s="3">
+        <v>江苏·南京/无锡</v>
+      </c>
+      <c r="D778" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E778" t="str" s="3">
+        <v>查询：site:njtech.edu.cn 科研平台 机器人 智能制造 重点实验室 / site:jiangnan.edu.cn 科研平台 机器人 重点实验室 / site:njust.edu.cn 科研平台 智能感知 机器人 实验室 / site:cczu.edu.cn 科研平台 机器人 重点实验室；线索：机器人与智能控制实验室；南京理工大学大型仪器设备共享管理平台；常州大学机器人研究所揭牌；龙城实验室-工业母机研究院；科研平台；国家级项目-南京工业大学智能制造研究院</v>
+      </c>
+      <c r="F778" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G778" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H778" t="str" s="3">
+        <v>https://zj.njust.edu.cn/znkz/2024/0615/c10860a110672/page.htm
+https://dxyq.njust.edu.cn/detail.action?equipDetail=true&amp;id=20257621
+https://www.cczu.edu.cn/2010/1026/c10356a102833/page.htm
+https://iimt.cczu.edu.cn/
+https://cpe.cczu.edu.cn/22509/list.htm
+https://iim.njtech.edu.cn/kydt/kyxm/gjjxm.htm</v>
+      </c>
+      <c r="I778" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第337项</v>
+      </c>
+    </row>
+    <row r="779" ht="52.5" customHeight="1">
+      <c r="A779" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B779" t="str" s="3">
+        <v>西安工程纺织智能装备两个已确认平台开放机制</v>
+      </c>
+      <c r="C779" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D779" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E779" t="str" s="3">
+        <v>查询："陕西省智能纺织装备研究院" "开放基金" / "西安市现代纺织装备智能制造" "开放课题" / "西安市现代智能纺织装备" "开放基金" / site:xpu.edu.cn "开放课题" "2027"；线索：功能性纺织材料及制品教育部重点实验室2026年度开放课题申报指南-功能性纺织材料及制品教育部重点实验室</v>
+      </c>
+      <c r="F779" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G779" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H779" t="str" s="3">
+        <v>https://klftpme.xpu.edu.cn/info/1042/1495.htm</v>
+      </c>
+      <c r="I779" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第338项</v>
+      </c>
+    </row>
+    <row r="780" ht="52.5" customHeight="1">
+      <c r="A780" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B780" t="str" s="3">
+        <v>北京信息科技现代测控及惯性声学平台年度资助补漏</v>
+      </c>
+      <c r="C780" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D780" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E780" t="str" s="3">
+        <v>查询：site:labmct.bistu.edu.cn "开放" "2026" / site:labmct.bistu.edu.cn "开放课题" "申请" / "惯性与声学传感技术" "开放基金" / "高端装备智能感知与控制" "开放基金"；线索：通知公告_北京信息科技大学现代测控技术教育部重点实验室；关于公布江苏省智能制造装备关键技术工程研究中心2025年度开放基金申请的通知-科技处；申请！一批次重点实验室课题基金申请指南 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑；全省极端环境材料表面与界面重点实验室开放基金项目申请指南 - 海洋关键材料全国重点实验室；非攻机器人实验室 | 西安交通大学；浣江实验室</v>
+      </c>
+      <c r="F780" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G780" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H780" t="str" s="3">
+        <v>https://labmct.bistu.edu.cn/xwgg/ggtz/index.html
+https://kjc.squ.edu.cn/info/1008/2302.htm
+https://www.letpub.com.cn/index.php?article_id=3242&amp;page=grant_article_details
+https://marinelab.nimte.cas.cn/news/notice/202606/t20260602_840372.html
+https://yanglaihao.github.io/
+https://huanjianglab.zju.edu.cn/product.aspx</v>
+      </c>
+      <c r="I780" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第339项</v>
+      </c>
+    </row>
+    <row r="781" ht="52.5" customHeight="1">
+      <c r="A781" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B781" t="str" s="3">
+        <v>贵州及云南省属高校机器人平台开放机制补漏</v>
+      </c>
+      <c r="C781" t="str" s="3">
+        <v>贵州/云南</v>
+      </c>
+      <c r="D781" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E781" t="str" s="3">
+        <v>查询：贵州理工学院 机器人 科研平台 开放基金 / 贵州师范大学 智能感知 重点实验室 开放课题 2026 2027 / 昆明学院 智能机器人 重点实验室 开放基金 / 云南民族大学 智能装备 重点实验室 开放基金；线索：人工智能实验室招标信息-人工智能实验室招标采购-采招网；贵州省粮油作物优质高效增产全省重点实验室2026年度开放课题申报指南（重点项目）；2026年实验室开放课题申请指南；贵州省生态特色食品新质化加工与贮藏 全省重点实验室开放课题申请指南；〖科研平台建设〗昆明学院获批立项建设云南省哲学社会科学重点实验室（试点）-昆明学院--昆明学院官方网站；2026年度云南省智能系统与计算重点实验室开放课题申请指南 - 云南大学信息学院</v>
+      </c>
+      <c r="F781" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G781" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H781" t="str" s="3">
+        <v>https://www.bidcenter.com.cn/zhaobiao/zbkeyw-75010.html
+https://st.gzu.edu.cn/2026/0518/c17883a273475/page.htm
+https://phy.sicnu.edu.cn/p/0/?StId=st_app_news_i_x639171130778395203
+https://st.gzu.edu.cn/2026/0316/c17883a265809/page.htm
+https://www.kmu.edu.cn/info/1066/14956.htm
+https://www.ise.ynu.edu.cn/page/166/?news_list_id=3</v>
+      </c>
+      <c r="I781" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第340项</v>
+      </c>
+    </row>
+    <row r="782" ht="52.5" customHeight="1">
+      <c r="A782" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B782" t="str" s="3">
+        <v>广西省属高校科研平台机器人开放机制补漏</v>
+      </c>
+      <c r="C782" t="str" s="3">
+        <v>广西</v>
+      </c>
+      <c r="D782" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E782" t="str" s="3">
+        <v>查询：广西科技大学 机器人 科研平台 开放基金 2026 2027 / 南宁师范大学 智能感知 重点实验室 开放基金 2026 / 桂林航天工业学院 机器人 重点实验室 开放基金 / 桂林电子科技大学 机器人 智能控制 开放课题 2027；线索：关于发布空间智能感知与大模型应用联合实验室2026年度开放基金课题申报指南的通知；〖广西高校重点实验室〗特种工程装备设计与智能驱动技术实验室-桂林航天工业学院；科研平台与团队-桂林航天工业学院；2025年度开放基金申请公告；基金简介----机器人与智能系统全国重点实验室；关于申报教育区块链与智能技术教育部重点实验室2026年度基金项目的通知</v>
+      </c>
+      <c r="F782" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G782" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H782" t="str" s="3">
+        <v>https://kyy.nuaa.edu.cn/2026/0604/c5817a400921/page.htm
+https://guat.edu.cn/info/1377/19646.htm
+https://www.guat.edu.cn/kxyj/kyptytd.htm
+https://robot.hit.edu.cn/2023/1016/c338a331151/page.htm
+https://rlab.sia.cas.cn/kfjj/jjjj/
+https://eb.gxnu.edu.cn/2026/0506/c11633a341305/page.htm</v>
+      </c>
+      <c r="I782" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第341项</v>
+      </c>
+    </row>
+    <row r="783" ht="52.5" customHeight="1">
+      <c r="A783" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B783" t="str" s="3">
+        <v>云南民族多域无人系统及昆明学院高校重点实验室基金补漏</v>
+      </c>
+      <c r="C783" t="str" s="3">
+        <v>云南</v>
+      </c>
+      <c r="D783" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E783" t="str" s="3">
+        <v>查询："多域无人系统信息化与智能化" "开放" 基金 / site:ymu.edu.cn "开放基金" 2026 2027 / site:kmu.edu.cn 高校重点实验室 智能 机器人 / site:kmu.edu.cn "开放课题" 2026 2027；线索：云南省难治性疾病细胞治疗研究重点实验室2026年度开放基金申请指南-昆明学院医学院；昆明学院三家单位获批云南省教育厅第八批云南省高校重点实验室-昆明学院科技处；关于开展2026年度省重点实验室建设申报工作的通知-昆明学院科技处；导师详细介绍一、个人基本情况杨波，博士研究生，2018 年 1 月获昆明理工大学矿物加工工程；昆明学院信息工程学院重点实验室设备采购项目竞争性谈判-资产与实验室管理处</v>
+      </c>
+      <c r="F783" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G783" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H783" t="str" s="3">
+        <v>https://yxy.kmu.edu.cn/info/1013/2851.htm
+https://kyc.kmu.edu.cn/info/1153/1236.htm
+https://kyc.kmu.edu.cn/info/1150/2054.htm
+https://hxx.kmu.edu.cn/__local/1/D2/15/16D49730C87F8AB9A39933E25AB_2C998CCA_2AB87.pdf?e=.pdf
+https://zcglc.kmu.edu.cn/info/1085/1624.htm</v>
+      </c>
+      <c r="I783" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第342项</v>
+      </c>
+    </row>
+    <row r="784" ht="52.5" customHeight="1">
+      <c r="A784" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B784" t="str" s="3">
+        <v>桂林航天校级机器人/低空融合平台年度补漏</v>
+      </c>
+      <c r="C784" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D784" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E784" t="str" s="3">
+        <v>查询：site:guat.edu.cn "机器人与焊接" "开放" / "现代工程装备流体驱动与智能控制" "开放" / "航空物流低空运输智能融合" "开放基金" / site:guat.edu.cn "开放基金" 2026 2027；线索：10项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑；关于2015年广西高校无人机遥测重点实验室开放课题和主任课题申请指南通知-科技处</v>
+      </c>
+      <c r="F784" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G784" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H784" t="str" s="3">
+        <v>https://www.letpub.com.cn/index.php?article_id=1576&amp;page=grant_article_details
+https://kjc.guat.edu.cn/info/1088/1539.htm</v>
+      </c>
+      <c r="I784" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第343项</v>
+      </c>
+    </row>
+    <row r="785" ht="52.5" customHeight="1">
+      <c r="A785" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B785" t="str" s="3">
+        <v>桂林航天自治区无人机/特种装备及高校重点实验室逐名开放机制</v>
+      </c>
+      <c r="C785" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D785" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E785" t="str" s="3">
+        <v>查询："小型无人机系统及应用工程研究中心" "开放" 基金 / "广西特种工程装备与控制" "开放" 课题 / "无人机系统与技术应用重点实验室" "开放基金" / "桂林航天工业学院" "智能检测与信息处理" "开放"；线索：关于2024年广西特种工程装备与控制重点实验室开放课题申报的通知-广西特种工程装备重点实验室；科技创新成果丰硕 开放开发精彩纷呈_央广网；2025第五届国际自主无人系统大会（ICAUS 2025）在上海顺利举办！ - 会展赛培坛 - 自动化网 ZiDongHua.com.cn ，自动化科技展示平台、“自动化者”人文交流平台。；关于发布空中交通管理系统与技术国家重点实验室2021年度开放基金课题指南的通知；技术基础实验，由此支撑起硬件基础综合实验、软件基础综合实验，以及对不同专业的不同实验项目与实验案例，像以网络为中心的计算实验、信息安全技术综合实验等；在更高层次上，支持研究探索型实验的设立，包括信息技术应用创新实验、综合性研究实验、产学研及校企联合工程性实验等；全面实施开放式实验教学，提供指定实验和任选实验，并结合教师科研课题、学科发展前沿、以及学生学习兴趣，指导学生完成开放式创新实验、发布学生科技创新基金项目。课外科技活动方面，有开放性实验以及各种校级、院级竞赛，有国际性、国家级和省级的赛事，像 ACM 程序设计大赛、世界大学生超算竞赛、大学生数学建模竞赛、CCF 大学生计算机系统与程序设计竞赛（CCSP）和计算机软件能力认证（CSP）、全国电子设计大赛、机器人大赛等，也有高水平职业技能竞赛、培训及认证考试等活动；此外，中心还与相关科技企业及创投基金合作建设了示范性大学生创新创业实践基地，面向广州大学城及省内各高校作示范性辐射和推广，重点支持无人机、金融大数据等方向，每年支持学生创业团队 3-5 个。根据不同专业、不同基础、不同能力层次，中心将实验教学内容合理分布在基础实验教学平台（如数字电路、模拟电路、程序设计语言、计算机应用基础等）、学科专业实验教学平台（电子与电路、数字逻辑、嵌入式系统、编译原理、数据库系统、操作系统、人工智能、数据挖掘、软件工程、云计算技术、数据存储、计算机网络、通信原理、数学建模、微电子工艺等）、研究型实验平台（依托国家超级计算广州中心、国家数字家庭工程技术研究中心、教育部信息伪装与对抗重点实验室、广东省信息安全技术重点实验室、教育部智能传感网络重点实验室）、开放式创新实验平台（包括移动终端创新实验室、中大-Cisco 网络实验室、中大-Apple 实验室、中大-HP 动漫实验室、中大-欧姆龙创新实验室、中大-Intel 嵌入式实验室、电子设计大赛实训中心、ACM 实训中心等）这四个层次上，以满足各类学生对基础技能、专业技能、科研技能以及工程研发技能等不同层次的学习需求。；10项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F785" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G785" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H785" t="str" s="3">
+        <v>https://seec.guat.edu.cn/info/1133/1103.htm
+https://gx.cnr.cn/cnrgx/kjjy/20210325/t20210325_525445219.shtml
+https://www.zidonghua.com.cn/news/exhibition/77966.html
+https://keyanpro.com/Htmls/htmlss/gov/gov2021-09/gov2021-09-09/proGov23453.html
+https://cse.sysu.edu.cn/eclc/sites/default/files/2023-07/sysu-report-2020.pdf
+https://www.letpub.com.cn/index.php?article_id=1576&amp;page=grant_article_details</v>
+      </c>
+      <c r="I785" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第344项</v>
+      </c>
+    </row>
+    <row r="786" ht="52.5" customHeight="1">
+      <c r="A786" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B786" t="str" s="3">
+        <v>桂林航天高校工程研究中心逐名开放机制</v>
+      </c>
+      <c r="C786" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D786" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E786" t="str" s="3">
+        <v>查询："特种工程装备设计与智能驱动" "开放" 基金 / "低空智能巡检技术应用" "开放基金" / "非标智能装备与流程控制" "开放课题" / "空天地信息融合与控制" "开放" 基金；线索：关于印发《2025年度省基础研究计划项目指南》及组织申报项目的通知；关于2026年广西特种工程装备与控制重点实验室开放课题申报的通知 - 矿业智能科技服务平台；〖湖南师范大学主办|早鸟优惠〗2026年信息技术、控制工程与北斗导航国际学术会议（ITCEBN 2026）_艾思科蓝_学术一站式服务平台；南京邮电大学2026年硕士研究生招生学院及专业方向介绍 - 中国考研网</v>
+      </c>
+      <c r="F786" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G786" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H786" t="str" s="3">
+        <v>https://ffxy.yzpc.edu.cn/2025/0221/c3491a67235/page.htm
+https://m.intelmining2018.com/sys-nd/2578.html
+https://m.ais.cn/attendees/index/QVQRNV
+https://www.chinakaoyan.com/info/article/id/637385.shtml</v>
+      </c>
+      <c r="I786" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第345项</v>
+      </c>
+    </row>
+    <row r="787" ht="52.5" customHeight="1">
+      <c r="A787" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B787" t="str" s="3">
+        <v>桂林航天特种工程装备及无人机基金各年度官方公告发现</v>
+      </c>
+      <c r="C787" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D787" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E787" t="str" s="3">
+        <v>查询：site:seec.guat.edu.cn "2026" "开放课题" / site:seec.guat.edu.cn "2027" "开放" / site:guat.edu.cn "无人机遥测" "开放课题" / site:guat.edu.cn "特种工程装备" "2025" "开放课题"；线索：关于2015年广西高校无人机遥测重点实验室开放课题和主任课题申请指南通知-科技处；广西特种工程装备重点实验室</v>
+      </c>
+      <c r="F787" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G787" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H787" t="str" s="3">
+        <v>https://kjc.guat.edu.cn/info/1088/1539.htm
+https://seec.guat.edu.cn/</v>
+      </c>
+      <c r="I787" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第346项</v>
+      </c>
+    </row>
+    <row r="788" ht="52.5" customHeight="1">
+      <c r="A788" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B788" t="str" s="3">
+        <v>西安工程大学</v>
+      </c>
+      <c r="C788" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D788" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E788" t="str" s="3">
+        <v>功能性纺织材料及制品教育部重点实验室；2026；N053；官方2026完整正文已读；智能可穿戴任务未细化，办法/申请表验证码</v>
+      </c>
+      <c r="F788" t="str" s="3">
+        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
+      </c>
+      <c r="G788" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H788" t="str" s="3">
+        <v>https://klftpme.xpu.edu.cn/info/1042/1495.htm</v>
+      </c>
+      <c r="I788" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="789" ht="52.5" customHeight="1">
+      <c r="A789" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B789" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="C789" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D789" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E789" t="str" s="3">
+        <v>广西高校无人机遥测重点实验室开放课题（主任基金仅内部，未纳入）；2015；N054；正式2015完整公告及成果额度对照表已读；2个DOC首次不可解析</v>
+      </c>
+      <c r="F789" t="str" s="3">
+        <v>2015历史机制；2 DOC首次工具不可解析/返回异常，需人工下载；Top范围、专利折算正文“授权含申请1.5万（申请.5+授权1）”与表“授权发明1.5万”不完全一致须确认；外拨/支付节点未载。现平台名称是否重组为目录无人机系统与技术应用未证实，不直接合并年度。</v>
+      </c>
+      <c r="G789" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H789" t="str" s="3">
+        <v>https://kjc.guat.edu.cn/info/1088/1539.htm</v>
+      </c>
+      <c r="I789" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="790" ht="52.5" customHeight="1">
+      <c r="A790" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B790" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="C790" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D790" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E790" t="str" s="3">
+        <v>广西特种工程装备与控制重点实验室；2024；N055；正式2024年度完整公告已核；管理办法与申请书首次验证码</v>
+      </c>
+      <c r="F790" t="str" s="3">
+        <v>2附件验证码；2024办法成果/署名/IP/资格细则及外拨比例未核。2026已有主任基金E069只限本校，不能由第三方2026开放标题或2024外拨机制认当期对外受理。</v>
+      </c>
+      <c r="G790" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H790" t="str" s="3">
+        <v>https://seec.guat.edu.cn/info/1133/1103.htm</v>
+      </c>
+      <c r="I790" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="791" ht="52.5" customHeight="1">
+      <c r="A791" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B791" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="C791" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D791" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E791" t="str" s="3">
+        <v>官方完整科研平台/团队32项，统计截至2025-01-09；确认自治区特种工程装备与控制、小型无人机；高校无人机、智能检测、特种驱动、低空巡检、非标装备流程、低空运输、空天地融合及校级机器人焊接/流体智能控制等12项逐名机制查询。</v>
+      </c>
+      <c r="F791" t="str" s="3">
+        <v>目录已读且12项逐名查过不等于2026现行名单全部更新；其余物联网/虚拟现实/汽车平台年度机制仍需补，2027未获正式公告；不把校级教学开放当有钱基金。</v>
+      </c>
+      <c r="G791" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H791" t="str" s="3">
+        <v>https://www.guat.edu.cn/kxyj/kyptytd.htm</v>
+      </c>
+      <c r="I791" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="792" ht="52.5" customHeight="1">
+      <c r="A792" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B792" t="str" s="3">
+        <v>桂林航天工业学院</v>
+      </c>
+      <c r="C792" t="str" s="3">
+        <v>广西·桂林</v>
+      </c>
+      <c r="D792" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E792" t="str" s="3">
+        <v>特种2024N055明确机器人姿态力检测反馈、移动平台机械臂实时协同规划及3—6万部分外拨；2015无人机N05414任务和成果金额折算表全文核。</v>
+      </c>
+      <c r="F792" t="str" s="3">
+        <v>2026主任基金E069仅本校已剔除复用；第三方2026开放题未获对应官方当期指南，不能推定受理；2024办法与2015DOC待人工，不套年份。</v>
+      </c>
+      <c r="G792" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H792" t="str" s="3">
+        <v>https://seec.guat.edu.cn/info/1133/1103.htm
+https://kjc.guat.edu.cn/info/1088/1539.htm</v>
+      </c>
+      <c r="I792" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="793" ht="52.5" customHeight="1">
+      <c r="A793" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B793" t="str" s="3">
+        <v>西安工程大学</v>
+      </c>
+      <c r="C793" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D793" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E793" t="str" s="3">
+        <v>机电完整科研平台2项：陕西智能纺织装备研究院、西安市现代纺织装备智能制造重点实验室；具体自动落纱/落布、机器视觉验布、柔性检测、线性驱动/电控/传感任务介绍已读，两个名称及别名逐名基金机制查询。</v>
+      </c>
+      <c r="F793" t="str" s="3">
+        <v>介绍已有产学研项目/技术成果不等于实验室设对外基金；2026—2027没定位当年开放公告不证明没有；其他学院目录未齐。</v>
+      </c>
+      <c r="G793" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H793" t="str" s="3">
+        <v>https://jidianxy.xpu.edu.cn/Subject_research/kypt.htm</v>
+      </c>
+      <c r="I793" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="794" ht="52.5" customHeight="1">
+      <c r="A794" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B794" t="str" s="3">
+        <v>西安工程大学</v>
+      </c>
+      <c r="C794" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D794" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E794" t="str" s="3">
+        <v>功能性纺织材料2026完整当年五方向N053，智能纤维/可穿戴未具体到机器人/HRI任务，优先外部、重点5万一般2万、论文+展示产品要求明确。</v>
+      </c>
+      <c r="F794" t="str" s="3">
+        <v>两附件首次验证码；任务和外拨/IP仍不足，已截止待核不正式相关历史/首页，平台简介加工装备不代替本年度任务。</v>
+      </c>
+      <c r="G794" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H794" t="str" s="3">
+        <v>https://klftpme.xpu.edu.cn/info/1042/1495.htm</v>
+      </c>
+      <c r="I794" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="795" ht="52.5" customHeight="1">
+      <c r="A795" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B795" t="str" s="3">
+        <v>北京信息科技大学</v>
+      </c>
+      <c r="C795" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D795" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E795" t="str" s="3">
+        <v>官方科研机构目录定位；现代测控教育部实验室开放课题历年/2026—2027及惯性声学、市高端装备感知基地逐名基金机制查询。</v>
+      </c>
+      <c r="F795" t="str" s="3">
+        <v>校级目录首次超时、现代测控通知目录502，合并人工目录入口；已获别家国家室开放课题新闻不当本基地发钱公告；现代测控2020结果不是受理指南。</v>
+      </c>
+      <c r="G795" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H795" t="str" s="3">
+        <v>https://www.bistu.edu.cn/kxyj/kyjg/index.html
+https://labmct.bistu.edu.cn/xwgg/ggtz/index.html</v>
+      </c>
+      <c r="I795" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="796" ht="52.5" customHeight="1">
+      <c r="A796" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B796" t="str" s="3">
+        <v>南京工业大学</v>
+      </c>
+      <c r="C796" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D796" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E796" t="str" s="3">
+        <v>自动化实验教学中心完整介绍：20余间专业室、5系本科教学、机器人夏令营等共享服务，核为教学平台。</v>
+      </c>
+      <c r="F796" t="str" s="3">
+        <v>不是已证对外资助机制；智能制造研究院国家级已承担项目列表不当开放征集；全校相关科研平台名单未齐。</v>
+      </c>
+      <c r="G796" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H796" t="str" s="3">
+        <v>https://eecs.njtech.edu.cn/lab/zxjj.htm</v>
+      </c>
+      <c r="I796" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="797" ht="52.5" customHeight="1">
+      <c r="A797" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B797" t="str" s="3">
+        <v>常州大学</v>
+      </c>
+      <c r="C797" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D797" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E797" t="str" s="3">
+        <v>工业母机工程研究院/龙城合作首页完整核：4研究方向，2026科技项目/研究生专项/2025通知；既有2026M175仅机械大数据学院内部遴选及2025历史通知复用，不重开。</v>
+      </c>
+      <c r="F797" t="str" s="3">
+        <v>首页定位研究合作不新增同一基金；校内专项与外部主任基金不能当本人项目，其他学院目录仍未齐。</v>
+      </c>
+      <c r="G797" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H797" t="str" s="3">
+        <v>https://iimt.cczu.edu.cn/</v>
+      </c>
+      <c r="I797" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="798" ht="52.5" customHeight="1">
+      <c r="A798" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B798" t="str" s="3">
+        <v>云南民族大学</v>
+      </c>
+      <c r="C798" t="str" s="3">
+        <v>云南·昆明</v>
+      </c>
+      <c r="D798" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E798" t="str" s="3">
+        <v>正式高校多域无人系统信息化与智能化重点实验室介绍定位；2026—2027/长期开放基金逐名查询。</v>
+      </c>
+      <c r="F798" t="str" s="3">
+        <v>介绍首次超时交人工；没有正式通知/金额，未加项目；完整大学科研平台目录未齐。</v>
+      </c>
+      <c r="G798" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H798" t="str" s="3">
+        <v>https://web.ymu.edu.cn/dqxxgc/info/1381/3761.htm</v>
+      </c>
+      <c r="I798" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="799" ht="52.5" customHeight="1">
+      <c r="A799" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B799" t="str" s="3">
+        <v>福建/江西本轮公告对账</v>
+      </c>
+      <c r="C799" t="str" s="3">
+        <v>福建/江西</v>
+      </c>
+      <c r="D799" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E799" t="str" s="3">
+        <v>闽江2026M088、厦门工学院柔性制造2026M102、南昌航空机载2026S001及智慧建筑2026N040已入台账复用，省属机构逐名发现没有新独立批次。</v>
+      </c>
+      <c r="F799" t="str" s="3">
+        <v>两南昌航空正文复读确认相同公告，无新条目；省属其他机构完整目录/平台年份仍未齐，不由零新增判断完成。</v>
+      </c>
+      <c r="G799" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H799" t="str" s="3">
+        <v>https://www.mju.edu.cn/imlab/2026/0724/c2194a223109/page.htm
+https://www.xit.edu.cn/kxyj/2026/0206/c1174a83598/page.htm
+https://www.nchu.edu.cn/xwzx/xngg/content_196002
+https://zhjz.nchu.edu.cn/tzgg/content_196076</v>
+      </c>
+      <c r="I799" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -42948,7 +44008,7 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="23" ht="96" customHeight="1">
+    <row r="23" ht="132" customHeight="1">
       <c r="A23" t="str" s="18">
         <v>已截止</v>
       </c>
@@ -44682,21 +45742,61 @@
     </row>
     <row r="109" ht="96" customHeight="1">
       <c r="A109" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B109" t="n" s="13">
+        <v>42175</v>
+      </c>
+      <c r="C109" t="str" s="14">
+        <v>桂林航天工业学院·广西高校无人机遥测重点实验室开放课题（主任基金仅内部，未纳入）</v>
+      </c>
+      <c r="D109" t="str" s="15">
+        <v>实际14项无人机任务：飞控模型、航迹规划、姿态控制、影像匹配、多用途系统/载荷设计、数传图传二次开发、行业应用、多机多任务协作、目标识别跟踪、特殊用途无人机、遥感系统、北斗飞控及无人机热点。</v>
+      </c>
+      <c r="E109" t="str" s="15">
+        <v>校外开放1—5万元/项拟2—3项；结题按实际成果折算增减资助，不承诺固定到账。主任基金3—6/3—4万元面向固定人员，不计本人对外资助金额。</v>
+      </c>
+      <c r="F109" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="110" ht="96" customHeight="1">
+      <c r="A110" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B110" t="n" s="13">
+        <v>45442</v>
+      </c>
+      <c r="C110" t="str" s="14">
+        <v>桂林航天工业学院·广西特种工程装备与控制重点实验室</v>
+      </c>
+      <c r="D110" t="str" s="15">
+        <v>2024方向二明确特种工程机器人：矿山/隧道/电力线路/抢险救灾/危险环境，姿态和受力检测、运动反馈控制、环境认知定位；非结构环境移动平台行走路径与机械臂关节实时协同规划。方向一含机构动力建模、工作状态辨识控制；材料方向并非凭实验室名称收录。</v>
+      </c>
+      <c r="E110" t="str" s="15">
+        <v>3—6万元/项；计划8—10项，各方向2—3项。</v>
+      </c>
+      <c r="F110" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="111" ht="96" customHeight="1">
+      <c r="A111" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B109" t="n" s="13">
+      <c r="B111" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C109" t="str" s="14">
+      <c r="C111" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D109" t="str" s="15">
+      <c r="D111" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E109" t="str" s="15">
+      <c r="E111" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F109" t="str" s="16">
+      <c r="F111" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -44892,8 +45992,8 @@
     <hyperlink ref="F100" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C101" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F101" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F109" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C109" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F111" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C111" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F102" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -44918,6 +46018,10 @@
     <hyperlink ref="F22" ns1:id="rIdResume108"/>
     <hyperlink ref="C23" location="'02项目完整详情'!A200" display="项目完整详情"/>
     <hyperlink ref="F23" ns1:id="rIdResume109"/>
+    <hyperlink ref="C109" location="'02项目完整详情'!A203" display="项目完整详情"/>
+    <hyperlink ref="F109" ns1:id="rIdResume110"/>
+    <hyperlink ref="C110" location="'02项目完整详情'!A204" display="项目完整详情"/>
+    <hyperlink ref="F110" ns1:id="rIdResume111"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -47015,24 +48119,50 @@
         <v>线索待核·已截止</v>
       </c>
       <c r="B73" t="n" s="13">
-        <v>46249</v>
+        <v>46158</v>
       </c>
       <c r="C73" t="str" s="14">
-        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+        <v>西安工程大学·功能性纺织材料及制品教育部重点实验室</v>
       </c>
       <c r="D73" t="str" s="15">
-        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
       </c>
       <c r="E73" t="str" s="15">
-        <v>合同金额2万元/项；计划≤10项。</v>
+        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
       </c>
       <c r="F73" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G73" t="str" s="3">
+        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
+      </c>
+      <c r="H73" t="str" s="3">
+        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
+      </c>
+    </row>
+    <row r="74" ht="132" customHeight="1">
+      <c r="A74" t="str" s="20">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B74" t="n" s="13">
+        <v>46249</v>
+      </c>
+      <c r="C74" t="str" s="14">
+        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+      </c>
+      <c r="D74" t="str" s="15">
+        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+      </c>
+      <c r="E74" t="str" s="15">
+        <v>合同金额2万元/项；计划≤10项。</v>
+      </c>
+      <c r="F74" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G74" t="str" s="3">
         <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
       </c>
-      <c r="H73" t="str" s="3">
+      <c r="H74" t="str" s="3">
         <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
       </c>
     </row>
@@ -47180,8 +48310,10 @@
     <hyperlink ref="F71" ns1:id="rIdResume73"/>
     <hyperlink ref="C72" location="'02项目完整详情'!A199" display="项目完整详情"/>
     <hyperlink ref="F72" ns1:id="rIdResume74"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A201" display="项目完整详情"/>
-    <hyperlink ref="F73" ns1:id="rIdResume75"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A201" display="项目完整详情"/>
+    <hyperlink ref="F74" ns1:id="rIdResume75"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A202" display="项目完整详情"/>
+    <hyperlink ref="F73" ns1:id="rIdResume76"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -18204,7 +18204,7 @@
         <v>同一联合公告两平台合并为1独立轮次，不拆成两笔基金；2025/2024另有索引但未核不套条款。</v>
       </c>
     </row>
-    <row r="202" ht="132" customHeight="1">
+    <row r="202" ht="147" customHeight="1">
       <c r="A202" t="str" s="3">
         <v>N053</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>申请条件、产品指标和优先外部已确认，但任务证据不足保持待核；不以平台简介智能加工装备判断本轮已相关。</v>
       </c>
     </row>
-    <row r="203" ht="132" customHeight="1">
+    <row r="203" ht="177" customHeight="1">
       <c r="A203" t="str" s="3">
         <v>N054</v>
       </c>
@@ -43541,6 +43541,448 @@
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
+    <row r="800" ht="52.5" customHeight="1">
+      <c r="A800" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B800" t="str" s="3">
+        <v>吉林省级高校人工智能及机器人平台认定名单查漏</v>
+      </c>
+      <c r="C800" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D800" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E800" t="str" s="3">
+        <v>查询：site:kjt.jl.gov.cn 重点实验室 智能机器人 名单 / site:jledu.gov.cn 重点实验室 机器人 智能装备 / 北华大学 机器人 重点实验室 开放基金 2026 / 长春工程学院 机器人 重点实验室 开放基金 2026；线索：2026年度开放基金评审结果公告；2026年度开放课题申请公告；管理办法----机器人与智能系统全国重点实验室；材料与表面技术教育部重点实验室2026年开放基金项目申报通知；2026年度稀土重点实验室（中国科学院）开放基金申请指南----中国科学院赣江创新研究院；省科技厅副厅长赵辉到长春理工大学调研省重点实验室建设情况</v>
+      </c>
+      <c r="F800" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G800" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H800" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://rlab.sia.cas.cn/kfjj/glbf/
+https://mse.xhu.edu.cn/_t316/b6/b3/c810a243379/page.htm
+https://www.gia.cas.cn/tzgg/202608/t20260804_8259053.html
+https://kjt.jl.gov.cn/xwzx/tpxw/201911/t20191115_6142327.html</v>
+      </c>
+      <c r="I800" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第347项</v>
+      </c>
+    </row>
+    <row r="801" ht="52.5" customHeight="1">
+      <c r="A801" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B801" t="str" s="3">
+        <v>辽宁省级高校机器人平台认定名单查漏</v>
+      </c>
+      <c r="C801" t="str" s="3">
+        <v>辽宁</v>
+      </c>
+      <c r="D801" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E801" t="str" s="3">
+        <v>查询：site:kjt.ln.gov.cn 重点实验室 智能机器人 名单 2026 / site:jyt.ln.gov.cn 重点实验室 机器人 智能装备 / 沈阳工业大学 科研平台 重点实验室 目录 / 辽宁科技大学 科研平台 机器人 重点实验室；线索：沈阳工业大学重点实验室-中国高校库-中国高校之窗；校级平台-首页科学研究；辽宁省智能科学与智能系统重点实验室简介；沈阳工业大学2026年博士研究生招生章程-沈阳工业大学研究生院；辽宁省机器视觉重点实验室-沈阳工业大学人工智能学院；研究内容：</v>
+      </c>
+      <c r="F801" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G801" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H801" t="str" s="3">
+        <v>https://www.gx211.cn/collegemanage/content332_06.shtml
+https://kxyj.situ.edu.cn/kypt/xjpt.htm
+https://www.ise.neu.edu.cn/2024/0603/c5332a256279/pagem.htm
+https://yjsxy.sut.edu.cn/info/1321/9841.htm
+https://sai.sut.edu.cn/info/1020/5254.htm
+https://kjt.ln.gov.cn/kjt/attachDir/2025/11/2025110716055421307.pdf</v>
+      </c>
+      <c r="I801" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第348项</v>
+      </c>
+    </row>
+    <row r="802" ht="52.5" customHeight="1">
+      <c r="A802" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B802" t="str" s="3">
+        <v>黑龙江省级及省属高校机器人实验室认定名单查漏</v>
+      </c>
+      <c r="C802" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D802" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E802" t="str" s="3">
+        <v>查询：site:kjt.hlj.gov.cn 重点实验室 机器人 智能 装备 名单 2025 2026 / site:jyt.hlj.gov.cn 重点实验室 智能装备 机器人 / 黑龙江工程学院 智能机器人 重点实验室 / 齐齐哈尔大学 机器人 智能装备 开放基金 2026；线索：黑龙江工程学院提档升级专业教学实验室项目(二次)招标公告-黑龙江工程学院；机器人工程实验室-船舶导航与控制实验教学中心；教育部重点实验室；重点实验室/中心/基地；〖省重点实验室〗黑龙江省复杂智能系统与集成重点实验室；2026年度开放基金评审结果公告</v>
+      </c>
+      <c r="F802" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G802" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H802" t="str" s="3">
+        <v>https://www.hljit.edu.cn/info/1481/75921.htm
+https://secn.hrbeu.edu.cn/info/1022/1031.htm
+https://jixie.hrbust.edu.cn/jybzdsys/
+https://www.hit.edu.cn/11577/list.htm
+https://kjc.hrbust.edu.cn/2021/1007/c3208a65565/page.htm
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm</v>
+      </c>
+      <c r="I802" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第349项</v>
+      </c>
+    </row>
+    <row r="803" ht="52.5" customHeight="1">
+      <c r="A803" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B803" t="str" s="3">
+        <v>北华大学及长春工程科研平台准确目录发现</v>
+      </c>
+      <c r="C803" t="str" s="3">
+        <v>吉林</v>
+      </c>
+      <c r="D803" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E803" t="str" s="3">
+        <v>查询：site:beihua.edu.cn 科研平台 重点实验室 机器人 / site:beihua.edu.cn "开放基金" / site:ccit.edu.cn 科研平台 重点实验室 智能 / site:ccit.edu.cn "开放基金"；线索：关于做好科研平台安全工作的通知-长春工程学院-科学研究处；吉林省城市污水处理重点实验室-长春工程学院市政与环境工程学院；重点实验室简介-长春工程学院 吉林省城市污水重点实验室；科研机构-长春工程学院-科学研究处；长春工程学院科研平台建设与管理办法；科研平台-长春工程学院土木工程学院</v>
+      </c>
+      <c r="F803" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G803" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H803" t="str" s="3">
+        <v>https://kjc.ccit.edu.cn/info/1024/1464.htm
+https://szhjgc.ccit.edu.cn/info/1051/1151.htm
+https://yjzx08.ccit.edu.cn/info/1002/1346.htm
+https://kjc.ccit.edu.cn/kyjg.htm
+https://kjc.ccit.edu.cn/__local/1/9D/BD/4E06313ECB1775A26683A27DEBD_E17BBB01_B334D.pdf
+https://tmxy.ccit.edu.cn/kxyj/kypt.htm</v>
+      </c>
+      <c r="I803" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第350项</v>
+      </c>
+    </row>
+    <row r="804" ht="52.5" customHeight="1">
+      <c r="A804" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B804" t="str" s="3">
+        <v>黑龙江工程及齐齐哈尔大学科研平台准确目录发现</v>
+      </c>
+      <c r="C804" t="str" s="3">
+        <v>黑龙江</v>
+      </c>
+      <c r="D804" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E804" t="str" s="3">
+        <v>查询：site:hljit.edu.cn 科研平台 重点实验室 智能 / site:hljit.edu.cn "开放基金" / site:qqhru.edu.cn 科研平台 重点实验室 智能 / site:qqhru.edu.cn "开放课题"；线索：科研平台-汽车与交通工程学院；喜报：我校获批一个省工程技术研究中心和一个省重点实验室-齐齐哈尔大学；通信与信息系统学科学术学位硕士研究生培养方案；黑龙江工程学院教育部重点实验室建设项目(二次)结果公告-黑龙江工程学院；化学工程与技术学科学术学位硕士研究生培养方案（学科代码：0817　　授予工学硕士学位）一、学科简介及研究方向化学工程与技术是研究化学工业及相关过程工业中的物质与能量转化，物质；齐齐哈尔大学学术型硕士学位研究生培养方案总则</v>
+      </c>
+      <c r="F804" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G804" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H804" t="str" s="3">
+        <v>https://www.hljit.edu.cn/qcgcxy/info/1551/9405.htm
+https://www.qqhru.edu.cn/info/1142/18523.htm
+https://www.qqhru.edu.cn/__local/3/8C/2C/195BCE6BDC404D220E0DF348F8F_2A960F50_863A5.pdf
+https://www.hljit.edu.cn/info/1401/14521.htm
+https://www.qqhru.edu.cn/__local/A/D0/07/6B5A6BC5499FF29E1A45E8E5F3A_28B15A68_3FD2A.pdf
+https://www.qqhru.edu.cn/__local/F/DA/FE/41D69D7880AC04BEF451005638C_9B970708_32B63.pdf</v>
+      </c>
+      <c r="I804" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第351项</v>
+      </c>
+    </row>
+    <row r="805" ht="52.5" customHeight="1">
+      <c r="A805" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B805" t="str" s="3">
+        <v>沈阳工业大学正确sut域名科研平台及机器视觉外部资助核实</v>
+      </c>
+      <c r="C805" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D805" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E805" t="str" s="3">
+        <v>查询：site:sut.edu.cn 科研平台 重点实验室 目录 / site:sut.edu.cn "机器视觉" "开放基金" / site:sut.edu.cn "开放课题" "2026" / site:sut.edu.cn "开放基金" "2027"；线索：重点实验室简介-沈阳工业大学新能源研究院；简介-沈阳工业大学研究生院；创新平台-信息科学与工程学院；风能科普基地简介-沈阳工业大学新能源研究院；一、研究生教育发展整体概况；创新型风电设计基础理论研究与装备开发-沈阳工业大学新能源研究院</v>
+      </c>
+      <c r="F805" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G805" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H805" t="str" s="3">
+        <v>https://syfd.sut.edu.cn/jspt/zdsysjj.htm
+https://yjsxy.sut.edu.cn/fwzn/jj.htm
+https://sise.sut.edu.cn/kxyj/cxpt.htm
+https://syfd.sut.edu.cn/jspt/fnkpjdjj.htm
+https://cfdea.sut.edu.cn/2021yjsndzlbg.pdf
+https://syfd.sut.edu.cn/kynl/cxxfdsjjcllyjyzbkf.htm</v>
+      </c>
+      <c r="I805" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第352项</v>
+      </c>
+    </row>
+    <row r="806" ht="52.5" customHeight="1">
+      <c r="A806" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B806" t="str" s="3">
+        <v>长春工程高端装备/先进制造/人工智能科研平台基金逐名补漏</v>
+      </c>
+      <c r="C806" t="str" s="3">
+        <v>吉林·长春</v>
+      </c>
+      <c r="D806" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E806" t="str" s="3">
+        <v>查询：site:ccit.edu.cn "高端装备智能制造" "开放基金" / site:ccit.edu.cn "先进制造技术" "开放课题" / site:ccit.edu.cn "人工智能技术研究院" "开放" 基金 / site:ccit.edu.cn "高端智能设施农业装备" "开放" 基金；线索：长春工程学院2024年全日制专业学位硕士研究生招生简章-长春工程学院；长春工程学院2023年全日制专业学位硕士研究生招生简章-长春工程学院；长春工程学院2024年全日制专业学位硕士研究生招生简章-长春工程学院-研究生处</v>
+      </c>
+      <c r="F806" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G806" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H806" t="str" s="3">
+        <v>https://www.ccit.edu.cn/info/1008/4519.htm
+https://www.ccit.edu.cn/info/1008/4417.htm
+https://yjsgzc.ccit.edu.cn/info/1103/1040.htm</v>
+      </c>
+      <c r="I806" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第353项</v>
+      </c>
+    </row>
+    <row r="807" ht="52.5" customHeight="1">
+      <c r="A807" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B807" t="str" s="3">
+        <v>沈阳工业航空健康及计算平台、长春工程汽车检测平台补漏</v>
+      </c>
+      <c r="C807" t="str" s="3">
+        <v>辽宁·沈阳/吉林·长春</v>
+      </c>
+      <c r="D807" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E807" t="str" s="3">
+        <v>查询："沈阳市航空发动机健康管理重点实验室" "开放" 基金 / "沈阳市先进计算与信创技术重点实验室" "开放基金" / site:ccit.edu.cn "汽车零部件制造在线检测" "开放基金" / site:ccit.edu.cn "汽车集成制造技术" "开放课题"；线索：辽宁省航空推进系统先进测试技术重点实验室 2023年开放课题申请指南-沈阳航空航天大学航空发动机学院；中国战略性新兴产业研究与发展·内燃机 | PDF</v>
+      </c>
+      <c r="F807" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G807" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H807" t="str" s="3">
+        <v>https://fdj.sau.edu.cn/info/1085/1243.htm
+https://www.scribd.com/document/1071415831/%E4%B8%AD%E5%9B%BD%E6%88%98%E7%95%A5%E6%80%A7%E6%96%B0%E5%85%B4%E4%BA%A7%E4%B8%9A%E7%A0%94%E7%A9%B6%E4%B8%8E%E5%8F%91%E5%B1%95-%E5%86%85%E7%87%83%E6%9C%BA</v>
+      </c>
+      <c r="I807" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第354项</v>
+      </c>
+    </row>
+    <row r="808" ht="52.5" customHeight="1">
+      <c r="A808" t="str" s="3">
+        <v>2026-10-09港澳及东北逐平台补漏</v>
+      </c>
+      <c r="B808" t="str" s="3">
+        <v>沈阳工业信息学院6平台已确认名称基金逐项补漏</v>
+      </c>
+      <c r="C808" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D808" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E808" t="str" s="3">
+        <v>查询："辽宁省高校先进在线检测技术实验室" "开放基金" / "辽宁省机器视觉重点实验室" "开放课题" / "辽宁省输油气管道内检测重点实验室" "开放" 基金 / "辽宁省长输油气管道内检测工程研究中心" "开放课题"；线索：三瑟科技 · 实验室管理与实训信息化整体方案；大连理工大学主页平台管理系统 Yang Xin Home Home；中国战略性新兴产业研究与发展·内燃机 | PDF</v>
+      </c>
+      <c r="F808" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G808" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H808" t="str" s="3">
+        <v>https://www.sansekeji.com/
+https://faculty.dlut.edu.cn/yangxin/en/index/949138/list/index.htm
+https://www.scribd.com/document/1071415831/%E4%B8%AD%E5%9B%BD%E6%88%98%E7%95%A5%E6%80%A7%E6%96%B0%E5%85%B4%E4%BA%A7%E4%B8%9A%E7%A0%94%E7%A9%B6%E4%B8%8E%E5%8F%91%E5%B1%95-%E5%86%85%E7%87%83%E6%9C%BA</v>
+      </c>
+      <c r="I808" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第355项</v>
+      </c>
+    </row>
+    <row r="809" ht="52.5" customHeight="1">
+      <c r="A809" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B809" t="str" s="3">
+        <v>沈阳工业大学</v>
+      </c>
+      <c r="C809" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D809" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E809" t="str" s="3">
+        <v>正确信息学院sut.edu.cn创新目录6项全文：市航空发动机健康、市先进计算信创、省高校先进在线检测、省机器视觉、省长输管道检测工程中心、省输油气管道内检重点室；6名称逐名2026—2027及历史基金查询。</v>
+      </c>
+      <c r="F809" t="str" s="3">
+        <v>sai机器视觉介绍首次不可访问交人工，未从同一介绍另路反复获取；信息学院目录可读保留。搜索situ.edu.cn是沈阳理工，不计沈阳工业覆盖；全校机械/人工智能学院完整目录仍缺。</v>
+      </c>
+      <c r="G809" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H809" t="str" s="3">
+        <v>https://sise.sut.edu.cn/kxyj/cxpt.htm
+https://sai.sut.edu.cn/info/1020/5254.htm</v>
+      </c>
+      <c r="I809" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="810" ht="52.5" customHeight="1">
+      <c r="A810" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B810" t="str" s="3">
+        <v>长春工程学院</v>
+      </c>
+      <c r="C810" t="str" s="3">
+        <v>吉林·长春</v>
+      </c>
+      <c r="D810" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E810" t="str" s="3">
+        <v>科研机构完整目录44项（政府批38、自设6）已读；高端装备智造、先进制造研究院、人工智能研究院、高端智能设施农业、汽车零部件在线检测、汽车集成制造6项逐名开放机制查询。</v>
+      </c>
+      <c r="F810" t="str" s="3">
+        <v>未定位本校对外正式公告/金额；38政府名单中其他平台具体年度机制尚未逐项核，配电/城市文化等不因智能词直接判相关；目录现行具体统计年月未载。</v>
+      </c>
+      <c r="G810" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H810" t="str" s="3">
+        <v>https://kjc.ccit.edu.cn/kyjg.htm</v>
+      </c>
+      <c r="I810" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="811" ht="52.5" customHeight="1">
+      <c r="A811" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B811" t="str" s="3">
+        <v>黑龙江工程学院</v>
+      </c>
+      <c r="C811" t="str" s="3">
+        <v>黑龙江·哈尔滨</v>
+      </c>
+      <c r="D811" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E811" t="str" s="3">
+        <v>学校及电气信息/汽车交通科研目录线索发现；正确hljit域名开放基金查询。</v>
+      </c>
+      <c r="F811" t="str" s="3">
+        <v>电气学院完整简介首超时交人工；设备采购/教学建设不当外部科研资金；汽车学院目录、全校名单及平台2026—2027尚未齐。</v>
+      </c>
+      <c r="G811" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H811" t="str" s="3">
+        <v>https://www.hljit.edu.cn/dqxxgcxy/xygk/xyjj.htm</v>
+      </c>
+      <c r="I811" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="812" ht="52.5" customHeight="1">
+      <c r="A812" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B812" t="str" s="3">
+        <v>沈阳航空航天大学</v>
+      </c>
+      <c r="C812" t="str" s="3">
+        <v>辽宁·沈阳</v>
+      </c>
+      <c r="D812" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E812" t="str" s="3">
+        <v>省航空推进系统先进测试技术2023正式开放指南搜索定位，属于44目录的另一个待筛平台。</v>
+      </c>
+      <c r="F812" t="str" s="3">
+        <v>首次全文超时，实际任务/资格金额未取得，先交人工不因测试控制词收正式项目；不合并N0522026联合批次。</v>
+      </c>
+      <c r="G812" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H812" t="str" s="3">
+        <v>https://fdj.sau.edu.cn/info/1085/1243.htm</v>
+      </c>
+      <c r="I812" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="813" ht="52.5" customHeight="1">
+      <c r="A813" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B813" t="str" s="3">
+        <v>东北地区省科技/教育目录查漏</v>
+      </c>
+      <c r="C813" t="str" s="3">
+        <v>辽宁/吉林/黑龙江</v>
+      </c>
+      <c r="D813" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E813" t="str" s="3">
+        <v>3省官方科技教育目录定向查询，定位高校目录和平台介绍，原始跨省结果保留；北华/齐齐哈尔/黑龙江工程/长春工程定向发现。</v>
+      </c>
+      <c r="F813" t="str" s="3">
+        <v>多数结果跨省、哈尔滨工业与哈尔滨理工混杂，不将搜索结果合集作全省名单；完整省认定机器人相关平台名单仍未取得。</v>
+      </c>
+      <c r="G813" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H813" t="str" s="3">
+        <v>resume_sources_20261009.json 搜索第347—355项</v>
+      </c>
+      <c r="I813" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>
@@ -45740,7 +46182,7 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="109" ht="96" customHeight="1">
+    <row r="109" ht="117" customHeight="1">
       <c r="A109" t="str" s="18">
         <v>已截止</v>
       </c>
@@ -45760,7 +46202,7 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="110" ht="96" customHeight="1">
+    <row r="110" ht="132" customHeight="1">
       <c r="A110" t="str" s="18">
         <v>已截止</v>
       </c>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -812,23 +812,23 @@
       </c>
     </row>
     <row r="15" ht="66" customHeight="1">
-      <c r="A15" s="12" t="str">
-        <v>受理中·条件待核</v>
-      </c>
-      <c r="B15" s="13" t="d">
-        <v>2026-11-10T00:00:00.000Z</v>
-      </c>
-      <c r="C15" s="14" t="str">
-        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
-      </c>
-      <c r="D15" s="15" t="str">
-        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
-      </c>
-      <c r="E15" s="15" t="str">
-        <v>0.5万元/项</v>
-      </c>
-      <c r="F15" s="16" t="str">
-        <v>公告</v>
+      <c r="A15" t="str" s="12">
+        <v>受理中·个人条件待核</v>
+      </c>
+      <c r="B15" t="n" s="13">
+        <v>46331</v>
+      </c>
+      <c r="C15" t="str" s="14">
+        <v>滁州学院·安徽省实景地理环境重点实验室</v>
+      </c>
+      <c r="D15" t="str" s="15">
+        <v>多无人机编队；室内定位导航；空地融合建模；三维重建；无人机巡检</v>
+      </c>
+      <c r="E15" t="str" s="15">
+        <v>重点≤8万；一般≤4万；产教≤15万</v>
+      </c>
+      <c r="F15" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="16" ht="66" customHeight="1">
@@ -836,16 +836,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B16" s="13" t="d">
-        <v>2026-11-15T00:00:00.000Z</v>
+        <v>2026-11-10T00:00:00.000Z</v>
       </c>
       <c r="C16" s="14" t="str">
-        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
       </c>
       <c r="D16" s="15" t="str">
-        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
       </c>
       <c r="E16" s="15" t="str">
-        <v>重点3万元、一般2万元</v>
+        <v>0.5万元/项</v>
       </c>
       <c r="F16" s="16" t="str">
         <v>公告</v>
@@ -856,18 +856,38 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B17" s="13" t="d">
+        <v>2026-11-15T00:00:00.000Z</v>
+      </c>
+      <c r="C17" s="14" t="str">
+        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+      </c>
+      <c r="D17" s="15" t="str">
+        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+      </c>
+      <c r="E17" s="15" t="str">
+        <v>重点3万元、一般2万元</v>
+      </c>
+      <c r="F17" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="12" t="str">
+        <v>受理中·条件待核</v>
+      </c>
+      <c r="B18" s="13" t="d">
         <v>2026-11-30T00:00:00.000Z</v>
       </c>
-      <c r="C17" s="14" t="str">
+      <c r="C18" s="14" t="str">
         <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
-      <c r="D17" s="15" t="str">
+      <c r="D18" s="15" t="str">
         <v>机器人加工技能学习与自主控制；多机器人协同；人形机器人感知、灵巧操作与全身控制</v>
       </c>
-      <c r="E17" s="15" t="str">
+      <c r="E18" s="15" t="str">
         <v>公告未公布资助强度，需咨询</v>
       </c>
-      <c r="F17" s="16" t="str">
+      <c r="F18" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
@@ -877,8 +897,8 @@
     <hyperlink ref="F2" ns1:id="R0703188348514edb"/>
     <hyperlink ref="C13" location="'02项目完整详情'!A10"/>
     <hyperlink ref="F13" ns1:id="R02deb72e2d4c4fc2"/>
-    <hyperlink ref="C15" location="'02项目完整详情'!A11"/>
-    <hyperlink ref="F15" ns1:id="Rb0dfb47d911a4186"/>
+    <hyperlink ref="C16" location="'02项目完整详情'!A11"/>
+    <hyperlink ref="F16" ns1:id="Rb0dfb47d911a4186"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A138"/>
     <hyperlink ref="F7" ns1:id="R03ccbeb508f24d98"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A3"/>
@@ -899,12 +919,14 @@
     <hyperlink ref="F11" ns1:id="R1fb1d42b338a46e2"/>
     <hyperlink ref="C14" location="'02项目完整详情'!A9"/>
     <hyperlink ref="F14" ns1:id="Rc8744d7119ac4fd0"/>
-    <hyperlink ref="C16" location="'02项目完整详情'!A12"/>
-    <hyperlink ref="F16" ns1:id="R59533ec0b37d42df"/>
-    <hyperlink ref="C17" location="'02项目完整详情'!A13"/>
-    <hyperlink ref="F17" ns1:id="Rc2d55cd36ec74ace"/>
+    <hyperlink ref="C17" location="'02项目完整详情'!A12"/>
+    <hyperlink ref="F17" ns1:id="R59533ec0b37d42df"/>
+    <hyperlink ref="C18" location="'02项目完整详情'!A13"/>
+    <hyperlink ref="F18" ns1:id="Rc2d55cd36ec74ace"/>
     <hyperlink ref="C5" location="'02项目完整详情'!A183" display="项目完整详情"/>
     <hyperlink ref="F5" ns1:id="rIdResume17"/>
+    <hyperlink ref="C15" location="'02项目完整详情'!A205" display="项目完整详情"/>
+    <hyperlink ref="F15" ns1:id="rIdResume18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -18451,6 +18473,339 @@
       </c>
       <c r="AA204" t="str" s="3">
         <v>2024对外批次与2026内部主任E069分别处理；网页上一篇2024立项不能当申请窗口仍开。</v>
+      </c>
+    </row>
+    <row r="205" ht="162" customHeight="1">
+      <c r="A205" t="str" s="3">
+        <v>N056</v>
+      </c>
+      <c r="B205" t="str" s="3">
+        <v>2026-10-03官方完整指南已读；申请DOC首次工具不支持，交人工</v>
+      </c>
+      <c r="C205" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="D205" t="str" s="3">
+        <v>安徽省实景地理环境重点实验室</v>
+      </c>
+      <c r="E205" t="str" s="3">
+        <v>受理中·个人条件待核</v>
+      </c>
+      <c r="F205" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G205" t="n" s="6">
+        <v>46331</v>
+      </c>
+      <c r="H205" t="str" s="3">
+        <v>具体截止时点未载</v>
+      </c>
+      <c r="I205" t="str" s="3">
+        <v>一般项目明确多无人机协同立体编队飞行、室内多障碍约束无人机高精度定位导航、空天塔地协同测绘；特殊纹理实景三维重建/动态映射；重点复杂场景空地融合建模、多模态标注泛化、实景三维视频融合；产教融合含低空无人机智慧巡检。生态反演等非机器人任务不据同一公告一并判断相关。</v>
+      </c>
+      <c r="J205" t="str" s="3">
+        <v>重点≤8万元/项；一般≤4万元/项；产教融合≤15万元/项，数量及具体金额评审决定。</v>
+      </c>
+      <c r="K205" t="str" s="3">
+        <v>重点/一般原则上博士，所在单位同意；面向国内外研究人员。产教融合面向具有技术研发能力单位，申请人有技术研发/工程应用经历。年龄/限项/在研限制未载。</v>
+      </c>
+      <c r="L205" t="str" s="3">
+        <v>必须联系实验室一名研究人员作为合作人，可由联系人推荐；执行期负责人至少线下交流1次。熟人关系不代表已落实。</v>
+      </c>
+      <c r="M205" t="str" s="3">
+        <v>预算合理安排、实报实销，在滁州学院财务处线下报销；未承诺外拨申请人单位或个人到账。产教融合经费由合作人认领，学校不收管理费；应用服务验收须实现1:3可支配到账经费，不含外协/交付设备。中检不合格或经费不合理可暂停/取消。</v>
+      </c>
+      <c r="N205" t="str" s="3">
+        <v>原则上2年：2027-01-01—2028-12-31；按任务书及年度计划完成，中检。</v>
+      </c>
+      <c r="O205" t="str" s="3">
+        <v>重点中科院一区SCI1篇且发明专利1项进入实审；一般二区SCI1篇或发明专利2项进入实审；滁州学院第一完成单位，负责人第一完成人。预警含曾经预警期刊论文不报销；成果须与课题相关。可由实验室认定相当成果（如省部及以上奖励1项，实验室主要完成单位）替代。产教融合信息化交源码/技术手册并测试/平台部署；服务类1:3可支配到账。成果署两平台：实景地理环境重点室、遥感与地理信息工程中心及2026RGE编号。</v>
+      </c>
+      <c r="P205" t="str" s="3">
+        <v>科研成果归本实验室和研究者所在单位共有；收益分配比例未载。</v>
+      </c>
+      <c r="Q205" t="str" s="3">
+        <v>2026-11-05前电子word和签字盖章PDF各1份，统一命名‘安徽省实景地理环境重点实验室开放课题-申请人姓名-项目名称’，邮箱ahpge2019@chzu.edu.cn。公示通过后填任务合同，经单位同意签章一式1份，胶装申请书+合同纸件提交；不把立项后纸件当申报前要求。</v>
+      </c>
+      <c r="R205" t="str" s="3">
+        <v>本人博士、南京信息工程大学现职；单位同意、固定合作人、限项及产教经历未确认。正式窗口已核，不据此判断个人可申请。</v>
+      </c>
+      <c r="S205" t="str" s="3">
+        <v>申请DOC首次工具不支持未取；年龄/限项/详细开支和收益分配未载。需表内追加条款；先保留正文明确线下报销，不写钱外拨/直接个人收入。</v>
+      </c>
+      <c r="T205" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm</v>
+      </c>
+      <c r="U205" t="str" s="3">
+        <v>https://www.chzu.edu.cn/_upload/article/files/ce/e0/4cfaf63c4da983ec12f8d2d19f1d/41ca46ff-f0e4-41d6-87ab-1963201cb757.doc；首次Unsupported application/msword，不重复尝试，人工N056。</v>
+      </c>
+      <c r="V205" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W205" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X205" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y205" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="Z205" t="str" s="3">
+        <v>陈老师0550-3519196；ahpge2019@chzu.edu.cn；滁州市会峰西路1号求真楼321，239000。</v>
+      </c>
+      <c r="AA205" t="str" s="3">
+        <v>新官方2026独立批次，揭榜挂帅须按列出的方向；产教服务类到账指标与普通论文项目分列，金额是项目预算不是个人现金。</v>
+      </c>
+    </row>
+    <row r="206" ht="132" customHeight="1">
+      <c r="A206" t="str" s="3">
+        <v>N057</v>
+      </c>
+      <c r="B206" t="str" s="3">
+        <v>2025正式全文任务和条件已读；申请DOC首次不支持，人工补取</v>
+      </c>
+      <c r="C206" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="D206" t="str" s="3">
+        <v>安徽省智能感知与健康养老工程研究中心</v>
+      </c>
+      <c r="E206" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F206" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G206" t="n" s="6">
+        <v>45986</v>
+      </c>
+      <c r="H206" t="str" s="3">
+        <v>具体时点未载</v>
+      </c>
+      <c r="I206" t="str" s="3">
+        <v>养老移动平台空间环境建模与主动安全感知；多模态行为理解/自然交互；动态非结构场景机器人自适应认知、行为预测、自主导航决策任务规划；健康能力评估、仿生可解释计算。</v>
+      </c>
+      <c r="J206" t="str" s="3">
+        <v>重点3万元拟1项；一般2万元拟5项。</v>
+      </c>
+      <c r="K206" t="str" s="3">
+        <v>具有科研基础、独立研究能力及条件，遵守法律及科研诚信；已有同内容资助不可重复，中心/实验室在研未结题负责人不得再申报。博士/职称年龄统一门槛正文未载，不能自加。</v>
+      </c>
+      <c r="L206" t="str" s="3">
+        <v>须有一定前期合作基础；外单位申报须联系平台1名高级职称或博士人员为合作人。访问次数未载。</v>
+      </c>
+      <c r="M206" t="str" s="3">
+        <v>预算及经费监督，不规范可取消；经费外拨/报账地点/劳务比例和支付节点正文未载，申请表待取。</v>
+      </c>
+      <c r="N206" t="str" s="3">
+        <v>2年：2025年12月—2027年11月。</v>
+      </c>
+      <c r="O206" t="str" s="3">
+        <v>预期成果至少满足4类中的2类：①二类以上期刊或EI会议论文一般2篇（重点3篇）；②申请发明1项；③行业/地方标准1项；④指导学生学科竞赛省级二等奖及以上1项。成果须相关且平台第一完成单位，标开放基金及编号；二类期刊目录未取得，不套SCI分区。年度进展、结题报告及成果验收。</v>
+      </c>
+      <c r="P206" t="str" s="3">
+        <v>正文未明确完整知识产权归属/收益分配，不由第一单位推断独占。</v>
+      </c>
+      <c r="Q206" t="str" s="3">
+        <v>截止2025-11-25；纸质盖章2份并电子申请发指定邮箱；立项签任务书。尚翠娟19909608096、王汇彬15155041897；wanghuibin@chzu.edu.cn；会峰西路1号。</v>
+      </c>
+      <c r="R206" t="str" s="3">
+        <v>本人博士及高校现职已知；本轮已截止，前期合作基础和固定合作人未落实、不以熟人推定。</v>
+      </c>
+      <c r="S206" t="str" s="3">
+        <v>申请DOC工具首次不支持；外拨/报销/IP/二类期刊目录未取得，需附件及官方补充。不据旧年度周期延续误判仍受理。</v>
+      </c>
+      <c r="T206" t="str" s="3">
+        <v>https://kyc.chzu.edu.cn/2025/1117/c15890a335209/page.htm</v>
+      </c>
+      <c r="U206" t="str" s="3">
+        <v>https://kyc.chzu.edu.cn/_upload/article/files/d0/9a/208112b3458c83c8864fbe1f58c7/a180352f-84cc-410f-b0e6-e189ff6ef9ce.doc</v>
+      </c>
+      <c r="V206" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W206" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X206" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y206" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="Z206" t="str" s="3">
+        <v>尚翠娟19909608096、王汇彬15155041897；wanghuibin@chzu.edu.cn；会峰西路1号。</v>
+      </c>
+      <c r="AA206" t="str" s="3">
+        <v>2025独立历史批次，2026—2027未定位新正式指南；研究期到2027不是延长申报。</v>
+      </c>
+    </row>
+    <row r="207" ht="132" customHeight="1">
+      <c r="A207" t="str" s="3">
+        <v>N058</v>
+      </c>
+      <c r="B207" t="str" s="3">
+        <v>高校官网完整转发安徽大学2022第一批指南；原实施单位与校内转发截止分开</v>
+      </c>
+      <c r="C207" t="str" s="3">
+        <v>安徽大学</v>
+      </c>
+      <c r="D207" t="str" s="3">
+        <v>高节能电机及控制技术国家地方联合工程实验室</v>
+      </c>
+      <c r="E207" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F207" t="str" s="3">
+        <v>2022第一批</v>
+      </c>
+      <c r="G207" t="n" s="6">
+        <v>44692</v>
+      </c>
+      <c r="H207" t="str" s="3">
+        <v>转发单位交科技处的日期；全国直接提交截止尚待实施单位确认</v>
+      </c>
+      <c r="I207" t="str" s="3">
+        <v>明确特种机器人电力巡检/消防/反恐排爆：自动导航、无线图像视频传输、避障、充电、灭火；球形关节带载闭环控制算法及硬件实现。输电、电机耦合等其他任务不因同公告全列相关。</v>
+      </c>
+      <c r="J207" t="str" s="3">
+        <v>一般2—3万元/项，按研究内容及预期成果决定。</v>
+      </c>
+      <c r="K207" t="str" s="3">
+        <v>全国高校科研单位相关领域科技工作者或同等研究能力研究人员；学历职称年龄限项未载。</v>
+      </c>
+      <c r="L207" t="str" s="3">
+        <v>欢迎客座/合作研究，未明确固定合作人或驻室硬性要求，管理办法未取。</v>
+      </c>
+      <c r="M207" t="str" s="3">
+        <v>正文未载费用、外拨报销/支付节点，不能套滁州本地2026线下报账办法。</v>
+      </c>
+      <c r="N207" t="str" s="3">
+        <v>1—2年；统一起止未載。</v>
+      </c>
+      <c r="O207" t="str" s="3">
+        <v>成果具体数量、第一单位/作者、报告及中检未载，须2022管理办法。</v>
+      </c>
+      <c r="P207" t="str" s="3">
+        <v>知识产权/收益未载，办法首次超时未取。</v>
+      </c>
+      <c r="Q207" t="str" s="3">
+        <v>转发要求2022-05-11前签名单位盖章申请书3份A4双面交滁州科技处；该流程是转发校内征集，南信大直接提交安徽大学的邮箱/地址及原全国截止未知。</v>
+      </c>
+      <c r="R207" t="str" s="3">
+        <v>高校博士现职对应科研人员类别，历史截止；实施单位原流程、限项和合作须后续官方确认。</v>
+      </c>
+      <c r="S207" t="str" s="3">
+        <v>2个DOC首次超时；实施单位原受理流程/全国期限、成果/IP/经费方式未取得。滁州联系人只是转发校内科技处，不能当安徽大学实验室联系人。</v>
+      </c>
+      <c r="T207" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm</v>
+      </c>
+      <c r="U207" t="str" s="3">
+        <v>https://www.chzu.edu.cn/_upload/article/files/c7/a7/c6da99814de0ab1e24aac9bc12a8/1b063095-97f9-42e6-b040-18eb1e89ba4b.doc
+https://www.chzu.edu.cn/_upload/article/files/c7/a7/c6da99814de0ab1e24aac9bc12a8/75c35e82-ce29-49bc-a0f2-764fa6a29a2d.doc</v>
+      </c>
+      <c r="V207" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W207" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X207" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y207" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="Z207" t="str" s="3">
+        <v>转发校科技处梅蔚然0550-3511013（滁州校内征集联系）；安徽大学实验室正式联系人未确认。</v>
+      </c>
+      <c r="AA207" t="str" s="3">
+        <v>依托安徽大学合肥，不因转发在滁州挂到滁州平台。转发05-11不冒充全国统一原截止。</v>
+      </c>
+    </row>
+    <row r="208" ht="132" customHeight="1">
+      <c r="A208" t="str" s="3">
+        <v>N059</v>
+      </c>
+      <c r="B208" t="str" s="3">
+        <v>2025正式全文任务和条件已读；申请DOC首次不支持，人工补取</v>
+      </c>
+      <c r="C208" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="D208" t="str" s="3">
+        <v>无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室</v>
+      </c>
+      <c r="E208" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F208" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G208" t="n" s="6">
+        <v>45986</v>
+      </c>
+      <c r="H208" t="str" s="3">
+        <v>具体时点未载</v>
+      </c>
+      <c r="I208" t="str" s="3">
+        <v>无人应急装备复杂环境视觉感知、目标识别、状态诊断；视觉任务定位跟踪与运动/执行系统协同作业控制；视觉红外传感行为多模态灾害识别预警。明确无人装备自主执行任务。</v>
+      </c>
+      <c r="J208" t="str" s="3">
+        <v>一般2万元/项，拟3项；正文成果提重点3篇但本批不设重点资助。</v>
+      </c>
+      <c r="K208" t="str" s="3">
+        <v>具有科研基础、独立研究能力及条件，遵守法律及科研诚信；已有同内容资助不可重复，中心/实验室在研未结题负责人不得再申报。博士/职称年龄统一门槛正文未载，不能自加。</v>
+      </c>
+      <c r="L208" t="str" s="3">
+        <v>须有一定前期合作基础；外单位申报须联系平台1名高级职称或博士人员为合作人。访问次数未载。</v>
+      </c>
+      <c r="M208" t="str" s="3">
+        <v>预算及经费监督，不规范可取消；经费外拨/报账地点/劳务比例和支付节点正文未载，申请表待取。</v>
+      </c>
+      <c r="N208" t="str" s="3">
+        <v>2年：2025年12月—2027年11月。</v>
+      </c>
+      <c r="O208" t="str" s="3">
+        <v>预期成果至少满足4类中的2类：①二类以上期刊或EI会议论文一般2篇（重点3篇）；②申请发明1项；③行业/地方标准1项；④指导学生学科竞赛省级二等奖及以上1项。成果须相关且平台第一完成单位，标开放基金及编号；二类期刊目录未取得，不套SCI分区。年度进展、结题报告及成果验收。</v>
+      </c>
+      <c r="P208" t="str" s="3">
+        <v>正文未明确完整知识产权归属/收益分配，不由第一单位推断独占。</v>
+      </c>
+      <c r="Q208" t="str" s="3">
+        <v>截止2025-11-25；纸质盖章2份并电子申请发指定邮箱；立项签任务书。曾海燕18326891813；2320725471@qq.com；滁州市会峰西路1号。</v>
+      </c>
+      <c r="R208" t="str" s="3">
+        <v>本人博士及高校现职已知；本轮已截止，前期合作基础和固定合作人未落实、不以熟人推定。</v>
+      </c>
+      <c r="S208" t="str" s="3">
+        <v>申请DOC工具首次不支持；外拨/报销/IP/二类期刊目录未取得，需附件及官方补充。不据旧年度周期延续误判仍受理。</v>
+      </c>
+      <c r="T208" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2025/1117/c18154a335226/page.htm</v>
+      </c>
+      <c r="U208" t="str" s="3">
+        <v>https://www.chzu.edu.cn/_upload/article/files/73/7a/a525a73f4d99a1e14662815bf77f/2f7634d0-138b-4a96-8803-88c4b457797e.doc</v>
+      </c>
+      <c r="V208" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W208" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X208" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y208" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="Z208" t="str" s="3">
+        <v>曾海燕18326891813；2320725471@qq.com；滁州市会峰西路1号。</v>
+      </c>
+      <c r="AA208" t="str" s="3">
+        <v>2025独立历史批次，2026—2027未定位新正式指南；研究期到2027不是延长申报。</v>
       </c>
     </row>
   </sheetData>
@@ -18877,6 +19232,10 @@
     <hyperlink ref="T202" ns1:id="rIdResume424"/>
     <hyperlink ref="T203" ns1:id="rIdResume425"/>
     <hyperlink ref="T204" ns1:id="rIdResume426"/>
+    <hyperlink ref="T205" ns1:id="rIdResume427"/>
+    <hyperlink ref="T206" ns1:id="rIdResume428"/>
+    <hyperlink ref="T207" ns1:id="rIdResume429"/>
+    <hyperlink ref="T208" ns1:id="rIdResume430"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -43980,6 +44339,755 @@
         <v>resume_sources_20261009.json 搜索第347—355项</v>
       </c>
       <c r="I813" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="814" ht="52.5" customHeight="1">
+      <c r="A814" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B814" t="str" s="3">
+        <v>江苏省属高校机器人研究平台与当年开放机制补漏A</v>
+      </c>
+      <c r="C814" t="str" s="3">
+        <v>江苏·南京/常州</v>
+      </c>
+      <c r="D814" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E814" t="str" s="3">
+        <v>查询：site:njit.edu.cn 机器人 重点实验室 开放基金 2026 2027 / site:jsut.edu.cn 机器人 重点实验室 开放课题 2026 2027 / site:czu.cn 机器人 智能装备 开放基金 2026 / site:njfu.edu.cn 智能装备 机器人 开放基金 2026；线索：科研平台-能源与动力工程学院；机械工程学院2026年度省、校研究生科研实践创新计划项目申报初审结果公示；教学实验室；等学校自然科学研究项目管理办法》印发给你们，请认真贯彻执；关于做好2026年高校“人工智能通识教育教学改革研究"专项课题立项建设申报的通知</v>
+      </c>
+      <c r="F814" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G814" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H814" t="str" s="3">
+        <v>https://nd.njit.edu.cn/kxyj/kypt.htm
+https://jxxy.jsut.edu.cn/2026/0616/c1295a214388/page.htm
+https://jxxy.jsut.edu.cn/jxsys/list.htm
+https://jz.njit.edu.cn/__local/C/23/24/7A576B69B59F44B9063DBDB0491_C2E25620_93AB1.pdf
+https://jw.jsut.edu.cn/2026/0904/c3461a216473/page.htm</v>
+      </c>
+      <c r="I814" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第356项</v>
+      </c>
+    </row>
+    <row r="815" ht="52.5" customHeight="1">
+      <c r="A815" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B815" t="str" s="3">
+        <v>江苏省属高校机器人研究平台与当年开放机制补漏B</v>
+      </c>
+      <c r="C815" t="str" s="3">
+        <v>江苏·连云港/淮安/盐城</v>
+      </c>
+      <c r="D815" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E815" t="str" s="3">
+        <v>查询：site:jou.edu.cn 机器人 重点实验室 开放基金 2026 2027 / site:hyit.edu.cn 机器人 重点实验室 开放基金 2026 / site:ycit.edu.cn 智能装备 开放基金 2026 2027 / site:ycit.edu.cn 科研平台 机器人 重点实验室；线索：数字孪生与智能制造技术研究所-盐城工学院-机械工程学院 优集学院；机械工业模具型腔智能加工技术重点实验室-盐城工学院-机械工程学院 优集学院；我校新增2个江苏高校重点实验室-盐城工学院 - YANCHENG INSTITUTE OF TECHNOLOGY 厚德格致 笃学重行；我校江苏省新型环保重点实验室2017-2019年省绩效评估获“良好”等级-盐城工学院 - YANCHENG INSTITUTE OF TECHNOLOGY 厚德格致 笃学重行；河南工程学院：立足应用型大学定位 助力科技自立自强-盐城工学院发展与改革办公室、高等教育研究院 &gt;&gt; 首页；外学术交流与合作研究，学校要提供配套条件和资金。</v>
+      </c>
+      <c r="F815" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G815" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H815" t="str" s="3">
+        <v>https://mech.ycit.edu.cn/kxyj/kyjg/szlsyznzzjsyjs.htm
+https://mech.ycit.edu.cn/info/1132/18146.htm
+https://www.ycit.edu.cn/info/1021/95586.htm
+https://www.ycit.edu.cn/info/1021/14611.htm
+https://fgbgjy.ycit.edu.cn/info/1012/2659.htm
+https://keji.jou.edu.cn/__local/0/8E/3D/4772E4083510509D749A27FF4E5_37DEEE04_5C9FD.pdf?e=.pdf</v>
+      </c>
+      <c r="I815" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第357项</v>
+      </c>
+    </row>
+    <row r="816" ht="52.5" customHeight="1">
+      <c r="A816" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B816" t="str" s="3">
+        <v>南京林业大学机械林业机器人科研平台及开放机制补齐</v>
+      </c>
+      <c r="C816" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D816" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E816" t="str" s="3">
+        <v>查询：site:njfu.edu.cn 科研平台 机械 机器人 / site:njfu.edu.cn "开放基金" / site:njfu.edu.cn "开放课题" "2026" / site:njfu.edu.cn "林业机械" "重点实验室"；线索：南京林业大学研究生院；林木遗传育种全国重点实验室（南京林业大学）；格力电器2025届博士秋季校园招聘简章-就业创业-南京林业大学研究生院</v>
+      </c>
+      <c r="F816" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G816" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H816" t="str" s="3">
+        <v>https://gs.njfu.edu.cn/gmis_nl/xkjsb/yjsdsfc.aspx?id=B7487A8671FA418993CA2042B4589090
+https://skltgb.njfu.edu.cn/
+https://gsnfu.njfu.edu.cn/jygz/20241107/i322530.html</v>
+      </c>
+      <c r="I816" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第358项</v>
+      </c>
+    </row>
+    <row r="817" ht="52.5" customHeight="1">
+      <c r="A817" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B817" t="str" s="3">
+        <v>盐城工学院新认定机器人平台及实验室机制查漏</v>
+      </c>
+      <c r="C817" t="str" s="3">
+        <v>江苏·盐城</v>
+      </c>
+      <c r="D817" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E817" t="str" s="3">
+        <v>查询：site:ycit.edu.cn "95586" / "模具型腔智能加工技术" "开放基金" / "盐城工学院" "数字孪生" "开放课题" / site:ycit.edu.cn "开放课题" "2026"；线索：科学研究-盐城工学院-机械工程学院 优集学院；江苏省3C增材制造与表面技术重点实验室学术委员会首次会议召开；盐城黄海湿地生态文明建设研究中心；张文惠-盐城-江苏省新型环保重点实验室</v>
+      </c>
+      <c r="F817" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G817" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H817" t="str" s="3">
+        <v>https://mech.ycit.edu.cn/kxyj/5.htm
+https://smsp.cumt.edu.cn/a0/04/c18888a696324/page.htm
+https://xcb.ycit.edu.cn/hhzk/index.htm
+https://ae.ycit.edu.cn/info/1053/1789.htm</v>
+      </c>
+      <c r="I817" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第359项</v>
+      </c>
+    </row>
+    <row r="818" ht="52.5" customHeight="1">
+      <c r="A818" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B818" t="str" s="3">
+        <v>南京工程/江苏理工/常州工学院机械机器人科研目录补齐</v>
+      </c>
+      <c r="C818" t="str" s="3">
+        <v>江苏·南京/常州</v>
+      </c>
+      <c r="D818" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E818" t="str" s="3">
+        <v>查询：site:njit.edu.cn 机械 科研平台 实验室 机器人 / site:jsut.edu.cn 科研平台 重点实验室 机器人 / site:czu.cn 科研平台 重点实验室 智能装备 / site:czu.cn "开放课题"；线索：省级科研平台；〖科研平台〗南京工程学院—燕山大学联合研究院：校校合作共建智能流体研发创新平台-南京工程学院；〖科研平台〗江苏省特种作业与康复机器人工程研究中心：紧跟科技前沿，助力行业发展-南京工程学院；我校获批建设“江苏省智能制造装备工程实验室”-南京工程学院；江苏省重点实验室；教学实验室</v>
+      </c>
+      <c r="F818" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G818" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H818" t="str" s="3">
+        <v>https://kyc.czu.cn/745/list.htm
+https://www.njit.edu.cn/info/1044/20881.htm
+https://www.njit.edu.cn/info/1044/20858.htm
+https://www.njit.edu.cn/info/1042/10252.htm
+https://dqxy.czu.cn/sysjs/list.htm
+https://jxxy.jsut.edu.cn/jxsys/list.htm</v>
+      </c>
+      <c r="I818" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第360项</v>
+      </c>
+    </row>
+    <row r="819" ht="52.5" customHeight="1">
+      <c r="A819" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B819" t="str" s="3">
+        <v>南京工程学院已确认机器人及智能装备省平台基金机制</v>
+      </c>
+      <c r="C819" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D819" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E819" t="str" s="3">
+        <v>查询："特种作业与康复机器人工程研究中心" "开放基金" / "特种作业与康复机器人工程研究中心" "开放课题" / "南京工程学院" "智能制造装备工程实验室" "开放" / site:njit.edu.cn "开放基金" "2027"；线索：我校获批建设“江苏省智能制造装备工程实验室”-南京工程学院；〖科研平台〗康尼机电产业技术研究院：以人才培养和科技创新服务地方经济社会发展-南京工程学院</v>
+      </c>
+      <c r="F819" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G819" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H819" t="str" s="3">
+        <v>https://www.njit.edu.cn/info/1042/10252.htm
+https://www.njit.edu.cn/info/1044/20732.htm</v>
+      </c>
+      <c r="I819" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第361项</v>
+      </c>
+    </row>
+    <row r="820" ht="52.5" customHeight="1">
+      <c r="A820" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B820" t="str" s="3">
+        <v>常州工学院省高校无人机/多源信息/电机平台年度基金补漏</v>
+      </c>
+      <c r="C820" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D820" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E820" t="str" s="3">
+        <v>查询："智能感知与无人机应用研究" "开放" 基金 / "智能多源信息处理与安全" "开放基金" / "特种电机研究与应用" "开放课题" / site:czu.cn "开放基金" 2026 2027；线索：2025年广西多源信息挖掘与安全重点验室开放课题基金（自筹经费）申请指南；10项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑；2026年安徽省实景地理环境重点实验室开放课题申报指南；“教学质量工程”第二批教学研究立项项目公示；开放申请！13项重点实验室基金开放课题申请指南-爱科会易；计算机应用研究</v>
+      </c>
+      <c r="F820" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G820" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H820" t="str" s="3">
+        <v>https://mims.gxnu.edu.cn/2025/1011/c6728a327370/page.htm
+https://www.letpub.com.cn/index.php?article_id=1576&amp;page=grant_article_details
+https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm
+https://energy.hust.edu.cn/info/1099/1251.htm
+https://www.uconf.com/news/3435
+https://www.arocmag.cn/?st=aipub</v>
+      </c>
+      <c r="I820" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第362项</v>
+      </c>
+    </row>
+    <row r="821" ht="52.5" customHeight="1">
+      <c r="A821" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B821" t="str" s="3">
+        <v>常州工学院特种加工/智能循环制造/建造平台基金补漏</v>
+      </c>
+      <c r="C821" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D821" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E821" t="str" s="3">
+        <v>查询："常州工学院" "特种加工" "开放基金" / "通用航空器关键部件智能循环制造" "开放" 基金 / "土木工程智能建造技术" "常州工学院" "开放课题" / "智能网联汽车信息安全" "常州工学院" "开放基金"；线索：江苏省通用航空器关键部件智能循环制造工程研究中心</v>
+      </c>
+      <c r="F821" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G821" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H821" t="str" s="3">
+        <v>https://jdxy.czu.cn/6898/listm.htm</v>
+      </c>
+      <c r="I821" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第363项</v>
+      </c>
+    </row>
+    <row r="822" ht="52.5" customHeight="1">
+      <c r="A822" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B822" t="str" s="3">
+        <v>盐城工学院新重点室具体研究任务及年度开放机制</v>
+      </c>
+      <c r="C822" t="str" s="3">
+        <v>江苏·盐城</v>
+      </c>
+      <c r="D822" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E822" t="str" s="3">
+        <v>查询："新能源退役资源再生再造技术及智能装备" "开放基金" / "AI融合储能工程" "开放课题" / site:ycit.edu.cn "模具型腔智能加工技术" "2026" / site:ycit.edu.cn "开放基金" "2027"；线索：机械工业模具型腔智能加工技术重点实验室-盐城工学院-机械工程学院 优集学院；科学研究-盐城工学院-机械工程学院 优集学院；昆明市中小企业数字化转型公共服务平台</v>
+      </c>
+      <c r="F822" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G822" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H822" t="str" s="3">
+        <v>https://mech.ycit.edu.cn/info/1132/18146.htm
+https://mech.ycit.edu.cn/kxyj/5.htm
+https://kmszpt.com/index/policy/info.html?id=935</v>
+      </c>
+      <c r="I822" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第364项</v>
+      </c>
+    </row>
+    <row r="823" ht="52.5" customHeight="1">
+      <c r="A823" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B823" t="str" s="3">
+        <v>滁州学院实景实验室2027年度补漏</v>
+      </c>
+      <c r="C823" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="D823" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E823" t="str" s="3">
+        <v>查询：site:chzu.edu.cn "实景地理" "开放" 2027 / site:chzu.edu.cn "机器人" "开放课题" / site:chzu.edu.cn 科研平台 重点实验室；线索：2025年度安徽省智能感知与健康养老工程研究中心开放课题申报通知；关于高节能电机及控制技术国家地方联合工程实验室关于接受2022年第一批开放课题申请的通知；地信学院：2016届校友张振在国际顶级期刊《Science》发表研究论文；国务院关于国家重大科研基础设施和大型科研仪器向社会开放的意见；2026年安徽省实景地理环境重点实验室开放课题申报指南</v>
+      </c>
+      <c r="F823" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G823" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H823" t="str" s="3">
+        <v>https://kyc.chzu.edu.cn/2025/1117/c15890a335209/page.htm
+https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm
+https://dxxy.chzu.edu.cn/2026/0605/c1989a345305/page.htm
+https://zcc.chzu.edu.cn/2017/0428/c4339a146709/page.htm
+https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm</v>
+      </c>
+      <c r="I823" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第365项</v>
+      </c>
+    </row>
+    <row r="824" ht="52.5" customHeight="1">
+      <c r="A824" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B824" t="str" s="3">
+        <v>常州工学院市级实验室机制</v>
+      </c>
+      <c r="C824" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D824" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E824" t="str" s="3">
+        <v>查询："常州市现代物流" "开放" 课题 / "常州市微特电机" "开放基金" / "常州市智能感知" "开放课题" / site:czu.cn "开放基金" 2026；线索：(PDF) Research on the Competitiveness of Changzhou’s Modern Logistics Industry under the Background of Supply-Side Reform</v>
+      </c>
+      <c r="F824" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G824" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H824" t="str" s="3">
+        <v>https://www.researchgate.net/publication/346233579_Research_on_the_Competitiveness_of_Changzhou%27s_Modern_Logistics_Industry_under_the_Background_of_Supply-Side_Reform</v>
+      </c>
+      <c r="I824" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第366项</v>
+      </c>
+    </row>
+    <row r="825" ht="52.5" customHeight="1">
+      <c r="A825" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B825" t="str" s="3">
+        <v>江苏理工学院与南京工程完整科研目录</v>
+      </c>
+      <c r="C825" t="str" s="3">
+        <v>江苏·南京常州</v>
+      </c>
+      <c r="D825" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E825" t="str" s="3">
+        <v>查询：site:jsut.edu.cn 科研平台 机器人 重点实验室 / site:jsut.edu.cn "开放课题" 2026 / site:njit.edu.cn "科研平台" 重点实验室 / site:njit.edu.cn "开放基金" 2026 2027；线索：〖科研平台〗碳中和与国土空间优化重点实验室南京工程学院研究中心：以校际交流合作与学科交叉融合助力学校高质量发展-南京工程学院；科研平台-能源与动力工程学院；南京工程学院硕士研究生（英文授课）专业招生简章；教学实验室；〖科研平台〗南京工程学院—燕山大学联合研究院：校校合作共建智能流体研发创新平台-南京工程学院；关于做好2026年度江苏省高等学校基础科学（自然科学）研究项目申报工作的通知-南京工程学院</v>
+      </c>
+      <c r="F825" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G825" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H825" t="str" s="3">
+        <v>https://www.njit.edu.cn/info/1044/20826.htm
+https://nd.njit.edu.cn/kxyj/kypt.htm
+https://sie.njit.edu.cn/__local/9/4A/07/68912A340FD3E5796A45333C8DA_0F61B445_8B936.pdf
+https://jxxy.jsut.edu.cn/jxsys/list.htm
+https://www.njit.edu.cn/info/1044/20881.htm
+https://www.njit.edu.cn/info/1043/27740.htm</v>
+      </c>
+      <c r="I825" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第367项</v>
+      </c>
+    </row>
+    <row r="826" ht="52.5" customHeight="1">
+      <c r="A826" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B826" t="str" s="3">
+        <v>滁州养老及无人应急2026/2027机制</v>
+      </c>
+      <c r="C826" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="D826" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E826" t="str" s="3">
+        <v>查询：site:chzu.edu.cn "健康养老" "开放课题" 2026 2027 / site:chzu.edu.cn "无人应急" "开放课题" / site:ahu.edu.cn "高节能电机" "开放课题" 2026 2027；线索：2025年度无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室开放课题申报通知；重点实验室2025年度开放基金申报公告；高节能电机及控制技术国家地方联合工程实验室；2025年度安徽省智能感知与健康养老工程研究中心开放课题申报通知；滁州大健康与养老产业研究院；2025年度中心开放课题拟立项公示</v>
+      </c>
+      <c r="F826" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G826" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H826" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2025/1117/c18154a335226/page.htm
+https://iset.chzu.edu.cn/2025/0417/c17123a321972/page.htm
+https://gjndj.ahu.edu.cn/_upload/article/files/18/ff/f9b091cf49068d1cfa42cc1458e8/a610b400-18d2-4a2a-bbe4-d50eb5dc8a96.pdf
+https://kyc.chzu.edu.cn/2025/1117/c15890a335209/page.htm
+https://healthcare.chzu.edu.cn/
+https://healthcare.chzu.edu.cn/2025/1129/c14488a336176/page.htm</v>
+      </c>
+      <c r="I826" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第368项</v>
+      </c>
+    </row>
+    <row r="827" ht="52.5" customHeight="1">
+      <c r="A827" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B827" t="str" s="3">
+        <v>南京工程五个机器人相关省部平台机制</v>
+      </c>
+      <c r="C827" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D827" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E827" t="str" s="3">
+        <v>查询："南京工程" "仿生控制" "开放基金" / "南京工程" "先进数控" "开放课题" 2026 2027 / "机械工业智能流体" "开放" 基金 / "南京工程" "服务机器人" "开放课题"；线索：关于特种重载机器人安徽省重点实验室2023年度开放基金项目评审结果的公示-特种重载机器人安徽省重点实验室；南京航空航天大学主页平台管理系统 Bu Yanling--Home-- 戳首页！首页！首页！；开放课题汇总；中心简介 - 中国科学院软件研究所 - 智能软件研究中心</v>
+      </c>
+      <c r="F827" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G827" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H827" t="str" s="3">
+        <v>https://robotlab.ahut.edu.cn/info/1549/1268.htm
+https://faculty.nuaa.edu.cn/buyanling/en/lwcg/389302/content/34889.htm
+https://ncrl.seu.edu.cn/kfkt/list.htm
+https://isrc.iscas.ac.cn/about/</v>
+      </c>
+      <c r="I827" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第369项</v>
+      </c>
+    </row>
+    <row r="828" ht="52.5" customHeight="1">
+      <c r="A828" t="str" s="3">
+        <v>2026-10-09江苏省属与安徽年度机制补漏</v>
+      </c>
+      <c r="B828" t="str" s="3">
+        <v>江苏理工省属新实验室机制</v>
+      </c>
+      <c r="C828" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D828" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E828" t="str" s="3">
+        <v>查询："江苏理工" "机器人" "重点实验室" "开放" / "江苏理工" "先进材料设计与增材制造" "开放课题" / "江苏理工" "智能" "开放基金" 2026 2027；线索：2021年承担项目-材料先进技术教育部重点实验室；开放课题汇总</v>
+      </c>
+      <c r="F828" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G828" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H828" t="str" s="3">
+        <v>https://klam.swjtu.edu.cn/info/1017/1909.htm
+https://ncrl.seu.edu.cn/kfkt/list.htm</v>
+      </c>
+      <c r="I828" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第370项</v>
+      </c>
+    </row>
+    <row r="829" ht="52.5" customHeight="1">
+      <c r="A829" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B829" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="C829" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="D829" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E829" t="str" s="3">
+        <v>安徽省实景地理环境重点实验室；2026；N056；2026-10-03官方完整指南已读；申请DOC首次工具不支持，交人工</v>
+      </c>
+      <c r="F829" t="str" s="3">
+        <v>申请DOC首次工具不支持未取；年龄/限项/详细开支和收益分配未载。需表内追加条款；先保留正文明确线下报销，不写钱外拨/直接个人收入。</v>
+      </c>
+      <c r="G829" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H829" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm</v>
+      </c>
+      <c r="I829" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="830" ht="52.5" customHeight="1">
+      <c r="A830" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B830" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="C830" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="D830" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E830" t="str" s="3">
+        <v>安徽省智能感知与健康养老工程研究中心；2025；N057；2025正式全文任务和条件已读；申请DOC首次不支持，人工补取</v>
+      </c>
+      <c r="F830" t="str" s="3">
+        <v>申请DOC工具首次不支持；外拨/报销/IP/二类期刊目录未取得，需附件及官方补充。不据旧年度周期延续误判仍受理。</v>
+      </c>
+      <c r="G830" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H830" t="str" s="3">
+        <v>https://kyc.chzu.edu.cn/2025/1117/c15890a335209/page.htm</v>
+      </c>
+      <c r="I830" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="831" ht="52.5" customHeight="1">
+      <c r="A831" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B831" t="str" s="3">
+        <v>安徽大学</v>
+      </c>
+      <c r="C831" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="D831" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E831" t="str" s="3">
+        <v>高节能电机及控制技术国家地方联合工程实验室；2022第一批；N058；高校官网完整转发安徽大学2022第一批指南；原实施单位与校内转发截止分开</v>
+      </c>
+      <c r="F831" t="str" s="3">
+        <v>2个DOC首次超时；实施单位原受理流程/全国期限、成果/IP/经费方式未取得。滁州联系人只是转发校内科技处，不能当安徽大学实验室联系人。</v>
+      </c>
+      <c r="G831" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H831" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm</v>
+      </c>
+      <c r="I831" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="832" ht="52.5" customHeight="1">
+      <c r="A832" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B832" t="str" s="3">
+        <v>滁州学院</v>
+      </c>
+      <c r="C832" t="str" s="3">
+        <v>安徽·滁州</v>
+      </c>
+      <c r="D832" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E832" t="str" s="3">
+        <v>无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室；2025；N059；2025正式全文任务和条件已读；申请DOC首次不支持，人工补取</v>
+      </c>
+      <c r="F832" t="str" s="3">
+        <v>申请DOC工具首次不支持；外拨/报销/IP/二类期刊目录未取得，需附件及官方补充。不据旧年度周期延续误判仍受理。</v>
+      </c>
+      <c r="G832" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H832" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2025/1117/c18154a335226/page.htm</v>
+      </c>
+      <c r="I832" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="833" ht="52.5" customHeight="1">
+      <c r="A833" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B833" t="str" s="3">
+        <v>常州工学院</v>
+      </c>
+      <c r="C833" t="str" s="3">
+        <v>江苏·常州</v>
+      </c>
+      <c r="D833" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E833" t="str" s="3">
+        <v>省级11项/市级7项/校级网页2学会完整目录；无人机2025新省高校重点室完整介绍，7省平台及市级无人机/微特电机/物流逐名基金查2026—2027及历史。</v>
+      </c>
+      <c r="F833" t="str" s="3">
+        <v>校级网页仅列学会，不能当全校完整实验室目录；未定位正式基金不写没有。</v>
+      </c>
+      <c r="G833" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H833" t="str" s="3">
+        <v>https://kyc.czu.cn/745/list.htm
+https://kyc.czu.cn/752/list.htm
+https://kyc.czu.cn/753/list.htm</v>
+      </c>
+      <c r="I833" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="834" ht="52.5" customHeight="1">
+      <c r="A834" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B834" t="str" s="3">
+        <v>南京工程学院</v>
+      </c>
+      <c r="C834" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D834" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E834" t="str" s="3">
+        <v>特种作业康复中心全文；智能制造装备2017批准全文含工业机器人/运动伺服；制造产业学院4平台完整；仿生/数控/智能流体/服务机器人逐名基金查。</v>
+      </c>
+      <c r="F834" t="str" s="3">
+        <v>学院目录非全校目录；机械PDF省平台4+研究所4未首次读取；实验室改名机制未全；外部获资助新闻非自身基金。</v>
+      </c>
+      <c r="G834" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H834" t="str" s="3">
+        <v>https://www.njit.edu.cn/info/1044/20858.htm
+https://www.njit.edu.cn/info/1042/10252.htm
+https://im.njit.edu.cn/kxyj/kypt.htm</v>
+      </c>
+      <c r="I834" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="835" ht="52.5" customHeight="1">
+      <c r="A835" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B835" t="str" s="3">
+        <v>南京林业大学</v>
+      </c>
+      <c r="C835" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D835" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E835" t="str" s="3">
+        <v>林业机器人平台及2026—2027基金查询；机械简介首次超时，交人工停。</v>
+      </c>
+      <c r="F835" t="str" s="3">
+        <v>机械平台完整名单及年度条款未取；同校遗传/材料基金不误收。</v>
+      </c>
+      <c r="G835" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H835" t="str" s="3">
+        <v>https://jidian.njfu.edu.cn/xygk/xyjj/</v>
+      </c>
+      <c r="I835" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="836" ht="52.5" customHeight="1">
+      <c r="A836" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B836" t="str" s="3">
+        <v>盐城工学院</v>
+      </c>
+      <c r="C836" t="str" s="3">
+        <v>江苏·盐城</v>
+      </c>
+      <c r="D836" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E836" t="str" s="3">
+        <v>2025-10-09新增2江苏高校重点室全文：退役再造智能装备/AI储能，2026—2027机制查询；模具型腔详情首次超时。</v>
+      </c>
+      <c r="F836" t="str" s="3">
+        <v>全校5省高校重点室其余3名未全；数字孪生研究所未读；相关具体年度任务未知。</v>
+      </c>
+      <c r="G836" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H836" t="str" s="3">
+        <v>https://www.ycit.edu.cn/info/1021/95586.htm
+https://mech.ycit.edu.cn/info/1132/18146.htm</v>
+      </c>
+      <c r="I836" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="837" ht="52.5" customHeight="1">
+      <c r="A837" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B837" t="str" s="3">
+        <v>滁州学院/安徽大学转发</v>
+      </c>
+      <c r="C837" t="str" s="3">
+        <v>安徽·滁州/合肥</v>
+      </c>
+      <c r="D837" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E837" t="str" s="3">
+        <v>N056实景2026完整公告，N057养老2025/N059无人应急2025全文，N058安徽大学电机2022官方转发；附件均首次失败；各平台2026—2027补漏查询。</v>
+      </c>
+      <c r="F837" t="str" s="3">
+        <v>滁州全校目录未读；2025平台2026正式新批未定位不能称不存在；安徽大学原全国截止及提交未取，转发校内期限分开。</v>
+      </c>
+      <c r="G837" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H837" t="str" s="3">
+        <v>https://www.chzu.edu.cn/2026/1003/c18559a352588/page.htm
+https://kyc.chzu.edu.cn/2025/1117/c15890a335209/page.htm
+https://www.chzu.edu.cn/2025/1117/c18154a335226/page.htm
+https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm</v>
+      </c>
+      <c r="I837" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -46222,23 +47330,83 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="111" ht="96" customHeight="1">
+    <row r="111" ht="102" customHeight="1">
       <c r="A111" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B111" t="n" s="13">
+        <v>45986</v>
+      </c>
+      <c r="C111" t="str" s="14">
+        <v>滁州学院·安徽省智能感知与健康养老工程研究中心</v>
+      </c>
+      <c r="D111" t="str" s="15">
+        <v>养老移动平台空间环境建模与主动安全感知；多模态行为理解/自然交互；动态非结构场景机器人自适应认知、行为预测、自主导航决策任务规划；健康能力评估、仿生可解释计算。</v>
+      </c>
+      <c r="E111" t="str" s="15">
+        <v>重点3万元拟1项；一般2万元拟5项。</v>
+      </c>
+      <c r="F111" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="112" ht="102" customHeight="1">
+      <c r="A112" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B112" t="n" s="13">
+        <v>44692</v>
+      </c>
+      <c r="C112" t="str" s="14">
+        <v>安徽大学·高节能电机及控制技术国家地方联合工程实验室</v>
+      </c>
+      <c r="D112" t="str" s="15">
+        <v>明确特种机器人电力巡检/消防/反恐排爆：自动导航、无线图像视频传输、避障、充电、灭火；球形关节带载闭环控制算法及硬件实现。输电、电机耦合等其他任务不因同公告全列相关。</v>
+      </c>
+      <c r="E112" t="str" s="15">
+        <v>一般2—3万元/项，按研究内容及预期成果决定。</v>
+      </c>
+      <c r="F112" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="113" ht="102" customHeight="1">
+      <c r="A113" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B113" t="n" s="13">
+        <v>45986</v>
+      </c>
+      <c r="C113" t="str" s="14">
+        <v>滁州学院·无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室</v>
+      </c>
+      <c r="D113" t="str" s="15">
+        <v>无人应急装备复杂环境视觉感知、目标识别、状态诊断；视觉任务定位跟踪与运动/执行系统协同作业控制；视觉红外传感行为多模态灾害识别预警。明确无人装备自主执行任务。</v>
+      </c>
+      <c r="E113" t="str" s="15">
+        <v>一般2万元/项，拟3项；正文成果提重点3篇但本批不设重点资助。</v>
+      </c>
+      <c r="F113" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="114" ht="96" customHeight="1">
+      <c r="A114" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B111" t="n" s="13">
+      <c r="B114" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C111" t="str" s="14">
+      <c r="C114" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D111" t="str" s="15">
+      <c r="D114" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E111" t="str" s="15">
+      <c r="E114" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F111" t="str" s="16">
+      <c r="F114" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -46434,8 +47602,8 @@
     <hyperlink ref="F100" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C101" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F101" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F111" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C111" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F114" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C114" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F102" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -46464,6 +47632,12 @@
     <hyperlink ref="F109" ns1:id="rIdResume110"/>
     <hyperlink ref="C110" location="'02项目完整详情'!A204" display="项目完整详情"/>
     <hyperlink ref="F110" ns1:id="rIdResume111"/>
+    <hyperlink ref="C111" location="'02项目完整详情'!A206" display="项目完整详情"/>
+    <hyperlink ref="F111" ns1:id="rIdResume112"/>
+    <hyperlink ref="C112" location="'02项目完整详情'!A207" display="项目完整详情"/>
+    <hyperlink ref="F112" ns1:id="rIdResume113"/>
+    <hyperlink ref="C113" location="'02项目完整详情'!A208" display="项目完整详情"/>
+    <hyperlink ref="F113" ns1:id="rIdResume114"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -18808,6 +18808,172 @@
         <v>2025独立历史批次，2026—2027未定位新正式指南；研究期到2027不是延长申报。</v>
       </c>
     </row>
+    <row r="209" ht="147" customHeight="1">
+      <c r="A209" t="str" s="3">
+        <v>N060</v>
+      </c>
+      <c r="B209" t="str" s="3">
+        <v>官方2026完整正文已读；申请DOCX验证码</v>
+      </c>
+      <c r="C209" t="str" s="3">
+        <v>西安石油大学</v>
+      </c>
+      <c r="D209" t="str" s="3">
+        <v>能源装备智能可视化检测技术陕西省高校工程研究中心</v>
+      </c>
+      <c r="E209" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F209" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G209" t="n" s="6">
+        <v>46162</v>
+      </c>
+      <c r="H209" t="str" s="3">
+        <v>17:00</v>
+      </c>
+      <c r="I209" t="str" s="3">
+        <v>实际智能检测装备任务：井下单目视频弱纹理/非均匀光照三维重建，裂缝孔洞几何复原和精度完整性验证；边缘部署孔眼形态位置异常轻量识别，中心提供视频数据集；浑浊50—100NTU图像改善及实时测井可行性；40/54mm承压照明样机100MPa、62—220mm管柱测试。应用为油气井检测仪器，不虚构机器人用途；流体配方/压裂评估不据同公告全判相关。</v>
+      </c>
+      <c r="J209" t="str" s="3">
+        <v>人民币2—4万元/项。</v>
+      </c>
+      <c r="K209" t="str" s="3">
+        <v>所在单位正式员工、硕士或中级及以上职称；有研究基础及投入时间；负责人限申报1项，年龄/在研限制未载。公告鼓励校内外，但申报表需学院审核，外校签约/负责资格细节待表。</v>
+      </c>
+      <c r="L209" t="str" s="3">
+        <v>未明确强制固定合作人/驻室次数；中心与正源井像、正实智能共建，不推定申请人已合作。</v>
+      </c>
+      <c r="M209" t="str" s="3">
+        <v>出资方西安正源井像以委托项目与西安石油大学签科研合同，定向支持中心研究；如何支付外校负责人单位、预算及报销费用/劳务/外拨比例未载，不把2—4万视个人收入。</v>
+      </c>
+      <c r="N209" t="str" s="3">
+        <v>不超过1年；起止由立项/合同确定，正文无统一日。</v>
+      </c>
+      <c r="O209" t="str" s="3">
+        <v>执行期至少中文核心1篇或中科院三区及以上SCI1篇；论文/专著报告软件专利成果等须注明中心开放基金资助。第一单位/作者顺序未载；三维重建须精度完整性验证，承压结构方向原理样机耐压密封测试。</v>
+      </c>
+      <c r="P209" t="str" s="3">
+        <v>有必要且可能申请专利的成果，专利权归出资方；论文/软件等完整IP及收益分配未载，勿写双方共有。</v>
+      </c>
+      <c r="Q209" t="str" s="3">
+        <v>学院（部）审核同意，电子申请和签章PDF于2026-05-20 17:00前发中心指定邮箱。正文没有公布邮箱，联系人手机核问；表DOCX待取。</v>
+      </c>
+      <c r="R209" t="str" s="3">
+        <v>本人博士、高校现职已知，学位对应硕士以上；本批截止。单位审核、中心合同如何接受外校PI及邮箱待确认。</v>
+      </c>
+      <c r="S209" t="str" s="3">
+        <v>申请表验证码；指定邮箱/外校负责和签约方式、经费外拨及报销详细、成果第一单位作者未取得；专利归出资方已明确不能待核成共有。</v>
+      </c>
+      <c r="T209" t="str" s="3">
+        <v>https://www.xsyu.edu.cn/info/1072/56329.htm</v>
+      </c>
+      <c r="U209" t="str" s="3">
+        <v>https://www.xsyu.edu.cn/system/_content/download.jsp?owner=1684603570&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=5702001</v>
+      </c>
+      <c r="V209" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W209" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X209" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y209" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="Z209" t="str" s="3">
+        <v>吴银川13379278661；周超18092707479；指定收件邮箱正文未载。</v>
+      </c>
+      <c r="AA209" t="str" s="3">
+        <v>保留实际视觉/三维重建/边缘识别装备任务和油气场景；合资工程中心项目委托机制，历史与当期分别记。</v>
+      </c>
+    </row>
+    <row r="210" ht="132" customHeight="1">
+      <c r="A210" t="str" s="3">
+        <v>N061</v>
+      </c>
+      <c r="B210" t="str" s="3">
+        <v>官方2025-10-30页面首次仅取得标题及平台简介；首次续读超时停止</v>
+      </c>
+      <c r="C210" t="str" s="3">
+        <v>宿迁学院</v>
+      </c>
+      <c r="D210" t="str" s="3">
+        <v>江苏省智能制造装备关键技术工程研究中心</v>
+      </c>
+      <c r="E210" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F210" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G210" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H210" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I210" t="str" s="3">
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+      </c>
+      <c r="J210" t="str" s="3">
+        <v>未取得当年金额/类型。</v>
+      </c>
+      <c r="K210" t="str" s="3">
+        <v>校内外申报条件、学位职称年龄及限项未取得。</v>
+      </c>
+      <c r="L210" t="str" s="3">
+        <v>固定合作与访问要求未取得。</v>
+      </c>
+      <c r="M210" t="str" s="3">
+        <v>费用、外拨/报销/支付节点未取得。</v>
+      </c>
+      <c r="N210" t="str" s="3">
+        <v>本轮周期未取得；简介3年关键技术突破是平台规划，不套课题周期。</v>
+      </c>
+      <c r="O210" t="str" s="3">
+        <v>论文专利样机/第一单位作者及验收未取得。</v>
+      </c>
+      <c r="P210" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="Q210" t="str" s="3">
+        <v>当年申请材料、截止及提交未取得。</v>
+      </c>
+      <c r="R210" t="str" s="3">
+        <v>本人学位现职已知；当期窗口与具体任务资格未核，不进首页。</v>
+      </c>
+      <c r="S210" t="str" s="3">
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+      </c>
+      <c r="T210" t="str" s="3">
+        <v>https://kjc.squ.edu.cn/info/1008/2302.htm</v>
+      </c>
+      <c r="U210" t="str" s="3">
+        <v>首次正文截断未取得附件具体链接，人工从原公告下载。</v>
+      </c>
+      <c r="V210" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W210" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X210" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y210" t="str" s="3">
+        <v>江苏·宿迁</v>
+      </c>
+      <c r="Z210" t="str" s="3">
+        <v>未取得当年项目联系人。</v>
+      </c>
+      <c r="AA210" t="str" s="3">
+        <v>2025官方公告线索；证据不足保待核，未按历史日期猜截止。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -19236,6 +19402,8 @@
     <hyperlink ref="T206" ns1:id="rIdResume428"/>
     <hyperlink ref="T207" ns1:id="rIdResume429"/>
     <hyperlink ref="T208" ns1:id="rIdResume430"/>
+    <hyperlink ref="T209" ns1:id="rIdResume431"/>
+    <hyperlink ref="T210" ns1:id="rIdResume432"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -45088,6 +45256,661 @@
 https://www.chzu.edu.cn/2022/0502/c18154a255066/page.htm</v>
       </c>
       <c r="I837" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="838" ht="52.5" customHeight="1">
+      <c r="A838" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B838" t="str" s="3">
+        <v>安徽省属新平台目录发现</v>
+      </c>
+      <c r="C838" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D838" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E838" t="str" s="3">
+        <v>查询：site:ahpu.edu.cn 科研平台 机器人 重点实验室 / site:ahstu.edu.cn "开放课题" 2026 2027 / site:wxc.edu.cn 机器人 重点实验室 开放基金 / site:hfuu.edu.cn "开放课题" 2026 2027；线索：实验室简介；安徽工程大学机器人实验室建设案例；2026年安徽省动物营养调控与健康重点实验室开放课题申请指南-安徽科技工程大学；科研平台；设备平台；先进数控与伺服驱动技术安徽省高校重点实验室 (培育基地)介绍</v>
+      </c>
+      <c r="F838" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G838" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H838" t="str" s="3">
+        <v>https://cee.ahpu.edu.cn/lapic/sysjj/list.htm
+https://rmic.ahpu.edu.cn/_upload/article/files/e7/58/713f187b43b5b7b81dbd6f65c6ba/096fd35c-1fff-4e7c-b1ab-53ff87e4e828.pdf
+https://newweb.ahstu.edu.cn/info/1131/400601.htm
+https://cee.ahpu.edu.cn/lapic/yqsb/list.psp
+https://rmic.ahpu.edu.cn/sxjx/list.htm
+https://kjc.ahpu.edu.cn/_t41/2020/0723/c762a138402/page.psp</v>
+      </c>
+      <c r="I838" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第371项</v>
+      </c>
+    </row>
+    <row r="839" ht="52.5" customHeight="1">
+      <c r="A839" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B839" t="str" s="3">
+        <v>河南省属新增平台目录发现</v>
+      </c>
+      <c r="C839" t="str" s="3">
+        <v>河南</v>
+      </c>
+      <c r="D839" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E839" t="str" s="3">
+        <v>查询：site:haust.edu.cn 科研平台 机器人 重点实验室 / site:zzuli.edu.cn 科研平台 机器人 重点实验室 / site:henau.edu.cn "开放基金" 2026 2027 机器人 / site:hnust.edu.cn "机器人" "开放基金" 2026；线索：科学研究-医学技术与工程学院；引进博士研究生30人，2024年济源职业技术学院高层次人才引进公告-党委研究生工作部；国家重点实验室名单；人工智能创新研究院-河南科技大学|未来产业创新研究院；协作式桌面机器人实验平台询价公告-财务与资产管理部；创新创业|研工部/研究生院组织博士研究生参观我校重点实验室-党委研究生工作部</v>
+      </c>
+      <c r="F839" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G839" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H839" t="str" s="3">
+        <v>https://yg.haust.edu.cn/xkjs1/kxyj1.htm
+https://ygb.haust.edu.cn/info/2118/23317.htm
+https://xkb.zzuli.edu.cn/2021/0909/c8049a248016/page.htm
+https://wly.haust.edu.cn/jjtd/rgzncxyjy.htm
+https://cwyzcglb.haust.edu.cn/info/1461/39341.htm
+https://ygb.haust.edu.cn/info/2002/6218.htm</v>
+      </c>
+      <c r="I839" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第372项</v>
+      </c>
+    </row>
+    <row r="840" ht="52.5" customHeight="1">
+      <c r="A840" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B840" t="str" s="3">
+        <v>山东省属与研究院补漏发现</v>
+      </c>
+      <c r="C840" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D840" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E840" t="str" s="3">
+        <v>查询：site:qlu.edu.cn "机器人" "开放基金" 2026 2027 / site:sdas.org "开放基金" 2026 机器人 / site:sdut.edu.cn 科研平台 机器人 重点实验室 / site:ytu.edu.cn "机器人" "开放课题" 2026；线索：第二届中国研究生机器人创新设计大赛预通知；科研平台；平台基地；山理工获批5个省高校未来产业科研平台-山东理工大学新闻网；科研平台；实验室与研究中心</v>
+      </c>
+      <c r="F840" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G840" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H840" t="str" s="3">
+        <v>https://yjsh.sdut.edu.cn/2020/0108/c5175a365376/page.htm
+https://qgxy.sdut.edu.cn/kxyj/listm.htm
+https://research.sdut.edu.cn/ptjd/main.htm
+https://lgwindow.sdut.edu.cn/info/1006/50943.htm
+https://qgxy.sdut.edu.cn/8398/listm.htm
+https://iec.sdut.edu.cn/sysyyjzx/list.htm</v>
+      </c>
+      <c r="I840" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第373项</v>
+      </c>
+    </row>
+    <row r="841" ht="52.5" customHeight="1">
+      <c r="A841" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B841" t="str" s="3">
+        <v>安徽工程机器人六平台机制A</v>
+      </c>
+      <c r="C841" t="str" s="3">
+        <v>安徽·芜湖</v>
+      </c>
+      <c r="D841" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E841" t="str" s="3">
+        <v>查询："智能机器人先进机构与控制技术" "开放基金" 2026 2027 / "智能装备质量与可靠性" "开放课题" / site:ahpu.edu.cn "具身智能" "开放基金" / site:ahpu.edu.cn "移动机器人" "开放课题"；线索：安徽工程大学机器人实验室建设案例；开放课题；人因工程与智能交互研究所-清华大学工业工程系；2026年度开放课题申请公告</v>
+      </c>
+      <c r="F841" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G841" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H841" t="str" s="3">
+        <v>https://rmic.ahpu.edu.cn/_upload/article/files/e7/58/713f187b43b5b7b81dbd6f65c6ba/096fd35c-1fff-4e7c-b1ab-53ff87e4e828.pdf
+https://cee.ahpu.edu.cn/lapic/kfkt/list.htm
+https://www.ie.tsinghua.edu.cn/kxyj/yjs/rygcyznjhyjs.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm</v>
+      </c>
+      <c r="I841" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第374项</v>
+      </c>
+    </row>
+    <row r="842" ht="52.5" customHeight="1">
+      <c r="A842" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B842" t="str" s="3">
+        <v>安徽工程机器人六平台机制B</v>
+      </c>
+      <c r="C842" t="str" s="3">
+        <v>安徽·芜湖</v>
+      </c>
+      <c r="D842" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E842" t="str" s="3">
+        <v>查询：site:ahpu.edu.cn "智能机械与机器人" 开放基金 / site:ahpu.edu.cn "仿生智能与智能系统" 开放课题 / site:ahpu.edu.cn "人形机器人" 开放基金 / site:ahpu.edu.cn "智能光学加工与检测" 开放基金；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F842" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G842" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H842" t="str" s="3"/>
+      <c r="I842" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第375项</v>
+      </c>
+    </row>
+    <row r="843" ht="52.5" customHeight="1">
+      <c r="A843" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B843" t="str" s="3">
+        <v>河南科技装备及自设平台补漏</v>
+      </c>
+      <c r="C843" t="str" s="3">
+        <v>河南·洛阳</v>
+      </c>
+      <c r="D843" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E843" t="str" s="3">
+        <v>查询："河南省机器人与智能控制工程研究中心" "开放" 课题 / site:haust.edu.cn "复合电源" "开放基金" / site:haust.edu.cn "智能矿山重型装备" "开放基金" 2026 2027；线索：科研平台-JDB电子；科研平台-河南科技大学信息工程学院（人工智能学院）；控制科学与工程学术学位硕士研究生培养方案</v>
+      </c>
+      <c r="F843" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G843" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H843" t="str" s="3">
+        <v>https://www.jdb-dz.com/kxyj/kypt.htm
+https://dx.haust.edu.cn/kxyj/kypt.htm
+https://aia.wust.edu.cn/__local/5/2A/AE/C34378C76B706A646A040C62CA2_37B458FA_1342FC.pdf</v>
+      </c>
+      <c r="I843" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第376项</v>
+      </c>
+    </row>
+    <row r="844" ht="52.5" customHeight="1">
+      <c r="A844" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B844" t="str" s="3">
+        <v>河南科技六机器人平台2026/27机制</v>
+      </c>
+      <c r="C844" t="str" s="3">
+        <v>河南·洛阳</v>
+      </c>
+      <c r="D844" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E844" t="str" s="3">
+        <v>查询："河南省机器人与智能系统" "开放" 基金 2026 2027 / "河南省机器人智能控制" "开放" 课题 / "河南省图像信息处理与智能检测" "开放基金" / "河南省高校智能技术与系统" "开放课题"；线索：网络_课题_基金_项目_论文_选题_热点_选题_2021最新_国家社科基金_社科规划_研究_报告_发表_选题宝；湖北开放职业学院学报（２０２６）第３９卷第１期；数据要素赋能企业创新机制研究 ——知识积累与动态能力视角</v>
+      </c>
+      <c r="F844" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G844" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H844" t="str" s="3">
+        <v>https://www.xuantibao.com/subject/detail?sid=3&amp;wid=4281
+https://hbxb.net/upfile/files/2026%E5%B9%B4/01/2026-1-20_%E9%A6%96%E7%8F%A9.pdf
+https://www.kjjb.org/article/2026/1001-7348/2026-43-6-002.htm</v>
+      </c>
+      <c r="I844" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第377项</v>
+      </c>
+    </row>
+    <row r="845" ht="52.5" customHeight="1">
+      <c r="A845" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B845" t="str" s="3">
+        <v>山东理工机械省级六平台年度机制</v>
+      </c>
+      <c r="C845" t="str" s="3">
+        <v>山东·淄博</v>
+      </c>
+      <c r="D845" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E845" t="str" s="3">
+        <v>查询："协作机器人关键技术与智能农业装备" "开放" 课题 / "高性能精密制造与复合加工" "开放基金" 2026 2027 / "风电装备测试评价与服役保障" "开放基金" / site:sdut.edu.cn "先进制造与装备" "开放课题"；线索：平台基地；附件1：2025年广东省高校自然科学类平台和项目拟立项一览表 | PDF</v>
+      </c>
+      <c r="F845" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G845" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H845" t="str" s="3">
+        <v>https://research.sdut.edu.cn/ptjd/main.htm
+https://www.scribd.com/document/938869438/%E9%99%84%E4%BB%B61-2025%E5%B9%B4%E5%B9%BF%E4%B8%9C%E7%9C%81%E9%AB%98%E6%A0%A1%E8%87%AA%E7%84%B6%E7%A7%91%E5%AD%A6%E7%B1%BB%E5%B9%B3%E5%8F%B0%E5%92%8C%E9%A1%B9%E7%9B%AE%E6%8B%9F%E7%AB%8B%E9%A1%B9%E4%B8%80%E8%A7%88%E8%A1%A8</v>
+      </c>
+      <c r="I845" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第378项</v>
+      </c>
+    </row>
+    <row r="846" ht="52.5" customHeight="1">
+      <c r="A846" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B846" t="str" s="3">
+        <v>山东省属实验室基金宽检索</v>
+      </c>
+      <c r="C846" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D846" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E846" t="str" s="3">
+        <v>查询：山东 "高校重点实验室" "机器人" "开放基金" 2026 2027 / 山东 "省重点实验室" "无人" "开放课题" 2026 / site:qlu.edu.cn "开放课题" 2027 / site:ytu.edu.cn "开放基金" 2026 智能；线索：中国科学院烟台海岸带研究所；开放课题；智能无人系统技术四川省高等学校重点实验室2026年度开放基金申报公告-智能无人系统技术四川省高等学校重点实验室；江苏省具身智能工业机器人及其人机协作高校重点实验室开放课题管理办法-电气与自动化工程学院；2025开放与合作交流-光电子器件与系统教育部广东省重点实验室；山东省科学院海洋仪器仪表研究所</v>
+      </c>
+      <c r="F846" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G846" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H846" t="str" s="3">
+        <v>https://yic.cas.cn/lep/
+https://cpnis.qlu.edu.cn/kfjl/list.htm
+https://znwrxt.sasu.edu.cn/info/1009/1062.htm
+https://dqxylib.szut.edu.cn/info/1016/27682.htm
+https://ods.szu.edu.cn/info/1029/2848.htm
+https://www.sdioi.com/ryxx/1359.html</v>
+      </c>
+      <c r="I846" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第379项</v>
+      </c>
+    </row>
+    <row r="847" ht="52.5" customHeight="1">
+      <c r="A847" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B847" t="str" s="3">
+        <v>中央高校外部平台业务费补漏2026/27</v>
+      </c>
+      <c r="C847" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D847" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E847" t="str" s="3">
+        <v>查询："2026" "基本科研业务费" "开放基金" "机器人" / "2027" "基本科研业务费" "开放课题" / "2026" "开放基金" "校外" "智能装备" / "2026" "开放课题" "省高校" "控制"；线索：福建省现代分离分析科学与技术重点实验室关于公布2026年度开放课题评审结果的... - 项目立项公示 - 泛研网；能源装备智能可视化检测技术陕西省高校工程研究中心2026年度开放基金课题申请公告-西安石油大学；申请！一批次重点实验室课题基金申请指南 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑；关于公布江苏省智能制造装备关键技术工程研究中心2025年度开放基金申请的通知-科技处；2026年度开放研究基金申请指南-数字教育湖北省重点实验室；2026年行星地质与深空探测湖北省重点实验室 开放基金申请指南-地球科学学院</v>
+      </c>
+      <c r="F847" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G847" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H847" t="str" s="3">
+        <v>https://www.funresearch.cn/granted/info/NmEzY2RlZDItNDdhMC00MDcxLTk4ODEtZjU2NTNmOTBkN2Jk
+https://www.xsyu.edu.cn/info/1072/56329.htm
+https://www.letpub.com.cn/index.php?article_id=3242&amp;page=grant_article_details
+https://kjc.squ.edu.cn/info/1008/2302.htm
+https://hrcei.ccnu.edu.cn/info/1203/3415.htm
+https://dxy.cug.edu.cn/info/1035/9306.htm</v>
+      </c>
+      <c r="I847" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第380项</v>
+      </c>
+    </row>
+    <row r="848" ht="52.5" customHeight="1">
+      <c r="A848" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B848" t="str" s="3">
+        <v>全国省属机器人2026/27宽检索补漏A</v>
+      </c>
+      <c r="C848" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D848" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E848" t="str" s="3">
+        <v>查询："2026" "开放基金" "人机交互" 实验室 / "2027" "开放课题" "机器人" / "2026" "开放课题" "柔顺控制" / "2026" "开放基金" "具身智能"；线索：多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；上海交大研究生院主页平台管理系统 胡洁--中文主页-- 高端重载机器人全国重点实验室开放课题；〖27届校招〗世界模型研究员_广州小鹏汽车科技有限公司校招_牛客网；智能制造装备与技术全国重点实验室2027年度开放课题申请通知-智能制造装备与技术全国重点实验室；2026年度开放基金评审结果公告；先进轨道交通自主运行全国重点实验室 开放课题基金申请指南（2027年） - 先进轨道交通自主运行全国重点实验室</v>
+      </c>
+      <c r="F848" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G848" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H848" t="str" s="3">
+        <v>https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://faculty.sjtu.edu.cn/hujie/zh_CN/kyxm/144025/content/114021.htm
+https://www.nowcoder.com/jobs/detail/461376
+https://imet.hust.edu.cn/info/1031/2870.htm
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm
+https://raolab.bjtu.edu.cn/news/3521.html</v>
+      </c>
+      <c r="I848" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第381项</v>
+      </c>
+    </row>
+    <row r="849" ht="52.5" customHeight="1">
+      <c r="A849" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B849" t="str" s="3">
+        <v>全国机器人任务2026/27宽检索补漏B</v>
+      </c>
+      <c r="C849" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D849" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E849" t="str" s="3">
+        <v>查询："2026" "开放课题" "自主导航" / "2026" "开放基金" "机械臂" / "2027" "开放基金" "机器人" / "2026" "开放课题" "机器人感知"；线索：机器视觉与虚拟现实山西省重点实验室 2026年度开放基金申请指南-中北大学；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；〖信息学院|科研〗关于2026年度智能感知与自主控制教育部工程中心开放课题暨揭榜挂帅任务的通知-北京工业大学信息科学技术学院；2026年度跨媒体通用人工智能全国重点实验室开放课题申请指南-北京大学智能学院；警用智能机器人达州市重点实验室2026年度开放基金申报公告-警用智能机器人达州市重点实验室；2026年度开放课题申请指南----处理器芯片全国重点实验室</v>
+      </c>
+      <c r="F849" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G849" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H849" t="str" s="3">
+        <v>https://www.nuc.edu.cn/info/1014/62433.htm
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://sist.bjut.edu.cn/info/1222/5293.htm
+https://sist.pku.edu.cn/info/2320/10785.htm
+https://jqr.sasu.edu.cn/info/1009/1061.htm
+https://sklp.ict.ac.cn/yxgl/kfkt/zntg/202606/t20260609_841349.html</v>
+      </c>
+      <c r="I849" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第382项</v>
+      </c>
+    </row>
+    <row r="850" ht="52.5" customHeight="1">
+      <c r="A850" t="str" s="3">
+        <v>2026-10-09河南安徽山东平台与全国年度补漏</v>
+      </c>
+      <c r="B850" t="str" s="3">
+        <v>西安石油及宿迁新机制2027/2026补漏</v>
+      </c>
+      <c r="C850" t="str" s="3">
+        <v>陕西·西安/江苏·宿迁</v>
+      </c>
+      <c r="D850" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E850" t="str" s="3">
+        <v>查询："能源装备智能可视化检测" "开放基金" 2027 / "江苏省智能制造装备关键技术" "开放基金" 2026 2027 / site:xsyu.edu.cn 科研基地 机器人 / site:squ.edu.cn "开放课题" "机器人" 2026；线索：能源装备智能可视化检测技术陕西省高校工程研究中心2026年度开放基金课题申请公告-西安石油大学；关于公布江苏省智能制造装备关键技术工程研究中心2025年度开放基金申请的通知-科技处；2025年度江苏省智能制造装备关键技术工程研究中心开放基金项目立项评审结果公示-科技处</v>
+      </c>
+      <c r="F850" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G850" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H850" t="str" s="3">
+        <v>https://www.xsyu.edu.cn/info/1072/56329.htm
+https://kjc.squ.edu.cn/info/1008/2302.htm
+https://kjc.squ.edu.cn/info/1008/2331.htm</v>
+      </c>
+      <c r="I850" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第383项</v>
+      </c>
+    </row>
+    <row r="851" ht="52.5" customHeight="1">
+      <c r="A851" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B851" t="str" s="3">
+        <v>西安石油大学</v>
+      </c>
+      <c r="C851" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D851" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E851" t="str" s="3">
+        <v>能源装备智能可视化检测技术陕西省高校工程研究中心；2026；N060；官方2026完整正文已读；申请DOCX验证码</v>
+      </c>
+      <c r="F851" t="str" s="3">
+        <v>申请表验证码；指定邮箱/外校负责和签约方式、经费外拨及报销详细、成果第一单位作者未取得；专利归出资方已明确不能待核成共有。</v>
+      </c>
+      <c r="G851" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H851" t="str" s="3">
+        <v>https://www.xsyu.edu.cn/info/1072/56329.htm</v>
+      </c>
+      <c r="I851" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="852" ht="52.5" customHeight="1">
+      <c r="A852" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B852" t="str" s="3">
+        <v>宿迁学院</v>
+      </c>
+      <c r="C852" t="str" s="3">
+        <v>江苏·宿迁</v>
+      </c>
+      <c r="D852" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E852" t="str" s="3">
+        <v>江苏省智能制造装备关键技术工程研究中心；2025；N061；官方2025-10-30页面首次仅取得标题及平台简介；首次续读超时停止</v>
+      </c>
+      <c r="F852" t="str" s="3">
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+      </c>
+      <c r="G852" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H852" t="str" s="3">
+        <v>https://kjc.squ.edu.cn/info/1008/2302.htm</v>
+      </c>
+      <c r="I852" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="853" ht="52.5" customHeight="1">
+      <c r="A853" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B853" t="str" s="3">
+        <v>河南科技大学</v>
+      </c>
+      <c r="C853" t="str" s="3">
+        <v>河南·洛阳</v>
+      </c>
+      <c r="D853" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E853" t="str" s="3">
+        <v>信息/人工智能学院科研机构完整16平台已读；机器人与智能系统省室、机器人智能控制/图像检测国际联合、机器人控制工程中心、高校智能技术开放室、复合电源智能控制及矿山全国平台逐名机制2026—2027及历史查。</v>
+      </c>
+      <c r="F853" t="str" s="3">
+        <v>信息学院完整不等于全校；机电/医工及机器人具体年度基金未取，查询未定位不认定无资助。</v>
+      </c>
+      <c r="G853" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H853" t="str" s="3">
+        <v>https://dx.haust.edu.cn/xygk/jgsz/kyji_gb.htm</v>
+      </c>
+      <c r="I853" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="854" ht="52.5" customHeight="1">
+      <c r="A854" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B854" t="str" s="3">
+        <v>安徽工程大学</v>
+      </c>
+      <c r="C854" t="str" s="3">
+        <v>安徽·芜湖</v>
+      </c>
+      <c r="D854" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E854" t="str" s="3">
+        <v>AI学院2026-05更新简介完整，国家机器人机构控制中心/智能装备可靠性省共建重点室及7研究中心所；2批逐名2026—2027机制查询；M042先进感知控制旧指南复用。</v>
+      </c>
+      <c r="F854" t="str" s="3">
+        <v>14教学实践平台非科研基金；先进感知控制开放目录首次超时交人工，旧已核项目不退回；机械/其他学院目录未齐。</v>
+      </c>
+      <c r="G854" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H854" t="str" s="3">
+        <v>https://sai.ahpu.edu.cn/7359/list.htm
+https://cee.ahpu.edu.cn/lapic/kfkt/list.htm</v>
+      </c>
+      <c r="I854" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="855" ht="52.5" customHeight="1">
+      <c r="A855" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B855" t="str" s="3">
+        <v>山东理工大学</v>
+      </c>
+      <c r="C855" t="str" s="3">
+        <v>山东·淄博</v>
+      </c>
+      <c r="D855" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E855" t="str" s="3">
+        <v>机械简介全文截至2025-04，12国家省教学科研平台但只列8名；协作机器人农业未来产业/精密加工/风电测试/先进制造平台逐名基金查询；机械科研平台页首成功无数据，校级目录首超时。</v>
+      </c>
+      <c r="F855" t="str" s="3">
+        <v>12总数不当完整12名；其余4与教学科研分类未清，校级/机械平台人工补取；不把获课题新闻当资助。</v>
+      </c>
+      <c r="G855" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H855" t="str" s="3">
+        <v>https://jxxy.sdut.edu.cn/4297/list.htm
+https://jxxy.sdut.edu.cn/kypt/list.htm
+https://research.sdut.edu.cn/ptjd/main.htm</v>
+      </c>
+      <c r="I855" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="856" ht="52.5" customHeight="1">
+      <c r="A856" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B856" t="str" s="3">
+        <v>齐鲁工业大学（山东省科学院）</v>
+      </c>
+      <c r="C856" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D856" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E856" t="str" s="3">
+        <v>网络融合开放课题目录首次超时，M067无人系统2026复用；2026—2027省属机制宽补漏。</v>
+      </c>
+      <c r="F856" t="str" s="3">
+        <v>cpnis目录实验室全名/任务及资金尚未取得，不自造项目；科学院其他所及校级目录未齐。</v>
+      </c>
+      <c r="G856" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H856" t="str" s="3">
+        <v>https://cpnis.qlu.edu.cn/kfjl/list.htm</v>
+      </c>
+      <c r="I856" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="857" ht="52.5" customHeight="1">
+      <c r="A857" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B857" t="str" s="3">
+        <v>中国人民大学</v>
+      </c>
+      <c r="C857" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D857" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E857" t="str" s="3">
+        <v>数据工程与知识工程2026正式完整指南已读，三项数据库内核/数据空间/社会治理可视分析，无机器人/相关智能装备具体任务，E083排除。</v>
+      </c>
+      <c r="F857" t="str" s="3">
+        <v>仅本年度3方向排除，其他学院机器人平台不据此排除；不深下载无关申报附件。</v>
+      </c>
+      <c r="G857" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H857" t="str" s="3">
+        <v>https://deke.ruc.edu.cn/kfkt/zntg/60672dcdbb0f47c0be213de8ef93d5e9.htm</v>
+      </c>
+      <c r="I857" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="858" ht="52.5" customHeight="1">
+      <c r="A858" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B858" t="str" s="3">
+        <v>全国年度交叉补漏</v>
+      </c>
+      <c r="C858" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D858" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E858" t="str" s="3">
+        <v>3组12词人机/机械臂/自主导航/机器人感知/业务费校外2026—2027；R0012027轨道、M001/M010/M014/M018/M059/M068/M078和M038内部排除逐URL对账复用。</v>
+      </c>
+      <c r="F858" t="str" s="3">
+        <v>跨省搜索不能算该省覆盖；未新取旧同轮公告，仍有逐机构目录未全，不能把宽检索当全国完成。</v>
+      </c>
+      <c r="G858" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H858" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+      <c r="I858" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -45819,24 +46642,24 @@
         <v>公告</v>
       </c>
     </row>
-    <row r="36" ht="66" customHeight="1">
-      <c r="A36" s="18" t="str">
+    <row r="36" ht="177" customHeight="1">
+      <c r="A36" t="str" s="18">
         <v>已截止</v>
       </c>
-      <c r="B36" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
-      </c>
-      <c r="C36" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室</v>
-      </c>
-      <c r="D36" s="15" t="str">
-        <v>工业机器人传动、机电耦合与高端装备传动</v>
-      </c>
-      <c r="E36" s="15" t="str">
-        <v>面上5—8万元。</v>
-      </c>
-      <c r="F36" s="16" t="str">
-        <v>公告</v>
+      <c r="B36" t="n" s="13">
+        <v>46162</v>
+      </c>
+      <c r="C36" t="str" s="14">
+        <v>西安石油大学·能源装备智能可视化检测技术陕西省高校工程研究中心</v>
+      </c>
+      <c r="D36" t="str" s="15">
+        <v>实际智能检测装备任务：井下单目视频弱纹理/非均匀光照三维重建，裂缝孔洞几何复原和精度完整性验证；边缘部署孔眼形态位置异常轻量识别，中心提供视频数据集；浑浊50—100NTU图像改善及实时测井可行性；40/54mm承压照明样机100MPa、62—220mm管柱测试。应用为油气井检测仪器，不虚构机器人用途；流体配方/压裂评估不据同公告全判相关。</v>
+      </c>
+      <c r="E36" t="str" s="15">
+        <v>人民币2—4万元/项。</v>
+      </c>
+      <c r="F36" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="37" ht="66" customHeight="1">
@@ -45844,16 +46667,16 @@
         <v>已截止</v>
       </c>
       <c r="B37" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C37" s="14" t="str">
-        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室</v>
       </c>
       <c r="D37" s="15" t="str">
-        <v>具身智能世界模型与开放环境视觉感知</v>
+        <v>工业机器人传动、机电耦合与高端装备传动</v>
       </c>
       <c r="E37" s="15" t="str">
-        <v>3万元</v>
+        <v>面上5—8万元。</v>
       </c>
       <c r="F37" s="16" t="str">
         <v>公告</v>
@@ -45864,16 +46687,16 @@
         <v>已截止</v>
       </c>
       <c r="B38" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C38" s="14" t="str">
-        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
+        <v>重庆大学·生物感知与多模态智能信息处理重庆市重点实验室</v>
       </c>
       <c r="D38" s="15" t="str">
-        <v>山区建造装备及机器人</v>
+        <v>具身智能世界模型与开放环境视觉感知</v>
       </c>
       <c r="E38" s="15" t="str">
-        <v>每项6万元。</v>
+        <v>3万元</v>
       </c>
       <c r="F38" s="16" t="str">
         <v>公告</v>
@@ -45884,16 +46707,16 @@
         <v>已截止</v>
       </c>
       <c r="B39" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C39" s="14" t="str">
-        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
+        <v>重庆大学·山区土木工程安全与韧性全国重点实验室</v>
       </c>
       <c r="D39" s="15" t="str">
-        <v>桥梁检测机器人与无人巡检装备</v>
+        <v>山区建造装备及机器人</v>
       </c>
       <c r="E39" s="15" t="str">
-        <v>5—10万元</v>
+        <v>每项6万元。</v>
       </c>
       <c r="F39" s="16" t="str">
         <v>公告</v>
@@ -45904,17 +46727,16 @@
         <v>已截止</v>
       </c>
       <c r="B40" s="13" t="d">
-        <v>2026-09-01T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C40" s="14" t="str">
-        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
+        <v>重庆建筑工程职业学院（联合交通企业共建）·山地城市交通设施智能检测重庆市高校工程研究中心</v>
       </c>
       <c r="D40" s="15" t="str">
-        <v>工业机器人及智能产线运维、故障预测与控制</v>
+        <v>桥梁检测机器人与无人巡检装备</v>
       </c>
       <c r="E40" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F40" s="16" t="str">
         <v>公告</v>
@@ -45925,13 +46747,13 @@
         <v>已截止</v>
       </c>
       <c r="B41" s="13" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-09-01T00:00:00.000Z</v>
       </c>
       <c r="C41" s="14" t="str">
-        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
+        <v>重庆城市职业学院·工业机器人运维重庆市高校工程中心</v>
       </c>
       <c r="D41" s="15" t="str">
-        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
+        <v>工业机器人及智能产线运维、故障预测与控制</v>
       </c>
       <c r="E41" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -45946,13 +46768,13 @@
         <v>已截止</v>
       </c>
       <c r="B42" s="13" t="d">
-        <v>2025-02-28T00:00:00.000Z</v>
+        <v>2026-05-22T00:00:00.000Z</v>
       </c>
       <c r="C42" s="14" t="str">
-        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
+        <v>徐工集团·高端工程机械智能制造全国重点实验室</v>
       </c>
       <c r="D42" s="15" t="str">
-        <v>重载机器人减速器、直驱电机及关键部件</v>
+        <v>工程机械多源感知、智能运动控制及智能制造装备（具体课题指标需逐项遵守）</v>
       </c>
       <c r="E42" s="15" t="str">
         <v>未在已取得官方资料中明确；
@@ -45967,16 +46789,17 @@
         <v>已截止</v>
       </c>
       <c r="B43" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-02-28T00:00:00.000Z</v>
       </c>
       <c r="C43" s="14" t="str">
-        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
+        <v>美的集团·重载机器人全国重点实验室（蓝橙实验室）</v>
       </c>
       <c r="D43" s="15" t="str">
-        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
+        <v>重载机器人减速器、直驱电机及关键部件</v>
       </c>
       <c r="E43" s="15" t="str">
-        <v>重点20万元；一般10万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F43" s="16" t="str">
         <v>公告</v>
@@ -45987,16 +46810,16 @@
         <v>已截止</v>
       </c>
       <c r="B44" s="13" t="d">
-        <v>2026-06-14T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C44" s="14" t="str">
-        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
+        <v>清华大学·智能绿色车辆与交通全国重点实验室</v>
       </c>
       <c r="D44" s="15" t="str">
-        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
+        <v>高可靠线控智能底盘；智能网联汽车安全驾驶脑（不以电池、热电动力方向作为机器人证据）</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>10万元</v>
+        <v>重点20万元；一般10万元</v>
       </c>
       <c r="F44" s="16" t="str">
         <v>公告</v>
@@ -46007,16 +46830,16 @@
         <v>已截止</v>
       </c>
       <c r="B45" s="13" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2026-06-14T00:00:00.000Z</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
+        <v>中国科学院计算技术研究所·处理器芯片全国重点实验室</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
+        <v>机器人VLA实时推理体系结构，抓取、移动与装配任务的实时控制</v>
       </c>
       <c r="E45" s="15" t="str">
-        <v>其他一般≤10万、重点≤15万</v>
+        <v>10万元</v>
       </c>
       <c r="F45" s="16" t="str">
         <v>公告</v>
@@ -46027,16 +46850,16 @@
         <v>已截止</v>
       </c>
       <c r="B46" s="13" t="d">
-        <v>2026-09-30T00:00:00.000Z</v>
+        <v>2026-09-24T00:00:00.000Z</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
+        <v>中国标准化研究院·人因与工效学重点实验室等多平台联合（2026）</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
+        <v>人机交互工效、动态人体功能可达与接触压力（须遵守联合平台具体指南）</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>10—15万元</v>
+        <v>其他一般≤10万、重点≤15万</v>
       </c>
       <c r="F46" s="16" t="str">
         <v>公告</v>
@@ -46047,16 +46870,16 @@
         <v>已截止</v>
       </c>
       <c r="B47" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-09-30T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
+        <v>中国科学院计算技术研究所·智能算法安全全国重点实验室</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
+        <v>2026指南B.4：视觉—语言—动作模型的物理对抗攻击、迁移与动作安全</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>3万元（首拨1万元，中期2万元）</v>
+        <v>10—15万元</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
@@ -46067,17 +46890,16 @@
         <v>已截止</v>
       </c>
       <c r="B48" s="13" t="d">
-        <v>2022-10-30T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
+        <v>长安大学·道路施工技术与装备教育部重点实验室</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
+        <v>道路建养装备智能控制（限具体装备任务，不泛化为施工机器人）</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>已核官方2022历史公告：5万元/项；
-未取得2026正式指南，不将历史额度视为当期额度。</v>
+        <v>3万元（首拨1万元，中期2万元）</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
@@ -46088,16 +46910,17 @@
         <v>已截止</v>
       </c>
       <c r="B49" s="13" t="d">
-        <v>2022-11-04T00:00:00.000Z</v>
+        <v>2022-10-30T00:00:00.000Z</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
+        <v>哈尔滨理工大学·先进制造智能化技术教育部重点实验室</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
+        <v>机器人辅助医疗装备及医工学技术（采用2022正式指南，不沿用双臂模仿学习概括）</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>一般2万元；重点4—6万元</v>
+        <v>已核官方2022历史公告：5万元/项；
+未取得2026正式指南，不将历史额度视为当期额度。</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
@@ -46108,16 +46931,16 @@
         <v>已截止</v>
       </c>
       <c r="B50" s="13" t="d">
-        <v>2023-07-30T00:00:00.000Z</v>
+        <v>2022-11-04T00:00:00.000Z</v>
       </c>
       <c r="C50" s="14" t="str">
-        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
+        <v>阳光学院·福建省空间信息感知与智能处理重点实验室</v>
       </c>
       <c r="D50" s="15" t="str">
-        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
+        <v>机器人导航：SLAM与视觉导航、雷达视觉融合、深度学习路径规划、ROS移动机器人开发</v>
       </c>
       <c r="E50" s="15" t="str">
-        <v>拟资助8—10项；单项金额未载</v>
+        <v>一般2万元；重点4—6万元</v>
       </c>
       <c r="F50" s="16" t="str">
         <v>公告</v>
@@ -46128,16 +46951,16 @@
         <v>已截止</v>
       </c>
       <c r="B51" s="13" t="d">
-        <v>2024-09-30T00:00:00.000Z</v>
+        <v>2023-07-30T00:00:00.000Z</v>
       </c>
       <c r="C51" s="14" t="str">
-        <v>南昌大学·智能机器人江西省重点实验室</v>
+        <v>中北大学·山西省恶劣环境智能装备技术重点实验室</v>
       </c>
       <c r="D51" s="15" t="str">
-        <v>智能机器人机构、感知与控制</v>
+        <v>开放方向（六）：机器人理论及技术；不以其他材料类方向作为保留依据</v>
       </c>
       <c r="E51" s="15" t="str">
-        <v>重点3万元、一般2万元（2024年度）</v>
+        <v>拟资助8—10项；单项金额未载</v>
       </c>
       <c r="F51" s="16" t="str">
         <v>公告</v>
@@ -46148,16 +46971,16 @@
         <v>已截止</v>
       </c>
       <c r="B52" s="13" t="d">
-        <v>2025-03-31T00:00:00.000Z</v>
+        <v>2024-09-30T00:00:00.000Z</v>
       </c>
       <c r="C52" s="14" t="str">
-        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
+        <v>南昌大学·智能机器人江西省重点实验室</v>
       </c>
       <c r="D52" s="15" t="str">
-        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
+        <v>智能机器人机构、感知与控制</v>
       </c>
       <c r="E52" s="15" t="str">
-        <v>2—3万元/项左右</v>
+        <v>重点3万元、一般2万元（2024年度）</v>
       </c>
       <c r="F52" s="16" t="str">
         <v>公告</v>
@@ -46168,16 +46991,16 @@
         <v>已截止</v>
       </c>
       <c r="B53" s="13" t="d">
-        <v>2025-04-25T00:00:00.000Z</v>
+        <v>2025-03-31T00:00:00.000Z</v>
       </c>
       <c r="C53" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>浙江大学·全省农业智能感知与机器人重点实验室</v>
       </c>
       <c r="D53" s="15" t="str">
-        <v>仿生机器人、新型驱动与感知及仿生装备</v>
+        <v>农业信息感知；作物收获与移栽装备；动物饲喂和产后处理机器人</v>
       </c>
       <c r="E53" s="15" t="str">
-        <v>5万元</v>
+        <v>2—3万元/项左右</v>
       </c>
       <c r="F53" s="16" t="str">
         <v>公告</v>
@@ -46188,16 +47011,16 @@
         <v>已截止</v>
       </c>
       <c r="B54" s="13" t="d">
-        <v>2025-04-30T00:00:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C54" s="14" t="str">
-        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D54" s="15" t="str">
-        <v>共融机器人控制、复杂智能体系统协同与控制</v>
+        <v>仿生机器人、新型驱动与感知及仿生装备</v>
       </c>
       <c r="E54" s="15" t="str">
-        <v>评审确定</v>
+        <v>5万元</v>
       </c>
       <c r="F54" s="16" t="str">
         <v>公告</v>
@@ -46208,16 +47031,16 @@
         <v>已截止</v>
       </c>
       <c r="B55" s="13" t="d">
-        <v>2025-09-03T00:00:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C55" s="14" t="str">
-        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
+        <v>安徽·安徽工业大学·复杂系统多学科管理与控制安徽普通高校重点实验室</v>
       </c>
       <c r="D55" s="15" t="str">
-        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
+        <v>共融机器人控制、复杂智能体系统协同与控制</v>
       </c>
       <c r="E55" s="15" t="str">
-        <v>5万元</v>
+        <v>评审确定</v>
       </c>
       <c r="F55" s="16" t="str">
         <v>公告</v>
@@ -46228,16 +47051,16 @@
         <v>已截止</v>
       </c>
       <c r="B56" s="13" t="d">
-        <v>2025-09-20T00:00:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C56" s="14" t="str">
-        <v>同济大学·自主智能无人系统全国重点实验室</v>
+        <v>安徽工程大学·高端装备先进感知与智能控制教育部重点实验室</v>
       </c>
       <c r="D56" s="15" t="str">
-        <v>自主智能无人系统与机器人感知、决策、控制</v>
+        <v>工业机器人控制与智能制造；无人机飞控与低空智联</v>
       </c>
       <c r="E56" s="15" t="str">
-        <v>一般5—10万元、重点20—30万元</v>
+        <v>5万元</v>
       </c>
       <c r="F56" s="16" t="str">
         <v>公告</v>
@@ -46248,17 +47071,16 @@
         <v>已截止</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2025-10-31T00:00:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
+        <v>同济大学·自主智能无人系统全国重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>机器人技术与系统、机器人学习、感知与控制</v>
+        <v>自主智能无人系统与机器人感知、决策、控制</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>一般5—10万元、重点20—30万元</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
@@ -46269,17 +47091,17 @@
         <v>已截止</v>
       </c>
       <c r="B58" s="13" t="d">
-        <v>2025-11-03T00:00:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C58" s="14" t="str">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
+        <v>哈尔滨工业大学·机器人技术与系统全国重点实验室</v>
       </c>
       <c r="D58" s="15" t="str">
-        <v>智能机器人感知、控制与系统</v>
+        <v>机器人技术与系统、机器人学习、感知与控制</v>
       </c>
       <c r="E58" s="15" t="str">
-        <v>校外开放基金1万元/项，拟5项；
-校内创新基金不同计划</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F58" s="16" t="str">
         <v>公告</v>
@@ -46290,16 +47112,17 @@
         <v>已截止</v>
       </c>
       <c r="B59" s="13" t="d">
-        <v>2025-11-07T00:00:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
+        <v>智能机器人感知、控制与系统</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>2万元</v>
+        <v>校外开放基金1万元/项，拟5项；
+校内创新基金不同计划</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
@@ -46310,16 +47133,16 @@
         <v>已截止</v>
       </c>
       <c r="B60" s="13" t="d">
-        <v>2025-11-14T00:00:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>上海交通大学·机械系统与振动全国重点实验室</v>
+        <v>中原工学院·河南省计算智能与智能系统重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>机器人设计、自主学习与神经接口</v>
+        <v>无人机相关优化及感知、规划与控制（限无人装备任务）</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>10—15万元</v>
+        <v>2万元</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
@@ -46330,16 +47153,16 @@
         <v>已截止</v>
       </c>
       <c r="B61" s="13" t="d">
-        <v>2025-11-21T00:00:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C61" s="14" t="str">
-        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
+        <v>上海交通大学·机械系统与振动全国重点实验室</v>
       </c>
       <c r="D61" s="15" t="str">
-        <v>机器人视觉相关计算与随机数学方法</v>
+        <v>机器人设计、自主学习与神经接口</v>
       </c>
       <c r="E61" s="15" t="str">
-        <v>1—2万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F61" s="16" t="str">
         <v>公告</v>
@@ -46350,16 +47173,16 @@
         <v>已截止</v>
       </c>
       <c r="B62" s="13" t="d">
-        <v>2025-11-30T00:00:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C62" s="14" t="str">
-        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
+        <v>湖南师范大学·计算与随机数学教育部重点实验室</v>
       </c>
       <c r="D62" s="15" t="str">
-        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
+        <v>机器人视觉相关计算与随机数学方法</v>
       </c>
       <c r="E62" s="15" t="str">
-        <v>不超过3万元</v>
+        <v>1—2万元</v>
       </c>
       <c r="F62" s="16" t="str">
         <v>公告</v>
@@ -46370,16 +47193,16 @@
         <v>已截止</v>
       </c>
       <c r="B63" s="13" t="d">
-        <v>2025-12-20T00:00:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C63" s="14" t="str">
-        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
+        <v>安徽工业大学·安徽省特种重载机器人重点实验室</v>
       </c>
       <c r="D63" s="15" t="str">
-        <v>山地农业机器人、果实收获视觉与智能农机</v>
+        <v>特种重载机器人、机器视觉、多源信息融合与控制</v>
       </c>
       <c r="E63" s="15" t="str">
-        <v>不超过5万元</v>
+        <v>不超过3万元</v>
       </c>
       <c r="F63" s="16" t="str">
         <v>公告</v>
@@ -46390,16 +47213,16 @@
         <v>已截止</v>
       </c>
       <c r="B64" s="13" t="d">
-        <v>2025-12-31T00:00:00.000Z</v>
+        <v>2025-12-20T00:00:00.000Z</v>
       </c>
       <c r="C64" s="14" t="str">
-        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
+        <v>贵州大学·贵州省山地智能农机全省重点实验室</v>
       </c>
       <c r="D64" s="15" t="str">
-        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
+        <v>山地农业机器人、果实收获视觉与智能农机</v>
       </c>
       <c r="E64" s="15" t="str">
-        <v>重点5万元、一般3万元</v>
+        <v>不超过5万元</v>
       </c>
       <c r="F64" s="16" t="str">
         <v>公告</v>
@@ -46410,16 +47233,16 @@
         <v>已截止</v>
       </c>
       <c r="B65" s="13" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C65" s="14" t="str">
-        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
+        <v>华东交通大学·交通智能运维技术与装备教育部重点实验室</v>
       </c>
       <c r="D65" s="15" t="str">
-        <v>深海无人潜航装备与智能控制</v>
+        <v>交通运维机器人设计、焊接、搬运、巡检与修复</v>
       </c>
       <c r="E65" s="15" t="str">
-        <v>不超过10万元</v>
+        <v>重点5万元、一般3万元</v>
       </c>
       <c r="F65" s="16" t="str">
         <v>公告</v>
@@ -46430,16 +47253,16 @@
         <v>已截止</v>
       </c>
       <c r="B66" s="13" t="d">
-        <v>2026-01-31T00:00:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C66" s="14" t="str">
-        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
+        <v>中国科学院深海科学与工程研究所·深海科学与智能技术全国重点实验室</v>
       </c>
       <c r="D66" s="15" t="str">
-        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
+        <v>深海无人潜航装备与智能控制</v>
       </c>
       <c r="E66" s="15" t="str">
-        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
+        <v>不超过10万元</v>
       </c>
       <c r="F66" s="16" t="str">
         <v>公告</v>
@@ -46450,16 +47273,16 @@
         <v>已截止</v>
       </c>
       <c r="B67" s="13" t="d">
-        <v>2026-03-10T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C67" s="14" t="str">
-        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
+        <v>天津大学·水利工程智能建设与运维全国重点实验室</v>
       </c>
       <c r="D67" s="15" t="str">
-        <v>工业机器人与柔性制造产线集成</v>
+        <v>少人化/无人化智能建设装备；异质智能建设装备群协同与规模化施工</v>
       </c>
       <c r="E67" s="15" t="str">
-        <v>4万元</v>
+        <v>一般5—8万元/项；特殊课题可经学委会专项审批增加，未载上限。</v>
       </c>
       <c r="F67" s="16" t="str">
         <v>公告</v>
@@ -46470,16 +47293,16 @@
         <v>已截止</v>
       </c>
       <c r="B68" s="13" t="d">
-        <v>2026-03-20T00:00:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C68" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室</v>
+        <v>厦门工学院·柔性制造装备集成福建省高校重点实验室</v>
       </c>
       <c r="D68" s="15" t="str">
-        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
+        <v>工业机器人与柔性制造产线集成</v>
       </c>
       <c r="E68" s="15" t="str">
-        <v>单项不超过10万元</v>
+        <v>4万元</v>
       </c>
       <c r="F68" s="16" t="str">
         <v>公告</v>
@@ -46490,16 +47313,16 @@
         <v>已截止</v>
       </c>
       <c r="B69" s="13" t="d">
-        <v>2026-04-15T00:00:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C69" s="14" t="str">
-        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室</v>
       </c>
       <c r="D69" s="15" t="str">
-        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
+        <v>交叉前沿中的智能无人系统；工艺、设备与控制一体化</v>
       </c>
       <c r="E69" s="15" t="str">
-        <v>一般5—8万元；重点20万元</v>
+        <v>单项不超过10万元</v>
       </c>
       <c r="F69" s="16" t="str">
         <v>公告</v>
@@ -46510,16 +47333,16 @@
         <v>已截止</v>
       </c>
       <c r="B70" s="13" t="d">
-        <v>2026-04-20T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C70" s="14" t="str">
-        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
+        <v>吉林大学·汽车底盘集成与仿生全国重点实验室</v>
       </c>
       <c r="D70" s="15" t="str">
-        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
+        <v>底盘动力学一体化自学习控制与域控制器；数字孪生智能运维、动力学仿真与测试装备</v>
       </c>
       <c r="E70" s="15" t="str">
-        <v>5万元</v>
+        <v>一般5—8万元；重点20万元</v>
       </c>
       <c r="F70" s="16" t="str">
         <v>公告</v>
@@ -46533,14 +47356,13 @@
         <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C71" s="14" t="str">
-        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
+        <v>宁波数字孪生（东方理工）研究院·宁波市空间智能与数字衍生重点实验室</v>
       </c>
       <c r="D71" s="15" t="str">
-        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
+        <v>人形机器人空间交互、地面多智能体协同与无人机群智能交互</v>
       </c>
       <c r="E71" s="15" t="str">
-        <v>单项原则上不超过10万元；
-100万元是本批次总额，不是单项额度。</v>
+        <v>5万元</v>
       </c>
       <c r="F71" s="16" t="str">
         <v>公告</v>
@@ -46551,16 +47373,17 @@
         <v>已截止</v>
       </c>
       <c r="B72" s="13" t="d">
-        <v>2026-04-22T00:00:00.000Z</v>
+        <v>2026-04-20T00:00:00.000Z</v>
       </c>
       <c r="C72" s="14" t="str">
-        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
+        <v>浙江大学·工业控制技术全国重点实验室（湖控专项）</v>
       </c>
       <c r="D72" s="15" t="str">
-        <v>无人系统多源感知、导航与控制</v>
+        <v>自主协同智能控制装备与智能无人系统（湖控专项）</v>
       </c>
       <c r="E72" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>单项原则上不超过10万元；
+100万元是本批次总额，不是单项额度。</v>
       </c>
       <c r="F72" s="16" t="str">
         <v>公告</v>
@@ -46571,16 +47394,16 @@
         <v>已截止</v>
       </c>
       <c r="B73" s="13" t="d">
-        <v>2026-04-28T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C73" s="14" t="str">
-        <v>吉林大学·工程仿生教育部重点实验室</v>
+        <v>齐鲁工业大学·山东省无人系统智能技术与装备重点实验室</v>
       </c>
       <c r="D73" s="15" t="str">
-        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
+        <v>无人系统多源感知、导航与控制</v>
       </c>
       <c r="E73" s="15" t="str">
-        <v>5万元/项；拟8项</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F73" s="16" t="str">
         <v>公告</v>
@@ -46591,16 +47414,16 @@
         <v>已截止</v>
       </c>
       <c r="B74" s="13" t="d">
-        <v>2026-04-30T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C74" s="14" t="str">
-        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
+        <v>吉林大学·工程仿生教育部重点实验室</v>
       </c>
       <c r="D74" s="15" t="str">
-        <v>智能无人系统感知、规划与控制</v>
+        <v>松软地面机械仿生行走理论与技术；生物生产及加工机械设计，不将仿生材料自动算机器人任务</v>
       </c>
       <c r="E74" s="15" t="str">
-        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
+        <v>5万元/项；拟8项</v>
       </c>
       <c r="F74" s="16" t="str">
         <v>公告</v>
@@ -46614,13 +47437,13 @@
         <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C75" s="14" t="str">
-        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
+        <v>四川文理学院·智能无人系统技术四川省高等学校重点实验室</v>
       </c>
       <c r="D75" s="15" t="str">
-        <v>警用智能机器人与协同任务</v>
+        <v>智能无人系统感知、规划与控制</v>
       </c>
       <c r="E75" s="15" t="str">
-        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
+        <v>重点2—3万元、一般1—2万元（结题后拨付）</v>
       </c>
       <c r="F75" s="16" t="str">
         <v>公告</v>
@@ -46631,16 +47454,16 @@
         <v>已截止</v>
       </c>
       <c r="B76" s="13" t="d">
-        <v>2026-05-06T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C76" s="14" t="str">
-        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
+        <v>四川文理学院·警用智能机器人达州市重点实验室</v>
       </c>
       <c r="D76" s="15" t="str">
-        <v>具身智能（仅保留正式指南第7项方向）</v>
+        <v>警用智能机器人与协同任务</v>
       </c>
       <c r="E76" s="15" t="str">
-        <v>10—15万元</v>
+        <v>重点1—2万元、一般0.5—1万元（结题后拨付）</v>
       </c>
       <c r="F76" s="16" t="str">
         <v>公告</v>
@@ -46651,16 +47474,16 @@
         <v>已截止</v>
       </c>
       <c r="B77" s="13" t="d">
-        <v>2026-05-14T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C77" s="14" t="str">
-        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
+        <v>中国科学院脑科学与智能技术卓越创新中心·脑认知与类脑智能全国重点实验室</v>
       </c>
       <c r="D77" s="15" t="str">
-        <v>具身机器人磨削、抛光及加工技能</v>
+        <v>具身智能（仅保留正式指南第7项方向）</v>
       </c>
       <c r="E77" s="15" t="str">
-        <v>一般1—2万元、重点3—5万元</v>
+        <v>10—15万元</v>
       </c>
       <c r="F77" s="16" t="str">
         <v>公告</v>
@@ -46671,16 +47494,16 @@
         <v>已截止</v>
       </c>
       <c r="B78" s="13" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-14T00:00:00.000Z</v>
       </c>
       <c r="C78" s="14" t="str">
-        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
+        <v>河南工业大学·河南省超硬磨料磨削装备重点实验室</v>
       </c>
       <c r="D78" s="15" t="str">
-        <v>前沿交叉方向中的手术机器人应用与验证</v>
+        <v>具身机器人磨削、抛光及加工技能</v>
       </c>
       <c r="E78" s="15" t="str">
-        <v>4万元</v>
+        <v>一般1—2万元、重点3—5万元</v>
       </c>
       <c r="F78" s="16" t="str">
         <v>公告</v>
@@ -46691,16 +47514,16 @@
         <v>已截止</v>
       </c>
       <c r="B79" s="13" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C79" s="14" t="str">
-        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
+        <v>山东大学齐鲁第二医院·山东省癌症数字医疗重点实验室（筹）</v>
       </c>
       <c r="D79" s="15" t="str">
-        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
+        <v>前沿交叉方向中的手术机器人应用与验证</v>
       </c>
       <c r="E79" s="15" t="str">
-        <v>不超过1万元</v>
+        <v>4万元</v>
       </c>
       <c r="F79" s="16" t="str">
         <v>公告</v>
@@ -46711,42 +47534,42 @@
         <v>已截止</v>
       </c>
       <c r="B80" s="13" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C80" s="14" t="str">
-        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
+        <v>中南民族大学·医学信息分析及肿瘤诊疗湖北省重点实验室</v>
       </c>
       <c r="D80" s="15" t="str">
-        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
+        <v>肿瘤手术导航、形变补偿、跟踪与标定</v>
       </c>
       <c r="E80" s="15" t="str">
-        <v>重点4万元、一般2万元</v>
+        <v>不超过1万元</v>
       </c>
       <c r="F80" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="81" ht="72" customHeight="1">
+    <row r="81" ht="66" customHeight="1">
       <c r="A81" s="18" t="str">
         <v>已截止</v>
       </c>
       <c r="B81" s="13" t="d">
-        <v>2026-06-30T00:00:00.000Z</v>
+        <v>2026-06-25T00:00:00.000Z</v>
       </c>
       <c r="C81" s="14" t="str">
-        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
+        <v>湖北·华中师范大学·数字教育湖北省重点实验室</v>
       </c>
       <c r="D81" s="15" t="str">
-        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
+        <v>一般项目中的机器人及其应用（区分机器人技术与单纯课程教学研究）</v>
       </c>
       <c r="E81" s="15" t="str">
-        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
+        <v>重点4万元、一般2万元</v>
       </c>
       <c r="F81" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="82" ht="66" customHeight="1">
+    <row r="82" ht="72" customHeight="1">
       <c r="A82" s="18" t="str">
         <v>已截止</v>
       </c>
@@ -46754,13 +47577,13 @@
         <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C82" s="14" t="str">
-        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
+        <v>同济大学·国家土建结构预制装配化工程技术研究中心沈祖炎专项开放基金</v>
       </c>
       <c r="D82" s="15" t="str">
-        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
+        <v>定向方向8：村镇模块化钢结构体系，以及焊接机器人适配工艺、路径和参数；同时包括建筑被动式降温任务</v>
       </c>
       <c r="E82" s="15" t="str">
-        <v>原则5万元/项；可按评审增加，上限未载</v>
+        <v>机器人相关方向为定向项目20万元；非定向每项7.5万元另列，不混填</v>
       </c>
       <c r="F82" s="16" t="str">
         <v>公告</v>
@@ -46771,16 +47594,16 @@
         <v>已截止</v>
       </c>
       <c r="B83" s="13" t="d">
-        <v>2026-07-10T00:00:00.000Z</v>
+        <v>2026-06-30T00:00:00.000Z</v>
       </c>
       <c r="C83" s="14" t="str">
-        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
+        <v>武汉软件工程职业学院／武汉开放大学·复杂零部件智能检测与识别湖北省工程研究中心</v>
       </c>
       <c r="D83" s="15" t="str">
-        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
+        <v>工业机器人五轴扫描路径规划；AMR与协作臂、三维扫描闭环联动；自适应支脚力反馈调平</v>
       </c>
       <c r="E83" s="15" t="str">
-        <v>5万元/项；专项拟2项</v>
+        <v>原则5万元/项；可按评审增加，上限未载</v>
       </c>
       <c r="F83" s="16" t="str">
         <v>公告</v>
@@ -46791,16 +47614,16 @@
         <v>已截止</v>
       </c>
       <c r="B84" s="13" t="d">
-        <v>2026-07-12T00:00:00.000Z</v>
+        <v>2026-07-10T00:00:00.000Z</v>
       </c>
       <c r="C84" s="14" t="str">
-        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
+        <v>湖南工学院·科技创新平台开放课题：汽车零部件产业链产教融合专项</v>
       </c>
       <c r="D84" s="15" t="str">
-        <v>无人机轨迹与协同、自主采样探测装备</v>
+        <v>方向6：轻型汽车电控悬架系统动力学建模与智能控制策略；其他育人管理方向不纳入</v>
       </c>
       <c r="E84" s="15" t="str">
-        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
+        <v>5万元/项；专项拟2项</v>
       </c>
       <c r="F84" s="16" t="str">
         <v>公告</v>
@@ -46811,16 +47634,16 @@
         <v>已截止</v>
       </c>
       <c r="B85" s="13" t="d">
-        <v>2026-07-19T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C85" s="14" t="str">
-        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
+        <v>吉林大学·地球信息探测仪器教育部重点实验室</v>
       </c>
       <c r="D85" s="15" t="str">
-        <v>具身智能传感、闭环感知与人机交互意图识别</v>
+        <v>无人机轨迹与协同、自主采样探测装备</v>
       </c>
       <c r="E85" s="15" t="str">
-        <v>10万元</v>
+        <v>5. 资助额度：重点课题不高于5万元，一般课题不高于3万元，青年人才培养课题不高于2万元。</v>
       </c>
       <c r="F85" s="16" t="str">
         <v>公告</v>
@@ -46831,16 +47654,16 @@
         <v>已截止</v>
       </c>
       <c r="B86" s="13" t="d">
-        <v>2026-07-25T00:00:00.000Z</v>
+        <v>2026-07-19T00:00:00.000Z</v>
       </c>
       <c r="C86" s="14" t="str">
-        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
+        <v>中国科学院上海微系统与信息技术研究所·传感器技术全国重点实验室</v>
       </c>
       <c r="D86" s="15" t="str">
-        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
+        <v>具身智能传感、闭环感知与人机交互意图识别</v>
       </c>
       <c r="E86" s="15" t="str">
-        <v>2—4万元</v>
+        <v>10万元</v>
       </c>
       <c r="F86" s="16" t="str">
         <v>公告</v>
@@ -46851,16 +47674,16 @@
         <v>已截止</v>
       </c>
       <c r="B87" s="13" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-07-25T00:00:00.000Z</v>
       </c>
       <c r="C87" s="14" t="str">
-        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
+        <v>桂林电子科技大学·广西高校智能综合自动化重点实验室</v>
       </c>
       <c r="D87" s="15" t="str">
-        <v>智能机器人信息感知、多源融合与控制</v>
+        <v>机器人视觉—力觉融合控制、医疗机器人与智能自动化</v>
       </c>
       <c r="E87" s="15" t="str">
-        <v>约2万元</v>
+        <v>2—4万元</v>
       </c>
       <c r="F87" s="16" t="str">
         <v>公告</v>
@@ -46871,16 +47694,16 @@
         <v>已截止</v>
       </c>
       <c r="B88" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C88" s="14" t="str">
-        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
+        <v>安徽师范大学·安徽省智能机器人信息融合与控制工程研究中心</v>
       </c>
       <c r="D88" s="15" t="str">
-        <v>机器人集成与医疗康复智能制造装备</v>
+        <v>智能机器人信息感知、多源融合与控制</v>
       </c>
       <c r="E88" s="15" t="str">
-        <v>一般2万元、重点3万元</v>
+        <v>约2万元</v>
       </c>
       <c r="F88" s="16" t="str">
         <v>公告</v>
@@ -46894,13 +47717,13 @@
         <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C89" s="14" t="str">
-        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
+        <v>湖北工业大学·现代制造质量工程湖北省重点实验室</v>
       </c>
       <c r="D89" s="15" t="str">
-        <v>桥梁与水下缺陷无人机器人检测</v>
+        <v>机器人集成与医疗康复智能制造装备</v>
       </c>
       <c r="E89" s="15" t="str">
-        <v>重点5万元、一般2万元</v>
+        <v>一般2万元、重点3万元</v>
       </c>
       <c r="F89" s="16" t="str">
         <v>公告</v>
@@ -46911,16 +47734,16 @@
         <v>已截止</v>
       </c>
       <c r="B90" s="13" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C90" s="14" t="str">
-        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
+        <v>辽宁省交通高等专科学校·辽宁省桥梁安全工程重点实验室</v>
       </c>
       <c r="D90" s="15" t="str">
-        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
+        <v>桥梁与水下缺陷无人机器人检测</v>
       </c>
       <c r="E90" s="15" t="str">
-        <v>5万元</v>
+        <v>重点5万元、一般2万元</v>
       </c>
       <c r="F90" s="16" t="str">
         <v>公告</v>
@@ -46931,16 +47754,16 @@
         <v>已截止</v>
       </c>
       <c r="B91" s="13" t="d">
-        <v>2026-08-30T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C91" s="14" t="str">
-        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
+        <v>上海科技大学·先进医用材料与医疗器械全国重点实验室（一般开放）</v>
       </c>
       <c r="D91" s="15" t="str">
-        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
+        <v>人机交互与共融医疗器械（限指南明确交互任务）</v>
       </c>
       <c r="E91" s="15" t="str">
-        <v>重点5万元；一般2万元；共6—8项</v>
+        <v>5万元</v>
       </c>
       <c r="F91" s="16" t="str">
         <v>公告</v>
@@ -46951,16 +47774,16 @@
         <v>已截止</v>
       </c>
       <c r="B92" s="13" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-30T00:00:00.000Z</v>
       </c>
       <c r="C92" s="14" t="str">
-        <v>四川警察学院·智能警务四川省重点实验室</v>
+        <v>江西飞行学院·低空地理信息与航路江西省教育厅重点实验室</v>
       </c>
       <c r="D92" s="15" t="str">
-        <v>无人机、车辆与机器狗异构协同及应急救援</v>
+        <v>低空航路规划；无人机AED快速投送与空地协同调度；空地协同城市航路规划</v>
       </c>
       <c r="E92" s="15" t="str">
-        <v>重点15万元、一般10万元、青年5万元</v>
+        <v>重点5万元；一般2万元；共6—8项</v>
       </c>
       <c r="F92" s="16" t="str">
         <v>公告</v>
@@ -46971,17 +47794,16 @@
         <v>已截止</v>
       </c>
       <c r="B93" s="13" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C93" s="14" t="str">
-        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
+        <v>四川警察学院·智能警务四川省重点实验室</v>
       </c>
       <c r="D93" s="15" t="str">
-        <v>特种机器人多源感知、轨迹与动力学控制</v>
+        <v>无人机、车辆与机器狗异构协同及应急救援</v>
       </c>
       <c r="E93" s="15" t="str">
-        <v>未在已取得官方资料中明确；
-待实验室确认。</v>
+        <v>重点15万元、一般10万元、青年5万元</v>
       </c>
       <c r="F93" s="16" t="str">
         <v>公告</v>
@@ -46992,16 +47814,17 @@
         <v>已截止</v>
       </c>
       <c r="B94" s="13" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C94" s="14" t="str">
-        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+        <v>兰州理工大学·成套装备智能化集成技术教育部重点实验室</v>
       </c>
       <c r="D94" s="15" t="str">
-        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+        <v>特种机器人多源感知、轨迹与动力学控制</v>
       </c>
       <c r="E94" s="15" t="str">
-        <v>不超过2万元</v>
+        <v>未在已取得官方资料中明确；
+待实验室确认。</v>
       </c>
       <c r="F94" s="16" t="str">
         <v>公告</v>
@@ -47012,40 +47835,39 @@
         <v>已截止</v>
       </c>
       <c r="B95" s="13" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="C95" s="14" t="str">
+        <v>华中科技大学·图像信息处理与智能控制教育部重点实验室</v>
+      </c>
+      <c r="D95" s="15" t="str">
+        <v>具身智能与图像信息处理、智能控制交叉任务</v>
+      </c>
+      <c r="E95" s="15" t="str">
+        <v>不超过2万元</v>
+      </c>
+      <c r="F95" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="96" ht="66" customHeight="1">
+      <c r="A96" s="18" t="str">
+        <v>已截止</v>
+      </c>
+      <c r="B96" s="13" t="d">
         <v>2026-09-27T00:00:00.000Z</v>
       </c>
-      <c r="C95" s="14" t="str">
+      <c r="C96" s="14" t="str">
         <v>云南大学·云南省智能系统与计算重点实验室</v>
       </c>
-      <c r="D95" s="15" t="str">
+      <c r="D96" s="15" t="str">
         <v>低空无人系统集群协同（仅保留具体无人装备方向）</v>
       </c>
-      <c r="E95" s="15" t="str">
+      <c r="E96" s="15" t="str">
         <v>重点≤8万元；
 一般≤2万元；
 定向1万元。</v>
       </c>
-      <c r="F95" s="16" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="96" ht="66" customHeight="1">
-      <c r="A96" s="18" t="str">
-        <v>已截止</v>
-      </c>
-      <c r="B96" s="13" t="d">
-        <v>2026-10-05T00:00:00.000Z</v>
-      </c>
-      <c r="C96" s="14" t="str">
-        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
-      </c>
-      <c r="D96" s="15" t="str">
-        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
-      </c>
-      <c r="E96" s="15" t="str">
-        <v>重点60—100万元；
-一般15—20万元</v>
-      </c>
       <c r="F96" s="16" t="str">
         <v>公告</v>
       </c>
@@ -47055,16 +47877,17 @@
         <v>已截止</v>
       </c>
       <c r="B97" s="13" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-05T00:00:00.000Z</v>
       </c>
       <c r="C97" s="14" t="str">
-        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
+        <v>安徽理工大学·煤炭无人化开采数智技术全国重点实验室</v>
       </c>
       <c r="D97" s="15" t="str">
-        <v>机器人遥操作、双臂操作与人机协同</v>
+        <v>煤矿无人装备及机器人作业、定位和自适应控制</v>
       </c>
       <c r="E97" s="15" t="str">
-        <v>公告未公布统一金额，评审确定。</v>
+        <v>重点60—100万元；
+一般15—20万元</v>
       </c>
       <c r="F97" s="16" t="str">
         <v>公告</v>
@@ -47078,13 +47901,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C98" s="14" t="str">
-        <v>中北大学·微纳器件与系统教育部重点实验室</v>
+        <v>上海科技大学·智能感知与人机协同教育部重点实验室</v>
       </c>
       <c r="D98" s="15" t="str">
-        <v>微型机器人及微纳执行器、精密定位</v>
+        <v>机器人遥操作、双臂操作与人机协同</v>
       </c>
       <c r="E98" s="15" t="str">
-        <v>2—4万元</v>
+        <v>公告未公布统一金额，评审确定。</v>
       </c>
       <c r="F98" s="16" t="str">
         <v>公告</v>
@@ -47098,13 +47921,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C99" s="14" t="str">
-        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
+        <v>中北大学·微纳器件与系统教育部重点实验室</v>
       </c>
       <c r="D99" s="15" t="str">
-        <v>机器人机械臂抓取、路径规划与自主导航</v>
+        <v>微型机器人及微纳执行器、精密定位</v>
       </c>
       <c r="E99" s="15" t="str">
-        <v>一般2万元；重点4万元（以评审为准）</v>
+        <v>2—4万元</v>
       </c>
       <c r="F99" s="16" t="str">
         <v>公告</v>
@@ -47118,13 +47941,13 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C100" s="14" t="str">
-        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
+        <v>中北大学·机器视觉与虚拟现实山西省重点实验室</v>
       </c>
       <c r="D100" s="15" t="str">
-        <v>无人平台智能探测与多源感知</v>
+        <v>机器人机械臂抓取、路径规划与自主导航</v>
       </c>
       <c r="E100" s="15" t="str">
-        <v>2—4万元/项，拟5—8项</v>
+        <v>一般2万元；重点4万元（以评审为准）</v>
       </c>
       <c r="F100" s="16" t="str">
         <v>公告</v>
@@ -47138,36 +47961,36 @@
         <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C101" s="14" t="str">
-        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+        <v>中北大学·智能探测技术与装备山西省重点实验室</v>
       </c>
       <c r="D101" s="15" t="str">
-        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+        <v>无人平台智能探测与多源感知</v>
       </c>
       <c r="E101" s="15" t="str">
-        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+        <v>2—4万元/项，拟5—8项</v>
       </c>
       <c r="F101" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
-    <row r="102" ht="96" customHeight="1">
-      <c r="A102" t="str" s="18">
+    <row r="102" ht="66" customHeight="1">
+      <c r="A102" s="18" t="str">
         <v>已截止</v>
       </c>
-      <c r="B102" t="n" s="13">
-        <v>46295</v>
-      </c>
-      <c r="C102" t="str" s="14">
-        <v>上海交通大学·海洋工程全国重点实验室</v>
-      </c>
-      <c r="D102" t="str" s="15">
-        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
-      </c>
-      <c r="E102" t="str" s="15">
-        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
-      </c>
-      <c r="F102" t="str" s="16">
-        <v>官方公告</v>
+      <c r="B102" s="13" t="d">
+        <v>2026-10-08T00:00:00.000Z</v>
+      </c>
+      <c r="C102" s="14" t="str">
+        <v>中铁大桥勘测设计院集团有限公司、中铁大桥局集团有限公司、西南交通大学（共同依托）·桥梁智能与绿色建造全国重点实验室</v>
+      </c>
+      <c r="D102" s="15" t="str">
+        <v>爬壁机器人负压吸附、曲面作业与控制</v>
+      </c>
+      <c r="E102" s="15" t="str">
+        <v>资助类型A/B/C分别20/15/10万元（与科研匹配等级无关）</v>
+      </c>
+      <c r="F102" s="16" t="str">
+        <v>公告</v>
       </c>
     </row>
     <row r="103" ht="96" customHeight="1">
@@ -47175,16 +47998,16 @@
         <v>已截止</v>
       </c>
       <c r="B103" t="n" s="13">
-        <v>45503</v>
+        <v>46295</v>
       </c>
       <c r="C103" t="str" s="14">
-        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
+        <v>上海交通大学·海洋工程全国重点实验室</v>
       </c>
       <c r="D103" t="str" s="15">
-        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
+        <v>方向3：海洋智能无人装备总体及系统；海洋环境感知与目标识别；无人系统自主推理、决策与控制。</v>
       </c>
       <c r="E103" t="str" s="15">
-        <v>3万元/项；计划10项。</v>
+        <v>重点15—20万元/项；自由探索5—10万元/项。</v>
       </c>
       <c r="F103" t="str" s="16">
         <v>官方公告</v>
@@ -47195,16 +48018,16 @@
         <v>已截止</v>
       </c>
       <c r="B104" t="n" s="13">
-        <v>46006</v>
+        <v>45503</v>
       </c>
       <c r="C104" t="str" s="14">
-        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
+        <v>东北农业大学·智慧农场技术与系统全国重点实验室</v>
       </c>
       <c r="D104" t="str" s="15">
-        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
+        <v>方向5：智慧农机智能装备研发；其余农业生物方向不作为机器人任务。</v>
       </c>
       <c r="E104" t="str" s="15">
-        <v>正文未公开具体资助金额。</v>
+        <v>3万元/项；计划10项。</v>
       </c>
       <c r="F104" t="str" s="16">
         <v>官方公告</v>
@@ -47215,16 +48038,16 @@
         <v>已截止</v>
       </c>
       <c r="B105" t="n" s="13">
-        <v>46193</v>
+        <v>46006</v>
       </c>
       <c r="C105" t="str" s="14">
-        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
+        <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
       <c r="D105" t="str" s="15">
-        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
+        <v>机器人曲面加工及多模态感知；多机器人协同加工与运动振动控制；人形机器人动力学、自然交互、感知、灵巧抓取和控制；多机协同管控。</v>
       </c>
       <c r="E105" t="str" s="15">
-        <v>一般项目≤5万元/项；计划12项。</v>
+        <v>正文未公开具体资助金额。</v>
       </c>
       <c r="F105" t="str" s="16">
         <v>官方公告</v>
@@ -47235,16 +48058,16 @@
         <v>已截止</v>
       </c>
       <c r="B106" t="n" s="13">
-        <v>44434</v>
+        <v>46193</v>
       </c>
       <c r="C106" t="str" s="14">
-        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
+        <v>贵州大学·贵州省粮油作物优质高效增产全省重点实验室（一般项目）</v>
       </c>
       <c r="D106" t="str" s="15">
-        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
+        <v>方向3：稻油轮作全程机械化、粮油智慧农作、山地小型农机创制与应用；不将育种及基因方向纳入机器人任务。</v>
       </c>
       <c r="E106" t="str" s="15">
-        <v>重点2万元/项；一般1万元/项。</v>
+        <v>一般项目≤5万元/项；计划12项。</v>
       </c>
       <c r="F106" t="str" s="16">
         <v>官方公告</v>
@@ -47255,96 +48078,96 @@
         <v>已截止</v>
       </c>
       <c r="B107" t="n" s="13">
-        <v>45163</v>
+        <v>44434</v>
       </c>
       <c r="C107" t="str" s="14">
-        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
+        <v>天津工业大学·天津市电气装备智能控制重点实验室</v>
       </c>
       <c r="D107" t="str" s="15">
-        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
+        <v>年度方向电机系统及智能控制、视觉感知与智能识别；背景明确三维视觉、机器人自主控制及无人机控制。半导体器件可靠性不作为机器人任务。</v>
       </c>
       <c r="E107" t="str" s="15">
-        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
+        <v>重点2万元/项；一般1万元/项。</v>
       </c>
       <c r="F107" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="108" ht="102" customHeight="1">
+    <row r="108" ht="96" customHeight="1">
       <c r="A108" t="str" s="18">
         <v>已截止</v>
       </c>
       <c r="B108" t="n" s="13">
-        <v>45991</v>
+        <v>45163</v>
       </c>
       <c r="C108" t="str" s="14">
-        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
+        <v>辽宁工程技术大学·矿山液压技术与装备国家地方联合工程研究中心</v>
       </c>
       <c r="D108" t="str" s="15">
-        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
+        <v>明确方向2机器人化智能开采装备与工艺；4工矿装备自动化智能化；6矿山流体动力与数智液控；7应急抢险装备。</v>
       </c>
       <c r="E108" t="str" s="15">
-        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
+        <v>重点平均3万元/项；一般平均2万元/项（保留平均口径）。</v>
       </c>
       <c r="F108" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="109" ht="117" customHeight="1">
+    <row r="109" ht="102" customHeight="1">
       <c r="A109" t="str" s="18">
         <v>已截止</v>
       </c>
       <c r="B109" t="n" s="13">
-        <v>42175</v>
+        <v>45991</v>
       </c>
       <c r="C109" t="str" s="14">
-        <v>桂林航天工业学院·广西高校无人机遥测重点实验室开放课题（主任基金仅内部，未纳入）</v>
+        <v>长春理工大学·跨尺度微纳制造教育部重点实验室</v>
       </c>
       <c r="D109" t="str" s="15">
-        <v>实际14项无人机任务：飞控模型、航迹规划、姿态控制、影像匹配、多用途系统/载荷设计、数传图传二次开发、行业应用、多机多任务协作、目标识别跟踪、特殊用途无人机、遥感系统、北斗飞控及无人机热点。</v>
+        <v>方向3明确机器人微纳操纵、微纳装配、二维/三维机器人微纳测量技术与系统；方向4有微纳制造过程智能感知、多参数信息融合质量控制及三维非接触在位检测；材料/细胞任务不据此扩充。</v>
       </c>
       <c r="E109" t="str" s="15">
-        <v>校外开放1—5万元/项拟2—3项；结题按实际成果折算增减资助，不承诺固定到账。主任基金3—6/3—4万元面向固定人员，不计本人对外资助金额。</v>
+        <v>重点8—10万元/项，2项；一般3—5万元/项，5—6项。</v>
       </c>
       <c r="F109" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="110" ht="132" customHeight="1">
+    <row r="110" ht="117" customHeight="1">
       <c r="A110" t="str" s="18">
         <v>已截止</v>
       </c>
       <c r="B110" t="n" s="13">
-        <v>45442</v>
+        <v>42175</v>
       </c>
       <c r="C110" t="str" s="14">
-        <v>桂林航天工业学院·广西特种工程装备与控制重点实验室</v>
+        <v>桂林航天工业学院·广西高校无人机遥测重点实验室开放课题（主任基金仅内部，未纳入）</v>
       </c>
       <c r="D110" t="str" s="15">
-        <v>2024方向二明确特种工程机器人：矿山/隧道/电力线路/抢险救灾/危险环境，姿态和受力检测、运动反馈控制、环境认知定位；非结构环境移动平台行走路径与机械臂关节实时协同规划。方向一含机构动力建模、工作状态辨识控制；材料方向并非凭实验室名称收录。</v>
+        <v>实际14项无人机任务：飞控模型、航迹规划、姿态控制、影像匹配、多用途系统/载荷设计、数传图传二次开发、行业应用、多机多任务协作、目标识别跟踪、特殊用途无人机、遥感系统、北斗飞控及无人机热点。</v>
       </c>
       <c r="E110" t="str" s="15">
-        <v>3—6万元/项；计划8—10项，各方向2—3项。</v>
+        <v>校外开放1—5万元/项拟2—3项；结题按实际成果折算增减资助，不承诺固定到账。主任基金3—6/3—4万元面向固定人员，不计本人对外资助金额。</v>
       </c>
       <c r="F110" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="111" ht="102" customHeight="1">
+    <row r="111" ht="132" customHeight="1">
       <c r="A111" t="str" s="18">
         <v>已截止</v>
       </c>
       <c r="B111" t="n" s="13">
-        <v>45986</v>
+        <v>45442</v>
       </c>
       <c r="C111" t="str" s="14">
-        <v>滁州学院·安徽省智能感知与健康养老工程研究中心</v>
+        <v>桂林航天工业学院·广西特种工程装备与控制重点实验室</v>
       </c>
       <c r="D111" t="str" s="15">
-        <v>养老移动平台空间环境建模与主动安全感知；多模态行为理解/自然交互；动态非结构场景机器人自适应认知、行为预测、自主导航决策任务规划；健康能力评估、仿生可解释计算。</v>
+        <v>2024方向二明确特种工程机器人：矿山/隧道/电力线路/抢险救灾/危险环境，姿态和受力检测、运动反馈控制、环境认知定位；非结构环境移动平台行走路径与机械臂关节实时协同规划。方向一含机构动力建模、工作状态辨识控制；材料方向并非凭实验室名称收录。</v>
       </c>
       <c r="E111" t="str" s="15">
-        <v>重点3万元拟1项；一般2万元拟5项。</v>
+        <v>3—6万元/项；计划8—10项，各方向2—3项。</v>
       </c>
       <c r="F111" t="str" s="16">
         <v>官方公告</v>
@@ -47355,16 +48178,16 @@
         <v>已截止</v>
       </c>
       <c r="B112" t="n" s="13">
-        <v>44692</v>
+        <v>45986</v>
       </c>
       <c r="C112" t="str" s="14">
-        <v>安徽大学·高节能电机及控制技术国家地方联合工程实验室</v>
+        <v>滁州学院·安徽省智能感知与健康养老工程研究中心</v>
       </c>
       <c r="D112" t="str" s="15">
-        <v>明确特种机器人电力巡检/消防/反恐排爆：自动导航、无线图像视频传输、避障、充电、灭火；球形关节带载闭环控制算法及硬件实现。输电、电机耦合等其他任务不因同公告全列相关。</v>
+        <v>养老移动平台空间环境建模与主动安全感知；多模态行为理解/自然交互；动态非结构场景机器人自适应认知、行为预测、自主导航决策任务规划；健康能力评估、仿生可解释计算。</v>
       </c>
       <c r="E112" t="str" s="15">
-        <v>一般2—3万元/项，按研究内容及预期成果决定。</v>
+        <v>重点3万元拟1项；一般2万元拟5项。</v>
       </c>
       <c r="F112" t="str" s="16">
         <v>官方公告</v>
@@ -47375,38 +48198,58 @@
         <v>已截止</v>
       </c>
       <c r="B113" t="n" s="13">
-        <v>45986</v>
+        <v>44692</v>
       </c>
       <c r="C113" t="str" s="14">
-        <v>滁州学院·无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室</v>
+        <v>安徽大学·高节能电机及控制技术国家地方联合工程实验室</v>
       </c>
       <c r="D113" t="str" s="15">
-        <v>无人应急装备复杂环境视觉感知、目标识别、状态诊断；视觉任务定位跟踪与运动/执行系统协同作业控制；视觉红外传感行为多模态灾害识别预警。明确无人装备自主执行任务。</v>
+        <v>明确特种机器人电力巡检/消防/反恐排爆：自动导航、无线图像视频传输、避障、充电、灭火；球形关节带载闭环控制算法及硬件实现。输电、电机耦合等其他任务不因同公告全列相关。</v>
       </c>
       <c r="E113" t="str" s="15">
-        <v>一般2万元/项，拟3项；正文成果提重点3篇但本批不设重点资助。</v>
+        <v>一般2—3万元/项，按研究内容及预期成果决定。</v>
       </c>
       <c r="F113" t="str" s="16">
         <v>官方公告</v>
       </c>
     </row>
-    <row r="114" ht="96" customHeight="1">
+    <row r="114" ht="102" customHeight="1">
       <c r="A114" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B114" t="n" s="13">
+        <v>45986</v>
+      </c>
+      <c r="C114" t="str" s="14">
+        <v>滁州学院·无人应急装备与灾害过程数字化重建安徽省联合共建学科重点实验室</v>
+      </c>
+      <c r="D114" t="str" s="15">
+        <v>无人应急装备复杂环境视觉感知、目标识别、状态诊断；视觉任务定位跟踪与运动/执行系统协同作业控制；视觉红外传感行为多模态灾害识别预警。明确无人装备自主执行任务。</v>
+      </c>
+      <c r="E114" t="str" s="15">
+        <v>一般2万元/项，拟3项；正文成果提重点3篇但本批不设重点资助。</v>
+      </c>
+      <c r="F114" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="115" ht="96" customHeight="1">
+      <c r="A115" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B114" t="n" s="13">
+      <c r="B115" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C114" t="str" s="14">
+      <c r="C115" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D114" t="str" s="15">
+      <c r="D115" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E114" t="str" s="15">
+      <c r="E115" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F114" t="str" s="16">
+      <c r="F115" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -47422,8 +48265,8 @@
     <hyperlink ref="F5" ns1:id="Rff2d595907084ed9"/>
     <hyperlink ref="C6" location="'02项目完整详情'!A61"/>
     <hyperlink ref="F6" ns1:id="R840dfc7ac2ef4322"/>
-    <hyperlink ref="C41" location="'02项目完整详情'!A113"/>
-    <hyperlink ref="F41" ns1:id="Re902984ea1114a1f"/>
+    <hyperlink ref="C42" location="'02项目完整详情'!A113"/>
+    <hyperlink ref="F42" ns1:id="Re902984ea1114a1f"/>
     <hyperlink ref="C7" location="'02项目完整详情'!A62"/>
     <hyperlink ref="F7" ns1:id="Ra6ff56d69fd14f0d"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A63"/>
@@ -47440,8 +48283,8 @@
     <hyperlink ref="F16" ns1:id="R5d6c0e16ca9148f1"/>
     <hyperlink ref="C17" location="'02项目完整详情'!A141"/>
     <hyperlink ref="F17" ns1:id="R29345038c30a4733"/>
-    <hyperlink ref="C42" location="'02项目完整详情'!A85"/>
-    <hyperlink ref="F42" ns1:id="R486c032b769d4524"/>
+    <hyperlink ref="C43" location="'02项目完整详情'!A85"/>
+    <hyperlink ref="F43" ns1:id="R486c032b769d4524"/>
     <hyperlink ref="C18" location="'02项目完整详情'!A99"/>
     <hyperlink ref="F18" ns1:id="R19ee0f6cf8d14ed3"/>
     <hyperlink ref="C19" location="'02项目完整详情'!A143"/>
@@ -47452,192 +48295,194 @@
     <hyperlink ref="F21" ns1:id="Ra979348b05084966"/>
     <hyperlink ref="C24" location="'02项目完整详情'!A66"/>
     <hyperlink ref="F24" ns1:id="R4dc201fc29cb4ab4"/>
-    <hyperlink ref="C43" location="'02项目完整详情'!A139"/>
-    <hyperlink ref="F43" ns1:id="Rf4dc98016cfb49fd"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A139"/>
+    <hyperlink ref="F44" ns1:id="Rf4dc98016cfb49fd"/>
     <hyperlink ref="C25" location="'02项目完整详情'!A151"/>
     <hyperlink ref="F25" ns1:id="R3d89872d06fd4b60"/>
     <hyperlink ref="C26" location="'02项目完整详情'!A67"/>
     <hyperlink ref="F26" ns1:id="R1e9b7d2bc63d4258"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A68"/>
-    <hyperlink ref="F44" ns1:id="R5d0261ffe45c4155"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A68"/>
+    <hyperlink ref="F45" ns1:id="R5d0261ffe45c4155"/>
     <hyperlink ref="C27" location="'02项目完整详情'!A69"/>
     <hyperlink ref="F27" ns1:id="Reeb11b878b934f2d"/>
     <hyperlink ref="C28" location="'02项目完整详情'!A70"/>
     <hyperlink ref="F28" ns1:id="R5b06defce5864a96"/>
     <hyperlink ref="C29" location="'02项目完整详情'!A71"/>
     <hyperlink ref="F29" ns1:id="Ra48afdb9842a4366"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A72"/>
-    <hyperlink ref="F45" ns1:id="Rb3b4681efcdd44d4"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A73"/>
-    <hyperlink ref="F46" ns1:id="R4f0b800598574b86"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A74"/>
-    <hyperlink ref="F47" ns1:id="R56697ca79cd54a14"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A72"/>
+    <hyperlink ref="F46" ns1:id="Rb3b4681efcdd44d4"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A73"/>
+    <hyperlink ref="F47" ns1:id="R4f0b800598574b86"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A74"/>
+    <hyperlink ref="F48" ns1:id="R56697ca79cd54a14"/>
     <hyperlink ref="C35" location="'02项目完整详情'!A75"/>
     <hyperlink ref="F35" ns1:id="R0814a7680dde4f9a"/>
-    <hyperlink ref="C36" location="'02项目完整详情'!A76"/>
-    <hyperlink ref="F36" ns1:id="R3f222e6bf9fa46ec"/>
-    <hyperlink ref="C37" location="'02项目完整详情'!A77"/>
-    <hyperlink ref="F37" ns1:id="Rc66c2cf37bbc404d"/>
-    <hyperlink ref="C38" location="'02项目完整详情'!A78"/>
-    <hyperlink ref="F38" ns1:id="R90e03710dfe04e74"/>
-    <hyperlink ref="C39" location="'02项目完整详情'!A79"/>
-    <hyperlink ref="F39" ns1:id="R80f5129c1ee24096"/>
-    <hyperlink ref="C40" location="'02项目完整详情'!A80"/>
-    <hyperlink ref="F40" ns1:id="R6360db00742b45ec"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A81"/>
-    <hyperlink ref="F48" ns1:id="Rc4146f6376594d01"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A156"/>
-    <hyperlink ref="F49" ns1:id="R97ba6e4965084c76"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A155"/>
-    <hyperlink ref="F50" ns1:id="Rcbdc080795344925"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A83"/>
-    <hyperlink ref="F51" ns1:id="R9e6afd1b359743bb"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A154"/>
-    <hyperlink ref="F52" ns1:id="Rb320e0a5ad524836"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A86"/>
-    <hyperlink ref="F53" ns1:id="R42a660aaeb1d4c95"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A87"/>
-    <hyperlink ref="F54" ns1:id="R88784a2520864683"/>
+    <hyperlink ref="C37" location="'02项目完整详情'!A76"/>
+    <hyperlink ref="F37" ns1:id="R3f222e6bf9fa46ec"/>
+    <hyperlink ref="C38" location="'02项目完整详情'!A77"/>
+    <hyperlink ref="F38" ns1:id="Rc66c2cf37bbc404d"/>
+    <hyperlink ref="C39" location="'02项目完整详情'!A78"/>
+    <hyperlink ref="F39" ns1:id="R90e03710dfe04e74"/>
+    <hyperlink ref="C40" location="'02项目完整详情'!A79"/>
+    <hyperlink ref="F40" ns1:id="R80f5129c1ee24096"/>
+    <hyperlink ref="C41" location="'02项目完整详情'!A80"/>
+    <hyperlink ref="F41" ns1:id="R6360db00742b45ec"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A81"/>
+    <hyperlink ref="F49" ns1:id="Rc4146f6376594d01"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A156"/>
+    <hyperlink ref="F50" ns1:id="R97ba6e4965084c76"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A155"/>
+    <hyperlink ref="F51" ns1:id="Rcbdc080795344925"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A83"/>
+    <hyperlink ref="F52" ns1:id="R9e6afd1b359743bb"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A154"/>
+    <hyperlink ref="F53" ns1:id="Rb320e0a5ad524836"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A86"/>
+    <hyperlink ref="F54" ns1:id="R42a660aaeb1d4c95"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A87"/>
+    <hyperlink ref="F55" ns1:id="R88784a2520864683"/>
     <hyperlink ref="C30" location="'02项目完整详情'!A88"/>
     <hyperlink ref="F30" ns1:id="Rcb8b33dae69a4731"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A89"/>
-    <hyperlink ref="F55" ns1:id="Rd5ea9c8442ca46ac"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A90"/>
-    <hyperlink ref="F56" ns1:id="R7734727212364cb2"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A91"/>
-    <hyperlink ref="F57" ns1:id="R78b8c8c0ca954ecb"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A92"/>
-    <hyperlink ref="F58" ns1:id="Rfdf5f46608d44776"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A93"/>
-    <hyperlink ref="F59" ns1:id="R82f06426c3d54976"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A94"/>
-    <hyperlink ref="F60" ns1:id="R3cae8e186c48414b"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A95"/>
-    <hyperlink ref="F61" ns1:id="Ra7f1aef2362a4a4a"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A96"/>
-    <hyperlink ref="F62" ns1:id="R8befa90ef3fc47c2"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A97"/>
-    <hyperlink ref="F63" ns1:id="Re7fdcbfdd1084572"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A98"/>
-    <hyperlink ref="F64" ns1:id="R65ca925ee60b42a7"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A100"/>
-    <hyperlink ref="F65" ns1:id="Reb76655df7374bc5"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A166"/>
-    <hyperlink ref="F66" ns1:id="R055caeb6a90642b5"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A102"/>
-    <hyperlink ref="F67" ns1:id="Rfff5ca38a0554ba3"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A103"/>
-    <hyperlink ref="F68" ns1:id="R0888add655cd4fba"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A89"/>
+    <hyperlink ref="F56" ns1:id="Rd5ea9c8442ca46ac"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A90"/>
+    <hyperlink ref="F57" ns1:id="R7734727212364cb2"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A91"/>
+    <hyperlink ref="F58" ns1:id="R78b8c8c0ca954ecb"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A92"/>
+    <hyperlink ref="F59" ns1:id="Rfdf5f46608d44776"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A93"/>
+    <hyperlink ref="F60" ns1:id="R82f06426c3d54976"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A94"/>
+    <hyperlink ref="F61" ns1:id="R3cae8e186c48414b"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A95"/>
+    <hyperlink ref="F62" ns1:id="Ra7f1aef2362a4a4a"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A96"/>
+    <hyperlink ref="F63" ns1:id="R8befa90ef3fc47c2"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A97"/>
+    <hyperlink ref="F64" ns1:id="Re7fdcbfdd1084572"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A98"/>
+    <hyperlink ref="F65" ns1:id="R65ca925ee60b42a7"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A100"/>
+    <hyperlink ref="F66" ns1:id="Reb76655df7374bc5"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A166"/>
+    <hyperlink ref="F67" ns1:id="R055caeb6a90642b5"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A102"/>
+    <hyperlink ref="F68" ns1:id="Rfff5ca38a0554ba3"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A103"/>
+    <hyperlink ref="F69" ns1:id="R0888add655cd4fba"/>
     <hyperlink ref="C34" location="'02项目完整详情'!A104"/>
     <hyperlink ref="F34" ns1:id="Rd9709f11bc9f4e83"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A163"/>
-    <hyperlink ref="F69" ns1:id="R20412a2edb1c448a"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A105"/>
-    <hyperlink ref="F70" ns1:id="R61772b79401a4268"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A106"/>
-    <hyperlink ref="F71" ns1:id="R987b8e6f52a74110"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A107"/>
-    <hyperlink ref="F72" ns1:id="R0c4396d550f2475f"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A162"/>
-    <hyperlink ref="F73" ns1:id="R4f11bd52ab71481c"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A108"/>
-    <hyperlink ref="F74" ns1:id="R4db82e37256244c2"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A109"/>
-    <hyperlink ref="F75" ns1:id="R4031c47a301e406d"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A110"/>
-    <hyperlink ref="F76" ns1:id="Raa160d321af04db8"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A163"/>
+    <hyperlink ref="F70" ns1:id="R20412a2edb1c448a"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A105"/>
+    <hyperlink ref="F71" ns1:id="R61772b79401a4268"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A106"/>
+    <hyperlink ref="F72" ns1:id="R987b8e6f52a74110"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A107"/>
+    <hyperlink ref="F73" ns1:id="R0c4396d550f2475f"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A162"/>
+    <hyperlink ref="F74" ns1:id="R4f11bd52ab71481c"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A108"/>
+    <hyperlink ref="F75" ns1:id="R4db82e37256244c2"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A109"/>
+    <hyperlink ref="F76" ns1:id="R4031c47a301e406d"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A110"/>
+    <hyperlink ref="F77" ns1:id="Raa160d321af04db8"/>
     <hyperlink ref="C31" location="'02项目完整详情'!A111"/>
     <hyperlink ref="F31" ns1:id="R769c1e9ff31b4410"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A112"/>
-    <hyperlink ref="F77" ns1:id="R4cdea66d1ef84e88"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A114"/>
-    <hyperlink ref="F78" ns1:id="Rfe9d4bacb83a4b3a"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A115"/>
-    <hyperlink ref="F79" ns1:id="Rdb52bb1fc14c4902"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A116"/>
-    <hyperlink ref="F80" ns1:id="Raea0cb8061aa4114"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A153"/>
-    <hyperlink ref="F81" ns1:id="Re209c4141aad4cc2"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A152"/>
-    <hyperlink ref="F82" ns1:id="R929ae2605c414e9f"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A165"/>
-    <hyperlink ref="F83" ns1:id="R1abe4cdaf9e34bae"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A117"/>
-    <hyperlink ref="F84" ns1:id="R0a10fce99c274f93"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A118"/>
-    <hyperlink ref="F85" ns1:id="R938383f864354c81"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A119"/>
-    <hyperlink ref="F86" ns1:id="Rf5654ce2b68c4be9"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A121"/>
-    <hyperlink ref="F87" ns1:id="Rcb7b406cd4eb4fbf"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A123"/>
-    <hyperlink ref="F88" ns1:id="R5815a7bd80814259"/>
-    <hyperlink ref="C89" location="'02项目完整详情'!A124"/>
-    <hyperlink ref="F89" ns1:id="R0c410df45d8a4e3d"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A112"/>
+    <hyperlink ref="F78" ns1:id="R4cdea66d1ef84e88"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A114"/>
+    <hyperlink ref="F79" ns1:id="Rfe9d4bacb83a4b3a"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A115"/>
+    <hyperlink ref="F80" ns1:id="Rdb52bb1fc14c4902"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A116"/>
+    <hyperlink ref="F81" ns1:id="Raea0cb8061aa4114"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A153"/>
+    <hyperlink ref="F82" ns1:id="Re209c4141aad4cc2"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A152"/>
+    <hyperlink ref="F83" ns1:id="R929ae2605c414e9f"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A165"/>
+    <hyperlink ref="F84" ns1:id="R1abe4cdaf9e34bae"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A117"/>
+    <hyperlink ref="F85" ns1:id="R0a10fce99c274f93"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A118"/>
+    <hyperlink ref="F86" ns1:id="R938383f864354c81"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A119"/>
+    <hyperlink ref="F87" ns1:id="Rf5654ce2b68c4be9"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A121"/>
+    <hyperlink ref="F88" ns1:id="Rcb7b406cd4eb4fbf"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A123"/>
+    <hyperlink ref="F89" ns1:id="R5815a7bd80814259"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A124"/>
+    <hyperlink ref="F90" ns1:id="R0c410df45d8a4e3d"/>
     <hyperlink ref="C32" location="'02项目完整详情'!A125"/>
     <hyperlink ref="F32" ns1:id="R431b21fd445f4abe"/>
-    <hyperlink ref="C90" location="'02项目完整详情'!A126"/>
-    <hyperlink ref="F90" ns1:id="R567091a279bf498d"/>
-    <hyperlink ref="C91" location="'02项目完整详情'!A164"/>
-    <hyperlink ref="F91" ns1:id="Re392bfd9b5274c72"/>
-    <hyperlink ref="C92" location="'02项目完整详情'!A128"/>
-    <hyperlink ref="F92" ns1:id="Re6cada6d8cc14329"/>
-    <hyperlink ref="C93" location="'02项目完整详情'!A129"/>
-    <hyperlink ref="F93" ns1:id="R8fc1cda8f3b6430e"/>
-    <hyperlink ref="C94" location="'02项目完整详情'!A130"/>
-    <hyperlink ref="F94" ns1:id="R27a55a96c3f24c5f"/>
-    <hyperlink ref="C95" location="'02项目完整详情'!A131"/>
-    <hyperlink ref="F95" ns1:id="R5e47895d5a614c2b"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A126"/>
+    <hyperlink ref="F91" ns1:id="R567091a279bf498d"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A164"/>
+    <hyperlink ref="F92" ns1:id="Re392bfd9b5274c72"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A128"/>
+    <hyperlink ref="F93" ns1:id="Re6cada6d8cc14329"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A129"/>
+    <hyperlink ref="F94" ns1:id="R8fc1cda8f3b6430e"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A130"/>
+    <hyperlink ref="F95" ns1:id="R27a55a96c3f24c5f"/>
+    <hyperlink ref="C96" location="'02项目完整详情'!A131"/>
+    <hyperlink ref="F96" ns1:id="R5e47895d5a614c2b"/>
     <hyperlink ref="C33" location="'02项目完整详情'!A132"/>
     <hyperlink ref="F33" ns1:id="R3b43825c6bac4d00"/>
-    <hyperlink ref="C96" location="'02项目完整详情'!A133"/>
-    <hyperlink ref="F96" ns1:id="R93e0d1bfa9de4923"/>
-    <hyperlink ref="C97" location="'02项目完整详情'!A40"/>
-    <hyperlink ref="F97" ns1:id="R8485fac45d264a2f"/>
-    <hyperlink ref="C98" location="'02项目完整详情'!A41"/>
-    <hyperlink ref="F98" ns1:id="R1c0f567749234b9c"/>
-    <hyperlink ref="C99" location="'02项目完整详情'!A42"/>
-    <hyperlink ref="F99" ns1:id="Rbf215fc93e064e7e"/>
-    <hyperlink ref="C100" location="'02项目完整详情'!A43"/>
-    <hyperlink ref="F100" ns1:id="R53db146b46f44f15"/>
-    <hyperlink ref="C101" location="'02项目完整详情'!A44"/>
-    <hyperlink ref="F101" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F114" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C114" location="'02项目完整详情'!A148"/>
-    <hyperlink ref="C102" location="'02项目完整详情'!A167" display="项目完整详情"/>
-    <hyperlink ref="F102" ns1:id="rIdSystematic98"/>
-    <hyperlink ref="C103" location="'02项目完整详情'!A168" display="项目完整详情"/>
-    <hyperlink ref="F103" ns1:id="rIdSystematic99"/>
-    <hyperlink ref="C104" location="'02项目完整详情'!A175" display="项目完整详情"/>
-    <hyperlink ref="F104" ns1:id="rIdSystematic100"/>
-    <hyperlink ref="C105" location="'02项目完整详情'!A176" display="项目完整详情"/>
-    <hyperlink ref="F105" ns1:id="rIdSystematic101"/>
+    <hyperlink ref="C97" location="'02项目完整详情'!A133"/>
+    <hyperlink ref="F97" ns1:id="R93e0d1bfa9de4923"/>
+    <hyperlink ref="C98" location="'02项目完整详情'!A40"/>
+    <hyperlink ref="F98" ns1:id="R8485fac45d264a2f"/>
+    <hyperlink ref="C99" location="'02项目完整详情'!A41"/>
+    <hyperlink ref="F99" ns1:id="R1c0f567749234b9c"/>
+    <hyperlink ref="C100" location="'02项目完整详情'!A42"/>
+    <hyperlink ref="F100" ns1:id="Rbf215fc93e064e7e"/>
+    <hyperlink ref="C101" location="'02项目完整详情'!A43"/>
+    <hyperlink ref="F101" ns1:id="R53db146b46f44f15"/>
+    <hyperlink ref="C102" location="'02项目完整详情'!A44"/>
+    <hyperlink ref="F102" ns1:id="R188b27dcb5574282"/>
+    <hyperlink ref="F115" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C115" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="C103" location="'02项目完整详情'!A167" display="项目完整详情"/>
+    <hyperlink ref="F103" ns1:id="rIdSystematic98"/>
+    <hyperlink ref="C104" location="'02项目完整详情'!A168" display="项目完整详情"/>
+    <hyperlink ref="F104" ns1:id="rIdSystematic99"/>
+    <hyperlink ref="C105" location="'02项目完整详情'!A175" display="项目完整详情"/>
+    <hyperlink ref="F105" ns1:id="rIdSystematic100"/>
+    <hyperlink ref="C106" location="'02项目完整详情'!A176" display="项目完整详情"/>
+    <hyperlink ref="F106" ns1:id="rIdSystematic101"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A177" display="项目完整详情"/>
     <hyperlink ref="F11" ns1:id="rIdSystematic102"/>
-    <hyperlink ref="C106" location="'02项目完整详情'!A182" display="项目完整详情"/>
-    <hyperlink ref="F106" ns1:id="rIdResume103"/>
-    <hyperlink ref="C107" location="'02项目完整详情'!A184" display="项目完整详情"/>
-    <hyperlink ref="F107" ns1:id="rIdResume104"/>
+    <hyperlink ref="C107" location="'02项目完整详情'!A182" display="项目完整详情"/>
+    <hyperlink ref="F107" ns1:id="rIdResume103"/>
+    <hyperlink ref="C108" location="'02项目完整详情'!A184" display="项目完整详情"/>
+    <hyperlink ref="F108" ns1:id="rIdResume104"/>
     <hyperlink ref="C14" location="'02项目完整详情'!A185" display="项目完整详情"/>
     <hyperlink ref="F14" ns1:id="rIdResume105"/>
-    <hyperlink ref="C108" location="'02项目完整详情'!A186" display="项目完整详情"/>
-    <hyperlink ref="F108" ns1:id="rIdResume106"/>
+    <hyperlink ref="C109" location="'02项目完整详情'!A186" display="项目完整详情"/>
+    <hyperlink ref="F109" ns1:id="rIdResume106"/>
     <hyperlink ref="C12" location="'02项目完整详情'!A191" display="项目完整详情"/>
     <hyperlink ref="F12" ns1:id="rIdResume107"/>
     <hyperlink ref="C22" location="'02项目完整详情'!A198" display="项目完整详情"/>
     <hyperlink ref="F22" ns1:id="rIdResume108"/>
     <hyperlink ref="C23" location="'02项目完整详情'!A200" display="项目完整详情"/>
     <hyperlink ref="F23" ns1:id="rIdResume109"/>
-    <hyperlink ref="C109" location="'02项目完整详情'!A203" display="项目完整详情"/>
-    <hyperlink ref="F109" ns1:id="rIdResume110"/>
-    <hyperlink ref="C110" location="'02项目完整详情'!A204" display="项目完整详情"/>
-    <hyperlink ref="F110" ns1:id="rIdResume111"/>
-    <hyperlink ref="C111" location="'02项目完整详情'!A206" display="项目完整详情"/>
-    <hyperlink ref="F111" ns1:id="rIdResume112"/>
-    <hyperlink ref="C112" location="'02项目完整详情'!A207" display="项目完整详情"/>
-    <hyperlink ref="F112" ns1:id="rIdResume113"/>
-    <hyperlink ref="C113" location="'02项目完整详情'!A208" display="项目完整详情"/>
-    <hyperlink ref="F113" ns1:id="rIdResume114"/>
+    <hyperlink ref="C110" location="'02项目完整详情'!A203" display="项目完整详情"/>
+    <hyperlink ref="F110" ns1:id="rIdResume110"/>
+    <hyperlink ref="C111" location="'02项目完整详情'!A204" display="项目完整详情"/>
+    <hyperlink ref="F111" ns1:id="rIdResume111"/>
+    <hyperlink ref="C112" location="'02项目完整详情'!A206" display="项目完整详情"/>
+    <hyperlink ref="F112" ns1:id="rIdResume112"/>
+    <hyperlink ref="C113" location="'02项目完整详情'!A207" display="项目完整详情"/>
+    <hyperlink ref="F113" ns1:id="rIdResume113"/>
+    <hyperlink ref="C114" location="'02项目完整详情'!A208" display="项目完整详情"/>
+    <hyperlink ref="F114" ns1:id="rIdResume114"/>
+    <hyperlink ref="C36" location="'02项目完整详情'!A209" display="项目完整详情"/>
+    <hyperlink ref="F36" ns1:id="rIdResume115"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -49780,6 +50625,32 @@
       </c>
       <c r="H74" t="str" s="3">
         <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
+      </c>
+    </row>
+    <row r="75" ht="132" customHeight="1">
+      <c r="A75" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B75" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C75" t="str" s="14">
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+      </c>
+      <c r="D75" t="str" s="15">
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+      </c>
+      <c r="E75" t="str" s="15">
+        <v>未取得当年金额/类型。</v>
+      </c>
+      <c r="F75" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G75" t="str" s="3">
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+      </c>
+      <c r="H75" t="str" s="3">
+        <v>未取得当年项目联系人。</v>
       </c>
     </row>
   </sheetData>
@@ -49930,6 +50801,8 @@
     <hyperlink ref="F74" ns1:id="rIdResume75"/>
     <hyperlink ref="C73" location="'02项目完整详情'!A202" display="项目完整详情"/>
     <hyperlink ref="F73" ns1:id="rIdResume76"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F75" ns1:id="rIdResume77"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -18974,6 +18974,172 @@
         <v>2025官方公告线索；证据不足保待核，未按历史日期猜截止。</v>
       </c>
     </row>
+    <row r="211" ht="132" customHeight="1">
+      <c r="A211" t="str" s="3">
+        <v>N062</v>
+      </c>
+      <c r="B211" t="str" s="3">
+        <v>官方搜索标题定位，正文首次超时未取得，停止工具访问</v>
+      </c>
+      <c r="C211" t="str" s="3">
+        <v>西安工业大学</v>
+      </c>
+      <c r="D211" t="str" s="3">
+        <v>陕西省特种加工重点实验室</v>
+      </c>
+      <c r="E211" t="str" s="3">
+        <v>线索待核</v>
+      </c>
+      <c r="F211" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G211" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H211" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I211" t="str" s="3">
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+      </c>
+      <c r="J211" t="str" s="3">
+        <v>未取得当年金额。</v>
+      </c>
+      <c r="K211" t="str" s="3">
+        <v>未取得学历职称年龄/校外资格及限项。</v>
+      </c>
+      <c r="L211" t="str" s="3">
+        <v>未取得固定合作及驻室要求。</v>
+      </c>
+      <c r="M211" t="str" s="3">
+        <v>经费开支外拨报销和支付节点未取得，不套同校其他实验室办法。</v>
+      </c>
+      <c r="N211" t="str" s="3">
+        <v>未取得当年周期。</v>
+      </c>
+      <c r="O211" t="str" s="3">
+        <v>成果指标数量/第一单位作者及验收未取得。</v>
+      </c>
+      <c r="P211" t="str" s="3">
+        <v>完整权属/收益未取得。</v>
+      </c>
+      <c r="Q211" t="str" s="3">
+        <v>截止、电子纸质材料及提交方式未取得。</v>
+      </c>
+      <c r="R211" t="str" s="3">
+        <v>本人博士现职已知；任务/资格/当前窗口未核，不进首页。</v>
+      </c>
+      <c r="S211" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="T211" t="str" s="3">
+        <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm</v>
+      </c>
+      <c r="U211" t="str" s="3">
+        <v>正文首次失败，附件具体URL未取得，请从公告下载。</v>
+      </c>
+      <c r="V211" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W211" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X211" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y211" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="Z211" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+      <c r="AA211" t="str" s="3">
+        <v>发现官方年度标题但正文受阻，保持待核，不猜截止或延续受理。</v>
+      </c>
+    </row>
+    <row r="212" ht="132" customHeight="1">
+      <c r="A212" t="str" s="3">
+        <v>N063</v>
+      </c>
+      <c r="B212" t="str" s="3">
+        <v>官方搜索标题定位，正文首次超时未取得，停止工具访问</v>
+      </c>
+      <c r="C212" t="str" s="3">
+        <v>重庆交通大学</v>
+      </c>
+      <c r="D212" t="str" s="3">
+        <v>绿色物流智能技术重庆市重点实验室</v>
+      </c>
+      <c r="E212" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F212" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G212" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H212" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I212" t="str" s="3">
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+      </c>
+      <c r="J212" t="str" s="3">
+        <v>未取得当年金额。</v>
+      </c>
+      <c r="K212" t="str" s="3">
+        <v>未取得学历职称年龄/校外资格及限项。</v>
+      </c>
+      <c r="L212" t="str" s="3">
+        <v>未取得固定合作及驻室要求。</v>
+      </c>
+      <c r="M212" t="str" s="3">
+        <v>经费开支外拨报销和支付节点未取得，不套同校其他实验室办法。</v>
+      </c>
+      <c r="N212" t="str" s="3">
+        <v>未取得当年周期。</v>
+      </c>
+      <c r="O212" t="str" s="3">
+        <v>成果指标数量/第一单位作者及验收未取得。</v>
+      </c>
+      <c r="P212" t="str" s="3">
+        <v>完整权属/收益未取得。</v>
+      </c>
+      <c r="Q212" t="str" s="3">
+        <v>截止、电子纸质材料及提交方式未取得。</v>
+      </c>
+      <c r="R212" t="str" s="3">
+        <v>本人博士现职已知；任务/资格/当前窗口未核，不进首页。</v>
+      </c>
+      <c r="S212" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="T212" t="str" s="3">
+        <v>https://news.cqjtu.edu.cn/info/1024/64273.htm</v>
+      </c>
+      <c r="U212" t="str" s="3">
+        <v>正文首次失败，附件具体URL未取得，请从公告下载。</v>
+      </c>
+      <c r="V212" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W212" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X212" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y212" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="Z212" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+      <c r="AA212" t="str" s="3">
+        <v>发现官方年度标题但正文受阻，保持待核，不猜截止或延续受理。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -19404,6 +19570,8 @@
     <hyperlink ref="T208" ns1:id="rIdResume430"/>
     <hyperlink ref="T209" ns1:id="rIdResume431"/>
     <hyperlink ref="T210" ns1:id="rIdResume432"/>
+    <hyperlink ref="T211" ns1:id="rIdResume433"/>
+    <hyperlink ref="T212" ns1:id="rIdResume434"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -45911,6 +46079,373 @@
         <v>resume_sources_20261009.json</v>
       </c>
       <c r="I858" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="859" ht="52.5" customHeight="1">
+      <c r="A859" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B859" t="str" s="3">
+        <v>陕西省属智能装备新增高校补漏</v>
+      </c>
+      <c r="C859" t="str" s="3">
+        <v>陕西</v>
+      </c>
+      <c r="D859" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E859" t="str" s="3">
+        <v>查询：site:xaut.edu.cn "开放课题" 2026 2027 机器人 / site:xust.edu.cn "开放基金" 2026 2027 机器人 / site:xatu.edu.cn "开放课题" 2026 2027 / site:xupt.edu.cn "开放基金" 2026 2027；线索：2026年度陕西省特种加工重点实验室开放基金申请通知-西安工业大学机电工程学院；网络与信息安全研究团队-西安理工大学计算机科学与工程学院</v>
+      </c>
+      <c r="F859" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G859" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H859" t="str" s="3">
+        <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm
+https://jsj.xaut.edu.cn/info/1028/1128.htm</v>
+      </c>
+      <c r="I859" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第384项</v>
+      </c>
+    </row>
+    <row r="860" ht="52.5" customHeight="1">
+      <c r="A860" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B860" t="str" s="3">
+        <v>重庆省属新平台目录补漏</v>
+      </c>
+      <c r="C860" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D860" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E860" t="str" s="3">
+        <v>查询：site:cqwu.edu.cn 科研平台 机器人 重点实验室 / site:cqut.edu.cn "开放课题" 2026 2027 机器人 / site:cqnu.edu.cn "开放基金" 2026 智能 / site:cqjtu.edu.cn 科研平台 机器人 重点实验室；线索：对标创新前沿 深化开放合作：重庆交通大学赴东北高校院所和企业开展交流调研-重庆交通大学新闻网；省部级科研平台-重庆交通大学--Welcome to Chongqing Jiaotong University !；交通工程应用机器人重庆市工程实验室 2026年度开放基金申报指南与中期、结题通知-重庆交通大学新闻网；重庆市交通工程应用机器人工程实验室2019年学术委员年会通知-重庆交通大学新闻网；重庆文理学院环境重点实验室</v>
+      </c>
+      <c r="F860" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G860" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H860" t="str" s="3">
+        <v>https://news.cqjtu.edu.cn/info/1021/67794.htm
+https://www.cqjtu.edu.cn/kxyj/sbjkypt.htm
+https://news.cqjtu.edu.cn/info/1024/68220.htm
+https://news.cqjtu.edu.cn/info/1024/34639.htm
+https://environment.cqwu.edu.cn/article_301113.html</v>
+      </c>
+      <c r="I860" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第385项</v>
+      </c>
+    </row>
+    <row r="861" ht="52.5" customHeight="1">
+      <c r="A861" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B861" t="str" s="3">
+        <v>重庆交通省部目录其余装备任务补漏</v>
+      </c>
+      <c r="C861" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D861" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E861" t="str" s="3">
+        <v>查询："特种船舶数字化设计与制造" "开放基金" / "水工建筑物健康诊断技术与设备" "开放课题" / "绿色航空能源动力" "开放基金" / "智能物流网络重庆市重点实验室" "开放基金"；线索：智能物流网络重庆市重点实验室2023年度开放基金申报指南-重庆交通大学新闻网；目、重庆市教委科学技术项目重点项目、重点实验室开放基金重点项目等 10 余项，主研 10 余项；获得 2018 年度重庆产学研创新成果奖一等奖、省部级教育科学优秀成果奖一等奖等；以第一作者/通讯作者发表 SCI/EI 检索学术论文 40 余篇（其中中科院一区、二区 Top 期刊 13 篇），以第一发明人授权 29 项中国发明专利；主编教育部高等学校机械类专业教学指导委员会规划教材 1 部。；主要从事新能源动力系统、智能电动载运装备（飞行器、汽车）、机电复合传动等领域教育教学和学术研究，包括新能源和智能网联汽车、航空发动机、航空新能源动力总成、无人机群协同控制、飞行汽车、机电复合传动系统等研究方向。主持国家自然科学基金面上项目和青年科学基金项目、重庆市技术创新与应用发展专项重点项目、重庆市教委科学技术项目重点项目、重点实验室开放基金重点项目等 10 余项，主研 10 余项；获得 2018 年度重庆产学研创新成果奖一等奖、省部级教育科学优秀成果奖一等奖等；以第一作者/通讯作者发表 SCI/EI 检索学术论文 40 余篇（其中中科院一区、二区 Top 期刊 13 篇），以第一发明人授权 29 项中国发明专利；主编教育部高等学校机械类专业教学指导委员会规划教材 1 部。</v>
+      </c>
+      <c r="F861" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G861" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H861" t="str" s="3">
+        <v>https://news.cqjtu.edu.cn/info/1024/51895.htm
+https://rsc.cqjtu.edu.cn/__local/5/0F/7B/565435934515F903046208BD8A2_B1BA7D38_123953.pdf
+https://rsc.cqjtu.edu.cn/__local/5/6B/70/E9E40E8742355117168C3A2177D_895C638E_138AD6.pdf</v>
+      </c>
+      <c r="I861" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第386项</v>
+      </c>
+    </row>
+    <row r="862" ht="52.5" customHeight="1">
+      <c r="A862" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B862" t="str" s="3">
+        <v>重庆交通完整省部目录相关七平台机制A</v>
+      </c>
+      <c r="C862" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D862" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E862" t="str" s="3">
+        <v>查询："城市轨道交通车辆系统集成与控制" "开放" 基金 2026 2027 / "公共交通装备设计与系统集成" "开放基金" / "山区道路复杂环境" "开放课题" 2026 2027 / "桥梁结构智能感知与控制" "开放基金" 2026 2027；线索：2026年桥梁智能与绿色建造全国重点实验室开放课题指南-桥梁智能与绿色建造全国重点试验室；省部共建山区桥梁及隧道工程国家重点实验室2021年度开放基金项目申报指南 • 时代学者；17项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F862" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G862" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H862" t="str" s="3">
+        <v>https://bridge.swjtu.edu.cn/info/1066/8471.htm
+https://www.shidaixuezhe.com/5720.html
+https://www.letpub.com.cn/index.php?article_id=984&amp;page=grant_article_details</v>
+      </c>
+      <c r="I862" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第387项</v>
+      </c>
+    </row>
+    <row r="863" ht="52.5" customHeight="1">
+      <c r="A863" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B863" t="str" s="3">
+        <v>重庆文理三机器人平台机制</v>
+      </c>
+      <c r="C863" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D863" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E863" t="str" s="3">
+        <v>查询："重庆市工业机器人集成应用" "开放" 基金 2026 2027 / "多维数据感知与智能识别" "开放" 课题 / "智能装备与先进制造" "重庆文理" "开放基金" / site:cqwu.edu.cn "开放基金" 2026 2027；线索：合肥工业大学主页平台管理系统 张慧--中文主页--首页；网络空间测绘与态势感知研究团队；基于多源数据融合与知识关联聚合的战略性新兴产业关键技术识别研究；学生发展指导平台</v>
+      </c>
+      <c r="F863" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G863" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H863" t="str" s="3">
+        <v>https://faculty.hfut.edu.cn/zhanghui123456/zh_CN/index.htm
+https://nmgroup.tsinghua.edu.cn/yjh/
+https://www.kjjb.org/article/2026/1001-7348/2026-43-5-006.htm
+https://www.shengyazhidao.com/smo/smoUniversityDetail?id=TIANJIAGAOXIAO000428</v>
+      </c>
+      <c r="I863" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第388项</v>
+      </c>
+    </row>
+    <row r="864" ht="52.5" customHeight="1">
+      <c r="A864" t="str" s="3">
+        <v>2026-10-09重庆全校目录逐平台及陕西2026补漏</v>
+      </c>
+      <c r="B864" t="str" s="3">
+        <v>陕西特种加工及重庆物流2026/27补漏</v>
+      </c>
+      <c r="C864" t="str" s="3">
+        <v>陕西·西安/重庆</v>
+      </c>
+      <c r="D864" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E864" t="str" s="3">
+        <v>查询：site:xatu.edu.cn "特种加工" "开放基金" 2026 / site:cqjtu.edu.cn "智能物流网络" "开放基金" 2026 2027 / site:cqjtu.edu.cn "桥梁结构智能感知" "开放" 2026；线索：2026年度陕西省特种加工重点实验室开放基金申请通知-西安工业大学机电工程学院；关于2025年度绿色物流智能技术重庆市重点实验室开放基金申报和结题相关事项的通知-重庆交通大学新闻网；智能物流网络重庆市重点实验室2023年度开放基金申报指南-重庆交通大学新闻网；目、重庆市教委科学技术项目重点项目、重点实验室开放基金重点项目等 10 余项，主研 10 余项；获得 2018 年度重庆产学研创新成果奖一等奖、省部级教育科学优秀成果奖一等奖等；以第一作者/通讯作者发表 SCI/EI 检索学术论文 40 余篇（其中中科院一区、二区 Top 期刊 13 篇），以第一发明人授权 29 项中国发明专利；主编教育部高等学校机械类专业教学指导委员会规划教材 1 部。；主要从事新能源动力系统、智能电动载运装备（飞行器、汽车）、机电复合传动等领域教育教学和学术研究，包括新能源和智能网联汽车、航空发动机、航空新能源动力总成、无人机群协同控制、飞行汽车、机电复合传动系统等研究方向。主持国家自然科学基金面上项目和青年科学基金项目、重庆市技术创新与应用发展专项重点项目、重庆市教委科学技术项目重点项目、重点实验室开放基金重点项目等 10 余项，主研 10 余项；获得 2018 年度重庆产学研创新成果奖一等奖、省部级教育科学优秀成果奖一等奖等；以第一作者/通讯作者发表 SCI/EI 检索学术论文 40 余篇（其中中科院一区、二区 Top 期刊 13 篇），以第一发明人授权 29 项中国发明专利；主编教育部高等学校机械类专业教学指导委员会规划教材 1 部。；精微与特种制造研究所-西安工业大学机电工程学院</v>
+      </c>
+      <c r="F864" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G864" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H864" t="str" s="3">
+        <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm
+https://news.cqjtu.edu.cn/info/1024/64273.htm
+https://news.cqjtu.edu.cn/info/1024/51895.htm
+https://rsc.cqjtu.edu.cn/__local/5/0F/7B/565435934515F903046208BD8A2_B1BA7D38_123953.pdf
+https://rsc.cqjtu.edu.cn/__local/5/6B/70/E9E40E8742355117168C3A2177D_895C638E_138AD6.pdf
+https://jdxy.xatu.edu.cn/info/14691/195255.htm</v>
+      </c>
+      <c r="I864" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第389项</v>
+      </c>
+    </row>
+    <row r="865" ht="52.5" customHeight="1">
+      <c r="A865" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B865" t="str" s="3">
+        <v>西安工业大学</v>
+      </c>
+      <c r="C865" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D865" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E865" t="str" s="3">
+        <v>陕西省特种加工重点实验室；2026；N062；官方搜索标题定位，正文首次超时未取得，停止工具访问</v>
+      </c>
+      <c r="F865" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="G865" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H865" t="str" s="3">
+        <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm</v>
+      </c>
+      <c r="I865" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="866" ht="52.5" customHeight="1">
+      <c r="A866" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B866" t="str" s="3">
+        <v>重庆交通大学</v>
+      </c>
+      <c r="C866" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D866" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E866" t="str" s="3">
+        <v>绿色物流智能技术重庆市重点实验室；2025；N063；官方搜索标题定位，正文首次超时未取得，停止工具访问</v>
+      </c>
+      <c r="F866" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="G866" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H866" t="str" s="3">
+        <v>https://news.cqjtu.edu.cn/info/1024/64273.htm</v>
+      </c>
+      <c r="I866" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="867" ht="52.5" customHeight="1">
+      <c r="A867" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B867" t="str" s="3">
+        <v>重庆交通大学</v>
+      </c>
+      <c r="C867" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D867" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E867" t="str" s="3">
+        <v>省部37平台全目录全文取得；城市轨道控制、公共交通装备、人车路协同、桥梁智能感知、特种船数字制造、水工健康装备、绿色航空/物流逐名基金2026—2027历史查；M100交通机器人工程2026复用。</v>
+      </c>
+      <c r="F867" t="str" s="3">
+        <v>全校省部目录完整不等于37平台年度全核；剩余国级与校级目录、非标题明显机器人任务的年度指南仍需核。</v>
+      </c>
+      <c r="G867" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H867" t="str" s="3">
+        <v>https://www.cqjtu.edu.cn/kxyj/sbjkypt.htm</v>
+      </c>
+      <c r="I867" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="868" ht="52.5" customHeight="1">
+      <c r="A868" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B868" t="str" s="3">
+        <v>重庆文理学院</v>
+      </c>
+      <c r="C868" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D868" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E868" t="str" s="3">
+        <v>全校市级平台目录全文（重点室/工程中心/协同/工程实验等）；机械硕士简介全文对照3科研平台：工业机器人集成、数据感知识别、智能装备先进制造，逐名机制2026—2027查。</v>
+      </c>
+      <c r="F868" t="str" s="3">
+        <v>专业实验实训室非科研开放现金基金；未定位3平台正式资助不认定无基金；国家/校级自设目录及其他学院年度未齐。</v>
+      </c>
+      <c r="G868" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H868" t="str" s="3">
+        <v>https://kjb.cqwu.edu.cn/channel_23028.html
+https://jdxy.cqwu.edu.cn/channel_24582.html</v>
+      </c>
+      <c r="I868" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="869" ht="52.5" customHeight="1">
+      <c r="A869" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B869" t="str" s="3">
+        <v>重庆交通大学经管物流</v>
+      </c>
+      <c r="C869" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D869" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E869" t="str" s="3">
+        <v>2023智能物流网络开放完整4方向已读，末端配送/制造物流/绿色共享/通道物流网络优化，无机器人或设备感知控制实际任务，E084排除；2025绿色物流首超时N063待核。</v>
+      </c>
+      <c r="F869" t="str" s="3">
+        <v>2025具体任务未知，不能套2023排除结论；两实验室是否重组改名未取得，逐年独立。</v>
+      </c>
+      <c r="G869" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H869" t="str" s="3">
+        <v>https://news.cqjtu.edu.cn/info/1024/51895.htm
+https://news.cqjtu.edu.cn/info/1024/64273.htm</v>
+      </c>
+      <c r="I869" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="870" ht="52.5" customHeight="1">
+      <c r="A870" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B870" t="str" s="3">
+        <v>西安工业大学</v>
+      </c>
+      <c r="C870" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D870" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E870" t="str" s="3">
+        <v>新2026陕西特种加工基金标题官方搜索定位，首正文超时N062待核/人工；西安理工/科技/邮电省属年度补漏查询有记录。</v>
+      </c>
+      <c r="F870" t="str" s="3">
+        <v>各校全目录未读，2026加工具体任务和全部条款未取，不能凭加工或控制标题相关。</v>
+      </c>
+      <c r="G870" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H870" t="str" s="3">
+        <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm</v>
+      </c>
+      <c r="I870" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -49826,31 +50361,33 @@
         <v>资料未取得</v>
       </c>
     </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="20" t="str">
+    <row r="44" ht="132" customHeight="1">
+      <c r="A44" t="str" s="20">
         <v>线索待核</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B44" t="str" s="13">
         <v>未取得</v>
       </c>
-      <c r="C44" s="14" t="str">
-        <v>重庆大学·高端装备机械传动全国重点实验室2026年度线索</v>
-      </c>
-      <c r="D44" s="15" t="str">
-        <v>2026指南未取得；2025机器人传动任务不得自动沿用</v>
-      </c>
-      <c r="E44" s="15" t="str">
-        <v>资料未取得</v>
-      </c>
-      <c r="F44" s="16" t="str">
-        <v>线索</v>
-      </c>
-      <c r="G44" s="3" t="str">
-        <v>核验纠错：现有90052.htm为科技活动周通知，不能作为2026开放课题公告；需重新寻找真正的年度通知、完整指南和机器人任务；历史M033不可套用。</v>
-      </c>
-      <c r="H44" s="3" t="str"/>
-    </row>
-    <row r="45" ht="52.5" customHeight="1">
+      <c r="C44" t="str" s="14">
+        <v>西安工业大学·陕西省特种加工重点实验室</v>
+      </c>
+      <c r="D44" t="str" s="15">
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+      </c>
+      <c r="E44" t="str" s="15">
+        <v>未取得当年金额。</v>
+      </c>
+      <c r="F44" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G44" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="H44" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="20" t="str">
         <v>线索待核</v>
       </c>
@@ -49858,10 +50395,10 @@
         <v>未取得</v>
       </c>
       <c r="C45" s="14" t="str">
-        <v>重庆邮电大学·工业物联网与网络化控制教育部重点实验室2025年度开放基金线索</v>
+        <v>重庆大学·高端装备机械传动全国重点实验室2026年度线索</v>
       </c>
       <c r="D45" s="15" t="str">
-        <v>官方首页出现2025年度开放基金条目；具体任务未取得，不套用2021仿生机器人方向</v>
+        <v>2026指南未取得；2025机器人传动任务不得自动沿用</v>
       </c>
       <c r="E45" s="15" t="str">
         <v>资料未取得</v>
@@ -49870,63 +50407,61 @@
         <v>线索</v>
       </c>
       <c r="G45" s="3" t="str">
-        <v>官方首页搜索快照显示2025开放基金；主页直接访问超时，停止重试。需手动点击年度通知补任务、截止、金额与全部条款；2026当期公告尚未取得。</v>
+        <v>核验纠错：现有90052.htm为科技活动周通知，不能作为2026开放课题公告；需重新寻找真正的年度通知、完整指南和机器人任务；历史M033不可套用。</v>
       </c>
       <c r="H45" s="3" t="str"/>
     </row>
-    <row r="46" ht="66" customHeight="1">
+    <row r="46" ht="52.5" customHeight="1">
       <c r="A46" s="20" t="str">
         <v>线索待核</v>
       </c>
-      <c r="B46" s="13" t="d">
-        <v>2026-08-15T00:00:00.000Z</v>
+      <c r="B46" s="13" t="str">
+        <v>未取得</v>
       </c>
       <c r="C46" s="14" t="str">
-        <v>科大讯飞股份有限公司／中国科学技术大学·认知智能全国重点实验室2026年高等教育科研专项</v>
+        <v>重庆邮电大学·工业物联网与网络化控制教育部重点实验室2025年度开放基金线索</v>
       </c>
       <c r="D46" s="15" t="str">
-        <v>高教教学管评测智能体；具身智能场景感知及虚实融合数据处理，机器人具体任务适用范围待核</v>
+        <v>官方首页出现2025年度开放基金条目；具体任务未取得，不套用2021仿生机器人方向</v>
       </c>
       <c r="E46" s="15" t="str">
-        <v>已取得正文未载</v>
+        <v>资料未取得</v>
       </c>
       <c r="F46" s="16" t="str">
-        <v>公告</v>
+        <v>线索</v>
       </c>
       <c r="G46" s="3" t="str">
-        <v>须核高教专项具身方向具体任务与机器人联系，以及管理办法资格、金额、外拨、署名和权属；属于已截止线索，不是当前受理。</v>
-      </c>
-      <c r="H46" s="3" t="str">
-        <v>江老师；jfjiang6@iflytek.com</v>
-      </c>
-    </row>
-    <row r="47" ht="57" customHeight="1">
+        <v>官方首页搜索快照显示2025开放基金；主页直接访问超时，停止重试。需手动点击年度通知补任务、截止、金额与全部条款；2026当期公告尚未取得。</v>
+      </c>
+      <c r="H46" s="3" t="str"/>
+    </row>
+    <row r="47" ht="66" customHeight="1">
       <c r="A47" s="20" t="str">
         <v>线索待核</v>
       </c>
-      <c r="B47" s="13" t="str">
-        <v>未取得</v>
+      <c r="B47" s="13" t="d">
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C47" s="14" t="str">
-        <v>中国科学院宁波材料技术与工程研究所·浙江省机器人与智能制造装备技术重点实验室长期开放机制</v>
+        <v>科大讯飞股份有限公司／中国科学技术大学·认知智能全国重点实验室2026年高等教育科研专项</v>
       </c>
       <c r="D47" s="15" t="str">
-        <v>精密驱动与控制、智能感知与测试、工业机器人；官方介绍明确设开放基金和开放课题</v>
+        <v>高教教学管评测智能体；具身智能场景感知及虚实融合数据处理，机器人具体任务适用范围待核</v>
       </c>
       <c r="E47" s="15" t="str">
-        <v>年度金额未取得</v>
+        <v>已取得正文未载</v>
       </c>
       <c r="F47" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G47" s="3" t="str">
-        <v>机制有官方证据，但2026—2027正式年度指南未取得；资格、合作、金额、窗口、经费、周期、成果及权属均需当期文件。</v>
+        <v>须核高教专项具身方向具体任务与机器人联系，以及管理办法资格、金额、外拨、署名和权属；属于已截止线索，不是当前受理。</v>
       </c>
       <c r="H47" s="3" t="str">
-        <v>郑天江0574-86324587</v>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1">
+        <v>江老师；jfjiang6@iflytek.com</v>
+      </c>
+    </row>
+    <row r="48" ht="57" customHeight="1">
       <c r="A48" s="20" t="str">
         <v>线索待核</v>
       </c>
@@ -49934,23 +50469,25 @@
         <v>未取得</v>
       </c>
       <c r="C48" s="14" t="str">
-        <v>新疆大学·新疆农牧机器人及智能装备工程研究中心长期开放机制</v>
+        <v>中国科学院宁波材料技术与工程研究所·浙江省机器人与智能制造装备技术重点实验室长期开放机制</v>
       </c>
       <c r="D48" s="15" t="str">
-        <v>农牧机器人与智能装备；取得开放课题管理制度，年度任务未取得</v>
+        <v>精密驱动与控制、智能感知与测试、工业机器人；官方介绍明确设开放基金和开放课题</v>
       </c>
       <c r="E48" s="15" t="str">
-        <v>中心建设总经费不是单项额度；年度金额未取得</v>
+        <v>年度金额未取得</v>
       </c>
       <c r="F48" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G48" s="3" t="str">
-        <v>管理制度文本存在其他领域模板措辞，不能推填年度申报条件；须2026—2027指南及实际资格、单项金额、窗口、周期、成果权属和外拨确认。</v>
-      </c>
-      <c r="H48" s="3" t="str"/>
-    </row>
-    <row r="49" ht="57" customHeight="1">
+        <v>机制有官方证据，但2026—2027正式年度指南未取得；资格、合作、金额、窗口、经费、周期、成果及权属均需当期文件。</v>
+      </c>
+      <c r="H48" s="3" t="str">
+        <v>郑天江0574-86324587</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="20" t="str">
         <v>线索待核</v>
       </c>
@@ -49958,47 +50495,45 @@
         <v>未取得</v>
       </c>
       <c r="C49" s="14" t="str">
-        <v>西南石油大学·机器人工程与智能制造南充市重点实验室—油气装备教育部重点实验室联合开放基金</v>
+        <v>新疆大学·新疆农牧机器人及智能装备工程研究中心长期开放机制</v>
       </c>
       <c r="D49" s="15" t="str">
-        <v>官方评审公示含蛇形机器人重大装备深腔检测等；原始任务指南未取得</v>
+        <v>农牧机器人与智能装备；取得开放课题管理制度，年度任务未取得</v>
       </c>
       <c r="E49" s="15" t="str">
-        <v>公示12项，不能由立项数推算单项金额</v>
+        <v>中心建设总经费不是单项额度；年度金额未取得</v>
       </c>
       <c r="F49" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G49" s="3" t="str">
+        <v>管理制度文本存在其他领域模板措辞，不能推填年度申报条件；须2026—2027指南及实际资格、单项金额、窗口、周期、成果权属和外拨确认。</v>
+      </c>
+      <c r="H49" s="3" t="str"/>
+    </row>
+    <row r="50" ht="57" customHeight="1">
+      <c r="A50" s="20" t="str">
+        <v>线索待核</v>
+      </c>
+      <c r="B50" s="13" t="str">
+        <v>未取得</v>
+      </c>
+      <c r="C50" s="14" t="str">
+        <v>西南石油大学·机器人工程与智能制造南充市重点实验室—油气装备教育部重点实验室联合开放基金</v>
+      </c>
+      <c r="D50" s="15" t="str">
+        <v>官方评审公示含蛇形机器人重大装备深腔检测等；原始任务指南未取得</v>
+      </c>
+      <c r="E50" s="15" t="str">
+        <v>公示12项，不能由立项数推算单项金额</v>
+      </c>
+      <c r="F50" s="16" t="str">
+        <v>公告</v>
+      </c>
+      <c r="G50" s="3" t="str">
         <v>仅取得2026-04-02拟立项公示，非申报通知。需原2026联合指南：任务、截止、资格合作、金额、周期、外拨、成果和知识产权。</v>
       </c>
-      <c r="H49" s="3" t="str"/>
-    </row>
-    <row r="50" ht="120" customHeight="1">
-      <c r="A50" t="str" s="20">
-        <v>线索待核</v>
-      </c>
-      <c r="B50" t="str" s="13">
-        <v>未确认</v>
-      </c>
-      <c r="C50" t="str" s="14">
-        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
-      </c>
-      <c r="D50" t="str" s="15">
-        <v>年度具体机器人研究任务尚未取得，不能用2025指南替代。</v>
-      </c>
-      <c r="E50" t="str" s="15">
-        <v>资料未取得</v>
-      </c>
-      <c r="F50" t="str" s="16">
-        <v>官方公告</v>
-      </c>
-      <c r="G50" t="str" s="3">
-        <v>2026正文打开失败；需完整正文及全部指南/管理/申请附件，逐项填截止、资格、金额、经费、周期、成果、IP和提交方式。</v>
-      </c>
-      <c r="H50" t="str" s="3">
-        <v>资料未取得</v>
-      </c>
+      <c r="H50" s="3" t="str"/>
     </row>
     <row r="51" ht="120" customHeight="1">
       <c r="A51" t="str" s="20">
@@ -50008,10 +50543,10 @@
         <v>未确认</v>
       </c>
       <c r="C51" t="str" s="14">
-        <v>广西科技大学·广西智能汽车多维信息融合重点实验室</v>
+        <v>武汉工程大学·智能机器人湖北省重点实验室</v>
       </c>
       <c r="D51" t="str" s="15">
-        <v>需核实年度指南是否包含自主驾驶感知、决策、规划或控制；不能仅凭汽车信息融合名称保留。</v>
+        <v>年度具体机器人研究任务尚未取得，不能用2025指南替代。</v>
       </c>
       <c r="E51" t="str" s="15">
         <v>资料未取得</v>
@@ -50020,7 +50555,7 @@
         <v>官方公告</v>
       </c>
       <c r="G51" t="str" s="3">
-        <v>正文502失败，需2026完整指南和附件，先筛具体任务再核金额、资格、合作、经费、周期、成果、IP及提交。</v>
+        <v>2026正文打开失败；需完整正文及全部指南/管理/申请附件，逐项填截止、资格、金额、经费、周期、成果、IP和提交方式。</v>
       </c>
       <c r="H51" t="str" s="3">
         <v>资料未取得</v>
@@ -50034,10 +50569,10 @@
         <v>未确认</v>
       </c>
       <c r="C52" t="str" s="14">
-        <v>济南空天信息山东省实验室·济南空天信息山东省实验室开放课题</v>
+        <v>广西科技大学·广西智能汽车多维信息融合重点实验室</v>
       </c>
       <c r="D52" t="str" s="15">
-        <v>年度任务资料未取得；只核无人系统/相关智能装备任务，不将一般遥感和空天信息自动纳入。</v>
+        <v>需核实年度指南是否包含自主驾驶感知、决策、规划或控制；不能仅凭汽车信息融合名称保留。</v>
       </c>
       <c r="E52" t="str" s="15">
         <v>资料未取得</v>
@@ -50046,13 +50581,13 @@
         <v>官方公告</v>
       </c>
       <c r="G52" t="str" s="3">
-        <v>公告502失败；需完整正文、指南及管理附件；先判定具体任务，相关者再填资格、金额、截止及经费、成果等。</v>
+        <v>正文502失败，需2026完整指南和附件，先筛具体任务再核金额、资格、合作、经费、周期、成果、IP及提交。</v>
       </c>
       <c r="H52" t="str" s="3">
         <v>资料未取得</v>
       </c>
     </row>
-    <row r="53" ht="66" customHeight="1">
+    <row r="53" ht="120" customHeight="1">
       <c r="A53" t="str" s="20">
         <v>线索待核</v>
       </c>
@@ -50060,22 +50595,22 @@
         <v>未确认</v>
       </c>
       <c r="C53" t="str" s="14">
-        <v>成都大学·四川省智能康复系统感知与控制国际联合研究中心</v>
+        <v>济南空天信息山东省实验室·济南空天信息山东省实验室开放课题</v>
       </c>
       <c r="D53" t="str" s="15">
-        <v>年度具体任务尚未取得；智能康复平台仅作相关候选。</v>
+        <v>年度任务资料未取得；只核无人系统/相关智能装备任务，不将一般遥感和空天信息自动纳入。</v>
       </c>
       <c r="E53" t="str" s="15">
-        <v>未取得/公开正文未载</v>
+        <v>资料未取得</v>
       </c>
       <c r="F53" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G53" t="str" s="3">
-        <v>需完整2025正文及附件；2026/2027新指南未取得。逐项核任务、校外资格、金额、截止、合作及经费、周期、成果、IP、提交。</v>
+        <v>公告502失败；需完整正文、指南及管理附件；先判定具体任务，相关者再填资格、金额、截止及经费、成果等。</v>
       </c>
       <c r="H53" t="str" s="3">
-        <v>未取得/公开正文未载</v>
+        <v>资料未取得</v>
       </c>
     </row>
     <row r="54" ht="66" customHeight="1">
@@ -50086,10 +50621,10 @@
         <v>未确认</v>
       </c>
       <c r="C54" t="str" s="14">
-        <v>西华大学·智能空地融合载具及管控教育部工程研究中心</v>
+        <v>成都大学·四川省智能康复系统感知与控制国际联合研究中心</v>
       </c>
       <c r="D54" t="str" s="15">
-        <v>年度具体无人/空地载具任务待取得；不把平台名当年度任务。</v>
+        <v>年度具体任务尚未取得；智能康复平台仅作相关候选。</v>
       </c>
       <c r="E54" t="str" s="15">
         <v>未取得/公开正文未载</v>
@@ -50098,7 +50633,7 @@
         <v>官方公告</v>
       </c>
       <c r="G54" t="str" s="3">
-        <v>需完整2026正文及指南/管理/申请附件，确认机器人自主系统任务与全部申报经费条款；2027未取得。</v>
+        <v>需完整2025正文及附件；2026/2027新指南未取得。逐项核任务、校外资格、金额、截止、合作及经费、周期、成果、IP、提交。</v>
       </c>
       <c r="H54" t="str" s="3">
         <v>未取得/公开正文未载</v>
@@ -50112,10 +50647,10 @@
         <v>未确认</v>
       </c>
       <c r="C55" t="str" s="14">
-        <v>云南农业大学·云南省作物生产与智慧农业重点实验室</v>
+        <v>西华大学·智能空地融合载具及管控教育部工程研究中心</v>
       </c>
       <c r="D55" t="str" s="15">
-        <v>具体任务未取得；须确认是否包含农机机器人/感知控制，不能因智慧农业名称保留为相关项目。</v>
+        <v>年度具体无人/空地载具任务待取得；不把平台名当年度任务。</v>
       </c>
       <c r="E55" t="str" s="15">
         <v>未取得/公开正文未载</v>
@@ -50124,37 +50659,36 @@
         <v>官方公告</v>
       </c>
       <c r="G55" t="str" s="3">
-        <v>需完整2026正文及附件，先核任务；无农机机器人及相关感知控制任务则剔除。其余资格、金额、截止、合作、经费、成果、IP待核。</v>
+        <v>需完整2026正文及指南/管理/申请附件，确认机器人自主系统任务与全部申报经费条款；2027未取得。</v>
       </c>
       <c r="H55" t="str" s="3">
         <v>未取得/公开正文未载</v>
       </c>
     </row>
     <row r="56" ht="66" customHeight="1">
-      <c r="A56" s="20" t="str">
-        <v>方向待核·公告已发布</v>
-      </c>
-      <c r="B56" s="13" t="d">
-        <v>2026-10-10T00:00:00.000Z</v>
-      </c>
-      <c r="C56" s="14" t="str">
-        <v>新疆工程学院·新疆煤炭资源绿色开采教育部重点实验室</v>
-      </c>
-      <c r="D56" s="15" t="str">
-        <v>方向待核：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。</v>
-      </c>
-      <c r="E56" s="15" t="str">
-        <v>5—10万元</v>
-      </c>
-      <c r="F56" s="16" t="str">
-        <v>公告</v>
-      </c>
-      <c r="G56" s="3" t="str">
-        <v>筛选/证据缺口：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。
-知识产权：已取得公开资料未载明知识产权的完整条款。</v>
-      </c>
-      <c r="H56" s="3" t="str">
-        <v>gcxykfkt2026@163.com</v>
+      <c r="A56" t="str" s="20">
+        <v>线索待核</v>
+      </c>
+      <c r="B56" t="str" s="13">
+        <v>未确认</v>
+      </c>
+      <c r="C56" t="str" s="14">
+        <v>云南农业大学·云南省作物生产与智慧农业重点实验室</v>
+      </c>
+      <c r="D56" t="str" s="15">
+        <v>具体任务未取得；须确认是否包含农机机器人/感知控制，不能因智慧农业名称保留为相关项目。</v>
+      </c>
+      <c r="E56" t="str" s="15">
+        <v>未取得/公开正文未载</v>
+      </c>
+      <c r="F56" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G56" t="str" s="3">
+        <v>需完整2026正文及附件，先核任务；无农机机器人及相关感知控制任务则剔除。其余资格、金额、截止、合作、经费、成果、IP待核。</v>
+      </c>
+      <c r="H56" t="str" s="3">
+        <v>未取得/公开正文未载</v>
       </c>
     </row>
     <row r="57" ht="66" customHeight="1">
@@ -50162,53 +50696,54 @@
         <v>方向待核·公告已发布</v>
       </c>
       <c r="B57" s="13" t="d">
-        <v>2026-10-12T00:00:00.000Z</v>
+        <v>2026-10-10T00:00:00.000Z</v>
       </c>
       <c r="C57" s="14" t="str">
-        <v>中北大学·电子测试技术全国重点实验室</v>
+        <v>新疆工程学院·新疆煤炭资源绿色开采教育部重点实验室</v>
       </c>
       <c r="D57" s="15" t="str">
-        <v>方向待核：本期方向为电子测试与仪器，正文未取得明确机器人任务证据；机器人文字出现在相邻文章，不能据此保留。</v>
+        <v>方向待核：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。</v>
       </c>
       <c r="E57" s="15" t="str">
-        <v>每项不超过10万元。</v>
+        <v>5—10万元</v>
       </c>
       <c r="F57" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G57" s="3" t="str">
+        <v>筛选/证据缺口：煤炭绿色开采及矿山智能化方向未明确机器人、无人开采装备的本期任务；须确认指南中的具体装备研究内容。
+知识产权：已取得公开资料未载明知识产权的完整条款。</v>
+      </c>
+      <c r="H57" s="3" t="str">
+        <v>gcxykfkt2026@163.com</v>
+      </c>
+    </row>
+    <row r="58" ht="66" customHeight="1">
+      <c r="A58" s="20" t="str">
+        <v>方向待核·公告已发布</v>
+      </c>
+      <c r="B58" s="13" t="d">
+        <v>2026-10-12T00:00:00.000Z</v>
+      </c>
+      <c r="C58" s="14" t="str">
+        <v>中北大学·电子测试技术全国重点实验室</v>
+      </c>
+      <c r="D58" s="15" t="str">
+        <v>方向待核：本期方向为电子测试与仪器，正文未取得明确机器人任务证据；机器人文字出现在相邻文章，不能据此保留。</v>
+      </c>
+      <c r="E58" s="15" t="str">
+        <v>每项不超过10万元。</v>
+      </c>
+      <c r="F58" s="16" t="str">
+        <v>公告</v>
+      </c>
+      <c r="G58" s="3" t="str">
         <v>筛选/证据缺口：本期方向为电子测试与仪器，正文未取得明确机器人任务证据；机器人文字出现在相邻文章，不能据此保留。
 经费使用及外拨：公告仅说明基金由实验室管理，未明确外拨和开支细则，须查管理办法或合同。
 知识产权：已取得公开资料未载明知识产权的完整条款。</v>
       </c>
-      <c r="H57" s="3" t="str">
+      <c r="H58" s="3" t="str">
         <v>zhangle@nuc.edu.cn</v>
-      </c>
-    </row>
-    <row r="58" ht="66" customHeight="1">
-      <c r="A58" s="20" t="str">
-        <v>方向待核·公告已发布</v>
-      </c>
-      <c r="B58" s="13" t="d">
-        <v>2026-10-31T00:00:00.000Z</v>
-      </c>
-      <c r="C58" s="14" t="str">
-        <v>中国科学技术大学·脑启发智能感知与认知教育部重点实验室</v>
-      </c>
-      <c r="D58" s="15" t="str">
-        <v>方向待核：公告资助脑启发感知、认知、芯片及示范系统，但未明确机器人验证对象；需确认机器人感知或具身任务是否属于本期范围。</v>
-      </c>
-      <c r="E58" s="15" t="str">
-        <v>5万元/项</v>
-      </c>
-      <c r="F58" s="16" t="str">
-        <v>公告</v>
-      </c>
-      <c r="G58" s="3" t="str">
-        <v>正文已取得完整资格/外拨/权属，不能重复列为未知；年度任务为脑成像、脑启发视觉听觉嗅觉、知识图谱推理决策、芯片系统。机器人相关具体任务适用范围仍待核；申请/任务书等附件未取得。</v>
-      </c>
-      <c r="H58" s="3" t="str">
-        <v>童老师0551-63607515；niant209@ustc.edu.cn</v>
       </c>
     </row>
     <row r="59" ht="66" customHeight="1">
@@ -50219,386 +50754,386 @@
         <v>2026-10-31T00:00:00.000Z</v>
       </c>
       <c r="C59" s="14" t="str">
-        <v>武汉理工大学·交通物联网技术湖北省重点实验室</v>
+        <v>中国科学技术大学·脑启发智能感知与认知教育部重点实验室</v>
       </c>
       <c r="D59" s="15" t="str">
-        <v>公告列交通信息多模态感知等4方向，未写明机器人/无人交通的具体任务；不仅凭物联网/感知名称判相关。</v>
+        <v>方向待核：公告资助脑启发感知、认知、芯片及示范系统，但未明确机器人验证对象；需确认机器人感知或具身任务是否属于本期范围。</v>
       </c>
       <c r="E59" s="15" t="str">
-        <v>拟5—8项；平均1—3万元/项（原文口径，非统一定额）。</v>
+        <v>5万元/项</v>
       </c>
       <c r="F59" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G59" s="3" t="str">
-        <v>申请书DOC工具不支持，需用户下载；需确认所申报机器人感知/自主交通具体任务是否属于年度范围，及允许报销科目和合同条款。</v>
+        <v>正文已取得完整资格/外拨/权属，不能重复列为未知；年度任务为脑成像、脑启发视觉听觉嗅觉、知识图谱推理决策、芯片系统。机器人相关具体任务适用范围仍待核；申请/任务书等附件未取得。</v>
       </c>
       <c r="H59" s="3" t="str">
-        <v>郭老师；iot@whut.edu.cn</v>
+        <v>童老师0551-63607515；niant209@ustc.edu.cn</v>
       </c>
     </row>
     <row r="60" ht="66" customHeight="1">
       <c r="A60" s="20" t="str">
-        <v>2026年度受理窗口待核</v>
-      </c>
-      <c r="B60" s="13" t="str">
-        <v>未取得</v>
+        <v>方向待核·公告已发布</v>
+      </c>
+      <c r="B60" s="13" t="d">
+        <v>2026-10-31T00:00:00.000Z</v>
       </c>
       <c r="C60" s="14" t="str">
-        <v>青岛大学／青岛大学附属医院·山东省数字医学与计算机辅助手术重点实验室</v>
+        <v>武汉理工大学·交通物联网技术湖北省重点实验室</v>
       </c>
       <c r="D60" s="15" t="str">
-        <v>虚拟手术机器人关键技术研发；计算机辅助手术设备、医学影像处理与医学数据分析、临床三维重建（官方年度指南明确列示）</v>
+        <v>公告列交通信息多模态感知等4方向，未写明机器人/无人交通的具体任务；不仅凭物联网/感知名称判相关。</v>
       </c>
       <c r="E60" s="15" t="str">
-        <v>1—3万元/项；公告提及2025及2026每年度各2项</v>
+        <v>拟5—8项；平均1—3万元/项（原文口径，非统一定额）。</v>
       </c>
       <c r="F60" s="16" t="str">
         <v>公告</v>
       </c>
       <c r="G60" s="3" t="str">
+        <v>申请书DOC工具不支持，需用户下载；需确认所申报机器人感知/自主交通具体任务是否属于年度范围，及允许报销科目和合同条款。</v>
+      </c>
+      <c r="H60" s="3" t="str">
+        <v>郭老师；iot@whut.edu.cn</v>
+      </c>
+    </row>
+    <row r="61" ht="66" customHeight="1">
+      <c r="A61" s="20" t="str">
+        <v>2026年度受理窗口待核</v>
+      </c>
+      <c r="B61" s="13" t="str">
+        <v>未取得</v>
+      </c>
+      <c r="C61" s="14" t="str">
+        <v>青岛大学／青岛大学附属医院·山东省数字医学与计算机辅助手术重点实验室</v>
+      </c>
+      <c r="D61" s="15" t="str">
+        <v>虚拟手术机器人关键技术研发；计算机辅助手术设备、医学影像处理与医学数据分析、临床三维重建（官方年度指南明确列示）</v>
+      </c>
+      <c r="E61" s="15" t="str">
+        <v>1—3万元/项；公告提及2025及2026每年度各2项</v>
+      </c>
+      <c r="F61" s="16" t="str">
+        <v>公告</v>
+      </c>
+      <c r="G61" s="3" t="str">
         <v>取得2025-10-10跨年度公开指南，但未核实2026批次当期受理。需确认2026实际受理窗口与截止时间、项目合同、经费外拨及临床数据/固定合作要求。</v>
       </c>
-      <c r="H60" s="3" t="str">
+      <c r="H61" s="3" t="str">
         <v>loojourney@163.com</v>
       </c>
     </row>
-    <row r="61" ht="66" customHeight="1">
-      <c r="A61" t="str" s="20">
+    <row r="62" ht="66" customHeight="1">
+      <c r="A62" t="str" s="20">
         <v>已截止·任务待核</v>
       </c>
-      <c r="B61" t="n" s="13">
+      <c r="B62" t="n" s="13">
         <v>46265</v>
       </c>
-      <c r="C61" t="str" s="14">
+      <c r="C62" t="str" s="14">
         <v>成都大学·模式识别与智能信息处理四川省教育厅高校重点实验室</v>
       </c>
-      <c r="D61" t="str" s="15">
+      <c r="D62" t="str" s="15">
         <v>年度具体任务在申报指南，尚未取得；不凭模式识别平台名确定机器人相关性。</v>
       </c>
-      <c r="E61" t="str" s="15">
+      <c r="E62" t="str" s="15">
         <v>未取得/公开正文未载</v>
-      </c>
-      <c r="F61" t="str" s="16">
-        <v>官方公告</v>
-      </c>
-      <c r="G61" t="str" s="3">
-        <v>需下载2026修订版指南，核实际任务、校外资格、金额、合作、周期、经费及外拨、成果和IP。正文截止已过，不列首页。</v>
-      </c>
-      <c r="H61" t="str" s="3">
-        <v>李老师；18853318883；ligen@cdu.edu.cn</v>
-      </c>
-    </row>
-    <row r="62" ht="87" customHeight="1">
-      <c r="A62" t="str" s="20">
-        <v>历史批次·截止条款待核</v>
-      </c>
-      <c r="B62" t="str" s="13">
-        <v>具体截止日未取得（2026-04-14已发布立项通知）</v>
-      </c>
-      <c r="C62" t="str" s="14">
-        <v>青海大学·新能源系统高端装备和智慧运行教育部工程研究中心</v>
-      </c>
-      <c r="D62" t="str" s="15">
-        <v>年度方向四2明确新能源场站先进机器人、自动巡检、故障排查及维修、无人机巡检、自动化清洁维护、机器人与AI融合实现自主运维；其他能源调度/材料任务不扩充。</v>
-      </c>
-      <c r="E62" t="str" s="15">
-        <v>5万元/项；拟资助3项。</v>
       </c>
       <c r="F62" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G62" t="str" s="3">
-        <v>2026立项结果已发布，非当前申报项目；待补PDF第6页截止/联系人/知识产权等及管理办法，核研究期与11月30报账时间关系；2027公告未取得。</v>
+        <v>需下载2026修订版指南，核实际任务、校外资格、金额、合作、周期、经费及外拨、成果和IP。正文截止已过，不列首页。</v>
       </c>
       <c r="H62" t="str" s="3">
-        <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
-      </c>
-    </row>
-    <row r="63" ht="72" customHeight="1">
+        <v>李老师；18853318883；ligen@cdu.edu.cn</v>
+      </c>
+    </row>
+    <row r="63" ht="87" customHeight="1">
       <c r="A63" t="str" s="20">
-        <v>历史批次·截止年份冲突待核</v>
+        <v>历史批次·截止条款待核</v>
       </c>
       <c r="B63" t="str" s="13">
-        <v>原文2024-07-15至2023-07-20；年份冲突</v>
+        <v>具体截止日未取得（2026-04-14已发布立项通知）</v>
       </c>
       <c r="C63" t="str" s="14">
-        <v>江西科技师范大学·江西省无人感知系统与人工智能技术工程研究中心</v>
+        <v>青海大学·新能源系统高端装备和智慧运行教育部工程研究中心</v>
       </c>
       <c r="D63" t="str" s="15">
-        <v>三维重建；目标感知与识别；无人移动载体自主导航及智能控制；无人移动载体协同工作控制；人工智能感知方法。</v>
+        <v>年度方向四2明确新能源场站先进机器人、自动巡检、故障排查及维修、无人机巡检、自动化清洁维护、机器人与AI融合实现自主运维；其他能源调度/材料任务不扩充。</v>
       </c>
       <c r="E63" t="str" s="15">
-        <v>一般课题不超过3万元/项</v>
+        <v>5万元/项；拟资助3项。</v>
       </c>
       <c r="F63" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G63" t="str" s="3">
-        <v>截止原文“2023年度”及2024-07-15—2023-07-20互相矛盾，不改写为2024-07-20；下载RAR中的申请指南、管理办法、申请书，补金额类别、经费/外拨、成果/IP、合作要求。2026—2027公告未定位，不能当当前窗口。</v>
+        <v>2026立项结果已发布，非当前申报项目；待补PDF第6页截止/联系人/知识产权等及管理办法，核研究期与11月30报账时间关系；2027公告未取得。</v>
       </c>
       <c r="H63" t="str" s="3">
-        <v>刘老师13576931367；20423232@qq.com</v>
-      </c>
-    </row>
-    <row r="64" ht="117" customHeight="1">
+        <v>具体申报联系人在未取得末页；学院公开邮箱seee@qhu.edu.cn仅作一般联系入口。</v>
+      </c>
+    </row>
+    <row r="64" ht="72" customHeight="1">
       <c r="A64" t="str" s="20">
-        <v>任务证据待核·窗口未截止</v>
-      </c>
-      <c r="B64" t="n" s="13">
-        <v>46305</v>
+        <v>历史批次·截止年份冲突待核</v>
+      </c>
+      <c r="B64" t="str" s="13">
+        <v>原文2024-07-15至2023-07-20；年份冲突</v>
       </c>
       <c r="C64" t="str" s="14">
-        <v>南昌航空大学·江西省智慧建筑工程研究中心等联署四个平台</v>
+        <v>江西科技师范大学·江西省无人感知系统与人工智能技术工程研究中心</v>
       </c>
       <c r="D64" t="str" s="15">
-        <v>公告列低空基础设施风险防控、韧性建造与智能运维、安全监测预警应急、智慧建筑绿色低碳、建筑及低空基础设施数字化智能系统、自主相关方向；未明确机器人感知、规划、控制等具体任务，须核附件，不因“低空”“智能”直接保留首页。</v>
+        <v>三维重建；目标感知与识别；无人移动载体自主导航及智能控制；无人移动载体协同工作控制；人工智能感知方法。</v>
       </c>
       <c r="E64" t="str" s="15">
-        <v>不超过2万元/项</v>
+        <v>一般课题不超过3万元/项</v>
       </c>
       <c r="F64" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G64" t="str" s="3">
-        <v>取得DOCX指南与DOC申请书，先核是否有实际机器人/自主装备相关任务；若无则剔除。金额上限/窗口已核，成果、IP、经费外拨、合作与签章条件待核。四个平台联合一轮，非四条独立项目。</v>
+        <v>截止原文“2023年度”及2024-07-15—2023-07-20互相矛盾，不改写为2024-07-20；下载RAR中的申请指南、管理办法、申请书，补金额类别、经费/外拨、成果/IP、合作要求。2026—2027公告未定位，不能当当前窗口。</v>
       </c>
       <c r="H64" t="str" s="3">
-        <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
-      </c>
-    </row>
-    <row r="65" ht="87" customHeight="1">
+        <v>刘老师13576931367；20423232@qq.com</v>
+      </c>
+    </row>
+    <row r="65" ht="117" customHeight="1">
       <c r="A65" t="str" s="20">
-        <v>历史批次·具体任务待核</v>
+        <v>任务证据待核·窗口未截止</v>
       </c>
       <c r="B65" t="n" s="13">
-        <v>43808</v>
+        <v>46305</v>
       </c>
       <c r="C65" t="str" s="14">
-        <v>宁夏大学·宁夏智能装备CAE重点实验室</v>
+        <v>南昌航空大学·江西省智慧建筑工程研究中心等联署四个平台</v>
       </c>
       <c r="D65" t="str" s="15">
-        <v>公告正文介绍多目标优化、多物理场、材料本构、复杂机电耦合；具体资助方向仅称见附件。不得以智能装备名称/优化关键词判定机器人相关，须核《开放课题设置.pdf》。</v>
+        <v>公告列低空基础设施风险防控、韧性建造与智能运维、安全监测预警应急、智慧建筑绿色低碳、建筑及低空基础设施数字化智能系统、自主相关方向；未明确机器人感知、规划、控制等具体任务，须核附件，不因“低空”“智能”直接保留首页。</v>
       </c>
       <c r="E65" t="str" s="15">
-        <v>3万元/项；成果突出可追加，追加额未载</v>
+        <v>不超过2万元/项</v>
       </c>
       <c r="F65" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G65" t="str" s="3">
-        <v>年度任务PDF首次无法读取；补机器人/自主装备具体任务证据，若无则剔除；另核管理条例、成果/IP、经费外拨及限定单位。2026—2027定向搜索未定位新公告。此前误用nu.edu.cn的空结果不作宁夏大学证据，正确域名nxu.edu.cn。</v>
+        <v>取得DOCX指南与DOC申请书，先核是否有实际机器人/自主装备相关任务；若无则剔除。金额上限/窗口已核，成果、IP、经费外拨、合作与签章条件待核。四个平台联合一轮，非四条独立项目。</v>
       </c>
       <c r="H65" t="str" s="3">
-        <v>王老师13895189949；cae@nxu.edu.cn；2019收件：贺兰山西路539号宁大C区机械工程学院750021</v>
+        <v>谢老师；71291@nchu.edu.cn；电话公告脱敏159******2519；丰和南大道696号民航与交通学院综合楼中803</v>
       </c>
     </row>
     <row r="66" ht="87" customHeight="1">
       <c r="A66" t="str" s="20">
-        <v>历史批次·公告全文待核</v>
-      </c>
-      <c r="B66" t="str" s="13">
-        <v>未取得2024准确截止</v>
+        <v>历史批次·具体任务待核</v>
+      </c>
+      <c r="B66" t="n" s="13">
+        <v>43808</v>
       </c>
       <c r="C66" t="str" s="14">
-        <v>南京航空航天大学·模式分析与机器智能工业和信息化部重点实验室</v>
+        <v>宁夏大学·宁夏智能装备CAE重点实验室</v>
       </c>
       <c r="D66" t="str" s="15">
-        <v>官方缓存列面向交互的视觉识别理解、复杂场景多模态感知、人机融合智能交互；并列特征表示、鲁棒学习、弱监督模式识别。须核全文，未限定医疗超声。</v>
+        <v>公告正文介绍多目标优化、多物理场、材料本构、复杂机电耦合；具体资助方向仅称见附件。不得以智能装备名称/优化关键词判定机器人相关，须核《开放课题设置.pdf》。</v>
       </c>
       <c r="E66" t="str" s="15">
-        <v>官方缓存：3—5万元/项，拟4—5项；全文待核</v>
+        <v>3万元/项；成果突出可追加，追加额未载</v>
       </c>
       <c r="F66" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G66" t="str" s="3">
-        <v>首次网页超时，不反复访问；需完整公告文字/网页PDF及全部附件，补准确截止、成果署名、经费外拨、IP、提交。2026—2027搜索仅定位2024批次，不当当前正式公告。</v>
+        <v>年度任务PDF首次无法读取；补机器人/自主装备具体任务证据，若无则剔除；另核管理条例、成果/IP、经费外拨及限定单位。2026—2027定向搜索未定位新公告。此前误用nu.edu.cn的空结果不作宁夏大学证据，正确域名nxu.edu.cn。</v>
       </c>
       <c r="H66" t="str" s="3">
-        <v>联系人邮箱未取得</v>
-      </c>
-    </row>
-    <row r="67" ht="102" customHeight="1">
+        <v>王老师13895189949；cae@nxu.edu.cn；2019收件：贺兰山西路539号宁大C区机械工程学院750021</v>
+      </c>
+    </row>
+    <row r="67" ht="87" customHeight="1">
       <c r="A67" t="str" s="20">
-        <v>历史批次·年度任务全文待核</v>
-      </c>
-      <c r="B67" t="n" s="13">
-        <v>45402</v>
+        <v>历史批次·公告全文待核</v>
+      </c>
+      <c r="B67" t="str" s="13">
+        <v>未取得2024准确截止</v>
       </c>
       <c r="C67" t="str" s="14">
-        <v>南京航空航天大学·高安全系统的软件开发与验证技术工业和信息化部重点实验室</v>
+        <v>南京航空航天大学·模式分析与机器智能工业和信息化部重点实验室</v>
       </c>
       <c r="D67" t="str" s="15">
-        <v>平台介绍含无人自主智能系统安全分析；已见年度方向片段仅高安全软件需求、建模及形式化验证，未取得完整年度任务。须确认当年是否支持无人自主系统，不能用平台简介代替年度任务。</v>
+        <v>官方缓存列面向交互的视觉识别理解、复杂场景多模态感知、人机融合智能交互；并列特征表示、鲁棒学习、弱监督模式识别。须核全文，未限定医疗超声。</v>
       </c>
       <c r="E67" t="str" s="15">
-        <v>缓存：2—4万元/项，拟5—10项；全文待核</v>
+        <v>官方缓存：3—5万元/项，拟4—5项；全文待核</v>
       </c>
       <c r="F67" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G67" t="str" s="3">
-        <v>年度完整方向/任务证据不足，若仅软件验证而无无人自主机器人任务则剔除；获取全文和申请模板，补资格、成果/IP、经费外拨、联系与窗口。2026—2027未定位新正式公告。</v>
+        <v>首次网页超时，不反复访问；需完整公告文字/网页PDF及全部附件，补准确截止、成果署名、经费外拨、IP、提交。2026—2027搜索仅定位2024批次，不当当前正式公告。</v>
       </c>
       <c r="H67" t="str" s="3">
         <v>联系人邮箱未取得</v>
       </c>
     </row>
-    <row r="68" ht="72" customHeight="1">
+    <row r="68" ht="102" customHeight="1">
       <c r="A68" t="str" s="20">
-        <v>公告及具体任务待核</v>
-      </c>
-      <c r="B68" t="str" s="13">
-        <v>2026准确截止未取得</v>
+        <v>历史批次·年度任务全文待核</v>
+      </c>
+      <c r="B68" t="n" s="13">
+        <v>45402</v>
       </c>
       <c r="C68" t="str" s="14">
-        <v>南京航空航天大学·民航飞机健康监测与智能维护重点实验室（基本科研业务费自主课题）</v>
+        <v>南京航空航天大学·高安全系统的软件开发与验证技术工业和信息化部重点实验室</v>
       </c>
       <c r="D68" t="str" s="15">
-        <v>现仅确认民航飞机健康监测与智能维护课题，年度机器人/自主装备相关研究任务尚未取得，不能仅智能维护名称保留首页。</v>
+        <v>平台介绍含无人自主智能系统安全分析；已见年度方向片段仅高安全软件需求、建模及形式化验证，未取得完整年度任务。须确认当年是否支持无人自主系统，不能用平台简介代替年度任务。</v>
       </c>
       <c r="E68" t="str" s="15">
-        <v>资助金额未取得</v>
+        <v>缓存：2—4万元/项，拟5—10项；全文待核</v>
       </c>
       <c r="F68" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G68" t="str" s="3">
-        <v>首次483，不再尝试；下载或复制完整2026公告及全部附件，先核真实机器人任务与外部资格；再补金额、截止、周期、成果、IP、合作、外协接收单位及提交。未进入首页。</v>
+        <v>年度完整方向/任务证据不足，若仅软件验证而无无人自主机器人任务则剔除；获取全文和申请模板，补资格、成果/IP、经费外拨、联系与窗口。2026—2027未定位新正式公告。</v>
       </c>
       <c r="H68" t="str" s="3">
-        <v>申报联系人及邮箱未取得</v>
-      </c>
-    </row>
-    <row r="69" ht="117" customHeight="1">
+        <v>联系人邮箱未取得</v>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1">
       <c r="A69" t="str" s="20">
-        <v>年度具体任务待核</v>
-      </c>
-      <c r="B69" t="n" s="13">
-        <v>46311</v>
+        <v>公告及具体任务待核</v>
+      </c>
+      <c r="B69" t="str" s="13">
+        <v>2026准确截止未取得</v>
       </c>
       <c r="C69" t="str" s="14">
-        <v>中北大学·半导体超精密加工技术与智能装备山西省重点实验室</v>
+        <v>南京航空航天大学·民航飞机健康监测与智能维护重点实验室（基本科研业务费自主课题）</v>
       </c>
       <c r="D69" t="str" s="15">
-        <v>年度方向：超精密加工理论与装备制造；多能场复合加工；半导体产业链核心装备及零部件；产线AI+智造基础理论与应用。尚未明确机器人感知、规划、控制或自主装备具体任务；不能凭AI/智能装备名称进入首页。</v>
+        <v>现仅确认民航飞机健康监测与智能维护课题，年度机器人/自主装备相关研究任务尚未取得，不能仅智能维护名称保留首页。</v>
       </c>
       <c r="E69" t="str" s="15">
-        <v>2—4万元/项，拟4—8项</v>
+        <v>资助金额未取得</v>
       </c>
       <c r="F69" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G69" t="str" s="3">
-        <v>先取得申请表及管理办法，核有无实际机器人/自主装备任务；无则剔除。附件验证码；经费外拨、IP、具体截止时点及第二邮箱用途未明示；不因日期未过直接写可申请。</v>
+        <v>首次483，不再尝试；下载或复制完整2026公告及全部附件，先核真实机器人任务与外部资格；再补金额、截止、周期、成果、IP、合作、外协接收单位及提交。未进入首页。</v>
       </c>
       <c r="H69" t="str" s="3">
-        <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
-      </c>
-    </row>
-    <row r="70" ht="102" customHeight="1">
+        <v>申报联系人及邮箱未取得</v>
+      </c>
+    </row>
+    <row r="70" ht="117" customHeight="1">
       <c r="A70" t="str" s="20">
-        <v>历史批次·公告附件待核</v>
+        <v>年度具体任务待核</v>
       </c>
       <c r="B70" t="n" s="13">
-        <v>46296</v>
+        <v>46311</v>
       </c>
       <c r="C70" t="str" s="14">
-        <v>山东科技大学·山东省智慧矿山信息技术重点实验室</v>
+        <v>中北大学·半导体超精密加工技术与智能装备山西省重点实验室</v>
       </c>
       <c r="D70" t="str" s="15">
-        <v>官方摘要明确煤矿全场景视觉感知、恶劣条件多模态增强感知与鲁棒分析、复杂矿山环境感知与设备自适应控制、智能巡检设备、矿山具身智能装备。其他地质/矿山大模型方向不代替机器人具体任务。</v>
+        <v>年度方向：超精密加工理论与装备制造；多能场复合加工；半导体产业链核心装备及零部件；产线AI+智造基础理论与应用。尚未明确机器人感知、规划、控制或自主装备具体任务；不能凭AI/智能装备名称进入首页。</v>
       </c>
       <c r="E70" t="str" s="15">
-        <v>资助金额及项数尚未取得</v>
+        <v>2—4万元/项，拟4—8项</v>
       </c>
       <c r="F70" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G70" t="str" s="3">
+        <v>先取得申请表及管理办法，核有无实际机器人/自主装备任务；无则剔除。附件验证码；经费外拨、IP、具体截止时点及第二邮箱用途未明示；不因日期未过直接写可申请。</v>
+      </c>
+      <c r="H70" t="str" s="3">
+        <v>宋天骄15525035460；songtjarvin@nuc.edu.cn；正文另列yuruien@nuc.edu.cn；山西太原尖草坪学院路3号中北大学030051</v>
+      </c>
+    </row>
+    <row r="71" ht="102" customHeight="1">
+      <c r="A71" t="str" s="20">
+        <v>历史批次·公告附件待核</v>
+      </c>
+      <c r="B71" t="n" s="13">
+        <v>46296</v>
+      </c>
+      <c r="C71" t="str" s="14">
+        <v>山东科技大学·山东省智慧矿山信息技术重点实验室</v>
+      </c>
+      <c r="D71" t="str" s="15">
+        <v>官方摘要明确煤矿全场景视觉感知、恶劣条件多模态增强感知与鲁棒分析、复杂矿山环境感知与设备自适应控制、智能巡检设备、矿山具身智能装备。其他地质/矿山大模型方向不代替机器人具体任务。</v>
+      </c>
+      <c r="E71" t="str" s="15">
+        <v>资助金额及项数尚未取得</v>
+      </c>
+      <c r="F71" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G71" t="str" s="3">
         <v>正文首次500，保存完整2026公告和附件；补金额、资格、合作、经费外拨、周期、成果/IP、联系方式及时点。截止已过，非当前申报项目；2027年度未取得。</v>
       </c>
-      <c r="H70" t="str" s="3">
+      <c r="H71" t="str" s="3">
         <v>指定邮箱、收件地址及联系人未取得</v>
-      </c>
-    </row>
-    <row r="71" ht="132" customHeight="1">
-      <c r="A71" t="str" s="20">
-        <v>历史线索·官方公告待核</v>
-      </c>
-      <c r="B71" t="n" s="13">
-        <v>46087</v>
-      </c>
-      <c r="C71" t="str" s="14">
-        <v>潍坊学院（机构与年度公告尚待官方核验）·山东省先进动力装备智能制造技术重点实验室</v>
-      </c>
-      <c r="D71" t="str" s="15">
-        <v>转载方向含多维制造信息融合感知与控制、非结构动态环境下人机协同制造、制造系统集成与智能运维、数字孪生建模、智能测试标定等。浙江工业教师主页另记2026多机械臂协同感知控制获本实验室基金，证明机制线索，不能代替完整年度正式任务及条款。</v>
-      </c>
-      <c r="E71" t="str" s="15">
-        <v>转载每项2—3万元，未取得官方确认</v>
-      </c>
-      <c r="F71" t="str" s="16">
-        <v>线索来源（非官方）</v>
-      </c>
-      <c r="G71" t="str" s="3">
-        <v>第三方不是正式凭据；候选官方URL无法读取且真实性未确认，需人工从学校机械学院官网定位2026指南及附件、管理办法。转载电话区号0356与潍坊所在地不同，原样保留待核不自行改为0536；日期/金额不得当作已核。</v>
-      </c>
-      <c r="H71" t="str" s="3">
-        <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
       </c>
     </row>
     <row r="72" ht="132" customHeight="1">
       <c r="A72" t="str" s="20">
-        <v>历史批次·公告末段附件待核</v>
-      </c>
-      <c r="B72" t="str" s="13">
-        <v>2024申报截止原文未取得；研究期已结束</v>
+        <v>历史线索·官方公告待核</v>
+      </c>
+      <c r="B72" t="n" s="13">
+        <v>46087</v>
       </c>
       <c r="C72" t="str" s="14">
-        <v>中国石油大学（华东）·自然资源部海上丝路海洋资源环境组网观测技术创新中心</v>
+        <v>潍坊学院（机构与年度公告尚待官方核验）·山东省先进动力装备智能制造技术重点实验室</v>
       </c>
       <c r="D72" t="str" s="15">
-        <v>1.2运动船载雷达目标检测与测向；1.4海雾/AIS碰撞风险建模及航行路径规划；2.1复杂地形动态气象下无人机集群组网观测；2.3声传播折射下水下航行器非线性卡尔曼定位；2.4水上/水下一体化导航。其他土壤/温盐反演和地质任务不凭关键词扩展。</v>
+        <v>转载方向含多维制造信息融合感知与控制、非结构动态环境下人机协同制造、制造系统集成与智能运维、数字孪生建模、智能测试标定等。浙江工业教师主页另记2026多机械臂协同感知控制获本实验室基金，证明机制线索，不能代替完整年度正式任务及条款。</v>
       </c>
       <c r="E72" t="str" s="15">
-        <v>正文已见部分未给金额，需管理办法确认；不是确认零资助</v>
+        <v>转载每项2—3万元，未取得官方确认</v>
       </c>
       <c r="F72" t="str" s="16">
-        <v>官方公告</v>
+        <v>线索来源（非官方）</v>
       </c>
       <c r="G72" t="str" s="3">
-        <v>首次正文前段可读，续读末段超时即停止；人工保存完整2024公告及附件1管理办法、附件2申请书，补截止、金额、提交、经费外拨/IP。2025第二批和2026第三批实为海洋流场/遥感环境任务，按各年任务独立剔除，不覆盖2024相关结论。</v>
+        <v>第三方不是正式凭据；候选官方URL无法读取且真实性未确认，需人工从学校机械学院官网定位2026指南及附件、管理办法。转载电话区号0356与潍坊所在地不同，原样保留待核不自行改为0536；日期/金额不得当作已核。</v>
       </c>
       <c r="H72" t="str" s="3">
-        <v>研究方向联系人：1.2纪永刚jiyonggang@upc.edu.cn、崔学荣cxr@upc.edu.cn；1.4刘善伟20110052@upc.edu.cn；2.1罗偲luo_cai@upc.edu.cn；2.3余相20240018@upc.edu.cn；2.4贺凯飞kfhe@upc.edu.cn。受理联系人及提交地址待末段，不能套2026联系信息。</v>
+        <v>转载王老师0356-8785603；20220051@wfu.edu.cn，须官网确认</v>
       </c>
     </row>
     <row r="73" ht="132" customHeight="1">
       <c r="A73" t="str" s="20">
-        <v>线索待核·已截止</v>
-      </c>
-      <c r="B73" t="n" s="13">
-        <v>46158</v>
+        <v>历史批次·公告末段附件待核</v>
+      </c>
+      <c r="B73" t="str" s="13">
+        <v>2024申报截止原文未取得；研究期已结束</v>
       </c>
       <c r="C73" t="str" s="14">
-        <v>西安工程大学·功能性纺织材料及制品教育部重点实验室</v>
+        <v>中国石油大学（华东）·自然资源部海上丝路海洋资源环境组网观测技术创新中心</v>
       </c>
       <c r="D73" t="str" s="15">
-        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
+        <v>1.2运动船载雷达目标检测与测向；1.4海雾/AIS碰撞风险建模及航行路径规划；2.1复杂地形动态气象下无人机集群组网观测；2.3声传播折射下水下航行器非线性卡尔曼定位；2.4水上/水下一体化导航。其他土壤/温盐反演和地质任务不凭关键词扩展。</v>
       </c>
       <c r="E73" t="str" s="15">
-        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
+        <v>正文已见部分未给金额，需管理办法确认；不是确认零资助</v>
       </c>
       <c r="F73" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G73" t="str" s="3">
-        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
+        <v>首次正文前段可读，续读末段超时即停止；人工保存完整2024公告及附件1管理办法、附件2申请书，补截止、金额、提交、经费外拨/IP。2025第二批和2026第三批实为海洋流场/遥感环境任务，按各年任务独立剔除，不覆盖2024相关结论。</v>
       </c>
       <c r="H73" t="str" s="3">
-        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
+        <v>研究方向联系人：1.2纪永刚jiyonggang@upc.edu.cn、崔学荣cxr@upc.edu.cn；1.4刘善伟20110052@upc.edu.cn；2.1罗偲luo_cai@upc.edu.cn；2.3余相20240018@upc.edu.cn；2.4贺凯飞kfhe@upc.edu.cn。受理联系人及提交地址待末段，不能套2026联系信息。</v>
       </c>
     </row>
     <row r="74" ht="132" customHeight="1">
@@ -50606,50 +51141,102 @@
         <v>线索待核·已截止</v>
       </c>
       <c r="B74" t="n" s="13">
-        <v>46249</v>
+        <v>46158</v>
       </c>
       <c r="C74" t="str" s="14">
-        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+        <v>西安工程大学·功能性纺织材料及制品教育部重点实验室</v>
       </c>
       <c r="D74" t="str" s="15">
-        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
       </c>
       <c r="E74" t="str" s="15">
-        <v>合同金额2万元/项；计划≤10项。</v>
+        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
       </c>
       <c r="F74" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G74" t="str" s="3">
-        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
       </c>
       <c r="H74" t="str" s="3">
-        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
+        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
       </c>
     </row>
     <row r="75" ht="132" customHeight="1">
       <c r="A75" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B75" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B75" t="n" s="13">
+        <v>46249</v>
       </c>
       <c r="C75" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
       </c>
       <c r="D75" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
       </c>
       <c r="E75" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>合同金额2万元/项；计划≤10项。</v>
       </c>
       <c r="F75" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G75" t="str" s="3">
+        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+      </c>
+      <c r="H75" t="str" s="3">
+        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
+      </c>
+    </row>
+    <row r="76" ht="132" customHeight="1">
+      <c r="A76" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B76" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C76" t="str" s="14">
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+      </c>
+      <c r="D76" t="str" s="15">
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+      </c>
+      <c r="E76" t="str" s="15">
+        <v>未取得当年金额。</v>
+      </c>
+      <c r="F76" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G76" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="H76" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="77" ht="132" customHeight="1">
+      <c r="A77" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B77" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C77" t="str" s="14">
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+      </c>
+      <c r="D77" t="str" s="15">
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+      </c>
+      <c r="E77" t="str" s="15">
+        <v>未取得当年金额/类型。</v>
+      </c>
+      <c r="F77" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G77" t="str" s="3">
         <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
       </c>
-      <c r="H75" t="str" s="3">
+      <c r="H77" t="str" s="3">
         <v>未取得当年项目联系人。</v>
       </c>
     </row>
@@ -50689,10 +51276,10 @@
     <hyperlink ref="F42" ns1:id="R651cdbe3b973431b"/>
     <hyperlink ref="C31" location="'02项目完整详情'!A24"/>
     <hyperlink ref="F31" ns1:id="R8bc1a14c968d4a7f"/>
-    <hyperlink ref="C44" location="'02项目完整详情'!A145"/>
-    <hyperlink ref="F44" ns1:id="R55eba21b61b14772"/>
-    <hyperlink ref="C45" location="'02项目完整详情'!A146"/>
-    <hyperlink ref="F45" ns1:id="R551a180caac345f8"/>
+    <hyperlink ref="C45" location="'02项目完整详情'!A145"/>
+    <hyperlink ref="F45" ns1:id="R55eba21b61b14772"/>
+    <hyperlink ref="C46" location="'02项目完整详情'!A146"/>
+    <hyperlink ref="F46" ns1:id="R551a180caac345f8"/>
     <hyperlink ref="C11" location="'02项目完整详情'!A25"/>
     <hyperlink ref="F11" ns1:id="R2086099d421348f4"/>
     <hyperlink ref="C12" location="'02项目完整详情'!A26"/>
@@ -50713,8 +51300,8 @@
     <hyperlink ref="F19" ns1:id="Rf8bf73189e1c43a5"/>
     <hyperlink ref="C8" location="'02项目完整详情'!A35"/>
     <hyperlink ref="F8" ns1:id="R367eed2074814656"/>
-    <hyperlink ref="C46" location="'02项目完整详情'!A158"/>
-    <hyperlink ref="F46" ns1:id="R99143e47e9a9434d"/>
+    <hyperlink ref="C47" location="'02项目完整详情'!A158"/>
+    <hyperlink ref="F47" ns1:id="R99143e47e9a9434d"/>
     <hyperlink ref="C20" location="'02项目完整详情'!A36"/>
     <hyperlink ref="F20" ns1:id="R8d34a7c2e0084c6a"/>
     <hyperlink ref="C21" location="'02项目完整详情'!A37"/>
@@ -50723,86 +51310,90 @@
     <hyperlink ref="F22" ns1:id="R23174a5763434750"/>
     <hyperlink ref="C23" location="'02项目完整详情'!A39"/>
     <hyperlink ref="F23" ns1:id="R8ec89a5433eb4d09"/>
-    <hyperlink ref="C56" location="'02项目完整详情'!A45"/>
-    <hyperlink ref="F56" ns1:id="Rba0663bbe3774f6b"/>
-    <hyperlink ref="C57" location="'02项目完整详情'!A46"/>
-    <hyperlink ref="F57" ns1:id="Rcf6a5473b1eb4a54"/>
-    <hyperlink ref="C58" location="'02项目完整详情'!A48"/>
-    <hyperlink ref="F58" ns1:id="R21f68751bbc1488c"/>
-    <hyperlink ref="C59" location="'02项目完整详情'!A49"/>
-    <hyperlink ref="F59" ns1:id="R007532abefe345a9"/>
+    <hyperlink ref="C57" location="'02项目完整详情'!A45"/>
+    <hyperlink ref="F57" ns1:id="Rba0663bbe3774f6b"/>
+    <hyperlink ref="C58" location="'02项目完整详情'!A46"/>
+    <hyperlink ref="F58" ns1:id="Rcf6a5473b1eb4a54"/>
+    <hyperlink ref="C59" location="'02项目完整详情'!A48"/>
+    <hyperlink ref="F59" ns1:id="R21f68751bbc1488c"/>
+    <hyperlink ref="C60" location="'02项目完整详情'!A49"/>
+    <hyperlink ref="F60" ns1:id="R007532abefe345a9"/>
     <hyperlink ref="C32" location="'02项目完整详情'!A50"/>
     <hyperlink ref="F32" ns1:id="R3e5ed88181034131"/>
-    <hyperlink ref="C47" location="'02项目完整详情'!A159"/>
-    <hyperlink ref="F47" ns1:id="R725c16463a9940fe"/>
+    <hyperlink ref="C48" location="'02项目完整详情'!A159"/>
+    <hyperlink ref="F48" ns1:id="R725c16463a9940fe"/>
     <hyperlink ref="C33" location="'02项目完整详情'!A52"/>
     <hyperlink ref="F33" ns1:id="Recebbd68e8654020"/>
     <hyperlink ref="C34" location="'02项目完整详情'!A53"/>
     <hyperlink ref="F34" ns1:id="R5196f78bbb2f4842"/>
     <hyperlink ref="C35" location="'02项目完整详情'!A54"/>
     <hyperlink ref="F35" ns1:id="Rcd1c66555fa04aa8"/>
-    <hyperlink ref="C48" location="'02项目完整详情'!A160"/>
-    <hyperlink ref="F48" ns1:id="R012f7526bec44e8b"/>
+    <hyperlink ref="C49" location="'02项目完整详情'!A160"/>
+    <hyperlink ref="F49" ns1:id="R012f7526bec44e8b"/>
     <hyperlink ref="C36" location="'02项目完整详情'!A56"/>
     <hyperlink ref="F36" ns1:id="R920674db049346a7"/>
-    <hyperlink ref="C49" location="'02项目完整详情'!A157"/>
-    <hyperlink ref="F49" ns1:id="R76467ef3865a4dcd"/>
+    <hyperlink ref="C50" location="'02项目完整详情'!A157"/>
+    <hyperlink ref="F50" ns1:id="R76467ef3865a4dcd"/>
     <hyperlink ref="C24" location="'02项目完整详情'!A161"/>
     <hyperlink ref="F24" ns1:id="R3b497cd64a5c4936"/>
     <hyperlink ref="C37" location="'02项目完整详情'!A57"/>
     <hyperlink ref="F37" ns1:id="Rc95eacc5d5994507"/>
-    <hyperlink ref="C60" location="'02项目完整详情'!A150"/>
-    <hyperlink ref="F60" ns1:id="Rca33aafc73934cba"/>
+    <hyperlink ref="C61" location="'02项目完整详情'!A150"/>
+    <hyperlink ref="F61" ns1:id="Rca33aafc73934cba"/>
     <hyperlink ref="C38" location="'02项目完整详情'!A58"/>
     <hyperlink ref="F38" ns1:id="Rc2e98f3f226b4076"/>
     <hyperlink ref="C41" location="'02项目完整详情'!A169" display="项目完整详情"/>
     <hyperlink ref="F41" ns1:id="rIdSystematic54"/>
     <hyperlink ref="C25" location="'02项目完整详情'!A170" display="项目完整详情"/>
     <hyperlink ref="F25" ns1:id="rIdSystematic55"/>
-    <hyperlink ref="C50" location="'02项目完整详情'!A171" display="项目完整详情"/>
-    <hyperlink ref="F50" ns1:id="rIdSystematic56"/>
-    <hyperlink ref="C51" location="'02项目完整详情'!A172" display="项目完整详情"/>
-    <hyperlink ref="F51" ns1:id="rIdSystematic57"/>
-    <hyperlink ref="C52" location="'02项目完整详情'!A173" display="项目完整详情"/>
-    <hyperlink ref="F52" ns1:id="rIdSystematic58"/>
+    <hyperlink ref="C51" location="'02项目完整详情'!A171" display="项目完整详情"/>
+    <hyperlink ref="F51" ns1:id="rIdSystematic56"/>
+    <hyperlink ref="C52" location="'02项目完整详情'!A172" display="项目完整详情"/>
+    <hyperlink ref="F52" ns1:id="rIdSystematic57"/>
+    <hyperlink ref="C53" location="'02项目完整详情'!A173" display="项目完整详情"/>
+    <hyperlink ref="F53" ns1:id="rIdSystematic58"/>
     <hyperlink ref="C43" location="'02项目完整详情'!A174" display="项目完整详情"/>
     <hyperlink ref="F43" ns1:id="rIdSystematic59"/>
-    <hyperlink ref="C61" location="'02项目完整详情'!A178" display="项目完整详情"/>
-    <hyperlink ref="F61" ns1:id="rIdResume60"/>
-    <hyperlink ref="C53" location="'02项目完整详情'!A179" display="项目完整详情"/>
-    <hyperlink ref="F53" ns1:id="rIdResume61"/>
-    <hyperlink ref="C54" location="'02项目完整详情'!A180" display="项目完整详情"/>
-    <hyperlink ref="F54" ns1:id="rIdResume62"/>
-    <hyperlink ref="C55" location="'02项目完整详情'!A181" display="项目完整详情"/>
-    <hyperlink ref="F55" ns1:id="rIdResume63"/>
-    <hyperlink ref="C62" location="'02项目完整详情'!A187" display="项目完整详情"/>
-    <hyperlink ref="F62" ns1:id="rIdResume64"/>
-    <hyperlink ref="C63" location="'02项目完整详情'!A188" display="项目完整详情"/>
-    <hyperlink ref="F63" ns1:id="rIdResume65"/>
-    <hyperlink ref="C64" location="'02项目完整详情'!A189" display="项目完整详情"/>
-    <hyperlink ref="F64" ns1:id="rIdResume66"/>
-    <hyperlink ref="C65" location="'02项目完整详情'!A190" display="项目完整详情"/>
-    <hyperlink ref="F65" ns1:id="rIdResume67"/>
-    <hyperlink ref="C66" location="'02项目完整详情'!A192" display="项目完整详情"/>
-    <hyperlink ref="F66" ns1:id="rIdResume68"/>
-    <hyperlink ref="C67" location="'02项目完整详情'!A193" display="项目完整详情"/>
-    <hyperlink ref="F67" ns1:id="rIdResume69"/>
-    <hyperlink ref="C68" location="'02项目完整详情'!A194" display="项目完整详情"/>
-    <hyperlink ref="F68" ns1:id="rIdResume70"/>
-    <hyperlink ref="C69" location="'02项目完整详情'!A195" display="项目完整详情"/>
-    <hyperlink ref="F69" ns1:id="rIdResume71"/>
-    <hyperlink ref="C70" location="'02项目完整详情'!A196" display="项目完整详情"/>
-    <hyperlink ref="F70" ns1:id="rIdResume72"/>
-    <hyperlink ref="C71" location="'02项目完整详情'!A197" display="项目完整详情"/>
-    <hyperlink ref="F71" ns1:id="rIdResume73"/>
-    <hyperlink ref="C72" location="'02项目完整详情'!A199" display="项目完整详情"/>
-    <hyperlink ref="F72" ns1:id="rIdResume74"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A201" display="项目完整详情"/>
-    <hyperlink ref="F74" ns1:id="rIdResume75"/>
-    <hyperlink ref="C73" location="'02项目完整详情'!A202" display="项目完整详情"/>
-    <hyperlink ref="F73" ns1:id="rIdResume76"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F75" ns1:id="rIdResume77"/>
+    <hyperlink ref="C62" location="'02项目完整详情'!A178" display="项目完整详情"/>
+    <hyperlink ref="F62" ns1:id="rIdResume60"/>
+    <hyperlink ref="C54" location="'02项目完整详情'!A179" display="项目完整详情"/>
+    <hyperlink ref="F54" ns1:id="rIdResume61"/>
+    <hyperlink ref="C55" location="'02项目完整详情'!A180" display="项目完整详情"/>
+    <hyperlink ref="F55" ns1:id="rIdResume62"/>
+    <hyperlink ref="C56" location="'02项目完整详情'!A181" display="项目完整详情"/>
+    <hyperlink ref="F56" ns1:id="rIdResume63"/>
+    <hyperlink ref="C63" location="'02项目完整详情'!A187" display="项目完整详情"/>
+    <hyperlink ref="F63" ns1:id="rIdResume64"/>
+    <hyperlink ref="C64" location="'02项目完整详情'!A188" display="项目完整详情"/>
+    <hyperlink ref="F64" ns1:id="rIdResume65"/>
+    <hyperlink ref="C65" location="'02项目完整详情'!A189" display="项目完整详情"/>
+    <hyperlink ref="F65" ns1:id="rIdResume66"/>
+    <hyperlink ref="C66" location="'02项目完整详情'!A190" display="项目完整详情"/>
+    <hyperlink ref="F66" ns1:id="rIdResume67"/>
+    <hyperlink ref="C67" location="'02项目完整详情'!A192" display="项目完整详情"/>
+    <hyperlink ref="F67" ns1:id="rIdResume68"/>
+    <hyperlink ref="C68" location="'02项目完整详情'!A193" display="项目完整详情"/>
+    <hyperlink ref="F68" ns1:id="rIdResume69"/>
+    <hyperlink ref="C69" location="'02项目完整详情'!A194" display="项目完整详情"/>
+    <hyperlink ref="F69" ns1:id="rIdResume70"/>
+    <hyperlink ref="C70" location="'02项目完整详情'!A195" display="项目完整详情"/>
+    <hyperlink ref="F70" ns1:id="rIdResume71"/>
+    <hyperlink ref="C71" location="'02项目完整详情'!A196" display="项目完整详情"/>
+    <hyperlink ref="F71" ns1:id="rIdResume72"/>
+    <hyperlink ref="C72" location="'02项目完整详情'!A197" display="项目完整详情"/>
+    <hyperlink ref="F72" ns1:id="rIdResume73"/>
+    <hyperlink ref="C73" location="'02项目完整详情'!A199" display="项目完整详情"/>
+    <hyperlink ref="F73" ns1:id="rIdResume74"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A201" display="项目完整详情"/>
+    <hyperlink ref="F75" ns1:id="rIdResume75"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A202" display="项目完整详情"/>
+    <hyperlink ref="F74" ns1:id="rIdResume76"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F77" ns1:id="rIdResume77"/>
+    <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
+    <hyperlink ref="F44" ns1:id="rIdResume78"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F76" ns1:id="rIdResume79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -19140,6 +19140,172 @@
         <v>发现官方年度标题但正文受阻，保持待核，不猜截止或延续受理。</v>
       </c>
     </row>
+    <row r="213" ht="147" customHeight="1">
+      <c r="A213" t="str" s="3">
+        <v>N064</v>
+      </c>
+      <c r="B213" t="str" s="3">
+        <v>2025官方完整指南已取得；智慧农场传感装备任务概括，申请DOCX首次工具异常</v>
+      </c>
+      <c r="C213" t="str" s="3">
+        <v>浙江师范大学（联合莫桑比克蒙德拉内大学、宁波工程学院）</v>
+      </c>
+      <c r="D213" t="str" s="3">
+        <v>中国—莫桑比克智慧农业“一带一路”联合实验室（筹）</v>
+      </c>
+      <c r="E213" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F213" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G213" t="n" s="6">
+        <v>45843</v>
+      </c>
+      <c r="H213" t="str" s="3">
+        <v>具体时点未载；窗口2025-06-26—07-05</v>
+      </c>
+      <c r="I213" t="str" s="3">
+        <v>5方向包括农业灾害、水土、作物种质、农情感知、管理装备；具体列农作物观测多模态模型、智慧农场关键技术/传感器及装备。但未细化机器人或装备感知—规划—控制任务，待核；作物基因/土壤等方向不凭智慧标题收相关。</v>
+      </c>
+      <c r="J213" t="str" s="3">
+        <v>重点8—12万元/项；一般4—7万元/项。</v>
+      </c>
+      <c r="K213" t="str" s="3">
+        <v>高级职称或博士，否则2位本领域高级专家推荐；国内外固定受聘单位且聘期覆盖课题期限。负责人只能1项，原则上不资助本室在研未结题者；逾期课题结题后2年不得新申报。</v>
+      </c>
+      <c r="L213" t="str" s="3">
+        <v>至少1名固定研究人员合作者作为成员/联络人，与科研团队合作，申请书明确合作计划；负责人参加成果报告会（通常当年12月）。</v>
+      </c>
+      <c r="M213" t="str" s="3">
+        <v>开支/外拨、报销地点比例及支付节点完整正文未载，申请DOCX待取；不由中外联合共建推定跨境直接支付。</v>
+      </c>
+      <c r="N213" t="str" s="3">
+        <v>2年；统一起止未载。签合同第一个自然年前交中期报告，原文表述需核；与室联合获省部级以上课题可同等优先滚动，最多新1项。</v>
+      </c>
+      <c r="O213" t="str" s="3">
+        <v>成果主要SCI、发明专利、标准等，具体数量正文未载；署实验室及依托单位，指定中英名称并列第一资助项目含编号，不等于第一完成单位。中期论文报告/小结，结题提交数据、资料、报告软件测试等归档。</v>
+      </c>
+      <c r="P213" t="str" s="3">
+        <v>取得成果（资料、数据、报告、软件及测试报告等）归研究者与实验室共有；具体收益比例未载。</v>
+      </c>
+      <c r="Q213" t="str" s="3">
+        <v>按2025标准格式申请；2025-07-05前签字盖章扫描发cmbrjlsa@zjnu.cn，邮件题2025年度联合实验室开放课题申请书—单位+姓名。先无纸化，批准后纸申请+合同提交，签任务合同复核后执行。</v>
+      </c>
+      <c r="R213" t="str" s="3">
+        <v>本人博士/高校现职对应学历类别；聘期、限项和固定合作未核，任务联系不足且截止，保持待核不推荐。</v>
+      </c>
+      <c r="S213" t="str" s="3">
+        <v>智慧农场传感装备缺具体机器人/智能装备细任务；申请DOCX首次异常，需附任务内容、经费/成果数补充。正文未载第一完成单位，不混淆第一基金标注。</v>
+      </c>
+      <c r="T213" t="str" s="3">
+        <v>https://cmbrjlsa.zjnu.edu.cn/2025/0702/c19124a523663/page.htm</v>
+      </c>
+      <c r="U213" t="str" s="3">
+        <v>https://cmbrjlsa.zjnu.edu.cn/_upload/article/files/87/a2/d5514bbd4fc49519a8f868015be9/64112aa8-0017-4541-92bd-1a439a0d9661.docx</v>
+      </c>
+      <c r="V213" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W213" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X213" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y213" t="str" s="3">
+        <v>浙江·金华/宁波</v>
+      </c>
+      <c r="Z213" t="str" s="3">
+        <v>陈老师0579-82280775、chenfeng@zjnu.edu.cn；申请cmbrjlsa@zjnu.cn；金华迎宾大道688号321004。</v>
+      </c>
+      <c r="AA213" t="str" s="3">
+        <v>2025独立历史待核；URL2025-07-02与发布06-24不同，均非截止。2026—2027未定位新批，不能当存在或不存在。</v>
+      </c>
+    </row>
+    <row r="214" ht="132" customHeight="1">
+      <c r="A214" t="str" s="3">
+        <v>N065</v>
+      </c>
+      <c r="B214" t="str" s="3">
+        <v>官方搜索定位2020开放基金；首次正文工具不可访问停止</v>
+      </c>
+      <c r="C214" t="str" s="3">
+        <v>广东工业大学</v>
+      </c>
+      <c r="D214" t="str" s="3">
+        <v>智能检测与制造物联教育部重点实验室</v>
+      </c>
+      <c r="E214" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F214" t="str" s="3">
+        <v>2020</v>
+      </c>
+      <c r="G214" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H214" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I214" t="str" s="3">
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
+      </c>
+      <c r="J214" t="str" s="3">
+        <v>未取得2020金额。</v>
+      </c>
+      <c r="K214" t="str" s="3">
+        <v>2020对外资格和限项未取得。</v>
+      </c>
+      <c r="L214" t="str" s="3">
+        <v>固定合作及访问未取得。</v>
+      </c>
+      <c r="M214" t="str" s="3">
+        <v>外拨报销科目/比例/支付节点未取得。</v>
+      </c>
+      <c r="N214" t="str" s="3">
+        <v>未取得本批周期。</v>
+      </c>
+      <c r="O214" t="str" s="3">
+        <v>成果数、第一单位/作者及报告验收未取得。</v>
+      </c>
+      <c r="P214" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="Q214" t="str" s="3">
+        <v>原截止及提交要求未取得。</v>
+      </c>
+      <c r="R214" t="str" s="3">
+        <v>本人博士现职已知；历史标题证据不足，不进当前页。</v>
+      </c>
+      <c r="S214" t="str" s="3">
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+      </c>
+      <c r="T214" t="str" s="3">
+        <v>https://idiotm.gdut.edu.cn/info/1157/1177.htm</v>
+      </c>
+      <c r="U214" t="str" s="3">
+        <v>首正文失败未取得附件直链，人工从官网取。</v>
+      </c>
+      <c r="V214" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W214" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X214" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y214" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="Z214" t="str" s="3">
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+      </c>
+      <c r="AA214" t="str" s="3">
+        <v>旧年度开放线索，未取得具体任务；省/部同学院平台不共享资助条款。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -19572,6 +19738,8 @@
     <hyperlink ref="T210" ns1:id="rIdResume432"/>
     <hyperlink ref="T211" ns1:id="rIdResume433"/>
     <hyperlink ref="T212" ns1:id="rIdResume434"/>
+    <hyperlink ref="T213" ns1:id="rIdResume435"/>
+    <hyperlink ref="T214" ns1:id="rIdResume436"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -46446,6 +46614,446 @@
         <v>https://jdxy.xatu.edu.cn/info/14679/197122.htm</v>
       </c>
       <c r="I870" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="871" ht="52.5" customHeight="1">
+      <c r="A871" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B871" t="str" s="3">
+        <v>珠三角省属高校新目录补漏</v>
+      </c>
+      <c r="C871" t="str" s="3">
+        <v>广东·广州东莞珠海</v>
+      </c>
+      <c r="D871" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E871" t="str" s="3">
+        <v>查询：site:gdut.edu.cn 科研平台 机器人 重点实验室 2026 / site:gdufe.edu.cn "开放基金" 2026 机器人 / site:dgut.edu.cn "开放课题" 2026 2027 / site:zhku.edu.cn "开放基金" 2026 2027；线索：广东工业大学教师主页平台管理系统 任志刚--中文主页--首页；中国—拉美和加勒比国家技术转移中心 拉美研究院章程-中国一拉美和加勒比国家技术转移中心；科研平台-广东工业大学自动化学院；广东省科技合作研究促进中心调研团 到访中拉技术转移中心拉美研究院-中国一拉美和加勒比国家技术转移中心；广东工业大学-电子精密制造装备及技术教育部重点实验室</v>
+      </c>
+      <c r="F871" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G871" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H871" t="str" s="3">
+        <v>https://teacher.gdut.edu.cn/renzhigang/zh_CN/index.htm
+https://clttc.dgut.edu.cn/info/1901/10651.htm
+https://automation.gdut.edu.cn/kxyj1/kypt.htm
+https://clttc.dgut.edu.cn/info/1101/11061.htm
+https://jdis.gdut.edu.cn/wdzweb/newslist.aspx?ctx=4B4811F135C116514FDB179F7C97391B</v>
+      </c>
+      <c r="I871" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第390项</v>
+      </c>
+    </row>
+    <row r="872" ht="52.5" customHeight="1">
+      <c r="A872" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B872" t="str" s="3">
+        <v>广州大学与广东技术师范省平台</v>
+      </c>
+      <c r="C872" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D872" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E872" t="str" s="3">
+        <v>查询：site:gzhu.edu.cn "机器人" "开放课题" 2026 2027 / site:gzhmt.edu.cn "开放基金" 机器人 / site:gpnu.edu.cn "开放基金" 2026 2027 / site:gdou.edu.cn "开放课题" 2026 机器人；线索：谭伟强-广州大学-广州大学人工智能与大数据安全研究所；广东省南海海洋牧场智能装备重点实验室；广东普通高校重点实验室管理办法(试行）；南方海洋科学与工程广东省实验室（湛江）2027年科研人员校园招聘公告 - 广州大学就业网；开放课题-广东省南海海洋牧场智能装备重点实验室；肖华 广东海洋大学副教授，硕导，湛江市 B 类高层次 | --- | --- 肖华 人才 Email: oliviaxh@gdou.edu.cn | 肖华 研究方向: | 肖华 纳米光电材料、半导体发光器、可见光通信、光电 | 肖华 器件失效分析研究、光谱优化算法 | 肖华 硕士招生专业： | 肖华 095136 农业工程与信息技术（专业学位型硕士） | 肖华 教育经历: | 肖华 2015-09 至 2020-02， 香港城市大学，机电工程系，博士 | 肖华 2011-09 至 2014-06， 厦门大学，电子科学系，硕士 | 肖华 2007-09 至 2011-06， 湖南师范大学，物理与电子科学学院，学士 | 肖华 工作经历： |2014/07-2015/07 湖南师范大学，物理与信息科学学院，行政管理</v>
+      </c>
+      <c r="F872" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G872" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H872" t="str" s="3">
+        <v>https://aicom.gzhu.edu.cn/info/1159/1243.htm
+https://iesmr.gdou.edu.cn/index.htm
+https://kjc.gdou.edu.cn/__local/9/49/82/81E9811807D03B22A6C02C80B73_9A23B77B_44587.pdf
+https://jy.gzhu.edu.cn/index.php/web/index/jobs-brief-detail?id=STUXSW6
+https://iesmr.gdou.edu.cn/kxyj/kfkt.htm
+https://dxxy.gdou.edu.cn/__local/E/B0/EB/E99A1050C31A7B824C52FB96AC1_F3A19351_2E6F4.pdf</v>
+      </c>
+      <c r="I872" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第391项</v>
+      </c>
+    </row>
+    <row r="873" ht="52.5" customHeight="1">
+      <c r="A873" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B873" t="str" s="3">
+        <v>浙江省属装备新机制补漏</v>
+      </c>
+      <c r="C873" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D873" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E873" t="str" s="3">
+        <v>查询：site:cjlu.edu.cn "开放基金" 2026 2027 机器人 / site:zjnu.edu.cn "开放课题" 2026 2027 / site:zafu.edu.cn "开放基金" 2026 2027 / site:wzu.edu.cn "开放基金" 2026 2027；线索：全省滩涂整治工程技术与全寿命智能监测重点实验室2026年度开放项目申报通知-温州大学建筑工程学院；全省流域环境数智监测与修复重点实验室2025年度开放课题申请指南；GUANGJUN NAN 英文主页 Research project 浙江师范大学教师个人主页系统；全省流域环境数智监测与修复重点实验室第一届学术委员会在浙师大召开；关于2026年度全省经济林品质调控与加工利用重点实验室开放基金申请的通知-浙江农林大学林学院（生命科学学院）；全省流域环境数智监测与修复重点实验室2025年度开放课题立项通知</v>
+      </c>
+      <c r="F873" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G873" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H873" t="str" s="3">
+        <v>https://cace.wzu.edu.cn/info/1702/157895.htm
+https://dlhj.zjnu.edu.cn/_t33/2025/0916/c19508a527275/page.htm
+https://mypage.zjnu.edu.cn/20184435/en/kyxm/140899/list/index.htm
+https://www.zjnu.edu.cn/2026/0107/c3997a546217/page.htm
+https://sky.zafu.edu.cn/info/1004/3098.htm
+https://dlhj.zjnu.edu.cn/2025/1013/c19508a529476/page.htm</v>
+      </c>
+      <c r="I873" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第392项</v>
+      </c>
+    </row>
+    <row r="874" ht="52.5" customHeight="1">
+      <c r="A874" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B874" t="str" s="3">
+        <v>浙江新机器人省平台及院所目录发现</v>
+      </c>
+      <c r="C874" t="str" s="3">
+        <v>浙江</v>
+      </c>
+      <c r="D874" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E874" t="str" s="3">
+        <v>查询：site:zjxu.edu.cn "开放课题" 2026 2027 / site:usx.edu.cn "开放基金" 2026 2027 / site:zucc.edu.cn 科研平台 机器人 重点实验室 / 浙江 "省属" "重点实验室" "机器人" "开放基金"；线索：全省生物基健康功能纤维材料重点实验室2026年度开放基金课题申报指南-嘉兴大学材料与纺织工程学院；科学研究-嘉兴大学 生物与化学工程学院；全省先进叠层光伏技术重点实验室关于2025年度开放课题拟立项课题的公示-嘉兴大学 生物与化学工程学院；全省先进叠层光伏技术重点实验室关于征集2025年度开放课题的通知-嘉兴大学 生物与化学工程学院；材料与纺织工程学院硕士研究生导师信息表</v>
+      </c>
+      <c r="F874" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G874" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H874" t="str" s="3">
+        <v>https://cfxy.zjxu.edu.cn/info/10626/3616.htm
+https://cbcse.zjxu.edu.cn/kxyj.htm
+https://cbcse.zjxu.edu.cn/info/10453/89274.htm
+https://cbcse.zjxu.edu.cn/info/10453/89244.htm
+https://cfxy.zjxu.edu.cn/__local/6/6F/45/286D30BD75CBC6C500E502FC00F_3F6C325E_4075E.pdf</v>
+      </c>
+      <c r="I874" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第393项</v>
+      </c>
+    </row>
+    <row r="875" ht="52.5" customHeight="1">
+      <c r="A875" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B875" t="str" s="3">
+        <v>广东工业自动化2026目录新低空及协同平台A</v>
+      </c>
+      <c r="C875" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D875" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E875" t="str" s="3">
+        <v>查询："低空感知探测技术与智能物联" "开放基金" 2026 2027 / "粤港智能决策与协同控制" "开放课题" 2026 2027 / "粤港澳离散制造智能化" "开放基金" / "智能检测与制造物联" "开放课题" 2026 2027；线索：2020年开放基金-智能检测与制造物联教育部重点实验室；申请！10项重点实验室开放课题基金申请指南_搜狐网；网络空间测绘与态势感知研究团队</v>
+      </c>
+      <c r="F875" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G875" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H875" t="str" s="3">
+        <v>https://idiotm.gdut.edu.cn/info/1157/1177.htm
+https://m.sohu.com/a/960101618_121124372
+https://nmgroup.tsinghua.edu.cn/yjh/</v>
+      </c>
+      <c r="I875" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第394项</v>
+      </c>
+    </row>
+    <row r="876" ht="52.5" customHeight="1">
+      <c r="A876" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B876" t="str" s="3">
+        <v>海洋牧场及智慧农业2026/27补漏</v>
+      </c>
+      <c r="C876" t="str" s="3">
+        <v>广东·湛江/浙江</v>
+      </c>
+      <c r="D876" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E876" t="str" s="3">
+        <v>查询："南海海洋牧场智能装备" "开放课题" 2026 2027 / "莫桑比克智慧农业" "开放课题" 2026 2027 / site:zjnu.edu.cn 机器人 科研平台 重点实验室 / site:cjlu.edu.cn 机器人 科研平台 重点实验室；线索：广东省南海海洋牧场智能装备重点实验室；中国-莫桑比克智慧农业“一带一路”联合实验室2025年度开放课题拟立项汇总表（公示）；工学院组织全省重点实验室创建专项调研与研讨；重点实验室；全省智能教育技术与应用重点实验室召开工作汇报会议；全省智能教育技术与应用重点实验室</v>
+      </c>
+      <c r="F876" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G876" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H876" t="str" s="3">
+        <v>https://iesmr.gdou.edu.cn/index.htm
+https://cmbrjlsa.zjnu.edu.cn/2025/1114/c19124a538273/page.htm
+https://gxy.zjnu.edu.cn/_t952/2024/0527/c1282a469224/page.htm
+https://www.zjnu.edu.cn/4016/list.htm
+https://ieta.zjnu.edu.cn/2025/0416/c10680a515521/page.htm
+https://ieta.zjnu.edu.cn/</v>
+      </c>
+      <c r="I876" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第395项</v>
+      </c>
+    </row>
+    <row r="877" ht="52.5" customHeight="1">
+      <c r="A877" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B877" t="str" s="3">
+        <v>广东工业自动化工程/高校平台C</v>
+      </c>
+      <c r="C877" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D877" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E877" t="str" s="3">
+        <v>查询："车载传感网与智能交通" "开放基金" / "超高精度自动化检测系统" "开放基金" / "离散制造知识自动化" "开放课题" / "自动化装备与集成实验室" "开放基金"；线索：广东工业大学教师主页平台管理系统 Zhigang Ren--Home--Home；中国环境科学研究院；大连理工大学主页平台管理系统 工业装备智能控制与优化教育部重点实验室 机构概况 中文主页；2026北京航天微系统与信息技术研究所九院研发中心校园招聘公告-编制招聘网；浣江实验室；9 2022年C-V2X和车路协同行业研究报告 | PDF</v>
+      </c>
+      <c r="F877" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G877" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H877" t="str" s="3">
+        <v>https://teacher.gdut.edu.cn/renzhigang/en/index.htm
+https://www.craes.cn/
+https://institution.dlut.edu.cn/lico/zh_CN/zhym/1107043/list/index.htm
+https://www.bianzhia.com/bj/20251216/218081.html
+https://huanjianglab.zju.edu.cn/product.aspx
+https://www.scribd.com/document/796168632/9-2022%25E5%25B9%25B4C-V2X%25E5%2592%258C%25E8%25BD%25A6%25E8%25B7%25AF%25E5%258D%258F%25E5%2590%258C%25E8%25A1%258C%25E4%25B8%259A%25E7%25A0%2594%25E7%25A9%25B6%25E6%258A%25A5%25E5%2591%258A</v>
+      </c>
+      <c r="I877" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第396项</v>
+      </c>
+    </row>
+    <row r="878" ht="52.5" customHeight="1">
+      <c r="A878" t="str" s="3">
+        <v>2026-10-09珠三角省属平台与浙江长期机制补漏</v>
+      </c>
+      <c r="B878" t="str" s="3">
+        <v>广东工业自动化省级智能决策CPS平台B</v>
+      </c>
+      <c r="C878" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D878" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E878" t="str" s="3">
+        <v>查询："广东省智能决策与协同控制重点实验室" 开放基金 / "广东省信息物理融合系统" "开放课题" / "广东省物联网信息技术" "开放基金" / "智能制造信息物理融合系统集成" "开放基金"；线索：陈权-广东工业大学研究生招生信息网；广东省智能决策与协同控制重点实验室2024年度开放课题申请指南-广东工业大学自动化学院；广东省数字信号与图像处理技术重点实验室</v>
+      </c>
+      <c r="F878" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G878" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H878" t="str" s="3">
+        <v>https://yzw.gdut.edu.cn/info/1068/3780.htm
+https://automation.gdut.edu.cn/info/1081/10158.htm
+https://imagelab.stu.edu.cn/Content.aspx?Content_ID=5507&amp;type=content</v>
+      </c>
+      <c r="I878" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第397项</v>
+      </c>
+    </row>
+    <row r="879" ht="52.5" customHeight="1">
+      <c r="A879" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B879" t="str" s="3">
+        <v>浙江师范大学（联合莫桑比克蒙德拉内大学、宁波工程学院）</v>
+      </c>
+      <c r="C879" t="str" s="3">
+        <v>浙江·金华/宁波</v>
+      </c>
+      <c r="D879" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E879" t="str" s="3">
+        <v>中国—莫桑比克智慧农业“一带一路”联合实验室（筹）；2025；N064；2025官方完整指南已取得；智慧农场传感装备任务概括，申请DOCX首次工具异常</v>
+      </c>
+      <c r="F879" t="str" s="3">
+        <v>智慧农场传感装备缺具体机器人/智能装备细任务；申请DOCX首次异常，需附任务内容、经费/成果数补充。正文未载第一完成单位，不混淆第一基金标注。</v>
+      </c>
+      <c r="G879" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H879" t="str" s="3">
+        <v>https://cmbrjlsa.zjnu.edu.cn/2025/0702/c19124a523663/page.htm</v>
+      </c>
+      <c r="I879" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="880" ht="52.5" customHeight="1">
+      <c r="A880" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B880" t="str" s="3">
+        <v>广东工业大学</v>
+      </c>
+      <c r="C880" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D880" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E880" t="str" s="3">
+        <v>智能检测与制造物联教育部重点实验室；2020；N065；官方搜索定位2020开放基金；首次正文工具不可访问停止</v>
+      </c>
+      <c r="F880" t="str" s="3">
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+      </c>
+      <c r="G880" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H880" t="str" s="3">
+        <v>https://idiotm.gdut.edu.cn/info/1157/1177.htm</v>
+      </c>
+      <c r="I880" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="881" ht="52.5" customHeight="1">
+      <c r="A881" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B881" t="str" s="3">
+        <v>广东工业大学</v>
+      </c>
+      <c r="C881" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D881" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E881" t="str" s="3">
+        <v>自动化2026-08-07全目录：国家/部13条+省11条+厅2条，其中粤港协同两牌同体不能重复算；3组12个低空/协同/制造/CPS/物联/车载/自动化检测高校平台逐名机制2026—2027及旧年度。R0042024复用，N065制造物联2020首不可访问。</v>
+      </c>
+      <c r="F881" t="str" s="3">
+        <v>学院26牌目不是26个独立实验室，也非全校；剩余集成电路/电力及全校其他学院目录年度未齐；新部低空平台无正式资金公告不编金额。</v>
+      </c>
+      <c r="G881" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H881" t="str" s="3">
+        <v>https://automation.gdut.edu.cn/kxyj1/kypt.htm
+https://idiotm.gdut.edu.cn/info/1157/1177.htm</v>
+      </c>
+      <c r="I881" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="882" ht="52.5" customHeight="1">
+      <c r="A882" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B882" t="str" s="3">
+        <v>广东海洋大学</v>
+      </c>
+      <c r="C882" t="str" s="3">
+        <v>广东·湛江</v>
+      </c>
+      <c r="D882" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E882" t="str" s="3">
+        <v>南海海洋牧场智能装备省室开放课题栏和研究方向栏全文均明示共0条，2026—2027定向补漏没定位新正式基金。</v>
+      </c>
+      <c r="F882" t="str" s="3">
+        <v>可确认这两栏目0条，不能推广为实验室无基金/全校完成；平台完整介绍和其他海洋装备平台仍未齐。</v>
+      </c>
+      <c r="G882" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H882" t="str" s="3">
+        <v>https://iesmr.gdou.edu.cn/kxyj/kfkt.htm
+https://iesmr.gdou.edu.cn/kxyj/kyfx.htm</v>
+      </c>
+      <c r="I882" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="883" ht="52.5" customHeight="1">
+      <c r="A883" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B883" t="str" s="3">
+        <v>浙江师范大学/宁波工程学院</v>
+      </c>
+      <c r="C883" t="str" s="3">
+        <v>浙江·金华/宁波</v>
+      </c>
+      <c r="D883" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E883" t="str" s="3">
+        <v>N064中莫智慧农业2025完整指南，2026—2027补漏；智慧农场传感器装备只概括，多模态是农作物观测，不虚构机器人；申请表首次工具异常。</v>
+      </c>
+      <c r="F883" t="str" s="3">
+        <v>实际机器人或智能装备任务细节不足待核；省高校其他机器人平台/全校目录未齐，不能因有钱和智慧关键词认确定相关。</v>
+      </c>
+      <c r="G883" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H883" t="str" s="3">
+        <v>https://cmbrjlsa.zjnu.edu.cn/2025/0702/c19124a523663/page.htm</v>
+      </c>
+      <c r="I883" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="884" ht="52.5" customHeight="1">
+      <c r="A884" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B884" t="str" s="3">
+        <v>珠三角/浙江省属补漏组</v>
+      </c>
+      <c r="C884" t="str" s="3">
+        <v>广东/浙江</v>
+      </c>
+      <c r="D884" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E884" t="str" s="3">
+        <v>东莞、仲恺、广州大学、广东技师/海大及计量/温州/浙师/农林/嘉兴/绍兴/浙大城院新年度查询，检索语句逐条留档；农林遗传材料/嘉兴光伏标题暂不深核为机器人。</v>
+      </c>
+      <c r="F884" t="str" s="3">
+        <v>只完成所列发现查询，不当各校目录查全；新行业基金须具体装备任务证据，跨省结果不计本地发现。</v>
+      </c>
+      <c r="G884" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H884" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+      <c r="I884" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -51190,28 +51798,28 @@
     </row>
     <row r="76" ht="132" customHeight="1">
       <c r="A76" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B76" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B76" t="n" s="13">
+        <v>45843</v>
       </c>
       <c r="C76" t="str" s="14">
-        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+        <v>浙江师范大学（联合莫桑比克蒙德拉内大学、宁波工程学院）·中国—莫桑比克智慧农业“一带一路”联合实验室（筹）</v>
       </c>
       <c r="D76" t="str" s="15">
-        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+        <v>5方向包括农业灾害、水土、作物种质、农情感知、管理装备；具体列农作物观测多模态模型、智慧农场关键技术/传感器及装备。但未细化机器人或装备感知—规划—控制任务，待核；作物基因/土壤等方向不凭智慧标题收相关。</v>
       </c>
       <c r="E76" t="str" s="15">
-        <v>未取得当年金额。</v>
+        <v>重点8—12万元/项；一般4—7万元/项。</v>
       </c>
       <c r="F76" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G76" t="str" s="3">
-        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+        <v>智慧农场传感装备缺具体机器人/智能装备细任务；申请DOCX首次异常，需附任务内容、经费/成果数补充。正文未载第一完成单位，不混淆第一基金标注。</v>
       </c>
       <c r="H76" t="str" s="3">
-        <v>年度联系人未取得。</v>
+        <v>陈老师0579-82280775、chenfeng@zjnu.edu.cn；申请cmbrjlsa@zjnu.cn；金华迎宾大道688号321004。</v>
       </c>
     </row>
     <row r="77" ht="132" customHeight="1">
@@ -51222,21 +51830,73 @@
         <v>未取得</v>
       </c>
       <c r="C77" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
       </c>
       <c r="D77" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
       </c>
       <c r="E77" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>未取得2020金额。</v>
       </c>
       <c r="F77" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G77" t="str" s="3">
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+      </c>
+      <c r="H77" t="str" s="3">
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+      </c>
+    </row>
+    <row r="78" ht="132" customHeight="1">
+      <c r="A78" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B78" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C78" t="str" s="14">
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+      </c>
+      <c r="D78" t="str" s="15">
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+      </c>
+      <c r="E78" t="str" s="15">
+        <v>未取得当年金额。</v>
+      </c>
+      <c r="F78" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G78" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="H78" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="79" ht="132" customHeight="1">
+      <c r="A79" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B79" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C79" t="str" s="14">
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+      </c>
+      <c r="D79" t="str" s="15">
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+      </c>
+      <c r="E79" t="str" s="15">
+        <v>未取得当年金额/类型。</v>
+      </c>
+      <c r="F79" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G79" t="str" s="3">
         <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
       </c>
-      <c r="H77" t="str" s="3">
+      <c r="H79" t="str" s="3">
         <v>未取得当年项目联系人。</v>
       </c>
     </row>
@@ -51388,12 +52048,16 @@
     <hyperlink ref="F75" ns1:id="rIdResume75"/>
     <hyperlink ref="C74" location="'02项目完整详情'!A202" display="项目完整详情"/>
     <hyperlink ref="F74" ns1:id="rIdResume76"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F77" ns1:id="rIdResume77"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F79" ns1:id="rIdResume77"/>
     <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
     <hyperlink ref="F44" ns1:id="rIdResume78"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A212" display="项目完整详情"/>
-    <hyperlink ref="F76" ns1:id="rIdResume79"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F78" ns1:id="rIdResume79"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A213" display="项目完整详情"/>
+    <hyperlink ref="F76" ns1:id="rIdResume80"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A214" display="项目完整详情"/>
+    <hyperlink ref="F77" ns1:id="rIdResume81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -47057,6 +47057,287 @@
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
+    <row r="885" ht="52.5" customHeight="1">
+      <c r="A885" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B885" t="str" s="3">
+        <v>华南理工自动化机械完整目录入口补漏</v>
+      </c>
+      <c r="C885" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D885" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E885" t="str" s="3">
+        <v>查询：site:scut.edu.cn/au 科研平台 重点实验室 / site:scut.edu.cn/sma 科研平台 重点实验室 / site:scut.edu.cn "机器人" "重点实验室" "2026" "开放" / site:scut.edu.cn "开放基金" "2027"；线索：国家重点实验室；广东省教育厅重点实验室；National research platforms；华南理工大学华南软物质科学与技术高等研究院；实验室工作与管理条例；National Engineering Research Centers</v>
+      </c>
+      <c r="F885" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G885" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H885" t="str" s="3">
+        <v>https://www.scut.edu.cn/new/270/list.htm
+https://www.scut.edu.cn/new/gdsjytzdsys/list.htm
+https://www.scut.edu.cn/en/610/list.htm
+https://www2.scut.edu.cn/aismst/gdszdsys/list.htm
+https://www2.scut.edu.cn/_upload/article/files/83/60/c81e54a04734bf1ec916f8356425/b65fdb7c-ebe6-46f9-8af1-6646c0d6cf27.pdf
+https://www.scut.edu.cn/en/498/list.htm</v>
+      </c>
+      <c r="I885" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第398项</v>
+      </c>
+    </row>
+    <row r="886" ht="52.5" customHeight="1">
+      <c r="A886" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B886" t="str" s="3">
+        <v>西北工业机械自动化目录未齐补漏</v>
+      </c>
+      <c r="C886" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D886" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E886" t="str" s="3">
+        <v>查询：site:me.nwpu.edu.cn 科研平台 机器人 重点实验室 / site:zdhxy.nwpu.edu.cn 科研平台 机器人 重点实验室 / site:nwpu.edu.cn "自主无人系统" "开放基金" 2026 2027 / site:nwpu.edu.cn "智能机器人" "开放课题" 2027；线索：自动化学院科研平台-西北工业大学自动化学院；自动化学院召开工程基础问题（1→0）研究工作推进会-西北工业大学自动化学院；移动机器人组件平台项目竞选公告-西北工业大学自动化学院；科研平台-西北工业大学自动化学院</v>
+      </c>
+      <c r="F886" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G886" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H886" t="str" s="3">
+        <v>https://zdhxy.nwpu.edu.cn/info/1050/1985.htm
+https://zdhxy.nwpu.edu.cn/info/1081/20733.htm
+https://zdhxy.nwpu.edu.cn/info/1121/33983.htm
+https://zdhxy.nwpu.edu.cn/kxyj/kypt.htm</v>
+      </c>
+      <c r="I886" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第399项</v>
+      </c>
+    </row>
+    <row r="887" ht="52.5" customHeight="1">
+      <c r="A887" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B887" t="str" s="3">
+        <v>重庆大学自动化机械完整目录入口补漏</v>
+      </c>
+      <c r="C887" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D887" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E887" t="str" s="3">
+        <v>查询：site:coe.cqu.edu.cn 科研平台 重点实验室 / site:ce.cqu.edu.cn 科研平台 重点实验室 / site:cmve.cqu.edu.cn 科研平台 实验室 / site:cqu.edu.cn "医工" "开放基金" 2026 2027；线索：基地平台-重庆大学光电工程学院主页；重庆大学光电工程学院召开三个科研平台学术（技术）委员会会议-重庆大学光电工程学院主页；光电技术及系统教育部重点实验室-重庆大学光电工程学院主页；中心简介-重庆大学微系统研究中心；中国电子科技集团公司第五十五研究所；实验室简介-重庆大学 光纤光子器件及系统</v>
+      </c>
+      <c r="F887" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G887" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H887" t="str" s="3">
+        <v>https://coe.cqu.edu.cn/kxyj/kypt1/jdpt.htm
+https://coe.cqu.edu.cn/info/1011/7933.htm
+https://coe.cqu.edu.cn/info/1178/2374.htm
+https://msc.coe.cqu.edu.cn/zxgk/zxjj.htm
+https://coe.cqu.edu.cn/__local/0/4A/70/547B0F4B43CB296157263CC2055_3BB16769_27419.pdf?e=.pdf
+https://oft.coe.cqu.edu.cn/sysjj.htm</v>
+      </c>
+      <c r="I887" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第400项</v>
+      </c>
+    </row>
+    <row r="888" ht="52.5" customHeight="1">
+      <c r="A888" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B888" t="str" s="3">
+        <v>西工大自动化完整13平台机制A</v>
+      </c>
+      <c r="C888" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D888" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E888" t="str" s="3">
+        <v>查询："陕西省飞行控制与仿真技术" "开放基金" 2026 2027 / "信息融合技术教育部重点实验室" "开放课题" 2026 2027 / "陕西省智能装备系统安全控制" "开放基金" / "航空安全综合监控系统" "开放课题"；线索：成套装备智能化集成技术教育部重点实验室开放课题申报指南（2026年度）-兰州理工大学机电学院 | 兰州理工大学机电工程学院，理工大学机电工程学院，兰州工大机电工程学院，兰州工大机电学院，工大机电学院，；2025年度国家省部级重点实验室开放课题；赵新宇副教授_校内导师_电子信息专硕MEI_硕士研究生导师_导师信息_研究生院、党委研究生工作部；2025年雷达成像与微波光子技术教育部重点实验室开放基金课题指南；中国煤炭行业知识服务平台www.chinacaj.net；项目-高可信软件技术教育部重点实验室(北京大学)</v>
+      </c>
+      <c r="F888" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G888" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H888" t="str" s="3">
+        <v>https://jidian.lut.edu.cn/info/1924/18496.htm
+https://www.hfuu.edu.cn/kjc/74/ff/c11997a161023/page.htm
+https://gra.hutb.edu.cn/dsxx1/ssyjsds/dzxxzsmei/xnds7/content_68381
+https://www.ebookmh.org/2025/0520/c11528a375517/page.htm
+https://www.mtxb.com.cn/cn/article/pdf/preview/efc3263e-69de-464c-96c4-09ca728a4fe3.pdf
+https://hcst.pku.edu.cn/xsyj/xm.htm</v>
+      </c>
+      <c r="I888" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第401项</v>
+      </c>
+    </row>
+    <row r="889" ht="52.5" customHeight="1">
+      <c r="A889" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B889" t="str" s="3">
+        <v>西工大自动化完整13平台机制C</v>
+      </c>
+      <c r="C889" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D889" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E889" t="str" s="3">
+        <v>查询："飞机电推进技术" "开放基金" 2026 2027 / "航空航天电机系统技术" "开放课题" / "陕西省航空电气系统" "开放基金" / "陕西省稀土永磁电机及控制" "开放基金"；线索：科技资讯 2024.05-厦门大学深圳研究院；10项重点实验室课题基金申请指南汇总 - 国家自然科学基金项目申请经验分享互动 - LetPub专业SCI论文编辑</v>
+      </c>
+      <c r="F889" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G889" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H889" t="str" s="3">
+        <v>https://szri.xmu.edu.cn/info/1231/4272.htm
+https://www.letpub.com.cn/index.php?article_id=1576&amp;page=grant_article_details</v>
+      </c>
+      <c r="I889" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第402项</v>
+      </c>
+    </row>
+    <row r="890" ht="52.5" customHeight="1">
+      <c r="A890" t="str" s="3">
+        <v>2026-10-09核心机构目录剩余范围补齐</v>
+      </c>
+      <c r="B890" t="str" s="3">
+        <v>西工大自动化完整13平台机制B</v>
+      </c>
+      <c r="C890" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D890" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E890" t="str" s="3">
+        <v>查询："西安市无人机信息安全" "开放基金" / "陕西省通用航空系统" "开放课题" / "陕西省交通安全监控网络" "开放基金" / "陕西省微特电机及驱动技术" "开放基金"；线索：陕西省国民经济和社会发展第十五个五年规划纲要 - 延安市中小企业公共服务平台</v>
+      </c>
+      <c r="F890" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G890" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H890" t="str" s="3">
+        <v>https://www.yanqitong.cn/index.php/zhongshengzixun/26871.html</v>
+      </c>
+      <c r="I890" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第403项</v>
+      </c>
+    </row>
+    <row r="891" ht="52.5" customHeight="1">
+      <c r="A891" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B891" t="str" s="3">
+        <v>西北工业大学</v>
+      </c>
+      <c r="C891" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D891" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E891" t="str" s="3">
+        <v>自动化科研目录4链接全部读，2018母页完整13平台（含2021无人机信息安全）；12个飞控/信息融合/安全装备/航空监控/无人机/交通安全/微特电机/电推进平台逐名基金2026—2027历史查，M053跨省兰理2026复用。</v>
+      </c>
+      <c r="F891" t="str" s="3">
+        <v>13表显示发布2018却含2021成立内容，不能当2026最新全校目录；新能源合作基地和机械/航空其他学院、全国平台仍有未查年度。</v>
+      </c>
+      <c r="G891" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H891" t="str" s="3">
+        <v>https://zdhxy.nwpu.edu.cn/kxyj/kypt.htm
+https://zdhxy.nwpu.edu.cn/info/1050/1985.htm</v>
+      </c>
+      <c r="I891" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="892" ht="52.5" customHeight="1">
+      <c r="A892" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B892" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C892" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D892" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E892" t="str" s="3">
+        <v>省教育厅重点实验室目录首次可访问仅标题30/94等占位，无平台名单，明确转人工而非完成目录。</v>
+      </c>
+      <c r="F892" t="str" s="3">
+        <v>实际省高校平台完整名称、官网入口及2026—2027机器人相关公告未取得；旧国家/学院资料仍保留。</v>
+      </c>
+      <c r="G892" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H892" t="str" s="3">
+        <v>https://www.scut.edu.cn/new/gdsjytzdsys/list.htm</v>
+      </c>
+      <c r="I892" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="893" ht="52.5" customHeight="1">
+      <c r="A893" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B893" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C893" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D893" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E893" t="str" s="3">
+        <v>光电工程学院基地平台官方目录首次412，停止并列人工。</v>
+      </c>
+      <c r="F893" t="str" s="3">
+        <v>光电目录完整及各感知/测控平台2026—2027公告、机械/自动化全校剩余范围未齐。</v>
+      </c>
+      <c r="G893" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H893" t="str" s="3">
+        <v>https://coe.cqu.edu.cn/kxyj/kypt1/jdpt.htm</v>
+      </c>
+      <c r="I893" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -47338,6 +47338,448 @@
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
+    <row r="894" ht="52.5" customHeight="1">
+      <c r="A894" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B894" t="str" s="3">
+        <v>自动化所当前全部科研机构目录补漏</v>
+      </c>
+      <c r="C894" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D894" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E894" t="str" s="3">
+        <v>查询：site:ia.cas.cn "科研部门" 实验室 / site:ia.cas.cn "研究机构" 2026 机器人 / site:ia.cas.cn "智能系统与工程" "开放" 基金 / site:ia.cas.cn "脑网络组" "开放课题" 2026 2027；线索：模式识别实验室----中国科学院自动化研究所；工业视觉智能装备技术工程实验室----中国科学院自动化研究所；脑图谱与类脑智能实验室----中国科学院自动化研究所；科研部门----中国科学院自动化研究所；紫东太初大模型研究中心----中国科学院自动化研究所；分子影像实验室----中国科学院自动化研究所</v>
+      </c>
+      <c r="F894" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G894" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H894" t="str" s="3">
+        <v>https://www.ia.cas.cn/jgsz/kyxt/ZNGZ/
+https://www.ia.cas.cn/jgsz/kyxt/gysj/
+https://ia.cas.cn/jgsz/kyxt/brain/
+https://www.ia.cas.cn/jgsz/kyxt/
+https://ia.cas.cn/jgsz/kyxt/zztc/
+https://www.ia.cas.cn/jgsz/kyxt/bm9/</v>
+      </c>
+      <c r="I894" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第404项</v>
+      </c>
+    </row>
+    <row r="895" ht="52.5" customHeight="1">
+      <c r="A895" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B895" t="str" s="3">
+        <v>科研院所装备开放基金全国补漏</v>
+      </c>
+      <c r="C895" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D895" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E895" t="str" s="3">
+        <v>查询：site:cas.cn "开放基金" 2026 "机器人" -ia.cas.cn -sia.cn / site:cas.cn "开放课题" 2027 智能控制 / site:cas.cn "开放基金" 2026 "自主" / site:cas.cn "开放基金" 2026 "感知"；线索：管理办法----机器人与智能系统全国重点实验室；多模态人工智能系统全国重点实验室2026年度开放课题申请指南----中国科学院自动化研究所；基金简介----机器人与智能系统全国重点实验室；中国科学院自动化研究所；生命过程小分子调控全国重点实验室2027年度开放课题申请指南--生命过程小分子调控全国重点实验室；江苏省工业人工智能重点实验室2026年度开放课题申请通知-- 中国科学院工业人工智能研究所</v>
+      </c>
+      <c r="F895" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G895" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H895" t="str" s="3">
+        <v>https://rlab.sia.cas.cn/kfjj/glbf/
+https://www.ia.cas.cn/qtgn/tzgg/202605/t20260515_8202627.html
+https://rlab.sia.cas.cn/kfjj/jjjj/
+https://ia.cas.cn/?W=71038
+https://sioc.cas.cn/sklcb/kfgx/kfkt/sqzn/202606/t20260630_8235628.html
+https://iaii.cas.cn/hzjl/kjhz/202607/t20260715_8248969.html</v>
+      </c>
+      <c r="I895" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第405项</v>
+      </c>
+    </row>
+    <row r="896" ht="52.5" customHeight="1">
+      <c r="A896" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B896" t="str" s="3">
+        <v>北京省部级新高校平台目录补漏</v>
+      </c>
+      <c r="C896" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D896" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E896" t="str" s="3">
+        <v>查询：site:btbu.edu.cn "开放基金" 2026 2027 智能 / site:buu.edu.cn "机器人" "重点实验室" 开放基金 / site:bipt.edu.cn "开放基金" 2026 2027 / site:biem.edu.cn "机器人" "开放课题"；线索：信息服务重点实验室 实验室简介；机器人学院北京市信息服务工程重点实验室举行北京市重点科技项目开题会；北京联合大学机器人学院（人工智能学院）作为共建单位成功获批北京市重点实验室；机器人学院北京市信息服务工程重点实验室承办中文信息学会计算语言学术沙龙</v>
+      </c>
+      <c r="F896" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G896" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H896" t="str" s="3">
+        <v>https://isekeylab.buu.edu.cn/col/col23614/index.html
+https://jqr.buu.edu.cn/art/2022/6/9/art_39336_783239.html
+https://jqr.buu.edu.cn/art/2025/4/15/art_39334_807433.html
+https://jqr.buu.edu.cn/art/2023/11/1/art_39297_782548.html</v>
+      </c>
+      <c r="I896" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第406项</v>
+      </c>
+    </row>
+    <row r="897" ht="52.5" customHeight="1">
+      <c r="A897" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B897" t="str" s="3">
+        <v>自动化所九科研部门发现名单逐名机制</v>
+      </c>
+      <c r="C897" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D897" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E897" t="str" s="3">
+        <v>查询：site:ia.cas.cn "工业视觉智能装备" "开放" 基金 / site:ia.cas.cn "分子影像实验室" "开放基金" 2026 2027 / site:ia.cas.cn "脑图谱与类脑智能" "开放课题" / site:ia.cas.cn "紫东太初" "开放" 基金；线索：崔海楠----中国科学院自动化研究所；紫东太初大模型开放服务平台2.0正式发布----中国科学院自动化研究所；中国科学院自动化研究所；中国科学院自动化研究所；中国光谷·多模态人工智能大会暨多模态人工智能产业联合体第三次全体会议成功召开----中国科学院自动化研究所；紫东太初大模型研究中心----中国科学院自动化研究所</v>
+      </c>
+      <c r="F897" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G897" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H897" t="str" s="3">
+        <v>https://ia.cas.cn/rcdw/fyjy/202404/t20240422_7130934.html
+https://ia.cas.cn/xwzx/cgzh/202308/t20230811_6858825.html
+https://www.ia.cas.cn/
+https://www.ia.cas.cn/?keyword=%E4%B8%AD%E5%9B%BD%E7%A7%91%E5%AD%A6%E9%99%A2%E5%A4%A7%E5%AD%A6%E8%87%AA%E5%8A%A8%E5%8C%96%E6%89%80
+https://ia.cas.cn/xwzx/cgzh/202311/t20231107_6916037.html
+https://ia.cas.cn/jgsz/kyxt/zztc/</v>
+      </c>
+      <c r="I897" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第407项</v>
+      </c>
+    </row>
+    <row r="898" ht="52.5" customHeight="1">
+      <c r="A898" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B898" t="str" s="3">
+        <v>北京联大2026-09简介五科研平台机制</v>
+      </c>
+      <c r="C898" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D898" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E898" t="str" s="3">
+        <v>查询："北京市信息服务工程重点实验室" "开放" 课题 2026 2027 / "北京市智能机械创新设计服务" "开放基金" / "多模态超级智能安全" "开放课题" / "车路协同自动驾驶北京工程研究中心" "开放" 基金；线索：我校首次承担的国家自然科学基金重大研究计划重点支持项目顺利通过结题验收</v>
+      </c>
+      <c r="F898" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G898" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H898" t="str" s="3">
+        <v>https://www.lzxjsl.com/html/art2018626art_13583_522466.html</v>
+      </c>
+      <c r="I898" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第408项</v>
+      </c>
+    </row>
+    <row r="899" ht="52.5" customHeight="1">
+      <c r="A899" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B899" t="str" s="3">
+        <v>北京联大脑认知及省属基金补漏</v>
+      </c>
+      <c r="C899" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D899" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E899" t="str" s="3">
+        <v>查询："脑与认知智能北京实验室" "开放基金" / site:buu.edu.cn "开放课题" 2026 2027 / site:btbu.edu.cn 科研平台 机器人 重点实验室 / site:bipt.edu.cn 科研平台 机器人 重点实验室；线索：北京工商大学科学研究院；学校现有代表性协同创新大平台四个：中关村；北京工商大学科学研究院；北京工商大学科学研究院；北石化人工智能研究院-学工动态</v>
+      </c>
+      <c r="F899" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G899" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H899" t="str" s="3">
+        <v>https://kyy.btbu.edu.cn/tzgg/105230.htm
+https://www.bipt.edu.cn/docs/2024-06/8d105ac3e90f47cc9e221a5e9779a1a8.pdf
+https://kyc.btbu.edu.cn/xwdt/7c92a24bfe654eb5a43355f5a851acea.htm
+https://kyy.btbu.edu.cn/tzgg/ce581bb029684e4c99d8911105c24e25.htm
+https://www.bipt.edu.cn/pub/ai/xwdt/xgdt/514eb2292ee746419b54f26bccaa105f.html</v>
+      </c>
+      <c r="I899" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第409项</v>
+      </c>
+    </row>
+    <row r="900" ht="52.5" customHeight="1">
+      <c r="A900" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B900" t="str" s="3">
+        <v>江西省属高校机器人平台补漏</v>
+      </c>
+      <c r="C900" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D900" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E900" t="str" s="3">
+        <v>查询：site:ecjtu.edu.cn "开放课题" 2026 2027 机器人 / site:jxust.edu.cn "开放基金" 2026 2027 / site:jxnu.edu.cn "开放课题" 2026 2027 / site:jxut.edu.cn "开放基金" 2026 2027 机器人；线索：交通智能运维技术与装备教育部重点实验室2026年度开放课题申请指南-华东交通大学机电与车辆工程学院网站；氟硅能源材料与化学教育部重点实验室（江西师范大学）2026年度开放课题基金申请通知；关于公布交通智能运维技术与装备教育部重点实验室2025年度开放课题评审结果的通知-交通智能运维技术与装备教育部重点实验室；交通智能运维技术与装备教育部重点实验室 2026 年度学术委员会会议顺利召开-交通智能运维技术与装备教育部重点实验室；山区土木工程安全与韧性全国重点实验室开放课题管理办法-山区土木工程安全与韧性全国重点实验室；山区土木工程安全与韧性全国重点实验室 2026年度开放基金申请指南-山区土木工程安全与韧性全国重点实验室</v>
+      </c>
+      <c r="F900" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G900" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H900" t="str" s="3">
+        <v>https://me.ecjtu.edu.cn/info/1156/5774.htm
+https://iasr.jxnu.edu.cn/2026/0701/c13498a295940/page.htm
+https://tiom.ecjtu.edu.cn/info/1047/3632.htm
+https://tiom.ecjtu.edu.cn/info/1047/3662.htm
+https://sqtmqz.ecjtu.edu.cn/info/1030/3801.htm
+https://sqtmqz.ecjtu.edu.cn/info/1031/3831.htm</v>
+      </c>
+      <c r="I900" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第410项</v>
+      </c>
+    </row>
+    <row r="901" ht="52.5" customHeight="1">
+      <c r="A901" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B901" t="str" s="3">
+        <v>福建省属机器人平台年度补漏</v>
+      </c>
+      <c r="C901" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D901" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E901" t="str" s="3">
+        <v>查询：site:jmu.edu.cn "开放基金" 2026 2027 机器人 / site:fafu.edu.cn "开放课题" 2026 2027 智能 / site:fjnu.edu.cn "开放基金" 2026 2027 机器人 / site:hqu.edu.cn "开放基金" 2026 2027 控制；线索：国家甘蔗工程技术研究中心</v>
+      </c>
+      <c r="F901" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G901" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H901" t="str" s="3">
+        <v>https://teacher.fafu.edu.cn/zxw/</v>
+      </c>
+      <c r="I901" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第411项</v>
+      </c>
+    </row>
+    <row r="902" ht="52.5" customHeight="1">
+      <c r="A902" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B902" t="str" s="3">
+        <v>湖南省属新智能装备机制补漏</v>
+      </c>
+      <c r="C902" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D902" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E902" t="str" s="3">
+        <v>查询：site:hnu.edu.cn "开放基金" 2027 机器人 / site:hnust.edu.cn "开放基金" 2026 2027 机器人 / site:csust.edu.cn "开放课题" 2026 2027 智能 / site:usc.edu.cn "开放基金" 2026 2027 机器人；线索：关于组织新进博士申报2026年上半年科研平台自由探索类开放基金项目的通知-长沙理工大学-科学技术处；高等学校重点实验室建设与管理暂行办法-长沙理工大学-科学技术处；关于2026年度湖南省普通高等学校（南华大学）环境健康与风险防控重点实验室开放基金项目申报的通知-南华大学-公共卫生学院；湖南省大学生研究性学习和创新性实；嵌入式与网络计算湖南省重点实验室</v>
+      </c>
+      <c r="F902" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G902" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H902" t="str" s="3">
+        <v>https://www.csust.edu.cn/kxyjb/info/1031/8608.htm
+https://www.csust.edu.cn/kxyjb/info/1115/5072.htm
+https://gwxy.usc.edu.cn/info/1051/7300.htm
+https://www.csust.edu.cn/__local/9/5B/29/9C3681AE421BBFE8A0F2301F348_24FA9A70_8CB9D.pdf?e=.pdf
+https://esnl.hnu.edu.cn/kfktjjgltl.pdf</v>
+      </c>
+      <c r="I902" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第412项</v>
+      </c>
+    </row>
+    <row r="903" ht="52.5" customHeight="1">
+      <c r="A903" t="str" s="3">
+        <v>2026-10-09北京与院所及闽赣湘年度补漏</v>
+      </c>
+      <c r="B903" t="str" s="3">
+        <v>北京石化机器人省室及自设感知平台机制</v>
+      </c>
+      <c r="C903" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D903" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E903" t="str" s="3">
+        <v>查询："光机电装备技术北京市重点实验室" "开放基金" 2026 2027 / "光机电装备技术" "开放课题" / "安全生产智能感知与大数据技术研究所" "开放基金" / site:bipt.edu.cn "开放课题" 2026 2027；线索：关于印发《北京市重点实验室认定与管理暂行办法》；实验室名称:特种弹性体复合材料北京市重点实；中国科学院合肥物质科学研究院；清华大学大型仪器共享服务平台</v>
+      </c>
+      <c r="F903" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G903" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H903" t="str" s="3">
+        <v>https://www.bipt.edu.cn/publish/kjc/docs/20200407135741445746.pdf
+https://www.bipt.edu.cn/pub/secm/docs/2017-09/20170907143325386423.pdf
+https://www.hf.cas.cn/hzjl/ydhz/hzxm/201402/t20140213_4032258.html
+https://yqgx.tsinghua.edu.cn/webSite/websiteAction.do?ms=toLabList</v>
+      </c>
+      <c r="I903" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第413项</v>
+      </c>
+    </row>
+    <row r="904" ht="52.5" customHeight="1">
+      <c r="A904" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B904" t="str" s="3">
+        <v>中国科学院自动化研究所</v>
+      </c>
+      <c r="C904" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D904" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E904" t="str" s="3">
+        <v>科研部门全目录首超时；官方搜索发现9科研部门页但非完整现行名单，工业视觉/分子影像/脑图谱/紫东太初逐名2026—2027基金查；多模态2026及江苏工业AI M073复用。</v>
+      </c>
+      <c r="F904" t="str" s="3">
+        <v>完整部门名单/改名关系未取，搜索又发现复杂系统认知与决策，不能算9个全部已查；大模型开放服务非科研资金。</v>
+      </c>
+      <c r="G904" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H904" t="str" s="3">
+        <v>https://www.ia.cas.cn/jgsz/kyxt/</v>
+      </c>
+      <c r="I904" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="905" ht="52.5" customHeight="1">
+      <c r="A905" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B905" t="str" s="3">
+        <v>北京联合大学</v>
+      </c>
+      <c r="C905" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D905" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E905" t="str" s="3">
+        <v>机器人AI学院截至2026-09简介全文，5省部科研平台逐名机制2026—2027/历史查；48教学实验室非48资金平台；所谓2023搜索入口实际教师简介，非基金公告；信息服务开放目录首超时。</v>
+      </c>
+      <c r="F905" t="str" s="3">
+        <v>信息服务正式年度与其他4平台规则未取；学院列表不是全校科研机构完整目录，无额外正式资助标题不编项目。</v>
+      </c>
+      <c r="G905" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H905" t="str" s="3">
+        <v>https://jqr.buu.edu.cn/col/col39301/index.html
+https://isekeylab.buu.edu.cn/col/col23453/index.html</v>
+      </c>
+      <c r="I905" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="906" ht="52.5" customHeight="1">
+      <c r="A906" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B906" t="str" s="3">
+        <v>北京石油化工学院</v>
+      </c>
+      <c r="C906" t="str" s="3">
+        <v>北京</v>
+      </c>
+      <c r="D906" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E906" t="str" s="3">
+        <v>官方g jd路径实际光机电装备北京市重点室单介绍：核电/建筑/水下/服务机器人明确；AI学院2026-08安全感知研究所校级单介绍；2平台2026—2027/历史机制查。</v>
+      </c>
+      <c r="F906" t="str" s="3">
+        <v>不是全校国家级或AI省部目录，校级实验室不遗漏但无正式基金证据不入项目；全校剩余名单未齐。</v>
+      </c>
+      <c r="G906" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H906" t="str" s="3">
+        <v>https://www.bipt.edu.cn/xkky/kypt/gjd.htm
+https://www.bipt.edu.cn/pub/sai/xkky/kypt/d81f19a5d94e4e03a38c22442fc58998.htm</v>
+      </c>
+      <c r="I906" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="907" ht="52.5" customHeight="1">
+      <c r="A907" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B907" t="str" s="3">
+        <v>长沙理工/闽赣湘跨省对账</v>
+      </c>
+      <c r="C907" t="str" s="3">
+        <v>湖南/福建/江西</v>
+      </c>
+      <c r="D907" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E907" t="str" s="3">
+        <v>2026上半年自由探索新进教师基金全文，本校教师身份成果/学院内部汇总且无校外负责人开放依据E085排除；闽赣湘12词补漏M048/M189同2026对账复用不重开。</v>
+      </c>
+      <c r="F907" t="str" s="3">
+        <v>各校平台目录未齐，仅本批教师扶持资格排除，不把长沙理工其他实验室对外基金排除；省认定目录仍未全。</v>
+      </c>
+      <c r="G907" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H907" t="str" s="3">
+        <v>https://www.csust.edu.cn/kxyjb/info/1031/8608.htm</v>
+      </c>
+      <c r="I907" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -19306,6 +19306,340 @@
         <v>旧年度开放线索，未取得具体任务；省/部同学院平台不共享资助条款。</v>
       </c>
     </row>
+    <row r="215" ht="132" customHeight="1">
+      <c r="A215" t="str" s="3">
+        <v>N066</v>
+      </c>
+      <c r="B215" t="str" s="3">
+        <v>2025正式指南完整正文已取得；申请DOCX首次工具不支持</v>
+      </c>
+      <c r="C215" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="D215" t="str" s="3">
+        <v>大气光电探测与信息融合国家级重点实验室培育建设点</v>
+      </c>
+      <c r="E215" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F215" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G215" t="n" s="6">
+        <v>45942</v>
+      </c>
+      <c r="H215" t="str" s="3">
+        <v>具体时点未载</v>
+      </c>
+      <c r="I215" t="str" s="3">
+        <v>年度仅列大气光学与大气辐射、大气光电探测技术与系统、智能光谱信息处理、光通信与信息融合四个概括方向。尚缺机器人或相关智能装备的具体任务证据，不凭智能/融合收为确定相关。</v>
+      </c>
+      <c r="J215" t="str" s="3">
+        <v>1—3万元/项，拟5—8项。</v>
+      </c>
+      <c r="K215" t="str" s="3">
+        <v>实验室固定人员以外的国内外业务技术人员和研究人员；博士学位或高级技术职称。年龄与限项正文未载。</v>
+      </c>
+      <c r="L215" t="str" s="3">
+        <v>校外申请人必须依托本室固定人员合作申报；同校非固定人员是否适用强制合作条款需确认，访问未载。</v>
+      </c>
+      <c r="M215" t="str" s="3">
+        <v>经费不外拨；主要用于课题相关材料费、测试费、资料复印费、会议费和差旅费。报销具体地点流程/劳务费支持未载。</v>
+      </c>
+      <c r="N215" t="str" s="3">
+        <v>1—2年；统一起止未载。</v>
+      </c>
+      <c r="O215" t="str" s="3">
+        <v>公开完整指南未载论文/专利数量、第一单位或作者、验收要求；申请表待取。</v>
+      </c>
+      <c r="P215" t="str" s="3">
+        <v>公开完整指南未载。</v>
+      </c>
+      <c r="Q215" t="str" s="3">
+        <v>单位同意签字盖章；签章页扫描插入电子申请文档，截止前发002402@nuist.edu.cn。获批后申请书随合同邮寄实验室，非申请前必须邮寄。批准后10工作日内通知手续。</v>
+      </c>
+      <c r="R215" t="str" s="3">
+        <v>本人博士/南信现职已知，是否属本室固定人员、限项及实际合作未核；历史窗口已过、任务证据不足。</v>
+      </c>
+      <c r="S215" t="str" s="3">
+        <v>申请DOCX首次不支持交人工；补具体装备任务、成果IP报销办法。同校非固定人员合作要求须核。未取得2026—2027新公告不表示不存在。</v>
+      </c>
+      <c r="T215" t="str" s="3">
+        <v>https://wdy.nuist.edu.cn/2025/0916/c2983a290115/pagem.htm</v>
+      </c>
+      <c r="U215" t="str" s="3">
+        <v>https://wdy.nuist.edu.cn/_upload/article/files/d7/3b/a78769914462914646dfdce79ced/04ebc495-12ca-4c62-bc86-e4804477787b.docx</v>
+      </c>
+      <c r="V215" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W215" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X215" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y215" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="Z215" t="str" s="3">
+        <v>刘丹025-58235587；002402@nuist.edu.cn；南京宁六路219号物理与光电工程学院210044。申请段邮箱有空格，联系段明确无空格。</v>
+      </c>
+      <c r="AA215" t="str" s="3">
+        <v>2025独立历史待核；webs镜像同公告，合并不计新项目。</v>
+      </c>
+    </row>
+    <row r="216" ht="192" customHeight="1">
+      <c r="A216" t="str" s="3">
+        <v>N067</v>
+      </c>
+      <c r="B216" t="str" s="3">
+        <v>2025正式指南完整正文已取得；3份申请/推荐DOCX首次不支持</v>
+      </c>
+      <c r="C216" t="str" s="3">
+        <v>福建理工大学</v>
+      </c>
+      <c r="D216" t="str" s="3">
+        <v>海洋智能装备福建省高校重点实验室</v>
+      </c>
+      <c r="E216" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F216" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G216" t="n" s="6">
+        <v>45853</v>
+      </c>
+      <c r="H216" t="str" s="3">
+        <v>具体时点未载；逾期不受理</v>
+      </c>
+      <c r="I216" t="str" s="3">
+        <v>水下图像退化/复原/小样本目标识别与实时嵌入部署；水下惯性水声地磁导航与卫星多源定位融合；水下光声模态差异图像融合；无人船/水下机器人集群编队动力学任务分配控制；装备运动学仿真与实虚协同；小型水下机器人传感集成自主控制与样机；结构水动力测试；智能测绘装备传感协同及集成验证。年度还含水声通信、水下机器人材料、鱼数量统计、海洋装备数据处理，应用背景原样保留。</v>
+      </c>
+      <c r="J216" t="str" s="3">
+        <v>每项不超过2万元，以正式批复为准。</v>
+      </c>
+      <c r="K216" t="str" s="3">
+        <v>校内外有科研经历、高级职称或博士的科研人员；在读博士须导师推荐，否则2名同领域正高推荐。单位同意且承诺按纵向经费管理；学历/职称证明。年龄、限项正文未载。</v>
+      </c>
+      <c r="L216" t="str" s="3">
+        <v>项目组应含至少1名实验室教师；访问时长正文未载。</v>
+      </c>
+      <c r="M216" t="str" s="3">
+        <v>按福工大科研〔2024〕14号平台开放基金办法；原则不购仪器等固定资产、不设间接经费，上级另规从之。正文直接费用列设备费、业务费、劳务费；设备费与不购固定资产范围需办法核，不擅自改为无设备费。外拨/报销地点/支付节点未载。</v>
+      </c>
+      <c r="N216" t="str" s="3">
+        <v>原则不超过2年；立项第12个月交中期报告；不合理用款/滞后可中止或收回。原则不延期，不可抗力提前3个月申请，可1次≤1年；逾期半年未结或验收不过撤项。结题余款可再用2年。</v>
+      </c>
+      <c r="O216" t="str" s="3">
+        <v>原则≥1篇以本室为第一署名单位的SCI或EI期刊论文；非EI会议替代。成果标实验室指定中英文来源、项目名称及批准号。到期前1个月申请验收：申请3份、技术报告和成果证明装订3份。作者排序正文未载。</v>
+      </c>
+      <c r="P216" t="str" s="3">
+        <v>公开完整指南未载；管理办法及合同待取。</v>
+      </c>
+      <c r="Q216" t="str" s="3">
+        <v>申请表、必要时导师/专家推荐、博士或职称证明；单位主管签字盖章纸件3份寄送，同时含签章扫描电子版发ZhouPD@fjut.edu.cn，2025-07-15截止。</v>
+      </c>
+      <c r="R216" t="str" s="3">
+        <v>本人博士/高校现职对应学历类别；单位经费管理承诺、固定教师合作及限项尚未核，历史参考。</v>
+      </c>
+      <c r="S216" t="str" s="3">
+        <v>3个DOCX首次工具不支持；需福工大科研〔2024〕14号办法、合同补IP/外拨/报销与支付及设备开支范围；2026—2027新批未定位，不声明无。</v>
+      </c>
+      <c r="T216" t="str" s="3">
+        <v>https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm</v>
+      </c>
+      <c r="U216" t="str" s="3">
+        <v>https://hyy.fjut.edu.cn/_upload/article/files/15/f8/616d9ddd4ed5bfba493285fd8e64/c5ae681d-4957-4f8d-8c86-2c44aeda189d.docx
+https://hyy.fjut.edu.cn/_upload/article/files/15/f8/616d9ddd4ed5bfba493285fd8e64/cae13612-d973-47f3-960a-4bb5099b9bc6.docx
+https://hyy.fjut.edu.cn/_upload/article/files/15/f8/616d9ddd4ed5bfba493285fd8e64/11bf6763-ed19-4179-9276-dc7594edaa16.docx</v>
+      </c>
+      <c r="V216" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W216" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X216" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y216" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="Z216" t="str" s="3">
+        <v>周老师15005997434；ZhouPD@fjut.edu.cn；福州闽侯上街学府南路69号旗山南区新技术研究楼3024，350118。</v>
+      </c>
+      <c r="AA216" t="str" s="3">
+        <v>2025独立年度，省高校重点室2023批准；非福建其他海洋平台同年度。</v>
+      </c>
+    </row>
+    <row r="217" ht="132" customHeight="1">
+      <c r="A217" t="str" s="3">
+        <v>N068</v>
+      </c>
+      <c r="B217" t="str" s="3">
+        <v>官方搜索发现2019正式开放课题标题；正文首次超时停止</v>
+      </c>
+      <c r="C217" t="str" s="3">
+        <v>福建农林大学</v>
+      </c>
+      <c r="D217" t="str" s="3">
+        <v>智慧农林福建省高校重点实验室</v>
+      </c>
+      <c r="E217" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F217" t="str" s="3">
+        <v>2019</v>
+      </c>
+      <c r="G217" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H217" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I217" t="str" s="3">
+        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+      </c>
+      <c r="J217" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K217" t="str" s="3">
+        <v>2019校外资格/限项未取得。</v>
+      </c>
+      <c r="L217" t="str" s="3">
+        <v>合作访问未取得。</v>
+      </c>
+      <c r="M217" t="str" s="3">
+        <v>外拨、费用、报销、支付均未取得。</v>
+      </c>
+      <c r="N217" t="str" s="3">
+        <v>2019周期未取得。</v>
+      </c>
+      <c r="O217" t="str" s="3">
+        <v>数量/第一单位/作者/验收未取得。</v>
+      </c>
+      <c r="P217" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="Q217" t="str" s="3">
+        <v>2019截止和提交未取得。</v>
+      </c>
+      <c r="R217" t="str" s="3">
+        <v>本人博士现职已知；旧公告资料不足待核，不进当前页。</v>
+      </c>
+      <c r="S217" t="str" s="3">
+        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+      </c>
+      <c r="T217" t="str" s="3">
+        <v>https://www.fafu.edu.cn/2019/0721/c136a46120/pagem.htm</v>
+      </c>
+      <c r="U217" t="str" s="3">
+        <v>正文首次失败，附件直链未取得。</v>
+      </c>
+      <c r="V217" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W217" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X217" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y217" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="Z217" t="str" s="3">
+        <v>年度基金联系人未取得。</v>
+      </c>
+      <c r="AA217" t="str" s="3">
+        <v>2019独立历史线索；2026—2027机制查未定位新正式指南。</v>
+      </c>
+    </row>
+    <row r="218" ht="132" customHeight="1">
+      <c r="A218" t="str" s="3">
+        <v>N069</v>
+      </c>
+      <c r="B218" t="str" s="3">
+        <v>2025正式指南完整正文已取得；申请DOCX下载页首次显示验证码</v>
+      </c>
+      <c r="C218" t="str" s="3">
+        <v>昆明理工大学</v>
+      </c>
+      <c r="D218" t="str" s="3">
+        <v>云南省低空经济和无人机技术创新中心（筹）</v>
+      </c>
+      <c r="E218" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F218" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G218" t="n" s="6">
+        <v>45919</v>
+      </c>
+      <c r="H218" t="str" s="3">
+        <v>正文要求“2025年9月19日之前”，是否含当日及小时未明确；已过窗口。</v>
+      </c>
+      <c r="I218" t="str" s="3">
+        <v>高原复杂环境无人机电路可靠性、轻量低功耗飞控/抗干扰传感接口；氢能垂起固定翼无人机气动动力耦合与轻量储供；长航时BMS SOC/SOH估计均衡热管理；无人机智能感知自主避障、协同集群控制、脑机/类脑人机交互实时控制算法。电池材料研究不据智能标题扩展通用材料项目。</v>
+      </c>
+      <c r="J218" t="str" s="3">
+        <v>重点10万元，拟2—3项；一般5万元，拟1—2项。</v>
+      </c>
+      <c r="K218" t="str" s="3">
+        <v>中心固定成员外国内外高校/科研机构/企业科技人员；博士或高级职称，单位同意；年龄/限项正文未载。</v>
+      </c>
+      <c r="L218" t="str" s="3">
+        <v>主要支持与中心人员科研合作的研究者，正文未给强制固定人员数量；访问未载，不能改写至少1固定。</v>
+      </c>
+      <c r="M218" t="str" s="3">
+        <v>专款专用；外拨、开支科目、报销地点比例及支付节点正文未载。</v>
+      </c>
+      <c r="N218" t="str" s="3">
+        <v>2年，统一起止未载；不定期检查，不执行计划可终止。</v>
+      </c>
+      <c r="O218" t="str" s="3">
+        <v>重点：中心为第一作者署名单位或通讯作者署名单位，≥2篇SCI/EI检索论文，或授权相关发明2项，或原理样机（电路板等）2套，或相关缩比原理样机1套。一般：同样署名，≥1篇SCI/EI检索期刊论文且申请相关发明≥1项（是且非或）。预警期刊不计。完成后2个月交报告/总结及成果证明；标中心中英文名称及致谢基金。</v>
+      </c>
+      <c r="P218" t="str" s="3">
+        <v>成果由实验室和研究人员所属单位共享；收益/转让细则正文未载。</v>
+      </c>
+      <c r="Q218" t="str" s="3">
+        <v>单位同意，2025-09-19之前申请2份、电子发yxm1434@163.com；获批后寄任务合同4份。申请签章/邮寄细节待申请表；官网联系段邮箱插空格，申报段无空格。</v>
+      </c>
+      <c r="R218" t="str" s="3">
+        <v>本人博士现职已知；合作、限项及申请签章细则未核，已截止历史参考。</v>
+      </c>
+      <c r="S218" t="str" s="3">
+        <v>验证码申请DOCX人工下载；补外拨报销支付/合同、普通项目论文+申请专利规则及截止是否含当日。2026—2027新公告未定位不代表不存在。</v>
+      </c>
+      <c r="T218" t="str" s="3">
+        <v>https://mhhk.kmust.edu.cn/info/1019/4253.htm</v>
+      </c>
+      <c r="U218" t="str" s="3">
+        <v>https://mhhk.kmust.edu.cn/system/_content/download.jsp?owner=1545230061&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=16633046</v>
+      </c>
+      <c r="V218" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W218" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X218" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y218" t="str" s="3">
+        <v>云南·昆明</v>
+      </c>
+      <c r="Z218" t="str" s="3">
+        <v>杨老师151-9886-9097；yxm1434@163.com；昆明理工大学公教楼127室650500（网页地址“1 27”）；具体递交地址待表核。</v>
+      </c>
+      <c r="AA218" t="str" s="3">
+        <v>2025独立历史；不能套云南复杂系统类脑2026已排除项目。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -19740,6 +20074,10 @@
     <hyperlink ref="T212" ns1:id="rIdResume434"/>
     <hyperlink ref="T213" ns1:id="rIdResume435"/>
     <hyperlink ref="T214" ns1:id="rIdResume436"/>
+    <hyperlink ref="T215" ns1:id="rIdResume437"/>
+    <hyperlink ref="T216" ns1:id="rIdResume438"/>
+    <hyperlink ref="T217" ns1:id="rIdResume439"/>
+    <hyperlink ref="T218" ns1:id="rIdResume440"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -47777,6 +48115,835 @@
         <v>https://www.csust.edu.cn/kxyjb/info/1031/8608.htm</v>
       </c>
       <c r="I907" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="908" ht="52.5" customHeight="1">
+      <c r="A908" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B908" t="str" s="3">
+        <v>南京省属与院所遗漏目录补漏</v>
+      </c>
+      <c r="C908" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D908" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E908" t="str" s="3">
+        <v>查询：site:nuist.edu.cn 机器人 科研平台 重点实验室 开放 / site:njtech.edu.cn "机器人" "开放基金" 2026 2027 / site:issas.ac.cn "开放课题" 2026 2027 / site:ioe.ac.cn "开放基金" 2026 智能；线索：南京信息工程大学主页平台管理系统 Zhou Wendong--Home--Home；南京信息工程大学主页平台管理系统 Zhou Wendong--Home--Home；南京信息工程大学主页平台管理系统 周文东--中文主页--首页；南京信息工程大学主页平台管理系统 项升--中文主页--首页；2026年水利部水文气象灾害机理与预警重点实验室开放基金申报指南；自动化学院举办科研实验室开放日活动</v>
+      </c>
+      <c r="F908" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G908" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H908" t="str" s="3">
+        <v>https://faculty.nuist.edu.cn/zhouwendong/en/index.htm
+https://faculty.nuist.edu.cn/zhouwendong/en/more/117257/jsjjgd/index.htm
+https://faculty.nuist.edu.cn/zhouwendong/zh_CN/index/117241/list/index.htm
+https://faculty.nuist.edu.cn/xiangsheng/zh_CN/index/123629/list/index.htm
+https://hymed.nuist.edu.cn/2026/0809/c8032a300578/page.htm
+https://auto.nuist.edu.cn/2020/0628/c313a160147/pagem.psp</v>
+      </c>
+      <c r="I908" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第414项</v>
+      </c>
+    </row>
+    <row r="909" ht="52.5" customHeight="1">
+      <c r="A909" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B909" t="str" s="3">
+        <v>北方省属机器人开放机制目录交叉补漏</v>
+      </c>
+      <c r="C909" t="str" s="3">
+        <v>天津河北山西</v>
+      </c>
+      <c r="D909" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E909" t="str" s="3">
+        <v>查询：site:tjpu.edu.cn "开放基金" 2026 2027 智能 / site:tjlg.edu.cn "开放课题" 2026 2027 / site:hebust.edu.cn "开放基金" 2026 2027 / site:tyust.edu.cn "开放课题" 2026 2027；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F909" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G909" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H909" t="str" s="3"/>
+      <c r="I909" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第415项</v>
+      </c>
+    </row>
+    <row r="910" ht="52.5" customHeight="1">
+      <c r="A910" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B910" t="str" s="3">
+        <v>江苏周边省高校机器人平台新目录补漏</v>
+      </c>
+      <c r="C910" t="str" s="3">
+        <v>江苏·苏州无锡常州镇江扬州</v>
+      </c>
+      <c r="D910" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E910" t="str" s="3">
+        <v>查询：site:usts.edu.cn 机器人 科研平台 重点实验室 / site:wuxiu.edu.cn "开放基金" 2026 2027 / site:yznu.edu.cn "开放基金" 2026 2027 / site:jsu.edu.cn "开放课题" "2027" 机器人；线索：科研平台-电子与信息工程学院；喜报！江苏省智能生物制造重点实验室（筹）获批 我院科研平台建设实现历史性突破-苏州科技大学化学与生命科学学院；关于组织申报2025年度苏州市重点实验室建设项目的通知-科技产业处；机械工程学院与企业共同建立STEAM创新实验室-苏州科技大学校园文化精品名录库；关于组织申报2025年度苏州市成果转化平台建设项目的通知-科技产业处</v>
+      </c>
+      <c r="F910" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G910" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H910" t="str" s="3">
+        <v>https://eie.usts.edu.cn/xygk/kypin.htm
+https://scls.usts.edu.cn/info/1042/4796.htm
+https://kjcyc.usts.edu.cn/info/1046/5273.htm
+https://www.usts.edu.cn/xywh/info/1043/1189.htm
+https://kjcyc.usts.edu.cn/info/1046/5245.htm</v>
+      </c>
+      <c r="I910" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第416项</v>
+      </c>
+    </row>
+    <row r="911" ht="52.5" customHeight="1">
+      <c r="A911" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B911" t="str" s="3">
+        <v>苏州科技大学省市机器人及装备平台</v>
+      </c>
+      <c r="C911" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D911" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E911" t="str" s="3">
+        <v>查询：site:usts.edu.cn ("共融机器人" OR "精密铜管" OR "现代测绘仪器") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:usts.edu.cn ("虚拟显示智能交互" OR "精密与高效加工" OR "空间信息智能") ("开放基金" OR "开放课题") / site:usts.edu.cn ("工业智能低碳" OR "光学精密测试" OR "移动网络") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F911" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G911" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H911" t="str" s="3"/>
+      <c r="I911" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第417项</v>
+      </c>
+    </row>
+    <row r="912" ht="52.5" customHeight="1">
+      <c r="A912" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B912" t="str" s="3">
+        <v>南京信息工程大学省部感知及装备平台</v>
+      </c>
+      <c r="C912" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D912" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E912" t="str" s="3">
+        <v>查询：site:nuist.edu.cn ("环境物联" OR "大气环境" OR "气象能源") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:nuist.edu.cn ("大数据分析" OR "智能医学图像" OR "智能网络") ("开放基金" OR "开放课题") / site:nuist.edu.cn ("气象探测与信息处理" OR "大气光电") ("开放基金" OR "开放课题") (2026 OR 2027)；线索：大气光电探测与信息融合国家级重点实验室培育建设点开放基金课题申请指南；南京信息工程大学主页平台管理系统 汪俊峰--中文主页--首页；南京信息工程大学主页平台管理系统 方巍--中文主页--首页；南京信息工程大学主页平台管理系统 杨元建--中文主页--首页；南京信息工程大学主页平台管理系统 饶建--中文主页--首页；南京信息工程大学主页平台管理系统 智协飞--中文主页--首页</v>
+      </c>
+      <c r="F912" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G912" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H912" t="str" s="3">
+        <v>https://webs.nuist.edu.cn/_s72/2025/0916/c2983a290115/page.psp
+https://faculty.nuist.edu.cn/wangjunfengnuist/zh_CN/index.htm
+https://faculty.nuist.edu.cn/fangwei/zh_CN/index.htm
+https://faculty.nuist.edu.cn/yangyuanjian/zh_CN/
+https://faculty.nuist.edu.cn/raojian/zh_CN/index.htm
+https://faculty.nuist.edu.cn/zhixiefei/zh_CN/index.htm</v>
+      </c>
+      <c r="I912" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第418项</v>
+      </c>
+    </row>
+    <row r="913" ht="52.5" customHeight="1">
+      <c r="A913" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B913" t="str" s="3">
+        <v>无锡学院及扬州大学机器人省高校平台</v>
+      </c>
+      <c r="C913" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D913" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E913" t="str" s="3">
+        <v>查询：site:cwxu.edu.cn ("开放基金" OR "开放课题") 机器人 / site:yzu.edu.cn ("机器人" OR "智能装备" OR "机器视觉") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:yzu.edu.cn 科研平台 省部级 实验室 智能；线索：关于中国气象局生态系统碳源汇重点开放实验室2024年度开放课题申请指南-无锡学院大气与遥感学院；关于转发南信大数字取证教育部工程研究中心开放课题（第一期）申报工作的通知-无锡学院科学技术处、社会科学处；江苏省级生物科学与技术虚拟仿真实验教学共享平台；江苏省级生物科学与技术虚拟仿真实验教学共享平台；校级虚拟仿真实验管理平台；公开 – 转座子实验室</v>
+      </c>
+      <c r="F913" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G913" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H913" t="str" s="3">
+        <v>https://dqy.cwxu.edu.cn/info/1168/3166.htm
+https://kjc.cwxu.edu.cn/info/1058/2272.htm
+https://bio.yzu.edu.cn/Main/Show
+https://bio.yzu.edu.cn/
+https://xnfzgxpt.yzu.edu.cn/project/list
+https://tnlab.yzu.edu.cn/category/uncategorized</v>
+      </c>
+      <c r="I913" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第419项</v>
+      </c>
+    </row>
+    <row r="914" ht="52.5" customHeight="1">
+      <c r="A914" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B914" t="str" s="3">
+        <v>天津工业天津理工河北科技太原科技省属机器人</v>
+      </c>
+      <c r="C914" t="str" s="3">
+        <v>天津/河北/山西</v>
+      </c>
+      <c r="D914" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E914" t="str" s="3">
+        <v>查询：site:tjpu.edu.cn ("机器人" OR "智能装备") ("开放基金" OR "开放课题") / site:tjut.edu.cn ("机器人" OR "智能装备") ("开放基金" OR "开放课题") / site:hebust.edu.cn ("机器人" OR "智能装备") ("开放基金" OR "开放课题") / site:tyust.edu.cn ("机器人" OR "智能装备") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F914" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G914" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H914" t="str" s="3"/>
+      <c r="I914" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第420项</v>
+      </c>
+    </row>
+    <row r="915" ht="52.5" customHeight="1">
+      <c r="A915" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B915" t="str" s="3">
+        <v>苏科市厅目录第二页控制装备补漏</v>
+      </c>
+      <c r="C915" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D915" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E915" t="str" s="3">
+        <v>查询：site:usts.edu.cn ("智能测控" OR "物联网的公共安全" OR "申龙电梯") ("开放课题" OR "开放基金") / site:usts.edu.cn ("铜管加工装备" OR "测绘仪器综合测试") ("开放课题" OR "开放基金")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F915" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G915" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H915" t="str" s="3"/>
+      <c r="I915" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第421项</v>
+      </c>
+    </row>
+    <row r="916" ht="52.5" customHeight="1">
+      <c r="A916" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B916" t="str" s="3">
+        <v>北方省属机器人科研平台目录发现</v>
+      </c>
+      <c r="C916" t="str" s="3">
+        <v>天津/河北/山西</v>
+      </c>
+      <c r="D916" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E916" t="str" s="3">
+        <v>查询：site:tjut.edu.cn 科研平台 机器人 重点实验室 / site:hebust.edu.cn 科研平台 机电 智能 / site:tyust.edu.cn 科研平台 智能 机器人 / site:tiangong.edu.cn 科研平台 控制 实验室；线索：科研平台；科研平台；天津市复杂系统控制理论及应用重点实验室-科学技术处；教学实验室；研究所介绍-计算机视觉研究所；省部共建国家重点实验室</v>
+      </c>
+      <c r="F916" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G916" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H916" t="str" s="3">
+        <v>https://ss.tiangong.edu.cn/7576/list.htm
+https://motor.tiangong.edu.cn/kypt/list.htm
+https://kjc.tjut.edu.cn/info/1053/1069.htm
+https://zdhydqgc.tiangong.edu.cn/5283/list.htm
+https://icv.tjut.edu.cn/yjsjs.htm
+https://membrane.tiangong.edu.cn/_upload/article/files/b3/a7/f2ec1e2e40bc9c60df9f2f0eeb6b/695103c7-a18d-4c8a-9c28-62241f818275.pdf</v>
+      </c>
+      <c r="I916" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第422项</v>
+      </c>
+    </row>
+    <row r="917" ht="52.5" customHeight="1">
+      <c r="A917" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B917" t="str" s="3">
+        <v>辽宁吉林省属装备控制目录发现</v>
+      </c>
+      <c r="C917" t="str" s="3">
+        <v>辽宁/吉林</v>
+      </c>
+      <c r="D917" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E917" t="str" s="3">
+        <v>查询：site:syu.edu.cn 重点实验室 开放课题 2026 / site:sut.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) / site:ccut.edu.cn ("开放课题" OR "开放基金") (控制 OR 机器人) / site:jlju.edu.cn ("开放课题" OR "开放基金") (机器人 OR 检测)；线索：实验室发布的开放课题指南选题并填写申报书，经所在单位签署意见并盖章，一式三份邮寄至实验室（邮寄地址见后），并同时将电子档（命名 2023 开放基金-姓名-单位）发送至 wanghuan@jlju.edu.cn。；2025年度吉林建筑大学寒地建筑综合节能教育部重点实验室 开放基金项目指南-吉林建筑大学寒地建筑综合节能教育部重点实验室；实验室科研项目-信息科学与工程学院；（研）2026年中国研究生创新实践系列大赛的报名通知-创新创业学院；2025年控制工程领域专业学位硕士研究生培养方案细则-长春工业大学电气与电子工程学院</v>
+      </c>
+      <c r="F917" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G917" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H917" t="str" s="3">
+        <v>https://hdzhjn.jlju.edu.cn/xinjian.pdf
+https://hdzhjn.jlju.edu.cn/info/1093/2304.htm
+https://sise.sut.edu.cn/jsgrzy/pxt/syskyxm.htm
+https://cxcy.sut.edu.cn/info/1098/9232.htm
+https://dqxy.ccut.edu.cn/info/1078/7520.htm</v>
+      </c>
+      <c r="I917" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第423项</v>
+      </c>
+    </row>
+    <row r="918" ht="52.5" customHeight="1">
+      <c r="A918" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B918" t="str" s="3">
+        <v>福建江西省属机器人装备平台补漏</v>
+      </c>
+      <c r="C918" t="str" s="3">
+        <v>福建/江西</v>
+      </c>
+      <c r="D918" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E918" t="str" s="3">
+        <v>查询：site:fjut.edu.cn ("开放课题" OR "开放基金") (机器人 OR 制造) / site:jxust.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) 2026 / site:fafu.edu.cn ("开放课题" OR "开放基金") 智能 装备 / site:fjnu.edu.cn ("开放课题" OR "开放基金") 机器人；线索：国家市场监督管理总局重点实验室（稀土产品检测与溯源）2026年度开放研究基金申请指南-江西理工大学科学技术处；农林生物安全全国重点实验室2025年开放基金课题申请指南-农林生物安全全国重点实验室；科技厅-福建省重点实验室管理办法；福建省网络安全与密码技术重点实验室；智慧农林福建省高校重点实验室2019年度开放课题申请指南；海洋智能装备福建省高校重点实验室2025年度开放基金申请指南</v>
+      </c>
+      <c r="F918" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G918" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H918" t="str" s="3">
+        <v>https://kjc.jxust.edu.cn/info/1018/4591.htm
+https://sklafb.fafu.edu.cn/info/1035/4871.htm
+https://kyc.fjut.edu.cn/2026/0119/c6913a263888/page.htm
+https://nscl.fjnu.edu.cn/_upload/article/files/0f/93/889a43fe4240b566f3c7f4cf197e/1c95e0ce-39ec-4cf9-b7b2-d15cbf426d86.pdf
+https://www.fafu.edu.cn/2019/0721/c136a46120/pagem.htm
+https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm</v>
+      </c>
+      <c r="I918" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第424项</v>
+      </c>
+    </row>
+    <row r="919" ht="52.5" customHeight="1">
+      <c r="A919" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B919" t="str" s="3">
+        <v>滇黔桂省属装备感知开放机制补漏</v>
+      </c>
+      <c r="C919" t="str" s="3">
+        <v>云南/贵州/广西</v>
+      </c>
+      <c r="D919" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E919" t="str" s="3">
+        <v>查询：site:kmust.edu.cn ("开放基金" OR "开放课题") (机器人 OR 制造) 2026 / site:guet.edu.cn ("开放基金" OR "开放课题") (机器人 OR 感知) 2026 / site:gxu.edu.cn ("开放基金" OR "开放课题") (机器人 OR 装备) 2026 / site:gznu.edu.cn ("开放基金" OR "开放课题") 机器人；线索：云南省复杂系统与类脑智能重点实验室（筹）2026 年度开放基金申请指南-昆明理工大学理学院；广西高校智能综合自动化重点实验室；广西高校人文社会科学重点研究基地亚太（东南亚）翻译与跨文化传播中心关于2026年度开放基金课题招标的通知-广西大学外国语学院；中国地质学会锡多金属矿成矿作用及勘查技术创新基地开放基金指南（2026）-国土资源工程学院；固体废弃物资源化国家工程研究中心2026年度开放基金拟立项项目公示 -环境科学与工程学院；2026年度开放课题申报常见问题答疑-广西大学外国语学院</v>
+      </c>
+      <c r="F919" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G919" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H919" t="str" s="3">
+        <v>https://lxy.kmust.edu.cn/info/1151/2522.htm
+https://www.guet.edu.cn/dept8/_t30/2026/0706/c1177a157316/page.htm
+https://fls.gxu.edu.cn/info/1286/5012.htm
+https://gzy.kmust.edu.cn/info/1093/3177.htm
+https://ese.kmust.edu.cn/info/1314/2805.htm
+https://fls.gxu.edu.cn/info/1286/5073.htm</v>
+      </c>
+      <c r="I919" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第425项</v>
+      </c>
+    </row>
+    <row r="920" ht="52.5" customHeight="1">
+      <c r="A920" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B920" t="str" s="3">
+        <v>西部宁青新藏省属平台补漏</v>
+      </c>
+      <c r="C920" t="str" s="3">
+        <v>宁夏/青海/新疆/西藏</v>
+      </c>
+      <c r="D920" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E920" t="str" s="3">
+        <v>查询：宁夏 重点实验室 开放基金 2026 机器人 / 青海 重点实验室 开放基金 2026 装备 / 新疆 重点实验室 开放课题 2026 机器人 / 西藏 重点实验室 开放课题 2026 感知；线索：中国石油大学(北京)克拉玛依校区新疆油气智能勘探与开发重点实验室；科学技术局、科协--通知公告--建筑钢结构智能制造技术兵团重点实验室2026年开放课题申报指南；中国科学技术大学 脑启发智能感知与认知教育部重点实验室--中文主页--2026年度开放课题申报通知；2026年度开放课题申请公告；2026年度认知智能全国重点实验室开放课题“高教认知智能核心技术研究及应用”专项申报通知 – 认知智能全国重点实验室；传感器技术全国重点实验室关于公布2026年度开放课题立项名单的通知----传感技术实验室</v>
+      </c>
+      <c r="F920" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G920" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H920" t="str" s="3">
+        <v>https://www.cupk.edu.cn/olgas/c/2026-05-30/534544.shtml
+https://kjj.xjbt.gov.cn/c/2026-04-01/8477891.shtml
+https://institution.ustc.edu.cn/BIPCLab/zh_CN/article/994106/content/5479.htm
+https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://cogskl.iflytek.com/archives/3471
+https://www.sim.cas.cn/kybm2016/cgjslhgjzdsys2016/xx_tzgg2016/202609/t20260928_8287372.html</v>
+      </c>
+      <c r="I920" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第426项</v>
+      </c>
+    </row>
+    <row r="921" ht="52.5" customHeight="1">
+      <c r="A921" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B921" t="str" s="3">
+        <v>天津两校机器人视觉自主智能开放机制</v>
+      </c>
+      <c r="C921" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D921" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E921" t="str" s="3">
+        <v>查询：site:tjut.edu.cn ("复杂系统控制" OR "学习型智能系统" OR "计算机视觉与系统") ("开放课题" OR "开放基金") (2026 OR 2027 OR 2025) / site:tiangong.edu.cn ("自主智能技术与系统" OR "数控多电机伺服") ("开放课题" OR "开放基金")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F921" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G921" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H921" t="str" s="3"/>
+      <c r="I921" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第427项</v>
+      </c>
+    </row>
+    <row r="922" ht="52.5" customHeight="1">
+      <c r="A922" t="str" s="3">
+        <v>2026-10-09南京周边省属目录与全国省高校机制补漏</v>
+      </c>
+      <c r="B922" t="str" s="3">
+        <v>福建理工海洋与昆明低空年度补漏</v>
+      </c>
+      <c r="C922" t="str" s="3">
+        <v>福建/云南</v>
+      </c>
+      <c r="D922" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E922" t="str" s="3">
+        <v>查询：site:fjut.edu.cn 海洋智能装备 开放 (2026 OR 2027) / site:kmust.edu.cn ("低空经济和无人机" OR "低空装备设计") ("开放课题" OR "开放基金") (2026 OR 2027) / site:fafu.edu.cn 智慧农林 开放课题 (2026 OR 2027 OR 2025)；线索：科研平台-民航与航空学院；农林生物安全全国重点实验室关于2025年开放课题基金项目的立项通知-农林生物安全全国重点实验室；智慧农林福建省高校重点实验室2019年度开放课题申请指南；农林生物安全全国重点实验室2025年开放基金课题申请指南-农林生物安全全国重点实验室；福建省特种淀粉品质科学与加工技术重点实验室 2025年开放课题申报指南</v>
+      </c>
+      <c r="F922" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G922" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H922" t="str" s="3">
+        <v>https://mhhk.kmust.edu.cn/xkky/kypt.htm
+https://sklafb.fafu.edu.cn/info/1035/5301.htm
+https://www.fafu.edu.cn/2019/0721/c136a46120/pagem.htm
+https://sklafb.fafu.edu.cn/info/1035/4871.htm
+https://spxy.fafu.edu.cn/5a/34/c429a416308/page.htm</v>
+      </c>
+      <c r="I922" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第428项</v>
+      </c>
+    </row>
+    <row r="923" ht="52.5" customHeight="1">
+      <c r="A923" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B923" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C923" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D923" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E923" t="str" s="3">
+        <v>大气光电探测与信息融合国家级重点实验室培育建设点；2025；N066；2025正式指南完整正文已取得；申请DOCX首次工具不支持</v>
+      </c>
+      <c r="F923" t="str" s="3">
+        <v>申请DOCX首次不支持交人工；补具体装备任务、成果IP报销办法。同校非固定人员合作要求须核。未取得2026—2027新公告不表示不存在。</v>
+      </c>
+      <c r="G923" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H923" t="str" s="3">
+        <v>https://wdy.nuist.edu.cn/2025/0916/c2983a290115/pagem.htm</v>
+      </c>
+      <c r="I923" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="924" ht="52.5" customHeight="1">
+      <c r="A924" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B924" t="str" s="3">
+        <v>福建理工大学</v>
+      </c>
+      <c r="C924" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="D924" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E924" t="str" s="3">
+        <v>海洋智能装备福建省高校重点实验室；2025；N067；2025正式指南完整正文已取得；3份申请/推荐DOCX首次不支持</v>
+      </c>
+      <c r="F924" t="str" s="3">
+        <v>3个DOCX首次工具不支持；需福工大科研〔2024〕14号办法、合同补IP/外拨/报销与支付及设备开支范围；2026—2027新批未定位，不声明无。</v>
+      </c>
+      <c r="G924" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H924" t="str" s="3">
+        <v>https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm</v>
+      </c>
+      <c r="I924" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="925" ht="52.5" customHeight="1">
+      <c r="A925" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B925" t="str" s="3">
+        <v>福建农林大学</v>
+      </c>
+      <c r="C925" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="D925" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E925" t="str" s="3">
+        <v>智慧农林福建省高校重点实验室；2019；N068；官方搜索发现2019正式开放课题标题；正文首次超时停止</v>
+      </c>
+      <c r="F925" t="str" s="3">
+        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+      </c>
+      <c r="G925" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H925" t="str" s="3">
+        <v>https://www.fafu.edu.cn/2019/0721/c136a46120/pagem.htm</v>
+      </c>
+      <c r="I925" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="926" ht="52.5" customHeight="1">
+      <c r="A926" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B926" t="str" s="3">
+        <v>昆明理工大学</v>
+      </c>
+      <c r="C926" t="str" s="3">
+        <v>云南·昆明</v>
+      </c>
+      <c r="D926" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E926" t="str" s="3">
+        <v>云南省低空经济和无人机技术创新中心（筹）；2025；N069；2025正式指南完整正文已取得；申请DOCX下载页首次显示验证码</v>
+      </c>
+      <c r="F926" t="str" s="3">
+        <v>验证码申请DOCX人工下载；补外拨报销支付/合同、普通项目论文+申请专利规则及截止是否含当日。2026—2027新公告未定位不代表不存在。</v>
+      </c>
+      <c r="G926" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H926" t="str" s="3">
+        <v>https://mhhk.kmust.edu.cn/info/1019/4253.htm</v>
+      </c>
+      <c r="I926" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="927" ht="52.5" customHeight="1">
+      <c r="A927" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B927" t="str" s="3">
+        <v>苏州科技大学</v>
+      </c>
+      <c r="C927" t="str" s="3">
+        <v>江苏·苏州</v>
+      </c>
+      <c r="D927" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E927" t="str" s="3">
+        <v>省部目录18牌目全文；市厅目录2页全部28记录全文。共融机器人省中心简介只有标题未得介绍；机器人/精密铜管/现代测绘/虚拟显示交互/空间信息/加工/光学精测/测控等逐名开放机制查。</v>
+      </c>
+      <c r="F927" t="str" s="3">
+        <v>校级其他目录首次超时人工；市级与省级同体多牌不重复算实验室，全校国家/协同目录未齐。名称查询未找到正式指南不等于无开放基金。</v>
+      </c>
+      <c r="G927" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H927" t="str" s="3">
+        <v>https://kjcyc.usts.edu.cn/kjpt/sbj.htm
+https://kjcyc.usts.edu.cn/kjpt/stj.htm
+https://kjcyc.usts.edu.cn/kjpt/stj/1.htm
+https://kjcyc.usts.edu.cn/kjpt/xjjqt.htm</v>
+      </c>
+      <c r="I927" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="928" ht="52.5" customHeight="1">
+      <c r="A928" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B928" t="str" s="3">
+        <v>南京信息工程大学</v>
+      </c>
+      <c r="C928" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D928" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E928" t="str" s="3">
+        <v>省部目录25条目全文（含研究院非全是实验室）；环境物联/大气环境装备/能源控制/大数据智能/医学图像/探测信息/智能网络逐名2026—2027与历史基金查；2025光电N066全文明确不外拨但具体机器人任务不足待核。</v>
+      </c>
+      <c r="F928" t="str" s="3">
+        <v>校级目录首次超时人工；25条目录不是25机器人平台，具体任务、合同及其余年度待核；物理光电DOCX首次不支持人工。</v>
+      </c>
+      <c r="G928" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H928" t="str" s="3">
+        <v>https://www.nuist.edu.cn/kxyj/sbjkypt.htm
+https://www.nuist.edu.cn/kxyj/xjkypt.htm
+https://wdy.nuist.edu.cn/2025/0916/c2983a290115/pagem.htm</v>
+      </c>
+      <c r="I928" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="929" ht="52.5" customHeight="1">
+      <c r="A929" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B929" t="str" s="3">
+        <v>天津工业大学</v>
+      </c>
+      <c r="C929" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D929" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E929" t="str" s="3">
+        <v>软件学院完整2平台介绍：自主智能市重点室/国际联合中心，机器人集群调度/三维重建明确；电机院平台列表9条实验系统不是9重点实验室；两平台及数控伺服开放机制逐名查。</v>
+      </c>
+      <c r="F929" t="str" s="3">
+        <v>全校现行省部/教育厅目录及其他学院未齐；未定位新正式通知不等于无机制。</v>
+      </c>
+      <c r="G929" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H929" t="str" s="3">
+        <v>https://ss.tiangong.edu.cn/7576/list.htm
+https://motor.tiangong.edu.cn/kypt/list.htm</v>
+      </c>
+      <c r="I929" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="930" ht="52.5" customHeight="1">
+      <c r="A930" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B930" t="str" s="3">
+        <v>天津理工大学</v>
+      </c>
+      <c r="C930" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D930" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E930" t="str" s="3">
+        <v>市科研基地单页15条全部可读；复杂系统控制2022简介明确机器人运动控制、多机器人规划、视觉导航/遥操作；计算机视觉所介绍明确机器人/三维及部重点室/工程中心，逐名机制2026—2027历史查。</v>
+      </c>
+      <c r="F930" t="str" s="3">
+        <v>部委和国家级目录未核；市目录15牌目包含非机器人平台；新增先进机电/智能计算须接续逐名查，不能称全校完成。</v>
+      </c>
+      <c r="G930" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H930" t="str" s="3">
+        <v>https://kjc.tjut.edu.cn/kyjd/tjskyjd.htm
+https://kjc.tjut.edu.cn/info/1053/1069.htm
+https://icv.tjut.edu.cn/yjsjs.htm</v>
+      </c>
+      <c r="I930" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="931" ht="52.5" customHeight="1">
+      <c r="A931" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B931" t="str" s="3">
+        <v>福建理工大学/福建农林大学</v>
+      </c>
+      <c r="C931" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D931" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E931" t="str" s="3">
+        <v>N067海洋智能装备2025完整任务条款/3表首次失败；N068智慧农林2019首超时；2026—2027年度机制查。AI夏令营/竞赛/教学农场不是科研经费受理。</v>
+      </c>
+      <c r="F931" t="str" s="3">
+        <v>全校省部高校平台目录未齐；福工大科研〔2024〕14号管理办法/IP与外拨未知；不能将首次打不开N068认定相关。</v>
+      </c>
+      <c r="G931" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H931" t="str" s="3">
+        <v>https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm
+https://www.fafu.edu.cn/2019/0721/c136a46120/pagem.htm</v>
+      </c>
+      <c r="I931" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="932" ht="52.5" customHeight="1">
+      <c r="A932" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B932" t="str" s="3">
+        <v>昆明理工大学</v>
+      </c>
+      <c r="C932" t="str" s="3">
+        <v>云南</v>
+      </c>
+      <c r="D932" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E932" t="str" s="3">
+        <v>N069低空经济无人机2025完整任务条款、10万/5万、论文专利且/或原样核；表验证码交人工；2026—2027机制查。复杂系统类脑2026原M153/E065已排除不重复打开。</v>
+      </c>
+      <c r="F932" t="str" s="3">
+        <v>学校完整目录未齐；低空装备设计中心与创新中心不得无依据合并；外拨/报销支付和合同未知。</v>
+      </c>
+      <c r="G932" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H932" t="str" s="3">
+        <v>https://mhhk.kmust.edu.cn/info/1019/4253.htm</v>
+      </c>
+      <c r="I932" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="933" ht="52.5" customHeight="1">
+      <c r="A933" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B933" t="str" s="3">
+        <v>吉林建筑大学及北方省属补漏</v>
+      </c>
+      <c r="C933" t="str" s="3">
+        <v>吉林/辽宁/河北/山西</v>
+      </c>
+      <c r="D933" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E933" t="str" s="3">
+        <v>寒地建筑2025完整9年度任务为设计节能/能耗/材料/新能源/建筑低能耗器件，E086排除；辽宁吉林及冀晋省属检索仅查询范围，非完整目录。</v>
+      </c>
+      <c r="F933" t="str" s="3">
+        <v>其余学校具体平台与年度未全；不把建筑AI/多目标优化推成机器人，不泛化剔除机构所有项目。</v>
+      </c>
+      <c r="G933" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H933" t="str" s="3">
+        <v>https://hdzhjn.jlju.edu.cn/info/1093/2304.htm</v>
+      </c>
+      <c r="I933" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="934" ht="52.5" customHeight="1">
+      <c r="A934" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B934" t="str" s="3">
+        <v>西部及滇黔桂跨省对账</v>
+      </c>
+      <c r="C934" t="str" s="3">
+        <v>云南/贵州/广西/宁夏/青海/新疆/西藏</v>
+      </c>
+      <c r="D934" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E934" t="str" s="3">
+        <v>本批年度发现查询已留档；桂电M070、新疆M072、脑启发M041、清华M016、南航M169复用；M071指南建议征集已排除受理清单；跨省搜索结果按机构实际所在地归属。</v>
+      </c>
+      <c r="F934" t="str" s="3">
+        <v>该批空结果不是对应省无项目；省教育厅认定目录和省属全校逐平台年度尚未齐。</v>
+      </c>
+      <c r="G934" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H934" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+      <c r="I934" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -50099,23 +51266,63 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="115" ht="96" customHeight="1">
+    <row r="115" ht="192" customHeight="1">
       <c r="A115" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B115" t="n" s="13">
+        <v>45853</v>
+      </c>
+      <c r="C115" t="str" s="14">
+        <v>福建理工大学·海洋智能装备福建省高校重点实验室</v>
+      </c>
+      <c r="D115" t="str" s="15">
+        <v>水下图像退化/复原/小样本目标识别与实时嵌入部署；水下惯性水声地磁导航与卫星多源定位融合；水下光声模态差异图像融合；无人船/水下机器人集群编队动力学任务分配控制；装备运动学仿真与实虚协同；小型水下机器人传感集成自主控制与样机；结构水动力测试；智能测绘装备传感协同及集成验证。年度还含水声通信、水下机器人材料、鱼数量统计、海洋装备数据处理，应用背景原样保留。</v>
+      </c>
+      <c r="E115" t="str" s="15">
+        <v>每项不超过2万元，以正式批复为准。</v>
+      </c>
+      <c r="F115" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="116" ht="147" customHeight="1">
+      <c r="A116" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B116" t="n" s="13">
+        <v>45919</v>
+      </c>
+      <c r="C116" t="str" s="14">
+        <v>昆明理工大学·云南省低空经济和无人机技术创新中心（筹）</v>
+      </c>
+      <c r="D116" t="str" s="15">
+        <v>高原复杂环境无人机电路可靠性、轻量低功耗飞控/抗干扰传感接口；氢能垂起固定翼无人机气动动力耦合与轻量储供；长航时BMS SOC/SOH估计均衡热管理；无人机智能感知自主避障、协同集群控制、脑机/类脑人机交互实时控制算法。电池材料研究不据智能标题扩展通用材料项目。</v>
+      </c>
+      <c r="E116" t="str" s="15">
+        <v>重点10万元，拟2—3项；一般5万元，拟1—2项。</v>
+      </c>
+      <c r="F116" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="117" ht="96" customHeight="1">
+      <c r="A117" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B115" t="n" s="13">
+      <c r="B117" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C115" t="str" s="14">
+      <c r="C117" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D115" t="str" s="15">
+      <c r="D117" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E115" t="str" s="15">
+      <c r="E117" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F115" t="str" s="16">
+      <c r="F117" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -50311,8 +51518,8 @@
     <hyperlink ref="F101" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F102" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F115" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C115" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F117" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C117" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F103" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C104" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -50349,6 +51556,10 @@
     <hyperlink ref="F114" ns1:id="rIdResume114"/>
     <hyperlink ref="C36" location="'02项目完整详情'!A209" display="项目完整详情"/>
     <hyperlink ref="F36" ns1:id="rIdResume115"/>
+    <hyperlink ref="C115" location="'02项目完整详情'!A216" display="项目完整详情"/>
+    <hyperlink ref="F115" ns1:id="rIdResume116"/>
+    <hyperlink ref="C116" location="'02项目完整详情'!A218" display="项目完整详情"/>
+    <hyperlink ref="F116" ns1:id="rIdResume117"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -52472,25 +53683,25 @@
         <v>线索待核·已截止</v>
       </c>
       <c r="B74" t="n" s="13">
-        <v>46158</v>
+        <v>45942</v>
       </c>
       <c r="C74" t="str" s="14">
-        <v>西安工程大学·功能性纺织材料及制品教育部重点实验室</v>
+        <v>南京信息工程大学·大气光电探测与信息融合国家级重点实验室培育建设点</v>
       </c>
       <c r="D74" t="str" s="15">
-        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
+        <v>年度仅列大气光学与大气辐射、大气光电探测技术与系统、智能光谱信息处理、光通信与信息融合四个概括方向。尚缺机器人或相关智能装备的具体任务证据，不凭智能/融合收为确定相关。</v>
       </c>
       <c r="E74" t="str" s="15">
-        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
+        <v>1—3万元/项，拟5—8项。</v>
       </c>
       <c r="F74" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G74" t="str" s="3">
-        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
+        <v>申请DOCX首次不支持交人工；补具体装备任务、成果IP报销办法。同校非固定人员合作要求须核。未取得2026—2027新公告不表示不存在。</v>
       </c>
       <c r="H74" t="str" s="3">
-        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
+        <v>刘丹025-58235587；002402@nuist.edu.cn；南京宁六路219号物理与光电工程学院210044。申请段邮箱有空格，联系段明确无空格。</v>
       </c>
     </row>
     <row r="75" ht="132" customHeight="1">
@@ -52498,25 +53709,25 @@
         <v>线索待核·已截止</v>
       </c>
       <c r="B75" t="n" s="13">
-        <v>46249</v>
+        <v>46158</v>
       </c>
       <c r="C75" t="str" s="14">
-        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
+        <v>西安工程大学·功能性纺织材料及制品教育部重点实验室</v>
       </c>
       <c r="D75" t="str" s="15">
-        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
+        <v>当年5项原方向：安全防护纺织品、结构—功能纺织复合材料、智能纤维及智能可穿戴、医用纺织材料、纺织产业碳中和。智能可穿戴仅领域名，未公开机器人/人机感知交互具体研究任务；简介纺织智能加工装备不能代替本年指南。</v>
       </c>
       <c r="E75" t="str" s="15">
-        <v>合同金额2万元/项；计划≤10项。</v>
+        <v>重点5万元/项拟2项；一般2万元/项拟15项。</v>
       </c>
       <c r="F75" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G75" t="str" s="3">
-        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
+        <v>智能纤维/可穿戴缺具体机器人、人机感知交互任务；2附件验证码。需当年细任务、管理办法外拨/IP条款，不能因领域智能收首页或写确定相关。</v>
       </c>
       <c r="H75" t="str" s="3">
-        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
+        <v>李老师18700931660；jybzdsys@xpu.edu.cn；西安碑林区金花南路19号功能性纺织材料及制品教育部重点实验室。</v>
       </c>
     </row>
     <row r="76" ht="132" customHeight="1">
@@ -52524,51 +53735,51 @@
         <v>线索待核·已截止</v>
       </c>
       <c r="B76" t="n" s="13">
-        <v>45843</v>
+        <v>46249</v>
       </c>
       <c r="C76" t="str" s="14">
-        <v>浙江师范大学（联合莫桑比克蒙德拉内大学、宁波工程学院）·中国—莫桑比克智慧农业“一带一路”联合实验室（筹）</v>
+        <v>沈阳航空航天大学·飞行器快速试制技术研究教育部重点实验室/航空制造技术国防重点学科与技术研究中心联合开放基金</v>
       </c>
       <c r="D76" t="str" s="15">
-        <v>5方向包括农业灾害、水土、作物种质、农情感知、管理装备；具体列农作物观测多模态模型、智慧农场关键技术/传感器及装备。但未细化机器人或装备感知—规划—控制任务，待核；作物基因/土壤等方向不凭智慧标题收相关。</v>
+        <v>2026四项原任务：新型结构创新设计及考核验证、航空高性能增材制造、智能化航空制造工艺、航空新结构智能制造及智能装备。正文未具体列机器人感知/规划/学习控制任务，不能由智能制造标题判定已相关；待附件/具体任务说明。</v>
       </c>
       <c r="E76" t="str" s="15">
-        <v>重点8—12万元/项；一般4—7万元/项。</v>
+        <v>合同金额2万元/项；计划≤10项。</v>
       </c>
       <c r="F76" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G76" t="str" s="3">
-        <v>智慧农场传感装备缺具体机器人/智能装备细任务；申请DOCX首次异常，需附任务内容、经费/成果数补充。正文未载第一完成单位，不混淆第一基金标注。</v>
+        <v>年度任务只有航空工艺/结构/智能装备大项，无具体机器人任务证据，放待核不首页。申请DOC验证码未取；须补任务细项、外拨报账、起止日期、第一单位/IP校外权属。</v>
       </c>
       <c r="H76" t="str" s="3">
-        <v>陈老师0579-82280775、chenfeng@zjnu.edu.cn；申请cmbrjlsa@zjnu.cn；金华迎宾大道688号321004。</v>
+        <v>赵朔024-89724538；136478034@qq.com；沈阳道义南大街37号110136（科研院页尾地址，未作为指定邮寄要求）。</v>
       </c>
     </row>
     <row r="77" ht="132" customHeight="1">
       <c r="A77" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B77" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B77" t="n" s="13">
+        <v>45843</v>
       </c>
       <c r="C77" t="str" s="14">
-        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
+        <v>浙江师范大学（联合莫桑比克蒙德拉内大学、宁波工程学院）·中国—莫桑比克智慧农业“一带一路”联合实验室（筹）</v>
       </c>
       <c r="D77" t="str" s="15">
-        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
+        <v>5方向包括农业灾害、水土、作物种质、农情感知、管理装备；具体列农作物观测多模态模型、智慧农场关键技术/传感器及装备。但未细化机器人或装备感知—规划—控制任务，待核；作物基因/土壤等方向不凭智慧标题收相关。</v>
       </c>
       <c r="E77" t="str" s="15">
-        <v>未取得2020金额。</v>
+        <v>重点8—12万元/项；一般4—7万元/项。</v>
       </c>
       <c r="F77" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G77" t="str" s="3">
-        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+        <v>智慧农场传感装备缺具体机器人/智能装备细任务；申请DOCX首次异常，需附任务内容、经费/成果数补充。正文未载第一完成单位，不混淆第一基金标注。</v>
       </c>
       <c r="H77" t="str" s="3">
-        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+        <v>陈老师0579-82280775、chenfeng@zjnu.edu.cn；申请cmbrjlsa@zjnu.cn；金华迎宾大道688号321004。</v>
       </c>
     </row>
     <row r="78" ht="132" customHeight="1">
@@ -52579,22 +53790,22 @@
         <v>未取得</v>
       </c>
       <c r="C78" t="str" s="14">
-        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
       </c>
       <c r="D78" t="str" s="15">
-        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
       </c>
       <c r="E78" t="str" s="15">
-        <v>未取得当年金额。</v>
+        <v>未取得2020金额。</v>
       </c>
       <c r="F78" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G78" t="str" s="3">
-        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
       </c>
       <c r="H78" t="str" s="3">
-        <v>年度联系人未取得。</v>
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
       </c>
     </row>
     <row r="79" ht="132" customHeight="1">
@@ -52605,22 +53816,74 @@
         <v>未取得</v>
       </c>
       <c r="C79" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
       </c>
       <c r="D79" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
       </c>
       <c r="E79" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>未取得当年金额。</v>
       </c>
       <c r="F79" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G79" t="str" s="3">
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+      </c>
+      <c r="H79" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="80" ht="132" customHeight="1">
+      <c r="A80" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B80" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C80" t="str" s="14">
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+      </c>
+      <c r="D80" t="str" s="15">
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+      </c>
+      <c r="E80" t="str" s="15">
+        <v>未取得当年金额/类型。</v>
+      </c>
+      <c r="F80" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G80" t="str" s="3">
         <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
       </c>
-      <c r="H79" t="str" s="3">
+      <c r="H80" t="str" s="3">
         <v>未取得当年项目联系人。</v>
+      </c>
+    </row>
+    <row r="81" ht="132" customHeight="1">
+      <c r="A81" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B81" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C81" t="str" s="14">
+        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
+      </c>
+      <c r="D81" t="str" s="15">
+        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+      </c>
+      <c r="E81" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F81" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G81" t="str" s="3">
+        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+      </c>
+      <c r="H81" t="str" s="3">
+        <v>年度基金联系人未取得。</v>
       </c>
     </row>
   </sheetData>
@@ -52767,20 +54030,24 @@
     <hyperlink ref="F72" ns1:id="rIdResume73"/>
     <hyperlink ref="C73" location="'02项目完整详情'!A199" display="项目完整详情"/>
     <hyperlink ref="F73" ns1:id="rIdResume74"/>
-    <hyperlink ref="C75" location="'02项目完整详情'!A201" display="项目完整详情"/>
-    <hyperlink ref="F75" ns1:id="rIdResume75"/>
-    <hyperlink ref="C74" location="'02项目完整详情'!A202" display="项目完整详情"/>
-    <hyperlink ref="F74" ns1:id="rIdResume76"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F79" ns1:id="rIdResume77"/>
+    <hyperlink ref="C76" location="'02项目完整详情'!A201" display="项目完整详情"/>
+    <hyperlink ref="F76" ns1:id="rIdResume75"/>
+    <hyperlink ref="C75" location="'02项目完整详情'!A202" display="项目完整详情"/>
+    <hyperlink ref="F75" ns1:id="rIdResume76"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F80" ns1:id="rIdResume77"/>
     <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
     <hyperlink ref="F44" ns1:id="rIdResume78"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A212" display="项目完整详情"/>
-    <hyperlink ref="F78" ns1:id="rIdResume79"/>
-    <hyperlink ref="C76" location="'02项目完整详情'!A213" display="项目完整详情"/>
-    <hyperlink ref="F76" ns1:id="rIdResume80"/>
-    <hyperlink ref="C77" location="'02项目完整详情'!A214" display="项目完整详情"/>
-    <hyperlink ref="F77" ns1:id="rIdResume81"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F79" ns1:id="rIdResume79"/>
+    <hyperlink ref="C77" location="'02项目完整详情'!A213" display="项目完整详情"/>
+    <hyperlink ref="F77" ns1:id="rIdResume80"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A214" display="项目完整详情"/>
+    <hyperlink ref="F78" ns1:id="rIdResume81"/>
+    <hyperlink ref="C74" location="'02项目完整详情'!A215" display="项目完整详情"/>
+    <hyperlink ref="F74" ns1:id="rIdResume82"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A217" display="项目完整详情"/>
+    <hyperlink ref="F81" ns1:id="rIdResume83"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -19444,8 +19444,8 @@
       <c r="R216" t="str" s="3">
         <v>本人博士/高校现职对应学历类别；单位经费管理承诺、固定教师合作及限项尚未核，历史参考。</v>
       </c>
-      <c r="S216" t="str" s="3">
-        <v>3个DOCX首次工具不支持；需福工大科研〔2024〕14号办法、合同补IP/外拨/报销与支付及设备开支范围；2026—2027新批未定位，不声明无。</v>
+      <c r="S216" s="3" t="str">
+        <v>3个申请/推荐DOCX首次不支持；福工大科研〔2024〕14号办法入口已找到但工具正文为空，人工取；合同/IP/外拨报销支付及设备开支范围待核。2026结题通知处理2023项目，非2026申请。</v>
       </c>
       <c r="T216" t="str" s="3">
         <v>https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm</v>
@@ -19638,6 +19638,425 @@
       </c>
       <c r="AA218" t="str" s="3">
         <v>2025独立历史；不能套云南复杂系统类脑2026已排除项目。</v>
+      </c>
+    </row>
+    <row r="219" ht="132" customHeight="1">
+      <c r="A219" t="str" s="3">
+        <v>N070</v>
+      </c>
+      <c r="B219" t="str" s="3">
+        <v>官方搜索定位2027业务费实验室开放基金申报指南；正文首次不可访问停止</v>
+      </c>
+      <c r="C219" t="str" s="3">
+        <v>中国地震局工程力学研究所</v>
+      </c>
+      <c r="D219" t="str" s="3">
+        <v>基本科研业务费专项实验室开放基金项目</v>
+      </c>
+      <c r="E219" t="str" s="3">
+        <v>线索待核·公告未取得</v>
+      </c>
+      <c r="F219" t="str" s="3">
+        <v>2027</v>
+      </c>
+      <c r="G219" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H219" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I219" t="str" s="3">
+        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+      </c>
+      <c r="J219" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K219" t="str" s="3">
+        <v>校外负责人资格/职称年龄限项未取得；研究所业务费不是仅中央高校。</v>
+      </c>
+      <c r="L219" t="str" s="3">
+        <v>合作访问未取得。</v>
+      </c>
+      <c r="M219" t="str" s="3">
+        <v>费用/外拨/报销/支付未取得。</v>
+      </c>
+      <c r="N219" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="O219" t="str" s="3">
+        <v>未取得数量/署名/验收。</v>
+      </c>
+      <c r="P219" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="Q219" t="str" s="3">
+        <v>截止材料提交均未取得。</v>
+      </c>
+      <c r="R219" t="str" s="3">
+        <v>本人博士现职已知；资料不足不进当前页，不推断可申请。</v>
+      </c>
+      <c r="S219" t="str" s="3">
+        <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
+      </c>
+      <c r="T219" t="str" s="3">
+        <v>https://iem.ac.cn/zxgl/info?id=4400</v>
+      </c>
+      <c r="U219" t="str" s="3">
+        <v>正文首次失败，附件直链未取得。</v>
+      </c>
+      <c r="V219" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W219" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X219" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y219" t="str" s="3">
+        <v>依托地区待官方目录核实</v>
+      </c>
+      <c r="Z219" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+      <c r="AA219" t="str" s="3">
+        <v>2027正式标题线索；未核具体实验室，不能与一般地震业务费或指南建议征集合并。</v>
+      </c>
+    </row>
+    <row r="220" ht="162" customHeight="1">
+      <c r="A220" t="str" s="3">
+        <v>N071</v>
+      </c>
+      <c r="B220" t="str" s="3">
+        <v>2026正式完整正文已取；任务仅概括结构检测/监测，3附件下载页或工具异常未获原件</v>
+      </c>
+      <c r="C220" t="str" s="3">
+        <v>长安大学</v>
+      </c>
+      <c r="D220" t="str" s="3">
+        <v>公路大型结构安全教育部工程研究中心</v>
+      </c>
+      <c r="E220" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F220" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G220" t="n" s="6">
+        <v>46280</v>
+      </c>
+      <c r="H220" t="str" s="3">
+        <v>17:00前</v>
+      </c>
+      <c r="I220" t="str" s="3">
+        <v>年度桥梁/隧道结构理论、抗震抗风、钢混组合结构、桥梁检测评估维护、施工控制、隧道环境防灾、大型结构安全监测与数据孪生。未细化机器人或智能检测装备感知规划控制任务，不能单凭监测/控制认定相关；任务联系待核。</v>
+      </c>
+      <c r="J220" t="str" s="3">
+        <v>3万元/项，立项先拨1万；一年中检达续拨条件再拨剩余。</v>
+      </c>
+      <c r="K220" t="str" s="3">
+        <v>非本校45岁以下研究者；副高及以上，或中级且博士；在研本校开放基金PI不能再申。年龄基准日/限项其他正文未载。</v>
+      </c>
+      <c r="L220" t="str" s="3">
+        <v>正文未强制每项固定人员合作；成果署名第3方案需中心固定人员第一通讯，具体方案须确认。访问未载。</v>
+      </c>
+      <c r="M220" t="str" s="3">
+        <v>拨付经费接受单位、外拨到外校还是校内账户、费用科目报销地点未知。首拨1万；中检不达条件可延期1年，再达条件续拨，否则余款不续拨。</v>
+      </c>
+      <c r="N220" t="str" s="3">
+        <v>2年执行；统一起止未载。一年中检，不达续拨可延期1年。</v>
+      </c>
+      <c r="O220" t="str" s="3">
+        <v>≥1篇B区及以上或1篇C/D区英文论文，分区是长安大学目录而非中科院；研究/综述计，简讯不计，增刊专刊原则不计（D区以上英文专刊例外）。署名三选一：PI第一作者/中心第一单位；PI第一通讯/其第一单位中心；PI第一作者/所在单位第一，中心固定人员第一通讯/通讯第一单位中心。成果标中心基金编号。</v>
+      </c>
+      <c r="P220" t="str" s="3">
+        <v>论文专利等归中心和PI所在单位共有且共同署名，收益细则未载。</v>
+      </c>
+      <c r="Q220" t="str" s="3">
+        <v>2026-09-15 17:00前签章电子申请发yao.li@chd.edu.cn，邮件题2026年度开放基金申请+姓名；纸件邮寄另通知。</v>
+      </c>
+      <c r="R220" t="str" s="3">
+        <v>本人博士现职已知；年龄、职称、在研限项及署名合作未核，窗口已过且任务联系待核。</v>
+      </c>
+      <c r="S220" t="str" s="3">
+        <v>需具体智能检测装备任务证据；3附件原件未取：申请DOC/高质量期刊目录/学校学术期刊目录；确认B/C/D目录口径及经费外拨报销。</v>
+      </c>
+      <c r="T220" t="str" s="3">
+        <v>https://highway.chd.edu.cn/info/1015/24577.htm</v>
+      </c>
+      <c r="U220" t="str" s="3">
+        <v>https://highway.chd.edu.cn/system/_content/download.jsp?owner=942513268&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=18223154
+https://highway.chd.edu.cn/system/_content/download.jsp?owner=942513268&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=18223156
+第三附件工具首次异常未返回直链，公告附件3链接可人工点击。</v>
+      </c>
+      <c r="V220" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W220" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X220" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y220" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="Z220" t="str" s="3">
+        <v>申请邮箱yao.li@chd.edu.cn；公告未载专门电话。学院公共029-82334453不是确认基金咨询电话。</v>
+      </c>
+      <c r="AA220" t="str" s="3">
+        <v>2026独立年度；不与道路施工装备基金等平台合并，研究任务尚待核。</v>
+      </c>
+    </row>
+    <row r="221" ht="162" customHeight="1">
+      <c r="A221" t="str" s="3">
+        <v>N072</v>
+      </c>
+      <c r="B221" t="str" s="3">
+        <v>2024正式指南完整正文已取得；申请DOCX首次不支持</v>
+      </c>
+      <c r="C221" t="str" s="3">
+        <v>青岛科技大学</v>
+      </c>
+      <c r="D221" t="str" s="3">
+        <v>低空飞行智能服务保障山东省工程研究中心</v>
+      </c>
+      <c r="E221" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F221" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G221" t="n" s="6">
+        <v>45427</v>
+      </c>
+      <c r="H221" t="str" s="3">
+        <v>正文要求“5月15日前”，是否含当日及小时未载；已过窗口。</v>
+      </c>
+      <c r="I221" t="str" s="3">
+        <v>崂山校区三维低空保障软硬件闭环验证平台；三维实景地图无人值守机场动态航线规划/评估及高度速度相机航点动作；地面目标多传感融合深度识别跟踪；环境/关系/历史航迹预测碰撞避免与预警；视觉激光雷达多模态三维重建/避障/盲降；消防无人机任务分配、包围控制精准灭火与编队通信拓扑优化；低空仿真及遥感图像校正识别3D测算。通信方案研究也在本批9题内，应用背景保留。</v>
+      </c>
+      <c r="J221" t="str" s="3">
+        <v>正文明确按评审给予经费资助，但未公布金额或课题数量。</v>
+      </c>
+      <c r="K221" t="str" s="3">
+        <v>国内外高校/科研院所等事业单位在编员工，博士或副高级以上，低空飞行领域良好前期基础；本中心在研或未按期/原计划完成PI当年不得申请。团队一般4—6人且≤6人；年龄正文未载。</v>
+      </c>
+      <c r="L221" t="str" s="3">
+        <v>与中心人员有良好合作基础者优先，非强制固定成员人数。必要时赴中心结题/学术报告；普通访问时长未载。</v>
+      </c>
+      <c r="M221" t="str" s="3">
+        <v>按青科财务制度，预算专账专款专用；两次拨付，首拨≤总支持40%，验收合格后拨余款。拨到外校或本校报销未载；资助之外申报执行费用自担，须垫支与结算流程待合同核。</v>
+      </c>
+      <c r="N221" t="str" s="3">
+        <v>一般≤2年；半年执行报告，一年总结及下一计划；变更/延期须提前获批准，结题后2个月提交结题报告。进展差可终止。</v>
+      </c>
+      <c r="O221" t="str" s="3">
+        <v>形成论文/专利/软著/原型系统等，数量、指定第一单位/作者正文未载；提交报告及成果材料，接受委托单位监理审计绩效检查。</v>
+      </c>
+      <c r="P221" t="str" s="3">
+        <v>完整公开指南未载，任务合同待核。</v>
+      </c>
+      <c r="Q221" t="str" s="3">
+        <v>加盖公章申请书截止前寄青岛科技大学数据学院，同时电子发zhaoqi_1995@163.com；入评审后不能更改申请及附件。获批签课题合同。</v>
+      </c>
+      <c r="R221" t="str" s="3">
+        <v>本人博士现职已知；在编身份、前期基础证明、限项/团队未核，不作能力判断；历史参考。</v>
+      </c>
+      <c r="S221" t="str" s="3">
+        <v>申请DOCX首不支持；金额未公布、外拨/垫支/验收数量署名IP需合同补。2025—2027机制查未定位新正式指南，不写无。</v>
+      </c>
+      <c r="T221" t="str" s="3">
+        <v>https://sjkx.qust.edu.cn/info/1061/1542.htm</v>
+      </c>
+      <c r="U221" t="str" s="3">
+        <v>https://sjkx.qust.edu.cn/system/_content/download.jsp?owner=1950452003&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=13246650</v>
+      </c>
+      <c r="V221" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W221" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X221" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y221" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="Z221" t="str" s="3">
+        <v>赵琦；zhaoqi_1995@163.com；青岛崂山松岭路99号数据科学学院。基金个人电话未载，学院公共0532-88959390。</v>
+      </c>
+      <c r="AA221" t="str" s="3">
+        <v>2024独立年度，不将教师获别家开放基金或2026招生当本中心新批。</v>
+      </c>
+    </row>
+    <row r="222" ht="192" customHeight="1">
+      <c r="A222" t="str" s="3">
+        <v>N073</v>
+      </c>
+      <c r="B222" t="str" s="3">
+        <v>标题2022年度指南、2023-02-09发布且02-20截止，完整正文已取；3个DOC首不支持</v>
+      </c>
+      <c r="C222" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="D222" t="str" s="3">
+        <v>安徽省工程机械智能制造重点实验室（2019省教育厅批准建设）</v>
+      </c>
+      <c r="E222" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F222" t="str" s="3">
+        <v>2022</v>
+      </c>
+      <c r="G222" t="n" s="6">
+        <v>44977</v>
+      </c>
+      <c r="H222" t="str" s="3">
+        <v>具体时点未载；标题年度2022不改为发布年度2023。</v>
+      </c>
+      <c r="I222" t="str" s="3">
+        <v>校外开放基金2题：面向智能制造多模态数据的知识图谱与工程机械故障诊断定位；典型工程机械施工场景数字模型、测试传感、在线监测调度和施工质量进展预测。校内主任基金另含复杂机械故障传播/新能源电驱供能，不能把校内专属任务当本人的开放选题。</v>
+      </c>
+      <c r="J222" t="str" s="3">
+        <v>校外开放基金约3万元/项，拟2项。校内主任基金约2万元/项，非外校申报类别。</v>
+      </c>
+      <c r="K222" t="str" s="3">
+        <v>国内外副高以上或博士科研人员，须实际主持人；不受理自然人申请，应依托单位。校外申请开放基金；主任基金只校内非固定研究者。年龄/限项正文未载。</v>
+      </c>
+      <c r="L222" t="str" s="3">
+        <v>须实验室固定人员为项目组成员，人数和访问时长未载。</v>
+      </c>
+      <c r="M222" t="str" s="3">
+        <v>按安徽建筑大学科研平台开放课题管理办法试行；首次DOC未取，外拨科目/报销支付比例未知。</v>
+      </c>
+      <c r="N222" t="str" s="3">
+        <v>2年，统一起止未载；按年提交技术进展报告。</v>
+      </c>
+      <c r="O222" t="str" s="3">
+        <v>校外开放基金SCI/EI收录期刊2篇（可发表/录用各1），或CSCD论文2篇（可发表/录用各1）、EI会议1篇；后者与会议的组合关系原文标点需管理办法核，不能改成任一篇。PI为成果第一或通讯；论文第一或通讯作者的第一单位须实验室，标基金项目号；成果与任务相关。</v>
+      </c>
+      <c r="P222" t="str" s="3">
+        <v>完整正文未载，管理办法及任务书待核。</v>
+      </c>
+      <c r="Q222" t="str" s="3">
+        <v>申请3份送交/邮寄合肥经开紫云路292号安徽建筑大学南校区机电楼本室，电子yuanbinwork@163.com；2023-02-20截止。签章细节待表。</v>
+      </c>
+      <c r="R222" t="str" s="3">
+        <v>本人博士/高校现职对应学历，单位名义、固定合作/限项及论文署名未核；只记录校外基金历史。</v>
+      </c>
+      <c r="S222" t="str" s="3">
+        <v>管理办法/申请书/任务书3DOC首次不支持；补经费外拨报销支付/IP、CSCD与会议成果组合及签章。2025—2027年度新指南未定位不声明无。</v>
+      </c>
+      <c r="T222" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/2023/0209/c145a209128/page.htm</v>
+      </c>
+      <c r="U222" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/_upload/article/files/55/7e/a1bd4404493cace7e1659ca46a5c/fad1ccf2-60e2-4ba3-a892-f61d58f0ca48.doc
+https://www.ahjzu.edu.cn/_upload/article/files/55/7e/a1bd4404493cace7e1659ca46a5c/4ecf7c4c-aedf-4765-9fe6-f34c61954ae9.doc
+https://www.ahjzu.edu.cn/_upload/article/files/55/7e/a1bd4404493cace7e1659ca46a5c/6a3d104d-ac0a-4c95-8e37-37f7f70cb037.doc</v>
+      </c>
+      <c r="V222" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W222" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X222" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y222" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="Z222" t="str" s="3">
+        <v>袁彬13721033638、0551-63828102；yuanbinwork@163.com；合肥紫云路292号南校区机电楼。</v>
+      </c>
+      <c r="AA222" t="str" s="3">
+        <v>2022独立指南；非徐工高端工程机械全国室M023，省教育厅平台属性按正文保留。</v>
+      </c>
+    </row>
+    <row r="223" ht="132" customHeight="1">
+      <c r="A223" t="str" s="3">
+        <v>N074</v>
+      </c>
+      <c r="B223" t="str" s="3">
+        <v>首次成功取得正文至一般课题结题要求；页尾续读首次超时停止</v>
+      </c>
+      <c r="C223" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="D223" t="str" s="3">
+        <v>安徽省智能地下探测重点实验室</v>
+      </c>
+      <c r="E223" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F223" t="str" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G223" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H223" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="I223" t="str" s="3">
+        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+      </c>
+      <c r="J223" t="str" s="3">
+        <v>金额未取得（正文页尾及附件未取得）。</v>
+      </c>
+      <c r="K223" t="str" s="3">
+        <v>已取部分称鼓励国内外高校科研机构研究者尤其青年；博士/职称年龄限项正式条款未取得，不能称无门槛。</v>
+      </c>
+      <c r="L223" t="str" s="3">
+        <v>获批后指定1位中级及以上固定研究者为联系人共同任务，任务书列合作计划；优先利用本室设备和数据平台；访问时长未取得。</v>
+      </c>
+      <c r="M223" t="str" s="3">
+        <v>费用/外拨/报销/支付未取得。</v>
+      </c>
+      <c r="N223" t="str" s="3">
+        <v>周期和起止未取得。</v>
+      </c>
+      <c r="O223" t="str" s="3">
+        <v>已取：重点以本室为主要完成单位之一，相关SCI/EI论文2篇；授权相关发明1项或软著2项。一般含主任论文1篇；授权发明1项或软著2项。论文与专利/软著为分别要求，作者顺序/其余验收页尾未取得。</v>
+      </c>
+      <c r="P223" t="str" s="3">
+        <v>未取得。</v>
+      </c>
+      <c r="Q223" t="str" s="3">
+        <v>截止/提交/表格/联系页尾未取得。</v>
+      </c>
+      <c r="R223" t="str" s="3">
+        <v>本人博士现职已知；具体资格、合作限项与机器人任务证据未齐，保持历史待核。</v>
+      </c>
+      <c r="S223" t="str" s="3">
+        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+      </c>
+      <c r="T223" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/cptulab/2023/1129/c13219a225180/page.htm</v>
+      </c>
+      <c r="U223" t="str" s="3">
+        <v>首次页尾超时，附件直链未取得。</v>
+      </c>
+      <c r="V223" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W223" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X223" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y223" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="Z223" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+      <c r="AA223" t="str" s="3">
+        <v>2023独立历史线索；不能将智能地下探测等同通用岩土模型或将主任基金推为外校可申请。</v>
       </c>
     </row>
   </sheetData>
@@ -20078,6 +20497,11 @@
     <hyperlink ref="T216" ns1:id="rIdResume438"/>
     <hyperlink ref="T217" ns1:id="rIdResume439"/>
     <hyperlink ref="T218" ns1:id="rIdResume440"/>
+    <hyperlink ref="T219" ns1:id="rIdResume441"/>
+    <hyperlink ref="T220" ns1:id="rIdResume442"/>
+    <hyperlink ref="T221" ns1:id="rIdResume443"/>
+    <hyperlink ref="T222" ns1:id="rIdResume444"/>
+    <hyperlink ref="T223" ns1:id="rIdResume445"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -48944,6 +49368,1138 @@
         <v>resume_sources_20261009.json</v>
       </c>
       <c r="I934" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="935" ht="52.5" customHeight="1">
+      <c r="A935" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B935" t="str" s="3">
+        <v>天津理工市级目录新增机电交互机制</v>
+      </c>
+      <c r="C935" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D935" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E935" t="str" s="3">
+        <v>查询：site:tjut.edu.cn "先进机电系统设计与智能控制" ("开放基金" OR "开放课题") / site:tjut.edu.cn "智能计算及软件新技术" ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025)；线索：天津市先进机电系统设计与智能控制重点实验室-科学技术处；实验室概况-天津理工大学计算机视觉与系统重点实验室；平台建设-机械工程学院</v>
+      </c>
+      <c r="F935" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G935" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H935" t="str" s="3">
+        <v>https://kjc.tjut.edu.cn/info/1053/1071.htm
+https://cvs.tjut.edu.cn/xyyw.htm
+https://me.tjut.edu.cn/szdw/ptjs.htm</v>
+      </c>
+      <c r="I935" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第429项</v>
+      </c>
+    </row>
+    <row r="936" ht="52.5" customHeight="1">
+      <c r="A936" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B936" t="str" s="3">
+        <v>福建理工海洋目录其余平台开放机制</v>
+      </c>
+      <c r="C936" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D936" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E936" t="str" s="3">
+        <v>查询：site:fjut.edu.cn "智能加工技术及装备" ("开放基金" OR "开放课题") / site:fjut.edu.cn "大数据挖掘与应用" ("开放基金" OR "开放课题") / site:fjut.edu.cn "海上智能管控" ("开放基金" OR "开放课题")；线索：关于做好2025年度福建理工大学重点科研创新平台开放基金项目结题验收工作的通知；福建理工大学主页平台管理系统 Zhang Shuzhong--Home-- 福建省智能加工技术及装备重点实验室；福建理工大学主页平台管理系统 63201833--Home--Scientific Research；福建理工大学主页平台管理系统 Shoujin Zeng--Home--Research Projects；福建理工大学主页平台管理系统 Kong linghua--Home--Scientific Research；科研创新平台</v>
+      </c>
+      <c r="F936" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G936" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H936" t="str" s="3">
+        <v>https://kyc.fjut.edu.cn/2025/0226/c6400a249489/page.htm
+https://faculty.fjut.edu.cn/zhangshuzhong/en/kyxm/42768/content/26447.htm
+https://faculty.fjut.edu.cn/63201833/en/zhym/66399/list/index.htm
+https://faculty.fjut.edu.cn/cengshoujin/en/kyxm/21042/list/index.htm
+https://faculty.fjut.edu.cn/konglinghua/en/zhym/7097/list/index.htm
+https://www.fjut.edu.cn/519/list.htm</v>
+      </c>
+      <c r="I936" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第430项</v>
+      </c>
+    </row>
+    <row r="937" ht="52.5" customHeight="1">
+      <c r="A937" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B937" t="str" s="3">
+        <v>江苏周边未齐全校目录入口</v>
+      </c>
+      <c r="C937" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D937" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E937" t="str" s="3">
+        <v>查询：site:cwxu.edu.cn "科研平台" 实验室 / site:yzu.edu.cn "科研平台（基地）" / site:jsu.edu.cn 省部级 科研平台 机器人 / site:usts.edu.cn 国家级 科技平台；线索：市厅级科研平台-无锡学院；集成电路测试联合实验室-无锡学院集成电路学院；关于中国气象局生态系统碳源汇重点开放实验室2024年度开放课题申请指南-无锡学院大气与遥感学院；关于组织申报科研平台建设资助的通知-无锡学院科学技术处、社会科学处；教学管理研究，创新管理机制，通过设立教学管理研究专项等措施激发创新意识。建立教学关键岗位的竞争上岗机制，选拔懂业务、会管理、有责任感的人员充实教学管理队伍。</v>
+      </c>
+      <c r="F937" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G937" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H937" t="str" s="3">
+        <v>https://www.cwxu.edu.cn/kxyj/kypt1/stjkypt.htm
+https://jdy.cwxu.edu.cn/info/1036/1366.htm
+https://dqy.cwxu.edu.cn/info/1168/3166.htm
+https://kjc.cwxu.edu.cn/info/1058/3956.htm
+https://xxgk.cwxu.edu.cn/__local/B/C9/2C/635E541A5632F651D37651092E3_3D9A1480_21163A.pdf</v>
+      </c>
+      <c r="I937" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第431项</v>
+      </c>
+    </row>
+    <row r="938" ht="52.5" customHeight="1">
+      <c r="A938" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B938" t="str" s="3">
+        <v>福建江西全校目录入口发现</v>
+      </c>
+      <c r="C938" t="str" s="3">
+        <v>福建/江西</v>
+      </c>
+      <c r="D938" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E938" t="str" s="3">
+        <v>查询：site:fjut.edu.cn 省部级 科研平台 重点实验室 / site:fafu.edu.cn 省部级 重点实验室 科研平台 / site:jxust.edu.cn 科研平台 重点实验室 / site:ecjtu.edu.cn 科研平台 省部级；线索：科研平台-江西理工大学科学技术处；科研创新平台；战略有色金属绿色低碳冶金江西省重点实验室-江西理工大学冶金工程学院；《江西发布》：江西第二家省实验室，为何叫赣南实验室-江西理工大学 - JiangXi University of Science and Technology；科技厅-福建省重点实验室管理办法；福建理工大学智能信息处理研究中心</v>
+      </c>
+      <c r="F938" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G938" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H938" t="str" s="3">
+        <v>https://kjc.jxust.edu.cn/kypt/1.htm
+https://www.fjut.edu.cn/512/list.htm
+https://clyjgc.jxust.edu.cn/info/1026/1840.htm
+https://www.jxust.edu.cn/info/1012/34192.htm
+https://kyc.fjut.edu.cn/2026/0119/c6913a263888/page.htm
+https://kyc.fjut.edu.cn/2018/0912/c6157a99136/page.psp</v>
+      </c>
+      <c r="I938" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第432项</v>
+      </c>
+    </row>
+    <row r="939" ht="52.5" customHeight="1">
+      <c r="A939" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B939" t="str" s="3">
+        <v>东北三省教育厅省高校重点室机器人目录补漏</v>
+      </c>
+      <c r="C939" t="str" s="3">
+        <v>辽宁/吉林/黑龙江</v>
+      </c>
+      <c r="D939" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E939" t="str" s="3">
+        <v>查询：site:jyt.ln.gov.cn 重点实验室 机器人 名单 / site:jyt.jl.gov.cn 重点实验室 机器人 名单 / site:jyt.hlj.gov.cn 重点实验室 智能 装备 名单 / site:sut.edu.cn 科研平台 省部级；线索：简介-沈阳工业大学研究生院；一、研究生教育发展整体概况；重点实验室简介-沈阳工业大学新能源研究院；科研平台-沈阳工业大学经济学院；结构振动控制多学科交叉创新研究团队-沈阳工业大学建筑与土木工程学院</v>
+      </c>
+      <c r="F939" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G939" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H939" t="str" s="3">
+        <v>https://yjsxy.sut.edu.cn/fwzn/jj.htm
+https://cfdea.sut.edu.cn/2021yjsndzlbg.pdf
+https://syfd.sut.edu.cn/jspt/zdsysjj.htm
+https://jjxy.sut.edu.cn/kxyj/kypt.htm
+https://jgxy.sut.edu.cn/info/1022/3681.htm</v>
+      </c>
+      <c r="I939" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第433项</v>
+      </c>
+    </row>
+    <row r="940" ht="52.5" customHeight="1">
+      <c r="A940" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B940" t="str" s="3">
+        <v>西南省高校重点实验室省认定入口补漏</v>
+      </c>
+      <c r="C940" t="str" s="3">
+        <v>云南/贵州/广西</v>
+      </c>
+      <c r="D940" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E940" t="str" s="3">
+        <v>查询：site:jyt.gxzf.gov.cn 重点实验室 机器人 名单 / site:jyt.yn.gov.cn 重点实验室 机器人 名单 / site:jyt.guizhou.gov.cn 重点实验室 智能 名单 / site:gzu.edu.cn 重点实验室 开放课题 2026 机器人；线索：贵州省粮油作物优质高效增产全省重点实验室2026年度开放课题申报指南（重点项目）；贵州省粮油作物优质高效增产全省重点实验室2026年度开放课题评审立项结果公示；〖申请指南〗贵州省古生物与古环境全省重点实验室2026年度开放基金申请通知；2026年度重点实验室开放基金申请通知；贵州省生态特色食品新质化加工与贮藏 全省重点实验室开放课题申请指南；天眼新闻：给山地农机装“最强大脑”！贵州重点实验室闯出丘陵山区农机化新路径</v>
+      </c>
+      <c r="F940" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G940" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H940" t="str" s="3">
+        <v>https://st.gzu.edu.cn/2026/0518/c17883a273475/page.htm
+https://agr.gzu.edu.cn/2026/0911/c17664a279354/page.htm
+https://re.gzu.edu.cn/2026/0610/c4729a275572/page.htm
+https://agbr.gzu.edu.cn/2021/0726/c15811a275139/page.htm
+https://st.gzu.edu.cn/2026/0316/c17883a265809/page.htm
+https://www.gzu.edu.cn/2026/0322/c22305a266359/page.htm</v>
+      </c>
+      <c r="I940" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第434项</v>
+      </c>
+    </row>
+    <row r="941" ht="52.5" customHeight="1">
+      <c r="A941" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B941" t="str" s="3">
+        <v>中部省属装备平台年度补漏</v>
+      </c>
+      <c r="C941" t="str" s="3">
+        <v>湖北/湖南/河南</v>
+      </c>
+      <c r="D941" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E941" t="str" s="3">
+        <v>查询：site:wust.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) 2026 / site:hbpu.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) / site:hnust.edu.cn ("开放课题" OR "开放基金") (机器人 OR 感知) 2026 / site:zzuli.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备)；线索：湖北省高校人文社科重点研究基地舆情研究中心2026年度拟立项课题评审结果公示-舆情研究中心（湖北省高校人文社科重点研究基地）；机械传动与制造工程湖北省重点实验室2026年度开放基金申报通知-机械传动与制造工程湖北省重点实验室；湖北省重点实验室管理暂行办法-肾脏疾病发生与干预湖北省重点实验室；王宪_湖南科技大学海洋实验室；6. 开放课题成果的奖励费用。；关于矿区环境污染控制与修复湖北省重点实验室2025年度开放课题申报的通知-湖北理工学院矿区环境污染控制与修复湖北省重点实验室</v>
+      </c>
+      <c r="F941" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G941" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H941" t="str" s="3">
+        <v>https://yqyjzx.wust.edu.cn/info/1962/2931.htm
+https://jxcd.wust.edu.cn/info/1201/3011.htm
+https://rdpi.hbpu.edu.cn/info/1110/1095.htm
+https://hys.hnust.edu.cn/yjdw/hdzywhtzbyjsyjry/ee29ac13743f42b9a77fd52abc673da9.htm
+https://mzh.wust.edu.cn/wuhankejidaxuemeizhuanhuayuxinxingtancailiaohubeishengzhongdianshiyanshi2025niandukaifangjijinshenqingzhinan.pdf
+https://kqhj.hbpu.edu.cn/info/1145/1613.htm</v>
+      </c>
+      <c r="I941" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第435项</v>
+      </c>
+    </row>
+    <row r="942" ht="52.5" customHeight="1">
+      <c r="A942" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B942" t="str" s="3">
+        <v>福建理工全校目录相关平台机制第一组</v>
+      </c>
+      <c r="C942" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D942" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E942" t="str" s="3">
+        <v>查询：site:fjut.edu.cn ("汽车电子与电驱动" OR "智能无人驾驶" OR "工业控制及数据分析") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:fjut.edu.cn ("工业制造物联网" OR "工业集成自动化" OR "工业自动化") ("开放基金" OR "开放课题") / site:fjut.edu.cn ("数控装备产业技术" OR "机床行业技术" OR "智能装备服务型制造") ("开放基金" OR "开放课题")；线索：关于做好2024年度福建理工大学重点科研创新平台开放基金项目结题验收工作的通知</v>
+      </c>
+      <c r="F942" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G942" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H942" t="str" s="3">
+        <v>https://kyc.fjut.edu.cn/2024/0306/c6400a229809/page.htm</v>
+      </c>
+      <c r="I942" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第436项</v>
+      </c>
+    </row>
+    <row r="943" ht="52.5" customHeight="1">
+      <c r="A943" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B943" t="str" s="3">
+        <v>福建理工全校目录相关平台机制第二组</v>
+      </c>
+      <c r="C943" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D943" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E943" t="str" s="3">
+        <v>查询：site:fjut.edu.cn ("模具工程技术" OR "精确成型制造" OR "智能绿色模具") ("开放基金" OR "开放课题") / site:fjut.edu.cn ("北斗导航与智慧交通" OR "隧道工程灾变" OR "新能源汽车控制系统") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F943" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G943" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H943" t="str" s="3"/>
+      <c r="I943" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第437项</v>
+      </c>
+    </row>
+    <row r="944" ht="52.5" customHeight="1">
+      <c r="A944" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B944" t="str" s="3">
+        <v>扬州大学官方目录与合作机制发现</v>
+      </c>
+      <c r="C944" t="str" s="3">
+        <v>江苏·扬州</v>
+      </c>
+      <c r="D944" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E944" t="str" s="3">
+        <v>查询：site:yzu.edu.cn "科研平台" "机器" / site:yzu.edu.cn "重点实验室" "机器人" "开放" / site:yzu.edu.cn "科学技术处" "科研平台"；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F944" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G944" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H944" t="str" s="3"/>
+      <c r="I944" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第438项</v>
+      </c>
+    </row>
+    <row r="945" ht="52.5" customHeight="1">
+      <c r="A945" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B945" t="str" s="3">
+        <v>福建理工校级统一开放基金及管理办法</v>
+      </c>
+      <c r="C945" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D945" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E945" t="str" s="3">
+        <v>查询：福建理工大学 开放基金 2026 / 福建理工大学 开放基金 2025 申请 通知 / "福工大科研" "2024" "14" 开放基金 / 福建理工大学 重点科研创新平台 开放基金 申请；线索：关于做好2026年度福建理工大学重点科研创新平台开放基金项目结题验收工作的通知；科研平台通知；海洋智能装备福建省高校重点实验室2025年度开放基金申请指南；功能晶体与器件全国重点实验室开放基金课题申请指南（2026年度）&lt;br/&gt;--功能晶体与器件全国重点实验室；2026“柔性制造装备集成福建省高校重点实验室”开放课题研究基金申报指南；转发《福建省科学技术厅等六部门关于开展2018年高水平科技研发创新平台补助经费申请工作的通知》的通知</v>
+      </c>
+      <c r="F945" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G945" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H945" t="str" s="3">
+        <v>https://kyc.fjut.edu.cn/2026/0512/c6400a267638/page.htm
+https://kyc.fjut.edu.cn/kypt_6400/list.htm
+https://hyy.fjut.edu.cn/2025/0617/c10557a255474/page.htm
+https://www.fjirsm.ac.cn/sklfcd/tzgg/202605/t20260508_8197508.html
+https://www.xit.edu.cn/kxyj/2026/0206/c1174a83598/page.htm
+https://www.fafu.edu.cn/2018/0510/c136a30737/pagem.htm</v>
+      </c>
+      <c r="I945" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第439项</v>
+      </c>
+    </row>
+    <row r="946" ht="52.5" customHeight="1">
+      <c r="A946" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B946" t="str" s="3">
+        <v>无锡苏州测控省市平台精准机制</v>
+      </c>
+      <c r="C946" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D946" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E946" t="str" s="3">
+        <v>查询："无锡市高端装备核心零部件" 开放 / "无锡市车联网重点实验室" 开放基金 / "苏州市共融机器人技术重点实验室" 开放基金 / "江苏省智能共融机器人工程研究中心" 开放课题；线索：序号 1 | 实验室名称 无锡市光伏电池及组件技术；苏州市共融机器人技术重点实验室-科技产业处；我区6家企业获无锡市重点实验室立项；我校举行“无锡学院 无锡市产业创新研究院”合作签约活动-无锡学院；江苏省大地感知与控灾工程研究中心</v>
+      </c>
+      <c r="F946" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G946" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H946" t="str" s="3">
+        <v>https://www.jetionsolar.com/Upload/2026/01/5fa5287a7cea44ce8ea06588db9be75d.pdf
+https://kjcyc.usts.edu.cn/info/1024/4810.htm
+https://www.jsxishan.gov.cn/doc/2025/02/18/4501852.shtml
+https://www.cwxu.edu.cn/info/1033/17937.htm
+https://file.smejs.cn/group1/M00/05/17/rBIAAWUShMSABeQlAAJW9x4lK-M692.pdf</v>
+      </c>
+      <c r="I946" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第440项</v>
+      </c>
+    </row>
+    <row r="947" ht="52.5" customHeight="1">
+      <c r="A947" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B947" t="str" s="3">
+        <v>扬州镇江高校智能装备平台精准机制</v>
+      </c>
+      <c r="C947" t="str" s="3">
+        <v>江苏</v>
+      </c>
+      <c r="D947" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E947" t="str" s="3">
+        <v>查询：扬州大学 开放基金 2026 机械 / 扬州大学 科研平台 重点实验室 目录 / 江苏大学 开放基金 2026 机器人 / 江苏大学 江苏省重点实验室 开放课题 2027；线索：扬州大学重点实验室-中国高校库-中国高校之窗；2027年度航空航天结构力学及控制全国重点实验室开放课题申请通知；江苏省生态环境厅 公告公示 生态环境部地表水环境有机污染物监测分析重点实验室2026年开放基金课题申报指南；江苏省高校通用人工智能与大模型重点实验室开放课题申报指南；江苏省重点实验室2019年度建设与运行报表；江苏省低维材料物理与物态调控高校重点实验室2026年度开放课题申报通知-江苏省低维材料物理与物态调控高校重点实验室</v>
+      </c>
+      <c r="F947" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G947" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H947" t="str" s="3">
+        <v>https://www.gx211.cn/collegemanage/content386_06.shtml
+https://skl.nuaa.edu.cn/2026/0905/c4738a409560/page.htm
+https://sthjt.jiangsu.gov.cn/art/2026/8/19/art_83844_11818138.html
+https://future.suda.edu.cn/e8/2a/c30836a714794/page.htm
+https://kjc.seu.edu.cn/_upload/article/files/64/16/3f10eb90424e95483ebe7630128c/8ab96c98-cd42-433b-8279-245e89a9ea55.pdf
+https://nic.cumt.edu.cn/dwclwl/info/1022/1201.htm</v>
+      </c>
+      <c r="I947" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第441项</v>
+      </c>
+    </row>
+    <row r="948" ht="52.5" customHeight="1">
+      <c r="A948" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B948" t="str" s="3">
+        <v>研究院所全国机器人开放平台遗漏类型</v>
+      </c>
+      <c r="C948" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D948" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E948" t="str" s="3">
+        <v>查询：省科学院 机器人 开放基金 2026 / 工业技术研究院 机器人 开放课题 2026 / 计量科学研究院 开放基金 2026 智能 装备 / 中国机械科学研究总院 开放课题 2026；线索：2026年度开放课题申请公告；中国标准化研究院2026年度省部级重点&lt;br&gt;实验室开放基金项目申报指南；高速公路筑养装备与技术教育部工程研究中心2026年开放基金申请指南；部门新闻·重庆城市职业学院关于申报2026年度工业机器人运维重庆市高校工程中心开放课题的通知；其他公开信息-中国机械科学研究总院集团有限公司；2026年度开放基金评审结果公告</v>
+      </c>
+      <c r="F948" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G948" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H948" t="str" s="3">
+        <v>https://robot.hit.edu.cn/2025/1015/c277a379743/page.htm
+https://www.cnis.ac.cn/wap/dh/tzgg/202609/t20260904_63600.html
+https://webplus.chd.edu.cn/_s204/2026/0605/c8633a261026/page.psp
+https://kyc.cqcvc.edu.cn/info.thtml?cid=74479&amp;pn=&amp;t=11322
+https://www.cifmt.cn/channels/649.html
+https://robot.hit.edu.cn/2026/0120/c277a386529/page.htm</v>
+      </c>
+      <c r="I948" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第442项</v>
+      </c>
+    </row>
+    <row r="949" ht="52.5" customHeight="1">
+      <c r="A949" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B949" t="str" s="3">
+        <v>中央高校业务费对外开放平台再交叉</v>
+      </c>
+      <c r="C949" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D949" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E949" t="str" s="3">
+        <v>查询："基本科研业务费" "开放基金" "2027" / "基本科研业务费" "开放基金" "2026" 机器人 / "基本科研业务费" "开放课题" "2026" "校外" / "重点科研平台" "开放基金" "2026" 智能；线索：关于做好2026年度福建理工大学重点科研创新平台开放基金项目结题验收工作的通知；中国地震局工程力学研究所2027年度基本科研业务费专项实验室开放基金项目申报指南 中国地震局工程力学研究所；图像信息处理与智能控制教育部重点实验室2026年度开放课题指南；关于申请2026年度南京航空航天大学基本科研业务费民航飞机健康监测与智能维护重点实验室自主课题的通知；云南省复杂系统与类脑智能重点实验室（筹）2026 年度开放基金申请指南-昆明理工大学理学院；云南省马铃薯生物学重点实验室开放基金申请通知-云南师范大学生命科学学院</v>
+      </c>
+      <c r="F949" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G949" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H949" t="str" s="3">
+        <v>https://kyc.fjut.edu.cn/2026/0512/c6400a267638/page.htm
+https://iem.ac.cn/zxgl/info?id=4400
+https://aia.hust.edu.cn/info/1174/11568.htm
+https://cca.nuaa.edu.cn/_t862/2026/0627/c15585a402933/page.htm
+https://lxy.kust.edu.cn/info/1151/2522.htm
+https://life.ynnu.edu.cn/info/1048/2855.htm</v>
+      </c>
+      <c r="I949" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第443项</v>
+      </c>
+    </row>
+    <row r="950" ht="52.5" customHeight="1">
+      <c r="A950" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B950" t="str" s="3">
+        <v>福建理工市校完整目录机器人装备机制补漏</v>
+      </c>
+      <c r="C950" t="str" s="3">
+        <v>福建</v>
+      </c>
+      <c r="D950" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E950" t="str" s="3">
+        <v>查询：site:fjut.edu.cn ("智能机器人研究所" OR "人工智能研究所" OR "智能信息处理研究中心") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:fjut.edu.cn ("高效精密加工" OR "能源装备与储能安全" OR "桥梁创新设计") ("开放基金" OR "开放课题") / site:fjut.edu.cn ("智能制造装备行业" OR "增材制造创新中心装备" OR "汽车机电行业") ("开放基金" OR "开放课题") / site:fjut.edu.cn ("工业集成自动化行业" OR "智能无人驾驶技术") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F950" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G950" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H950" t="str" s="3"/>
+      <c r="I950" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第444项</v>
+      </c>
+    </row>
+    <row r="951" ht="52.5" customHeight="1">
+      <c r="A951" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B951" t="str" s="3">
+        <v>东北智能制造省属院校第二组</v>
+      </c>
+      <c r="C951" t="str" s="3">
+        <v>辽宁/吉林/黑龙江</v>
+      </c>
+      <c r="D951" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E951" t="str" s="3">
+        <v>查询：site:djtu.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) / site:usth.edu.cn ("开放课题" OR "开放基金") (机器人 OR 感知) / site:jmsu.edu.cn ("开放课题" OR "开放基金") (机器人 OR 农机) / site:beihua.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备)；线索：大连交通大学2026年博士研究生招生专业目录 - 大连交通大学研究生工作处；佳木斯大学实验室开放管理规定-佳木斯大学外国语学院；黑龙江科技大学全日制专业学位硕士研究生培养方案（龙江工程师学院）</v>
+      </c>
+      <c r="F951" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G951" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H951" t="str" s="3">
+        <v>https://gs.djtu.edu.cn/6/593.html?tpid=47
+https://wgy.jmsu.edu.cn/info/1086/9298.htm
+https://ceie.usth.edu.cn/__local/0/63/09/5E3604DAF54F39FDB8ED36278F5_1D50369A_40A61.pdf</v>
+      </c>
+      <c r="I951" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第445项</v>
+      </c>
+    </row>
+    <row r="952" ht="52.5" customHeight="1">
+      <c r="A952" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B952" t="str" s="3">
+        <v>山东河南省属装备平台第二组</v>
+      </c>
+      <c r="C952" t="str" s="3">
+        <v>山东/河南</v>
+      </c>
+      <c r="D952" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E952" t="str" s="3">
+        <v>查询：site:sdjtu.edu.cn ("开放课题" OR "开放基金") 智能 / site:qust.edu.cn ("开放课题" OR "开放基金") 机器人 / site:qut.edu.cn ("开放课题" OR "开放基金") 装备 2026 / site:hnpust.edu.cn ("开放课题" OR "开放基金") 机器人；线索：云基物联网高速公路建养设备智能化实验室开放课题指南-云基物联网高速公路建养设备智能化实验室；低空飞行智能服务保障山东省工程研究中心 2024年度开放课题申报指南-数据科学学院；2025年度橡塑材料与工程教育部重点实验室 开放课题项目申报通知-青岛科技大学高分子科学与工程学院；光电传感与生命分析教育部重点实验室2024年度开放基金申报通知-青岛科技大学；关于开展2024年度重点实验室开放课题申报的通知-山东交通学院交通行业重点实验室；王洪振-橡塑材料与工程教育部重点实验室</v>
+      </c>
+      <c r="F952" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G952" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H952" t="str" s="3">
+        <v>https://cloudhighway.sdjtu.edu.cn/info/1029/1271.htm
+https://sjkx.qust.edu.cn/info/1061/1542.htm
+https://gfz.qust.edu.cn/info/1072/3557.htm
+https://www.qust.edu.cn/info/1553/27795.htm
+https://qcvdlab.sdjtu.edu.cn/info/1003/1452.htm
+https://rubber.qust.edu.cn/info/1024/3151.htm</v>
+      </c>
+      <c r="I952" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第446项</v>
+      </c>
+    </row>
+    <row r="953" ht="52.5" customHeight="1">
+      <c r="A953" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B953" t="str" s="3">
+        <v>浙江安徽省属装备平台第二组</v>
+      </c>
+      <c r="C953" t="str" s="3">
+        <v>浙江/安徽</v>
+      </c>
+      <c r="D953" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E953" t="str" s="3">
+        <v>查询：site:zjweu.edu.cn ("开放课题" OR "开放基金") 智能 / site:nbut.edu.cn ("开放课题" OR "开放基金") 机器人 / site:ahut.edu.cn ("开放课题" OR "开放基金") (机器人 OR 装备) 2026 / site:ahjzu.edu.cn ("开放课题" OR "开放基金") 机器人；线索：安徽省特种重载机器人重点实验室2026年度开放基金申请指南 -特种重载机器人安徽省重点实验室；关于安徽省特种重载机器人重点实验室2026年度开放基金项目评审结果的公示-特种重载机器人安徽省重点实验室；开放基金课题合同书、任务书；2026年煤清洁转化与高值化利用安徽省重点实验室开放课题申请指南-煤清洁转化与高值化利用安徽省重点实验室；安徽省智能破拆装备工程实验室2025年度开放基金拟资助项目公示-欢迎访问安徽工业大学门户网站！；冶金减排与资源综合利用教育部重点实验室2026年度开放基金申请指南-安徽工业大学公开网（党务校务公开网）</v>
+      </c>
+      <c r="F953" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G953" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H953" t="str" s="3">
+        <v>https://robotlab.ahut.edu.cn/info/1549/1412.htm
+https://robotlab.ahut.edu.cn/info/1549/1418.htm
+https://www.ahjzu.edu.cn/gjgcsys/2024/0517/c9702a232756/page.htm
+https://ccchvu.ahut.edu.cn/info/1176/1336.htm?urltype=tree.TreeTempUrl&amp;wbtreeid=1209
+https://www.ahut.edu.cn/info/1103/27706.htm
+https://xwgk.ahut.edu.cn/info/4879/26686.htm</v>
+      </c>
+      <c r="I953" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第447项</v>
+      </c>
+    </row>
+    <row r="954" ht="52.5" customHeight="1">
+      <c r="A954" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B954" t="str" s="3">
+        <v>海南西北省属装备平台第二组</v>
+      </c>
+      <c r="C954" t="str" s="3">
+        <v>海南/甘肃/宁夏/青海/新疆</v>
+      </c>
+      <c r="D954" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E954" t="str" s="3">
+        <v>查询：site:hnnu.edu.cn ("开放课题" OR "开放基金") 机器人 / site:nxu.edu.cn ("开放课题" OR "开放基金") 装备 2026 / site:lut.edu.cn ("开放课题" OR "开放基金") 机器人 2026 / site:xju.edu.cn ("开放课题" OR "开放基金") 智能 2026；线索：成套装备智能化集成技术教育部重点实验室开放课题申报指南（2026年度）-兰州理工大学机电学院 | 兰州理工大学机电工程学院，理工大学机电工程学院，兰州工大机电工程学院，兰州工大机电学院，工大机电学院，；特种泵阀及流控系统教育部重点实验室2026年度开放基金申请指南-能源与动力工程学院；新疆智能与绿色纺织重点实验室开放课题申报指南-新疆大学纺织与服装学院；新疆历史文化旅游可持续发展重点实验室规章制度-新疆历史文化旅游可持续发展重点实验室；新疆特种机器人与智能控制工程技术研究中心；新疆农牧机器人及智能装备工程研究中心学术委员会</v>
+      </c>
+      <c r="F954" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G954" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H954" t="str" s="3">
+        <v>https://jidian.lut.edu.cn/info/1924/18496.htm
+https://ndxy.lut.edu.cn/info/1077/7544.htm
+https://ffxy.xju.edu.cn/info/1054/3133.htm
+https://hct.xju.edu.cn/info/1143/1264.htm
+https://jxxy.xju.edu.cn/__local/3/ED/01/57D53B8402BA6F8B6249E4AC47A_64A19621_10EB5E.pdf
+https://https-jxxy-xju-edu-cn-443.webvpn1.xju.edu.cn/__local/0/23/6F/B2938303B9580E6741F5D6F72BE_A1C96726_4AE3B.pdf</v>
+      </c>
+      <c r="I954" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第448项</v>
+      </c>
+    </row>
+    <row r="955" ht="52.5" customHeight="1">
+      <c r="A955" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B955" t="str" s="3">
+        <v>全国新年度机器人任务关键词末端补漏</v>
+      </c>
+      <c r="C955" t="str" s="3">
+        <v>全国</v>
+      </c>
+      <c r="D955" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E955" t="str" s="3">
+        <v>查询："开放课题" "2027" "机器人" / "开放基金" "2026" "力控" / "开放课题" "2026" "自主避障" / "开放基金" "2026" "阻抗"；线索：机器人与智能系统全国重点实验室 2025年度开放课题申请指南--中国科学院沈阳自动化研究所；智能制造装备与技术全国重点实验室2027年度开放课题申请通知-智能制造装备与技术全国重点实验室；〖27届校招〗世界模型研究员_广州小鹏汽车科技有限公司校招_牛客网；先进轨道交通自主运行全国重点实验室 开放课题基金申请指南（2027年） - 先进轨道交通自主运行全国重点实验室；警用智能机器人达州市重点实验室2026年度开放基金申报公告-警用智能机器人达州市重点实验室；江苏省工业人工智能重点实验室2026年度开放课题申请通知-- 中国科学院工业人工智能研究所</v>
+      </c>
+      <c r="F955" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G955" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H955" t="str" s="3">
+        <v>https://www.sia.ac.cn/xwzx/tzgg/202507/t20250711_7884994.html
+https://imet.hust.edu.cn/info/1031/2870.htm
+https://www.nowcoder.com/jobs/detail/461376
+https://raolab.bjtu.edu.cn/news/3521.html
+https://jqr.sasu.edu.cn/info/1009/1061.htm
+https://iaii.cas.cn/hzjl/kjhz/202607/t20260715_8248969.html</v>
+      </c>
+      <c r="I955" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第449项</v>
+      </c>
+    </row>
+    <row r="956" ht="52.5" customHeight="1">
+      <c r="A956" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B956" t="str" s="3">
+        <v>新发现长期机制2026—2027补漏</v>
+      </c>
+      <c r="C956" t="str" s="3">
+        <v>山东/安徽</v>
+      </c>
+      <c r="D956" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E956" t="str" s="3">
+        <v>查询：site:cloudhighway.sdjtu.edu.cn 开放课题 2026 2027 / site:qust.edu.cn "低空飞行智能服务保障" ("2026" OR "2027" OR "2025") 开放 / site:ahjzu.edu.cn "工程机械智能制造" "开放" ("2026" OR "2027" OR "2025") / site:ahjzu.edu.cn "智能地下探测" "开放" ("2026" OR "2027" OR "2025")；线索：云基物联网高速公路建养设备智能化实验室开放课题指南-云基物联网高速公路建养设备智能化实验室；潘为刚主任-云基物联网高速公路建养设备智能化实验室</v>
+      </c>
+      <c r="F956" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G956" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H956" t="str" s="3">
+        <v>https://cloudhighway.sdjtu.edu.cn/info/1029/1271.htm
+https://cloudhighway.sdjtu.edu.cn/info/1005/1073.htm</v>
+      </c>
+      <c r="I956" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第450项</v>
+      </c>
+    </row>
+    <row r="957" ht="52.5" customHeight="1">
+      <c r="A957" t="str" s="3">
+        <v>2026-10-09天津福建完整目录及跨省年度机制补漏</v>
+      </c>
+      <c r="B957" t="str" s="3">
+        <v>港澳机器人对外开放现金机制目录末端交叉</v>
+      </c>
+      <c r="C957" t="str" s="3">
+        <v>澳门/香港</v>
+      </c>
+      <c r="D957" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E957" t="str" s="3">
+        <v>查询：site:um.edu.mo "open research" "fund" robotics 2026 / site:must.edu.mo "开放" "基金" 机器人 / site:polyu.edu.hk "open fund" robotics 2026 / site:hkust.edu.hk "open research" "fund" robotics 2026；线索：Out-of-order execution enabled deep reinforcement learning for dynamic additive manufacturing scheduling | PolyU Institutional Research Archive；澳科大「香山文化知识库」正式上线，活化史料助力研究 - 澳门科技大学 - 科大新闻；聯合研究基金與支持項目 | SKLCRCC；Funding Support by SKL-CRCC | SKLCRCC</v>
+      </c>
+      <c r="F957" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G957" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H957" t="str" s="3">
+        <v>https://ira.lib.polyu.edu.hk/handle/10397/115393?mode=full
+https://www.must.edu.mo/id-13630/article/view/id-41048.html?locale=zh_CN
+https://www.polyu.edu.hk/sklcrcc/research/funding-support/?sc_lang=tc
+https://www.polyu.edu.hk/sklcrcc/research/funding-support/</v>
+      </c>
+      <c r="I957" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第451项</v>
+      </c>
+    </row>
+    <row r="958" ht="52.5" customHeight="1">
+      <c r="A958" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B958" t="str" s="3">
+        <v>中国地震局工程力学研究所</v>
+      </c>
+      <c r="C958" t="str" s="3">
+        <v>依托地区待官方目录核实</v>
+      </c>
+      <c r="D958" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E958" t="str" s="3">
+        <v>基本科研业务费专项实验室开放基金项目；2027；N070；官方搜索定位2027业务费实验室开放基金申报指南；正文首次不可访问停止</v>
+      </c>
+      <c r="F958" t="str" s="3">
+        <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
+      </c>
+      <c r="G958" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H958" t="str" s="3">
+        <v>https://iem.ac.cn/zxgl/info?id=4400</v>
+      </c>
+      <c r="I958" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="959" ht="52.5" customHeight="1">
+      <c r="A959" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B959" t="str" s="3">
+        <v>长安大学</v>
+      </c>
+      <c r="C959" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D959" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E959" t="str" s="3">
+        <v>公路大型结构安全教育部工程研究中心；2026；N071；2026正式完整正文已取；任务仅概括结构检测/监测，3附件下载页或工具异常未获原件</v>
+      </c>
+      <c r="F959" t="str" s="3">
+        <v>需具体智能检测装备任务证据；3附件原件未取：申请DOC/高质量期刊目录/学校学术期刊目录；确认B/C/D目录口径及经费外拨报销。</v>
+      </c>
+      <c r="G959" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H959" t="str" s="3">
+        <v>https://highway.chd.edu.cn/info/1015/24577.htm</v>
+      </c>
+      <c r="I959" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="960" ht="52.5" customHeight="1">
+      <c r="A960" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B960" t="str" s="3">
+        <v>青岛科技大学</v>
+      </c>
+      <c r="C960" t="str" s="3">
+        <v>山东·青岛</v>
+      </c>
+      <c r="D960" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E960" t="str" s="3">
+        <v>低空飞行智能服务保障山东省工程研究中心；2024；N072；2024正式指南完整正文已取得；申请DOCX首次不支持</v>
+      </c>
+      <c r="F960" t="str" s="3">
+        <v>申请DOCX首不支持；金额未公布、外拨/垫支/验收数量署名IP需合同补。2025—2027机制查未定位新正式指南，不写无。</v>
+      </c>
+      <c r="G960" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H960" t="str" s="3">
+        <v>https://sjkx.qust.edu.cn/info/1061/1542.htm</v>
+      </c>
+      <c r="I960" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="961" ht="52.5" customHeight="1">
+      <c r="A961" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B961" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="C961" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="D961" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E961" t="str" s="3">
+        <v>安徽省工程机械智能制造重点实验室（2019省教育厅批准建设）；2022；N073；标题2022年度指南、2023-02-09发布且02-20截止，完整正文已取；3个DOC首不支持</v>
+      </c>
+      <c r="F961" t="str" s="3">
+        <v>管理办法/申请书/任务书3DOC首次不支持；补经费外拨报销支付/IP、CSCD与会议成果组合及签章。2025—2027年度新指南未定位不声明无。</v>
+      </c>
+      <c r="G961" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H961" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/2023/0209/c145a209128/page.htm</v>
+      </c>
+      <c r="I961" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="962" ht="52.5" customHeight="1">
+      <c r="A962" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B962" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="C962" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="D962" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E962" t="str" s="3">
+        <v>安徽省智能地下探测重点实验室；2023；N074；首次成功取得正文至一般课题结题要求；页尾续读首次超时停止</v>
+      </c>
+      <c r="F962" t="str" s="3">
+        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+      </c>
+      <c r="G962" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H962" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/cptulab/2023/1129/c13219a225180/page.htm</v>
+      </c>
+      <c r="I962" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="963" ht="52.5" customHeight="1">
+      <c r="A963" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B963" t="str" s="3">
+        <v>天津理工大学</v>
+      </c>
+      <c r="C963" t="str" s="3">
+        <v>天津</v>
+      </c>
+      <c r="D963" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E963" t="str" s="3">
+        <v>市15牌目已取后补国家/部委目录；部目录4条全文（视觉/学习型智能2机器人平台已逐名查）；先进机电/智能计算简介全文，前者明确微纳并联移动机器人及力载荷组织工程，2026—2027/历史机制查询。</v>
+      </c>
+      <c r="F963" t="str" s="3">
+        <v>国家目录仅导航空页、未明确共0，不能认定无国家平台，人工核名单；其他材料平台年度任务未全，校级/新重组未齐。</v>
+      </c>
+      <c r="G963" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H963" t="str" s="3">
+        <v>https://kjc.tjut.edu.cn/kyjd/gjjkyjd.htm
+https://kjc.tjut.edu.cn/kyjd/gbwkyjd.htm
+https://kjc.tjut.edu.cn/info/1053/1071.htm
+https://kjc.tjut.edu.cn/info/1053/1070.htm</v>
+      </c>
+      <c r="I963" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="964" ht="52.5" customHeight="1">
+      <c r="A964" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B964" t="str" s="3">
+        <v>福建理工大学</v>
+      </c>
+      <c r="C964" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="D964" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E964" t="str" s="3">
+        <v>2026-09-10更新省部65牌目全文，省高校/协同/工程室均含；市厅栏目3页30条、校级4页49条全部页读，栏目有省高校重复条目不可按栏目重复计；海洋学院6平台全文。20余机器人/装备/无人驾驶/模具/制造物联/测控/交通/AI相关名机制2026—2027及旧年度查；机器人所4实际方向全文。</v>
+      </c>
+      <c r="F964" t="str" s="3">
+        <v>省部+市校目录不是144独立机器人平台；余下平台实际任务/各自通知未全。科研平台通知3页2023-12至2026-09全部查但页面总数41/42不一致，不强称准确42；年度申报只N067海洋2025，2026结题针对2023，未视新受理。开放基金办法网页仅标题空白交N067人工。</v>
+      </c>
+      <c r="G964" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H964" t="str" s="3">
+        <v>https://www.fjut.edu.cn/519/list.htm
+https://kyc.fjut.edu.cn/stjpt/list.htm
+https://kyc.fjut.edu.cn/xjpt/list.htm
+https://kyc.fjut.edu.cn/kypt_6400/list.htm
+https://kyc.fjut.edu.cn/2024/1203/c6913a244712/page.htm
+https://kyc.fjut.edu.cn/2020/1222/c6157a164479/page.psp</v>
+      </c>
+      <c r="I964" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="965" ht="52.5" customHeight="1">
+      <c r="A965" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B965" t="str" s="3">
+        <v>无锡学院</v>
+      </c>
+      <c r="C965" t="str" s="3">
+        <v>江苏·无锡</v>
+      </c>
+      <c r="D965" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E965" t="str" s="3">
+        <v>市厅完整3条平台目录；2026-03装备零部件介绍全文，高精检测/多传感融合/车间动态协同感知自主决策明确，基金精确名称查询；车联网简介首次超时、省部目录首次超时。工业机器人实践中心为教学不冒资金。</v>
+      </c>
+      <c r="F965" t="str" s="3">
+        <v>省部完整名单、车联网实际任务、各平台年度开放资助尚缺，人工2入口；无公告不能编当前项目。</v>
+      </c>
+      <c r="G965" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H965" t="str" s="3">
+        <v>https://www.cwxu.edu.cn/kxyj/kypt1/stjkypt.htm
+https://www.cwxu.edu.cn/info/1395/20359.htm
+https://www.cwxu.edu.cn/kxyj/kypt1/sbjkypt.htm
+https://www.cwxu.edu.cn/info/1395/17282.htm</v>
+      </c>
+      <c r="I965" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="966" ht="52.5" customHeight="1">
+      <c r="A966" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B966" t="str" s="3">
+        <v>苏州科技大学/江苏周边</v>
+      </c>
+      <c r="C966" t="str" s="3">
+        <v>江苏·苏州/扬州/镇江</v>
+      </c>
+      <c r="D966" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E966" t="str" s="3">
+        <v>苏科国家目录明示1条污水资源化国家地方工程室，省18/市28已取后机制精确查；扬州及镇江补漏，域名jsu与ujs区别，跨省出现结果按实际单位归属，南航M152/苏医2026立项复用。</v>
+      </c>
+      <c r="F966" t="str" s="3">
+        <v>苏科校级已有人工，协同目录未取；扬州全校科研平台名单未定位，机构不完成；非官方zbsjzx仿页面不当扬州官方目录。</v>
+      </c>
+      <c r="G966" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H966" t="str" s="3">
+        <v>https://kjcyc.usts.edu.cn/kjpt/gjj.htm</v>
+      </c>
+      <c r="I966" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="967" ht="52.5" customHeight="1">
+      <c r="A967" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B967" t="str" s="3">
+        <v>江西理工大学</v>
+      </c>
+      <c r="C967" t="str" s="3">
+        <v>江西</v>
+      </c>
+      <c r="D967" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E967" t="str" s="3">
+        <v>科研平台目录第1.htm入口首次不可访问停止，保存官方URL；机制查询稀土检测2026等仅标题，不凭装备词认相关。</v>
+      </c>
+      <c r="F967" t="str" s="3">
+        <v>完整国家/省高校/校级平台名单及年度未取得，目录交人工；未查完。</v>
+      </c>
+      <c r="G967" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H967" t="str" s="3">
+        <v>https://kjc.jxust.edu.cn/kypt/1.htm</v>
+      </c>
+      <c r="I967" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="968" ht="52.5" customHeight="1">
+      <c r="A968" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B968" t="str" s="3">
+        <v>山东交通/青岛科技</v>
+      </c>
+      <c r="C968" t="str" s="3">
+        <v>山东</v>
+      </c>
+      <c r="D968" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E968" t="str" s="3">
+        <v>山东交通云基2022首次正文超时，但本次官方搜索缓存明确机器人导航/编队任务、一般无资助青年只本校在读生，E087排除个人拿钱清单。N072青科低空2024完整9任务，金额未载，首≤40%验收拨余，申请表首异常；2025—2027机制查。</v>
+      </c>
+      <c r="F968" t="str" s="3">
+        <v>山东交通智能建造省室2025标题又出现须对账后接续；全校目录未齐；现金支持不由机器人任务自动推得，不把青年1—2万给校外研究者。</v>
+      </c>
+      <c r="G968" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H968" t="str" s="3">
+        <v>https://cloudhighway.sdjtu.edu.cn/info/1029/1271.htm
+https://sjkx.qust.edu.cn/info/1061/1542.htm</v>
+      </c>
+      <c r="I968" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="969" ht="52.5" customHeight="1">
+      <c r="A969" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B969" t="str" s="3">
+        <v>安徽建筑大学</v>
+      </c>
+      <c r="C969" t="str" s="3">
+        <v>安徽·合肥</v>
+      </c>
+      <c r="D969" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E969" t="str" s="3">
+        <v>N073标题2022、2023发布/截止，全文仅校外开放约3万/2题；主任校内约2万排除外校类别。N074地下2023正文仅前段，首次续读超时：深海装备仍概括待核；2025—2027新年度查。</v>
+      </c>
+      <c r="F969" t="str" s="3">
+        <v>全校省高校目录未齐；N073三DOC与N074完整指南交人工；不能套徐工全国室M023或把2022公告改2023批。</v>
+      </c>
+      <c r="G969" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H969" t="str" s="3">
+        <v>https://www.ahjzu.edu.cn/2023/0209/c145a209128/page.htm
+https://www.ahjzu.edu.cn/cptulab/2023/1129/c13219a225180/page.htm</v>
+      </c>
+      <c r="I969" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="970" ht="52.5" customHeight="1">
+      <c r="A970" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B970" t="str" s="3">
+        <v>研究院所业务费/全国及港澳交叉</v>
+      </c>
+      <c r="C970" t="str" s="3">
+        <v>全国/澳门/香港</v>
+      </c>
+      <c r="D970" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E970" t="str" s="3">
+        <v>N070工程力学2027业务费首次不可访问；N071长安结构2026全文但无具体robot任务待核。中央业务费/研究所/高校私立类型宽查，厦门M102、重庆M103、标准院M148、HUST M0292027/N0252026、兰理E078、澳门M165及排除M123/M164复用。</v>
+      </c>
+      <c r="F970" t="str" s="3">
+        <v>发现查询不当31省逐目录全覆盖；港澳轨道funding与新澳门芯片镜像须先历史对账，未重开；中央业务费外部资格逐公告核。</v>
+      </c>
+      <c r="G970" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H970" t="str" s="3">
+        <v>https://iem.ac.cn/zxgl/info?id=4400
+https://highway.chd.edu.cn/info/1015/24577.htm</v>
+      </c>
+      <c r="I970" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -51306,23 +52862,63 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="117" ht="96" customHeight="1">
+    <row r="117" ht="192" customHeight="1">
       <c r="A117" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B117" t="n" s="13">
+        <v>45427</v>
+      </c>
+      <c r="C117" t="str" s="14">
+        <v>青岛科技大学·低空飞行智能服务保障山东省工程研究中心</v>
+      </c>
+      <c r="D117" t="str" s="15">
+        <v>崂山校区三维低空保障软硬件闭环验证平台；三维实景地图无人值守机场动态航线规划/评估及高度速度相机航点动作；地面目标多传感融合深度识别跟踪；环境/关系/历史航迹预测碰撞避免与预警；视觉激光雷达多模态三维重建/避障/盲降；消防无人机任务分配、包围控制精准灭火与编队通信拓扑优化；低空仿真及遥感图像校正识别3D测算。通信方案研究也在本批9题内，应用背景保留。</v>
+      </c>
+      <c r="E117" t="str" s="15">
+        <v>正文明确按评审给予经费资助，但未公布金额或课题数量。</v>
+      </c>
+      <c r="F117" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="118" ht="132" customHeight="1">
+      <c r="A118" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B118" t="n" s="13">
+        <v>44977</v>
+      </c>
+      <c r="C118" t="str" s="14">
+        <v>安徽建筑大学·安徽省工程机械智能制造重点实验室（2019省教育厅批准建设）</v>
+      </c>
+      <c r="D118" t="str" s="15">
+        <v>校外开放基金2题：面向智能制造多模态数据的知识图谱与工程机械故障诊断定位；典型工程机械施工场景数字模型、测试传感、在线监测调度和施工质量进展预测。校内主任基金另含复杂机械故障传播/新能源电驱供能，不能把校内专属任务当本人的开放选题。</v>
+      </c>
+      <c r="E118" t="str" s="15">
+        <v>校外开放基金约3万元/项，拟2项。校内主任基金约2万元/项，非外校申报类别。</v>
+      </c>
+      <c r="F118" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="119" ht="96" customHeight="1">
+      <c r="A119" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B117" t="n" s="13">
+      <c r="B119" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C117" t="str" s="14">
+      <c r="C119" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D117" t="str" s="15">
+      <c r="D119" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E117" t="str" s="15">
+      <c r="E119" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F117" t="str" s="16">
+      <c r="F119" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -51518,8 +53114,8 @@
     <hyperlink ref="F101" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F102" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F117" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C117" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F119" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C119" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F103" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C104" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -51560,6 +53156,10 @@
     <hyperlink ref="F115" ns1:id="rIdResume116"/>
     <hyperlink ref="C116" location="'02项目完整详情'!A218" display="项目完整详情"/>
     <hyperlink ref="F116" ns1:id="rIdResume117"/>
+    <hyperlink ref="C117" location="'02项目完整详情'!A221" display="项目完整详情"/>
+    <hyperlink ref="F117" ns1:id="rIdResume118"/>
+    <hyperlink ref="C118" location="'02项目完整详情'!A222" display="项目完整详情"/>
+    <hyperlink ref="F118" ns1:id="rIdResume119"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -53784,28 +55384,28 @@
     </row>
     <row r="78" ht="132" customHeight="1">
       <c r="A78" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B78" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B78" t="n" s="13">
+        <v>46280</v>
       </c>
       <c r="C78" t="str" s="14">
-        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
+        <v>长安大学·公路大型结构安全教育部工程研究中心</v>
       </c>
       <c r="D78" t="str" s="15">
-        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
+        <v>年度桥梁/隧道结构理论、抗震抗风、钢混组合结构、桥梁检测评估维护、施工控制、隧道环境防灾、大型结构安全监测与数据孪生。未细化机器人或智能检测装备感知规划控制任务，不能单凭监测/控制认定相关；任务联系待核。</v>
       </c>
       <c r="E78" t="str" s="15">
-        <v>未取得2020金额。</v>
+        <v>3万元/项，立项先拨1万；一年中检达续拨条件再拨剩余。</v>
       </c>
       <c r="F78" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G78" t="str" s="3">
-        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+        <v>需具体智能检测装备任务证据；3附件原件未取：申请DOC/高质量期刊目录/学校学术期刊目录；确认B/C/D目录口径及经费外拨报销。</v>
       </c>
       <c r="H78" t="str" s="3">
-        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+        <v>申请邮箱yao.li@chd.edu.cn；公告未载专门电话。学院公共029-82334453不是确认基金咨询电话。</v>
       </c>
     </row>
     <row r="79" ht="132" customHeight="1">
@@ -53816,22 +55416,22 @@
         <v>未取得</v>
       </c>
       <c r="C79" t="str" s="14">
-        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
       </c>
       <c r="D79" t="str" s="15">
-        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
       </c>
       <c r="E79" t="str" s="15">
-        <v>未取得当年金额。</v>
+        <v>未取得2020金额。</v>
       </c>
       <c r="F79" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G79" t="str" s="3">
-        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
       </c>
       <c r="H79" t="str" s="3">
-        <v>年度联系人未取得。</v>
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
       </c>
     </row>
     <row r="80" ht="132" customHeight="1">
@@ -53842,22 +55442,22 @@
         <v>未取得</v>
       </c>
       <c r="C80" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
       </c>
       <c r="D80" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
       </c>
       <c r="E80" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>未取得当年金额。</v>
       </c>
       <c r="F80" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G80" t="str" s="3">
-        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
       </c>
       <c r="H80" t="str" s="3">
-        <v>未取得当年项目联系人。</v>
+        <v>年度联系人未取得。</v>
       </c>
     </row>
     <row r="81" ht="132" customHeight="1">
@@ -53868,22 +55468,100 @@
         <v>未取得</v>
       </c>
       <c r="C81" t="str" s="14">
-        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
       </c>
       <c r="D81" t="str" s="15">
-        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
       </c>
       <c r="E81" t="str" s="15">
-        <v>未取得</v>
+        <v>未取得当年金额/类型。</v>
       </c>
       <c r="F81" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G81" t="str" s="3">
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+      </c>
+      <c r="H81" t="str" s="3">
+        <v>未取得当年项目联系人。</v>
+      </c>
+    </row>
+    <row r="82" ht="132" customHeight="1">
+      <c r="A82" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B82" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C82" t="str" s="14">
+        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
+      </c>
+      <c r="D82" t="str" s="15">
+        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+      </c>
+      <c r="E82" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F82" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G82" t="str" s="3">
         <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
       </c>
-      <c r="H81" t="str" s="3">
+      <c r="H82" t="str" s="3">
         <v>年度基金联系人未取得。</v>
+      </c>
+    </row>
+    <row r="83" ht="147" customHeight="1">
+      <c r="A83" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B83" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C83" t="str" s="14">
+        <v>安徽建筑大学·安徽省智能地下探测重点实验室</v>
+      </c>
+      <c r="D83" t="str" s="15">
+        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+      </c>
+      <c r="E83" t="str" s="15">
+        <v>金额未取得（正文页尾及附件未取得）。</v>
+      </c>
+      <c r="F83" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G83" t="str" s="3">
+        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+      </c>
+      <c r="H83" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+    </row>
+    <row r="84" ht="132" customHeight="1">
+      <c r="A84" t="str" s="20">
+        <v>线索待核·公告未取得</v>
+      </c>
+      <c r="B84" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C84" t="str" s="14">
+        <v>中国地震局工程力学研究所·基本科研业务费专项实验室开放基金项目</v>
+      </c>
+      <c r="D84" t="str" s="15">
+        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+      </c>
+      <c r="E84" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F84" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G84" t="str" s="3">
+        <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
+      </c>
+      <c r="H84" t="str" s="3">
+        <v>本批联系人未取得。</v>
       </c>
     </row>
   </sheetData>
@@ -54034,20 +55712,26 @@
     <hyperlink ref="F76" ns1:id="rIdResume75"/>
     <hyperlink ref="C75" location="'02项目完整详情'!A202" display="项目完整详情"/>
     <hyperlink ref="F75" ns1:id="rIdResume76"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F80" ns1:id="rIdResume77"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F81" ns1:id="rIdResume77"/>
     <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
     <hyperlink ref="F44" ns1:id="rIdResume78"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A212" display="项目完整详情"/>
-    <hyperlink ref="F79" ns1:id="rIdResume79"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F80" ns1:id="rIdResume79"/>
     <hyperlink ref="C77" location="'02项目完整详情'!A213" display="项目完整详情"/>
     <hyperlink ref="F77" ns1:id="rIdResume80"/>
-    <hyperlink ref="C78" location="'02项目完整详情'!A214" display="项目完整详情"/>
-    <hyperlink ref="F78" ns1:id="rIdResume81"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A214" display="项目完整详情"/>
+    <hyperlink ref="F79" ns1:id="rIdResume81"/>
     <hyperlink ref="C74" location="'02项目完整详情'!A215" display="项目完整详情"/>
     <hyperlink ref="F74" ns1:id="rIdResume82"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A217" display="项目完整详情"/>
-    <hyperlink ref="F81" ns1:id="rIdResume83"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A217" display="项目完整详情"/>
+    <hyperlink ref="F82" ns1:id="rIdResume83"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A219" display="项目完整详情"/>
+    <hyperlink ref="F84" ns1:id="rIdResume84"/>
+    <hyperlink ref="C78" location="'02项目完整详情'!A220" display="项目完整详情"/>
+    <hyperlink ref="F78" ns1:id="rIdResume85"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A223" display="项目完整详情"/>
+    <hyperlink ref="F83" ns1:id="rIdResume86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -48622,8 +48622,8 @@
       <c r="F910" t="str" s="3">
         <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
       </c>
-      <c r="G910" t="str" s="3">
-        <v>仅所列查询完成；不代表机构查全。</v>
+      <c r="G910" s="3" t="str">
+        <v>原查询含jsu.edu.cn实际吉首大学，不算江苏大学/镇江已查证据；本批改正确ujs.edu.cn补查。其他词只完成列出发现查询。</v>
       </c>
       <c r="H910" t="str" s="3">
         <v>https://eie.usts.edu.cn/xygk/kypin.htm
@@ -49455,8 +49455,8 @@
       <c r="F937" t="str" s="3">
         <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
       </c>
-      <c r="G937" t="str" s="3">
-        <v>仅所列查询完成；不代表机构查全。</v>
+      <c r="G937" s="3" t="str">
+        <v>原查询含jsu.edu.cn实际吉首大学，不算江苏大学/镇江已查证据；本批改正确ujs.edu.cn补查。其他词只完成列出发现查询。</v>
       </c>
       <c r="H937" t="str" s="3">
         <v>https://www.cwxu.edu.cn/kxyj/kypt1/stjkypt.htm
@@ -50500,6 +50500,440 @@
 https://highway.chd.edu.cn/info/1015/24577.htm</v>
       </c>
       <c r="I970" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="971" ht="52.5" customHeight="1">
+      <c r="A971" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B971" t="str" s="3">
+        <v>南京大学及南京理工全校目录剩余补齐入口</v>
+      </c>
+      <c r="C971" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D971" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E971" t="str" s="3">
+        <v>查询：site:nju.edu.cn 科研平台 重点实验室 目录 人工智能 / site:njust.edu.cn "科研平台" "省" "实验室" / site:automation.njust.edu.cn "科研平台" / site:ai.nju.edu.cn 实验室 研究中心；线索：江苏省科研平台；国家级科研平台；〖聚焦中心·聚力发展〗专访科学技术研究院常务副院长王赓；〖本科教育面面观〗以全方位育人平台助力学生全面成长成才；开放课题基金指南；复杂多体系统动力学全国重点实验室成立活动在南京举行</v>
+      </c>
+      <c r="F971" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G971" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H971" t="str" s="3">
+        <v>https://scit.nju.edu.cn/jsszdsys/listm2.htm
+https://scit.nju.edu.cn/gjzdsys/listm.htm
+https://zs.njust.edu.cn/73/2c/c12338a226092/page.htm
+https://zs.njust.edu.cn/ff/fd/c12822a327677/page.htm
+https://keysoftlab.nju.edu.cn/1573/list.htm
+https://zs.njust.edu.cn/fe/ab/c12822a327339/page.htm</v>
+      </c>
+      <c r="I971" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第452项</v>
+      </c>
+    </row>
+    <row r="972" ht="52.5" customHeight="1">
+      <c r="A972" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B972" t="str" s="3">
+        <v>华南理工学院及重点目录其余入口</v>
+      </c>
+      <c r="C972" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D972" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E972" t="str" s="3">
+        <v>查询：site:scut.edu.cn/au "科研平台" / site:scut.edu.cn/sma "科研平台" / site:scut.edu.cn "重点实验室" "机器人" "开放基金" / site:scut.edu.cn "省重点实验室" "工业" "控制"；线索：省社科联研究基地2025年度评估结果出炉　学校6家基地获评优秀；持续推进食品工程技术创新与转化　淀粉与植物蛋白深加工教育部工程研究中心召开学术会议</v>
+      </c>
+      <c r="F972" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G972" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H972" t="str" s="3">
+        <v>https://news.scut.edu.cn/2026/0916/c41a60548/page.htm
+https://news.scut.edu.cn/2026/0121/c160a59353/page.htm</v>
+      </c>
+      <c r="I972" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第453项</v>
+      </c>
+    </row>
+    <row r="973" ht="52.5" customHeight="1">
+      <c r="A973" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B973" t="str" s="3">
+        <v>重庆大学自动化机械学院真实目录补齐入口</v>
+      </c>
+      <c r="C973" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D973" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E973" t="str" s="3">
+        <v>查询：site:cqu.edu.cn 自动化学院 科研平台 / site:cqu.edu.cn 机械 运载 科研平台 重点实验室 / site:cqu.edu.cn 智能机器人 实验室 开放课题 2026 / site:cqu.edu.cn 医工 重点实验室 开放课题 2026；线索：山地城镇建设与新技术教育部重点实验室2026年开放课题申请通知-山地城镇建设与新技术教育部重点实验室主页；生物感知与多模态智能信息处理重庆市重点实验室2026年度开放基金立项评审结果公示-重庆大学微电子与通信工程学院；2026年开放课题研究基金项目申请指南-低品位能源利用技术及系统教育部重点实验室；实验室简介-高端装备机械传动全国重点实验室（测试版）；国家级平台-重庆大学科学技术发展研究院；高端装备机械传动全国重点实验室（测试版）</v>
+      </c>
+      <c r="F973" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G973" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H973" t="str" s="3">
+        <v>https://chongjian-lab.cqu.edu.cn/info/1012/2272.htm
+https://www.ccee.cqu.edu.cn/info/1397/7804.htm
+https://www.lgeuts.cqu.edu.cn/nry.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=1974&amp;wbtreeid=1026
+https://slmt.cqu.edu.cn/info/10665/88298.htm
+https://kjc.cqu.edu.cn/kyjd1/gjjpt.htm
+https://slmt.cqu.edu.cn/</v>
+      </c>
+      <c r="I973" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第454项</v>
+      </c>
+    </row>
+    <row r="974" ht="52.5" customHeight="1">
+      <c r="A974" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B974" t="str" s="3">
+        <v>西工大机械航空省部机器人目录其余入口</v>
+      </c>
+      <c r="C974" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D974" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E974" t="str" s="3">
+        <v>查询：site:me.nwpu.edu.cn "科研平台" / site:hangkong.nwpu.edu.cn "科研平台" / site:nwpu.edu.cn "省重点实验室" "机器人" / site:nwpu.edu.cn "实验室" "基本科研业务费" "开放" 2026；线索：科学研究-航空学院；《Research》发表材料学院齐卫宏教授和刘维民院士关于高性能镍/二硫化钼红外光电探测器的研究成果-西北工业大学；科研平台-航空学院；全省自主水下仿生机器人重点实验室获批！-宁波研究院；〖研究生招生〗航海学院2024年研究生招生简章-航海学院；航空学院参与的山东省航空航天电磁功能结构电磁调控与多功能集成技术重点实验室正式获批-航空学院</v>
+      </c>
+      <c r="F974" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G974" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H974" t="str" s="3">
+        <v>https://hangkong.nwpu.edu.cn/kxyj.htm
+https://www.nwpu.edu.cn/info/1198/69438.htm
+https://hangkong.nwpu.edu.cn/kxyj/kypt.htm
+https://ningbo.nwpu.edu.cn/info/1013/3979.htm
+https://hanghai.nwpu.edu.cn/info/1946/13152.htm
+https://hangkong.nwpu.edu.cn/info/1603/43184.htm</v>
+      </c>
+      <c r="I974" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第455项</v>
+      </c>
+    </row>
+    <row r="975" ht="52.5" customHeight="1">
+      <c r="A975" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B975" t="str" s="3">
+        <v>镇江江苏大学正确官方域名目录补漏</v>
+      </c>
+      <c r="C975" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D975" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E975" t="str" s="3">
+        <v>查询：site:ujs.edu.cn "科研平台" "机器人" / site:ujs.edu.cn "开放基金" "2026" 智能 / site:ujs.edu.cn "开放课题" "2027" / site:ujs.edu.cn "科研平台" "机械"；线索：机械工业金属基复合与功能材料重点实验室-江苏大学材料科学与工程学院；江苏省机械及工程结构损伤诊断与管理工程技术研究中心-低空技术学院；机械工业机械结构损伤检测评估技术重点实验室-土木工程与力学学院；高端装备用材表（界）面技术与工程省高校重点实验室-江苏大学材料科学与工程学院；江苏大学主页平台管理系统 yangyangyang--Home--Home；科研平台-江苏大学流体机械工程技术研究中心</v>
+      </c>
+      <c r="F975" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G975" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H975" t="str" s="3">
+        <v>https://material.ujs.edu.cn/info/1464/36642.htm
+https://slat.ujs.edu.cn/info/1321/3841.htm
+https://cm.ujs.edu.cn/info/1051/2960.htm
+https://material.ujs.edu.cn/info/1464/36622.htm
+https://faculty.ujs.edu.cn/yangyangyang/en/index.htm
+https://ltzx.ujs.edu.cn/kxyj/kypt.htm</v>
+      </c>
+      <c r="I975" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第456项</v>
+      </c>
+    </row>
+    <row r="976" ht="52.5" customHeight="1">
+      <c r="A976" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B976" t="str" s="3">
+        <v>南大已取分层目录实际技术平台机制</v>
+      </c>
+      <c r="C976" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D976" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E976" t="str" s="3">
+        <v>查询：site:nju.edu.cn ("近代声学" OR "极端性能光电" OR "精准光子") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:nju.edu.cn ("分布式光纤传感" OR "物流技术" OR "智慧城市规划") ("开放基金" OR "开放课题") / site:nju.edu.cn ("城市AI" OR "生物智能材料" OR "大地感知与控灾") ("开放基金" OR "开放课题") / site:nju.edu.cn ("电子科学与工程学院学科" OR "自旋芯片") ("开放基金" OR "开放课题")；线索：研究生招生网</v>
+      </c>
+      <c r="F976" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G976" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H976" t="str" s="3">
+        <v>https://yzb.nju.edu.cn/main.htm</v>
+      </c>
+      <c r="I976" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第457项</v>
+      </c>
+    </row>
+    <row r="977" ht="52.5" customHeight="1">
+      <c r="A977" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B977" t="str" s="3">
+        <v>华工国家英文目录装备检测机制</v>
+      </c>
+      <c r="C977" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D977" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E977" t="str" s="3">
+        <v>查询：site:scut.edu.cn ("移动超声" OR "组织修复" OR "医用植入器械") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:scut.edu.cn ("汽车零部件技术" OR "聚合物新型成型装备") ("开放基金" OR "开放课题") / site:scut.edu.cn ("风电控制与并网" OR "金属材料近净成形") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F977" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G977" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H977" t="str" s="3"/>
+      <c r="I977" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第458项</v>
+      </c>
+    </row>
+    <row r="978" ht="52.5" customHeight="1">
+      <c r="A978" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B978" t="str" s="3">
+        <v>西工航空已取平台逐名开放机制</v>
+      </c>
+      <c r="C978" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D978" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E978" t="str" s="3">
+        <v>查询：site:nwpu.edu.cn ("航空器体系评估与赋能设计" OR "飞行器基础布局" OR "强度与结构完整性") ("开放基金" OR "开放课题") (2026 OR 2027) / site:nwpu.edu.cn ("飞行器智能认知与控制" OR "应急救援无人机" OR "飞行器综合设计数智化") ("开放基金" OR "开放课题") / site:nwpu.edu.cn ("飞行器极端力学" OR "试验飞机设计与试验技术" OR "冲击动力学与工程应用") ("开放基金" OR "开放课题")；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F978" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G978" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H978" t="str" s="3"/>
+      <c r="I978" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第459项</v>
+      </c>
+    </row>
+    <row r="979" ht="52.5" customHeight="1">
+      <c r="A979" t="str" s="3">
+        <v>2026-10-09核心高校分层目录及镇江正确域名补漏</v>
+      </c>
+      <c r="B979" t="str" s="3">
+        <v>江苏大学2026新智能学院现行平台机制</v>
+      </c>
+      <c r="C979" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D979" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E979" t="str" s="3">
+        <v>查询：site:ujs.edu.cn ("机械及工程结构损伤" OR "机械结构损伤检测") ("开放基金" OR "开放课题") (2026 OR 2027 OR 2025) / site:ujs.edu.cn ("农机" OR "机器人" OR "机械工业") ("开放基金" OR "开放课题") / site:ujs.edu.cn "智能科学与工程学院" "科研平台"；线索：智能制造综合创新平台及智能制造专业实验平台采购信息公示-采购与招标；科研平台-食品科学与工程学院；郭志明教授组Top期刊Advanced Functional Materials发表研究成果-食品科学与工程学院；江苏大学主页平台管理系统 杨杰--中文主页--首页</v>
+      </c>
+      <c r="F979" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G979" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H979" t="str" s="3">
+        <v>https://cgb.ujs.edu.cn/info/1491/72750.htm
+https://spswxy.ujs.edu.cn/xkky/kypt.htm
+https://spswxy.ujs.edu.cn/info/2239/76276.htm
+https://faculty.ujs.edu.cn/yangjie1/zh_CN/index.htm</v>
+      </c>
+      <c r="I979" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第460项</v>
+      </c>
+    </row>
+    <row r="980" ht="52.5" customHeight="1">
+      <c r="A980" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B980" t="str" s="3">
+        <v>南京大学</v>
+      </c>
+      <c r="C980" t="str" s="3">
+        <v>江苏·南京</v>
+      </c>
+      <c r="D980" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E980" t="str" s="3">
+        <v>国级单页13、教育部2页20、其他部委单页13目录全文；省目录第2页14+第3页13=27名称/总41，首链第一页失败；校级目录工具只有导航空白。近代声学/极端光电/精准光子/分布光纤/物流/智慧城市/城市AI/生物智能/大地感知/电子学科/自旋等逐名2026—2027及旧基金机制查。M021及固体微结构M194排除复用。</v>
+      </c>
+      <c r="F980" t="str" s="3">
+        <v>省首14名、校级全部名单交人工，其他目录中共建平台重叠不算46独立机器人室；仅机制词查询完成、年度未齐，不称全校完成。</v>
+      </c>
+      <c r="G980" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H980" t="str" s="3">
+        <v>https://scit.nju.edu.cn/gjzdsys/listm.htm
+https://scit.nju.edu.cn/jybzdsys/listm.htm
+https://scit.nju.edu.cn/gczx/listm.htm
+https://scit.nju.edu.cn/jsszdsys/listm2.htm
+https://scit.nju.edu.cn/jsszdsys/listm3.htm
+https://scit.nju.edu.cn/jsszdsys/listm1.htm
+https://scit.nju.edu.cn/qtpt/listm.htm</v>
+      </c>
+      <c r="I980" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="981" ht="52.5" customHeight="1">
+      <c r="A981" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B981" t="str" s="3">
+        <v>华南理工大学</v>
+      </c>
+      <c r="C981" t="str" s="3">
+        <v>广东·广州</v>
+      </c>
+      <c r="D981" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E981" t="str" s="3">
+        <v>国家中文目录首次超时；同批独立英文国级目录全文19条牌目含3国家室/工程平台，未给现行重组版本时点，不能用页脚2025当名单核定年。移动超声、组织修复、植入器械、汽车零部件、聚合物成型装备、风电控制、近净成形逐名2026—2027历史基金机制查。</v>
+      </c>
+      <c r="F981" t="str" s="3">
+        <v>国家中文现行名单人工，省高校旧入口已有人工不重复访问；不按平台名认任务相关，学院/省其他年度未齐。</v>
+      </c>
+      <c r="G981" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H981" t="str" s="3">
+        <v>https://www.scut.edu.cn/new/270/list.htm
+https://www.scut.edu.cn/en/610/list.htm</v>
+      </c>
+      <c r="I981" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="982" ht="52.5" customHeight="1">
+      <c r="A982" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B982" t="str" s="3">
+        <v>重庆大学</v>
+      </c>
+      <c r="C982" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D982" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E982" t="str" s="3">
+        <v>真实自动化主页accu及国级科研平台目录首次均412；新搜索定位机械mve/cme/全国机械传动测试版不重复已有M类公告。光电coe已有失败不重试，不再将其当自动化目录。</v>
+      </c>
+      <c r="F982" t="str" s="3">
+        <v>国家/自动化现行完整名单交人工；机械/医工其他学院和各年度尚未齐，三个故障不是机构无基金。</v>
+      </c>
+      <c r="G982" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H982" t="str" s="3">
+        <v>https://kjc.cqu.edu.cn/kyjd1/gjjpt.htm
+https://accu.cqu.edu.cn/</v>
+      </c>
+      <c r="I982" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="983" ht="52.5" customHeight="1">
+      <c r="A983" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B983" t="str" s="3">
+        <v>西北工业大学航空学院</v>
+      </c>
+      <c r="C983" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D983" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E983" t="str" s="3">
+        <v>航空目录首次读到12个平台名称：部新航空体系评估、全国布局/强度分部、部极端力学、省/省高校综合数智设计、市飞行器认知控制、应急无人机等；成功页尾续读首次超时，停止。相关9名称2026—2027/长期机制查，未据无搜索命中作无基金。</v>
+      </c>
+      <c r="F983" t="str" s="3">
+        <v>完整目录页尾分页情况人工核，机械/航海等其他学院未齐；首次取得12名不是证明全院只有12个平台。</v>
+      </c>
+      <c r="G983" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H983" t="str" s="3">
+        <v>https://hangkong.nwpu.edu.cn/kxyj/kypt.htm</v>
+      </c>
+      <c r="I983" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="984" ht="52.5" customHeight="1">
+      <c r="A984" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B984" t="str" s="3">
+        <v>江苏大学</v>
+      </c>
+      <c r="C984" t="str" s="3">
+        <v>江苏·镇江</v>
+      </c>
+      <c r="D984" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E984" t="str" s="3">
+        <v>更正域名：江苏大学ujs.edu.cn，先前江苏周边查询中jsu.edu.cn是吉首不能计镇江；本批ujs定向。新智能学院2026-03成立简介全文只列损伤诊断省工程中心/机械工业检测重点室2科研平台及2国家教学平台；两名和农机/robot开放机制查。</v>
+      </c>
+      <c r="F984" t="str" s="3">
+        <v>该简介用等字不是完整平台清单；国家教学中心不当基金；全校完整目录与机器人农机平台年度仍缺，不称镇江完成。</v>
+      </c>
+      <c r="G984" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H984" t="str" s="3">
+        <v>https://znxy.ujs.edu.cn/xygk/xyjj.htm</v>
+      </c>
+      <c r="I984" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -20059,6 +20059,677 @@
         <v>2023独立历史线索；不能将智能地下探测等同通用岩土模型或将主任基金推为外校可申请。</v>
       </c>
     </row>
+    <row r="224" ht="132" customHeight="1">
+      <c r="A224" t="str" s="3">
+        <v>N075</v>
+      </c>
+      <c r="B224" t="str" s="3">
+        <v>官方通知正文仅PDF附件；目录发布2025-09-25，附件首次验证码停止。</v>
+      </c>
+      <c r="C224" t="str" s="3">
+        <v>山东交通学院</v>
+      </c>
+      <c r="D224" t="str" s="3">
+        <v>山东省智能建造装备关键技术与系统重点实验室</v>
+      </c>
+      <c r="E224" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F224" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G224" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H224" t="str" s="3">
+        <v>具体时点未取得</v>
+      </c>
+      <c r="I224" t="str" s="3">
+        <v>年度具体任务未取得，不据智能名称认定机器人相关。</v>
+      </c>
+      <c r="J224" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K224" t="str" s="3">
+        <v>资格与限项未取得。</v>
+      </c>
+      <c r="L224" t="str" s="3">
+        <v>合作访问未取得。</v>
+      </c>
+      <c r="M224" t="str" s="3">
+        <v>外拨/报销/科目/支付未取得。</v>
+      </c>
+      <c r="N224" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O224" t="str" s="3">
+        <v>数量、单位作者署名、验收未取得。</v>
+      </c>
+      <c r="P224" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q224" t="str" s="3">
+        <v>提交要求未取得。</v>
+      </c>
+      <c r="R224" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；历史或资料待核，不等同可申请。</v>
+      </c>
+      <c r="S224" t="str" s="3">
+        <v>下载完整通知PDF，确认2025年度实际机器人/装备任务及截止、外部资格、金额、合作、外拨报销、周期成果IP提交；目录2025-12已立项，不能当当前受理。</v>
+      </c>
+      <c r="T224" t="str" s="3">
+        <v>https://kyc.sdjtu.edu.cn/info/1056/3085.htm</v>
+      </c>
+      <c r="U224" t="str" s="3">
+        <v>https://kyc.sdjtu.edu.cn/system/_content/download.jsp?owner=1592971087&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=A2979916BB15FFA2DEB21E83D71F510F</v>
+      </c>
+      <c r="V224" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W224" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X224" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y224" t="str" s="3">
+        <v>山东·济南</v>
+      </c>
+      <c r="Z224" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+      <c r="AA224" t="str" s="3">
+        <v>仅正式附件入口，2025年度从通知和后续立项列表归属；不从实验室名称推断相关任务。</v>
+      </c>
+    </row>
+    <row r="225" ht="132" customHeight="1">
+      <c r="A225" t="str" s="3">
+        <v>N076</v>
+      </c>
+      <c r="B225" t="str" s="3">
+        <v>2024正式申报公告全文已取；指南ZIP/公告DOC首次超时。</v>
+      </c>
+      <c r="C225" t="str" s="3">
+        <v>四川轻化工大学</v>
+      </c>
+      <c r="D225" t="str" s="3">
+        <v>过程装备与控制工程四川省高校重点实验室</v>
+      </c>
+      <c r="E225" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F225" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G225" t="n" s="6">
+        <v>45434</v>
+      </c>
+      <c r="H225" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I225" t="str" s="3">
+        <v>当年正文仅概括多相流及环保装备、安全应急装备、智能制造与智能装备；缺指南具体机器人感知/规划/控制任务，不能将2011智能焊接机器人立项套为2024任务。</v>
+      </c>
+      <c r="J225" t="str" s="3">
+        <v>公开正文未载金额；重点/一般两类，待指南。</v>
+      </c>
+      <c r="K225" t="str" s="3">
+        <v>面向国内高校企业研究院所相关科研人员；重点博士或副高以上，一般原则博士或副高级以上，否则2副高级以上推荐；在读博士单独申请导师推荐。每PI1项且不得为组员参与同年其他项目；组员每年≤2项；有本室未结项目PI不得申报。无组员原则不支持。</v>
+      </c>
+      <c r="L225" t="str" s="3">
+        <v>校外须本室人员参与；联合多单位明确职责且提交协议/合同原件1份。访问要求未载。</v>
+      </c>
+      <c r="M225" t="str" s="3">
+        <v>签任务书后一次划拨，按批准预算及学校上级文件使用；无正常理由延期或违规可撤项追回。是否外拨南信及具体报销科目未载，不将一次划拨等同外拨。</v>
+      </c>
+      <c r="N225" t="str" s="3">
+        <v>重点≤3年，一般≤2年；申报起止填2024-07-01至2026-06-30或2027-06-30，实际以任务下达为准；不允许延期。</v>
+      </c>
+      <c r="O225" t="str" s="3">
+        <v>重点四类任意2项：新产品/装备（包括在审发明1或授权实用1）；高水平论文≥2；PI获省部级以上纵向；转让产业化到校经费≥资助2倍。一般四类任意2项：产品/装备或在审发明1或授权实用1；高水平论文≥1；PI获市厅级以上纵向；转让到校≥资助额。成果标基金号且本室完成单位之一，非硬第一单位；论文层级/作者序未载。</v>
+      </c>
+      <c r="P225" t="str" s="3">
+        <v>本室和PI单位共有；转让须双方单位同意；校外专利、软件和数据库登记须四川轻化工大学为权人之一。</v>
+      </c>
+      <c r="Q225" t="str" s="3">
+        <v>2024-04-23至05-22受理，单位科研部门审查申请2份及详细联系资料送室，电子595628323@qq.com；获批1月内任务书盖章交室。正文下载说明出现2023但附件标题2024，须以ZIP原件核，不将2023错字改年度。</v>
+      </c>
+      <c r="R225" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；历史或资料待核，不等同可申请。</v>
+      </c>
+      <c r="S225" t="str" s="3">
+        <v>ZIP指南与DOC首超时交人工，补实际任务/金额/费用外拨/论文界定；2026—2027未定位新指南不代表无。</v>
+      </c>
+      <c r="T225" t="str" s="3">
+        <v>https://webadm.suse.edu.cn/_s57/2024/0425/c4268a110770/page.psp</v>
+      </c>
+      <c r="U225" t="str" s="3">
+        <v>https://webadm.suse.edu.cn/_upload/article/files/91/28/437740ac47cdaac0efcef4982af9/bd1cf1ad-0af7-4635-93bc-d9314574508b.zip
+https://webadm.suse.edu.cn/_upload/article/files/91/28/437740ac47cdaac0efcef4982af9/6ba40d89-533f-44dc-82bc-f3f59b712c19.doc</v>
+      </c>
+      <c r="V225" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W225" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X225" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y225" t="str" s="3">
+        <v>四川·宜宾</v>
+      </c>
+      <c r="Z225" t="str" s="3">
+        <v>李轩13550763677/0831-5980344；595628323@qq.com；宜宾临港大学城188号宜宾校区A7-213，644004。</v>
+      </c>
+      <c r="AA225" t="str" s="3">
+        <v>2011获批项目仅长期开放机制证据，不当新项目或当前受理。</v>
+      </c>
+    </row>
+    <row r="226" ht="162" customHeight="1">
+      <c r="A226" t="str" s="3">
+        <v>N077</v>
+      </c>
+      <c r="B226" t="str" s="3">
+        <v>2025正式指南全文及后续立项正文已取；申报附件首次验证码且标题为另一实验室。</v>
+      </c>
+      <c r="C226" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="D226" t="str" s="3">
+        <v>电磁感应与节能技术十堰市重点实验室</v>
+      </c>
+      <c r="E226" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F226" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G226" t="n" s="6">
+        <v>46011</v>
+      </c>
+      <c r="H226" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I226" t="str" s="3">
+        <v>人工智能及机器人：机器学习/深度学习/视觉/强化学习，机器人高性能传感、精密驱动、先进控制及电机减速器控制器传感器部件；伺服/永磁电机驱动与能量管理；工业设备温振压流采集与故障诊断。另含电磁感应及工业网络安全，保留实际应用不泛化。</v>
+      </c>
+      <c r="J226" t="str" s="3">
+        <v>一般1—2万元/项。</v>
+      </c>
+      <c r="K226" t="str" s="3">
+        <v>讲师以上职称、硕士以上学位或相应水平的研究人员；年龄和限项未载，原文并列关系不擅自改为博士且副高。</v>
+      </c>
+      <c r="L226" t="str" s="3">
+        <v>指南允许单独或与实验室人员联合；后续立项规定校外PI须确定本室所在学校校内联络人，区别固定合作者。访问未载。</v>
+      </c>
+      <c r="M226" t="str" s="3">
+        <v>公开指南和立项正文未载开支、外拨、报销、支付节点。</v>
+      </c>
+      <c r="N226" t="str" s="3">
+        <v>一般2年；统一起止未载。</v>
+      </c>
+      <c r="O226" t="str" s="3">
+        <v>成果须署本室指定中英文名，未载第一单位、作者排序、论文专利数量及验收指标；后续立项称署名要求见任务书。</v>
+      </c>
+      <c r="P226" t="str" s="3">
+        <v>指南明确论文/专利/奖项等成果归实验室所有；非共有。</v>
+      </c>
+      <c r="Q226" t="str" s="3">
+        <v>2025-12-20前纸质2份+电子，20200016@huat.edu.cn；后续立项任务书PI签字电子同邮箱截至2025-12-31，该日期非申报截止。签章/邮寄地址细节待附件。</v>
+      </c>
+      <c r="R226" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；历史或资料待核，不等同可申请。</v>
+      </c>
+      <c r="S226" t="str" s="3">
+        <v>申报附件名却为汽车制造室，首次验证码；需确认正确表及任务书/费用外拨成果要求，保留异名不套另一项目。2026—2027未定位新受理。</v>
+      </c>
+      <c r="T226" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3476.htm</v>
+      </c>
+      <c r="U226" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15601401
+https://kjc.huat.edu.cn/info/1046/3496.htm
+https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15602171</v>
+      </c>
+      <c r="V226" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W226" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X226" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y226" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z226" t="str" s="3">
+        <v>程诗卿15926161114；20200016@huat.edu.cn；简介电话0719-8207316，非明确邮寄点。</v>
+      </c>
+      <c r="AA226" t="str" s="3">
+        <v>2025独立批；立项3496同年度补充，不另计项目。</v>
+      </c>
+    </row>
+    <row r="227" ht="162" customHeight="1">
+      <c r="A227" t="str" s="3">
+        <v>N078</v>
+      </c>
+      <c r="B227" t="str" s="3">
+        <v>2025正式指南及立项正文已取；指南页发布时间11-18/落款11-20不一致。</v>
+      </c>
+      <c r="C227" t="str" s="3">
+        <v>湖北汽车工业学院（联合东风设备制造有限公司）</v>
+      </c>
+      <c r="D227" t="str" s="3">
+        <v>汽车制造智能装备及智慧运维十堰市重点实验室</v>
+      </c>
+      <c r="E227" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F227" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G227" t="n" s="6">
+        <v>45991</v>
+      </c>
+      <c r="H227" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I227" t="str" s="3">
+        <v>智能机器人加工系统、智能制造单元产线、智能感知状态监测、决策工艺优化和控制执行；图像语音识别、行为感知、工业协作/服务/特种机器人、人机交互、自主导航、场景适配；装备多源采集故障诊断寿命预测智能运维与远程系统。</v>
+      </c>
+      <c r="J227" t="str" s="3">
+        <v>一般0.5—1万元/项。</v>
+      </c>
+      <c r="K227" t="str" s="3">
+        <v>讲师、助理研究员及以上职称，或博士（或同等研究水平）；年龄、限项未载。</v>
+      </c>
+      <c r="L227" t="str" s="3">
+        <v>非本室固定人员须≥1固定成员联合申请；后续立项校外PI还须校内联络人；不能称已有合作者。访问未载。</v>
+      </c>
+      <c r="M227" t="str" s="3">
+        <v>公开指南及立项正文未载外拨报销、开支、支付节点。</v>
+      </c>
+      <c r="N227" t="str" s="3">
+        <v>一般2年；统一起止未载。</v>
+      </c>
+      <c r="O227" t="str" s="3">
+        <v>须本室中英文署名；中文指南写法省略重点实验室字样，立项完整名称，两种原文保留；第一单位/作者、论文数量和验收指标未载。</v>
+      </c>
+      <c r="P227" t="str" s="3">
+        <v>论文专利奖项等成果归实验室所有。</v>
+      </c>
+      <c r="Q227" t="str" s="3">
+        <v>截至2025-11-30纸质2份+电子发25932564@qq.com；后续立项2025-12-09是签任务书电子回传期限，非申请截止。申请签章寄送细节未载。</v>
+      </c>
+      <c r="R227" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；历史或资料待核，不等同可申请。</v>
+      </c>
+      <c r="S227" t="str" s="3">
+        <v>申报DOC原件需人工（同文件链接已在N077首次验证码，不重复）；补任务书、费用外拨、成果指标和正式署名。2026—2027新受理未定位不表示无。</v>
+      </c>
+      <c r="T227" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3456.htm</v>
+      </c>
+      <c r="U227" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15601401
+https://kjc.huat.edu.cn/info/1046/3475.htm
+https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15601400</v>
+      </c>
+      <c r="V227" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W227" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X227" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y227" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z227" t="str" s="3">
+        <v>贺茂13972453788；25932564@qq.com；平台简介周学良13635727952。</v>
+      </c>
+      <c r="AA227" t="str" s="3">
+        <v>2025独立年度；简介有具身字样/正式名称不含具身。3456申报/3475下达合并一项，11-18页面与11-20落款冲突标注。</v>
+      </c>
+    </row>
+    <row r="228" ht="132" customHeight="1">
+      <c r="A228" t="str" s="3">
+        <v>N079</v>
+      </c>
+      <c r="B228" t="str" s="3">
+        <v>2025正式拟资助公示完整，非原申报指南；已评审不当当前受理。</v>
+      </c>
+      <c r="C228" t="str" s="3">
+        <v>湖北汽车工业学院（联合中国联通十堰市分公司）</v>
+      </c>
+      <c r="D228" t="str" s="3">
+        <v>空地群智协同技术与应用十堰市重点实验室</v>
+      </c>
+      <c r="E228" t="str" s="3">
+        <v>线索待核·历史已评审</v>
+      </c>
+      <c r="F228" t="str" s="3">
+        <v>2025</v>
+      </c>
+      <c r="G228" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H228" t="str" s="3">
+        <v>具体时点未取得</v>
+      </c>
+      <c r="I228" t="str" s="3">
+        <v>本批公示明确拟资助无人机山区高速公路二次事故识别预警；平台简介群智感知、互联协作、规划控制，只作背景，年度完整任务待原指南。</v>
+      </c>
+      <c r="J228" t="str" s="3">
+        <v>本批重点1万元/项、一般0.5万元/项；拟4重点12一般，不从个别PI项目经费推范围。</v>
+      </c>
+      <c r="K228" t="str" s="3">
+        <v>公示对象含校外申报单位；具体学历职称年龄限项未载。</v>
+      </c>
+      <c r="L228" t="str" s="3">
+        <v>合作访问未取得。</v>
+      </c>
+      <c r="M228" t="str" s="3">
+        <v>外拨/报销/科目/支付未取得。</v>
+      </c>
+      <c r="N228" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O228" t="str" s="3">
+        <v>数量、单位作者署名、验收未取得。</v>
+      </c>
+      <c r="P228" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q228" t="str" s="3">
+        <v>提交要求未取得。</v>
+      </c>
+      <c r="R228" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；历史或资料待核，不等同可申请。</v>
+      </c>
+      <c r="S228" t="str" s="3">
+        <v>需原2025申报指南、拟资助清单和任务书，补申报截止（公示12-12至12-15非申请）、完整任务、资格合作、周期、费用外拨、成果IP提交；2026—2027年度未定位，不据此无基金。</v>
+      </c>
+      <c r="T228" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1047/3468.htm</v>
+      </c>
+      <c r="U228" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15601380</v>
+      </c>
+      <c r="V228" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W228" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X228" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y228" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z228" t="str" s="3">
+        <v>公示陈西亮13437277037；平台简介陈宇峰13477971492，原申请邮箱未取。</v>
+      </c>
+      <c r="AA228" t="str" s="3">
+        <v>仅已有2025批次历史机制；首次未找到原申报指南，不以公示期代截止。</v>
+      </c>
+    </row>
+    <row r="229" ht="132" customHeight="1">
+      <c r="A229" t="str" s="3">
+        <v>N080</v>
+      </c>
+      <c r="B229" t="str" s="3">
+        <v>正式年度指南完整正文已取得；申请DOCX首次验证码。</v>
+      </c>
+      <c r="C229" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="D229" t="str" s="3">
+        <v>汽车动力传动与电子控制湖北省重点实验室</v>
+      </c>
+      <c r="E229" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F229" t="str" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G229" t="n" s="6">
+        <v>45207</v>
+      </c>
+      <c r="H229" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I229" t="str" s="3">
+        <v>汽车环境感知与认知、智能驾驶线控底盘、拟人化与人因工程、在线故障诊断及通讯；动力电池控制、变速/悬架转向制动控制、动态性能仿真检测和汽车电子网络控制。其余节能减排/CAE轻量化保留行业背景。</v>
+      </c>
+      <c r="J229" t="str" s="3">
+        <v>一般2万元/项。</v>
+      </c>
+      <c r="K229" t="str" s="3">
+        <v>中级以上职称或硕士以上学位科研人员，可单独或联合；年龄和限项未载。</v>
+      </c>
+      <c r="L229" t="str" s="3">
+        <v>允许单独或联合，未载强制固定合作者及访问；不可套2026校内联络人条款为2023硬要求。</v>
+      </c>
+      <c r="M229" t="str" s="3">
+        <v>PI负责限额使用，开支科目、外拨、报销地点及支付节点公开指南未载。</v>
+      </c>
+      <c r="N229" t="str" s="3">
+        <v>一般1—2年；统一起止未载。</v>
+      </c>
+      <c r="O229" t="str" s="3">
+        <v>须本室指定中英文署名，第一单位和作者序、成果数量及验收指标未载。</v>
+      </c>
+      <c r="P229" t="str" s="3">
+        <v>论文、专利、奖项等成果由实验室与研究者所在单位共有。</v>
+      </c>
+      <c r="Q229" t="str" s="3">
+        <v>2023-10-08截止；申请纸质1份+电子，yang516516@163.com；签章/寄送点待附件。</v>
+      </c>
+      <c r="R229" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；职称年龄限项和校内联络人未确认；已截止仅历史参考。</v>
+      </c>
+      <c r="S229" t="str" s="3">
+        <v>申请DOCX验证码人工；补外拨报销支付、成果指标、验收及签章寄送；已取得2026另记N081，不能套金额。</v>
+      </c>
+      <c r="T229" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/2747.htm</v>
+      </c>
+      <c r="U229" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=12129289</v>
+      </c>
+      <c r="V229" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W229" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X229" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y229" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z229" t="str" s="3">
+        <v>杨正才18107199839；yang516516@163.com。</v>
+      </c>
+      <c r="AA229" t="str" s="3">
+        <v>2023独立批次；不将2023一般2万套2026一般1万。</v>
+      </c>
+    </row>
+    <row r="230" ht="132" customHeight="1">
+      <c r="A230" t="str" s="3">
+        <v>N081</v>
+      </c>
+      <c r="B230" t="str" s="3">
+        <v>正式年度指南完整正文已取得；申请DOCX首次验证码。</v>
+      </c>
+      <c r="C230" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="D230" t="str" s="3">
+        <v>汽车动力传动与电子控制湖北省重点实验室</v>
+      </c>
+      <c r="E230" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F230" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G230" t="n" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H230" t="str" s="3">
+        <v>以申报书电子邮件收讫时间为准，未载小时。</v>
+      </c>
+      <c r="I230" t="str" s="3">
+        <v>汽车环境感知认知、智驾座舱环境感知AI、智能驾驶拟人化与人因工程、商用车智能底盘；飞行汽车结构及感知—决策—控制；动力、电池/整车能量、变速、悬架转向制动和网络控制、动态仿真检测、在线故障诊断。其他节能轻量化按原应用保留。</v>
+      </c>
+      <c r="J230" t="str" s="3">
+        <v>重点2万元/项；一般1万元/项。后续7月立项2重点16一般，非新申报。</v>
+      </c>
+      <c r="K230" t="str" s="3">
+        <v>中级以上职称或硕士以上学位科研人员，可单独或联合；年龄限项未载。</v>
+      </c>
+      <c r="L230" t="str" s="3">
+        <v>申报指南可单独/联合；2026-07-30立项明确校外PI须1校内联络人，未说必须固定成员，不混写。访问未载。</v>
+      </c>
+      <c r="M230" t="str" s="3">
+        <v>PI负责限额使用，开支科目、外拨、报销地点及支付节点公开指南未载。</v>
+      </c>
+      <c r="N230" t="str" s="3">
+        <v>一般1—2年；统一起止未载。</v>
+      </c>
+      <c r="O230" t="str" s="3">
+        <v>须本室中英文署名，指南英文Key Laboratory of Automotive Power Train and Electronic Control，立项Hubei Provincial Key Laboratory of Automotive Power Transmission and Electronic Control，两原文差异需任务书确认；第一单位/作者及数量验收未载。</v>
+      </c>
+      <c r="P230" t="str" s="3">
+        <v>论文、专利、奖项等成果由实验室与研究者所在单位共有。</v>
+      </c>
+      <c r="Q230" t="str" s="3">
+        <v>2026-05-30以电子收讫为准，盖章纸质+电子各1份；邮寄车城西167号王天田；邮箱原文wtt 31@126.com有空格，需核正确地址。</v>
+      </c>
+      <c r="R230" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；职称年龄限项和校内联络人未确认；已截止仅历史参考。</v>
+      </c>
+      <c r="S230" t="str" s="3">
+        <v>申请DOCX首次验证码、2026拟资助公示3625首次超时均人工；补费用外拨成果考核、正确邮箱及英文署名，原指南2026截止已核。</v>
+      </c>
+      <c r="T230" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3592.htm</v>
+      </c>
+      <c r="U230" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15608910
+https://kjc.huat.edu.cn/info/1046/3637.htm
+https://kjc.huat.edu.cn/info/1047/3625.htm</v>
+      </c>
+      <c r="V230" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W230" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X230" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y230" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z230" t="str" s="3">
+        <v>王天田17777822593；原文wtt 31@126.com（空格地址待确认）；十堰车城西167号。</v>
+      </c>
+      <c r="AA230" t="str" s="3">
+        <v>2026正式指南3592/公示3625/立项3637同批，三来源一项目。</v>
+      </c>
+    </row>
+    <row r="231" ht="132" customHeight="1">
+      <c r="A231" t="str" s="3">
+        <v>N082</v>
+      </c>
+      <c r="B231" t="str" s="3">
+        <v>2026正式指南全文已取；申请DOCX首次超时。</v>
+      </c>
+      <c r="C231" t="str" s="3">
+        <v>湖北汽车工业学院/实验室共建单位待原表核</v>
+      </c>
+      <c r="D231" t="str" s="3">
+        <v>储能与动力电池湖北省重点实验室</v>
+      </c>
+      <c r="E231" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F231" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G231" t="n" s="6">
+        <v>46178</v>
+      </c>
+      <c r="H231" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I231" t="str" s="3">
+        <v>年度16项主要电池材料工艺、电解质及表界面、耐温材料、回收与评价，另有锂离子电池无损检测技术开发。该条检测手段、机器人感知/相关装备的具体任务未载；不能凭研究领域中的智能装备收为确定相关。</v>
+      </c>
+      <c r="J231" t="str" s="3">
+        <v>资助强度视项目具体情况，未公开统一金额。</v>
+      </c>
+      <c r="K231" t="str" s="3">
+        <v>副高级以上职称或博士及以上学位研究人员可单独或联合；年龄限项未载。</v>
+      </c>
+      <c r="L231" t="str" s="3">
+        <v>可单独或与本室人员联合；未载强制固定合作者/访问。</v>
+      </c>
+      <c r="M231" t="str" s="3">
+        <v>PI负责限额使用，开支科目、外拨、报销地点及支付节点公开指南未载。</v>
+      </c>
+      <c r="N231" t="str" s="3">
+        <v>一般1—2年；统一起止未载。</v>
+      </c>
+      <c r="O231" t="str" s="3">
+        <v>须本室中文/英文Hubei Key Laboratory of Energy Storage and Power Battery署名；第一单位、作者、数量验收未载。</v>
+      </c>
+      <c r="P231" t="str" s="3">
+        <v>论文、专利、奖项等成果由实验室与研究者所在单位共有。</v>
+      </c>
+      <c r="Q231" t="str" s="3">
+        <v>2026-06-05截止，申请纸质2份+电子shanghao@huat.edu.cn；湖北汽车工业学院车城西路尚浩收442002；单位签章未载待表。</v>
+      </c>
+      <c r="R231" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；职称年龄限项和校内联络人未确认；已截止仅历史参考。</v>
+      </c>
+      <c r="S231" t="str" s="3">
+        <v>申请DOCX首超时人工，先补无损检测具体任务联系和方法、金额及外拨报销、成果验收；2025第二批材料/焊接评价另排除，不因同室套2026相关。</v>
+      </c>
+      <c r="T231" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3595.htm</v>
+      </c>
+      <c r="U231" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/system/_content/download.jsp?owner=1443488055&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=15609829</v>
+      </c>
+      <c r="V231" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W231" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X231" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y231" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="Z231" t="str" s="3">
+        <v>尚浩18086496989；shanghao@huat.edu.cn；十堰张湾车城西湖北汽车工业学院442002。</v>
+      </c>
+      <c r="AA231" t="str" s="3">
+        <v>2026独立批；不同于2025第二批，任务证据不足保持待核。</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="'04本轮信息核验日志'!A2" ns1:id="rIdArchiveAnchor1"/>
@@ -20502,6 +21173,14 @@
     <hyperlink ref="T221" ns1:id="rIdResume443"/>
     <hyperlink ref="T222" ns1:id="rIdResume444"/>
     <hyperlink ref="T223" ns1:id="rIdResume445"/>
+    <hyperlink ref="T224" ns1:id="rIdResume446"/>
+    <hyperlink ref="T225" ns1:id="rIdResume447"/>
+    <hyperlink ref="T226" ns1:id="rIdResume448"/>
+    <hyperlink ref="T227" ns1:id="rIdResume449"/>
+    <hyperlink ref="T228" ns1:id="rIdResume450"/>
+    <hyperlink ref="T229" ns1:id="rIdResume451"/>
+    <hyperlink ref="T230" ns1:id="rIdResume452"/>
+    <hyperlink ref="T231" ns1:id="rIdResume453"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -50934,6 +51613,711 @@
         <v>https://znxy.ujs.edu.cn/xygk/xyjj.htm</v>
       </c>
       <c r="I984" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="985" ht="52.5" customHeight="1">
+      <c r="A985" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B985" t="str" s="3">
+        <v>山东交通/新疆大学/四川轻化工/湖北汽车工业学院</v>
+      </c>
+      <c r="C985" t="str" s="3">
+        <v>山东/新疆/四川/湖北</v>
+      </c>
+      <c r="D985" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E985" t="str" s="3">
+        <v>查询：site:sdjtu.edu.cn "智能建造装备" "开放" "2025" / site:ffxy.xju.edu.cn "开放" "2026" / site:suse.edu.cn "机器人" "开放基金" / site:huat.edu.cn "开放课题" "2026"；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F985" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G985" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H985" t="str" s="3"/>
+      <c r="I985" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第461项</v>
+      </c>
+    </row>
+    <row r="986" ht="52.5" customHeight="1">
+      <c r="A986" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B986" t="str" s="3">
+        <v>山东交通/新疆大学/四川轻化工/湖北汽车工业学院</v>
+      </c>
+      <c r="C986" t="str" s="3">
+        <v>山东/新疆/四川/湖北</v>
+      </c>
+      <c r="D986" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E986" t="str" s="3">
+        <v>查询：site:sdjtu.edu.cn "智能建造装备" "开放课题通知" / site:suse.edu.cn "过程装备与控制工程" "开放" "2026" / site:ffxy.xju.edu.cn "3133" / site:huat.edu.cn 科研平台 机器人 湖北省重点实验室；线索：汽车制造智能装备及智慧运维十堰市重点实验室（简介）-湖北汽车工业学院；〖重点科研平台“打开看”〗探秘“智能”核心：制造装备数字化国家工程研究分中心-湖北汽车工业学院宣传部；省人民政府关于印发湖北省科技创新“十三五”规划的通知-湖北汽车工业学院科学技术发展研究院；汽车工程学院省属高校科研平台简介-汽车工程学院；| 研究生导师介绍 姓名： 任爱华 | 性别： 女 --- | --- | ---；湖北汽车工业学院2024 年硕士研究生招生简章</v>
+      </c>
+      <c r="F986" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G986" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H986" t="str" s="3">
+        <v>https://www.huat.edu.cn/info/1093/22705.htm
+https://xcb.huat.edu.cn/info/1014/3742.htm
+https://kjc.huat.edu.cn/info/1069/1130.htm
+https://auto.huat.edu.cn/info/1167/5817.htm
+https://jxxy.huat.edu.cn/__local/9/3A/41/6C71C6754FBCF66D19A56D1431F_1A9F7902_2BB80.pdf
+https://aixy.huat.edu.cn/__local/D/AB/F3/B89F9BF5C338F9B87F7CB6AE7E2_353E5A6E_6F550.pdf</v>
+      </c>
+      <c r="I986" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第462项</v>
+      </c>
+    </row>
+    <row r="987" ht="52.5" customHeight="1">
+      <c r="A987" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B987" t="str" s="3">
+        <v>湖北汽车工业学院/四川轻化工大学</v>
+      </c>
+      <c r="C987" t="str" s="3">
+        <v>湖北/四川</v>
+      </c>
+      <c r="D987" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E987" t="str" s="3">
+        <v>查询：site:huat.edu.cn "汽车制造" "开放基金" "指南" / site:huat.edu.cn "空地群智" "开放" / site:suse.edu.cn "过程装备" "开放基金" 申报 / site:huat.edu.cn "电磁感应与节能" "开放基金" "指南"；线索：空地群智协同技术与应用十堰市重点实验室开放基金2025年度拟资助项目公示-湖北汽车工业学院科学技术发展研究院；关于过程装备与控制工程四川省高校重点实验室 2024年度开放基金项目申报公告；过程装备与控制工程四川省高校重点实验室召开2024年开放基金项目评审会；我校过控和绿色催化四川省高校重点实验室开放基金项目通过专家评审</v>
+      </c>
+      <c r="F987" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G987" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H987" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1047/3468.htm
+https://webadm.suse.edu.cn/_s57/2024/0425/c4268a110770/page.psp
+https://webadm.suse.edu.cn/_s57/2024/0708/c2625a109708/page.psp
+https://webadm.suse.edu.cn/_s3/_t256/2011/1101/c58a11051/page.psp</v>
+      </c>
+      <c r="I987" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第463项</v>
+      </c>
+    </row>
+    <row r="988" ht="52.5" customHeight="1">
+      <c r="A988" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B988" t="str" s="3">
+        <v>湖北汽院与四川轻化工年度开放机制</v>
+      </c>
+      <c r="C988" t="str" s="3">
+        <v>湖北/四川</v>
+      </c>
+      <c r="D988" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E988" t="str" s="3">
+        <v>查询：site:huat.edu.cn "汽车制造智能装备及智慧运维" "指南" / site:huat.edu.cn "空地群智协同" "申报" "2025" / site:huat.edu.cn "电磁感应与节能" "指南" / site:suse.edu.cn "开放基金" "2025" "过程装备"；线索：我院获批高等学校虚拟仿真教学创新实验室项目-智能网联汽车学院；空地群智协同技术与应用十堰市重点实验室开放基金2025年度拟资助项目公示-湖北汽车工业学院科学技术发展研究院；学校两实验室双双获批十堰市重点实验室-湖北汽车工业学院新闻网；汽车制造智能装备及智慧运维十堰市重点实验室（简介）-湖北汽车工业学院</v>
+      </c>
+      <c r="F988" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G988" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H988" t="str" s="3">
+        <v>https://icv.huat.edu.cn/info/1094/5028.htm
+https://kjc.huat.edu.cn/info/1047/3468.htm
+https://news.huat.edu.cn/info/1002/26818.htm
+https://www.huat.edu.cn/info/1093/22705.htm</v>
+      </c>
+      <c r="I988" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第464项</v>
+      </c>
+    </row>
+    <row r="989" ht="52.5" customHeight="1">
+      <c r="A989" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B989" t="str" s="3">
+        <v>湖北汽院/山东交通/四川轻化工2026—2027补漏</v>
+      </c>
+      <c r="C989" t="str" s="3">
+        <v>湖北/山东/四川</v>
+      </c>
+      <c r="D989" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E989" t="str" s="3">
+        <v>查询：site:kjc.huat.edu.cn "空地群智" "指南" / site:kjc.huat.edu.cn "汽车制造" "申报" / site:sdjtu.edu.cn "智能建造装备" "2026" "开放" / site:suse.edu.cn "过程装备" "开放基金" "2027"；线索：汽车制造智能装备及智慧运维十堰市重点实验室（简介）-湖北汽车工业学院科学技术发展研究院；中共湖北省委 湖北省人民政府 关于新时代推动湖北高质量发展 加快建成中部地区崛起重要战略支点 的实施意见-湖北汽车工业学院科学技术发展研究院</v>
+      </c>
+      <c r="F989" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G989" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H989" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1158/3413.htm
+https://kjc.huat.edu.cn/info/1069/2209.htm</v>
+      </c>
+      <c r="I989" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第465项</v>
+      </c>
+    </row>
+    <row r="990" ht="52.5" customHeight="1">
+      <c r="A990" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B990" t="str" s="3">
+        <v>湖北汽院逐平台年度机制补漏</v>
+      </c>
+      <c r="C990" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D990" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E990" t="str" s="3">
+        <v>查询："空地群智协同技术与应用" "开放基金" "2025" "截止" / "汽车动力传动与电子控制" "开放基金" "2026" / "制造装备数字化" "湖北汽车" "开放基金" / "空地群智协同技术与应用" "2026" "2027" "开放"；线索：从实验室走向产业赛场 南京如何织就“6G之城”全链生态_中共江苏省委新闻网</v>
+      </c>
+      <c r="F990" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G990" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H990" t="str" s="3">
+        <v>https://zgjssw.gov.cn/shixianchuanzhen/nanjing/202604/t20260426_8570246.shtml</v>
+      </c>
+      <c r="I990" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第466项</v>
+      </c>
+    </row>
+    <row r="991" ht="52.5" customHeight="1">
+      <c r="A991" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B991" t="str" s="3">
+        <v>湖北汽院年度受理和汽车电子平台机制</v>
+      </c>
+      <c r="C991" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D991" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E991" t="str" s="3">
+        <v>查询：site:huat.edu.cn "开放基金" "2026" "汽车" / site:huat.edu.cn "开放基金" "2027" / site:huat.edu.cn "空地群智" "2025年度" "指南" / site:huat.edu.cn "汽车动力传动与电子控制" "开放" "申报"；线索：通知公告-湖北汽车工业学院科学技术发展研究院；关于发布先进轻合金材料十堰市重点实验室开放基金2026年度项目指南的通知（汽院科〔2025〕101号）-湖北汽车工业学院科学技术发展研究院；关于下达先进轻合金材料十堰市重点实验室开放基金2026年度项目的通知（汽院科〔2026〕5号）-湖北汽车工业学院科学技术发展研究院；汽车工程学院省属高校科研平台简介-汽车工程学院；：刘勇，男，博士，讲师，硕士研究生导师。</v>
+      </c>
+      <c r="F991" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G991" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H991" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/tzgg/27.htm
+https://kjc.huat.edu.cn/info/1046/3474.htm
+https://kjc.huat.edu.cn/info/1046/3503.htm
+https://auto.huat.edu.cn/info/1167/5817.htm
+https://aixy.huat.edu.cn/__local/6/65/5E/CCCFA9345D91DA89734DD338603_EB2A9546_2E983.pdf</v>
+      </c>
+      <c r="I991" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第467项</v>
+      </c>
+    </row>
+    <row r="992" ht="52.5" customHeight="1">
+      <c r="A992" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B992" t="str" s="3">
+        <v>四川轻化工/湖南理工/湖南工业/湖北工业目录和年度发现</v>
+      </c>
+      <c r="C992" t="str" s="3">
+        <v>四川/湖南/湖北</v>
+      </c>
+      <c r="D992" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E992" t="str" s="3">
+        <v>查询：site:suse.edu.cn 科研平台 "实验室" "机器人" / site:hnist.edu.cn "开放基金" "2026" / site:hnut.edu.cn "开放课题" "机器人" / site:hbut.edu.cn 科研平台 重点实验室；线索：省级平台-湖北工业大学科学技术发展研究院；实验室简介-发酵工程教育部重点实验室；〖科学网〗人工量子二维材料湖北省重点实验室正式启动-湖北工业大学新闻网；材料与化学工程学院召开科研平台建设工作会议-湖北工业大学材料与化学工程学院；科研平台-材料与化学工程学院；国家自然科学基金锦屏重大科学基础设施国际合作研究计划专项2026年度项目指南-湖北工业大学科学技术发展研究院</v>
+      </c>
+      <c r="F992" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G992" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H992" t="str" s="3">
+        <v>https://kjcy.hbut.edu.cn/kyjd/sjpt.htm
+https://klfe.hbut.edu.cn/sysgk/sysjj.htm
+https://news.hbut.edu.cn/info/1013/38012.htm
+https://smce.hbut.edu.cn/info/1068/3219.htm
+https://smce.hbut.edu.cn/old/kxyj/kypt.htm
+https://kjcy.hbut.edu.cn/info/1052/11075.htm</v>
+      </c>
+      <c r="I992" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第468项</v>
+      </c>
+    </row>
+    <row r="993" ht="52.5" customHeight="1">
+      <c r="A993" t="str" s="3">
+        <v>2026-10-09山东四川湖北省属平台目录与年度接续</v>
+      </c>
+      <c r="B993" t="str" s="3">
+        <v>湖北工业省级农机/包装/检测/算力平台机制</v>
+      </c>
+      <c r="C993" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D993" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E993" t="str" s="3">
+        <v>查询：site:hbut.edu.cn "农机装备智能化" "开放" / site:hbut.edu.cn "包装装备" "开放基金" / site:hbut.edu.cn "无损检测" "开放课题" / site:hbut.edu.cn "绿色智能算力网络" "开放基金"；线索：2026年度绿色智能算力网络湖北省重点实验室开放课题申报通知-欢迎访问湖北工业大学计算机科学与人工智能学院官方网站；2025年度绿色智能算力网络湖北省重点实验室开放课题申报通知-湖北工业大学绿色智能算力网络湖北省重点实验室；主任简介-湖北工业大学绿色智能算力网络湖北省重点实验室；叶志伟-湖北工业大学绿色智能算力网络湖北省重点实验室；陈涛-湖北工业大学研究生院；2026年度开放基金申请指南-现代制造质量工程湖北省重点实验室</v>
+      </c>
+      <c r="F993" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G993" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H993" t="str" s="3">
+        <v>https://scs.hbut.edu.cn/info/1043/6747.htm
+https://scs.hbut.edu.cn/lsznslwl/info/1031/1150.htm
+https://scs.hbut.edu.cn/lsznslwl/sysgk/zrjj.htm
+https://scs.hbut.edu.cn/lsznslwl/info/1045/1122.htm
+https://yjs.hbut.edu.cn/info/1101/18813.htm
+https://mmqe.hbut.edu.cn/info/1047/2232.htm</v>
+      </c>
+      <c r="I993" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第469项</v>
+      </c>
+    </row>
+    <row r="994" ht="52.5" customHeight="1">
+      <c r="A994" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B994" t="str" s="3">
+        <v>山东交通学院</v>
+      </c>
+      <c r="C994" t="str" s="3">
+        <v>山东·济南</v>
+      </c>
+      <c r="D994" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E994" t="str" s="3">
+        <v>山东省智能建造装备关键技术与系统重点实验室；2025；N075；官方通知正文仅PDF附件；目录发布2025-09-25，附件首次验证码停止。</v>
+      </c>
+      <c r="F994" t="str" s="3">
+        <v>下载完整通知PDF，确认2025年度实际机器人/装备任务及截止、外部资格、金额、合作、外拨报销、周期成果IP提交；目录2025-12已立项，不能当当前受理。</v>
+      </c>
+      <c r="G994" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H994" t="str" s="3">
+        <v>https://kyc.sdjtu.edu.cn/info/1056/3085.htm</v>
+      </c>
+      <c r="I994" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="995" ht="52.5" customHeight="1">
+      <c r="A995" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B995" t="str" s="3">
+        <v>四川轻化工大学</v>
+      </c>
+      <c r="C995" t="str" s="3">
+        <v>四川·宜宾</v>
+      </c>
+      <c r="D995" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E995" t="str" s="3">
+        <v>过程装备与控制工程四川省高校重点实验室；2024；N076；2024正式申报公告全文已取；指南ZIP/公告DOC首次超时。</v>
+      </c>
+      <c r="F995" t="str" s="3">
+        <v>ZIP指南与DOC首超时交人工，补实际任务/金额/费用外拨/论文界定；2026—2027未定位新指南不代表无。</v>
+      </c>
+      <c r="G995" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H995" t="str" s="3">
+        <v>https://webadm.suse.edu.cn/_s57/2024/0425/c4268a110770/page.psp</v>
+      </c>
+      <c r="I995" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="996" ht="52.5" customHeight="1">
+      <c r="A996" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B996" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="C996" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D996" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E996" t="str" s="3">
+        <v>电磁感应与节能技术十堰市重点实验室；2025；N077；2025正式指南全文及后续立项正文已取；申报附件首次验证码且标题为另一实验室。</v>
+      </c>
+      <c r="F996" t="str" s="3">
+        <v>申报附件名却为汽车制造室，首次验证码；需确认正确表及任务书/费用外拨成果要求，保留异名不套另一项目。2026—2027未定位新受理。</v>
+      </c>
+      <c r="G996" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H996" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3476.htm</v>
+      </c>
+      <c r="I996" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="997" ht="52.5" customHeight="1">
+      <c r="A997" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B997" t="str" s="3">
+        <v>湖北汽车工业学院（联合东风设备制造有限公司）</v>
+      </c>
+      <c r="C997" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D997" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E997" t="str" s="3">
+        <v>汽车制造智能装备及智慧运维十堰市重点实验室；2025；N078；2025正式指南及立项正文已取；指南页发布时间11-18/落款11-20不一致。</v>
+      </c>
+      <c r="F997" t="str" s="3">
+        <v>申报DOC原件需人工（同文件链接已在N077首次验证码，不重复）；补任务书、费用外拨、成果指标和正式署名。2026—2027新受理未定位不表示无。</v>
+      </c>
+      <c r="G997" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H997" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3456.htm</v>
+      </c>
+      <c r="I997" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="998" ht="52.5" customHeight="1">
+      <c r="A998" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B998" t="str" s="3">
+        <v>湖北汽车工业学院（联合中国联通十堰市分公司）</v>
+      </c>
+      <c r="C998" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D998" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E998" t="str" s="3">
+        <v>空地群智协同技术与应用十堰市重点实验室；2025；N079；2025正式拟资助公示完整，非原申报指南；已评审不当当前受理。</v>
+      </c>
+      <c r="F998" t="str" s="3">
+        <v>需原2025申报指南、拟资助清单和任务书，补申报截止（公示12-12至12-15非申请）、完整任务、资格合作、周期、费用外拨、成果IP提交；2026—2027年度未定位，不据此无基金。</v>
+      </c>
+      <c r="G998" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H998" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1047/3468.htm</v>
+      </c>
+      <c r="I998" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="999" ht="52.5" customHeight="1">
+      <c r="A999" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B999" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="C999" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D999" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E999" t="str" s="3">
+        <v>汽车动力传动与电子控制湖北省重点实验室；2023；N080；正式年度指南完整正文已取得；申请DOCX首次验证码。</v>
+      </c>
+      <c r="F999" t="str" s="3">
+        <v>申请DOCX验证码人工；补外拨报销支付、成果指标、验收及签章寄送；已取得2026另记N081，不能套金额。</v>
+      </c>
+      <c r="G999" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H999" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/2747.htm</v>
+      </c>
+      <c r="I999" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1000" ht="52.5" customHeight="1">
+      <c r="A1000" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1000" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="C1000" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D1000" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1000" t="str" s="3">
+        <v>汽车动力传动与电子控制湖北省重点实验室；2026；N081；正式年度指南完整正文已取得；申请DOCX首次验证码。</v>
+      </c>
+      <c r="F1000" t="str" s="3">
+        <v>申请DOCX首次验证码、2026拟资助公示3625首次超时均人工；补费用外拨成果考核、正确邮箱及英文署名，原指南2026截止已核。</v>
+      </c>
+      <c r="G1000" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1000" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3592.htm</v>
+      </c>
+      <c r="I1000" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1001" ht="52.5" customHeight="1">
+      <c r="A1001" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1001" t="str" s="3">
+        <v>湖北汽车工业学院/实验室共建单位待原表核</v>
+      </c>
+      <c r="C1001" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D1001" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1001" t="str" s="3">
+        <v>储能与动力电池湖北省重点实验室；2026；N082；2026正式指南全文已取；申请DOCX首次超时。</v>
+      </c>
+      <c r="F1001" t="str" s="3">
+        <v>申请DOCX首超时人工，先补无损检测具体任务联系和方法、金额及外拨报销、成果验收；2025第二批材料/焊接评价另排除，不因同室套2026相关。</v>
+      </c>
+      <c r="G1001" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1001" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/info/1046/3595.htm</v>
+      </c>
+      <c r="I1001" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1002" ht="52.5" customHeight="1">
+      <c r="A1002" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1002" t="str" s="3">
+        <v>山东交通学院</v>
+      </c>
+      <c r="C1002" t="str" s="3">
+        <v>山东·济南</v>
+      </c>
+      <c r="D1002" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1002" t="str" s="3">
+        <v>2024-12-31省部级/市厅目录各1名单XLSX，首次均验证码；校级目录明示共0条，仅该栏目空不推无校级科研机构。科研通知首页2025-09-25智能建造装备基金N075仅PDF入口首验证码；云基物联已复用E087校外一般无资助/青年仅本校研究生。2026/27逐名机制查询未定位新通知。</v>
+      </c>
+      <c r="F1002" t="str" s="3">
+        <v>完整省市XLSX待人工；共建及学院平台仍未齐。N075实际任务/全部条款待原PDF，非当前受理。</v>
+      </c>
+      <c r="G1002" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1002" t="str" s="3">
+        <v>https://kyc.sdjtu.edu.cn/kypt/sbjpt.htm
+https://kyc.sdjtu.edu.cn/info/1058/3043.htm
+https://kyc.sdjtu.edu.cn/info/1059/3044.htm
+https://kyc.sdjtu.edu.cn/kypt/xjpt.htm</v>
+      </c>
+      <c r="I1002" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1003" ht="52.5" customHeight="1">
+      <c r="A1003" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1003" t="str" s="3">
+        <v>四川轻化工大学</v>
+      </c>
+      <c r="C1003" t="str" s="3">
+        <v>四川·宜宾/自贡</v>
+      </c>
+      <c r="D1003" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1003" t="str" s="3">
+        <v>机械学院2024过程装备与控制高校重点室N076完整申报公告，指南ZIP/DOC首次超时；2011校外申报/焊接机器人立项仅长期机制；2026/27及2025逐名查询只教师已获项目不充新公告。</v>
+      </c>
+      <c r="F1003" t="str" s="3">
+        <v>2024具体机器人任务与金额待指南，PIs/合作/外拨/成果已逐字段记。全校平台目录仍未齐，不以1平台代表全校。</v>
+      </c>
+      <c r="G1003" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1003" t="str" s="3">
+        <v>https://webadm.suse.edu.cn/_s57/2024/0425/c4268a110770/page.psp</v>
+      </c>
+      <c r="I1003" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1004" ht="52.5" customHeight="1">
+      <c r="A1004" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1004" t="str" s="3">
+        <v>湖北汽车工业学院</v>
+      </c>
+      <c r="C1004" t="str" s="3">
+        <v>湖北·十堰</v>
+      </c>
+      <c r="D1004" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1004" t="str" s="3">
+        <v>科研处总目录单页15平台、省单页9名已取，市分类目录首超时；平台车制造/空地/电磁/汽车电子简介已取。综合通知首页+第2/3/4页与旧第9页已读：2026-08到2025-10及2023-09；缓存总552/556与页码36/37更新有差，非全历史通知完成。第5页34首超时；通知文件分类首页独立取得至2026-09，非对失败页改途径。2026汽车电子原指南+立项合并N081；2023 N080；2025制造N078/电磁N077/空地公示N079。</v>
+      </c>
+      <c r="F1004" t="str" s="3">
+        <v>原2025空地/2025汽车电子申报指南未定位；市名单/2025第5页交人工；未读更早页；2026/27各平台有查询但新年度和院级仍缺，不能写全校完成。</v>
+      </c>
+      <c r="G1004" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1004" t="str" s="3">
+        <v>https://kjc.huat.edu.cn/kypt.htm
+https://kjc.huat.edu.cn/kypt/sjpt.htm
+https://kjc.huat.edu.cn/kypt/sjpt1.htm
+https://kjc.huat.edu.cn/tzgg.htm
+https://kjc.huat.edu.cn/tzgg/37.htm
+https://kjc.huat.edu.cn/tzgg/36.htm
+https://kjc.huat.edu.cn/tzgg/35.htm
+https://kjc.huat.edu.cn/tzgg/34.htm
+https://kjc.huat.edu.cn/tzgg/27.htm
+https://kjc.huat.edu.cn/tzgg/tzwj.htm</v>
+      </c>
+      <c r="I1004" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1005" ht="52.5" customHeight="1">
+      <c r="A1005" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1005" t="str" s="3">
+        <v>湖北工业大学</v>
+      </c>
+      <c r="C1005" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1005" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1005" t="str" s="3">
+        <v>国家部委目录完整7牌目；省级目录完整55牌目：7重点室/7人文智库/21工程/5中试/2协同/1转移/2国际/4引智/6厅局，不能当55机器人室。市首超时人工；已有M086现代制造2026复用。绿色算力2025/2026年度完整任务为算网治理安全绿色化，与实际机器人装备任务无证据，E091/E092排除。</v>
+      </c>
+      <c r="F1005" t="str" s="3">
+        <v>省目录实际机器人装备任务及逐平台年度尚需补齐，不因全取目录称全查。已查农机/包装/无损检测/算力机制词；国家装备检测/桥梁/制造数智/电网等下一批接续。</v>
+      </c>
+      <c r="G1005" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1005" t="str" s="3">
+        <v>https://kjcy.hbut.edu.cn/kyjd/sjpt.htm
+https://kjcy.hbut.edu.cn/kyjd/gjbwping_ta.htm
+https://kjcy.hbut.edu.cn/kyjd/sjpt1.htm
+https://scs.hbut.edu.cn/info/1043/6747.htm
+https://scs.hbut.edu.cn/lsznslwl/info/1031/1150.htm</v>
+      </c>
+      <c r="I1005" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1006" ht="52.5" customHeight="1">
+      <c r="A1006" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1006" t="str" s="3">
+        <v>新疆大学纺织与服装学院</v>
+      </c>
+      <c r="C1006" t="str" s="3">
+        <v>新疆·乌鲁木齐</v>
+      </c>
+      <c r="D1006" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1006" t="str" s="3">
+        <v>2025新疆智能与绿色纺织开放指南完整3方向为特色纺织材料/低碳染整功能纺织/智能时尚服装功能，E089排除；公告2025不是搜索2026即年度2026。已有N010农牧robot机制复用。</v>
+      </c>
+      <c r="F1006" t="str" s="3">
+        <v>本公告剔除不代表全校项目无关；其他新疆平台完整目录与年度仍缺。</v>
+      </c>
+      <c r="G1006" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1006" t="str" s="3">
+        <v>https://ffxy.xju.edu.cn/info/1054/3133.htm</v>
+      </c>
+      <c r="I1006" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1007" ht="52.5" customHeight="1">
+      <c r="A1007" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1007" t="str" s="3">
+        <v>湖南工业大学/湖南理工学院</v>
+      </c>
+      <c r="C1007" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D1007" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1007" t="str" s="3">
+        <v>本批hnist湖南理工发现查询未定位新增正式入口；hnut.edu.cn不得当湖南工业大学已查证据，后续使用正确hut.edu.cn。</v>
+      </c>
+      <c r="F1007" t="str" s="3">
+        <v>湖南工业正确域名及官方目录仍需接续；不按本次错误域名认为机构完成。</v>
+      </c>
+      <c r="G1007" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1007" t="str" s="3"/>
+      <c r="I1007" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -53336,23 +54720,103 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="119" ht="96" customHeight="1">
+    <row r="119" ht="132" customHeight="1">
       <c r="A119" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B119" t="n" s="13">
+        <v>46011</v>
+      </c>
+      <c r="C119" t="str" s="14">
+        <v>湖北汽车工业学院·电磁感应与节能技术十堰市重点实验室</v>
+      </c>
+      <c r="D119" t="str" s="15">
+        <v>人工智能及机器人：机器学习/深度学习/视觉/强化学习，机器人高性能传感、精密驱动、先进控制及电机减速器控制器传感器部件；伺服/永磁电机驱动与能量管理；工业设备温振压流采集与故障诊断。另含电磁感应及工业网络安全，保留实际应用不泛化。</v>
+      </c>
+      <c r="E119" t="str" s="15">
+        <v>一般1—2万元/项。</v>
+      </c>
+      <c r="F119" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="120" ht="117" customHeight="1">
+      <c r="A120" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B120" t="n" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C120" t="str" s="14">
+        <v>湖北汽车工业学院（联合东风设备制造有限公司）·汽车制造智能装备及智慧运维十堰市重点实验室</v>
+      </c>
+      <c r="D120" t="str" s="15">
+        <v>智能机器人加工系统、智能制造单元产线、智能感知状态监测、决策工艺优化和控制执行；图像语音识别、行为感知、工业协作/服务/特种机器人、人机交互、自主导航、场景适配；装备多源采集故障诊断寿命预测智能运维与远程系统。</v>
+      </c>
+      <c r="E120" t="str" s="15">
+        <v>一般0.5—1万元/项。</v>
+      </c>
+      <c r="F120" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="121" ht="117" customHeight="1">
+      <c r="A121" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B121" t="n" s="13">
+        <v>45207</v>
+      </c>
+      <c r="C121" t="str" s="14">
+        <v>湖北汽车工业学院·汽车动力传动与电子控制湖北省重点实验室</v>
+      </c>
+      <c r="D121" t="str" s="15">
+        <v>汽车环境感知与认知、智能驾驶线控底盘、拟人化与人因工程、在线故障诊断及通讯；动力电池控制、变速/悬架转向制动控制、动态性能仿真检测和汽车电子网络控制。其余节能减排/CAE轻量化保留行业背景。</v>
+      </c>
+      <c r="E121" t="str" s="15">
+        <v>一般2万元/项。</v>
+      </c>
+      <c r="F121" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="122" ht="132" customHeight="1">
+      <c r="A122" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B122" t="n" s="13">
+        <v>46172</v>
+      </c>
+      <c r="C122" t="str" s="14">
+        <v>湖北汽车工业学院·汽车动力传动与电子控制湖北省重点实验室</v>
+      </c>
+      <c r="D122" t="str" s="15">
+        <v>汽车环境感知认知、智驾座舱环境感知AI、智能驾驶拟人化与人因工程、商用车智能底盘；飞行汽车结构及感知—决策—控制；动力、电池/整车能量、变速、悬架转向制动和网络控制、动态仿真检测、在线故障诊断。其他节能轻量化按原应用保留。</v>
+      </c>
+      <c r="E122" t="str" s="15">
+        <v>重点2万元/项；一般1万元/项。后续7月立项2重点16一般，非新申报。</v>
+      </c>
+      <c r="F122" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="123" ht="96" customHeight="1">
+      <c r="A123" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B119" t="n" s="13">
+      <c r="B123" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C119" t="str" s="14">
+      <c r="C123" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D119" t="str" s="15">
+      <c r="D123" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E119" t="str" s="15">
+      <c r="E123" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F119" t="str" s="16">
+      <c r="F123" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -53548,8 +55012,8 @@
     <hyperlink ref="F101" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F102" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F119" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C119" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F123" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C123" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F103" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C104" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -53594,6 +55058,14 @@
     <hyperlink ref="F117" ns1:id="rIdResume118"/>
     <hyperlink ref="C118" location="'02项目完整详情'!A222" display="项目完整详情"/>
     <hyperlink ref="F118" ns1:id="rIdResume119"/>
+    <hyperlink ref="C119" location="'02项目完整详情'!A226" display="项目完整详情"/>
+    <hyperlink ref="F119" ns1:id="rIdResume120"/>
+    <hyperlink ref="C120" location="'02项目完整详情'!A227" display="项目完整详情"/>
+    <hyperlink ref="F120" ns1:id="rIdResume121"/>
+    <hyperlink ref="C121" location="'02项目完整详情'!A229" display="项目完整详情"/>
+    <hyperlink ref="F121" ns1:id="rIdResume122"/>
+    <hyperlink ref="C122" location="'02项目完整详情'!A230" display="项目完整详情"/>
+    <hyperlink ref="F122" ns1:id="rIdResume123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -55844,54 +57316,54 @@
     </row>
     <row r="79" ht="132" customHeight="1">
       <c r="A79" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B79" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B79" t="n" s="13">
+        <v>45434</v>
       </c>
       <c r="C79" t="str" s="14">
-        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
+        <v>四川轻化工大学·过程装备与控制工程四川省高校重点实验室</v>
       </c>
       <c r="D79" t="str" s="15">
-        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
+        <v>当年正文仅概括多相流及环保装备、安全应急装备、智能制造与智能装备；缺指南具体机器人感知/规划/控制任务，不能将2011智能焊接机器人立项套为2024任务。</v>
       </c>
       <c r="E79" t="str" s="15">
-        <v>未取得2020金额。</v>
+        <v>公开正文未载金额；重点/一般两类，待指南。</v>
       </c>
       <c r="F79" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G79" t="str" s="3">
-        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+        <v>ZIP指南与DOC首超时交人工，补实际任务/金额/费用外拨/论文界定；2026—2027未定位新指南不代表无。</v>
       </c>
       <c r="H79" t="str" s="3">
-        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+        <v>李轩13550763677/0831-5980344；595628323@qq.com；宜宾临港大学城188号宜宾校区A7-213，644004。</v>
       </c>
     </row>
     <row r="80" ht="132" customHeight="1">
       <c r="A80" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B80" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B80" t="n" s="13">
+        <v>46178</v>
       </c>
       <c r="C80" t="str" s="14">
-        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+        <v>湖北汽车工业学院/实验室共建单位待原表核·储能与动力电池湖北省重点实验室</v>
       </c>
       <c r="D80" t="str" s="15">
-        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+        <v>年度16项主要电池材料工艺、电解质及表界面、耐温材料、回收与评价，另有锂离子电池无损检测技术开发。该条检测手段、机器人感知/相关装备的具体任务未载；不能凭研究领域中的智能装备收为确定相关。</v>
       </c>
       <c r="E80" t="str" s="15">
-        <v>未取得当年金额。</v>
+        <v>资助强度视项目具体情况，未公开统一金额。</v>
       </c>
       <c r="F80" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G80" t="str" s="3">
-        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+        <v>申请DOCX首超时人工，先补无损检测具体任务联系和方法、金额及外拨报销、成果验收；2025第二批材料/焊接评价另排除，不因同室套2026相关。</v>
       </c>
       <c r="H80" t="str" s="3">
-        <v>年度联系人未取得。</v>
+        <v>尚浩18086496989；shanghao@huat.edu.cn；十堰张湾车城西湖北汽车工业学院442002。</v>
       </c>
     </row>
     <row r="81" ht="132" customHeight="1">
@@ -55902,22 +57374,22 @@
         <v>未取得</v>
       </c>
       <c r="C81" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
       </c>
       <c r="D81" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
       </c>
       <c r="E81" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>未取得2020金额。</v>
       </c>
       <c r="F81" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G81" t="str" s="3">
-        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
       </c>
       <c r="H81" t="str" s="3">
-        <v>未取得当年项目联系人。</v>
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
       </c>
     </row>
     <row r="82" ht="132" customHeight="1">
@@ -55928,25 +57400,25 @@
         <v>未取得</v>
       </c>
       <c r="C82" t="str" s="14">
-        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
       </c>
       <c r="D82" t="str" s="15">
-        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
       </c>
       <c r="E82" t="str" s="15">
-        <v>未取得</v>
+        <v>未取得当年金额。</v>
       </c>
       <c r="F82" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G82" t="str" s="3">
-        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
       </c>
       <c r="H82" t="str" s="3">
-        <v>年度基金联系人未取得。</v>
-      </c>
-    </row>
-    <row r="83" ht="147" customHeight="1">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="83" ht="132" customHeight="1">
       <c r="A83" t="str" s="20">
         <v>线索待核·历史公告</v>
       </c>
@@ -55954,36 +57426,36 @@
         <v>未取得</v>
       </c>
       <c r="C83" t="str" s="14">
-        <v>安徽建筑大学·安徽省智能地下探测重点实验室</v>
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
       </c>
       <c r="D83" t="str" s="15">
-        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
       </c>
       <c r="E83" t="str" s="15">
-        <v>金额未取得（正文页尾及附件未取得）。</v>
+        <v>未取得当年金额/类型。</v>
       </c>
       <c r="F83" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G83" t="str" s="3">
-        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
       </c>
       <c r="H83" t="str" s="3">
-        <v>本批联系人未取得。</v>
+        <v>未取得当年项目联系人。</v>
       </c>
     </row>
     <row r="84" ht="132" customHeight="1">
       <c r="A84" t="str" s="20">
-        <v>线索待核·公告未取得</v>
+        <v>线索待核·历史公告</v>
       </c>
       <c r="B84" t="str" s="13">
         <v>未取得</v>
       </c>
       <c r="C84" t="str" s="14">
-        <v>中国地震局工程力学研究所·基本科研业务费专项实验室开放基金项目</v>
+        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
       </c>
       <c r="D84" t="str" s="15">
-        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
       </c>
       <c r="E84" t="str" s="15">
         <v>未取得</v>
@@ -55992,10 +57464,114 @@
         <v>官方公告</v>
       </c>
       <c r="G84" t="str" s="3">
+        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+      </c>
+      <c r="H84" t="str" s="3">
+        <v>年度基金联系人未取得。</v>
+      </c>
+    </row>
+    <row r="85" ht="147" customHeight="1">
+      <c r="A85" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B85" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C85" t="str" s="14">
+        <v>安徽建筑大学·安徽省智能地下探测重点实验室</v>
+      </c>
+      <c r="D85" t="str" s="15">
+        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+      </c>
+      <c r="E85" t="str" s="15">
+        <v>金额未取得（正文页尾及附件未取得）。</v>
+      </c>
+      <c r="F85" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G85" t="str" s="3">
+        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+      </c>
+      <c r="H85" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+    </row>
+    <row r="86" ht="132" customHeight="1">
+      <c r="A86" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B86" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C86" t="str" s="14">
+        <v>山东交通学院·山东省智能建造装备关键技术与系统重点实验室</v>
+      </c>
+      <c r="D86" t="str" s="15">
+        <v>年度具体任务未取得，不据智能名称认定机器人相关。</v>
+      </c>
+      <c r="E86" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F86" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G86" t="str" s="3">
+        <v>下载完整通知PDF，确认2025年度实际机器人/装备任务及截止、外部资格、金额、合作、外拨报销、周期成果IP提交；目录2025-12已立项，不能当当前受理。</v>
+      </c>
+      <c r="H86" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="87" ht="132" customHeight="1">
+      <c r="A87" t="str" s="20">
+        <v>线索待核·公告未取得</v>
+      </c>
+      <c r="B87" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C87" t="str" s="14">
+        <v>中国地震局工程力学研究所·基本科研业务费专项实验室开放基金项目</v>
+      </c>
+      <c r="D87" t="str" s="15">
+        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+      </c>
+      <c r="E87" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F87" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G87" t="str" s="3">
         <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
       </c>
-      <c r="H84" t="str" s="3">
+      <c r="H87" t="str" s="3">
         <v>本批联系人未取得。</v>
+      </c>
+    </row>
+    <row r="88" ht="132" customHeight="1">
+      <c r="A88" t="str" s="20">
+        <v>线索待核·历史已评审</v>
+      </c>
+      <c r="B88" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C88" t="str" s="14">
+        <v>湖北汽车工业学院（联合中国联通十堰市分公司）·空地群智协同技术与应用十堰市重点实验室</v>
+      </c>
+      <c r="D88" t="str" s="15">
+        <v>本批公示明确拟资助无人机山区高速公路二次事故识别预警；平台简介群智感知、互联协作、规划控制，只作背景，年度完整任务待原指南。</v>
+      </c>
+      <c r="E88" t="str" s="15">
+        <v>本批重点1万元/项、一般0.5万元/项；拟4重点12一般，不从个别PI项目经费推范围。</v>
+      </c>
+      <c r="F88" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G88" t="str" s="3">
+        <v>需原2025申报指南、拟资助清单和任务书，补申报截止（公示12-12至12-15非申请）、完整任务、资格合作、周期、费用外拨、成果IP提交；2026—2027年度未定位，不据此无基金。</v>
+      </c>
+      <c r="H88" t="str" s="3">
+        <v>公示陈西亮13437277037；平台简介陈宇峰13477971492，原申请邮箱未取。</v>
       </c>
     </row>
   </sheetData>
@@ -56146,26 +57722,34 @@
     <hyperlink ref="F76" ns1:id="rIdResume75"/>
     <hyperlink ref="C75" location="'02项目完整详情'!A202" display="项目完整详情"/>
     <hyperlink ref="F75" ns1:id="rIdResume76"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F81" ns1:id="rIdResume77"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F83" ns1:id="rIdResume77"/>
     <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
     <hyperlink ref="F44" ns1:id="rIdResume78"/>
-    <hyperlink ref="C80" location="'02项目完整详情'!A212" display="项目完整详情"/>
-    <hyperlink ref="F80" ns1:id="rIdResume79"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F82" ns1:id="rIdResume79"/>
     <hyperlink ref="C77" location="'02项目完整详情'!A213" display="项目完整详情"/>
     <hyperlink ref="F77" ns1:id="rIdResume80"/>
-    <hyperlink ref="C79" location="'02项目完整详情'!A214" display="项目完整详情"/>
-    <hyperlink ref="F79" ns1:id="rIdResume81"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A214" display="项目完整详情"/>
+    <hyperlink ref="F81" ns1:id="rIdResume81"/>
     <hyperlink ref="C74" location="'02项目完整详情'!A215" display="项目完整详情"/>
     <hyperlink ref="F74" ns1:id="rIdResume82"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A217" display="项目完整详情"/>
-    <hyperlink ref="F82" ns1:id="rIdResume83"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A219" display="项目完整详情"/>
-    <hyperlink ref="F84" ns1:id="rIdResume84"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A217" display="项目完整详情"/>
+    <hyperlink ref="F84" ns1:id="rIdResume83"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A219" display="项目完整详情"/>
+    <hyperlink ref="F87" ns1:id="rIdResume84"/>
     <hyperlink ref="C78" location="'02项目完整详情'!A220" display="项目完整详情"/>
     <hyperlink ref="F78" ns1:id="rIdResume85"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A223" display="项目完整详情"/>
-    <hyperlink ref="F83" ns1:id="rIdResume86"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A223" display="项目完整详情"/>
+    <hyperlink ref="F85" ns1:id="rIdResume86"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A224" display="项目完整详情"/>
+    <hyperlink ref="F86" ns1:id="rIdResume87"/>
+    <hyperlink ref="C79" location="'02项目完整详情'!A225" display="项目完整详情"/>
+    <hyperlink ref="F79" ns1:id="rIdResume88"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A228" display="项目完整详情"/>
+    <hyperlink ref="F88" ns1:id="rIdResume89"/>
+    <hyperlink ref="C80" location="'02项目完整详情'!A231" display="项目完整详情"/>
+    <hyperlink ref="F80" ns1:id="rIdResume90"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -632,23 +632,23 @@
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="12" t="str">
-        <v>受理中·条件待核</v>
-      </c>
-      <c r="B6" s="13" t="d">
-        <v>2026-10-18T00:00:00.000Z</v>
-      </c>
-      <c r="C6" s="14" t="str">
-        <v>天津大学·精密测试技术及仪器全国重点实验室</v>
-      </c>
-      <c r="D6" s="15" t="str">
-        <v>水下无人平台协同的稳健水声通信；数控机床六自由度误差在线测量与补偿</v>
-      </c>
-      <c r="E6" s="15" t="str">
-        <v>普通4—8万元</v>
-      </c>
-      <c r="F6" s="16" t="str">
-        <v>公告</v>
+      <c r="A6" t="str" s="12">
+        <v>受理中·个人条件待确认</v>
+      </c>
+      <c r="B6" t="n" s="13">
+        <v>46310</v>
+      </c>
+      <c r="C6" t="str" s="14">
+        <v>武汉纺织大学·湖北省服装信息化工程技术研究中心</v>
+      </c>
+      <c r="D6" t="str" s="15">
+        <v>智能可穿戴生物传感；运动状态监测；睡眠状态分析</v>
+      </c>
+      <c r="E6" t="str" s="15">
+        <v>1—2万元/项</v>
+      </c>
+      <c r="F6" t="str" s="16">
+        <v>官方公告</v>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
@@ -656,16 +656,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B7" s="13" t="d">
-        <v>2026-10-20T00:00:00.000Z</v>
+        <v>2026-10-18T00:00:00.000Z</v>
       </c>
       <c r="C7" s="14" t="str">
-        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
+        <v>天津大学·精密测试技术及仪器全国重点实验室</v>
       </c>
       <c r="D7" s="15" t="str">
-        <v>具身智能在自主系统中的应用；运载工具协同控制；多模态运行环境感知及跨场景泛化</v>
+        <v>水下无人平台协同的稳健水声通信；数控机床六自由度误差在线测量与补偿</v>
       </c>
       <c r="E7" s="15" t="str">
-        <v>4—10万元；约10项</v>
+        <v>普通4—8万元</v>
       </c>
       <c r="F7" s="16" t="str">
         <v>公告</v>
@@ -679,13 +679,13 @@
         <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C8" s="14" t="str">
-        <v>北京航空航天大学·空地一体新航行系统技术全国重点实验室</v>
+        <v>北京交通大学·先进轨道交通自主运行全国重点实验室</v>
       </c>
       <c r="D8" s="15" t="str">
-        <v>基于通信质量感知的低空三维航路规划；安全约束下航路规划与原理验证</v>
+        <v>具身智能在自主系统中的应用；运载工具协同控制；多模态运行环境感知及跨场景泛化</v>
       </c>
       <c r="E8" s="15" t="str">
-        <v>需求牵引不超过25万元，前沿探索不超过15万元</v>
+        <v>4—10万元；约10项</v>
       </c>
       <c r="F8" s="16" t="str">
         <v>公告</v>
@@ -699,13 +699,13 @@
         <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C9" s="14" t="str">
-        <v>南昌航空大学·江西省机载系统智能检测技术产业技术工程化中心（同公告联署：南昌市航空软件共性技术研发重点实验室）</v>
+        <v>北京航空航天大学·空地一体新航行系统技术全国重点实验室</v>
       </c>
       <c r="D9" s="15" t="str">
-        <v>机载智能导航与人类导航信息统一；拓扑与几何规划耦合；机载巡检目标识别；智能对抗与系统测试（保留公告1—5方向）</v>
+        <v>基于通信质量感知的低空三维航路规划；安全约束下航路规划与原理验证</v>
       </c>
       <c r="E9" s="15" t="str">
-        <v>0.5—1万元/项（4—5项）</v>
+        <v>需求牵引不超过25万元，前沿探索不超过15万元</v>
       </c>
       <c r="F9" s="16" t="str">
         <v>公告</v>
@@ -716,16 +716,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B10" s="13" t="d">
-        <v>2026-10-26T00:00:00.000Z</v>
+        <v>2026-10-20T00:00:00.000Z</v>
       </c>
       <c r="C10" s="14" t="str">
-        <v>西南交通大学·轨道交通运载系统全国重点实验室</v>
+        <v>南昌航空大学·江西省机载系统智能检测技术产业技术工程化中心（同公告联署：南昌市航空软件共性技术研发重点实验室）</v>
       </c>
       <c r="D10" s="15" t="str">
-        <v>面向检修作业的具身智能与人机协同</v>
+        <v>机载智能导航与人类导航信息统一；拓扑与几何规划耦合；机载巡检目标识别；智能对抗与系统测试（保留公告1—5方向）</v>
       </c>
       <c r="E10" s="15" t="str">
-        <v>8—10万元</v>
+        <v>0.5—1万元/项（4—5项）</v>
       </c>
       <c r="F10" s="16" t="str">
         <v>公告</v>
@@ -736,16 +736,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B11" s="13" t="d">
-        <v>2026-10-27T00:00:00.000Z</v>
+        <v>2026-10-26T00:00:00.000Z</v>
       </c>
       <c r="C11" s="14" t="str">
-        <v>大连理工大学·工业装备智能控制与优化教育部重点实验室</v>
+        <v>西南交通大学·轨道交通运载系统全国重点实验室</v>
       </c>
       <c r="D11" s="15" t="str">
-        <v>工业装备的智能检测与控制技术；工业控制嵌入式软件及系统</v>
+        <v>面向检修作业的具身智能与人机协同</v>
       </c>
       <c r="E11" s="15" t="str">
-        <v>3万元</v>
+        <v>8—10万元</v>
       </c>
       <c r="F11" s="16" t="str">
         <v>公告</v>
@@ -756,16 +756,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B12" s="13" t="d">
-        <v>2026-10-30T00:00:00.000Z</v>
+        <v>2026-10-27T00:00:00.000Z</v>
       </c>
       <c r="C12" s="14" t="str">
-        <v>重庆交通大学·交通工程应用机器人重庆市工程实验室</v>
+        <v>大连理工大学·工业装备智能控制与优化教育部重点实验室</v>
       </c>
       <c r="D12" s="15" t="str">
-        <v>交通基础设施建设、管理与养护机器人；交通装备运行维护机器人关键技术与整机集成</v>
+        <v>工业装备的智能检测与控制技术；工业控制嵌入式软件及系统</v>
       </c>
       <c r="E12" s="15" t="str">
-        <v>0.5—2万元/项；方向1—3各1—3项；调研方向另列。</v>
+        <v>3万元</v>
       </c>
       <c r="F12" s="16" t="str">
         <v>公告</v>
@@ -776,16 +776,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B13" s="13" t="d">
-        <v>2026-10-31T00:00:00.000Z</v>
+        <v>2026-10-30T00:00:00.000Z</v>
       </c>
       <c r="C13" s="14" t="str">
-        <v>苏州工学院·江苏省具身智能工业机器人及其人机协作高校重点实验室</v>
+        <v>重庆交通大学·交通工程应用机器人重庆市工程实验室</v>
       </c>
       <c r="D13" s="15" t="str">
-        <v>具身智能导航与灵巧操作；医疗机器人力触觉反馈与人机协同；特种机器人</v>
+        <v>交通基础设施建设、管理与养护机器人；交通装备运行维护机器人关键技术与整机集成</v>
       </c>
       <c r="E13" s="15" t="str">
-        <v>1—3万元/项。</v>
+        <v>0.5—2万元/项；方向1—3各1—3项；调研方向另列。</v>
       </c>
       <c r="F13" s="16" t="str">
         <v>公告</v>
@@ -799,56 +799,56 @@
         <v>2026-10-31T00:00:00.000Z</v>
       </c>
       <c r="C14" s="14" t="str">
-        <v>浙江大学·流体动力基础件与机电系统全国重点实验室</v>
+        <v>苏州工学院·江苏省具身智能工业机器人及其人机协作高校重点实验室</v>
       </c>
       <c r="D14" s="15" t="str">
-        <v>电液系统集成与控制；智能机电系统动力学建模、多源感知融合、先进检测与控制</v>
+        <v>具身智能导航与灵巧操作；医疗机器人力触觉反馈与人机协同；特种机器人</v>
       </c>
       <c r="E14" s="15" t="str">
-        <v>5—8万元/项。</v>
+        <v>1—3万元/项。</v>
       </c>
       <c r="F14" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
     <row r="15" ht="66" customHeight="1">
-      <c r="A15" t="str" s="12">
+      <c r="A15" s="12" t="str">
+        <v>受理中·条件待核</v>
+      </c>
+      <c r="B15" s="13" t="d">
+        <v>2026-10-31T00:00:00.000Z</v>
+      </c>
+      <c r="C15" s="14" t="str">
+        <v>浙江大学·流体动力基础件与机电系统全国重点实验室</v>
+      </c>
+      <c r="D15" s="15" t="str">
+        <v>电液系统集成与控制；智能机电系统动力学建模、多源感知融合、先进检测与控制</v>
+      </c>
+      <c r="E15" s="15" t="str">
+        <v>5—8万元/项。</v>
+      </c>
+      <c r="F15" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" t="str" s="12">
         <v>受理中·个人条件待核</v>
       </c>
-      <c r="B15" t="n" s="13">
+      <c r="B16" t="n" s="13">
         <v>46331</v>
       </c>
-      <c r="C15" t="str" s="14">
+      <c r="C16" t="str" s="14">
         <v>滁州学院·安徽省实景地理环境重点实验室</v>
       </c>
-      <c r="D15" t="str" s="15">
+      <c r="D16" t="str" s="15">
         <v>多无人机编队；室内定位导航；空地融合建模；三维重建；无人机巡检</v>
       </c>
-      <c r="E15" t="str" s="15">
+      <c r="E16" t="str" s="15">
         <v>重点≤8万；一般≤4万；产教≤15万</v>
       </c>
-      <c r="F15" t="str" s="16">
+      <c r="F16" t="str" s="16">
         <v>官方公告</v>
-      </c>
-    </row>
-    <row r="16" ht="66" customHeight="1">
-      <c r="A16" s="12" t="str">
-        <v>受理中·条件待核</v>
-      </c>
-      <c r="B16" s="13" t="d">
-        <v>2026-11-10T00:00:00.000Z</v>
-      </c>
-      <c r="C16" s="14" t="str">
-        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
-      </c>
-      <c r="D16" s="15" t="str">
-        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
-      </c>
-      <c r="E16" s="15" t="str">
-        <v>0.5万元/项</v>
-      </c>
-      <c r="F16" s="16" t="str">
-        <v>公告</v>
       </c>
     </row>
     <row r="17" ht="66" customHeight="1">
@@ -856,16 +856,16 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B17" s="13" t="d">
-        <v>2026-11-15T00:00:00.000Z</v>
+        <v>2026-11-10T00:00:00.000Z</v>
       </c>
       <c r="C17" s="14" t="str">
-        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+        <v>苏州大学·江苏省高校通用人工智能与大模型重点实验室</v>
       </c>
       <c r="D17" s="15" t="str">
-        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+        <v>视觉—语言—动作模型、机器人灵巧操作与自主导航；多机器人、多无人系统协同</v>
       </c>
       <c r="E17" s="15" t="str">
-        <v>重点3万元、一般2万元</v>
+        <v>0.5万元/项</v>
       </c>
       <c r="F17" s="16" t="str">
         <v>公告</v>
@@ -876,18 +876,38 @@
         <v>受理中·条件待核</v>
       </c>
       <c r="B18" s="13" t="d">
+        <v>2026-11-15T00:00:00.000Z</v>
+      </c>
+      <c r="C18" s="14" t="str">
+        <v>武汉科技大学·机械传动与制造工程湖北省重点实验室</v>
+      </c>
+      <c r="D18" s="15" t="str">
+        <v>液压传动及机电液系统控制；机械传动系统设计与动力学（工业控制与智能制造装备背景）</v>
+      </c>
+      <c r="E18" s="15" t="str">
+        <v>重点3万元、一般2万元</v>
+      </c>
+      <c r="F18" s="16" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="12" t="str">
+        <v>受理中·条件待核</v>
+      </c>
+      <c r="B19" s="13" t="d">
         <v>2026-11-30T00:00:00.000Z</v>
       </c>
-      <c r="C18" s="14" t="str">
+      <c r="C19" s="14" t="str">
         <v>华中科技大学·智能制造装备与技术全国重点实验室</v>
       </c>
-      <c r="D18" s="15" t="str">
+      <c r="D19" s="15" t="str">
         <v>机器人加工技能学习与自主控制；多机器人协同；人形机器人感知、灵巧操作与全身控制</v>
       </c>
-      <c r="E18" s="15" t="str">
+      <c r="E19" s="15" t="str">
         <v>公告未公布资助强度，需咨询</v>
       </c>
-      <c r="F18" s="16" t="str">
+      <c r="F19" s="16" t="str">
         <v>公告</v>
       </c>
     </row>
@@ -895,38 +915,40 @@
   <hyperlinks>
     <hyperlink ref="C2" location="'02项目完整详情'!A2"/>
     <hyperlink ref="F2" ns1:id="R0703188348514edb"/>
-    <hyperlink ref="C13" location="'02项目完整详情'!A10"/>
-    <hyperlink ref="F13" ns1:id="R02deb72e2d4c4fc2"/>
-    <hyperlink ref="C16" location="'02项目完整详情'!A11"/>
-    <hyperlink ref="F16" ns1:id="Rb0dfb47d911a4186"/>
-    <hyperlink ref="C7" location="'02项目完整详情'!A138"/>
-    <hyperlink ref="F7" ns1:id="R03ccbeb508f24d98"/>
-    <hyperlink ref="C8" location="'02项目完整详情'!A3"/>
-    <hyperlink ref="F8" ns1:id="Rf39712aab58b4977"/>
-    <hyperlink ref="C12" location="'02项目完整详情'!A4"/>
-    <hyperlink ref="F12" ns1:id="R29f5a7d822fa4ff0"/>
+    <hyperlink ref="C14" location="'02项目完整详情'!A10"/>
+    <hyperlink ref="F14" ns1:id="R02deb72e2d4c4fc2"/>
+    <hyperlink ref="C17" location="'02项目完整详情'!A11"/>
+    <hyperlink ref="F17" ns1:id="Rb0dfb47d911a4186"/>
+    <hyperlink ref="C8" location="'02项目完整详情'!A138"/>
+    <hyperlink ref="F8" ns1:id="R03ccbeb508f24d98"/>
+    <hyperlink ref="C9" location="'02项目完整详情'!A3"/>
+    <hyperlink ref="F9" ns1:id="Rf39712aab58b4977"/>
+    <hyperlink ref="C13" location="'02项目完整详情'!A4"/>
+    <hyperlink ref="F13" ns1:id="R29f5a7d822fa4ff0"/>
     <hyperlink ref="C3" location="'02项目完整详情'!A47"/>
     <hyperlink ref="F3" ns1:id="Rfa73da6bd12f484e"/>
     <hyperlink ref="C4" location="'02项目完整详情'!A5"/>
     <hyperlink ref="F4" ns1:id="Rcec38ef0c81f4e03"/>
-    <hyperlink ref="C6" location="'02项目完整详情'!A6"/>
-    <hyperlink ref="F6" ns1:id="Rcc6b937cc2db4463"/>
-    <hyperlink ref="C9" location="'02项目完整详情'!A149"/>
-    <hyperlink ref="F9" ns1:id="R7683ff081f9341d2"/>
-    <hyperlink ref="C10" location="'02项目完整详情'!A7"/>
-    <hyperlink ref="F10" ns1:id="R5649c5cdeb214215"/>
-    <hyperlink ref="C11" location="'02项目完整详情'!A8"/>
-    <hyperlink ref="F11" ns1:id="R1fb1d42b338a46e2"/>
-    <hyperlink ref="C14" location="'02项目完整详情'!A9"/>
-    <hyperlink ref="F14" ns1:id="Rc8744d7119ac4fd0"/>
-    <hyperlink ref="C17" location="'02项目完整详情'!A12"/>
-    <hyperlink ref="F17" ns1:id="R59533ec0b37d42df"/>
-    <hyperlink ref="C18" location="'02项目完整详情'!A13"/>
-    <hyperlink ref="F18" ns1:id="Rc2d55cd36ec74ace"/>
+    <hyperlink ref="C7" location="'02项目完整详情'!A6"/>
+    <hyperlink ref="F7" ns1:id="Rcc6b937cc2db4463"/>
+    <hyperlink ref="C10" location="'02项目完整详情'!A149"/>
+    <hyperlink ref="F10" ns1:id="R7683ff081f9341d2"/>
+    <hyperlink ref="C11" location="'02项目完整详情'!A7"/>
+    <hyperlink ref="F11" ns1:id="R5649c5cdeb214215"/>
+    <hyperlink ref="C12" location="'02项目完整详情'!A8"/>
+    <hyperlink ref="F12" ns1:id="R1fb1d42b338a46e2"/>
+    <hyperlink ref="C15" location="'02项目完整详情'!A9"/>
+    <hyperlink ref="F15" ns1:id="Rc8744d7119ac4fd0"/>
+    <hyperlink ref="C18" location="'02项目完整详情'!A12"/>
+    <hyperlink ref="F18" ns1:id="R59533ec0b37d42df"/>
+    <hyperlink ref="C19" location="'02项目完整详情'!A13"/>
+    <hyperlink ref="F19" ns1:id="Rc2d55cd36ec74ace"/>
     <hyperlink ref="C5" location="'02项目完整详情'!A183" display="项目完整详情"/>
     <hyperlink ref="F5" ns1:id="rIdResume17"/>
-    <hyperlink ref="C15" location="'02项目完整详情'!A205" display="项目完整详情"/>
-    <hyperlink ref="F15" ns1:id="rIdResume18"/>
+    <hyperlink ref="C16" location="'02项目完整详情'!A205" display="项目完整详情"/>
+    <hyperlink ref="F16" ns1:id="rIdResume18"/>
+    <hyperlink ref="C6" location="'02项目完整详情'!A234" display="项目完整详情"/>
+    <hyperlink ref="F6" ns1:id="rIdResume19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20728,6 +20750,840 @@
       </c>
       <c r="AA231" t="str" s="3">
         <v>2026独立批；不同于2025第二批，任务证据不足保持待核。</v>
+      </c>
+    </row>
+    <row r="232" ht="132" customHeight="1">
+      <c r="A232" t="str" s="3">
+        <v>N083</v>
+      </c>
+      <c r="B232" t="str" s="3">
+        <v>正式2025—2026通知全文；指南验证码，申请DOC超时。</v>
+      </c>
+      <c r="C232" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D232" t="str" s="3">
+        <v>湖北省数字化纺织装备重点实验室</v>
+      </c>
+      <c r="E232" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F232" t="str" s="3">
+        <v>2025—2026</v>
+      </c>
+      <c r="G232" t="n" s="6">
+        <v>45971</v>
+      </c>
+      <c r="H232" t="str" s="3">
+        <v>原文11月10日前，是否含当日未明确；已截止。</v>
+      </c>
+      <c r="I232" t="str" s="3">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="J232" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K232" t="str" s="3">
+        <v>资格与限项未取得。</v>
+      </c>
+      <c r="L232" t="str" s="3">
+        <v>合作与访问未取得。</v>
+      </c>
+      <c r="M232" t="str" s="3">
+        <v>外拨、费用、报销和支付未取得。</v>
+      </c>
+      <c r="N232" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O232" t="str" s="3">
+        <v>成果数量、单位/作者署名、验收未取得。</v>
+      </c>
+      <c r="P232" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q232" t="str" s="3">
+        <v>申请纸质2份邮寄阳光大道1号武汉纺织大学实验室办公室430200，电子sfzb@wtu.edu.cn。</v>
+      </c>
+      <c r="R232" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S232" t="str" s="3">
+        <v>下载指南/表补实际机器人/装备任务及金额资格合作外拨周期成果IP；网页发布2025-10-27而落款2024-10-19冲突，不擅自改成2024项目。</v>
+      </c>
+      <c r="T232" t="str" s="3">
+        <v>https://me.wtu.edu.cn/info/1041/13404.htm</v>
+      </c>
+      <c r="U232" t="str" s="3">
+        <v>https://me.wtu.edu.cn/system/_content/download.jsp?owner=1594497525&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=FF3D4C5C12F264EBE77A3CCD3D75F6DA
+https://me.wtu.edu.cn/system/_content/download.jsp?owner=1594497525&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=8C45BF736F35C6378B483A6EE6B3B13D</v>
+      </c>
+      <c r="V232" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W232" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X232" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y232" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z232" t="str" s="3">
+        <v>陈振15072325406/027-59367842；sfzb@wtu.edu.cn。</v>
+      </c>
+      <c r="AA232" t="str" s="3">
+        <v>一个2025—2026共同批，不拆两项；落款年份原样标冲突。</v>
+      </c>
+    </row>
+    <row r="233" ht="132" customHeight="1">
+      <c r="A233" t="str" s="3">
+        <v>N084</v>
+      </c>
+      <c r="B233" t="str" s="3">
+        <v>原页首次404停止；后续独立平台机制查询的官方搜索缓存呈现完整指南，逐字段用缓存证据，不重试原页。</v>
+      </c>
+      <c r="C233" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D233" t="str" s="3">
+        <v>智能微纳医学检验装备及关键技术湖北省工程研究中心/湖北省功能纤维加工及检测工程技术研究中心</v>
+      </c>
+      <c r="E233" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F233" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G233" t="n" s="6">
+        <v>46295</v>
+      </c>
+      <c r="H233" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I233" t="str" s="3">
+        <v>医学影像大模型设计及智能分析；重大疾病智能穿戴检测与健康管理；肿瘤检测先进理论技术、智能纤维制造应用和其他检测；以实际检验装备/影像/穿戴任务收录，不虚构机器人应用。</v>
+      </c>
+      <c r="J233" t="str" s="3">
+        <v>正式官方缓存完整正文未载资助金额。</v>
+      </c>
+      <c r="K233" t="str" s="3">
+        <v>实际PI保证时间精力；主要对象副高及以上或博士，在境内外高校科研机构企业任职科研工程人员；同年度限1项。年龄未载。</v>
+      </c>
+      <c r="L233" t="str" s="3">
+        <v>同等条件学科交叉优势互补优先；未载强制固定合作与访问。</v>
+      </c>
+      <c r="M233" t="str" s="3">
+        <v>主要用于实验材料、测试、版面和差旅；外拨、报销地点、支付未载。</v>
+      </c>
+      <c r="N233" t="str" s="3">
+        <v>1—2年；统一起止未载。</v>
+      </c>
+      <c r="O233" t="str" s="3">
+        <v>结题专利、技术报告或论文1份；须本共享两个中心指定中英文署名。论文级别、第一单位、作者排序未载；原文一份/或不改为全部均要。</v>
+      </c>
+      <c r="P233" t="str" s="3">
+        <v>官方缓存完整正文未载。</v>
+      </c>
+      <c r="Q233" t="str" s="3">
+        <v>纸质申请2份，本人及单位负责人签字公章；电子签章扫描邮件80641842@qq.com；截至2026-09-30。邮寄江夏庙山开发区阳光大道1号电子电气学院430200。</v>
+      </c>
+      <c r="R233" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S233" t="str" s="3">
+        <v>原页404交人工保存完整正文及申请DOCX；核金额、IP外拨和署名验收细则。缓存条款已取保留，不回退全部未知。</v>
+      </c>
+      <c r="T233" t="str" s="3">
+        <v>https://ei.wtu.edu.cn/info/1360/17785.htm</v>
+      </c>
+      <c r="U233" t="str" s="3">
+        <v>https://ei.wtu.edu.cn/info/1360/17785.htm（申请DOCX直链未取得）</v>
+      </c>
+      <c r="V233" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W233" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X233" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y233" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z233" t="str" s="3">
+        <v>刘老师18971520301；80641842@qq.com。</v>
+      </c>
+      <c r="AA233" t="str" s="3">
+        <v>两中心共享一份2026公告计1项；缓存来源见本批逐名搜索第6组。</v>
+      </c>
+    </row>
+    <row r="234" ht="132" customHeight="1">
+      <c r="A234" t="str" s="3">
+        <v>N085</v>
+      </c>
+      <c r="B234" t="str" s="3">
+        <v>2026正式指南全文，截止当前未过；申请DOC首次验证码。</v>
+      </c>
+      <c r="C234" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D234" t="str" s="3">
+        <v>湖北省服装信息化工程技术研究中心</v>
+      </c>
+      <c r="E234" t="str" s="3">
+        <v>受理中·个人条件待确认</v>
+      </c>
+      <c r="F234" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G234" t="n" s="6">
+        <v>46310</v>
+      </c>
+      <c r="H234" t="str" s="3">
+        <v>原文10月15日前，是否含当日及小时未明确；2026-10-09核查仍窗口内。</v>
+      </c>
+      <c r="I234" t="str" s="3">
+        <v>智能可穿戴设备与健康监测：智能纺织品生物传感器、运动状态监测、睡眠状态分析；另有AIGC织物图案生成/多模态设计逆向解析、智能服装推荐画像等，原用途客观保留，不将推荐任务改机器人。</v>
+      </c>
+      <c r="J234" t="str" s="3">
+        <v>1—2万元/项；拟4项。</v>
+      </c>
+      <c r="K234" t="str" s="3">
+        <v>境内外高校科研机构科研人员或大型企事业技术开发在编在岗人员；原则副高及以上或博士；年龄/限项未载。</v>
+      </c>
+      <c r="L234" t="str" s="3">
+        <v>每年可不定期赴中心或派研究生，非明确必访天数；正文未载强制固定合作。</v>
+      </c>
+      <c r="M234" t="str" s="3">
+        <v>按中心2024修订经费管理办法，随立项通知发；具体费用、报销地点、外拨和支付节点未取得。</v>
+      </c>
+      <c r="N234" t="str" s="3">
+        <v>1—2年；统一起止未载。</v>
+      </c>
+      <c r="O234" t="str" s="3">
+        <v>半年进展报告；成果须中心指定中英文署名；论文/专利数量、第一单位和作者、验收指标未載。</v>
+      </c>
+      <c r="P234" t="str" s="3">
+        <v>中心及成果完成人共享；转让产业化需中心同意，经济收益1:1。</v>
+      </c>
+      <c r="Q234" t="str" s="3">
+        <v>10月15日前本人签字+单位负责人签字盖章申请3份寄中心，Word及签章页扫描发11094362@qq.com。</v>
+      </c>
+      <c r="R234" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S234" t="str" s="3">
+        <v>申请DOC验证码人工；经费管理办法随立项才发送尚缺，核外拨报销支付、成果指标及寄件邮编；本人在编在岗与实际限项待核。</v>
+      </c>
+      <c r="T234" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/19597.htm</v>
+      </c>
+      <c r="U234" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/system/_content/download.jsp?owner=1741397481&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=D046C08616CA299D335B4CA6219A93D5</v>
+      </c>
+      <c r="V234" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W234" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X234" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y234" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z234" t="str" s="3">
+        <v>罗老师027-59367297；11094362@qq.com；阳光大道1号计算机与人工智能学院。申报段邮编430073而页脚430200，须核寄件邮编。</v>
+      </c>
+      <c r="AA234" t="str" s="3">
+        <v>2026独立中心项目；不是2024纺织服装智能化机器人基金，不能因同邮箱合并。</v>
+      </c>
+    </row>
+    <row r="235" ht="132" customHeight="1">
+      <c r="A235" t="str" s="3">
+        <v>N086</v>
+      </c>
+      <c r="B235" t="str" s="3">
+        <v>官方搜索2026申报指南；原页首次超时停止。</v>
+      </c>
+      <c r="C235" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D235" t="str" s="3">
+        <v>先进纺纱织造及清洁生产国家地方联合工程实验室</v>
+      </c>
+      <c r="E235" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F235" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G235" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H235" t="str" s="3">
+        <v>具体时点未取得</v>
+      </c>
+      <c r="I235" t="str" s="3">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="J235" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K235" t="str" s="3">
+        <v>资格与限项未取得。</v>
+      </c>
+      <c r="L235" t="str" s="3">
+        <v>合作与访问未取得。</v>
+      </c>
+      <c r="M235" t="str" s="3">
+        <v>外拨、费用、报销和支付未取得。</v>
+      </c>
+      <c r="N235" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O235" t="str" s="3">
+        <v>成果数量、单位/作者署名、验收未取得。</v>
+      </c>
+      <c r="P235" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q235" t="str" s="3">
+        <v>提交要求未取得。</v>
+      </c>
+      <c r="R235" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S235" t="str" s="3">
+        <v>原页全文及附件人工保存，补具体机器人/装备任务和全部条款；未取得截止不能当当前受理。</v>
+      </c>
+      <c r="T235" t="str" s="3">
+        <v>https://nel.wtu.edu.cn/info/1552/2305.htm</v>
+      </c>
+      <c r="U235" t="str" s="3">
+        <v>原正文首次超时，附件链接未取得。</v>
+      </c>
+      <c r="V235" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W235" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X235" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y235" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z235" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+      <c r="AA235" t="str" s="3">
+        <v>国家地方联合工程室，非全国材料室同项目。</v>
+      </c>
+    </row>
+    <row r="236" ht="132" customHeight="1">
+      <c r="A236" t="str" s="3">
+        <v>N087</v>
+      </c>
+      <c r="B236" t="str" s="3">
+        <v>2022开放通知完整；指南/申请/管理RAR首次工具不支持。</v>
+      </c>
+      <c r="C236" t="str" s="3">
+        <v>闽江学院（现闽江大学）</v>
+      </c>
+      <c r="D236" t="str" s="3">
+        <v>工业机器人应用福建省高校工程研究中心</v>
+      </c>
+      <c r="E236" t="str" s="3">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="F236" t="str" s="3">
+        <v>2022</v>
+      </c>
+      <c r="G236" t="str" s="6">
+        <v>未取得</v>
+      </c>
+      <c r="H236" t="str" s="3">
+        <v>具体时点未取得</v>
+      </c>
+      <c r="I236" t="str" s="3">
+        <v>通知明确工业机器人基础技术创新，但年度具体任务只在RAR指南，待核；不借2026信息处理室套本中心任务。</v>
+      </c>
+      <c r="J236" t="str" s="3">
+        <v>1万元/项，拟2项。</v>
+      </c>
+      <c r="K236" t="str" s="3">
+        <v>海内外高校、科研机构等人员可按指南申请；详细学历职称年龄限项未载待RAR。</v>
+      </c>
+      <c r="L236" t="str" s="3">
+        <v>鼓励客座PI与中心固定人员共同申请，非已取得强制条款；访问未载。</v>
+      </c>
+      <c r="M236" t="str" s="3">
+        <v>外拨、费用、报销和支付未取得。</v>
+      </c>
+      <c r="N236" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O236" t="str" s="3">
+        <v>成果数量、单位/作者署名、验收未取得。</v>
+      </c>
+      <c r="P236" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q236" t="str" s="3">
+        <v>提交要求未取得。</v>
+      </c>
+      <c r="R236" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S236" t="str" s="3">
+        <v>下载RAR解压申请指南/申请书/管理办法，补具体任务、截止、资格合作、周期、外拨成果IP提交；同站2022-06-10公示说明已评审，不能当当前。</v>
+      </c>
+      <c r="T236" t="str" s="3">
+        <v>https://www.mju.edu.cn/imlab/2022/0408/c2194a131707/page.htm</v>
+      </c>
+      <c r="U236" t="str" s="3">
+        <v>https://www.mju.edu.cn/_upload/article/files/a6/fa/b3d491fe4d6f8cc152e0dbf0b597/7a8c2451-c4aa-400b-9b6c-8aaa7b628c40.rar</v>
+      </c>
+      <c r="V236" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W236" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X236" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y236" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="Z236" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+      <c r="AA236" t="str" s="3">
+        <v>2022中心基金1项；不是M088信息处理智能控制2026；网页当前署闽江大学，旧公告闽江学院。</v>
+      </c>
+    </row>
+    <row r="237" ht="132" customHeight="1">
+      <c r="A237" t="str" s="3">
+        <v>N088</v>
+      </c>
+      <c r="B237" t="str" s="3">
+        <v>2026正式通知完整；申请DOCX/汇总XLSX首验证码。</v>
+      </c>
+      <c r="C237" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D237" t="str" s="3">
+        <v>纺织新材料与先进加工全国重点实验室</v>
+      </c>
+      <c r="E237" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F237" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G237" t="n" s="6">
+        <v>46295</v>
+      </c>
+      <c r="H237" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I237" t="str" s="3">
+        <v>资助范围含纺织材料跨尺度成型方法与智能装备、柔性可穿戴智能化/先进制造，但未展开装备感知控制等任务；当前机器人联系证据不足待细化，不能只凭智能装备收为确定相关。其余多功能材料/医学材料/纤维/印染原样保留。</v>
+      </c>
+      <c r="J237" t="str" s="3">
+        <v>校外可申报类别：重点6—10万元、一般2—4万元；重大100万元与经纬未来2—4万元明确面向全校，不当本人类别。</v>
+      </c>
+      <c r="K237" t="str" s="3">
+        <v>高校科研产业固定岗位校内外人员，无科研道德不良；博士或高级含副高；≤60周岁，年龄基准未载；每年1项，有本室未结项目不受理。重大及经纬未来限本校，后者≤35优先不套校外。</v>
+      </c>
+      <c r="L237" t="str" s="3">
+        <v>必须联合本室固定人员实质合作，获批为流动人员；访问时长未载。</v>
+      </c>
+      <c r="M237" t="str" s="3">
+        <v>先50%拨PI单位、结题后50%拨PI单位，明确外拨；按专款办法/合同，开支科目及报销细节未取。</v>
+      </c>
+      <c r="N237" t="str" s="3">
+        <v>2年，2027-01-01至2028-12-31；不按期提前3月申请延期。</v>
+      </c>
+      <c r="O237" t="str" s="3">
+        <v>重点≥2篇中科院一区且IF≥15，一般≥1篇同标准；责任作者第一或通讯所在单位须有本室署名和基金号；第一机构未强制。Advanced Textiles每篇等同1合格论文。特殊领域书面申请可报告结合专利标准产品；重大8篇+1省部二等奖或符合国奖推荐学会一等奖指标仅本校类别。</v>
+      </c>
+      <c r="P237" t="str" s="3">
+        <v>完整通知未载成果权属/转让。</v>
+      </c>
+      <c r="Q237" t="str" s="3">
+        <v>申请书及汇总表，签字盖章PDF仅电子无纸，fzxcljgjs@wtu.edu.cn；本人+单位负责人签字单位公章，主题姓名-单位-2026基金；9月30日截止。11月30前书面通知是结果期限。</v>
+      </c>
+      <c r="R237" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S237" t="str" s="3">
+        <v>申请/汇总验证码人工；补实际机器人/可穿戴装备任务、IP、费用报销及合同。不把重大100万放校外金额；2027—2028是执行周期非2027申报。</v>
+      </c>
+      <c r="T237" t="str" s="3">
+        <v>https://fzcljs.wtu.edu.cn/info/1017/9306.htm</v>
+      </c>
+      <c r="U237" t="str" s="3">
+        <v>https://fzcljs.wtu.edu.cn/system/_content/download.jsp?owner=1361027038&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=8324319F414B7F819B62D059CC45F211
+https://fzcljs.wtu.edu.cn/system/_content/download.jsp?owner=1361027038&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=39EF323B6330301EE64C3632B55E538D</v>
+      </c>
+      <c r="V237" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W237" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X237" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y237" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z237" t="str" s="3">
+        <v>李老师027-59367824；fzxcljgjs@wtu.edu.cn；阳光校区建全科学中心217室430200。</v>
+      </c>
+      <c r="AA237" t="str" s="3">
+        <v>一个2026通知含多类别，校内专属类别如实标限；不将2027执行期限拆新年度。</v>
+      </c>
+    </row>
+    <row r="238" ht="132" customHeight="1">
+      <c r="A238" t="str" s="3">
+        <v>N089</v>
+      </c>
+      <c r="B238" t="str" s="3">
+        <v>2024正式指南全文；申请DOC首验证码。</v>
+      </c>
+      <c r="C238" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D238" t="str" s="3">
+        <v>纺织服装智能化湖北省工程研究中心</v>
+      </c>
+      <c r="E238" t="str" s="3">
+        <v>已截止</v>
+      </c>
+      <c r="F238" t="str" s="3">
+        <v>2024</v>
+      </c>
+      <c r="G238" t="n" s="6">
+        <v>45550</v>
+      </c>
+      <c r="H238" t="str" s="3">
+        <v>9月15日前，是否含当日及小时未载；已过。</v>
+      </c>
+      <c r="I238" t="str" s="3">
+        <v>机器人视觉下语义分割、目标检测识别；机器人对布料服装柔性对象操纵；三维人体建模测量检测姿态估计；另含服装大数据跨模态/知识图谱/趋势推荐生成等原行业任务。</v>
+      </c>
+      <c r="J238" t="str" s="3">
+        <v>1—2万元/项，拟4—5项。</v>
+      </c>
+      <c r="K238" t="str" s="3">
+        <v>境内外高校科研机构科研人员或大型企事业技术开发在编在岗人员；原则副高及以上或博士；年龄/限项未载。</v>
+      </c>
+      <c r="L238" t="str" s="3">
+        <v>每年可不定期赴中心或派研究生，非明确必访天数；正文未载强制固定合作。</v>
+      </c>
+      <c r="M238" t="str" s="3">
+        <v>按中心2024修订经费管理办法，随立项通知发；具体费用、报销地点、外拨和支付节点未取得。</v>
+      </c>
+      <c r="N238" t="str" s="3">
+        <v>1—2年；统一起止未载。</v>
+      </c>
+      <c r="O238" t="str" s="3">
+        <v>成果须本室指定中英文署名；数量、第一机构/作者、验收指标未载；未载半年报告不套2026服装信息化要求。</v>
+      </c>
+      <c r="P238" t="str" s="3">
+        <v>中心及成果完成人共享；转让产业化需中心同意，经济收益1:1。</v>
+      </c>
+      <c r="Q238" t="str" s="3">
+        <v>9月15日前本人和单位负责人签字盖章申请3份寄中心，Word加签章页扫描发11094362@qq.com。</v>
+      </c>
+      <c r="R238" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S238" t="str" s="3">
+        <v>申请DOC验证码；补2024经费办法/合同、外拨报销支付成果验收和邮编；未定位2026/27本中心新公告不当无基金。</v>
+      </c>
+      <c r="T238" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/7067.htm</v>
+      </c>
+      <c r="U238" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/system/_content/download.jsp?owner=1741397481&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=00AB214587230719C2F9832CD2DE97FB</v>
+      </c>
+      <c r="V238" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W238" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X238" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y238" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z238" t="str" s="3">
+        <v>罗老师027-59367297；11094362@qq.com；阳光大道1号计算机与人工智能学院。申报段邮编430073而页脚430200，须核寄件邮编。</v>
+      </c>
+      <c r="AA238" t="str" s="3">
+        <v>2024明确机器人柔性操纵任务，独立于2026服装信息化，即使联系人邮箱相同也不合并。</v>
+      </c>
+    </row>
+    <row r="239" ht="132" customHeight="1">
+      <c r="A239" t="str" s="3">
+        <v>N090</v>
+      </c>
+      <c r="B239" t="str" s="3">
+        <v>2026指南全文；申请DOC首次超时。</v>
+      </c>
+      <c r="C239" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D239" t="str" s="3">
+        <v>纺织新材料及其应用研究湖北省重点实验室</v>
+      </c>
+      <c r="E239" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F239" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G239" t="n" s="6">
+        <v>46302</v>
+      </c>
+      <c r="H239" t="str" s="3">
+        <v>以邮件收到为准，小时未载；已过。</v>
+      </c>
+      <c r="I239" t="str" s="3">
+        <v>5方向为功能高分子/纤维、无机复合材料、纤维可穿戴供能器件、柔性智能材料与传感器件设计、加工极端服役；具体机器人感知/设备集成任务未展开，传感器件联系待原表或方向任务核，不只凭智能保留。</v>
+      </c>
+      <c r="J239" t="str" s="3">
+        <v>1—3万元/项。</v>
+      </c>
+      <c r="K239" t="str" s="3">
+        <v>境内外高校科研企业在职，博士或中级及以上，相关科研基础；PI限1项、有本室未结不支持。年龄未载。</v>
+      </c>
+      <c r="L239" t="str" s="3">
+        <v>鼓励固定合作，非强制；PI须参加实验室年会并成果汇报，无固定驻室时长。</v>
+      </c>
+      <c r="M239" t="str" s="3">
+        <v>完整指南未载外拨费用报销支付。</v>
+      </c>
+      <c r="N239" t="str" s="3">
+        <v>一般1年，2027-01-01至2027-12-31。</v>
+      </c>
+      <c r="O239" t="str" s="3">
+        <v>PI第一或通讯SCI期刊1篇，本室第一或第二机构且武汉纺织大学共同署名；指定基金致谢。需参加年会汇报。</v>
+      </c>
+      <c r="P239" t="str" s="3">
+        <v>完整指南未载。</v>
+      </c>
+      <c r="Q239" t="str" s="3">
+        <v>Word+签章PDF电子lpchen@wtu.edu.cn，主题2026开放课题申请-姓名-单位；以签章PDF为准无纸，10月7日邮件收到截止。</v>
+      </c>
+      <c r="R239" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S239" t="str" s="3">
+        <v>原DOC首超时人工；先补柔性传感具体装备/感知联系，再补IP外拨费用及签章细节。公告发布9-16/落款9-14均保留；2027是执行周期。</v>
+      </c>
+      <c r="T239" t="str" s="3">
+        <v>https://mse.wtu.edu.cn/info/1021/16089.htm</v>
+      </c>
+      <c r="U239" t="str" s="3">
+        <v>https://mse.wtu.edu.cn/system/_content/download.jsp?owner=1781605617&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=E984920A683C293035A055D13B1D5088</v>
+      </c>
+      <c r="V239" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W239" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X239" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y239" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z239" t="str" s="3">
+        <v>陈老师18030816728；lpchen@wtu.edu.cn；阳光大道1号材料学院430200。</v>
+      </c>
+      <c r="AA239" t="str" s="3">
+        <v>2026独立省室，非全国材料室；传感器件不能自动认机器人任务。</v>
+      </c>
+    </row>
+    <row r="240" ht="132" customHeight="1">
+      <c r="A240" t="str" s="3">
+        <v>N091</v>
+      </c>
+      <c r="B240" t="str" s="3">
+        <v>2026指南完整；申请DOCX/汇总XLSX首次验证码。</v>
+      </c>
+      <c r="C240" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D240" t="str" s="3">
+        <v>生物质纤维与生态染整湖北省重点实验室</v>
+      </c>
+      <c r="E240" t="str" s="3">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="F240" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G240" t="n" s="6">
+        <v>46295</v>
+      </c>
+      <c r="H240" t="str" s="3">
+        <v>具体时点未载。</v>
+      </c>
+      <c r="I240" t="str" s="3">
+        <v>年度广义范围纤维表界面/生物质生态染整、跨尺度成型智能装备、柔性可穿戴/先进制造等，未细化机器人或相关装备具体感知控制任务，不能凭平台名称直接剔除或凭智能装备认相关。</v>
+      </c>
+      <c r="J240" t="str" s="3">
+        <v>重点5万元、一般2万元、青年1万元。青年类别额外资格未载。</v>
+      </c>
+      <c r="K240" t="str" s="3">
+        <v>高校科研产业固定岗位校内外人员，无道德不良；高级或博士，≤50周岁；每年度1项，年龄计算基准未载。</v>
+      </c>
+      <c r="L240" t="str" s="3">
+        <v>要求联合本室固定人员实质合作，获批流动人员；访问时长未载。</v>
+      </c>
+      <c r="M240" t="str" s="3">
+        <v>立项授权金额直接拨申请人单位，明确外拨；按专款办法/合同，支付节点和开支细节未取。</v>
+      </c>
+      <c r="N240" t="str" s="3">
+        <v>2年，2027-01-01至2028-12-31；延期提前3月申请。</v>
+      </c>
+      <c r="O240" t="str" s="3">
+        <v>重点≥1中科院一区且IF≥5；一般≥1中科院二区以上；青年≥1纺织类SCI。责任作者第一/通讯机构须署本室及基金号，第一单位未强制。Advanced Textiles原文等同一区且IF≥10，保留与重点门槛差异；特殊领域书面申请报告结合专利标准产品。</v>
+      </c>
+      <c r="P240" t="str" s="3">
+        <v>完整通知未载权属/转让。</v>
+      </c>
+      <c r="Q240" t="str" s="3">
+        <v>申请及汇总签章PDF电子fzgc@wtu.edu.cn，无纸；本人/单位负责人签字、公章，主题姓名-单位-2026基金，9-30截止；10-30结果期限不是申请。</v>
+      </c>
+      <c r="R240" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S240" t="str" s="3">
+        <v>申请汇总验证码人工，先补具体装备/可穿戴任务，再补IP、费用办法及青年额外限制；不套全国材料室IF15指标。</v>
+      </c>
+      <c r="T240" t="str" s="3">
+        <v>https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="U240" t="str" s="3">
+        <v>https://te.wtu.edu.cn/system/_content/download.jsp?owner=1269691753&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=7684D0C3D17A96816FD40DB45D2139C1
+https://te.wtu.edu.cn/system/_content/download.jsp?owner=1269691753&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=9C4C7C31E518CBEC2664C685076663ED</v>
+      </c>
+      <c r="V240" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W240" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X240" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y240" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z240" t="str" s="3">
+        <v>胡老师027-59367695；fzgc@wtu.edu.cn；阳光校区430200。</v>
+      </c>
+      <c r="AA240" t="str" s="3">
+        <v>2026省室独立年度，2027—28是周期，非另两年度项目。</v>
+      </c>
+    </row>
+    <row r="241" ht="132" customHeight="1">
+      <c r="A241" t="str" s="3">
+        <v>N092</v>
+      </c>
+      <c r="B241" t="str" s="3">
+        <v>2026通知完整；指南/申请首次验证码，实际任务未取不进首页。</v>
+      </c>
+      <c r="C241" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="D241" t="str" s="3">
+        <v>工业雷管智能装配湖北省工程研究中心</v>
+      </c>
+      <c r="E241" t="str" s="3">
+        <v>线索待核·截止未到</v>
+      </c>
+      <c r="F241" t="str" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G241" t="n" s="6">
+        <v>46310</v>
+      </c>
+      <c r="H241" t="str" s="3">
+        <v>10月15日前，是否含当日及小时未载，现日历未到但缺任务资格。</v>
+      </c>
+      <c r="I241" t="str" s="3">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="J241" t="str" s="3">
+        <v>未取得</v>
+      </c>
+      <c r="K241" t="str" s="3">
+        <v>资格与限项未取得。</v>
+      </c>
+      <c r="L241" t="str" s="3">
+        <v>合作与访问未取得。</v>
+      </c>
+      <c r="M241" t="str" s="3">
+        <v>外拨、费用、报销和支付未取得。</v>
+      </c>
+      <c r="N241" t="str" s="3">
+        <v>周期未取得。</v>
+      </c>
+      <c r="O241" t="str" s="3">
+        <v>成果数量、单位/作者署名、验收未取得。</v>
+      </c>
+      <c r="P241" t="str" s="3">
+        <v>知识产权未取得。</v>
+      </c>
+      <c r="Q241" t="str" s="3">
+        <v>申请纸质2份邮寄阳光校区10号楼516办公室，电子wchen@wtu.edu.cn；截止10-15前。</v>
+      </c>
+      <c r="R241" t="str" s="3">
+        <v>本人博士/南京信息工程大学现职已知；个人条件及合作未核，不等同可申请。</v>
+      </c>
+      <c r="S241" t="str" s="3">
+        <v>下载2026指南/申请，确认具体机器人装配/感知/控制任务、金额资格合作、费用外拨周期成果IP；不得以截止未到直接写可申请。通讯邮编430073而学院页脚430200冲突待核。</v>
+      </c>
+      <c r="T241" t="str" s="3">
+        <v>https://me.wtu.edu.cn/info/1041/16914.htm</v>
+      </c>
+      <c r="U241" t="str" s="3">
+        <v>https://me.wtu.edu.cn/system/_content/download.jsp?owner=1594497525&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=4909228D626CA720170BA21B693B5937
+https://me.wtu.edu.cn/system/_content/download.jsp?owner=1594497525&amp;urltype=news.DownloadAttachUrl&amp;wbfileid=8F6FABC6BB6C6F311ACA60372EA53E9F</v>
+      </c>
+      <c r="V241" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="W241" t="str" s="3">
+        <v>尚未落实合作人员</v>
+      </c>
+      <c r="X241" t="str" s="3">
+        <v>客观条款及具体缺口见对应字段；不作评分或推荐。</v>
+      </c>
+      <c r="Y241" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="Z241" t="str" s="3">
+        <v>陈伟027-59367513；wchen@wtu.edu.cn；阳光校区10号楼516，公告邮编430073待核。</v>
+      </c>
+      <c r="AA241" t="str" s="3">
+        <v>当前正式通知存在但年度任务指南未取，待核非首页；不凭智能装配标题入相关。</v>
       </c>
     </row>
   </sheetData>
@@ -21181,6 +22037,16 @@
     <hyperlink ref="T229" ns1:id="rIdResume451"/>
     <hyperlink ref="T230" ns1:id="rIdResume452"/>
     <hyperlink ref="T231" ns1:id="rIdResume453"/>
+    <hyperlink ref="T232" ns1:id="rIdResume454"/>
+    <hyperlink ref="T233" ns1:id="rIdResume455"/>
+    <hyperlink ref="T234" ns1:id="rIdResume456"/>
+    <hyperlink ref="T235" ns1:id="rIdResume457"/>
+    <hyperlink ref="T236" ns1:id="rIdResume458"/>
+    <hyperlink ref="T237" ns1:id="rIdResume459"/>
+    <hyperlink ref="T238" ns1:id="rIdResume460"/>
+    <hyperlink ref="T239" ns1:id="rIdResume461"/>
+    <hyperlink ref="T240" ns1:id="rIdResume462"/>
+    <hyperlink ref="T241" ns1:id="rIdResume463"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -52318,6 +53184,703 @@
       </c>
       <c r="H1007" t="str" s="3"/>
       <c r="I1007" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1008" ht="52.5" customHeight="1">
+      <c r="A1008" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1008" t="str" s="3">
+        <v>湖南理工学院/湖南工业大学/湖北文理学院/武汉纺织大学</v>
+      </c>
+      <c r="C1008" t="str" s="3">
+        <v>湖南/湖北</v>
+      </c>
+      <c r="D1008" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1008" t="str" s="3">
+        <v>查询：site:hnist.edu.cn "开放基金" 机器人 / site:hut.edu.cn "开放课题" "2026" / site:hbuas.edu.cn "开放基金" "2026" / site:wtu.edu.cn "开放课题" 机器人；线索：关于纺织服装智能化湖北省工程研究中心2024年度开放课题申报的通知-武汉纺织大学-计算机与人工智能学院；2026年先进纺纱织造及清洁生产国家地方联合工程实验室开放课题申报指南-武汉纺织大学国家工程实验室；智能微纳医学检验装备及关键技术湖北省工程研究中心/湖北省功能纤维加工及检测工程技术研究中心2026年度开放课题申请通知-武汉纺织大学-电子与电气工程学院；纺织新材料与先进加工全国重点实验室 2026年度开放课题申请通知-纺织新材料与先进加工全国重点实验室；关于湖北省服装信息化工程技术研究中心2026年度开放课题申报的通知-武汉纺织大学-计算机与人工智能学院；生物质纤维与生态染整湖北省重点实验室 2026年度开放课题申请通知-武汉纺织大学 纺织科学与工程学院</v>
+      </c>
+      <c r="F1008" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1008" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1008" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/7067.htm
+https://nel.wtu.edu.cn/info/1552/2305.htm
+https://ei.wtu.edu.cn/info/1360/17785.htm
+https://fzcljs.wtu.edu.cn/info/1017/9306.htm
+https://csai.wtu.edu.cn/info/1063/19597.htm
+https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="I1008" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第470项</v>
+      </c>
+    </row>
+    <row r="1009" ht="52.5" customHeight="1">
+      <c r="A1009" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1009" t="str" s="3">
+        <v>太原科技大学/安徽工程大学/闽江学院/湖南工程学院</v>
+      </c>
+      <c r="C1009" t="str" s="3">
+        <v>山西/安徽/福建/湖南</v>
+      </c>
+      <c r="D1009" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1009" t="str" s="3">
+        <v>查询：site:tyust.edu.cn "开放基金" "2026" / site:ahpu.edu.cn "开放课题" "2026" / site:mju.edu.cn "开放基金" 机器人 / site:hnie.edu.cn "开放基金" "2026"；线索：闽江学院计算机科学与技术应用型学科 2020年度开放基金申请指南；工业机器人应用福建省高校工程研究中心2022年度开放基金申请通知；关于福建省信息处理与智能控制重点实验室(闽江学院) 2021年度拟立项开放课题的公示；生态纺织教育部重点实验室（江南大学）；福建省海洋传感功能材料重点实验室；福建省海洋传感功能材料重点实验室</v>
+      </c>
+      <c r="F1009" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1009" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1009" t="str" s="3">
+        <v>https://jsj.mju.edu.cn/_t265/2020/1203/c2269a101364/page.htm
+https://www.mju.edu.cn/imlab/2022/0408/c2194a131707/page.htm
+https://www.mju.edu.cn/imlab/2021/0414/c2194a110829/page.htm
+https://www.mju.edu.cn/_upload/article/files/91/bc/5b9e7ddd4997ae7487fdb5bafad9/3af08798-d2bc-4806-adff-8a2e9f3709a5.pdf
+https://www.mju.edu.cn/_upload/article/files/c0/0b/066ff07546bba1df85141926e4d3/3a7c1565-fea4-4dfe-a1a6-c69b68b03d46.pdf
+https://www.mju.edu.cn/_upload/article/files/a3/8b/1800ef7f4a5ba8699f834655dbf5/de4a7df6-2941-4302-8eb6-b0a0f02f2d62.pdf</v>
+      </c>
+      <c r="I1009" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第471项</v>
+      </c>
+    </row>
+    <row r="1010" ht="52.5" customHeight="1">
+      <c r="A1010" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1010" t="str" s="3">
+        <v>武汉纺织与闽江目录/2026—2027年度机器人机制</v>
+      </c>
+      <c r="C1010" t="str" s="3">
+        <v>湖北/福建</v>
+      </c>
+      <c r="D1010" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1010" t="str" s="3">
+        <v>查询：site:wtu.edu.cn "纺织服装智能化" "2026" "开放" / site:wtu.edu.cn "科研平台" "重点实验室" / site:mju.edu.cn "工业机器人应用" "2026" "开放" / site:mju.edu.cn "工业机器人应用" "2027" "开放"；线索：武汉纺织大学-技术研究院；关于进一步完善技术研究党委及下属各单位运行机制和议事规则的意见-武汉纺织大学-技术研究院；科研平台-武汉纺织大学官方主页；技术研究院开展实验室研究生党员先锋示范岗专项检查 筑牢科研安全防线-武汉纺织大学-技术研究院；省部级科研平台-武汉纺织大学科学技术发展院；关于收集全体教师荣誉证书与奖章扫描件的通知-纺织新材料与先进加工全国重点实验室</v>
+      </c>
+      <c r="F1010" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1010" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1010" t="str" s="3">
+        <v>https://tri.wtu.edu.cn/index.htm
+https://tri.wtu.edu.cn/info/1411/12562.htm
+https://www.wtu.edu.cn/kxyj/kypt.htm
+https://tri.wtu.edu.cn/info/1451/7412.htm
+https://kyc.wtu.edu.cn/kypt/sbjkypt.htm
+https://fzcljs.wtu.edu.cn/info/1019/8836.htm</v>
+      </c>
+      <c r="I1010" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第472项</v>
+      </c>
+    </row>
+    <row r="1011" ht="52.5" customHeight="1">
+      <c r="A1011" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1011" t="str" s="3">
+        <v>武汉纺织省部装备平台逐名</v>
+      </c>
+      <c r="C1011" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D1011" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1011" t="str" s="3">
+        <v>查询：site:wtu.edu.cn "工业雷管智能装配" "开放" / site:wtu.edu.cn "智慧感知与计算" "开放" / site:wtu.edu.cn "高端纺织装备" "开放课题" / site:wtu.edu.cn "三维纺织" "开放课题"；线索：生物质纤维与生态染整湖北省重点实验室 2026年度开放课题申请通知-武汉纺织大学 纺织科学与工程学院</v>
+      </c>
+      <c r="F1011" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1011" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1011" t="str" s="3">
+        <v>https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="I1011" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第473项</v>
+      </c>
+    </row>
+    <row r="1012" ht="52.5" customHeight="1">
+      <c r="A1012" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1012" t="str" s="3">
+        <v>武汉纺织相关平台2026—2027补漏</v>
+      </c>
+      <c r="C1012" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D1012" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1012" t="str" s="3">
+        <v>查询：site:wtu.edu.cn "纺织服装智能化" "开放" "2026" / site:wtu.edu.cn "数字化纺织装备" "开放" "2027" / site:wtu.edu.cn "纺织纤维及制品" "开放" "2026" / site:wtu.edu.cn "智能微纳医学" "开放" "2027"；线索：武汉纺织大学-技术研究院；罗梦颖-武汉纺织大学-技术研究院；关于纺织新材料及其应用研究湖北省重点实验室2026年度开放课题申请的通知-武汉纺织大学材料科学与工程学院；钟亚平-武汉纺织大学-技术研究院；王文-武汉纺织大学-技术研究院；技术研究院关于开展“书记主任面对面”活动的通知-武汉纺织大学-技术研究院</v>
+      </c>
+      <c r="F1012" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1012" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1012" t="str" s="3">
+        <v>https://tri.wtu.edu.cn/
+https://tri.wtu.edu.cn/info/1241/12152.htm
+https://mse.wtu.edu.cn/info/1021/16089.htm
+https://tri.wtu.edu.cn/info/1241/12072.htm
+https://tri.wtu.edu.cn/info/1231/12272.htm
+https://tri.wtu.edu.cn/info/1004/7062.htm</v>
+      </c>
+      <c r="I1012" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第474项</v>
+      </c>
+    </row>
+    <row r="1013" ht="52.5" customHeight="1">
+      <c r="A1013" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1013" t="str" s="3">
+        <v>武汉纺织目录相关平台2026—2027剩余机制</v>
+      </c>
+      <c r="C1013" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D1013" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1013" t="str" s="3">
+        <v>查询：site:wtu.edu.cn "功能纤维加工及检测" "开放" "2026" / site:wtu.edu.cn "高端纺织装备" "开放" "2026" "2027" / site:wtu.edu.cn "智慧感知与计算" "开放" "2026" "2027" / site:wtu.edu.cn "工业雷管智能装配" "开放" "2026" "2027"；线索：智能微纳医学检验装备及关键技术湖北省工程研究中心/湖北省功能纤维加工及检测工程技术研究中心2026年度开放课题申请通知-武汉纺织大学-电子与电气工程学院；生物质纤维与生态染整湖北省重点实验室 2026年度开放课题申请通知-武汉纺织大学 纺织科学与工程学院</v>
+      </c>
+      <c r="F1013" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1013" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1013" t="str" s="3">
+        <v>https://ei.wtu.edu.cn/info/1360/17785.htm
+https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="I1013" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第475项</v>
+      </c>
+    </row>
+    <row r="1014" ht="52.5" customHeight="1">
+      <c r="A1014" t="str" s="3">
+        <v>2026-10-09武汉纺织全目录及闽江机器人接续</v>
+      </c>
+      <c r="B1014" t="str" s="3">
+        <v>湖北工业目录装备相关平台剩余机制</v>
+      </c>
+      <c r="C1014" t="str" s="3">
+        <v>湖北</v>
+      </c>
+      <c r="D1014" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1014" t="str" s="3">
+        <v>查询：site:hbut.edu.cn "制造工业数智化" "开放" / site:hbut.edu.cn "桥梁安全监控技术与装备" "开放" / site:hbut.edu.cn "水环境污染检测先进技术与装备" "开放" / site:hbut.edu.cn "电网智能控制与装备" "开放"；线索：2026年开放基金（基础研究类）申报指南征集通知-太阳能高效利用及储能运行控制湖北省重点实验室；2025年开放基金（基础研究类）申报指南征集通知-太阳能高效利用湖北省协同创新中心；学院获批2项省级科研平台-欢迎访问湖北工业大学计算机科学与人工智能学院官方网站；关于调整、公布学校实验室名称的通知（湖工大资[2018]6号）-湖北工业大学实验室与资产管理处；工业和信息化部办公厅关于组织开展 2025 年未来产业创新任务揭榜挂帅工作的通知-湖北工业大学科学技术发展研究院</v>
+      </c>
+      <c r="F1014" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1014" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1014" t="str" s="3">
+        <v>https://sees.hbut.edu.cn/info/1021/2192.htm
+https://hbsolar.hbut.edu.cn/info/1013/1783.htm
+https://scs.hbut.edu.cn/info/1030/4492.htm
+https://zcc.hbut.edu.cn/info/1171/1119.htm
+https://kjcy.hbut.edu.cn/info/1052/5539.htm</v>
+      </c>
+      <c r="I1014" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第476项</v>
+      </c>
+    </row>
+    <row r="1015" ht="52.5" customHeight="1">
+      <c r="A1015" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1015" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1015" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1015" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1015" t="str" s="3">
+        <v>湖北省数字化纺织装备重点实验室；2025—2026；N083；正式2025—2026通知全文；指南验证码，申请DOC超时。</v>
+      </c>
+      <c r="F1015" t="str" s="3">
+        <v>下载指南/表补实际机器人/装备任务及金额资格合作外拨周期成果IP；网页发布2025-10-27而落款2024-10-19冲突，不擅自改成2024项目。</v>
+      </c>
+      <c r="G1015" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1015" t="str" s="3">
+        <v>https://me.wtu.edu.cn/info/1041/13404.htm</v>
+      </c>
+      <c r="I1015" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1016" ht="52.5" customHeight="1">
+      <c r="A1016" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1016" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1016" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1016" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1016" t="str" s="3">
+        <v>智能微纳医学检验装备及关键技术湖北省工程研究中心/湖北省功能纤维加工及检测工程技术研究中心；2026；N084；原页首次404停止；后续独立平台机制查询的官方搜索缓存呈现完整指南，逐字段用缓存证据，不重试原页。</v>
+      </c>
+      <c r="F1016" t="str" s="3">
+        <v>原页404交人工保存完整正文及申请DOCX；核金额、IP外拨和署名验收细则。缓存条款已取保留，不回退全部未知。</v>
+      </c>
+      <c r="G1016" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1016" t="str" s="3">
+        <v>https://ei.wtu.edu.cn/info/1360/17785.htm</v>
+      </c>
+      <c r="I1016" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1017" ht="52.5" customHeight="1">
+      <c r="A1017" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1017" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1017" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1017" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1017" t="str" s="3">
+        <v>湖北省服装信息化工程技术研究中心；2026；N085；2026正式指南全文，截止当前未过；申请DOC首次验证码。</v>
+      </c>
+      <c r="F1017" t="str" s="3">
+        <v>申请DOC验证码人工；经费管理办法随立项才发送尚缺，核外拨报销支付、成果指标及寄件邮编；本人在编在岗与实际限项待核。</v>
+      </c>
+      <c r="G1017" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1017" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/19597.htm</v>
+      </c>
+      <c r="I1017" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1018" ht="52.5" customHeight="1">
+      <c r="A1018" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1018" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1018" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1018" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1018" t="str" s="3">
+        <v>先进纺纱织造及清洁生产国家地方联合工程实验室；2026；N086；官方搜索2026申报指南；原页首次超时停止。</v>
+      </c>
+      <c r="F1018" t="str" s="3">
+        <v>原页全文及附件人工保存，补具体机器人/装备任务和全部条款；未取得截止不能当当前受理。</v>
+      </c>
+      <c r="G1018" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1018" t="str" s="3">
+        <v>https://nel.wtu.edu.cn/info/1552/2305.htm</v>
+      </c>
+      <c r="I1018" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1019" ht="52.5" customHeight="1">
+      <c r="A1019" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1019" t="str" s="3">
+        <v>闽江学院（现闽江大学）</v>
+      </c>
+      <c r="C1019" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="D1019" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1019" t="str" s="3">
+        <v>工业机器人应用福建省高校工程研究中心；2022；N087；2022开放通知完整；指南/申请/管理RAR首次工具不支持。</v>
+      </c>
+      <c r="F1019" t="str" s="3">
+        <v>下载RAR解压申请指南/申请书/管理办法，补具体任务、截止、资格合作、周期、外拨成果IP提交；同站2022-06-10公示说明已评审，不能当当前。</v>
+      </c>
+      <c r="G1019" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1019" t="str" s="3">
+        <v>https://www.mju.edu.cn/imlab/2022/0408/c2194a131707/page.htm</v>
+      </c>
+      <c r="I1019" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1020" ht="52.5" customHeight="1">
+      <c r="A1020" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1020" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1020" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1020" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1020" t="str" s="3">
+        <v>纺织新材料与先进加工全国重点实验室；2026；N088；2026正式通知完整；申请DOCX/汇总XLSX首验证码。</v>
+      </c>
+      <c r="F1020" t="str" s="3">
+        <v>申请/汇总验证码人工；补实际机器人/可穿戴装备任务、IP、费用报销及合同。不把重大100万放校外金额；2027—2028是执行周期非2027申报。</v>
+      </c>
+      <c r="G1020" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1020" t="str" s="3">
+        <v>https://fzcljs.wtu.edu.cn/info/1017/9306.htm</v>
+      </c>
+      <c r="I1020" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1021" ht="52.5" customHeight="1">
+      <c r="A1021" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1021" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1021" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1021" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1021" t="str" s="3">
+        <v>纺织服装智能化湖北省工程研究中心；2024；N089；2024正式指南全文；申请DOC首验证码。</v>
+      </c>
+      <c r="F1021" t="str" s="3">
+        <v>申请DOC验证码；补2024经费办法/合同、外拨报销支付成果验收和邮编；未定位2026/27本中心新公告不当无基金。</v>
+      </c>
+      <c r="G1021" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1021" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/7067.htm</v>
+      </c>
+      <c r="I1021" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1022" ht="52.5" customHeight="1">
+      <c r="A1022" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1022" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1022" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1022" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1022" t="str" s="3">
+        <v>纺织新材料及其应用研究湖北省重点实验室；2026；N090；2026指南全文；申请DOC首次超时。</v>
+      </c>
+      <c r="F1022" t="str" s="3">
+        <v>原DOC首超时人工；先补柔性传感具体装备/感知联系，再补IP外拨费用及签章细节。公告发布9-16/落款9-14均保留；2027是执行周期。</v>
+      </c>
+      <c r="G1022" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1022" t="str" s="3">
+        <v>https://mse.wtu.edu.cn/info/1021/16089.htm</v>
+      </c>
+      <c r="I1022" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1023" ht="52.5" customHeight="1">
+      <c r="A1023" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1023" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1023" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1023" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1023" t="str" s="3">
+        <v>生物质纤维与生态染整湖北省重点实验室；2026；N091；2026指南完整；申请DOCX/汇总XLSX首次验证码。</v>
+      </c>
+      <c r="F1023" t="str" s="3">
+        <v>申请汇总验证码人工，先补具体装备/可穿戴任务，再补IP、费用办法及青年额外限制；不套全国材料室IF15指标。</v>
+      </c>
+      <c r="G1023" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1023" t="str" s="3">
+        <v>https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="I1023" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1024" ht="52.5" customHeight="1">
+      <c r="A1024" t="str" s="3">
+        <v>2026-10-09独立年度公告核验</v>
+      </c>
+      <c r="B1024" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1024" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1024" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1024" t="str" s="3">
+        <v>工业雷管智能装配湖北省工程研究中心；2026；N092；2026通知完整；指南/申请首次验证码，实际任务未取不进首页。</v>
+      </c>
+      <c r="F1024" t="str" s="3">
+        <v>下载2026指南/申请，确认具体机器人装配/感知/控制任务、金额资格合作、费用外拨周期成果IP；不得以截止未到直接写可申请。通讯邮编430073而学院页脚430200冲突待核。</v>
+      </c>
+      <c r="G1024" t="str" s="3">
+        <v>本公告完整正文已读，不等于所有平台查全。</v>
+      </c>
+      <c r="H1024" t="str" s="3">
+        <v>https://me.wtu.edu.cn/info/1041/16914.htm</v>
+      </c>
+      <c r="I1024" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1025" ht="52.5" customHeight="1">
+      <c r="A1025" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1025" t="str" s="3">
+        <v>武汉纺织大学</v>
+      </c>
+      <c r="C1025" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1025" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1025" t="str" s="3">
+        <v>官网科研平台完整42牌目；科研处省部行业目录完整34牌目，含市级项及旧名称，两个重叠清单不相加76独立实验室。机械院科研机构完整5项；2025—26数字装备N083、2026国家联合N086首指南失败；2026雷管N092通知完整指南验证码，虽10-15截止任务资格未知待核。智能micro检验/功能纤维2026共享N084首次404，但独立平台机制查询官方缓存全文取得，保留已核条款；医学影像与穿戴实际任务，不套机器人应用。</v>
+      </c>
+      <c r="F1025" t="str" s="3">
+        <v>已取目录不等于42平台年度完成；纺织机电中心及行业智慧感知/高端装备/三维纺织等机制查询未定位新正式指南。未知费用/当期任务交人工，不重复失败；相关学院与旧年度机制仍可接续。</v>
+      </c>
+      <c r="G1025" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1025" t="str" s="3">
+        <v>https://www.wtu.edu.cn/kxyj/kypt.htm
+https://kyc.wtu.edu.cn/kypt/sbjkypt.htm
+https://me.wtu.edu.cn/kxyj/kyjg.htm</v>
+      </c>
+      <c r="I1025" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1026" ht="52.5" customHeight="1">
+      <c r="A1026" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1026" t="str" s="3">
+        <v>武汉纺织大学计算机与人工智能学院</v>
+      </c>
+      <c r="C1026" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1026" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1026" t="str" s="3">
+        <v>2024纺织服装智能化N089全文明确机器人视觉语义分割检测/布料柔性对象操纵/人体3D；2026服装信息化N085全文实际可穿戴生物传感/运动睡眠监测，截止10-15在窗18首页。两个不同工程中心、年度不可因同联系邮箱合并。两申请DOC验证码。</v>
+      </c>
+      <c r="F1026" t="str" s="3">
+        <v>经费2024修订办法随立项发尚缺，外拨/报销费用及成果数量/第一单位未知；2026地址邮编与页脚不同，待表核。N085不将服装推荐和AIGC变机器人任务。</v>
+      </c>
+      <c r="G1026" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1026" t="str" s="3">
+        <v>https://csai.wtu.edu.cn/info/1063/7067.htm
+https://csai.wtu.edu.cn/info/1063/19597.htm</v>
+      </c>
+      <c r="I1026" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1027" ht="52.5" customHeight="1">
+      <c r="A1027" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1027" t="str" s="3">
+        <v>武汉纺织大学全国及省材料/生物质平台</v>
+      </c>
+      <c r="C1027" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1027" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1027" t="str" s="3">
+        <v>2026全国纺织材料N088全文校外重点6—10万一般2—4万，100万重大/经纬未来限本校，期限2027—28不当2027申报；前50/后50外拨。省纺织材料N0901—3万/1SCI第一或通讯本室1或2机构+武汉共同，截止10-07；生物质N091重点5一般2青年1，直接外拨。三室广义材料/装备/可穿戴方向缺机器人或装备具体任务，均待核已截止，不因材料名剔除也不凭智能收相关。</v>
+      </c>
+      <c r="F1027" t="str" s="3">
+        <v>三室申请附件首验证码/超时人工；需具体任务联系及IP/费用细则，论文署名/阈值逐室分别保留，不互套。</v>
+      </c>
+      <c r="G1027" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1027" t="str" s="3">
+        <v>https://fzcljs.wtu.edu.cn/info/1017/9306.htm
+https://mse.wtu.edu.cn/info/1021/16089.htm
+https://te.wtu.edu.cn/info/1052/24351.htm</v>
+      </c>
+      <c r="I1027" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1028" ht="52.5" customHeight="1">
+      <c r="A1028" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1028" t="str" s="3">
+        <v>闽江学院（现闽江大学）</v>
+      </c>
+      <c r="C1028" t="str" s="3">
+        <v>福建·福州</v>
+      </c>
+      <c r="D1028" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1028" t="str" s="3">
+        <v>同站基金通知列表第1页14/总54页4，2021—2026公告；M088信息处理智能控制2026已存在复用；工业机器人中心2022独立N087全文1万拟2，RAR首不支持。2025/24信息处理原通知标题仅机制发现，不称已深核；2026/27工业robot机制词查询未定位新指南。</v>
+      </c>
+      <c r="F1028" t="str" s="3">
+        <v>第2—4页未读（多旧机制），全校平台目录与其他院级未齐；2022RAR具体任务和资格周期截止/成果外拨交人工，不把2026M088套中心。</v>
+      </c>
+      <c r="G1028" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1028" t="str" s="3">
+        <v>https://www.mju.edu.cn/imlab/2194/list.htm
+https://www.mju.edu.cn/imlab/2022/0408/c2194a131707/page.htm</v>
+      </c>
+      <c r="I1028" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1029" ht="52.5" customHeight="1">
+      <c r="A1029" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1029" t="str" s="3">
+        <v>湖南工业大学/湖南理工/太原科技/安徽工程/湖北文理/湖南工程</v>
+      </c>
+      <c r="C1029" t="str" s="3">
+        <v>湖南/山西/安徽/湖北</v>
+      </c>
+      <c r="D1029" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1029" t="str" s="3">
+        <v>正确hut.edu.cn湖南工业、hnist.edu.cn湖南理工等分别2026或机器人开放基金发现词查询，未定位可直接核的新正式机器人公告；安徽到账列表、教师论文项目非申请公告。</v>
+      </c>
+      <c r="F1029" t="str" s="3">
+        <v>只完成列明查询，官方完整目录尚未取得；不得写六机构完成或因无命中称无基金。</v>
+      </c>
+      <c r="G1029" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1029" t="str" s="3"/>
+      <c r="I1029" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1030" ht="52.5" customHeight="1">
+      <c r="A1030" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1030" t="str" s="3">
+        <v>湖北工业大学</v>
+      </c>
+      <c r="C1030" t="str" s="3">
+        <v>湖北·武汉</v>
+      </c>
+      <c r="D1030" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1030" t="str" s="3">
+        <v>在已取国部7/省55目录基础，农机/包装/无损/算力之外本批逐名补制造工业数智、桥梁监控装备、水环境污染检测装备国家中心、电网智能控制装备机制；太阳能2026发现指南建议征集，7-20建议截止非开放课题受理。已有项目和E类复用不重计。</v>
+      </c>
+      <c r="F1030" t="str" s="3">
+        <v>这些平台2026/27实际正式受理指南仍未齐；能源/环保普通行业任务不凭装备标题入，后续机制与院目录还需查。</v>
+      </c>
+      <c r="G1030" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1030" t="str" s="3">
+        <v>https://kjcy.hbut.edu.cn/kyjd/sjpt.htm
+https://sees.hbut.edu.cn/info/1021/2192.htm</v>
+      </c>
+      <c r="I1030" t="str" s="3">
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
@@ -54800,23 +56363,63 @@
         <v>官方公告</v>
       </c>
     </row>
-    <row r="123" ht="96" customHeight="1">
+    <row r="123" ht="102" customHeight="1">
       <c r="A123" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B123" t="n" s="13">
+        <v>46295</v>
+      </c>
+      <c r="C123" t="str" s="14">
+        <v>武汉纺织大学·智能微纳医学检验装备及关键技术湖北省工程研究中心/湖北省功能纤维加工及检测工程技术研究中心</v>
+      </c>
+      <c r="D123" t="str" s="15">
+        <v>医学影像大模型设计及智能分析；重大疾病智能穿戴检测与健康管理；肿瘤检测先进理论技术、智能纤维制造应用和其他检测；以实际检验装备/影像/穿戴任务收录，不虚构机器人应用。</v>
+      </c>
+      <c r="E123" t="str" s="15">
+        <v>正式官方缓存完整正文未载资助金额。</v>
+      </c>
+      <c r="F123" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="124" ht="96" customHeight="1">
+      <c r="A124" t="str" s="18">
+        <v>已截止</v>
+      </c>
+      <c r="B124" t="n" s="13">
+        <v>45550</v>
+      </c>
+      <c r="C124" t="str" s="14">
+        <v>武汉纺织大学·纺织服装智能化湖北省工程研究中心</v>
+      </c>
+      <c r="D124" t="str" s="15">
+        <v>机器人视觉下语义分割、目标检测识别；机器人对布料服装柔性对象操纵；三维人体建模测量检测姿态估计；另含服装大数据跨模态/知识图谱/趋势推荐生成等原行业任务。</v>
+      </c>
+      <c r="E124" t="str" s="15">
+        <v>1—2万元/项，拟4—5项。</v>
+      </c>
+      <c r="F124" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+    </row>
+    <row r="125" ht="96" customHeight="1">
+      <c r="A125" t="str" s="18">
         <v>已截止·管理细则待核</v>
       </c>
-      <c r="B123" t="n" s="13">
+      <c r="B125" t="n" s="13">
         <v>46188</v>
       </c>
-      <c r="C123" t="str" s="14">
+      <c r="C125" t="str" s="14">
         <v>北京航天控制仪器研究所等联合群体·智能多源自主导航国家卓越群体2026开放基金</v>
       </c>
-      <c r="D123" t="str" s="15">
+      <c r="D125" t="str" s="15">
         <v>复杂交通环境无人车多源导航智能故障诊断；VLA多源自主导航可重构性；退化环境无人系统导航自主重构；多源信息导航决策与运动预测</v>
       </c>
-      <c r="E123" t="str" s="15">
+      <c r="E125" t="str" s="15">
         <v>官方高校转载明确｜10万元/项</v>
       </c>
-      <c r="F123" t="str" s="16">
+      <c r="F125" t="str" s="16">
         <v>公告</v>
       </c>
     </row>
@@ -55012,8 +56615,8 @@
     <hyperlink ref="F101" ns1:id="R53db146b46f44f15"/>
     <hyperlink ref="C102" location="'02项目完整详情'!A44"/>
     <hyperlink ref="F102" ns1:id="R188b27dcb5574282"/>
-    <hyperlink ref="F123" ns1:id="rIdMergeR011"/>
-    <hyperlink ref="C123" location="'02项目完整详情'!A148"/>
+    <hyperlink ref="F125" ns1:id="rIdMergeR011"/>
+    <hyperlink ref="C125" location="'02项目完整详情'!A148"/>
     <hyperlink ref="C103" location="'02项目完整详情'!A167" display="项目完整详情"/>
     <hyperlink ref="F103" ns1:id="rIdSystematic98"/>
     <hyperlink ref="C104" location="'02项目完整详情'!A168" display="项目完整详情"/>
@@ -55066,6 +56669,10 @@
     <hyperlink ref="F121" ns1:id="rIdResume122"/>
     <hyperlink ref="C122" location="'02项目完整详情'!A230" display="项目完整详情"/>
     <hyperlink ref="F122" ns1:id="rIdResume123"/>
+    <hyperlink ref="C123" location="'02项目完整详情'!A233" display="项目完整详情"/>
+    <hyperlink ref="F123" ns1:id="rIdResume124"/>
+    <hyperlink ref="C124" location="'02项目完整详情'!A238" display="项目完整详情"/>
+    <hyperlink ref="F124" ns1:id="rIdResume125"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -57368,109 +58975,109 @@
     </row>
     <row r="81" ht="132" customHeight="1">
       <c r="A81" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B81" t="str" s="13">
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B81" t="n" s="13">
+        <v>45971</v>
+      </c>
+      <c r="C81" t="str" s="14">
+        <v>武汉纺织大学·湖北省数字化纺织装备重点实验室</v>
+      </c>
+      <c r="D81" t="str" s="15">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="E81" t="str" s="15">
         <v>未取得</v>
-      </c>
-      <c r="C81" t="str" s="14">
-        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
-      </c>
-      <c r="D81" t="str" s="15">
-        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
-      </c>
-      <c r="E81" t="str" s="15">
-        <v>未取得2020金额。</v>
       </c>
       <c r="F81" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G81" t="str" s="3">
-        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
+        <v>下载指南/表补实际机器人/装备任务及金额资格合作外拨周期成果IP；网页发布2025-10-27而落款2024-10-19冲突，不擅自改成2024项目。</v>
       </c>
       <c r="H81" t="str" s="3">
-        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
+        <v>陈振15072325406/027-59367842；sfzb@wtu.edu.cn。</v>
       </c>
     </row>
     <row r="82" ht="132" customHeight="1">
       <c r="A82" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B82" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B82" t="n" s="13">
+        <v>46295</v>
       </c>
       <c r="C82" t="str" s="14">
-        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
+        <v>武汉纺织大学·纺织新材料与先进加工全国重点实验室</v>
       </c>
       <c r="D82" t="str" s="15">
-        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
+        <v>资助范围含纺织材料跨尺度成型方法与智能装备、柔性可穿戴智能化/先进制造，但未展开装备感知控制等任务；当前机器人联系证据不足待细化，不能只凭智能装备收为确定相关。其余多功能材料/医学材料/纤维/印染原样保留。</v>
       </c>
       <c r="E82" t="str" s="15">
-        <v>未取得当年金额。</v>
+        <v>校外可申报类别：重点6—10万元、一般2—4万元；重大100万元与经纬未来2—4万元明确面向全校，不当本人类别。</v>
       </c>
       <c r="F82" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G82" t="str" s="3">
-        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
+        <v>申请/汇总验证码人工；补实际机器人/可穿戴装备任务、IP、费用报销及合同。不把重大100万放校外金额；2027—2028是执行周期非2027申报。</v>
       </c>
       <c r="H82" t="str" s="3">
-        <v>年度联系人未取得。</v>
+        <v>李老师027-59367824；fzxcljgjs@wtu.edu.cn；阳光校区建全科学中心217室430200。</v>
       </c>
     </row>
     <row r="83" ht="132" customHeight="1">
       <c r="A83" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B83" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B83" t="n" s="13">
+        <v>46302</v>
       </c>
       <c r="C83" t="str" s="14">
-        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
+        <v>武汉纺织大学·纺织新材料及其应用研究湖北省重点实验室</v>
       </c>
       <c r="D83" t="str" s="15">
-        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
+        <v>5方向为功能高分子/纤维、无机复合材料、纤维可穿戴供能器件、柔性智能材料与传感器件设计、加工极端服役；具体机器人感知/设备集成任务未展开，传感器件联系待原表或方向任务核，不只凭智能保留。</v>
       </c>
       <c r="E83" t="str" s="15">
-        <v>未取得当年金额/类型。</v>
+        <v>1—3万元/项。</v>
       </c>
       <c r="F83" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G83" t="str" s="3">
-        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
+        <v>原DOC首超时人工；先补柔性传感具体装备/感知联系，再补IP外拨费用及签章细节。公告发布9-16/落款9-14均保留；2027是执行周期。</v>
       </c>
       <c r="H83" t="str" s="3">
-        <v>未取得当年项目联系人。</v>
+        <v>陈老师18030816728；lpchen@wtu.edu.cn；阳光大道1号材料学院430200。</v>
       </c>
     </row>
     <row r="84" ht="132" customHeight="1">
       <c r="A84" t="str" s="20">
-        <v>线索待核·历史公告</v>
-      </c>
-      <c r="B84" t="str" s="13">
-        <v>未取得</v>
+        <v>线索待核·已截止</v>
+      </c>
+      <c r="B84" t="n" s="13">
+        <v>46295</v>
       </c>
       <c r="C84" t="str" s="14">
-        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
+        <v>武汉纺织大学·生物质纤维与生态染整湖北省重点实验室</v>
       </c>
       <c r="D84" t="str" s="15">
-        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
+        <v>年度广义范围纤维表界面/生物质生态染整、跨尺度成型智能装备、柔性可穿戴/先进制造等，未细化机器人或相关装备具体感知控制任务，不能凭平台名称直接剔除或凭智能装备认相关。</v>
       </c>
       <c r="E84" t="str" s="15">
-        <v>未取得</v>
+        <v>重点5万元、一般2万元、青年1万元。青年类别额外资格未载。</v>
       </c>
       <c r="F84" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G84" t="str" s="3">
-        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+        <v>申请汇总验证码人工，先补具体装备/可穿戴任务，再补IP、费用办法及青年额外限制；不套全国材料室IF15指标。</v>
       </c>
       <c r="H84" t="str" s="3">
-        <v>年度基金联系人未取得。</v>
-      </c>
-    </row>
-    <row r="85" ht="147" customHeight="1">
+        <v>胡老师027-59367695；fzgc@wtu.edu.cn；阳光校区430200。</v>
+      </c>
+    </row>
+    <row r="85" ht="132" customHeight="1">
       <c r="A85" t="str" s="20">
         <v>线索待核·历史公告</v>
       </c>
@@ -57478,22 +59085,22 @@
         <v>未取得</v>
       </c>
       <c r="C85" t="str" s="14">
-        <v>安徽建筑大学·安徽省智能地下探测重点实验室</v>
+        <v>广东工业大学·智能检测与制造物联教育部重点实验室</v>
       </c>
       <c r="D85" t="str" s="15">
-        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+        <v>2020具体任务未取得，不据检测/物联/智能标题认定机器人。</v>
       </c>
       <c r="E85" t="str" s="15">
-        <v>金额未取得（正文页尾及附件未取得）。</v>
+        <v>未取得2020金额。</v>
       </c>
       <c r="F85" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G85" t="str" s="3">
-        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+        <v>2020完整公告及附件首不可访问，人工保存；不能套广东省智能决策协同2024 R004，也不是已取得2026基金。</v>
       </c>
       <c r="H85" t="str" s="3">
-        <v>本批联系人未取得。</v>
+        <v>基金联系人未取得；学院公共联系方式不是确认基金联系。</v>
       </c>
     </row>
     <row r="86" ht="132" customHeight="1">
@@ -57504,19 +59111,19 @@
         <v>未取得</v>
       </c>
       <c r="C86" t="str" s="14">
-        <v>山东交通学院·山东省智能建造装备关键技术与系统重点实验室</v>
+        <v>重庆交通大学·绿色物流智能技术重庆市重点实验室</v>
       </c>
       <c r="D86" t="str" s="15">
-        <v>年度具体任务未取得，不据智能名称认定机器人相关。</v>
+        <v>年度具体任务未取得；不能由特种加工/物流智能平台标题推定机器人相关。</v>
       </c>
       <c r="E86" t="str" s="15">
-        <v>未取得</v>
+        <v>未取得当年金额。</v>
       </c>
       <c r="F86" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G86" t="str" s="3">
-        <v>下载完整通知PDF，确认2025年度实际机器人/装备任务及截止、外部资格、金额、合作、外拨报销、周期成果IP提交；目录2025-12已立项，不能当当前受理。</v>
+        <v>首次超时，人工保存完整年度正文及全部附件，补实际任务及逐字段条款。N063与2023旧智能物流是否重组改名缺依据，不合并或照搬2023；N062加工任务须实际装备控制/感知证据。</v>
       </c>
       <c r="H86" t="str" s="3">
         <v>年度联系人未取得。</v>
@@ -57524,54 +59131,236 @@
     </row>
     <row r="87" ht="132" customHeight="1">
       <c r="A87" t="str" s="20">
-        <v>线索待核·公告未取得</v>
+        <v>线索待核·历史公告</v>
       </c>
       <c r="B87" t="str" s="13">
         <v>未取得</v>
       </c>
       <c r="C87" t="str" s="14">
-        <v>中国地震局工程力学研究所·基本科研业务费专项实验室开放基金项目</v>
+        <v>宿迁学院·江苏省智能制造装备关键技术工程研究中心</v>
       </c>
       <c r="D87" t="str" s="15">
-        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+        <v>只取得平台简介涉及高端装备、机器人、控制和传感系统；2025年度具体任务未取得，不能由简介判断本批确定相关。</v>
       </c>
       <c r="E87" t="str" s="15">
-        <v>未取得</v>
+        <v>未取得当年金额/类型。</v>
       </c>
       <c r="F87" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G87" t="str" s="3">
-        <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
+        <v>官网正文首次截断、续读首超时；须保存2025公告完整正文及全部附件，补具体任务与截止金额条款。不是已确认当前受理，也不把平台简介机器人当任务证据。</v>
       </c>
       <c r="H87" t="str" s="3">
-        <v>本批联系人未取得。</v>
+        <v>未取得当年项目联系人。</v>
       </c>
     </row>
     <row r="88" ht="132" customHeight="1">
       <c r="A88" t="str" s="20">
-        <v>线索待核·历史已评审</v>
+        <v>线索待核·历史公告</v>
       </c>
       <c r="B88" t="str" s="13">
         <v>未取得</v>
       </c>
       <c r="C88" t="str" s="14">
-        <v>湖北汽车工业学院（联合中国联通十堰市分公司）·空地群智协同技术与应用十堰市重点实验室</v>
+        <v>福建农林大学·智慧农林福建省高校重点实验室</v>
       </c>
       <c r="D88" t="str" s="15">
-        <v>本批公示明确拟资助无人机山区高速公路二次事故识别预警；平台简介群智感知、互联协作、规划控制，只作背景，年度完整任务待原指南。</v>
+        <v>未取得2019具体任务；不据智慧农林名称或2026教学农场/机器人竞赛认定本批相关。</v>
       </c>
       <c r="E88" t="str" s="15">
-        <v>本批重点1万元/项、一般0.5万元/项；拟4重点12一般，不从个别PI项目经费推范围。</v>
+        <v>未取得</v>
       </c>
       <c r="F88" t="str" s="16">
         <v>官方公告</v>
       </c>
       <c r="G88" t="str" s="3">
+        <v>完整2019正文与附件首次超时，交人工；补年度任务及全部条款，不能套农林生物安全2025或竞赛/夏令营。</v>
+      </c>
+      <c r="H88" t="str" s="3">
+        <v>年度基金联系人未取得。</v>
+      </c>
+    </row>
+    <row r="89" ht="147" customHeight="1">
+      <c r="A89" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B89" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C89" t="str" s="14">
+        <v>安徽建筑大学·安徽省智能地下探测重点实验室</v>
+      </c>
+      <c r="D89" t="str" s="15">
+        <v>2023公开部分列深地精细探测/岩土力学/灾害预测/地热/大数据，深海探测装备研制、应用系统开发集成/数据解译及AI融合，行星有效载荷与任务/表面观测数据融合/就位探测。深海装备任务仍概括，缺机器人或装备感知规划控制的具体要求，暂待核，地学一般任务不凭智能保留。</v>
+      </c>
+      <c r="E89" t="str" s="15">
+        <v>金额未取得（正文页尾及附件未取得）。</v>
+      </c>
+      <c r="F89" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G89" t="str" s="3">
+        <v>页尾首次续读超时；人工保存完整2023公告及全部附件，补具体智能探测装备任务、金额、资格、周期、期限、费用外拨、IP和提交联系；主任基金外校资格未知，不代套其他实验室。</v>
+      </c>
+      <c r="H89" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+    </row>
+    <row r="90" ht="132" customHeight="1">
+      <c r="A90" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B90" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C90" t="str" s="14">
+        <v>山东交通学院·山东省智能建造装备关键技术与系统重点实验室</v>
+      </c>
+      <c r="D90" t="str" s="15">
+        <v>年度具体任务未取得，不据智能名称认定机器人相关。</v>
+      </c>
+      <c r="E90" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F90" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G90" t="str" s="3">
+        <v>下载完整通知PDF，确认2025年度实际机器人/装备任务及截止、外部资格、金额、合作、外拨报销、周期成果IP提交；目录2025-12已立项，不能当当前受理。</v>
+      </c>
+      <c r="H90" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="91" ht="132" customHeight="1">
+      <c r="A91" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B91" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C91" t="str" s="14">
+        <v>武汉纺织大学·先进纺纱织造及清洁生产国家地方联合工程实验室</v>
+      </c>
+      <c r="D91" t="str" s="15">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="E91" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F91" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G91" t="str" s="3">
+        <v>原页全文及附件人工保存，补具体机器人/装备任务和全部条款；未取得截止不能当当前受理。</v>
+      </c>
+      <c r="H91" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="92" ht="132" customHeight="1">
+      <c r="A92" t="str" s="20">
+        <v>线索待核·历史公告</v>
+      </c>
+      <c r="B92" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C92" t="str" s="14">
+        <v>闽江学院（现闽江大学）·工业机器人应用福建省高校工程研究中心</v>
+      </c>
+      <c r="D92" t="str" s="15">
+        <v>通知明确工业机器人基础技术创新，但年度具体任务只在RAR指南，待核；不借2026信息处理室套本中心任务。</v>
+      </c>
+      <c r="E92" t="str" s="15">
+        <v>1万元/项，拟2项。</v>
+      </c>
+      <c r="F92" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G92" t="str" s="3">
+        <v>下载RAR解压申请指南/申请书/管理办法，补具体任务、截止、资格合作、周期、外拨成果IP提交；同站2022-06-10公示说明已评审，不能当当前。</v>
+      </c>
+      <c r="H92" t="str" s="3">
+        <v>年度联系人未取得。</v>
+      </c>
+    </row>
+    <row r="93" ht="132" customHeight="1">
+      <c r="A93" t="str" s="20">
+        <v>线索待核·公告未取得</v>
+      </c>
+      <c r="B93" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C93" t="str" s="14">
+        <v>中国地震局工程力学研究所·基本科研业务费专项实验室开放基金项目</v>
+      </c>
+      <c r="D93" t="str" s="15">
+        <v>2027具体平台及年度任务未取得，不据工程力学或开放基金标题认定机器人。</v>
+      </c>
+      <c r="E93" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F93" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G93" t="str" s="3">
+        <v>2027完整指南正文及全部附件首次不可访问，人工补平台名单/具体机器人任务及全部资金申报条款。</v>
+      </c>
+      <c r="H93" t="str" s="3">
+        <v>本批联系人未取得。</v>
+      </c>
+    </row>
+    <row r="94" ht="132" customHeight="1">
+      <c r="A94" t="str" s="20">
+        <v>线索待核·历史已评审</v>
+      </c>
+      <c r="B94" t="str" s="13">
+        <v>未取得</v>
+      </c>
+      <c r="C94" t="str" s="14">
+        <v>湖北汽车工业学院（联合中国联通十堰市分公司）·空地群智协同技术与应用十堰市重点实验室</v>
+      </c>
+      <c r="D94" t="str" s="15">
+        <v>本批公示明确拟资助无人机山区高速公路二次事故识别预警；平台简介群智感知、互联协作、规划控制，只作背景，年度完整任务待原指南。</v>
+      </c>
+      <c r="E94" t="str" s="15">
+        <v>本批重点1万元/项、一般0.5万元/项；拟4重点12一般，不从个别PI项目经费推范围。</v>
+      </c>
+      <c r="F94" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G94" t="str" s="3">
         <v>需原2025申报指南、拟资助清单和任务书，补申报截止（公示12-12至12-15非申请）、完整任务、资格合作、周期、费用外拨、成果IP提交；2026—2027年度未定位，不据此无基金。</v>
       </c>
-      <c r="H88" t="str" s="3">
+      <c r="H94" t="str" s="3">
         <v>公示陈西亮13437277037；平台简介陈宇峰13477971492，原申请邮箱未取。</v>
+      </c>
+    </row>
+    <row r="95" ht="132" customHeight="1">
+      <c r="A95" t="str" s="20">
+        <v>线索待核·截止未到</v>
+      </c>
+      <c r="B95" t="n" s="13">
+        <v>46310</v>
+      </c>
+      <c r="C95" t="str" s="14">
+        <v>武汉纺织大学·工业雷管智能装配湖北省工程研究中心</v>
+      </c>
+      <c r="D95" t="str" s="15">
+        <v>具体年度任务未取得；不凭实验室智能名称判断机器人相关。</v>
+      </c>
+      <c r="E95" t="str" s="15">
+        <v>未取得</v>
+      </c>
+      <c r="F95" t="str" s="16">
+        <v>官方公告</v>
+      </c>
+      <c r="G95" t="str" s="3">
+        <v>下载2026指南/申请，确认具体机器人装配/感知/控制任务、金额资格合作、费用外拨周期成果IP；不得以截止未到直接写可申请。通讯邮编430073而学院页脚430200冲突待核。</v>
+      </c>
+      <c r="H95" t="str" s="3">
+        <v>陈伟027-59367513；wchen@wtu.edu.cn；阳光校区10号楼516，公告邮编430073待核。</v>
       </c>
     </row>
   </sheetData>
@@ -57722,34 +59511,48 @@
     <hyperlink ref="F76" ns1:id="rIdResume75"/>
     <hyperlink ref="C75" location="'02项目完整详情'!A202" display="项目完整详情"/>
     <hyperlink ref="F75" ns1:id="rIdResume76"/>
-    <hyperlink ref="C83" location="'02项目完整详情'!A210" display="项目完整详情"/>
-    <hyperlink ref="F83" ns1:id="rIdResume77"/>
+    <hyperlink ref="C87" location="'02项目完整详情'!A210" display="项目完整详情"/>
+    <hyperlink ref="F87" ns1:id="rIdResume77"/>
     <hyperlink ref="C44" location="'02项目完整详情'!A211" display="项目完整详情"/>
     <hyperlink ref="F44" ns1:id="rIdResume78"/>
-    <hyperlink ref="C82" location="'02项目完整详情'!A212" display="项目完整详情"/>
-    <hyperlink ref="F82" ns1:id="rIdResume79"/>
+    <hyperlink ref="C86" location="'02项目完整详情'!A212" display="项目完整详情"/>
+    <hyperlink ref="F86" ns1:id="rIdResume79"/>
     <hyperlink ref="C77" location="'02项目完整详情'!A213" display="项目完整详情"/>
     <hyperlink ref="F77" ns1:id="rIdResume80"/>
-    <hyperlink ref="C81" location="'02项目完整详情'!A214" display="项目完整详情"/>
-    <hyperlink ref="F81" ns1:id="rIdResume81"/>
+    <hyperlink ref="C85" location="'02项目完整详情'!A214" display="项目完整详情"/>
+    <hyperlink ref="F85" ns1:id="rIdResume81"/>
     <hyperlink ref="C74" location="'02项目完整详情'!A215" display="项目完整详情"/>
     <hyperlink ref="F74" ns1:id="rIdResume82"/>
-    <hyperlink ref="C84" location="'02项目完整详情'!A217" display="项目完整详情"/>
-    <hyperlink ref="F84" ns1:id="rIdResume83"/>
-    <hyperlink ref="C87" location="'02项目完整详情'!A219" display="项目完整详情"/>
-    <hyperlink ref="F87" ns1:id="rIdResume84"/>
+    <hyperlink ref="C88" location="'02项目完整详情'!A217" display="项目完整详情"/>
+    <hyperlink ref="F88" ns1:id="rIdResume83"/>
+    <hyperlink ref="C93" location="'02项目完整详情'!A219" display="项目完整详情"/>
+    <hyperlink ref="F93" ns1:id="rIdResume84"/>
     <hyperlink ref="C78" location="'02项目完整详情'!A220" display="项目完整详情"/>
     <hyperlink ref="F78" ns1:id="rIdResume85"/>
-    <hyperlink ref="C85" location="'02项目完整详情'!A223" display="项目完整详情"/>
-    <hyperlink ref="F85" ns1:id="rIdResume86"/>
-    <hyperlink ref="C86" location="'02项目完整详情'!A224" display="项目完整详情"/>
-    <hyperlink ref="F86" ns1:id="rIdResume87"/>
+    <hyperlink ref="C89" location="'02项目完整详情'!A223" display="项目完整详情"/>
+    <hyperlink ref="F89" ns1:id="rIdResume86"/>
+    <hyperlink ref="C90" location="'02项目完整详情'!A224" display="项目完整详情"/>
+    <hyperlink ref="F90" ns1:id="rIdResume87"/>
     <hyperlink ref="C79" location="'02项目完整详情'!A225" display="项目完整详情"/>
     <hyperlink ref="F79" ns1:id="rIdResume88"/>
-    <hyperlink ref="C88" location="'02项目完整详情'!A228" display="项目完整详情"/>
-    <hyperlink ref="F88" ns1:id="rIdResume89"/>
+    <hyperlink ref="C94" location="'02项目完整详情'!A228" display="项目完整详情"/>
+    <hyperlink ref="F94" ns1:id="rIdResume89"/>
     <hyperlink ref="C80" location="'02项目完整详情'!A231" display="项目完整详情"/>
     <hyperlink ref="F80" ns1:id="rIdResume90"/>
+    <hyperlink ref="C81" location="'02项目完整详情'!A232" display="项目完整详情"/>
+    <hyperlink ref="F81" ns1:id="rIdResume91"/>
+    <hyperlink ref="C91" location="'02项目完整详情'!A235" display="项目完整详情"/>
+    <hyperlink ref="F91" ns1:id="rIdResume92"/>
+    <hyperlink ref="C92" location="'02项目完整详情'!A236" display="项目完整详情"/>
+    <hyperlink ref="F92" ns1:id="rIdResume93"/>
+    <hyperlink ref="C82" location="'02项目完整详情'!A237" display="项目完整详情"/>
+    <hyperlink ref="F82" ns1:id="rIdResume94"/>
+    <hyperlink ref="C83" location="'02项目完整详情'!A239" display="项目完整详情"/>
+    <hyperlink ref="F83" ns1:id="rIdResume95"/>
+    <hyperlink ref="C84" location="'02项目完整详情'!A240" display="项目完整详情"/>
+    <hyperlink ref="F84" ns1:id="rIdResume96"/>
+    <hyperlink ref="C95" location="'02项目完整详情'!A241" display="项目完整详情"/>
+    <hyperlink ref="F95" ns1:id="rIdResume97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -53884,6 +53884,427 @@
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
+    <row r="1031" ht="52.5" customHeight="1">
+      <c r="A1031" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1031" t="str" s="3">
+        <v>湖南理工/湖南工业/湖南工程/湖北文理官方科研目录发现</v>
+      </c>
+      <c r="C1031" t="str" s="3">
+        <v>湖南/湖北</v>
+      </c>
+      <c r="D1031" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1031" t="str" s="3">
+        <v>查询：湖南理工学院 科研平台 重点实验室 / 湖南工业大学 科研平台 重点实验室 机器人 / 湖南工程学院 重点实验室 科研平台 / 湖北文理学院 科研平台 机器人；线索：我校省级科研平台立项取得新突破-湖南工程学院；湖南工学院科技创新平台一览表(更新至2025年12月)-湖南工学院科技与校企合作处；平台与团队-湖南理工大学科研院；曾立新赴湖南理工学院调研省级科技创新平台建设情况-湖南省科学技术厅；湖南工程学院获批组建两个省级重点实验室-湖南省科学技术厅；科研平台一览表-自动化学院官方网站</v>
+      </c>
+      <c r="F1031" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1031" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1031" t="str" s="3">
+        <v>https://www.hnie.edu.cn/info/1042/9691.htm
+https://www.hnit.edu.cn/kjc/info/1190/4557.htm
+https://kjc.hnist.cn/ptytd.htm
+https://kjt.hunan.gov.cn/kjt/xxgk/gzdt/szdt/yuey/202108/t20210806_20287402.html
+https://kjt.hunan.gov.cn/kjt/xxgk/gzdt/szdt/xt/201808/t20180820_5075594.html
+https://soa.csu.edu.cn/info/1273/8316.htm</v>
+      </c>
+      <c r="I1031" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第477项</v>
+      </c>
+    </row>
+    <row r="1032" ht="52.5" customHeight="1">
+      <c r="A1032" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1032" t="str" s="3">
+        <v>太原科技/安徽工程/陕西理工/江西理工官方科研目录发现</v>
+      </c>
+      <c r="C1032" t="str" s="3">
+        <v>山西/安徽/陕西/江西</v>
+      </c>
+      <c r="D1032" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1032" t="str" s="3">
+        <v>查询：太原科技大学 科研平台 重点实验室 / 安徽工程大学 科研平台 机器人 开放基金 / 陕西理工大学 科研平台 机器人 开放基金 / 江西理工大学 机器人 开放基金 2026 2027；线索：科研平台-太原科技大学主站；关于“高端装备先进感知与智能控制教育部重点实验室”与“皖江高端装备制造协同创新中心”2025年度开放课题申请的通知；关于申报大数据分析与并行计算山西省重点实验室2025年自主研究课题的通知-计算机科学与技术学院；材料科学与工程（0805）学科简介-太原科技大学 研究生学院；“煤电清洁智能控制”教育部重点实验室；关于征集安徽省人形机器人重点实验室2026年度开放基金指南建议的通知 - 江淮实验室</v>
+      </c>
+      <c r="F1032" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1032" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1032" t="str" s="3">
+        <v>https://www.tyust.edu.cn/info/1033/11775.htm
+https://cee.ahpu.edu.cn/lapic/2025/0827/c7174a253666/page.htm
+https://cs.tyust.edu.cn/info/1106/4317.htm
+https://yjsxy.tyust.edu.cn/info/1214/3575.htm
+https://cicce.tyut.edu.cn/
+https://www.jhatc.cn/html/mobile/kexue/pingtaichanpin/2098331115939979266.html</v>
+      </c>
+      <c r="I1032" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第478项</v>
+      </c>
+    </row>
+    <row r="1033" ht="52.5" customHeight="1">
+      <c r="A1033" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1033" t="str" s="3">
+        <v>太原科技机器人/智能控制/视觉/测量平台2026—2027机制</v>
+      </c>
+      <c r="C1033" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D1033" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1033" t="str" s="3">
+        <v>查询：site:tyust.edu.cn "先进控制与工业智能" "开放" / site:tyust.edu.cn "重载装备作业智能化与机器人系统" "开放" / site:tyust.edu.cn "工业视觉" "开放基金" / site:tyust.edu.cn "精密测量与在线检测装备" "开放"；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F1033" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1033" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1033" t="str" s="3"/>
+      <c r="I1033" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第479项</v>
+      </c>
+    </row>
+    <row r="1034" ht="52.5" customHeight="1">
+      <c r="A1034" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1034" t="str" s="3">
+        <v>湖南工学院人机/装备感知平台2026—2027机制</v>
+      </c>
+      <c r="C1034" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D1034" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1034" t="str" s="3">
+        <v>查询：site:hnit.edu.cn "复杂人机交互系统" "开放基金" / site:hnit.edu.cn "人误预警" "开放基金" / site:hnit.edu.cn "电力装备智能计量与感知" "开放" / site:hnit.edu.cn "输变电装备智能传感" "开放"；线索：蒋建军-人因与安全工程研究院；湖南工学院科技创新平台一览表(更新至2025年12月)-湖南工学院科技与校企合作处；湖南工学院科技创新平台及创新能力建设项目批文-湖南工学院科技与校企合作处</v>
+      </c>
+      <c r="F1034" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1034" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1034" t="str" s="3">
+        <v>https://www.hnit.edu.cn/ryyaqgcyjy/info/1034/1064.htm
+https://www.hnit.edu.cn/kjc/info/1190/4557.htm
+https://www.hnit.edu.cn/kjc/info/1160/4581.htm</v>
+      </c>
+      <c r="I1034" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第480项</v>
+      </c>
+    </row>
+    <row r="1035" ht="52.5" customHeight="1">
+      <c r="A1035" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1035" t="str" s="3">
+        <v>太原科技目录其他装备平台机制2026—2027/历史</v>
+      </c>
+      <c r="C1035" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D1035" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1035" t="str" s="3">
+        <v>查询：site:tyust.edu.cn "智能物流装备" "开放" / site:tyust.edu.cn "重型装备智能化技术与系统" "开放" / site:tyust.edu.cn "装备数字化与故障预测" "开放" / site:tyust.edu.cn "运动健康智能装备" "开放"；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F1035" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1035" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1035" t="str" s="3"/>
+      <c r="I1035" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第481项</v>
+      </c>
+    </row>
+    <row r="1036" ht="52.5" customHeight="1">
+      <c r="A1036" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1036" t="str" s="3">
+        <v>湖南理工省高校/三维/健康感知机制2026—2027/历史</v>
+      </c>
+      <c r="C1036" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D1036" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1036" t="str" s="3">
+        <v>查询：site:hnist.cn "复杂工业物流系统智能控制与优化" "开放" / site:hnist.cn "复杂系统优化与控制" "开放基金" / site:hnist.cn "三维重建与智能应用" "开放" / site:hnist.cn "多模态健康传感与智能分析" "开放"；线索：涂兵-湖南理工学院图像处理与计算机视觉技术实验室；湖南理工大学研究生工作部；湖南理工大学研究生工作部；何伟-湖南理工学院图像处理与计算机视觉技术实验室；郭龙源-湖南理工学院图像处理与计算机视觉技术实验室</v>
+      </c>
+      <c r="F1036" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1036" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1036" t="str" s="3">
+        <v>https://ipcv.hnist.cn/info/1180/1057.htm
+https://xk.hnist.cn/search.jsp?currentnum=88&amp;newskeycode2=&amp;searchScope=0&amp;wbtreeid=1039
+https://xk.hnist.cn/search.jsp?currentnum=88&amp;newskeycode2=&amp;searchScope=0&amp;wbtreeid=1023
+https://ipcv.hnist.cn/info/1180/1058.htm
+https://ipcv.hnist.cn/info/1180/1055.htm</v>
+      </c>
+      <c r="I1036" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第482项</v>
+      </c>
+    </row>
+    <row r="1037" ht="52.5" customHeight="1">
+      <c r="A1037" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1037" t="str" s="3">
+        <v>湖南理工省高校嵌入/智能制造装备机制2026—2027/历史</v>
+      </c>
+      <c r="C1037" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D1037" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1037" t="str" s="3">
+        <v>查询：site:hnist.cn "复杂网络与嵌入式系统" "开放基金" / site:hnist.cn "工业智联网自主数据感知与处理" "开放" / site:hnist.cn "电磁装备设计与制造" "开放基金" / site:hnist.cn "激光磨削复合智能制造" "开放基金"；线索：2020年度湖南理工学院激光磨削复合智能制造与服役性能优化中国机械工业重点实验室开放基金拟资助项目公示-机械工程学院</v>
+      </c>
+      <c r="F1037" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1037" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1037" t="str" s="3">
+        <v>https://jdx.hnist.cn/info/1211/3391.htm</v>
+      </c>
+      <c r="I1037" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第483项</v>
+      </c>
+    </row>
+    <row r="1038" ht="52.5" customHeight="1">
+      <c r="A1038" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1038" t="str" s="3">
+        <v>湖南理工/湖南工学院/太原科技基金机制独立交叉</v>
+      </c>
+      <c r="C1038" t="str" s="3">
+        <v>湖南/山西</v>
+      </c>
+      <c r="D1038" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1038" t="str" s="3">
+        <v>查询：site:hnist.cn "激光磨削复合智能制造" "申请" "开放" / site:hnist.cn "复杂工业物流系统" "开放课题" / site:hnit.edu.cn "复杂人机交互系统" "开放课题" / site:tyust.edu.cn "开放课题" "机器人"；线索：复杂人机交互系统人误智能预防湖南省重点实验室简介-湖南工学院科技与校企合作处；学科建设概况-湖南工学院研究生与学科建设处；蔡星娟-复杂系统与计算智能实验室；2020年度湖南理工学院激光磨削复合智能制造与服役性能优化中国机械工业重点实验室开放基金拟资助项目公示-机械工程学院</v>
+      </c>
+      <c r="F1038" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1038" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1038" t="str" s="3">
+        <v>https://www.hnit.edu.cn/kjc/info/1188/4148.htm
+https://www.hnit.edu.cn/xkjszx/index/xkjsgk.htm
+https://yjjg.tyust.edu.cn/info/1133/1231.htm
+https://jdx.hnist.cn/info/1211/3391.htm</v>
+      </c>
+      <c r="I1038" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第484项</v>
+      </c>
+    </row>
+    <row r="1039" ht="52.5" customHeight="1">
+      <c r="A1039" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1039" t="str" s="3">
+        <v>太原科技2026—2027逐平台定向核补</v>
+      </c>
+      <c r="C1039" t="str" s="3">
+        <v>山西</v>
+      </c>
+      <c r="D1039" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1039" t="str" s="3">
+        <v>查询：site:tyust.edu.cn "开放" "2026" "2027" 智能物流 装备 / site:tyust.edu.cn "开放基金" "2026" 控制 / site:tyust.edu.cn "开放课题" "2027" / site:tyust.edu.cn "开放基金" "2026" 视觉；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F1039" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1039" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1039" t="str" s="3"/>
+      <c r="I1039" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第485项</v>
+      </c>
+    </row>
+    <row r="1040" ht="52.5" customHeight="1">
+      <c r="A1040" t="str" s="3">
+        <v>2026-10-09湖南山西省属高校分层目录及逐名机制补查</v>
+      </c>
+      <c r="B1040" t="str" s="3">
+        <v>湖南理工/湖南工学院2026—2027逐平台核补</v>
+      </c>
+      <c r="C1040" t="str" s="3">
+        <v>湖南</v>
+      </c>
+      <c r="D1040" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1040" t="str" s="3">
+        <v>查询：site:hnist.cn "开放基金" "2026" / site:hnist.cn "开放课题" "2027" / site:hnit.edu.cn "开放基金" "2026" / site:hnit.edu.cn "开放课题" "2027"；线索：未定位新增正式入口</v>
+      </c>
+      <c r="F1040" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1040" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1040" t="str" s="3"/>
+      <c r="I1040" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第486项</v>
+      </c>
+    </row>
+    <row r="1041" ht="52.5" customHeight="1">
+      <c r="A1041" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1041" t="str" s="3">
+        <v>太原科技大学</v>
+      </c>
+      <c r="C1041" t="str" s="3">
+        <v>山西·太原</v>
+      </c>
+      <c r="D1041" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1041" t="str" s="3">
+        <v>2025-01-08官网科研平台完整34牌目，含国部4、省重点7、创新中心5、中试1、省工程8、教育厅2、1331协同3、人文3/马院1；不是34机器人室。机器人重载作业、先进控制工业智能、工业视觉、精密测量、智能物流、重型装备智能化、数字化故障预测、运动健康智能装备逐名开放机制查；2026/2027单独年度词交叉未定位新正式开放公告。</v>
+      </c>
+      <c r="F1041" t="str" s="3">
+        <v>全校现行重组增减、学院/市校级目录未齐；其余装备检测/液压等及年度尚可接续，不将教师承担其他基金/招聘当本校申报。</v>
+      </c>
+      <c r="G1041" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1041" t="str" s="3">
+        <v>https://www.tyust.edu.cn/info/1033/11775.htm</v>
+      </c>
+      <c r="I1041" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1042" ht="52.5" customHeight="1">
+      <c r="A1042" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1042" t="str" s="3">
+        <v>湖南理工学院（官网现署湖南理工大学）</v>
+      </c>
+      <c r="C1042" t="str" s="3">
+        <v>湖南·岳阳</v>
+      </c>
+      <c r="D1042" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1042" t="str" s="3">
+        <v>2025-09-05省部以上完整42牌目含大量人文、联盟/基地；2022-09-01市级完整9牌目（6市重点/1创新中心/2联盟），版本时点明确不相加51机器人室。正确现行官网hnist.cn科研院取得，前轮hnist.edu.cn查询不能当现行目录完整证据。省高校复杂系统优化控制/复杂网络嵌入、省物流控制/三维重建/多模态健康/工业数据/电磁/激光磨削8名字逐名机制及2026/27年词查。</v>
+      </c>
+      <c r="F1042" t="str" s="3">
+        <v>只发现2020激光磨削拟资助公示标题，原指南/年度具体机器人任务未取得，先机制线索不当当前项目；全校校级/其他学院和2026/27受理仍未齐。</v>
+      </c>
+      <c r="G1042" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1042" t="str" s="3">
+        <v>https://kjc.hnist.cn/ptytd.htm
+https://kjc.hnist.cn/info/1085/2690.htm
+https://kjc.hnist.cn/info/1086/2691.htm
+https://jdx.hnist.cn/info/1211/3391.htm</v>
+      </c>
+      <c r="I1042" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1043" ht="52.5" customHeight="1">
+      <c r="A1043" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1043" t="str" s="3">
+        <v>湖南工学院</v>
+      </c>
+      <c r="C1043" t="str" s="3">
+        <v>湖南·衡阳</v>
+      </c>
+      <c r="D1043" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1043" t="str" s="3">
+        <v>官网科技创新平台完整表名更新至2025-12，发布栏2025-03-26两时点原样保留；共63名称行含国级/共建/省/教育科学/市/校，校级9条部分清理或升级后停止建设，不因此抹除仍列省市上级平台。人误预防省重点/预警工程室、电力智能计量感知高校重点/输变电传感工程中心4名机制及2026/27词查询未定位新增指南。</v>
+      </c>
+      <c r="F1043" t="str" s="3">
+        <v>有拨款是平台建设资助，不等校外可申领基金；其余检测/泵/汽车平台及学院目录/年度仍需补查，不将完整目录标全机构查完。</v>
+      </c>
+      <c r="G1043" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1043" t="str" s="3">
+        <v>https://www.hnit.edu.cn/kjc/info/1190/4557.htm</v>
+      </c>
+      <c r="I1043" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1044" ht="52.5" customHeight="1">
+      <c r="A1044" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1044" t="str" s="3">
+        <v>安徽工程大学/江淮实验室</v>
+      </c>
+      <c r="C1044" t="str" s="3">
+        <v>安徽</v>
+      </c>
+      <c r="D1044" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1044" t="str" s="3">
+        <v>发现安徽工程2025高端装备MOE/皖江共同开放指南为既有M042复用不重复项目；江淮人形2026指南建议征集M064复用，不当正式受理。其余安徽工程科研目录仍缺，到账/教师项目不是申报。</v>
+      </c>
+      <c r="F1044" t="str" s="3">
+        <v>安徽工程省市/校级及机器人平台2026—2027原公告未齐；不因复用已知公告称全校完成。</v>
+      </c>
+      <c r="G1044" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1044" t="str" s="3">
+        <v>https://cee.ahpu.edu.cn/lapic/2025/0827/c7174a253666/page.htm
+https://www.jhatc.cn/html/mobile/kexue/pingtaichanpin/2098331115939979266.html</v>
+      </c>
+      <c r="I1044" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>

--- a/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
+++ b/全国机器人开放课题_个人申报台账_结构精简版_20261009.xlsx
@@ -54305,6 +54305,508 @@
         <v>resume_sources_20261009.json</v>
       </c>
     </row>
+    <row r="1045" ht="52.5" customHeight="1">
+      <c r="A1045" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1045" t="str" s="3">
+        <v>广东广西海南福建省高校机器人2026—2027交叉</v>
+      </c>
+      <c r="C1045" t="str" s="3">
+        <v>广东/广西/海南/福建</v>
+      </c>
+      <c r="D1045" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1045" t="str" s="3">
+        <v>查询："省高校重点实验室" "开放" "机器人" "2026" / "省教育厅" "开放基金" "机器人" "2027" / "海南" "开放课题" "2026" "机器人" / "广东" "开放课题" "2027" 机器人；线索：开放课题申请结果的通知-采招网；人工智能与数字经济广东省实验室（深圳） 2026年开放课题基金申请指南；Search | 深圳市人工智能与机器人研究院；江苏省高校通用人工智能与大模型重点实验室开放课题申报指南；珠海企业服务平台(政企通)通知公告；2026年度国家卫生健康委食品安全风险评估与标准研制特色实验室（营养素与特殊膳食食品）开放课题申请指南_检测_研究_超重</v>
+      </c>
+      <c r="F1045" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1045" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1045" t="str" s="3">
+        <v>https://m.bidcenter.com.cn/news-4-436919463.html
+https://www.gml.ac.cn/xxgs/923.html
+https://airs.cuhk.edu.cn/search
+https://future.suda.edu.cn/e8/2a/c30836a714794/page.htm
+https://www.zhsme.org.cn/notices/getNoticesByNoticesId?noticesId=ec239efa-c5da-4192-b43e-af99f0a37228
+https://www.sohu.com/a/1002002958_121106875</v>
+      </c>
+      <c r="I1045" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第487项</v>
+      </c>
+    </row>
+    <row r="1046" ht="52.5" customHeight="1">
+      <c r="A1046" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1046" t="str" s="3">
+        <v>西北西南及东北省高校机器人2026—2027交叉</v>
+      </c>
+      <c r="C1046" t="str" s="3">
+        <v>西北/西南/东北</v>
+      </c>
+      <c r="D1046" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1046" t="str" s="3">
+        <v>查询："云南" "开放基金" "2026" 机器人 / "贵州" "开放课题" "2026" 机器人 / "吉林" "开放基金" "2027" 机器人 / "内蒙古" "开放课题" "2026" 机器人；线索：关于2026年度开放课题立项的通知-中国地质大学内蒙古研究院；贵州省山地智能农机全省重点实验室 2025年度开放课题立项公示；关于发布大规模储能技术教育部工程研究中心2026年度开放课题征集的通知-大规模储能技术教育部工程研究中心；关于内蒙古自治区高等学校磁学与磁性材料重点实验室开展2026年度开放课题申报的通知-包头师范学院；贵州省粮油作物优质高效增产全省重点实验室2026年度开放课题申报指南（一般项目）；关于申报2026年度赤水河中游流域生态系统贵州省野外科学观测研究站项目的公告</v>
+      </c>
+      <c r="F1046" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1046" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1046" t="str" s="3">
+        <v>https://imit.cug.edu.cn/info/1501/5741.htm
+https://st.gzu.edu.cn/2026/0112/c17883a264387/page.htm
+https://lest.imut.edu.cn/info/1115/6280.htm
+https://www.bttc.edu.cn/info/1011/20548.htm
+https://st.gzu.edu.cn/2026/0518/c17883a273474/page.htm
+https://www.moutai.com.cn/mtjt/2026-05/19/article_2026051915401741669.html</v>
+      </c>
+      <c r="I1046" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第488项</v>
+      </c>
+    </row>
+    <row r="1047" ht="52.5" customHeight="1">
+      <c r="A1047" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1047" t="str" s="3">
+        <v>香港理工大学内地研究院逐院外部基金2026—2027</v>
+      </c>
+      <c r="C1047" t="str" s="3">
+        <v>香港/南京/杭州/晋江/温州</v>
+      </c>
+      <c r="D1047" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1047" t="str" s="3">
+        <v>查询："香港理工大学" "南京" "开放课题" / "香港理工大学" "晋江" "开放基金" / "香港理工大学" "温州" "开放课题" / "香港理工大学" "杭州" "开放研究" "基金"；线索：南京大学固体微结构物理实验室第二十七批开放课题批准项目；南京大学固体微结构物理实验室第三十四批开放课题批准项目；地震动力学国家重点实验室·２０１０年度报告；先进环境装备与污染防治技术全国重点实验室2025年度开放课题立项通知----先进环境装备与污染防治技术全国重点实验室；Research &amp; Consultancy；南开大学眼科学研究院召开2023年度开放课题启动仪式暨学术研讨会</v>
+      </c>
+      <c r="F1047" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1047" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1047" t="str" s="3">
+        <v>https://vlssm.nju.edu.cn/98/a9/c22709a366761/page.htm
+https://vlssm.nju.edu.cn/15/05/c22709a529669/page.htm
+https://www.eqlab.ac.cn/upload/b66458e7-221f-4767-b42e-d9c645a398cd/2010.pdf
+https://sklaet.gig.ac.cn/kydt/qt/202509/t20250910_768300.html
+https://www.polyu.edu.hk/me/-/media/department/me/content/news-and-events/publications/annual-report-pdf/annual-report-2021-22-%281%29.pdf?hash=EA7C87B7D9CD3C35117316AB0EA89B75&amp;rev=3585efdcae9142499f0a6d36d3b439f8
+https://eye.nankai.edu.cn/2023/0625/c32731a515332/page.htm</v>
+      </c>
+      <c r="I1047" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第489项</v>
+      </c>
+    </row>
+    <row r="1048" ht="52.5" customHeight="1">
+      <c r="A1048" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1048" t="str" s="3">
+        <v>华南理工及西工大尚未查学院官方目录入口</v>
+      </c>
+      <c r="C1048" t="str" s="3">
+        <v>广东/陕西</v>
+      </c>
+      <c r="D1048" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1048" t="str" s="3">
+        <v>查询：site:www2.scut.edu.cn "自动化" "科研平台" / site:www2.scut.edu.cn "机械" "科研平台" / site:hanghai.nwpu.edu.cn "科研平台" / site:nwpu.edu.cn "无人系统" "开放课题" "2026"；线索：工程博士（按类别）研究生培养方案 |  |；从海院出发，点燃你人生的灯塔——航海学院举办研究生招生介绍会-航海学院；航海学院赴中国船舶集团第七一五研究所调研-航海学院；清华大学社会科学学院研究中心来航海学院调研-航海学院</v>
+      </c>
+      <c r="F1048" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1048" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1048" t="str" s="3">
+        <v>https://www2.scut.edu.cn/_upload/article/files/f3/03/9916b645489680ad4c9137a11fa9/7b21dd9d-ab6e-4ee2-8297-ccc50d923a47.pdf
+https://hanghai.nwpu.edu.cn/info/1878/8610.htm
+https://hanghai.nwpu.edu.cn/info/1546/14202.htm
+https://hanghai.nwpu.edu.cn/info/1598/9624.htm</v>
+      </c>
+      <c r="I1048" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第490项</v>
+      </c>
+    </row>
+    <row r="1049" ht="52.5" customHeight="1">
+      <c r="A1049" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1049" t="str" s="3">
+        <v>华南理工自动化机械学院目录入口</v>
+      </c>
+      <c r="C1049" t="str" s="3">
+        <v>珠三角</v>
+      </c>
+      <c r="D1049" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1049" t="str" s="3">
+        <v>查询：华南理工大学 自动化学院 科研平台 重点实验室 / 华南理工大学 机械 汽车 科研平台 重点实验室；线索：华南理工大学师生赴汽车车身先进设计制造国家重点实验室交流访问-整车先进设计制造技术全国重点实验室；华南理工大学广东省电动汽车研究重点实验室 - 中国汽车工程学会；我校机器人与焊接技术重点实验室举办机器人视觉讲座-科技处；科研平台-广东石油化工学院自动化学院</v>
+      </c>
+      <c r="F1049" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1049" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1049" t="str" s="3">
+        <v>https://dmvb.hnu.edu.cn/info/1009/1165.htm
+https://www.sae-china.org/omember/info.php?id=234
+https://kjc.guat.edu.cn/info/1115/1939.htm
+https://www.gdupt.edu.cn/zdh/info/1029/1774.htm</v>
+      </c>
+      <c r="I1049" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第491项</v>
+      </c>
+    </row>
+    <row r="1050" ht="52.5" customHeight="1">
+      <c r="A1050" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1050" t="str" s="3">
+        <v>西北工业大学航海与重庆大学机械医工目录入口</v>
+      </c>
+      <c r="C1050" t="str" s="3">
+        <v>西安/重庆</v>
+      </c>
+      <c r="D1050" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1050" t="str" s="3">
+        <v>查询：site:hanghai.nwpu.edu.cn "实验室" "重点" / 重庆大学 机械 研究平台 重点实验室 / 重庆大学 生物工程 科研平台 重点实验室；线索：平台概况-生物工程学院(测试版)；生物流变科学与技术教育部重点实验室主页；高端装备机械传动全国重点实验室（测试版）；高端装备机械传动全国重点实验室学术副主任遴选通知-重庆大学科学技术发展研究院；生物工程学院细胞生物学实验室；高速水洞实验室-航海学院</v>
+      </c>
+      <c r="F1050" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1050" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1050" t="str" s="3">
+        <v>https://bio.cqu.edu.cn/xygk/ptgk.htm
+https://biolab.cqu.edu.cn/
+https://slmt.cqu.edu.cn/
+https://kjc.cqu.edu.cn/info/1024/23829.htm
+https://songlab.cqu.edu.cn/
+https://hanghai.nwpu.edu.cn/info/1609/6537.htm</v>
+      </c>
+      <c r="I1050" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第492项</v>
+      </c>
+    </row>
+    <row r="1051" ht="52.5" customHeight="1">
+      <c r="A1051" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1051" t="str" s="3">
+        <v>广东石油化工学院4平台及人工智能研究院</v>
+      </c>
+      <c r="C1051" t="str" s="3">
+        <v>广东·茂名</v>
+      </c>
+      <c r="D1051" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1051" t="str" s="3">
+        <v>查询：site:gdupt.edu.cn "开放基金" "2026" / site:gdupt.edu.cn "开放课题" "2027" / "广东石油化工学院" "人工智能" "开放课题" / "广东石油化工学院" "智能感官" "开放基金"；线索：崔志华-复杂系统与计算智能实验室；广东省先进绿色润滑材料企业重点实验室关于2023年度开放基金结题验收通知-广油—瑞派设计创新学院；关于公布省部共建精密电子制造技术与装备国家重点实验室 2021年度开放课题立项结果的通知</v>
+      </c>
+      <c r="F1051" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1051" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1051" t="str" s="3">
+        <v>https://yjjg.tyust.edu.cn/info/1133/1521.htm
+https://site.gdupt.edu.cn/rpcx/info/1082/1271.htm
+https://nkszri.nankai.edu.cn/2023/0520/c22237a512842/page.htm</v>
+      </c>
+      <c r="I1051" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第493项</v>
+      </c>
+    </row>
+    <row r="1052" ht="52.5" customHeight="1">
+      <c r="A1052" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1052" t="str" s="3">
+        <v>西工航海相关机制与研究团队目录</v>
+      </c>
+      <c r="C1052" t="str" s="3">
+        <v>西安</v>
+      </c>
+      <c r="D1052" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1052" t="str" s="3">
+        <v>查询：site:hanghai.nwpu.edu.cn "开放基金" / site:hanghai.nwpu.edu.cn "开放课题" "2026" / site:hanghai.nwpu.edu.cn "开放课题" "2027" / site:hanghai.nwpu.edu.cn "科研团队"；线索：高速水洞实验室-航海学院；〖学术会议〗海洋声学信息感知工信部重点实验室学术会议暨船舶与海洋工程高峰论坛-航海学院；从海院出发，点燃你人生的灯塔——航海学院举办研究生招生介绍会-航海学院；航海学院2024年研究生招生政策宣讲会圆满举行-航海学院</v>
+      </c>
+      <c r="F1052" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1052" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1052" t="str" s="3">
+        <v>https://hanghai.nwpu.edu.cn/info/1609/6537.htm
+https://hanghai.nwpu.edu.cn/info/1548/9997.htm
+https://hanghai.nwpu.edu.cn/info/1546/8609.htm
+https://hanghai.nwpu.edu.cn/info/1546/16152.htm</v>
+      </c>
+      <c r="I1052" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第494项</v>
+      </c>
+    </row>
+    <row r="1053" ht="52.5" customHeight="1">
+      <c r="A1053" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1053" t="str" s="3">
+        <v>重庆大学生物力学数字健康机制</v>
+      </c>
+      <c r="C1053" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D1053" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1053" t="str" s="3">
+        <v>查询："重庆大学" "生物流变" "开放" "2026" / "重庆大学" "生物流变" "开放" "2027" / "重庆大学" "智能数字健康" "开放基金" / "重庆大学" "生物工程" "开放课题"；线索：生物流变科学与技术教育部重点实验室主页；2013年开放课题批准公告；生物流变科学与技术教育部重点实验室（重庆大学）与生物医学信息工程教育部重点实验室（西安交通大学）开展战略合作共建交流-重庆国家生物产业基地公共实验中心；教育部重点实验室召开2016年学术委员会第二次会议-生物流变科学与技术教育部重点实验室主页；〖自强卓越〗厦大2026进展(AI杰延/超精密智能加工:承担国家级大型科研平台建设筹备工作)-网大论坛 - Powered by Discuz!</v>
+      </c>
+      <c r="F1053" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1053" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1053" t="str" s="3">
+        <v>https://biolab.cqu.edu.cn/
+https://meplab.fudan.edu.cn/ed/d7/c24113a257495/page.htm
+https://publab.cqu.edu.cn/info/1013/1565.htm
+https://biolab.cqu.edu.cn/info/1010/1053.htm
+https://netbig.top/forum.php?extra=page%3D1%26filter%3Dauthor%26orderby%3Ddateline&amp;mobile=1&amp;mod=viewthread&amp;page=53&amp;tid=83571</v>
+      </c>
+      <c r="I1053" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第495项</v>
+      </c>
+    </row>
+    <row r="1054" ht="52.5" customHeight="1">
+      <c r="A1054" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1054" t="str" s="3">
+        <v>西工航海水下控制工信平台逐名年度机制</v>
+      </c>
+      <c r="C1054" t="str" s="3">
+        <v>西安</v>
+      </c>
+      <c r="D1054" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1054" t="str" s="3">
+        <v>查询："水下信息与控制" "开放基金" / "无人水下运载技术" "开放课题" / "海洋声学信息感知" "开放" "2026" / "海洋声学信息感知" "开放" "2027"；线索：声学与海洋信息全国重点实验室2026年开放课题申请通知--中国科学院声学研究所；科学网—Applied Sciences 西北工业大学赵瑞琴教授和申晓红教授主持特刊：水下通信网络 - MDPI开放科学的博文；关于组织博士研究生开题公开答辩报告会的通知-航海学院；中国科学院深海科学与工程研究所</v>
+      </c>
+      <c r="F1054" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1054" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1054" t="str" s="3">
+        <v>https://www.ioa.cas.cn/tzgg/202603/t20260313_8159297.html
+https://wap.sciencenet.cn/blog-3516770-1532449.html
+https://hanghai.nwpu.edu.cn/info/1548/26472.htm
+https://www.idsse.ac.cn/</v>
+      </c>
+      <c r="I1054" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第496项</v>
+      </c>
+    </row>
+    <row r="1055" ht="52.5" customHeight="1">
+      <c r="A1055" t="str" s="3">
+        <v>2026-10-09核心航海医工与全国分层机制接续</v>
+      </c>
+      <c r="B1055" t="str" s="3">
+        <v>重庆生物流变访问学者年度入口</v>
+      </c>
+      <c r="C1055" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D1055" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1055" t="str" s="3">
+        <v>查询：site:biolab.cqu.edu.cn "2024年度" "申请通知" / site:biolab.cqu.edu.cn "基金申请及管理条例" / site:biolab.cqu.edu.cn "2026" "基金" / site:biolab.cqu.edu.cn "2027" "基金"；线索：生物流变科学与技术教育部重点实验室主页</v>
+      </c>
+      <c r="F1055" t="str" s="3">
+        <v>2026—2027及长期机制查询结果需归属/年度对账；不能把外部课题获资助或教学开放当本实验室资金。</v>
+      </c>
+      <c r="G1055" t="str" s="3">
+        <v>仅所列查询完成；不代表机构查全。</v>
+      </c>
+      <c r="H1055" t="str" s="3">
+        <v>https://biolab.cqu.edu.cn/</v>
+      </c>
+      <c r="I1055" t="str" s="3">
+        <v>resume_sources_20261009.json搜索第497项</v>
+      </c>
+    </row>
+    <row r="1056" ht="52.5" customHeight="1">
+      <c r="A1056" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1056" t="str" s="3">
+        <v>西北工业大学航海学院</v>
+      </c>
+      <c r="C1056" t="str" s="3">
+        <v>陕西·西安</v>
+      </c>
+      <c r="D1056" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1056" t="str" s="3">
+        <v>科研团队目录正文全取且明确1/1页：11个2023团队（水下机器人、自主航行器、海洋声学信息感知、声学电子、声场感知隐身、海洋观测、海洋电磁、水下通信协同、水下推进超空泡、水下仿生流动、海洋智能感知网络）；另2条新闻不是新增团队。高速水洞2026-06-17正文为设施/教学/合作介绍，无申报公告。水下信息与控制、无人水下运载技术、海洋声学信息感知机制及2026/2027查询；历史论文标基金只作机制线索。</v>
+      </c>
+      <c r="F1056" t="str" s="3">
+        <v>团队目录不是全院科研平台名单；国防/工信平台年度申报、外部负责人资格及机器人具体任务仍未取得。声学所2026命中应按既有条目复用，不能归西工。</v>
+      </c>
+      <c r="G1056" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1056" t="str" s="3">
+        <v>https://hanghai.nwpu.edu.cn/kxyj/kytd.htm
+https://hanghai.nwpu.edu.cn/info/1609/6537.htm</v>
+      </c>
+      <c r="I1056" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1057" ht="52.5" customHeight="1">
+      <c r="A1057" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1057" t="str" s="3">
+        <v>广东石油化工学院自动化学院</v>
+      </c>
+      <c r="C1057" t="str" s="3">
+        <v>广东·茂名</v>
+      </c>
+      <c r="D1057" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1057" t="str" s="3">
+        <v>2026-03-12学院科研平台完整正文4条：复杂过程智能感知安全控制团队、智能感官感知团队、过程监控系统安全研究院、茂名石化自动化工程中心；另介绍人工智能自动化研究院（是否与列表研究院同一未确认）。明确机器人、视觉、自主无人方向，但未发布对外资金指南。2026/2027及研究院/智能感官开放机制查询已做；教师申请闽江等别校基金不算本校受理。</v>
+      </c>
+      <c r="F1057" t="str" s="3">
+        <v>全校及其他学院/省市平台名单未齐；学院机构是否更名合并及逐年度开放指南未取得。</v>
+      </c>
+      <c r="G1057" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1057" t="str" s="3">
+        <v>https://www.gdupt.edu.cn/zdh/info/1029/1774.htm</v>
+      </c>
+      <c r="I1057" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1058" ht="52.5" customHeight="1">
+      <c r="A1058" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1058" t="str" s="3">
+        <v>重庆大学机械与运载工程学院/生物工程学院</v>
+      </c>
+      <c r="C1058" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D1058" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1058" t="str" s="3">
+        <v>机械学科概况、生物平台概况首次均412，未重试。生物官方搜索缓存只概括14国部平台且仅列生物流变/生物力学组织修复111/血管植入3名，非14完整名册。机械缓存9市平台只列制造系统/表面精密加工，非9完整名册。</v>
+      </c>
+      <c r="F1058" t="str" s="3">
+        <v>两个完整目录名单、更新时间及逐机器人装备医工平台2026/2027公告待人工；机械传动既有项目不重记。</v>
+      </c>
+      <c r="G1058" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1058" t="str" s="3">
+        <v>https://mve.cqu.edu.cn/xkky/xkgk.htm
+https://bio.cqu.edu.cn/xygk/ptgk.htm</v>
+      </c>
+      <c r="I1058" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1059" ht="52.5" customHeight="1">
+      <c r="A1059" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1059" t="str" s="3">
+        <v>重庆大学生物流变科学与技术教育部重点实验室</v>
+      </c>
+      <c r="C1059" t="str" s="3">
+        <v>重庆</v>
+      </c>
+      <c r="D1059" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1059" t="str" s="3">
+        <v>2026/2027及访问学者机制搜索：官方主页缓存列2025-10-16、2024-10-08、2022-12-07访问学者基金申请通知和2016-05-02管理条例；主页首次412不重试。只公告标题，具体年度任务/外部资格/金额/访室/外拨/成果/IP均未取得。</v>
+      </c>
+      <c r="F1059" t="str" s="3">
+        <v>原2025/2024/2022通知及2016条例交人工；当前未见2026/2027正式公告不等确认不存在。不凭生物流变名称或访问学者标签新建相关项目。</v>
+      </c>
+      <c r="G1059" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1059" t="str" s="3">
+        <v>https://biolab.cqu.edu.cn/</v>
+      </c>
+      <c r="I1059" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
+    <row r="1060" ht="52.5" customHeight="1">
+      <c r="A1060" t="str" s="3">
+        <v>2026-10-09官方目录与机制分类</v>
+      </c>
+      <c r="B1060" t="str" s="3">
+        <v>香港理工大学内地研究院</v>
+      </c>
+      <c r="C1060" t="str" s="3">
+        <v>港澳/重点地区</v>
+      </c>
+      <c r="D1060" t="str" s="3">
+        <v>2026-10-09</v>
+      </c>
+      <c r="E1060" t="str" s="3">
+        <v>南京、晋江、温州、杭州研究院开放课题/基金组合查，只发现年报、交流、其他单位受理线索，未定位新增本院正式指南。原港校目录/资金核验复用。</v>
+      </c>
+      <c r="F1060" t="str" s="3">
+        <v>四院各自目录、年度对外任务及经费机制未查完整；无命中不当无基金、不当香港全域完成。</v>
+      </c>
+      <c r="G1060" t="str" s="3">
+        <v>仅所列完整目录/机制/年度已核，仍有明确未查范围。</v>
+      </c>
+      <c r="H1060" t="str" s="3"/>
+      <c r="I1060" t="str" s="3">
+        <v>resume_sources_20261009.json</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:I1"/>
